--- a/docs/collections/koten/metadata/data.xlsx
+++ b/docs/collections/koten/metadata/data.xlsx
@@ -32,7 +32,7 @@
     <t>著者</t>
   </si>
   <si>
-    <t>出版社</t>
+    <t>出版者</t>
   </si>
   <si>
     <t>出版年（西暦）</t>

--- a/docs/collections/koten/metadata/data.xlsx
+++ b/docs/collections/koten/metadata/data.xlsx
@@ -4256,7 +4256,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/eccd9915-68ba-9ff1-5ea7-e09091ea8864</t>
   </si>
   <si>
-    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/a1591b850505b55cc094709b168e3452574b1f46.jpg</t>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/202076306be178c3cbb734198ae7c2ed89e09471.jpg</t>
   </si>
   <si>
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1168698</t>
@@ -4286,7 +4286,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/dbfb9dad-0969-5742-4095-0704e4f30b93</t>
   </si>
   <si>
-    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/996a47e42fe5756731b8721f5404ad6d96011fa8.jpg</t>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/5eac4ea7af939335ddcf02715e1955bb6ae73d9c.jpg</t>
   </si>
   <si>
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1168699</t>
@@ -28205,7 +28205,7 @@
       <c r="AF161" t="s"/>
       <c r="AG161" t="s"/>
       <c r="AH161" t="n">
-        <v>59</v>
+        <v>46</v>
       </c>
     </row>
     <row r="162" spans="1:34">
@@ -28295,7 +28295,7 @@
       <c r="AF162" t="s"/>
       <c r="AG162" t="s"/>
       <c r="AH162" t="n">
-        <v>46</v>
+        <v>59</v>
       </c>
     </row>
     <row r="163" spans="1:34">

--- a/docs/collections/koten/metadata/data.xlsx
+++ b/docs/collections/koten/metadata/data.xlsx
@@ -761,42 +761,34 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>甲午日記 : 天保五年正月吉日</t>
+          <t>おちくほのさうし</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>A00:4613</t>
+          <t>A00:4083</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>コウゴ ニッキ : テンポウ ゴネン ショウガツ キチジツ</t>
+          <t>オチクボ ノ ソウシ</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>天保五年馬琴日記</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>滝沢 馬琴</t>
-        </is>
-      </c>
+          <t>おちくほ物語|御本</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>瀧澤馬琴 [自筆]</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>1834</t>
-        </is>
-      </c>
+          <t>[書写者不明]</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>天保5</t>
+          <t>[江戸前期]</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -812,7 +804,7 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>書名は扉による|巻末に「已上午年日記畢」とあり|裏表紙に「神田 瀧澤」とあり|内容: 天保五甲午年春正月-12月|墨抹, 胡粉による修正あり|巻末の識語末に「昭和五年十二月に至って脩覆を了せり」とあり|虫損あり (裏打ち補修あり)</t>
+          <t>書名は題簽による|毎半帖10行|漢字平仮名交じり文|奈良絵本|桜唐草文様緞子表紙, 松葉散しに山雲の金箔見返し, 金泥下絵鳥の子紙を使用|列帖装|二重箱入り</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -828,12 +820,12 @@
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/c91cb308-03bd-94f5-3c56-9d0fac9424d3.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/8aa19100-0937-5fd9-29f1-ba41ad8d1830.json</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>c91cb308-03bd-94f5-3c56-9d0fac9424d3</t>
+          <t>8aa19100-0937-5fd9-29f1-ba41ad8d1830</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -843,7 +835,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/c91cb308-03bd-94f5-3c56-9d0fac9424d3</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/8aa19100-0937-5fd9-29f1-ba41ad8d1830</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -853,12 +845,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/92f1a1f83433e8cf04243d82fb0811e6cf653db2.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/124815802d3a78d8f78dd4fbb98d24d55e5c3b34.jpg</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1182820</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1182819</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -881,7 +873,7 @@
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/c91cb308-03bd-94f5-3c56-9d0fac9424d3/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/8aa19100-0937-5fd9-29f1-ba41ad8d1830/manifest</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr"/>
@@ -889,40 +881,48 @@
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="n">
-        <v>172</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>おちくほのさうし</t>
+          <t>甲午日記 : 天保五年正月吉日</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>A00:4083</t>
+          <t>A00:4613</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>オチクボ ノ ソウシ</t>
+          <t>コウゴ ニッキ : テンポウ ゴネン ショウガツ キチジツ</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>おちくほ物語|御本</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
+          <t>天保五年馬琴日記</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>滝沢 馬琴</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>[書写者不明]</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
+          <t>瀧澤馬琴 [自筆]</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>1834</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>[江戸前期]</t>
+          <t>天保5</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -938,7 +938,7 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>書名は題簽による|毎半帖10行|漢字平仮名交じり文|奈良絵本|桜唐草文様緞子表紙, 松葉散しに山雲の金箔見返し, 金泥下絵鳥の子紙を使用|列帖装|二重箱入り</t>
+          <t>書名は扉による|巻末に「已上午年日記畢」とあり|裏表紙に「神田 瀧澤」とあり|内容: 天保五甲午年春正月-12月|墨抹, 胡粉による修正あり|巻末の識語末に「昭和五年十二月に至って脩覆を了せり」とあり|虫損あり (裏打ち補修あり)</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -954,12 +954,12 @@
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/8aa19100-0937-5fd9-29f1-ba41ad8d1830.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/c91cb308-03bd-94f5-3c56-9d0fac9424d3.json</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>8aa19100-0937-5fd9-29f1-ba41ad8d1830</t>
+          <t>c91cb308-03bd-94f5-3c56-9d0fac9424d3</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/8aa19100-0937-5fd9-29f1-ba41ad8d1830</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/c91cb308-03bd-94f5-3c56-9d0fac9424d3</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -979,12 +979,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/124815802d3a78d8f78dd4fbb98d24d55e5c3b34.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/92f1a1f83433e8cf04243d82fb0811e6cf653db2.jpg</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1182819</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1182820</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/8aa19100-0937-5fd9-29f1-ba41ad8d1830/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/c91cb308-03bd-94f5-3c56-9d0fac9424d3/manifest</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr"/>
@@ -1015,7 +1015,7 @@
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="n">
-        <v>33</v>
+        <v>172</v>
       </c>
     </row>
     <row r="5">

--- a/docs/collections/koten/metadata/data.xlsx
+++ b/docs/collections/koten/metadata/data.xlsx
@@ -761,21 +761,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>各種殘經 : 出鄯善縣土峪溝</t>
+          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [17]</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>A00:4033</t>
+          <t>A00:6257</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>カクシュ ザンキョウ : シュツ ゼンゼンケン トヨクコウ</t>
+          <t>レキダイ ザンケツ ニッキ</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>黒川 春村</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>[書写者不明]</t>
@@ -784,7 +788,7 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>[書写年不明]</t>
+          <t>[安政5 (1858)]</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -796,12 +800,12 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>写本残片|書名は題簽による|題簽に「出鄯善縣土峪溝 素文珍藏」とあり|識語に「為楊枝甘露滴入紙中展巻把玩但覺異香盈字 晉卿」, 「右二紙係亜利安字 晉卿」, 「右二紙係畏吾児字 晉卿」とあり|蔵書票に「殘經佛像梵字 十五段 鄯善」, 「梵字第一號」とあり|巻子本|箱入|印記: 「臣樹枏印」, 「晉卿」, 「王仲子」, 「王樹枏印」</t>
+          <t>写本|責任表示及び書写年は『日本古典籍総合目録データベース』による|内容: 6: 光明院御記, 後光嚴院御記, 後小松院宸記, 天聴集. 28: 参議藤定長卿記 : 稱山丞記. 37: 定高卿記, 晴御会部類記, 家光卿御記, 權中納言平範輔卿記. 38: 左大史小槻季継記, 後堀川安貞二年放生會(実基公記), 石清水八幡宮, 弁官拝賀次第. 39: 大外記師光記, 資季卿記, 荒凉記, 忠高卿記. 40: 冷泉公相公記, 勝延法眼記 : 東寺大行事, 後中記 : 小路中納言資頼卿記葉室. 41: 中光記, 師兼記, 陽龍記. 42: 大宮司長則記, 口筆 : 實經, 顕朝卿記, 鴨御幸記. 43: 寳治二年記, 深心院關白記, 藤公親記, 照念院関白兼平公記. 44: 頼親記, 亀山殿行幸記 : 雅言卿記, 兼基公記. 45: 大嘗會御禊節下次第, 建治三年丁丑日記 : 三善康有, 建治四年正月廿一日 : 徳大寺大相國公孝記, 冬定卿記, 左大史小槻兼文記|内容: 46: 經任卿記, 前豊前守藤憲説記, 實兼公記. 47: 継塵記抄出. 48: 管見記, 公衡公記, 大外記師顕記, 大外記中原師淳記. 49: 真光院禪助僧正記, 吉田内府卿記. 50: 定清記, 叅議雅俊卿記, 太政大臣(公守公)御上表雜事, 仙洞御灌頂日記, 正安二年八月十一日於仙洞被始行熾盛光法, 正安三年御譲位記. 51: 實躬卿記. 52: 公茂公記, 冬平公記, 隆長卿記. 53: 忠教公記, 官記, 正三位長基卿記, 北面秀長記, 大外記中原師右記. 54: 文保元年, 日野中納言資朝卿記, 洞院大納言公敏卿記. 55: 隆蔭卿記, 文保三年記, 尹大納言師賢卿記, 革命記, 立倚子記, 萬里小路中納言藤藤房卿記|内容: 56: 資名卿記, 公秀公記, 一條家記装束抄出, 頼定卿記. 63: 松亞記, 日野大納言時光卿記, 後八條内府實継公記. 74: 成恩寺関白記. 78: 山科家礼記. 82: 諒闇記 : 後成恩寺殿, 宗典僧正記, 綱光公記, 贈従二位宗賢卿記, 義政公記. 84: 長禄二年戊寅正月, 見聞雜記. 87: 言國卿記. 88: 長興宿祢記, 元長卿記, 兼顕卿記, 小槻晴冨記|28末の原奥書に「右山丞記依 仰挍合書冩/享和二年四月 日撿挍保己一」とあり|50「正安二年八月十一日於仙洞被始行熾盛光法」末の原奥書に「文化十五年春二月以南山法曼院藏夲書冩之 撿挍保己一」とあり|横刷毛目表紙を使用|朱点, 朱引, 朱墨筆書き入れあり|付箋あり|蔵書印主信濃須坂藩主堀直格の命によって編集された古記録|他の原本は関東大震災により焼失|極札に「桂壽」(6), 「尚信」(53)との極書, 「武清」(44, 53), 「永海」(51), 「了伴」(52), 「了甫」(74), 「定時」(84, 88)との極印あり|印記: 「花廼家文庫」, 「墨阪十一代主寫藏記」(堀直格(1806-1880)), 「東京大學法理文學部書庫所藏」, 「閲覧室用 FOR USE IN THE READING ROOM」|虫損あり</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>中国語</t>
+          <t>日本語</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -812,12 +816,12 @@
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/704d2c7a-4882-6fc8-60d1-94c1e2799bbd.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/37d790df-458b-48bf-6b67-3f4755f40f0f.json</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>704d2c7a-4882-6fc8-60d1-94c1e2799bbd</t>
+          <t>37d790df-458b-48bf-6b67-3f4755f40f0f</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -827,7 +831,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/704d2c7a-4882-6fc8-60d1-94c1e2799bbd</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/37d790df-458b-48bf-6b67-3f4755f40f0f</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -837,12 +841,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/4cc89d9a25687c69b3dc3791fd39ac740de2c4a0.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/dae05b3fca02a35e3363b381527ea7a899ca4f74.jpg</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296165</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296217</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -865,7 +869,7 @@
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/704d2c7a-4882-6fc8-60d1-94c1e2799bbd/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/37d790df-458b-48bf-6b67-3f4755f40f0f/manifest</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr"/>
@@ -873,29 +877,29 @@
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="n">
-        <v>22</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>和漢朗詠集 2巻 [1]</t>
+          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [18]</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>A00:4081</t>
+          <t>A00:6257</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ワカン ロウエイシュウ</t>
+          <t>レキダイ ザンケツ ニッキ</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>藤原 公任</t>
+          <t>黒川 春村</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -906,19 +910,19 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>[江戸前期]</t>
+          <t>[安政5 (1858)]</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>写本|書名は目首及び題簽による|外箱の書名: 御本|責任表示は『日本古典籍総合目録データベース』による|巻上: 春, 夏, 秋, 冬. 巻下: 雜|題簽による巻冊次表示: 上, 下|毎半帖8行|漢字平仮名交じり文|鳳凰菱繋ぎ文様緞子表紙, 松葉散しに山雲の金箔見返し, 金泥下絵鳥の子紙を使用|列帖装|二重箱入り</t>
+          <t>写本|責任表示及び書写年は『日本古典籍総合目録データベース』による|内容: 6: 光明院御記, 後光嚴院御記, 後小松院宸記, 天聴集. 28: 参議藤定長卿記 : 稱山丞記. 37: 定高卿記, 晴御会部類記, 家光卿御記, 權中納言平範輔卿記. 38: 左大史小槻季継記, 後堀川安貞二年放生會(実基公記), 石清水八幡宮, 弁官拝賀次第. 39: 大外記師光記, 資季卿記, 荒凉記, 忠高卿記. 40: 冷泉公相公記, 勝延法眼記 : 東寺大行事, 後中記 : 小路中納言資頼卿記葉室. 41: 中光記, 師兼記, 陽龍記. 42: 大宮司長則記, 口筆 : 實經, 顕朝卿記, 鴨御幸記. 43: 寳治二年記, 深心院關白記, 藤公親記, 照念院関白兼平公記. 44: 頼親記, 亀山殿行幸記 : 雅言卿記, 兼基公記. 45: 大嘗會御禊節下次第, 建治三年丁丑日記 : 三善康有, 建治四年正月廿一日 : 徳大寺大相國公孝記, 冬定卿記, 左大史小槻兼文記|内容: 46: 經任卿記, 前豊前守藤憲説記, 實兼公記. 47: 継塵記抄出. 48: 管見記, 公衡公記, 大外記師顕記, 大外記中原師淳記. 49: 真光院禪助僧正記, 吉田内府卿記. 50: 定清記, 叅議雅俊卿記, 太政大臣(公守公)御上表雜事, 仙洞御灌頂日記, 正安二年八月十一日於仙洞被始行熾盛光法, 正安三年御譲位記. 51: 實躬卿記. 52: 公茂公記, 冬平公記, 隆長卿記. 53: 忠教公記, 官記, 正三位長基卿記, 北面秀長記, 大外記中原師右記. 54: 文保元年, 日野中納言資朝卿記, 洞院大納言公敏卿記. 55: 隆蔭卿記, 文保三年記, 尹大納言師賢卿記, 革命記, 立倚子記, 萬里小路中納言藤藤房卿記|内容: 56: 資名卿記, 公秀公記, 一條家記装束抄出, 頼定卿記. 63: 松亞記, 日野大納言時光卿記, 後八條内府實継公記. 74: 成恩寺関白記. 78: 山科家礼記. 82: 諒闇記 : 後成恩寺殿, 宗典僧正記, 綱光公記, 贈従二位宗賢卿記, 義政公記. 84: 長禄二年戊寅正月, 見聞雜記. 87: 言國卿記. 88: 長興宿祢記, 元長卿記, 兼顕卿記, 小槻晴冨記|28末の原奥書に「右山丞記依 仰挍合書冩/享和二年四月 日撿挍保己一」とあり|50「正安二年八月十一日於仙洞被始行熾盛光法」末の原奥書に「文化十五年春二月以南山法曼院藏夲書冩之 撿挍保己一」とあり|横刷毛目表紙を使用|朱点, 朱引, 朱墨筆書き入れあり|付箋あり|蔵書印主信濃須坂藩主堀直格の命によって編集された古記録|他の原本は関東大震災により焼失|極札に「桂壽」(6), 「尚信」(53)との極書, 「武清」(44, 53), 「永海」(51), 「了伴」(52), 「了甫」(74), 「定時」(84, 88)との極印あり|印記: 「花廼家文庫」, 「墨阪十一代主寫藏記」(堀直格(1806-1880)), 「東京大學法理文學部書庫所藏」, 「閲覧室用 FOR USE IN THE READING ROOM」|虫損あり</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -934,12 +938,12 @@
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/ba79db36-23e8-1a8a-1ad9-a5809c1109be.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/c69854e0-18e9-71b3-a7b1-22422a16688b.json</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>ba79db36-23e8-1a8a-1ad9-a5809c1109be</t>
+          <t>c69854e0-18e9-71b3-a7b1-22422a16688b</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -949,7 +953,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/ba79db36-23e8-1a8a-1ad9-a5809c1109be</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/c69854e0-18e9-71b3-a7b1-22422a16688b</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -959,12 +963,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/0dbc6905fbe6d7441026c6ec7f4092a564cd7606.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/584cfd5ec1bb0f374ab03f25ca3600a8ec2e67bf.jpg</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296166</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296218</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -987,7 +991,7 @@
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/ba79db36-23e8-1a8a-1ad9-a5809c1109be/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/c69854e0-18e9-71b3-a7b1-22422a16688b/manifest</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr"/>
@@ -995,29 +999,29 @@
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="n">
-        <v>54</v>
+        <v>77</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>和漢朗詠集 2巻 [2]</t>
+          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [19]</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>A00:4081</t>
+          <t>A00:6257</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ワカン ロウエイシュウ</t>
+          <t>レキダイ ザンケツ ニッキ</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>藤原 公任</t>
+          <t>黒川 春村</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1028,19 +1032,19 @@
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>[江戸前期]</t>
+          <t>[安政5 (1858)]</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>写本|書名は目首及び題簽による|外箱の書名: 御本|責任表示は『日本古典籍総合目録データベース』による|巻上: 春, 夏, 秋, 冬. 巻下: 雜|題簽による巻冊次表示: 上, 下|毎半帖8行|漢字平仮名交じり文|鳳凰菱繋ぎ文様緞子表紙, 松葉散しに山雲の金箔見返し, 金泥下絵鳥の子紙を使用|列帖装|二重箱入り</t>
+          <t>写本|責任表示及び書写年は『日本古典籍総合目録データベース』による|内容: 6: 光明院御記, 後光嚴院御記, 後小松院宸記, 天聴集. 28: 参議藤定長卿記 : 稱山丞記. 37: 定高卿記, 晴御会部類記, 家光卿御記, 權中納言平範輔卿記. 38: 左大史小槻季継記, 後堀川安貞二年放生會(実基公記), 石清水八幡宮, 弁官拝賀次第. 39: 大外記師光記, 資季卿記, 荒凉記, 忠高卿記. 40: 冷泉公相公記, 勝延法眼記 : 東寺大行事, 後中記 : 小路中納言資頼卿記葉室. 41: 中光記, 師兼記, 陽龍記. 42: 大宮司長則記, 口筆 : 實經, 顕朝卿記, 鴨御幸記. 43: 寳治二年記, 深心院關白記, 藤公親記, 照念院関白兼平公記. 44: 頼親記, 亀山殿行幸記 : 雅言卿記, 兼基公記. 45: 大嘗會御禊節下次第, 建治三年丁丑日記 : 三善康有, 建治四年正月廿一日 : 徳大寺大相國公孝記, 冬定卿記, 左大史小槻兼文記|内容: 46: 經任卿記, 前豊前守藤憲説記, 實兼公記. 47: 継塵記抄出. 48: 管見記, 公衡公記, 大外記師顕記, 大外記中原師淳記. 49: 真光院禪助僧正記, 吉田内府卿記. 50: 定清記, 叅議雅俊卿記, 太政大臣(公守公)御上表雜事, 仙洞御灌頂日記, 正安二年八月十一日於仙洞被始行熾盛光法, 正安三年御譲位記. 51: 實躬卿記. 52: 公茂公記, 冬平公記, 隆長卿記. 53: 忠教公記, 官記, 正三位長基卿記, 北面秀長記, 大外記中原師右記. 54: 文保元年, 日野中納言資朝卿記, 洞院大納言公敏卿記. 55: 隆蔭卿記, 文保三年記, 尹大納言師賢卿記, 革命記, 立倚子記, 萬里小路中納言藤藤房卿記|内容: 56: 資名卿記, 公秀公記, 一條家記装束抄出, 頼定卿記. 63: 松亞記, 日野大納言時光卿記, 後八條内府實継公記. 74: 成恩寺関白記. 78: 山科家礼記. 82: 諒闇記 : 後成恩寺殿, 宗典僧正記, 綱光公記, 贈従二位宗賢卿記, 義政公記. 84: 長禄二年戊寅正月, 見聞雜記. 87: 言國卿記. 88: 長興宿祢記, 元長卿記, 兼顕卿記, 小槻晴冨記|28末の原奥書に「右山丞記依 仰挍合書冩/享和二年四月 日撿挍保己一」とあり|50「正安二年八月十一日於仙洞被始行熾盛光法」末の原奥書に「文化十五年春二月以南山法曼院藏夲書冩之 撿挍保己一」とあり|横刷毛目表紙を使用|朱点, 朱引, 朱墨筆書き入れあり|付箋あり|蔵書印主信濃須坂藩主堀直格の命によって編集された古記録|他の原本は関東大震災により焼失|極札に「桂壽」(6), 「尚信」(53)との極書, 「武清」(44, 53), 「永海」(51), 「了伴」(52), 「了甫」(74), 「定時」(84, 88)との極印あり|印記: 「花廼家文庫」, 「墨阪十一代主寫藏記」(堀直格(1806-1880)), 「東京大學法理文學部書庫所藏」, 「閲覧室用 FOR USE IN THE READING ROOM」|虫損あり</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -1056,12 +1060,12 @@
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/a241b0e6-90d9-46db-1fe8-bf35f1e616c5.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/1373f0d8-7cc0-4591-2c18-798fa20f483d.json</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>a241b0e6-90d9-46db-1fe8-bf35f1e616c5</t>
+          <t>1373f0d8-7cc0-4591-2c18-798fa20f483d</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -1071,7 +1075,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/a241b0e6-90d9-46db-1fe8-bf35f1e616c5</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/1373f0d8-7cc0-4591-2c18-798fa20f483d</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1081,12 +1085,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/f46b1242e2b77ba4f0d99feac20562f5cd3a0ee2.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/326ed2db044321d7b007462c9ac98badfd7f671a.jpg</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296167</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296219</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1109,7 +1113,7 @@
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/a241b0e6-90d9-46db-1fe8-bf35f1e616c5/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/1373f0d8-7cc0-4591-2c18-798fa20f483d/manifest</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr"/>
@@ -1117,29 +1121,29 @@
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="n">
-        <v>48</v>
+        <v>69</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>つれつれ草</t>
+          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [20]</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>A00:4082</t>
+          <t>A00:6257</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ツレズレグサ</t>
+          <t>レキダイ ザンケツ ニッキ</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>吉田 兼好</t>
+          <t>黒川 春村</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1150,7 +1154,7 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>[江戸前期]</t>
+          <t>[安政5 (1858)]</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1162,7 +1166,7 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>写本|書名は題簽による|書名の繰返し部分は踊り字|外箱の書名: 御本|責任表示は『日本古典籍総合目録データベース』による|毎半帖10行|漢字平仮名交じり文|花草窠文様緞子表紙, 松葉散しに山雲の金箔見返し, 金泥下絵鳥の子紙を使用|列帖装|二重箱入り</t>
+          <t>写本|責任表示及び書写年は『日本古典籍総合目録データベース』による|内容: 6: 光明院御記, 後光嚴院御記, 後小松院宸記, 天聴集. 28: 参議藤定長卿記 : 稱山丞記. 37: 定高卿記, 晴御会部類記, 家光卿御記, 權中納言平範輔卿記. 38: 左大史小槻季継記, 後堀川安貞二年放生會(実基公記), 石清水八幡宮, 弁官拝賀次第. 39: 大外記師光記, 資季卿記, 荒凉記, 忠高卿記. 40: 冷泉公相公記, 勝延法眼記 : 東寺大行事, 後中記 : 小路中納言資頼卿記葉室. 41: 中光記, 師兼記, 陽龍記. 42: 大宮司長則記, 口筆 : 實經, 顕朝卿記, 鴨御幸記. 43: 寳治二年記, 深心院關白記, 藤公親記, 照念院関白兼平公記. 44: 頼親記, 亀山殿行幸記 : 雅言卿記, 兼基公記. 45: 大嘗會御禊節下次第, 建治三年丁丑日記 : 三善康有, 建治四年正月廿一日 : 徳大寺大相國公孝記, 冬定卿記, 左大史小槻兼文記|内容: 46: 經任卿記, 前豊前守藤憲説記, 實兼公記. 47: 継塵記抄出. 48: 管見記, 公衡公記, 大外記師顕記, 大外記中原師淳記. 49: 真光院禪助僧正記, 吉田内府卿記. 50: 定清記, 叅議雅俊卿記, 太政大臣(公守公)御上表雜事, 仙洞御灌頂日記, 正安二年八月十一日於仙洞被始行熾盛光法, 正安三年御譲位記. 51: 實躬卿記. 52: 公茂公記, 冬平公記, 隆長卿記. 53: 忠教公記, 官記, 正三位長基卿記, 北面秀長記, 大外記中原師右記. 54: 文保元年, 日野中納言資朝卿記, 洞院大納言公敏卿記. 55: 隆蔭卿記, 文保三年記, 尹大納言師賢卿記, 革命記, 立倚子記, 萬里小路中納言藤藤房卿記|内容: 56: 資名卿記, 公秀公記, 一條家記装束抄出, 頼定卿記. 63: 松亞記, 日野大納言時光卿記, 後八條内府實継公記. 74: 成恩寺関白記. 78: 山科家礼記. 82: 諒闇記 : 後成恩寺殿, 宗典僧正記, 綱光公記, 贈従二位宗賢卿記, 義政公記. 84: 長禄二年戊寅正月, 見聞雜記. 87: 言國卿記. 88: 長興宿祢記, 元長卿記, 兼顕卿記, 小槻晴冨記|28末の原奥書に「右山丞記依 仰挍合書冩/享和二年四月 日撿挍保己一」とあり|50「正安二年八月十一日於仙洞被始行熾盛光法」末の原奥書に「文化十五年春二月以南山法曼院藏夲書冩之 撿挍保己一」とあり|横刷毛目表紙を使用|朱点, 朱引, 朱墨筆書き入れあり|付箋あり|蔵書印主信濃須坂藩主堀直格の命によって編集された古記録|他の原本は関東大震災により焼失|極札に「桂壽」(6), 「尚信」(53)との極書, 「武清」(44, 53), 「永海」(51), 「了伴」(52), 「了甫」(74), 「定時」(84, 88)との極印あり|印記: 「花廼家文庫」, 「墨阪十一代主寫藏記」(堀直格(1806-1880)), 「東京大學法理文學部書庫所藏」, 「閲覧室用 FOR USE IN THE READING ROOM」|虫損あり</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1178,12 +1182,12 @@
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/d19a62f6-4729-0ee3-3ea7-08f573851a48.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/d64280ea-576f-4bf3-9413-1b0bf6485e16.json</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>d19a62f6-4729-0ee3-3ea7-08f573851a48</t>
+          <t>d64280ea-576f-4bf3-9413-1b0bf6485e16</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1193,7 +1197,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/d19a62f6-4729-0ee3-3ea7-08f573851a48</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/d64280ea-576f-4bf3-9413-1b0bf6485e16</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1203,12 +1207,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/7966b7312c84644ee577a0390937964b1989586d.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/c5e3a0bdc0b67f7429d47677a33485a6a498e20f.jpg</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296168</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296220</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1231,7 +1235,7 @@
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/d19a62f6-4729-0ee3-3ea7-08f573851a48/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/d64280ea-576f-4bf3-9413-1b0bf6485e16/manifest</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr"/>
@@ -1239,29 +1243,29 @@
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="inlineStr"/>
       <c r="AH6" t="n">
-        <v>142</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>日本廿四孝 6巻 [1]</t>
+          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [21]</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>A00:4084</t>
+          <t>A00:6257</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ヤマト ニジュウシコウ</t>
+          <t>レキダイ ザンケツ ニッキ</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>浅井 了意</t>
+          <t>黒川 春村</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1272,19 +1276,19 @@
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>[江戸前期]</t>
+          <t>[安政5 (1858)]</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>写本|書名は目首及び題簽による|内箱の書名: 大和廿四孝|外箱の書名: 御本|責任表示は『日本古典籍総合目録データベース』による|1: 第1-4. 2: 第5-8. 3: 第9-12. 4: 第13-16. 5: 第17-20. 6: 第21-24|毎半帖10行|漢字平仮名交じり文|奈良絵本|梅唐草文様緞子表紙, 松葉散しに山雲の金箔見返し, 金泥下絵鳥の子紙を使用|列帖装|竪本|二重箱入り|糸切れあり</t>
+          <t>写本|責任表示及び書写年は『日本古典籍総合目録データベース』による|内容: 6: 光明院御記, 後光嚴院御記, 後小松院宸記, 天聴集. 28: 参議藤定長卿記 : 稱山丞記. 37: 定高卿記, 晴御会部類記, 家光卿御記, 權中納言平範輔卿記. 38: 左大史小槻季継記, 後堀川安貞二年放生會(実基公記), 石清水八幡宮, 弁官拝賀次第. 39: 大外記師光記, 資季卿記, 荒凉記, 忠高卿記. 40: 冷泉公相公記, 勝延法眼記 : 東寺大行事, 後中記 : 小路中納言資頼卿記葉室. 41: 中光記, 師兼記, 陽龍記. 42: 大宮司長則記, 口筆 : 實經, 顕朝卿記, 鴨御幸記. 43: 寳治二年記, 深心院關白記, 藤公親記, 照念院関白兼平公記. 44: 頼親記, 亀山殿行幸記 : 雅言卿記, 兼基公記. 45: 大嘗會御禊節下次第, 建治三年丁丑日記 : 三善康有, 建治四年正月廿一日 : 徳大寺大相國公孝記, 冬定卿記, 左大史小槻兼文記|内容: 46: 經任卿記, 前豊前守藤憲説記, 實兼公記. 47: 継塵記抄出. 48: 管見記, 公衡公記, 大外記師顕記, 大外記中原師淳記. 49: 真光院禪助僧正記, 吉田内府卿記. 50: 定清記, 叅議雅俊卿記, 太政大臣(公守公)御上表雜事, 仙洞御灌頂日記, 正安二年八月十一日於仙洞被始行熾盛光法, 正安三年御譲位記. 51: 實躬卿記. 52: 公茂公記, 冬平公記, 隆長卿記. 53: 忠教公記, 官記, 正三位長基卿記, 北面秀長記, 大外記中原師右記. 54: 文保元年, 日野中納言資朝卿記, 洞院大納言公敏卿記. 55: 隆蔭卿記, 文保三年記, 尹大納言師賢卿記, 革命記, 立倚子記, 萬里小路中納言藤藤房卿記|内容: 56: 資名卿記, 公秀公記, 一條家記装束抄出, 頼定卿記. 63: 松亞記, 日野大納言時光卿記, 後八條内府實継公記. 74: 成恩寺関白記. 78: 山科家礼記. 82: 諒闇記 : 後成恩寺殿, 宗典僧正記, 綱光公記, 贈従二位宗賢卿記, 義政公記. 84: 長禄二年戊寅正月, 見聞雜記. 87: 言國卿記. 88: 長興宿祢記, 元長卿記, 兼顕卿記, 小槻晴冨記|28末の原奥書に「右山丞記依 仰挍合書冩/享和二年四月 日撿挍保己一」とあり|50「正安二年八月十一日於仙洞被始行熾盛光法」末の原奥書に「文化十五年春二月以南山法曼院藏夲書冩之 撿挍保己一」とあり|横刷毛目表紙を使用|朱点, 朱引, 朱墨筆書き入れあり|付箋あり|蔵書印主信濃須坂藩主堀直格の命によって編集された古記録|他の原本は関東大震災により焼失|極札に「桂壽」(6), 「尚信」(53)との極書, 「武清」(44, 53), 「永海」(51), 「了伴」(52), 「了甫」(74), 「定時」(84, 88)との極印あり|印記: 「花廼家文庫」, 「墨阪十一代主寫藏記」(堀直格(1806-1880)), 「東京大學法理文學部書庫所藏」, 「閲覧室用 FOR USE IN THE READING ROOM」|虫損あり</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1300,12 +1304,12 @@
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/bf17bb0e-6d63-718e-218b-614134ee011d.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/decc377c-887e-7362-3bf7-81b1c9c58641.json</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>bf17bb0e-6d63-718e-218b-614134ee011d</t>
+          <t>decc377c-887e-7362-3bf7-81b1c9c58641</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1315,7 +1319,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/bf17bb0e-6d63-718e-218b-614134ee011d</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/decc377c-887e-7362-3bf7-81b1c9c58641</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1325,12 +1329,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/2c48d85abc93bce026f680cc699c748fb0a877e2.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/cfd0eab55fb67ed7ab341ab27bc1cb892d7a575c.jpg</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296169</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296221</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1353,7 +1357,7 @@
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/bf17bb0e-6d63-718e-218b-614134ee011d/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/decc377c-887e-7362-3bf7-81b1c9c58641/manifest</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr"/>
@@ -1361,29 +1365,29 @@
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="inlineStr"/>
       <c r="AH7" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>日本廿四孝 6巻 [2]</t>
+          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [22]</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>A00:4084</t>
+          <t>A00:6257</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ヤマト ニジュウシコウ</t>
+          <t>レキダイ ザンケツ ニッキ</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>浅井 了意</t>
+          <t>黒川 春村</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1394,19 +1398,19 @@
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>[江戸前期]</t>
+          <t>[安政5 (1858)]</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>写本|書名は目首及び題簽による|内箱の書名: 大和廿四孝|外箱の書名: 御本|責任表示は『日本古典籍総合目録データベース』による|1: 第1-4. 2: 第5-8. 3: 第9-12. 4: 第13-16. 5: 第17-20. 6: 第21-24|毎半帖10行|漢字平仮名交じり文|奈良絵本|梅唐草文様緞子表紙, 松葉散しに山雲の金箔見返し, 金泥下絵鳥の子紙を使用|列帖装|竪本|二重箱入り|糸切れあり</t>
+          <t>写本|責任表示及び書写年は『日本古典籍総合目録データベース』による|内容: 6: 光明院御記, 後光嚴院御記, 後小松院宸記, 天聴集. 28: 参議藤定長卿記 : 稱山丞記. 37: 定高卿記, 晴御会部類記, 家光卿御記, 權中納言平範輔卿記. 38: 左大史小槻季継記, 後堀川安貞二年放生會(実基公記), 石清水八幡宮, 弁官拝賀次第. 39: 大外記師光記, 資季卿記, 荒凉記, 忠高卿記. 40: 冷泉公相公記, 勝延法眼記 : 東寺大行事, 後中記 : 小路中納言資頼卿記葉室. 41: 中光記, 師兼記, 陽龍記. 42: 大宮司長則記, 口筆 : 實經, 顕朝卿記, 鴨御幸記. 43: 寳治二年記, 深心院關白記, 藤公親記, 照念院関白兼平公記. 44: 頼親記, 亀山殿行幸記 : 雅言卿記, 兼基公記. 45: 大嘗會御禊節下次第, 建治三年丁丑日記 : 三善康有, 建治四年正月廿一日 : 徳大寺大相國公孝記, 冬定卿記, 左大史小槻兼文記|内容: 46: 經任卿記, 前豊前守藤憲説記, 實兼公記. 47: 継塵記抄出. 48: 管見記, 公衡公記, 大外記師顕記, 大外記中原師淳記. 49: 真光院禪助僧正記, 吉田内府卿記. 50: 定清記, 叅議雅俊卿記, 太政大臣(公守公)御上表雜事, 仙洞御灌頂日記, 正安二年八月十一日於仙洞被始行熾盛光法, 正安三年御譲位記. 51: 實躬卿記. 52: 公茂公記, 冬平公記, 隆長卿記. 53: 忠教公記, 官記, 正三位長基卿記, 北面秀長記, 大外記中原師右記. 54: 文保元年, 日野中納言資朝卿記, 洞院大納言公敏卿記. 55: 隆蔭卿記, 文保三年記, 尹大納言師賢卿記, 革命記, 立倚子記, 萬里小路中納言藤藤房卿記|内容: 56: 資名卿記, 公秀公記, 一條家記装束抄出, 頼定卿記. 63: 松亞記, 日野大納言時光卿記, 後八條内府實継公記. 74: 成恩寺関白記. 78: 山科家礼記. 82: 諒闇記 : 後成恩寺殿, 宗典僧正記, 綱光公記, 贈従二位宗賢卿記, 義政公記. 84: 長禄二年戊寅正月, 見聞雜記. 87: 言國卿記. 88: 長興宿祢記, 元長卿記, 兼顕卿記, 小槻晴冨記|28末の原奥書に「右山丞記依 仰挍合書冩/享和二年四月 日撿挍保己一」とあり|50「正安二年八月十一日於仙洞被始行熾盛光法」末の原奥書に「文化十五年春二月以南山法曼院藏夲書冩之 撿挍保己一」とあり|横刷毛目表紙を使用|朱点, 朱引, 朱墨筆書き入れあり|付箋あり|蔵書印主信濃須坂藩主堀直格の命によって編集された古記録|他の原本は関東大震災により焼失|極札に「桂壽」(6), 「尚信」(53)との極書, 「武清」(44, 53), 「永海」(51), 「了伴」(52), 「了甫」(74), 「定時」(84, 88)との極印あり|印記: 「花廼家文庫」, 「墨阪十一代主寫藏記」(堀直格(1806-1880)), 「東京大學法理文學部書庫所藏」, 「閲覧室用 FOR USE IN THE READING ROOM」|虫損あり</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1422,12 +1426,12 @@
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/c2996e14-8070-09ae-328a-159e60d17016.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/b6bde9f3-3f94-81f1-4307-d86d59d90fa3.json</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>c2996e14-8070-09ae-328a-159e60d17016</t>
+          <t>b6bde9f3-3f94-81f1-4307-d86d59d90fa3</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1437,7 +1441,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/c2996e14-8070-09ae-328a-159e60d17016</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/b6bde9f3-3f94-81f1-4307-d86d59d90fa3</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -1447,12 +1451,12 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/27ba12aa7661321f36193a30b8d8ffb8b32e574c.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/eda09740787be30df4b5cefc348bc2c063c8932c.jpg</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296170</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296222</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -1475,7 +1479,7 @@
       <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/c2996e14-8070-09ae-328a-159e60d17016/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/b6bde9f3-3f94-81f1-4307-d86d59d90fa3/manifest</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr"/>
@@ -1483,29 +1487,29 @@
       <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="inlineStr"/>
       <c r="AH8" t="n">
-        <v>103</v>
+        <v>62</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>日本廿四孝 6巻 [3]</t>
+          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [23]</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>A00:4084</t>
+          <t>A00:6257</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ヤマト ニジュウシコウ</t>
+          <t>レキダイ ザンケツ ニッキ</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>浅井 了意</t>
+          <t>黒川 春村</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1516,19 +1520,19 @@
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>[江戸前期]</t>
+          <t>[安政5 (1858)]</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>写本|書名は目首及び題簽による|内箱の書名: 大和廿四孝|外箱の書名: 御本|責任表示は『日本古典籍総合目録データベース』による|1: 第1-4. 2: 第5-8. 3: 第9-12. 4: 第13-16. 5: 第17-20. 6: 第21-24|毎半帖10行|漢字平仮名交じり文|奈良絵本|梅唐草文様緞子表紙, 松葉散しに山雲の金箔見返し, 金泥下絵鳥の子紙を使用|列帖装|竪本|二重箱入り|糸切れあり</t>
+          <t>写本|責任表示及び書写年は『日本古典籍総合目録データベース』による|内容: 6: 光明院御記, 後光嚴院御記, 後小松院宸記, 天聴集. 28: 参議藤定長卿記 : 稱山丞記. 37: 定高卿記, 晴御会部類記, 家光卿御記, 權中納言平範輔卿記. 38: 左大史小槻季継記, 後堀川安貞二年放生會(実基公記), 石清水八幡宮, 弁官拝賀次第. 39: 大外記師光記, 資季卿記, 荒凉記, 忠高卿記. 40: 冷泉公相公記, 勝延法眼記 : 東寺大行事, 後中記 : 小路中納言資頼卿記葉室. 41: 中光記, 師兼記, 陽龍記. 42: 大宮司長則記, 口筆 : 實經, 顕朝卿記, 鴨御幸記. 43: 寳治二年記, 深心院關白記, 藤公親記, 照念院関白兼平公記. 44: 頼親記, 亀山殿行幸記 : 雅言卿記, 兼基公記. 45: 大嘗會御禊節下次第, 建治三年丁丑日記 : 三善康有, 建治四年正月廿一日 : 徳大寺大相國公孝記, 冬定卿記, 左大史小槻兼文記|内容: 46: 經任卿記, 前豊前守藤憲説記, 實兼公記. 47: 継塵記抄出. 48: 管見記, 公衡公記, 大外記師顕記, 大外記中原師淳記. 49: 真光院禪助僧正記, 吉田内府卿記. 50: 定清記, 叅議雅俊卿記, 太政大臣(公守公)御上表雜事, 仙洞御灌頂日記, 正安二年八月十一日於仙洞被始行熾盛光法, 正安三年御譲位記. 51: 實躬卿記. 52: 公茂公記, 冬平公記, 隆長卿記. 53: 忠教公記, 官記, 正三位長基卿記, 北面秀長記, 大外記中原師右記. 54: 文保元年, 日野中納言資朝卿記, 洞院大納言公敏卿記. 55: 隆蔭卿記, 文保三年記, 尹大納言師賢卿記, 革命記, 立倚子記, 萬里小路中納言藤藤房卿記|内容: 56: 資名卿記, 公秀公記, 一條家記装束抄出, 頼定卿記. 63: 松亞記, 日野大納言時光卿記, 後八條内府實継公記. 74: 成恩寺関白記. 78: 山科家礼記. 82: 諒闇記 : 後成恩寺殿, 宗典僧正記, 綱光公記, 贈従二位宗賢卿記, 義政公記. 84: 長禄二年戊寅正月, 見聞雜記. 87: 言國卿記. 88: 長興宿祢記, 元長卿記, 兼顕卿記, 小槻晴冨記|28末の原奥書に「右山丞記依 仰挍合書冩/享和二年四月 日撿挍保己一」とあり|50「正安二年八月十一日於仙洞被始行熾盛光法」末の原奥書に「文化十五年春二月以南山法曼院藏夲書冩之 撿挍保己一」とあり|横刷毛目表紙を使用|朱点, 朱引, 朱墨筆書き入れあり|付箋あり|蔵書印主信濃須坂藩主堀直格の命によって編集された古記録|他の原本は関東大震災により焼失|極札に「桂壽」(6), 「尚信」(53)との極書, 「武清」(44, 53), 「永海」(51), 「了伴」(52), 「了甫」(74), 「定時」(84, 88)との極印あり|印記: 「花廼家文庫」, 「墨阪十一代主寫藏記」(堀直格(1806-1880)), 「東京大學法理文學部書庫所藏」, 「閲覧室用 FOR USE IN THE READING ROOM」|虫損あり</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1544,12 +1548,12 @@
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/8bf2f649-5d15-2afc-2f36-84e0ac2f513e.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/8bd2b968-05d3-77b9-352f-f36fa2260d39.json</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>8bf2f649-5d15-2afc-2f36-84e0ac2f513e</t>
+          <t>8bd2b968-05d3-77b9-352f-f36fa2260d39</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1559,7 +1563,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/8bf2f649-5d15-2afc-2f36-84e0ac2f513e</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/8bd2b968-05d3-77b9-352f-f36fa2260d39</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
@@ -1569,12 +1573,12 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/5841d5cb8d9895d0b483a2f842afc32f67e1719b.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/30225b7ec7795f0c4d6102081bbf79b701183504.jpg</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296171</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296223</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -1597,7 +1601,7 @@
       <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/8bf2f649-5d15-2afc-2f36-84e0ac2f513e/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/8bd2b968-05d3-77b9-352f-f36fa2260d39/manifest</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr"/>
@@ -1605,29 +1609,29 @@
       <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="inlineStr"/>
       <c r="AH9" t="n">
-        <v>47</v>
+        <v>74</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>日本廿四孝 6巻 [4]</t>
+          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [24]</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A00:4084</t>
+          <t>A00:6257</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ヤマト ニジュウシコウ</t>
+          <t>レキダイ ザンケツ ニッキ</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>浅井 了意</t>
+          <t>黒川 春村</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1638,19 +1642,19 @@
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>[江戸前期]</t>
+          <t>[安政5 (1858)]</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>写本|書名は目首及び題簽による|内箱の書名: 大和廿四孝|外箱の書名: 御本|責任表示は『日本古典籍総合目録データベース』による|1: 第1-4. 2: 第5-8. 3: 第9-12. 4: 第13-16. 5: 第17-20. 6: 第21-24|毎半帖10行|漢字平仮名交じり文|奈良絵本|梅唐草文様緞子表紙, 松葉散しに山雲の金箔見返し, 金泥下絵鳥の子紙を使用|列帖装|竪本|二重箱入り|糸切れあり</t>
+          <t>写本|責任表示及び書写年は『日本古典籍総合目録データベース』による|内容: 6: 光明院御記, 後光嚴院御記, 後小松院宸記, 天聴集. 28: 参議藤定長卿記 : 稱山丞記. 37: 定高卿記, 晴御会部類記, 家光卿御記, 權中納言平範輔卿記. 38: 左大史小槻季継記, 後堀川安貞二年放生會(実基公記), 石清水八幡宮, 弁官拝賀次第. 39: 大外記師光記, 資季卿記, 荒凉記, 忠高卿記. 40: 冷泉公相公記, 勝延法眼記 : 東寺大行事, 後中記 : 小路中納言資頼卿記葉室. 41: 中光記, 師兼記, 陽龍記. 42: 大宮司長則記, 口筆 : 實經, 顕朝卿記, 鴨御幸記. 43: 寳治二年記, 深心院關白記, 藤公親記, 照念院関白兼平公記. 44: 頼親記, 亀山殿行幸記 : 雅言卿記, 兼基公記. 45: 大嘗會御禊節下次第, 建治三年丁丑日記 : 三善康有, 建治四年正月廿一日 : 徳大寺大相國公孝記, 冬定卿記, 左大史小槻兼文記|内容: 46: 經任卿記, 前豊前守藤憲説記, 實兼公記. 47: 継塵記抄出. 48: 管見記, 公衡公記, 大外記師顕記, 大外記中原師淳記. 49: 真光院禪助僧正記, 吉田内府卿記. 50: 定清記, 叅議雅俊卿記, 太政大臣(公守公)御上表雜事, 仙洞御灌頂日記, 正安二年八月十一日於仙洞被始行熾盛光法, 正安三年御譲位記. 51: 實躬卿記. 52: 公茂公記, 冬平公記, 隆長卿記. 53: 忠教公記, 官記, 正三位長基卿記, 北面秀長記, 大外記中原師右記. 54: 文保元年, 日野中納言資朝卿記, 洞院大納言公敏卿記. 55: 隆蔭卿記, 文保三年記, 尹大納言師賢卿記, 革命記, 立倚子記, 萬里小路中納言藤藤房卿記|内容: 56: 資名卿記, 公秀公記, 一條家記装束抄出, 頼定卿記. 63: 松亞記, 日野大納言時光卿記, 後八條内府實継公記. 74: 成恩寺関白記. 78: 山科家礼記. 82: 諒闇記 : 後成恩寺殿, 宗典僧正記, 綱光公記, 贈従二位宗賢卿記, 義政公記. 84: 長禄二年戊寅正月, 見聞雜記. 87: 言國卿記. 88: 長興宿祢記, 元長卿記, 兼顕卿記, 小槻晴冨記|28末の原奥書に「右山丞記依 仰挍合書冩/享和二年四月 日撿挍保己一」とあり|50「正安二年八月十一日於仙洞被始行熾盛光法」末の原奥書に「文化十五年春二月以南山法曼院藏夲書冩之 撿挍保己一」とあり|横刷毛目表紙を使用|朱点, 朱引, 朱墨筆書き入れあり|付箋あり|蔵書印主信濃須坂藩主堀直格の命によって編集された古記録|他の原本は関東大震災により焼失|極札に「桂壽」(6), 「尚信」(53)との極書, 「武清」(44, 53), 「永海」(51), 「了伴」(52), 「了甫」(74), 「定時」(84, 88)との極印あり|印記: 「花廼家文庫」, 「墨阪十一代主寫藏記」(堀直格(1806-1880)), 「東京大學法理文學部書庫所藏」, 「閲覧室用 FOR USE IN THE READING ROOM」|虫損あり</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1666,12 +1670,12 @@
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/59c5b4a7-529d-5e9f-454f-8879e85023eb.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/c6e97538-22ed-8a51-0e3a-550b7d652860.json</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>59c5b4a7-529d-5e9f-454f-8879e85023eb</t>
+          <t>c6e97538-22ed-8a51-0e3a-550b7d652860</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1681,7 +1685,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/59c5b4a7-529d-5e9f-454f-8879e85023eb</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/c6e97538-22ed-8a51-0e3a-550b7d652860</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
@@ -1691,12 +1695,12 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/e4d2c0aa6489eb2a071834a4a14714fecb372bce.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/a04dfdaed6c9dc7211358c5ad96c4bc6e9312747.jpg</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296172</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296224</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
@@ -1719,7 +1723,7 @@
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/59c5b4a7-529d-5e9f-454f-8879e85023eb/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/c6e97538-22ed-8a51-0e3a-550b7d652860/manifest</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr"/>
@@ -1727,29 +1731,29 @@
       <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="inlineStr"/>
       <c r="AH10" t="n">
-        <v>76</v>
+        <v>62</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>日本廿四孝 6巻 [5]</t>
+          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [25]</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A00:4084</t>
+          <t>A00:6257</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ヤマト ニジュウシコウ</t>
+          <t>レキダイ ザンケツ ニッキ</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>浅井 了意</t>
+          <t>黒川 春村</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1760,19 +1764,19 @@
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>[江戸前期]</t>
+          <t>[安政5 (1858)]</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>写本|書名は目首及び題簽による|内箱の書名: 大和廿四孝|外箱の書名: 御本|責任表示は『日本古典籍総合目録データベース』による|1: 第1-4. 2: 第5-8. 3: 第9-12. 4: 第13-16. 5: 第17-20. 6: 第21-24|毎半帖10行|漢字平仮名交じり文|奈良絵本|梅唐草文様緞子表紙, 松葉散しに山雲の金箔見返し, 金泥下絵鳥の子紙を使用|列帖装|竪本|二重箱入り|糸切れあり</t>
+          <t>写本|責任表示及び書写年は『日本古典籍総合目録データベース』による|内容: 6: 光明院御記, 後光嚴院御記, 後小松院宸記, 天聴集. 28: 参議藤定長卿記 : 稱山丞記. 37: 定高卿記, 晴御会部類記, 家光卿御記, 權中納言平範輔卿記. 38: 左大史小槻季継記, 後堀川安貞二年放生會(実基公記), 石清水八幡宮, 弁官拝賀次第. 39: 大外記師光記, 資季卿記, 荒凉記, 忠高卿記. 40: 冷泉公相公記, 勝延法眼記 : 東寺大行事, 後中記 : 小路中納言資頼卿記葉室. 41: 中光記, 師兼記, 陽龍記. 42: 大宮司長則記, 口筆 : 實經, 顕朝卿記, 鴨御幸記. 43: 寳治二年記, 深心院關白記, 藤公親記, 照念院関白兼平公記. 44: 頼親記, 亀山殿行幸記 : 雅言卿記, 兼基公記. 45: 大嘗會御禊節下次第, 建治三年丁丑日記 : 三善康有, 建治四年正月廿一日 : 徳大寺大相國公孝記, 冬定卿記, 左大史小槻兼文記|内容: 46: 經任卿記, 前豊前守藤憲説記, 實兼公記. 47: 継塵記抄出. 48: 管見記, 公衡公記, 大外記師顕記, 大外記中原師淳記. 49: 真光院禪助僧正記, 吉田内府卿記. 50: 定清記, 叅議雅俊卿記, 太政大臣(公守公)御上表雜事, 仙洞御灌頂日記, 正安二年八月十一日於仙洞被始行熾盛光法, 正安三年御譲位記. 51: 實躬卿記. 52: 公茂公記, 冬平公記, 隆長卿記. 53: 忠教公記, 官記, 正三位長基卿記, 北面秀長記, 大外記中原師右記. 54: 文保元年, 日野中納言資朝卿記, 洞院大納言公敏卿記. 55: 隆蔭卿記, 文保三年記, 尹大納言師賢卿記, 革命記, 立倚子記, 萬里小路中納言藤藤房卿記|内容: 56: 資名卿記, 公秀公記, 一條家記装束抄出, 頼定卿記. 63: 松亞記, 日野大納言時光卿記, 後八條内府實継公記. 74: 成恩寺関白記. 78: 山科家礼記. 82: 諒闇記 : 後成恩寺殿, 宗典僧正記, 綱光公記, 贈従二位宗賢卿記, 義政公記. 84: 長禄二年戊寅正月, 見聞雜記. 87: 言國卿記. 88: 長興宿祢記, 元長卿記, 兼顕卿記, 小槻晴冨記|28末の原奥書に「右山丞記依 仰挍合書冩/享和二年四月 日撿挍保己一」とあり|50「正安二年八月十一日於仙洞被始行熾盛光法」末の原奥書に「文化十五年春二月以南山法曼院藏夲書冩之 撿挍保己一」とあり|横刷毛目表紙を使用|朱点, 朱引, 朱墨筆書き入れあり|付箋あり|蔵書印主信濃須坂藩主堀直格の命によって編集された古記録|他の原本は関東大震災により焼失|極札に「桂壽」(6), 「尚信」(53)との極書, 「武清」(44, 53), 「永海」(51), 「了伴」(52), 「了甫」(74), 「定時」(84, 88)との極印あり|印記: 「花廼家文庫」, 「墨阪十一代主寫藏記」(堀直格(1806-1880)), 「東京大學法理文學部書庫所藏」, 「閲覧室用 FOR USE IN THE READING ROOM」|虫損あり</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1788,12 +1792,12 @@
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/ff7eb5a9-8bd0-64c0-3cbf-03a54ac07e65.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/48123112-700b-8619-731b-649449ff034b.json</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>ff7eb5a9-8bd0-64c0-3cbf-03a54ac07e65</t>
+          <t>48123112-700b-8619-731b-649449ff034b</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1803,7 +1807,7 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/ff7eb5a9-8bd0-64c0-3cbf-03a54ac07e65</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/48123112-700b-8619-731b-649449ff034b</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
@@ -1813,12 +1817,12 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/550abdb28c4a764b0c1330b7551c32cee807416f.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/4c918a15ed3dc97a18f7bc977b4dc2e8c724d774.jpg</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296173</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296225</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
@@ -1841,7 +1845,7 @@
       <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/ff7eb5a9-8bd0-64c0-3cbf-03a54ac07e65/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/48123112-700b-8619-731b-649449ff034b/manifest</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr"/>
@@ -1849,29 +1853,29 @@
       <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="inlineStr"/>
       <c r="AH11" t="n">
-        <v>87</v>
+        <v>78</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>日本廿四孝 6巻 [6]</t>
+          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [26]</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>A00:4084</t>
+          <t>A00:6257</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ヤマト ニジュウシコウ</t>
+          <t>レキダイ ザンケツ ニッキ</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>浅井 了意</t>
+          <t>黒川 春村</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1882,19 +1886,19 @@
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>[江戸前期]</t>
+          <t>[安政5 (1858)]</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>写本|書名は目首及び題簽による|内箱の書名: 大和廿四孝|外箱の書名: 御本|責任表示は『日本古典籍総合目録データベース』による|1: 第1-4. 2: 第5-8. 3: 第9-12. 4: 第13-16. 5: 第17-20. 6: 第21-24|毎半帖10行|漢字平仮名交じり文|奈良絵本|梅唐草文様緞子表紙, 松葉散しに山雲の金箔見返し, 金泥下絵鳥の子紙を使用|列帖装|竪本|二重箱入り|糸切れあり</t>
+          <t>写本|責任表示及び書写年は『日本古典籍総合目録データベース』による|内容: 6: 光明院御記, 後光嚴院御記, 後小松院宸記, 天聴集. 28: 参議藤定長卿記 : 稱山丞記. 37: 定高卿記, 晴御会部類記, 家光卿御記, 權中納言平範輔卿記. 38: 左大史小槻季継記, 後堀川安貞二年放生會(実基公記), 石清水八幡宮, 弁官拝賀次第. 39: 大外記師光記, 資季卿記, 荒凉記, 忠高卿記. 40: 冷泉公相公記, 勝延法眼記 : 東寺大行事, 後中記 : 小路中納言資頼卿記葉室. 41: 中光記, 師兼記, 陽龍記. 42: 大宮司長則記, 口筆 : 實經, 顕朝卿記, 鴨御幸記. 43: 寳治二年記, 深心院關白記, 藤公親記, 照念院関白兼平公記. 44: 頼親記, 亀山殿行幸記 : 雅言卿記, 兼基公記. 45: 大嘗會御禊節下次第, 建治三年丁丑日記 : 三善康有, 建治四年正月廿一日 : 徳大寺大相國公孝記, 冬定卿記, 左大史小槻兼文記|内容: 46: 經任卿記, 前豊前守藤憲説記, 實兼公記. 47: 継塵記抄出. 48: 管見記, 公衡公記, 大外記師顕記, 大外記中原師淳記. 49: 真光院禪助僧正記, 吉田内府卿記. 50: 定清記, 叅議雅俊卿記, 太政大臣(公守公)御上表雜事, 仙洞御灌頂日記, 正安二年八月十一日於仙洞被始行熾盛光法, 正安三年御譲位記. 51: 實躬卿記. 52: 公茂公記, 冬平公記, 隆長卿記. 53: 忠教公記, 官記, 正三位長基卿記, 北面秀長記, 大外記中原師右記. 54: 文保元年, 日野中納言資朝卿記, 洞院大納言公敏卿記. 55: 隆蔭卿記, 文保三年記, 尹大納言師賢卿記, 革命記, 立倚子記, 萬里小路中納言藤藤房卿記|内容: 56: 資名卿記, 公秀公記, 一條家記装束抄出, 頼定卿記. 63: 松亞記, 日野大納言時光卿記, 後八條内府實継公記. 74: 成恩寺関白記. 78: 山科家礼記. 82: 諒闇記 : 後成恩寺殿, 宗典僧正記, 綱光公記, 贈従二位宗賢卿記, 義政公記. 84: 長禄二年戊寅正月, 見聞雜記. 87: 言國卿記. 88: 長興宿祢記, 元長卿記, 兼顕卿記, 小槻晴冨記|28末の原奥書に「右山丞記依 仰挍合書冩/享和二年四月 日撿挍保己一」とあり|50「正安二年八月十一日於仙洞被始行熾盛光法」末の原奥書に「文化十五年春二月以南山法曼院藏夲書冩之 撿挍保己一」とあり|横刷毛目表紙を使用|朱点, 朱引, 朱墨筆書き入れあり|付箋あり|蔵書印主信濃須坂藩主堀直格の命によって編集された古記録|他の原本は関東大震災により焼失|極札に「桂壽」(6), 「尚信」(53)との極書, 「武清」(44, 53), 「永海」(51), 「了伴」(52), 「了甫」(74), 「定時」(84, 88)との極印あり|印記: 「花廼家文庫」, 「墨阪十一代主寫藏記」(堀直格(1806-1880)), 「東京大學法理文學部書庫所藏」, 「閲覧室用 FOR USE IN THE READING ROOM」|虫損あり</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1910,12 +1914,12 @@
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/0106be3f-16cb-3945-1c3c-419a27f26c16.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/9b2b928b-4eda-76c6-0dfd-03bde69c046c.json</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>0106be3f-16cb-3945-1c3c-419a27f26c16</t>
+          <t>9b2b928b-4eda-76c6-0dfd-03bde69c046c</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1925,7 +1929,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/0106be3f-16cb-3945-1c3c-419a27f26c16</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/9b2b928b-4eda-76c6-0dfd-03bde69c046c</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
@@ -1935,12 +1939,12 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/b1c4cf868676ac5b8b2f574249475349a7a90813.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/7903cd89a232a0d9b4b243d90852d31d93c80300.jpg</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296174</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296226</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
@@ -1963,7 +1967,7 @@
       <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/0106be3f-16cb-3945-1c3c-419a27f26c16/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/9b2b928b-4eda-76c6-0dfd-03bde69c046c/manifest</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr"/>
@@ -1971,29 +1975,29 @@
       <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="inlineStr"/>
       <c r="AH12" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>京ものかたり</t>
+          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [27]</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>A00:4085</t>
+          <t>A00:6257</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>キョウモノガタリ</t>
+          <t>レキダイ ザンケツ ニッキ</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>洛陽散人</t>
+          <t>黒川 春村</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2004,7 +2008,7 @@
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>[江戸前期]</t>
+          <t>[安政5 (1858)]</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2016,7 +2020,7 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>写本|書名は題簽による|[跋]中の書名: 見ぬ京ものかたり|外箱の書名: 御本|[跋]に「万治元年の秋夜長きひ ... いぬの年九月の末のはふのなん時 洛陽散人たれ某」とあり|内容: 儒佛の論, など|毎半帖10行|漢字平仮名交じり文|桜唐草文様緞子表紙, 松葉散しに山雲の金箔見返し, 金泥下絵鳥の子紙を使用|列帖装|二重箱入り</t>
+          <t>写本|責任表示及び書写年は『日本古典籍総合目録データベース』による|内容: 6: 光明院御記, 後光嚴院御記, 後小松院宸記, 天聴集. 28: 参議藤定長卿記 : 稱山丞記. 37: 定高卿記, 晴御会部類記, 家光卿御記, 權中納言平範輔卿記. 38: 左大史小槻季継記, 後堀川安貞二年放生會(実基公記), 石清水八幡宮, 弁官拝賀次第. 39: 大外記師光記, 資季卿記, 荒凉記, 忠高卿記. 40: 冷泉公相公記, 勝延法眼記 : 東寺大行事, 後中記 : 小路中納言資頼卿記葉室. 41: 中光記, 師兼記, 陽龍記. 42: 大宮司長則記, 口筆 : 實經, 顕朝卿記, 鴨御幸記. 43: 寳治二年記, 深心院關白記, 藤公親記, 照念院関白兼平公記. 44: 頼親記, 亀山殿行幸記 : 雅言卿記, 兼基公記. 45: 大嘗會御禊節下次第, 建治三年丁丑日記 : 三善康有, 建治四年正月廿一日 : 徳大寺大相國公孝記, 冬定卿記, 左大史小槻兼文記|内容: 46: 經任卿記, 前豊前守藤憲説記, 實兼公記. 47: 継塵記抄出. 48: 管見記, 公衡公記, 大外記師顕記, 大外記中原師淳記. 49: 真光院禪助僧正記, 吉田内府卿記. 50: 定清記, 叅議雅俊卿記, 太政大臣(公守公)御上表雜事, 仙洞御灌頂日記, 正安二年八月十一日於仙洞被始行熾盛光法, 正安三年御譲位記. 51: 實躬卿記. 52: 公茂公記, 冬平公記, 隆長卿記. 53: 忠教公記, 官記, 正三位長基卿記, 北面秀長記, 大外記中原師右記. 54: 文保元年, 日野中納言資朝卿記, 洞院大納言公敏卿記. 55: 隆蔭卿記, 文保三年記, 尹大納言師賢卿記, 革命記, 立倚子記, 萬里小路中納言藤藤房卿記|内容: 56: 資名卿記, 公秀公記, 一條家記装束抄出, 頼定卿記. 63: 松亞記, 日野大納言時光卿記, 後八條内府實継公記. 74: 成恩寺関白記. 78: 山科家礼記. 82: 諒闇記 : 後成恩寺殿, 宗典僧正記, 綱光公記, 贈従二位宗賢卿記, 義政公記. 84: 長禄二年戊寅正月, 見聞雜記. 87: 言國卿記. 88: 長興宿祢記, 元長卿記, 兼顕卿記, 小槻晴冨記|28末の原奥書に「右山丞記依 仰挍合書冩/享和二年四月 日撿挍保己一」とあり|50「正安二年八月十一日於仙洞被始行熾盛光法」末の原奥書に「文化十五年春二月以南山法曼院藏夲書冩之 撿挍保己一」とあり|横刷毛目表紙を使用|朱点, 朱引, 朱墨筆書き入れあり|付箋あり|蔵書印主信濃須坂藩主堀直格の命によって編集された古記録|他の原本は関東大震災により焼失|極札に「桂壽」(6), 「尚信」(53)との極書, 「武清」(44, 53), 「永海」(51), 「了伴」(52), 「了甫」(74), 「定時」(84, 88)との極印あり|印記: 「花廼家文庫」, 「墨阪十一代主寫藏記」(堀直格(1806-1880)), 「東京大學法理文學部書庫所藏」, 「閲覧室用 FOR USE IN THE READING ROOM」|虫損あり</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -2032,12 +2036,12 @@
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/13969a60-692e-663a-3a83-97b8168b8fbe.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/ccc6c3da-1648-49f5-91fc-2faaf5400387.json</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>13969a60-692e-663a-3a83-97b8168b8fbe</t>
+          <t>ccc6c3da-1648-49f5-91fc-2faaf5400387</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -2047,7 +2051,7 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/13969a60-692e-663a-3a83-97b8168b8fbe</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/ccc6c3da-1648-49f5-91fc-2faaf5400387</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
@@ -2057,12 +2061,12 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/b4c216cdd7c363c063be4e90de6eea21dd1da6e3.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/1e476c24ffbe9fd54b432acbf27eb918fc4162d0.jpg</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296175</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296227</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -2085,7 +2089,7 @@
       <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/13969a60-692e-663a-3a83-97b8168b8fbe/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/ccc6c3da-1648-49f5-91fc-2faaf5400387/manifest</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr"/>
@@ -2093,52 +2097,52 @@
       <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="inlineStr"/>
       <c r="AH13" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>北遊漫録 3巻再1巻 [1]</t>
+          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [28]</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>A00:4099</t>
+          <t>A00:6257</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ホクユウ マンロク</t>
+          <t>レキダイ ザンケツ ニッキ</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>久保田 米僊</t>
+          <t>黒川 春村</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>久保田米僊 [自筆]</t>
+          <t>[書写者不明]</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>明治21 [1888]-明治24 [1891]</t>
+          <t>[安政5 (1858)]</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>写本|書名は扉による|帙題簽に「久保田米僊草稿」とあり|扉に「明治廿一年はる五月」(乾), 「明治廿一年はる六月」(坤), 「明治廿一年はる六月中澣」(瑞啚), 「明治廿四年五月十九日」(再)とあり|乾末に「増補考古畫譜五巻 發兌書肆 有隣堂」とあり|おもに図版|彩色あり|双葉装|印記: 「田寛之印」, 「山脊与弥との」</t>
+          <t>写本|責任表示及び書写年は『日本古典籍総合目録データベース』による|内容: 6: 光明院御記, 後光嚴院御記, 後小松院宸記, 天聴集. 28: 参議藤定長卿記 : 稱山丞記. 37: 定高卿記, 晴御会部類記, 家光卿御記, 權中納言平範輔卿記. 38: 左大史小槻季継記, 後堀川安貞二年放生會(実基公記), 石清水八幡宮, 弁官拝賀次第. 39: 大外記師光記, 資季卿記, 荒凉記, 忠高卿記. 40: 冷泉公相公記, 勝延法眼記 : 東寺大行事, 後中記 : 小路中納言資頼卿記葉室. 41: 中光記, 師兼記, 陽龍記. 42: 大宮司長則記, 口筆 : 實經, 顕朝卿記, 鴨御幸記. 43: 寳治二年記, 深心院關白記, 藤公親記, 照念院関白兼平公記. 44: 頼親記, 亀山殿行幸記 : 雅言卿記, 兼基公記. 45: 大嘗會御禊節下次第, 建治三年丁丑日記 : 三善康有, 建治四年正月廿一日 : 徳大寺大相國公孝記, 冬定卿記, 左大史小槻兼文記|内容: 46: 經任卿記, 前豊前守藤憲説記, 實兼公記. 47: 継塵記抄出. 48: 管見記, 公衡公記, 大外記師顕記, 大外記中原師淳記. 49: 真光院禪助僧正記, 吉田内府卿記. 50: 定清記, 叅議雅俊卿記, 太政大臣(公守公)御上表雜事, 仙洞御灌頂日記, 正安二年八月十一日於仙洞被始行熾盛光法, 正安三年御譲位記. 51: 實躬卿記. 52: 公茂公記, 冬平公記, 隆長卿記. 53: 忠教公記, 官記, 正三位長基卿記, 北面秀長記, 大外記中原師右記. 54: 文保元年, 日野中納言資朝卿記, 洞院大納言公敏卿記. 55: 隆蔭卿記, 文保三年記, 尹大納言師賢卿記, 革命記, 立倚子記, 萬里小路中納言藤藤房卿記|内容: 56: 資名卿記, 公秀公記, 一條家記装束抄出, 頼定卿記. 63: 松亞記, 日野大納言時光卿記, 後八條内府實継公記. 74: 成恩寺関白記. 78: 山科家礼記. 82: 諒闇記 : 後成恩寺殿, 宗典僧正記, 綱光公記, 贈従二位宗賢卿記, 義政公記. 84: 長禄二年戊寅正月, 見聞雜記. 87: 言國卿記. 88: 長興宿祢記, 元長卿記, 兼顕卿記, 小槻晴冨記|28末の原奥書に「右山丞記依 仰挍合書冩/享和二年四月 日撿挍保己一」とあり|50「正安二年八月十一日於仙洞被始行熾盛光法」末の原奥書に「文化十五年春二月以南山法曼院藏夲書冩之 撿挍保己一」とあり|横刷毛目表紙を使用|朱点, 朱引, 朱墨筆書き入れあり|付箋あり|蔵書印主信濃須坂藩主堀直格の命によって編集された古記録|他の原本は関東大震災により焼失|極札に「桂壽」(6), 「尚信」(53)との極書, 「武清」(44, 53), 「永海」(51), 「了伴」(52), 「了甫」(74), 「定時」(84, 88)との極印あり|印記: 「花廼家文庫」, 「墨阪十一代主寫藏記」(堀直格(1806-1880)), 「東京大學法理文學部書庫所藏」, 「閲覧室用 FOR USE IN THE READING ROOM」|虫損あり</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -2154,12 +2158,12 @@
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/fdb2f4c7-47bb-0fc6-53e6-e8ffb5796046.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/9f3a126c-84bb-8f96-2916-b65ace30a616.json</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>fdb2f4c7-47bb-0fc6-53e6-e8ffb5796046</t>
+          <t>9f3a126c-84bb-8f96-2916-b65ace30a616</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -2169,7 +2173,7 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/fdb2f4c7-47bb-0fc6-53e6-e8ffb5796046</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/9f3a126c-84bb-8f96-2916-b65ace30a616</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
@@ -2179,12 +2183,12 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/789ef89fb4fc813de5d276f3c43f982c6760d60b.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/fc4844ae32ad2dd582e3570965cb142f5f370f74.jpg</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296176</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296228</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -2207,7 +2211,7 @@
       <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/fdb2f4c7-47bb-0fc6-53e6-e8ffb5796046/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/9f3a126c-84bb-8f96-2916-b65ace30a616/manifest</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr"/>
@@ -2215,52 +2219,52 @@
       <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="inlineStr"/>
       <c r="AH14" t="n">
-        <v>31</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>北遊漫録 3巻再1巻 [2]</t>
+          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [29]</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>A00:4099</t>
+          <t>A00:6257</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ホクユウ マンロク</t>
+          <t>レキダイ ザンケツ ニッキ</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>久保田 米僊</t>
+          <t>黒川 春村</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>久保田米僊 [自筆]</t>
+          <t>[書写者不明]</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>明治21 [1888]-明治24 [1891]</t>
+          <t>[安政5 (1858)]</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>写本|書名は扉による|帙題簽に「久保田米僊草稿」とあり|扉に「明治廿一年はる五月」(乾), 「明治廿一年はる六月」(坤), 「明治廿一年はる六月中澣」(瑞啚), 「明治廿四年五月十九日」(再)とあり|乾末に「増補考古畫譜五巻 發兌書肆 有隣堂」とあり|おもに図版|彩色あり|双葉装|印記: 「田寛之印」, 「山脊与弥との」</t>
+          <t>写本|責任表示及び書写年は『日本古典籍総合目録データベース』による|内容: 6: 光明院御記, 後光嚴院御記, 後小松院宸記, 天聴集. 28: 参議藤定長卿記 : 稱山丞記. 37: 定高卿記, 晴御会部類記, 家光卿御記, 權中納言平範輔卿記. 38: 左大史小槻季継記, 後堀川安貞二年放生會(実基公記), 石清水八幡宮, 弁官拝賀次第. 39: 大外記師光記, 資季卿記, 荒凉記, 忠高卿記. 40: 冷泉公相公記, 勝延法眼記 : 東寺大行事, 後中記 : 小路中納言資頼卿記葉室. 41: 中光記, 師兼記, 陽龍記. 42: 大宮司長則記, 口筆 : 實經, 顕朝卿記, 鴨御幸記. 43: 寳治二年記, 深心院關白記, 藤公親記, 照念院関白兼平公記. 44: 頼親記, 亀山殿行幸記 : 雅言卿記, 兼基公記. 45: 大嘗會御禊節下次第, 建治三年丁丑日記 : 三善康有, 建治四年正月廿一日 : 徳大寺大相國公孝記, 冬定卿記, 左大史小槻兼文記|内容: 46: 經任卿記, 前豊前守藤憲説記, 實兼公記. 47: 継塵記抄出. 48: 管見記, 公衡公記, 大外記師顕記, 大外記中原師淳記. 49: 真光院禪助僧正記, 吉田内府卿記. 50: 定清記, 叅議雅俊卿記, 太政大臣(公守公)御上表雜事, 仙洞御灌頂日記, 正安二年八月十一日於仙洞被始行熾盛光法, 正安三年御譲位記. 51: 實躬卿記. 52: 公茂公記, 冬平公記, 隆長卿記. 53: 忠教公記, 官記, 正三位長基卿記, 北面秀長記, 大外記中原師右記. 54: 文保元年, 日野中納言資朝卿記, 洞院大納言公敏卿記. 55: 隆蔭卿記, 文保三年記, 尹大納言師賢卿記, 革命記, 立倚子記, 萬里小路中納言藤藤房卿記|内容: 56: 資名卿記, 公秀公記, 一條家記装束抄出, 頼定卿記. 63: 松亞記, 日野大納言時光卿記, 後八條内府實継公記. 74: 成恩寺関白記. 78: 山科家礼記. 82: 諒闇記 : 後成恩寺殿, 宗典僧正記, 綱光公記, 贈従二位宗賢卿記, 義政公記. 84: 長禄二年戊寅正月, 見聞雜記. 87: 言國卿記. 88: 長興宿祢記, 元長卿記, 兼顕卿記, 小槻晴冨記|28末の原奥書に「右山丞記依 仰挍合書冩/享和二年四月 日撿挍保己一」とあり|50「正安二年八月十一日於仙洞被始行熾盛光法」末の原奥書に「文化十五年春二月以南山法曼院藏夲書冩之 撿挍保己一」とあり|横刷毛目表紙を使用|朱点, 朱引, 朱墨筆書き入れあり|付箋あり|蔵書印主信濃須坂藩主堀直格の命によって編集された古記録|他の原本は関東大震災により焼失|極札に「桂壽」(6), 「尚信」(53)との極書, 「武清」(44, 53), 「永海」(51), 「了伴」(52), 「了甫」(74), 「定時」(84, 88)との極印あり|印記: 「花廼家文庫」, 「墨阪十一代主寫藏記」(堀直格(1806-1880)), 「東京大學法理文學部書庫所藏」, 「閲覧室用 FOR USE IN THE READING ROOM」|虫損あり</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -2276,12 +2280,12 @@
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/01f5e469-1d82-36bd-3e33-34c56a942a2d.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/7cdebe3a-8fb4-14b4-7ddb-3f92f3be9668.json</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>01f5e469-1d82-36bd-3e33-34c56a942a2d</t>
+          <t>7cdebe3a-8fb4-14b4-7ddb-3f92f3be9668</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -2291,7 +2295,7 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/01f5e469-1d82-36bd-3e33-34c56a942a2d</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/7cdebe3a-8fb4-14b4-7ddb-3f92f3be9668</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
@@ -2301,12 +2305,12 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/0e331722b5a82ea48f273a6b7465d2784dc8a44c.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/08f5648a7b5512a896986520a6449d3620439071.jpg</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296177</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296229</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
@@ -2329,7 +2333,7 @@
       <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/01f5e469-1d82-36bd-3e33-34c56a942a2d/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/7cdebe3a-8fb4-14b4-7ddb-3f92f3be9668/manifest</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr"/>
@@ -2337,52 +2341,52 @@
       <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="inlineStr"/>
       <c r="AH15" t="n">
-        <v>31</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>北遊漫録 3巻再1巻 [3]</t>
+          <t>普賢延命</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>A00:4099</t>
+          <t>A00:6264</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ホクユウ マンロク</t>
+          <t>フゲン エンメイ</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>久保田 米僊</t>
+          <t>興然</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>久保田米僊 [自筆]</t>
+          <t>長円 [写]</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>明治21 [1888]-明治24 [1891]</t>
+          <t>嘉禎2 [1236] 奥書</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>写本|書名は扉による|帙題簽に「久保田米僊草稿」とあり|扉に「明治廿一年はる五月」(乾), 「明治廿一年はる六月」(坤), 「明治廿一年はる六月中澣」(瑞啚), 「明治廿四年五月十九日」(再)とあり|乾末に「増補考古畫譜五巻 發兌書肆 有隣堂」とあり|おもに図版|彩色あり|双葉装|印記: 「田寛之印」, 「山脊与弥との」</t>
+          <t>写本|内題下に「師 理教」, 「嘉禎二年奥書アリ 長円書」とあり|巻末に「越前闍梨浄与口傳 興然夲」とあり|奥書に「嘉禎二年四月六月奉傳受空達御房ノ長円」とあり|裏に「正和元年壬子八月廿九日於成身院奉伝受之了」とあり|巻子本|送り仮名, 傍訓あり|虫損あり (裏打ち補修あり)</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2398,12 +2402,12 @@
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/1a4a12a3-0ae7-8858-3851-f3845f60709b.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/e57fef06-5cfd-a602-6a89-f4d7d4360e87.json</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>1a4a12a3-0ae7-8858-3851-f3845f60709b</t>
+          <t>e57fef06-5cfd-a602-6a89-f4d7d4360e87</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -2413,7 +2417,7 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/1a4a12a3-0ae7-8858-3851-f3845f60709b</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/e57fef06-5cfd-a602-6a89-f4d7d4360e87</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
@@ -2423,12 +2427,12 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/3897bac3ffa751a75c02bb59922c185ca93a9f1e.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/eec20da7736c221a3c86321abead9d8d9429dceb.jpg</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296178</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296230</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
@@ -2451,7 +2455,7 @@
       <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/1a4a12a3-0ae7-8858-3851-f3845f60709b/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/e57fef06-5cfd-a602-6a89-f4d7d4360e87/manifest</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr"/>
@@ -2459,52 +2463,52 @@
       <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="inlineStr"/>
       <c r="AH16" t="n">
-        <v>31</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>北遊漫録 3巻再1巻 [4]</t>
+          <t>如法愛染王</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>A00:4099</t>
+          <t>A00:6265</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ホクユウ マンロク</t>
+          <t>ニョホウ アイゼンオウ</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>久保田 米僊</t>
+          <t>仁海</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>久保田米僊 [自筆]</t>
+          <t>禅喜 [写]</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>明治21 [1888]-明治24 [1891]</t>
+          <t>嘉暦2 [1327] 奥書</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>写本|書名は扉による|帙題簽に「久保田米僊草稿」とあり|扉に「明治廿一年はる五月」(乾), 「明治廿一年はる六月」(坤), 「明治廿一年はる六月中澣」(瑞啚), 「明治廿四年五月十九日」(再)とあり|乾末に「増補考古畫譜五巻 發兌書肆 有隣堂」とあり|おもに図版|彩色あり|双葉装|印記: 「田寛之印」, 「山脊与弥との」</t>
+          <t>写本|表紙の書名: 如法愛染|内題下に「付小野大次苐修之」とあり|本奥書に「延慶二年夘月十日於仁和寺真光院書写了 金剛佛子印法 生年卅二」とあり|奥書に「嘉暦二年正月廿二日全写了 禅喜 生年卅一」とあり|巻子本|小野流|淡墨界の料紙を使用(界匡廓: 23.8×2.2cm)|巻頭下部の貼紙に「嘉暦二年巨今五百八十二年鎌倉時代四一ノ六九七号」とあり|破損, 虫損あり (裏打ち補修あり)</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2520,12 +2524,12 @@
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/73cbda29-23d4-a760-5213-0395cd767491.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/e321350d-483d-6e38-81a2-a637b8f798fb.json</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>73cbda29-23d4-a760-5213-0395cd767491</t>
+          <t>e321350d-483d-6e38-81a2-a637b8f798fb</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -2535,7 +2539,7 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/73cbda29-23d4-a760-5213-0395cd767491</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/e321350d-483d-6e38-81a2-a637b8f798fb</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
@@ -2545,12 +2549,12 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/74a9af6c2a682e260aa96f2ded5a07abfcd3098c.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/355285a0ec0b1cc8f12ae2c98e5215bdc9477998.jpg</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296179</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296231</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
@@ -2573,7 +2577,7 @@
       <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/73cbda29-23d4-a760-5213-0395cd767491/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/e321350d-483d-6e38-81a2-a637b8f798fb/manifest</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr"/>
@@ -2581,36 +2585,40 @@
       <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="inlineStr"/>
       <c r="AH17" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>蘭主之書翰使節持参叅途中之図</t>
+          <t>三摩耶戒作法 : 東寺</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>A00:4146</t>
+          <t>A00:6266</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ランシュ ノ ショカン シセツ ジサン トチュウ ノ ズ</t>
+          <t>サンマヤカイ サホウ : トウジ</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>聖快</t>
+        </is>
+      </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>[製作者不明]</t>
+          <t>道快 [自筆]</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>天保15 [1844] 識語</t>
+          <t>康暦元 [1379] 奥書</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2622,7 +2630,7 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>書名は題簽による|箱の書名: 和蘭國軍艦人物兵器等図|冒頭に「天保十五年甲辰秋七月二日和蘭國官船奉其主命来進於我﨑嶴茲掲略圖摸其全般及内面結構所備之諸兵器等」との識語あり|絵巻|彩色あり|印記: 「籌海庫」</t>
+          <t>写本|書名は表紙による|本奥書に「康和元年十月廿日午時書了 深禅夲(第三轉)」, 「以小野僧正御夲理趣房書御夲也(初轉)」, 「承暦四年十一月十二日給預又書冩并傳受了 峯大阿闍梨御房事也(第二轉)」とあり|奥書に「康暦元年八月十二日於地藏院以平等坊永嚴自筆夲書冩之訖 東寺沙門道快」, 「同十四日於同院以或夲重挍合入落字注異説削謬詞尤可秘藏而已」とあり|表紙の貼紙に「康暦元年八月十二日於地藏院以平等坊永嚴自筆本書写之訖 東寺沙門道快 南北類」とある|巻子本|朱筆書き入れあり|淡墨界の料紙を使用(界匡廓: 19.5×2.0cm)|印記: 「僧正弘基」|破損, 虫損あり</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2638,12 +2646,12 @@
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/ca3ac8e1-6c03-5832-3987-70b1fa71258a.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/2b2562eb-7577-32f6-4c99-462a84e0647c.json</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>ca3ac8e1-6c03-5832-3987-70b1fa71258a</t>
+          <t>2b2562eb-7577-32f6-4c99-462a84e0647c</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -2653,7 +2661,7 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/ca3ac8e1-6c03-5832-3987-70b1fa71258a</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/2b2562eb-7577-32f6-4c99-462a84e0647c</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
@@ -2663,12 +2671,12 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/32f72c2d68d9e56e4f46528e6997cbb4c330cc23.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/60a9be2785b442f57f54089c594f63b8df5ae1f4.jpg</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296180</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296232</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
@@ -2691,7 +2699,7 @@
       <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/ca3ac8e1-6c03-5832-3987-70b1fa71258a/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/2b2562eb-7577-32f6-4c99-462a84e0647c/manifest</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr"/>
@@ -2699,48 +2707,52 @@
       <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="inlineStr"/>
       <c r="AH18" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>喎蘭軍艦プレカット並銃劍等之図</t>
+          <t>騁懐帖 2巻 [1]</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>A00:4147</t>
+          <t>A00:6379</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>オランダ グンカン プレカット ナラビニ ジュウケン トウ ノ ズ</t>
+          <t>テイカイジョウ</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>芳賀 矢一</t>
+        </is>
+      </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>[製作者不明]</t>
+          <t>芳賀矢一 [ほか自筆]</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>[天保弘化年間]</t>
+          <t>[明治-昭和年間]</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
-          <t>書名は題簽による|箱の書名: 和蘭國軍艦人物兵器等図|巻末に「圖説」あり|絵巻|彩色あり</t>
+          <t>写本|書名及び巻冊次は題簽による|跋末に「松夲生名ハ百藏東京帝國大學ノ使丁タリ職ヲ山上會議所ニ奉スルコト四十有餘年 ... 頃来マタ諸賢ノ揮毫ヲ乞上名ケテ騁懐帖トイフ ... 帖成リテ予ニ其由来ヲ記セシコトヲ求ム乃チ之ヲ録シテ以テ跋後トス 昭和二年三月 辻善之助識」とあり|折本|書画帖|彩色あり|名録2冊(大和綴)を付す|落款朱印: 「長成」(坪井九馬三), 「圭卿」(市村瓚次郎), 「簣山」(鹽谷時敏), 「維亭」(塚本靖), 「土肥慶藏」, 「忠太」(伊東忠太), 「萬」(和田万吉), 「芳溪」(呉秀三), 「前田慧雲」, 「大澤謙二」, 「南條文雄」, 「有坂氏」(有坂鉊藏), 「博」, 「石亭」(林博太郎), 「長與又郎」, 「宇野哲人」, ほかあり</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2756,12 +2768,12 @@
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/8509e124-5c2f-173b-2502-4d9cd27f9f85.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/bfdc576b-6ce2-9274-914e-8cc9c52c04de.json</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>8509e124-5c2f-173b-2502-4d9cd27f9f85</t>
+          <t>bfdc576b-6ce2-9274-914e-8cc9c52c04de</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -2771,7 +2783,7 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/8509e124-5c2f-173b-2502-4d9cd27f9f85</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/bfdc576b-6ce2-9274-914e-8cc9c52c04de</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
@@ -2781,12 +2793,12 @@
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/18d2fe489472e7f697dd92568da44185793c8f4d.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/4061afb959aba92577bf3357712e3556cd07cf8e.jpg</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296181</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296233</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
@@ -2809,7 +2821,7 @@
       <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/8509e124-5c2f-173b-2502-4d9cd27f9f85/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/bfdc576b-6ce2-9274-914e-8cc9c52c04de/manifest</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr"/>
@@ -2817,48 +2829,52 @@
       <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="inlineStr"/>
       <c r="AH19" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>能面圗譜</t>
+          <t>騁懐帖 2巻 [2]</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>A00:4269</t>
+          <t>A00:6379</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ノウメン ズフ</t>
+          <t>テイカイジョウ</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>芳賀 矢一</t>
+        </is>
+      </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>[製作者不明]</t>
+          <t>芳賀矢一 [ほか自筆]</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>[江戸中期以降]</t>
+          <t>[明治-昭和年間]</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
-          <t>折本|書名は題簽(墨書)による|帙題簽の書名(墨書): 能面圖譜|絹本彩色|図42幅|本紙: 16×13cm|金切箔散し料紙, 福寿文字布目地表紙を使用</t>
+          <t>写本|書名及び巻冊次は題簽による|跋末に「松夲生名ハ百藏東京帝國大學ノ使丁タリ職ヲ山上會議所ニ奉スルコト四十有餘年 ... 頃来マタ諸賢ノ揮毫ヲ乞上名ケテ騁懐帖トイフ ... 帖成リテ予ニ其由来ヲ記セシコトヲ求ム乃チ之ヲ録シテ以テ跋後トス 昭和二年三月 辻善之助識」とあり|折本|書画帖|彩色あり|名録2冊(大和綴)を付す|落款朱印: 「長成」(坪井九馬三), 「圭卿」(市村瓚次郎), 「簣山」(鹽谷時敏), 「維亭」(塚本靖), 「土肥慶藏」, 「忠太」(伊東忠太), 「萬」(和田万吉), 「芳溪」(呉秀三), 「前田慧雲」, 「大澤謙二」, 「南條文雄」, 「有坂氏」(有坂鉊藏), 「博」, 「石亭」(林博太郎), 「長與又郎」, 「宇野哲人」, ほかあり</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2874,12 +2890,12 @@
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/8b3019c4-7584-208c-0c75-7c855ddc0b9e.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/6a4c18fb-90e9-6d15-1234-9cadcc683544.json</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>8b3019c4-7584-208c-0c75-7c855ddc0b9e</t>
+          <t>6a4c18fb-90e9-6d15-1234-9cadcc683544</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -2889,7 +2905,7 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/8b3019c4-7584-208c-0c75-7c855ddc0b9e</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/6a4c18fb-90e9-6d15-1234-9cadcc683544</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
@@ -2899,12 +2915,12 @@
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/3109e43cd273e3e02f2a227b4f1053cc1d4558bb.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/f705bcd1873bb88e3f1edef2b79dcc86dc2c417b.jpg</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296182</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296234</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
@@ -2927,7 +2943,7 @@
       <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/8b3019c4-7584-208c-0c75-7c855ddc0b9e/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/6a4c18fb-90e9-6d15-1234-9cadcc683544/manifest</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr"/>
@@ -2935,40 +2951,40 @@
       <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="inlineStr"/>
       <c r="AH20" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>法蕐經集驗記 2巻</t>
+          <t>清玩書巻</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>A00:4273</t>
+          <t>A00:6380</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ホケキョウ シュウゲンキ</t>
+          <t>セイガン ショカン</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>義寂</t>
+          <t>石黒 忠悳</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>[書写者不明]</t>
+          <t>石黒忠悳 [ほか自筆]</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
-          <t>[平安時代]</t>
+          <t>[明治大正年間]</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2980,7 +2996,7 @@
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
-          <t>鈔本|書名は卷下の巻頭による|大尾の書名: 法蕐集驗記|後付題簽の書名: 法花經集驗記|箱の書名: 法華驗記|卷下の内題下に「并序沙門寂撰」とあり|奥書に「護持僧(花押)夲之」とあり|巻末識語に「嘉應二年庚寅二月十八日傳得之釈子有慶在判」, 「十帋半」とあり|卷上: 諷誦第1. 卷下: 轉讀第2, 書寫第3, 聽聞第4|巻子本|訓点付|卷上の巻頭を欠損|原十紙半を1軸に合綴|朱筆書き入れあり|破損, 虫損あり (裏打ち補修あり)</t>
+          <t>写本|書名は題簽による|その他の筆者: 市村瓚次郎, 外山正一, 緒方正規, 村上専精, 佐藤進, 菊池大麓, 三宅秀, 箕作佳吉, 三上參次, 箕作元八|冒頭に井上哲の題辞「清玩」あり|巻末に萩野由之の識語あり|収集者は『理翰片影』&lt;BC06713253&gt;の跋による|巻子本|往来書簡貼付集|名録1冊(大和綴)を付す|落款朱印: 「文学博士」, 「井上喆」, 「井上哲印」(井上哲次郎), 「和葊」(萩野由之)</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2996,12 +3012,12 @@
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/ec4bceb1-0ab9-74c7-0dc7-f90d0a98a66e.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/ae3b180b-9cbe-6902-48c2-f0abfdf0a27e.json</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>ec4bceb1-0ab9-74c7-0dc7-f90d0a98a66e</t>
+          <t>ae3b180b-9cbe-6902-48c2-f0abfdf0a27e</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -3011,7 +3027,7 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/ec4bceb1-0ab9-74c7-0dc7-f90d0a98a66e</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/ae3b180b-9cbe-6902-48c2-f0abfdf0a27e</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
@@ -3021,12 +3037,12 @@
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/d1c457097d78f2d8a4b38eebd630ef233026cc5e.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/e799186565cb40d919d91c02eef1308118771dd3.jpg</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296183</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296235</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
@@ -3049,7 +3065,7 @@
       <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/ec4bceb1-0ab9-74c7-0dc7-f90d0a98a66e/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/ae3b180b-9cbe-6902-48c2-f0abfdf0a27e/manifest</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr"/>
@@ -3057,36 +3073,40 @@
       <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="inlineStr"/>
       <c r="AH21" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>道成寺</t>
+          <t>聚珍書巻</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>A00:4276</t>
+          <t>A00:6381</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ドウジョウジ</t>
+          <t>シュウチン ショカン</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>浜尾 新</t>
+        </is>
+      </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>[製作者不明]</t>
+          <t>濱尾新 [ほか自筆]</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
-          <t>天明2 [1782] 識語</t>
+          <t>[明治年間]</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -3098,7 +3118,7 @@
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
-          <t>書名は識語による|巻末識語に「道成寺建立年号大長五年三月吉日以後于二百三拾年去テ延長六戊子暦八月十日鐘巻也」, 「時天明二壬寅十月 尚良書之」とあり|絵巻|紙本著色|彩色あり|本紙: 855×28cm|界高: 25.8cm|軸物|軸頭欠損あり|印記: 「尚良印」|破損あり (裏打ち補修あり)</t>
+          <t>写本|書名は題簽による|題辞に「聚珍 明治己酉夏八十三老人成斎題」とあり|巻末識語に「松本百蔵為東亰帝國大學厮養二十餘年毎掃故紙籠見有文字者輒収而弆之頃揀其署名氏者十餘紙装潢成卷皆名賢鉅公碩學鴻儒之筆也 ... 明治庚戌二月初夏 豊城陳人恒書時年七十又二」とあり|その他の筆者: 細川潤次郎, 渡邊洪基, 加藤弘之, 川田剛, 辻新次, 中村正直, 古市公威, 小中村清矩, 木村正辭, 島田重禮|巻子本|往来書簡貼付集|名録1冊(大和綴)を付す|落款朱印: 「晩香」, 「徳天」, 「星野恒印」, 「續古堂」, 「重野」, 「重埜士徳」, 「藤原安繹」</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -3114,12 +3134,12 @@
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/79185d0c-7fa3-2efd-863e-93927e137a23.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/4e78ded3-2829-990e-572b-4b5e029a69cc.json</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>79185d0c-7fa3-2efd-863e-93927e137a23</t>
+          <t>4e78ded3-2829-990e-572b-4b5e029a69cc</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -3129,7 +3149,7 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/79185d0c-7fa3-2efd-863e-93927e137a23</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/4e78ded3-2829-990e-572b-4b5e029a69cc</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
@@ -3139,12 +3159,12 @@
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/0c47939e767d716fe085cc41c86d91be28f9df1a.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/fe6e0e801688014b204ebe9deee8085c19831bc3.jpg</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296184</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296236</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
@@ -3167,7 +3187,7 @@
       <c r="AB22" t="inlineStr"/>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/79185d0c-7fa3-2efd-863e-93927e137a23/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/4e78ded3-2829-990e-572b-4b5e029a69cc/manifest</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr"/>
@@ -3175,52 +3195,52 @@
       <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="inlineStr"/>
       <c r="AH22" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>名家短冊 [1]</t>
+          <t>理翰片影</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>A00:4277</t>
+          <t>A00:6382</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>メイカ タンザク</t>
+          <t>リカン ヘンエイ</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>慶運</t>
+          <t>井上 毅</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>慶運 [ほか自筆]</t>
+          <t>井上毅 [ほか自筆]</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
-          <t>[鎌倉時代-江戸前期]</t>
+          <t>[明治大正年間]</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
-          <t>折本|書名及び巻冊次は題簽による|2の筆者: 慶運 牡丹花, 了流, 宗長, 兼載, 宗碩, 宗牧, 一竿, 正廣, 正般, 祖田, 堯憲, 宗二, 利盛, 増春, 了向, 榮弘, 梅雪, 宗栁, 等惠, 宗訊, 宗養, 乘阿, 兼如, 壽慶, 意運, 本阿彌光悦, 松花堂昭乘, 紹巴, 玄仍, 玄仲, 玄陳, 玄的, 里村玄祥, 昌叱, 昌琢, 昌俔, 昌程, 昌隱, 昌通|3の筆者: 祐守, 祐夏, 詮平, 直國, 興國, 隆國, 武光, 祐範, 宗純, 等貴,  順, 最嶽, 策彦, 幽之, 應其, 堯然, 尊道, 尊應, 尊朝, 道永, 弘覺, 良俊, 道増, 道應, 道興, 藤之, 立承, 性舜, 義俊, 空性, 尊譽, 揚, 道澄, 興意, 道晃|4の筆者: 有三, 他阿, 教, 尊雅, 應猷, 秀順, 可ト, 圓祐, 道順, 実如, 兼俊, 公助, 應祐, 公順, 空慶, 看世, 定信, 玄桂, 道三, 道春, 永喜, 豊永, 葉由, 常弘|2: 古筆切40枚, 極札43枚|3: 古筆切36枚, 極札36枚|4: 古筆切28枚, 極札20枚|毎半面古筆切2枚|原104枚短冊を3帖に合綴|印記: 「順」, 「最嶽」|極印: 「琴山」, 「栄」(古筆了栄)|折り目破損あり</t>
+          <t>写本|書名は題簽による|敘に「松本百藏君我が東京帝國大學に縁故ある諸君の筆蹟を蒐集シ己ニ三卷をなす此卷収む事といわは故子爵井上毅先生をはじめとし神保小虎博士に至るまで十二君の消息なり ... 大正十四年春日三上参次(花押)」とあり|跋に「松本百藏奉職東京帝國大學勞使四十年夙昔不怠其所勤非尋常也大正十四年以古稀辤其軄以平生所収簡牘装潢之得四巻二帖納大學書庫 ... 大正十五年五月於東京帝國大學夲部象軒平野直文識」とあり|その他の筆者: 八代六郎, 垪和爲昌, 鶴田賢次, 長井長義, 久原躬弦, 藤澤利喜太郎, 小藤文次郎, 寺野精一, 青山胤通, 佐藤三吉, 神保小乕|巻子本|往来書簡貼付集|落款朱印: 「士可」, 「虚坣居士」, 「平野直文」</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -3236,12 +3256,12 @@
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/1469b736-a0ee-61aa-1e00-7a2cfa949411.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/31b15e19-44d8-6c52-9780-873a7f1a2480.json</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>1469b736-a0ee-61aa-1e00-7a2cfa949411</t>
+          <t>31b15e19-44d8-6c52-9780-873a7f1a2480</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -3251,7 +3271,7 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/1469b736-a0ee-61aa-1e00-7a2cfa949411</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/31b15e19-44d8-6c52-9780-873a7f1a2480</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
@@ -3261,12 +3281,12 @@
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/7693d9aa48dbd471c84817ef0239807a5e246d64.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/c34f4eff76edef5a959de5048f588d40ac1cccac.jpg</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296185</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296237</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
@@ -3289,7 +3309,7 @@
       <c r="AB23" t="inlineStr"/>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/1469b736-a0ee-61aa-1e00-7a2cfa949411/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/31b15e19-44d8-6c52-9780-873a7f1a2480/manifest</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr"/>
@@ -3297,52 +3317,52 @@
       <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="inlineStr"/>
       <c r="AH23" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>名家短冊 [2]</t>
+          <t>學海拾遺珠</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>A00:4277</t>
+          <t>A00:6383</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>メイカ タンザク</t>
+          <t>ガッカイ シュウイシュ</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>慶運</t>
+          <t>渡辺 渡</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>慶運 [ほか自筆]</t>
+          <t>渡邊渡 [ほか自筆]</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
-          <t>[鎌倉時代-江戸前期]</t>
+          <t>[明治大正年間]</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
-          <t>折本|書名及び巻冊次は題簽による|2の筆者: 慶運 牡丹花, 了流, 宗長, 兼載, 宗碩, 宗牧, 一竿, 正廣, 正般, 祖田, 堯憲, 宗二, 利盛, 増春, 了向, 榮弘, 梅雪, 宗栁, 等惠, 宗訊, 宗養, 乘阿, 兼如, 壽慶, 意運, 本阿彌光悦, 松花堂昭乘, 紹巴, 玄仍, 玄仲, 玄陳, 玄的, 里村玄祥, 昌叱, 昌琢, 昌俔, 昌程, 昌隱, 昌通|3の筆者: 祐守, 祐夏, 詮平, 直國, 興國, 隆國, 武光, 祐範, 宗純, 等貴,  順, 最嶽, 策彦, 幽之, 應其, 堯然, 尊道, 尊應, 尊朝, 道永, 弘覺, 良俊, 道増, 道應, 道興, 藤之, 立承, 性舜, 義俊, 空性, 尊譽, 揚, 道澄, 興意, 道晃|4の筆者: 有三, 他阿, 教, 尊雅, 應猷, 秀順, 可ト, 圓祐, 道順, 実如, 兼俊, 公助, 應祐, 公順, 空慶, 看世, 定信, 玄桂, 道三, 道春, 永喜, 豊永, 葉由, 常弘|2: 古筆切40枚, 極札43枚|3: 古筆切36枚, 極札36枚|4: 古筆切28枚, 極札20枚|毎半面古筆切2枚|原104枚短冊を3帖に合綴|印記: 「順」, 「最嶽」|極印: 「琴山」, 「栄」(古筆了栄)|折り目破損あり</t>
+          <t>写本|書名は題簽による|題辞に「學海拾遺珠 大正十二年初夏 讀律書屋主人題」とあり|巻末識語に「東京帝國大學の地小丘有り丘上に會議所有り總長教授等會食聚議の處と為に松本君其の役たると久し親しく碩學大家に接し之を敬するを知る留意して敗紙中に諸家の手跡を索め嵗月を累収て十数家に及へは輙ち裝潢して卷を成す今や第三卷成り文を予に求む松本君孤影孑然會議所に起臥す伴侶は唯名家手簡と手栽の盆柎有るのみ ... 大正十二年二月十九日 隨軒學人」とあり|その他の筆者: 和田垣謙三, 川瀬善太郎, 高松豊吉, 田中義成, 永井久一郎, 中村恭平, 山川健次郎, 松井直吉, 松村任三, 古在由直, 寺尾寿, 櫻井錠二, 清水彦五郎|巻子本|往来書簡貼付集|名録1冊(大和綴)を付す|落款朱印: 「讀經堂主人號随軒」, 「服部宇之吉印記」, 「直文」(平野直文)</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -3358,12 +3378,12 @@
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/53041b9e-294f-71af-3d1a-e305956f5560.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/9639e5f3-92bd-7423-1bf1-08c4dc087bdf.json</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>53041b9e-294f-71af-3d1a-e305956f5560</t>
+          <t>9639e5f3-92bd-7423-1bf1-08c4dc087bdf</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -3373,7 +3393,7 @@
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/53041b9e-294f-71af-3d1a-e305956f5560</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/9639e5f3-92bd-7423-1bf1-08c4dc087bdf</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
@@ -3383,12 +3403,12 @@
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/11759cf221ad40925619344bacc4027d06e015ce.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/b210fc9854d945b959acd96b0e4fa57d3578ea07.jpg</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296186</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296238</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
@@ -3411,7 +3431,7 @@
       <c r="AB24" t="inlineStr"/>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/53041b9e-294f-71af-3d1a-e305956f5560/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/9639e5f3-92bd-7423-1bf1-08c4dc087bdf/manifest</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr"/>
@@ -3419,52 +3439,52 @@
       <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="inlineStr"/>
       <c r="AH24" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>名家短冊 [3]</t>
+          <t>御成敗式目</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>A00:4277</t>
+          <t>A00:6456</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>メイカ タンザク</t>
+          <t>ゴセイバイ シキモク</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>慶運</t>
+          <t>平泰時 [ほか定]</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>慶運 [ほか自筆]</t>
+          <t>[書写者不明]</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
-          <t>[鎌倉時代-江戸前期]</t>
+          <t>康永2 [1343] 奥書</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
-          <t>折本|書名及び巻冊次は題簽による|2の筆者: 慶運 牡丹花, 了流, 宗長, 兼載, 宗碩, 宗牧, 一竿, 正廣, 正般, 祖田, 堯憲, 宗二, 利盛, 増春, 了向, 榮弘, 梅雪, 宗栁, 等惠, 宗訊, 宗養, 乘阿, 兼如, 壽慶, 意運, 本阿彌光悦, 松花堂昭乘, 紹巴, 玄仍, 玄仲, 玄陳, 玄的, 里村玄祥, 昌叱, 昌琢, 昌俔, 昌程, 昌隱, 昌通|3の筆者: 祐守, 祐夏, 詮平, 直國, 興國, 隆國, 武光, 祐範, 宗純, 等貴,  順, 最嶽, 策彦, 幽之, 應其, 堯然, 尊道, 尊應, 尊朝, 道永, 弘覺, 良俊, 道増, 道應, 道興, 藤之, 立承, 性舜, 義俊, 空性, 尊譽, 揚, 道澄, 興意, 道晃|4の筆者: 有三, 他阿, 教, 尊雅, 應猷, 秀順, 可ト, 圓祐, 道順, 実如, 兼俊, 公助, 應祐, 公順, 空慶, 看世, 定信, 玄桂, 道三, 道春, 永喜, 豊永, 葉由, 常弘|2: 古筆切40枚, 極札43枚|3: 古筆切36枚, 極札36枚|4: 古筆切28枚, 極札20枚|毎半面古筆切2枚|原104枚短冊を3帖に合綴|印記: 「順」, 「最嶽」|極印: 「琴山」, 「栄」(古筆了栄)|折り目破損あり</t>
+          <t>写本|本文末に「貞永元年七月十日 沙弥浄圎/相模大掾藤原業時/玄蕃允三善康連/左衞門少尉藤原朝臣基綱/沙弥行然/散位三善朝臣倫重/加賀守三善朝臣康俊/沙弥行西/前出羽守藤原朝臣家長/前駿河守平義村/前攝津守中原師貟/武蔵守平泰時/相模守平時房」との連署名あり|巻末に「嘉禎三年八月十七日評定之」, 「延應二年五月廾五日評定之」, 「暦仁元年十二月十九日評定之」, 「延應元年九月廾日評定之改嫁事」, 「仁治三十二五評定」, 「嘉禎四年九月二十七日評定之」, 「仁治四二廾五追評定之」, 「延應二年五月廾五日評定之」, 「延應二四廾五評」など追加補抄及び「御式目事」(貞永元八月八日 武蔵守御判/するかの守殿)書簡抄を付す|奥書に「康永二年三月三日於高辻冨小路宿所書冩之訖」とあり|毎葉7行17字注文双行|本文は真字, 送り仮名, 返り点を施し|金砂子散し花菱繋ぎの見返し, 押界を施した楮紙打紙を使用|朱墨筆書き入れあり|軸物(打紙継ぎ)|桐箱入り|印記: 「本立堂記」|汚損, 虫損あり</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -3480,12 +3500,12 @@
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/3d4ceb9b-9516-779a-7ced-f893e9d93b4e.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/1dc60eb8-0dd2-1716-521a-8b436e899759.json</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>3d4ceb9b-9516-779a-7ced-f893e9d93b4e</t>
+          <t>1dc60eb8-0dd2-1716-521a-8b436e899759</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -3495,7 +3515,7 @@
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/3d4ceb9b-9516-779a-7ced-f893e9d93b4e</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/1dc60eb8-0dd2-1716-521a-8b436e899759</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
@@ -3505,12 +3525,12 @@
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/8fd1defea23c7c93fc4d908835c1fea38040580e.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/8182eba23e72331505a8074acdfe6b5481d358fd.jpg</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296187</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296239</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
@@ -3533,7 +3553,7 @@
       <c r="AB25" t="inlineStr"/>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/3d4ceb9b-9516-779a-7ced-f893e9d93b4e/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/1dc60eb8-0dd2-1716-521a-8b436e899759/manifest</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr"/>
@@ -3541,52 +3561,52 @@
       <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="inlineStr"/>
       <c r="AH25" t="n">
-        <v>24</v>
+        <v>45</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>御成敗式目絵鈔</t>
+          <t>辨證配劑醫燈 3巻 [1]</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>A00:4737</t>
+          <t>A00:6517</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ゴセイバイ シキモク エショウ</t>
+          <t>ベンショウ ハイザイ イトウ</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>岡本 竹籔</t>
+          <t>曲直瀬 道三</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>岡夲竹籔 : 松川半山 [書]</t>
+          <t>道三 [自筆]</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
-          <t>[幕末期]</t>
+          <t>元亀2 [1571] 大尾</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
-          <t>写本|序首の書名: 御成敗式目繪鈔|版心の書名: 式目繪鈔|題簽に「板下本」とあり|巻末に「筆工 岡夲竹籔/画工 松川半山」とあり(「岡本」, 「憲道」, 「義卿」, 「翠宋堂長」との落款朱印あり)|巻末広告に「山田賞月堂先生筆 無雙用文章大成 全一冊」とあり|四周単辺有界2段5行, 内匡廓: 22.3×16.4cm, 白口無魚尾|頭書あり|付訓あり</t>
+          <t>写本|巻之2の巻頭書名: 辨證配剤醫燈|大尾に「治病用藥之時欲使侄姪孫一覧如指掌而已/旹元亀第二辛未年冬日南至六十五齢老眼寒窓/日東洛下雖知苦斎盍静翁 道三」とあり|巻末識語に「辨證配劑醫燈全三册壹帙一溪叟道三所親筆也不可忽諸故附一語於後耳」とあり|箱に「和氣道三自書寫配劑醫燈三卷林道春跋之櫻井老人苐一家藏子孫永寶之 葛辰識」との墨書あり|毎半面11行|朱点, 朱引, 朱藍筆書き入れあり|付箋あり|箱入り|印記: 「石堂」, 「昃印」|虫損, 汚損あり</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -3602,12 +3622,12 @@
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/463ab967-60a4-9ff1-3ef2-d2dee79b5315.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/ede81088-3a4b-221d-711c-889d446e8d7e.json</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>463ab967-60a4-9ff1-3ef2-d2dee79b5315</t>
+          <t>ede81088-3a4b-221d-711c-889d446e8d7e</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -3617,7 +3637,7 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/463ab967-60a4-9ff1-3ef2-d2dee79b5315</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/ede81088-3a4b-221d-711c-889d446e8d7e</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
@@ -3627,12 +3647,12 @@
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/e0977d9ba261ea59386ce9f5104a412a5dccaf3f.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/1089675f22f8a9e5e8d856bf42c0b3fa7e2b5168.jpg</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296188</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296240</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
@@ -3655,7 +3675,7 @@
       <c r="AB26" t="inlineStr"/>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/463ab967-60a4-9ff1-3ef2-d2dee79b5315/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/ede81088-3a4b-221d-711c-889d446e8d7e/manifest</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr"/>
@@ -3663,52 +3683,52 @@
       <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="inlineStr"/>
       <c r="AH26" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>金界入壇作法</t>
+          <t>辨證配劑醫燈 3巻 [2]</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>A00:5975</t>
+          <t>A00:6517</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>コンカイ ニュウダン サホウ</t>
+          <t>ベンショウ ハイザイ イトウ</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>良円</t>
+          <t>曲直瀬 道三</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>良円 [写]</t>
+          <t>道三 [自筆]</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
-          <t>寛元元 [1243] 奥書</t>
+          <t>元亀2 [1571] 大尾</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
-          <t>写本|奥書に「寛元々年五月七日以先師法印御夲於常住護国院房以他筆書冩校點了良円」とあり|送り仮名, 返点あり|淡墨界の料紙を使用(界匡廓: 23.7×2.5cm)|貼紙あり|巻子本|箱入り|破損, 虫損あり (裏打ち補修あり)</t>
+          <t>写本|巻之2の巻頭書名: 辨證配剤醫燈|大尾に「治病用藥之時欲使侄姪孫一覧如指掌而已/旹元亀第二辛未年冬日南至六十五齢老眼寒窓/日東洛下雖知苦斎盍静翁 道三」とあり|巻末識語に「辨證配劑醫燈全三册壹帙一溪叟道三所親筆也不可忽諸故附一語於後耳」とあり|箱に「和氣道三自書寫配劑醫燈三卷林道春跋之櫻井老人苐一家藏子孫永寶之 葛辰識」との墨書あり|毎半面11行|朱点, 朱引, 朱藍筆書き入れあり|付箋あり|箱入り|印記: 「石堂」, 「昃印」|虫損, 汚損あり</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -3724,12 +3744,12 @@
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/ff6e2dd7-8128-3264-2081-15ad4e41857e.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/93511b52-3de6-4102-980b-24d00b6c5851.json</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>ff6e2dd7-8128-3264-2081-15ad4e41857e</t>
+          <t>93511b52-3de6-4102-980b-24d00b6c5851</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -3739,7 +3759,7 @@
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/ff6e2dd7-8128-3264-2081-15ad4e41857e</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/93511b52-3de6-4102-980b-24d00b6c5851</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
@@ -3749,12 +3769,12 @@
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/7e2372f45914ea75c8d903fc80f309f16238b39f.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/a82992bab1da44c99dc71e9ac8ef6ff3d626dc4d.jpg</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296189</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296241</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
@@ -3777,7 +3797,7 @@
       <c r="AB27" t="inlineStr"/>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/ff6e2dd7-8128-3264-2081-15ad4e41857e/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/93511b52-3de6-4102-980b-24d00b6c5851/manifest</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr"/>
@@ -3785,52 +3805,52 @@
       <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="inlineStr"/>
       <c r="AH27" t="n">
-        <v>39</v>
+        <v>52</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>玉蘂 [1]</t>
+          <t>辨證配劑醫燈 3巻 [3]</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>A00:6067</t>
+          <t>A00:6517</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ギョクズイ</t>
+          <t>ベンショウ ハイザイ イトウ</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>藤原 道家</t>
+          <t>曲直瀬 道三</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>野宮定基 : 久世通夏 [ほか写]</t>
+          <t>道三 [自筆]</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
-          <t>元禄12 [1699]-宝永3 [1706] 奥書</t>
+          <t>元亀2 [1571] 大尾</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
-          <t>写本|書名及び巻冊次は表紙による|奥中の書名: 光明峯寺禅閤道家公記, 峯禅閤記, 峯摂政記, 峯入道摂政記|承元4年の原奥書に「右即位記一卷者光明峯寺禅閤自筆正記也以件本左令吾基春卿透以写之云々加挍正之 ... 永正七年夷則上浣 從一位(花押)」とあり|奥書に「右以或人夲自常州到来令書写之彼夲端書云此冊上下卷 ... 元禄第十二暦仲夏中旬 羽林左衞中郎将藤原定基丗一才」(承元3), 「右光明峯寺禅閤道家公承元二年三月五六月八月四年二三月九月十十一十二月記は借請或人之夲自常州邊来書写之加一挍了/于時元禄第十二端午節也 左中郎将藤原定基丗才」(承元4), 「右玉蘂建暦元年少弟左中将通清朝臣助筆僅加一挍原本文字不正後来得正夲可改之者也/元禄十三年九月十日 松堂閑士(花押)丗二才」(建暦元), 「右玉蘂峯禅閤記建暦二年自二月至九月一冊以或人夲自常州邊来命家僚令書写手自加挍合了/元禄十二年五月六日 左中郎将藤原定基丗一才」(建暦2年上), 「宝永二年十月一日書写畢/承久二春玉蘂以故常州牧權中納言光圀公夲謄写之于時俗務紛擾先請慈兄源亜相公所被写也今以彼夲手自馳禿筆 余識藤(花押)丗七才/同三年二月廿五日一挍了」(承久2年上), 「右峯摂政承久二年記命傭書謄冩之手自一挍了/元禄第十二嵗次著雍単閼蕤賓中旬 羽林軍左衞中郎将藤原定基丗一才」(承久2年下), 「嘉禎四年正月二月閏二月三月四月六月玉蘂先年假借故常州牧前中納言光圀夲無剋力速遂書写之功建暦元年建暦二年下承久二年上及此卷等先献慈兄亜相君写之今及数年申復彼夲謄写之 ... 宝永三年十二月念日 参議從三位行左近衞權中将藤原朝臣定基生年卅八才」(嘉禎4年)とあり|毎半葉11行注文双行|漢文体日記|拠徳川光圀本及び中院通躬鈔本謄写|朱筆書き入れあり|印記: 「定基」(野宮定基), 「野宮書印」|虫損あり (裏打ち補修あり)</t>
+          <t>写本|巻之2の巻頭書名: 辨證配剤醫燈|大尾に「治病用藥之時欲使侄姪孫一覧如指掌而已/旹元亀第二辛未年冬日南至六十五齢老眼寒窓/日東洛下雖知苦斎盍静翁 道三」とあり|巻末識語に「辨證配劑醫燈全三册壹帙一溪叟道三所親筆也不可忽諸故附一語於後耳」とあり|箱に「和氣道三自書寫配劑醫燈三卷林道春跋之櫻井老人苐一家藏子孫永寶之 葛辰識」との墨書あり|毎半面11行|朱点, 朱引, 朱藍筆書き入れあり|付箋あり|箱入り|印記: 「石堂」, 「昃印」|虫損, 汚損あり</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -3846,12 +3866,12 @@
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/b13a7a09-88d0-62d3-44e5-379780395f17.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/a23dae2e-701a-8d7c-1359-fe786c2e2cdd.json</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>b13a7a09-88d0-62d3-44e5-379780395f17</t>
+          <t>a23dae2e-701a-8d7c-1359-fe786c2e2cdd</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -3861,7 +3881,7 @@
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/b13a7a09-88d0-62d3-44e5-379780395f17</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/a23dae2e-701a-8d7c-1359-fe786c2e2cdd</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
@@ -3871,12 +3891,12 @@
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/f7ae1bd23dec8f323199a9add81e315f1a653d24.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/21b02bac7c065db97c214037acfa4b232d2ddc89.jpg</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296190</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296242</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
@@ -3899,7 +3919,7 @@
       <c r="AB28" t="inlineStr"/>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/b13a7a09-88d0-62d3-44e5-379780395f17/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/a23dae2e-701a-8d7c-1359-fe786c2e2cdd/manifest</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr"/>
@@ -3907,52 +3927,52 @@
       <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="inlineStr"/>
       <c r="AH28" t="n">
-        <v>129</v>
+        <v>63</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>玉蘂 [2]</t>
+          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [16]</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>A00:6067</t>
+          <t>A00:6257</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ギョクズイ</t>
+          <t>レキダイ ザンケツ ニッキ</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>藤原 道家</t>
+          <t>黒川 春村</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>野宮定基 : 久世通夏 [ほか写]</t>
+          <t>[書写者不明]</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
-          <t>元禄12 [1699]-宝永3 [1706] 奥書</t>
+          <t>[安政5 (1858)]</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
-          <t>写本|書名及び巻冊次は表紙による|奥中の書名: 光明峯寺禅閤道家公記, 峯禅閤記, 峯摂政記, 峯入道摂政記|承元4年の原奥書に「右即位記一卷者光明峯寺禅閤自筆正記也以件本左令吾基春卿透以写之云々加挍正之 ... 永正七年夷則上浣 從一位(花押)」とあり|奥書に「右以或人夲自常州到来令書写之彼夲端書云此冊上下卷 ... 元禄第十二暦仲夏中旬 羽林左衞中郎将藤原定基丗一才」(承元3), 「右光明峯寺禅閤道家公承元二年三月五六月八月四年二三月九月十十一十二月記は借請或人之夲自常州邊来書写之加一挍了/于時元禄第十二端午節也 左中郎将藤原定基丗才」(承元4), 「右玉蘂建暦元年少弟左中将通清朝臣助筆僅加一挍原本文字不正後来得正夲可改之者也/元禄十三年九月十日 松堂閑士(花押)丗二才」(建暦元), 「右玉蘂峯禅閤記建暦二年自二月至九月一冊以或人夲自常州邊来命家僚令書写手自加挍合了/元禄十二年五月六日 左中郎将藤原定基丗一才」(建暦2年上), 「宝永二年十月一日書写畢/承久二春玉蘂以故常州牧權中納言光圀公夲謄写之于時俗務紛擾先請慈兄源亜相公所被写也今以彼夲手自馳禿筆 余識藤(花押)丗七才/同三年二月廿五日一挍了」(承久2年上), 「右峯摂政承久二年記命傭書謄冩之手自一挍了/元禄第十二嵗次著雍単閼蕤賓中旬 羽林軍左衞中郎将藤原定基丗一才」(承久2年下), 「嘉禎四年正月二月閏二月三月四月六月玉蘂先年假借故常州牧前中納言光圀夲無剋力速遂書写之功建暦元年建暦二年下承久二年上及此卷等先献慈兄亜相君写之今及数年申復彼夲謄写之 ... 宝永三年十二月念日 参議從三位行左近衞權中将藤原朝臣定基生年卅八才」(嘉禎4年)とあり|毎半葉11行注文双行|漢文体日記|拠徳川光圀本及び中院通躬鈔本謄写|朱筆書き入れあり|印記: 「定基」(野宮定基), 「野宮書印」|虫損あり (裏打ち補修あり)</t>
+          <t>写本|責任表示及び書写年は『日本古典籍総合目録データベース』による|内容: 6: 光明院御記, 後光嚴院御記, 後小松院宸記, 天聴集. 28: 参議藤定長卿記 : 稱山丞記. 37: 定高卿記, 晴御会部類記, 家光卿御記, 權中納言平範輔卿記. 38: 左大史小槻季継記, 後堀川安貞二年放生會(実基公記), 石清水八幡宮, 弁官拝賀次第. 39: 大外記師光記, 資季卿記, 荒凉記, 忠高卿記. 40: 冷泉公相公記, 勝延法眼記 : 東寺大行事, 後中記 : 小路中納言資頼卿記葉室. 41: 中光記, 師兼記, 陽龍記. 42: 大宮司長則記, 口筆 : 實經, 顕朝卿記, 鴨御幸記. 43: 寳治二年記, 深心院關白記, 藤公親記, 照念院関白兼平公記. 44: 頼親記, 亀山殿行幸記 : 雅言卿記, 兼基公記. 45: 大嘗會御禊節下次第, 建治三年丁丑日記 : 三善康有, 建治四年正月廿一日 : 徳大寺大相國公孝記, 冬定卿記, 左大史小槻兼文記|内容: 46: 經任卿記, 前豊前守藤憲説記, 實兼公記. 47: 継塵記抄出. 48: 管見記, 公衡公記, 大外記師顕記, 大外記中原師淳記. 49: 真光院禪助僧正記, 吉田内府卿記. 50: 定清記, 叅議雅俊卿記, 太政大臣(公守公)御上表雜事, 仙洞御灌頂日記, 正安二年八月十一日於仙洞被始行熾盛光法, 正安三年御譲位記. 51: 實躬卿記. 52: 公茂公記, 冬平公記, 隆長卿記. 53: 忠教公記, 官記, 正三位長基卿記, 北面秀長記, 大外記中原師右記. 54: 文保元年, 日野中納言資朝卿記, 洞院大納言公敏卿記. 55: 隆蔭卿記, 文保三年記, 尹大納言師賢卿記, 革命記, 立倚子記, 萬里小路中納言藤藤房卿記|内容: 56: 資名卿記, 公秀公記, 一條家記装束抄出, 頼定卿記. 63: 松亞記, 日野大納言時光卿記, 後八條内府實継公記. 74: 成恩寺関白記. 78: 山科家礼記. 82: 諒闇記 : 後成恩寺殿, 宗典僧正記, 綱光公記, 贈従二位宗賢卿記, 義政公記. 84: 長禄二年戊寅正月, 見聞雜記. 87: 言國卿記. 88: 長興宿祢記, 元長卿記, 兼顕卿記, 小槻晴冨記|28末の原奥書に「右山丞記依 仰挍合書冩/享和二年四月 日撿挍保己一」とあり|50「正安二年八月十一日於仙洞被始行熾盛光法」末の原奥書に「文化十五年春二月以南山法曼院藏夲書冩之 撿挍保己一」とあり|横刷毛目表紙を使用|朱点, 朱引, 朱墨筆書き入れあり|付箋あり|蔵書印主信濃須坂藩主堀直格の命によって編集された古記録|他の原本は関東大震災により焼失|極札に「桂壽」(6), 「尚信」(53)との極書, 「武清」(44, 53), 「永海」(51), 「了伴」(52), 「了甫」(74), 「定時」(84, 88)との極印あり|印記: 「花廼家文庫」, 「墨阪十一代主寫藏記」(堀直格(1806-1880)), 「東京大學法理文學部書庫所藏」, 「閲覧室用 FOR USE IN THE READING ROOM」|虫損あり</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -3968,12 +3988,12 @@
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/20ddaef2-73cc-5ae8-949d-0bdc521924e9.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/31b47601-839e-83b4-6a49-7d11ed020385.json</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>20ddaef2-73cc-5ae8-949d-0bdc521924e9</t>
+          <t>31b47601-839e-83b4-6a49-7d11ed020385</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -3983,7 +4003,7 @@
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/20ddaef2-73cc-5ae8-949d-0bdc521924e9</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/31b47601-839e-83b4-6a49-7d11ed020385</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
@@ -3993,12 +4013,12 @@
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/e2bfc2adbffcfb9eb459e7863108300f2722cdd2.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/d78a0b64be5f71b37b264b3b2eb8172d4e8a5002.jpg</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296191</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296216</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
@@ -4021,7 +4041,7 @@
       <c r="AB29" t="inlineStr"/>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/20ddaef2-73cc-5ae8-949d-0bdc521924e9/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/31b47601-839e-83b4-6a49-7d11ed020385/manifest</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr"/>
@@ -4029,52 +4049,52 @@
       <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="inlineStr"/>
       <c r="AH29" t="n">
-        <v>104</v>
+        <v>58</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>玉蘂 [3]</t>
+          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [15]</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>A00:6067</t>
+          <t>A00:6257</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ギョクズイ</t>
+          <t>レキダイ ザンケツ ニッキ</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>藤原 道家</t>
+          <t>黒川 春村</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>野宮定基 : 久世通夏 [ほか写]</t>
+          <t>[書写者不明]</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
-          <t>元禄12 [1699]-宝永3 [1706] 奥書</t>
+          <t>[安政5 (1858)]</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
-          <t>写本|書名及び巻冊次は表紙による|奥中の書名: 光明峯寺禅閤道家公記, 峯禅閤記, 峯摂政記, 峯入道摂政記|承元4年の原奥書に「右即位記一卷者光明峯寺禅閤自筆正記也以件本左令吾基春卿透以写之云々加挍正之 ... 永正七年夷則上浣 從一位(花押)」とあり|奥書に「右以或人夲自常州到来令書写之彼夲端書云此冊上下卷 ... 元禄第十二暦仲夏中旬 羽林左衞中郎将藤原定基丗一才」(承元3), 「右光明峯寺禅閤道家公承元二年三月五六月八月四年二三月九月十十一十二月記は借請或人之夲自常州邊来書写之加一挍了/于時元禄第十二端午節也 左中郎将藤原定基丗才」(承元4), 「右玉蘂建暦元年少弟左中将通清朝臣助筆僅加一挍原本文字不正後来得正夲可改之者也/元禄十三年九月十日 松堂閑士(花押)丗二才」(建暦元), 「右玉蘂峯禅閤記建暦二年自二月至九月一冊以或人夲自常州邊来命家僚令書写手自加挍合了/元禄十二年五月六日 左中郎将藤原定基丗一才」(建暦2年上), 「宝永二年十月一日書写畢/承久二春玉蘂以故常州牧權中納言光圀公夲謄写之于時俗務紛擾先請慈兄源亜相公所被写也今以彼夲手自馳禿筆 余識藤(花押)丗七才/同三年二月廿五日一挍了」(承久2年上), 「右峯摂政承久二年記命傭書謄冩之手自一挍了/元禄第十二嵗次著雍単閼蕤賓中旬 羽林軍左衞中郎将藤原定基丗一才」(承久2年下), 「嘉禎四年正月二月閏二月三月四月六月玉蘂先年假借故常州牧前中納言光圀夲無剋力速遂書写之功建暦元年建暦二年下承久二年上及此卷等先献慈兄亜相君写之今及数年申復彼夲謄写之 ... 宝永三年十二月念日 参議從三位行左近衞權中将藤原朝臣定基生年卅八才」(嘉禎4年)とあり|毎半葉11行注文双行|漢文体日記|拠徳川光圀本及び中院通躬鈔本謄写|朱筆書き入れあり|印記: 「定基」(野宮定基), 「野宮書印」|虫損あり (裏打ち補修あり)</t>
+          <t>写本|責任表示及び書写年は『日本古典籍総合目録データベース』による|内容: 6: 光明院御記, 後光嚴院御記, 後小松院宸記, 天聴集. 28: 参議藤定長卿記 : 稱山丞記. 37: 定高卿記, 晴御会部類記, 家光卿御記, 權中納言平範輔卿記. 38: 左大史小槻季継記, 後堀川安貞二年放生會(実基公記), 石清水八幡宮, 弁官拝賀次第. 39: 大外記師光記, 資季卿記, 荒凉記, 忠高卿記. 40: 冷泉公相公記, 勝延法眼記 : 東寺大行事, 後中記 : 小路中納言資頼卿記葉室. 41: 中光記, 師兼記, 陽龍記. 42: 大宮司長則記, 口筆 : 實經, 顕朝卿記, 鴨御幸記. 43: 寳治二年記, 深心院關白記, 藤公親記, 照念院関白兼平公記. 44: 頼親記, 亀山殿行幸記 : 雅言卿記, 兼基公記. 45: 大嘗會御禊節下次第, 建治三年丁丑日記 : 三善康有, 建治四年正月廿一日 : 徳大寺大相國公孝記, 冬定卿記, 左大史小槻兼文記|内容: 46: 經任卿記, 前豊前守藤憲説記, 實兼公記. 47: 継塵記抄出. 48: 管見記, 公衡公記, 大外記師顕記, 大外記中原師淳記. 49: 真光院禪助僧正記, 吉田内府卿記. 50: 定清記, 叅議雅俊卿記, 太政大臣(公守公)御上表雜事, 仙洞御灌頂日記, 正安二年八月十一日於仙洞被始行熾盛光法, 正安三年御譲位記. 51: 實躬卿記. 52: 公茂公記, 冬平公記, 隆長卿記. 53: 忠教公記, 官記, 正三位長基卿記, 北面秀長記, 大外記中原師右記. 54: 文保元年, 日野中納言資朝卿記, 洞院大納言公敏卿記. 55: 隆蔭卿記, 文保三年記, 尹大納言師賢卿記, 革命記, 立倚子記, 萬里小路中納言藤藤房卿記|内容: 56: 資名卿記, 公秀公記, 一條家記装束抄出, 頼定卿記. 63: 松亞記, 日野大納言時光卿記, 後八條内府實継公記. 74: 成恩寺関白記. 78: 山科家礼記. 82: 諒闇記 : 後成恩寺殿, 宗典僧正記, 綱光公記, 贈従二位宗賢卿記, 義政公記. 84: 長禄二年戊寅正月, 見聞雜記. 87: 言國卿記. 88: 長興宿祢記, 元長卿記, 兼顕卿記, 小槻晴冨記|28末の原奥書に「右山丞記依 仰挍合書冩/享和二年四月 日撿挍保己一」とあり|50「正安二年八月十一日於仙洞被始行熾盛光法」末の原奥書に「文化十五年春二月以南山法曼院藏夲書冩之 撿挍保己一」とあり|横刷毛目表紙を使用|朱点, 朱引, 朱墨筆書き入れあり|付箋あり|蔵書印主信濃須坂藩主堀直格の命によって編集された古記録|他の原本は関東大震災により焼失|極札に「桂壽」(6), 「尚信」(53)との極書, 「武清」(44, 53), 「永海」(51), 「了伴」(52), 「了甫」(74), 「定時」(84, 88)との極印あり|印記: 「花廼家文庫」, 「墨阪十一代主寫藏記」(堀直格(1806-1880)), 「東京大學法理文學部書庫所藏」, 「閲覧室用 FOR USE IN THE READING ROOM」|虫損あり</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -4090,12 +4110,12 @@
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/7f62eb7a-844c-22ea-196e-998226c991ea.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/acf20dd5-459a-5438-8dd8-cbc11fe122bf.json</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>7f62eb7a-844c-22ea-196e-998226c991ea</t>
+          <t>acf20dd5-459a-5438-8dd8-cbc11fe122bf</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -4105,7 +4125,7 @@
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/7f62eb7a-844c-22ea-196e-998226c991ea</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/acf20dd5-459a-5438-8dd8-cbc11fe122bf</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
@@ -4115,12 +4135,12 @@
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/ac4d01393f2eb0586033bfface43acc61e64021e.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/cfeece07d99889e30589237e6d78b4933a56b7d6.jpg</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296192</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296215</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
@@ -4143,7 +4163,7 @@
       <c r="AB30" t="inlineStr"/>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/7f62eb7a-844c-22ea-196e-998226c991ea/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/acf20dd5-459a-5438-8dd8-cbc11fe122bf/manifest</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr"/>
@@ -4151,52 +4171,52 @@
       <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="inlineStr"/>
       <c r="AH30" t="n">
-        <v>77</v>
+        <v>64</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>玉蘂 [4]</t>
+          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [14]</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>A00:6067</t>
+          <t>A00:6257</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ギョクズイ</t>
+          <t>レキダイ ザンケツ ニッキ</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>藤原 道家</t>
+          <t>黒川 春村</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>野宮定基 : 久世通夏 [ほか写]</t>
+          <t>[書写者不明]</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
-          <t>元禄12 [1699]-宝永3 [1706] 奥書</t>
+          <t>[安政5 (1858)]</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
-          <t>写本|書名及び巻冊次は表紙による|奥中の書名: 光明峯寺禅閤道家公記, 峯禅閤記, 峯摂政記, 峯入道摂政記|承元4年の原奥書に「右即位記一卷者光明峯寺禅閤自筆正記也以件本左令吾基春卿透以写之云々加挍正之 ... 永正七年夷則上浣 從一位(花押)」とあり|奥書に「右以或人夲自常州到来令書写之彼夲端書云此冊上下卷 ... 元禄第十二暦仲夏中旬 羽林左衞中郎将藤原定基丗一才」(承元3), 「右光明峯寺禅閤道家公承元二年三月五六月八月四年二三月九月十十一十二月記は借請或人之夲自常州邊来書写之加一挍了/于時元禄第十二端午節也 左中郎将藤原定基丗才」(承元4), 「右玉蘂建暦元年少弟左中将通清朝臣助筆僅加一挍原本文字不正後来得正夲可改之者也/元禄十三年九月十日 松堂閑士(花押)丗二才」(建暦元), 「右玉蘂峯禅閤記建暦二年自二月至九月一冊以或人夲自常州邊来命家僚令書写手自加挍合了/元禄十二年五月六日 左中郎将藤原定基丗一才」(建暦2年上), 「宝永二年十月一日書写畢/承久二春玉蘂以故常州牧權中納言光圀公夲謄写之于時俗務紛擾先請慈兄源亜相公所被写也今以彼夲手自馳禿筆 余識藤(花押)丗七才/同三年二月廿五日一挍了」(承久2年上), 「右峯摂政承久二年記命傭書謄冩之手自一挍了/元禄第十二嵗次著雍単閼蕤賓中旬 羽林軍左衞中郎将藤原定基丗一才」(承久2年下), 「嘉禎四年正月二月閏二月三月四月六月玉蘂先年假借故常州牧前中納言光圀夲無剋力速遂書写之功建暦元年建暦二年下承久二年上及此卷等先献慈兄亜相君写之今及数年申復彼夲謄写之 ... 宝永三年十二月念日 参議從三位行左近衞權中将藤原朝臣定基生年卅八才」(嘉禎4年)とあり|毎半葉11行注文双行|漢文体日記|拠徳川光圀本及び中院通躬鈔本謄写|朱筆書き入れあり|印記: 「定基」(野宮定基), 「野宮書印」|虫損あり (裏打ち補修あり)</t>
+          <t>写本|責任表示及び書写年は『日本古典籍総合目録データベース』による|内容: 6: 光明院御記, 後光嚴院御記, 後小松院宸記, 天聴集. 28: 参議藤定長卿記 : 稱山丞記. 37: 定高卿記, 晴御会部類記, 家光卿御記, 權中納言平範輔卿記. 38: 左大史小槻季継記, 後堀川安貞二年放生會(実基公記), 石清水八幡宮, 弁官拝賀次第. 39: 大外記師光記, 資季卿記, 荒凉記, 忠高卿記. 40: 冷泉公相公記, 勝延法眼記 : 東寺大行事, 後中記 : 小路中納言資頼卿記葉室. 41: 中光記, 師兼記, 陽龍記. 42: 大宮司長則記, 口筆 : 實經, 顕朝卿記, 鴨御幸記. 43: 寳治二年記, 深心院關白記, 藤公親記, 照念院関白兼平公記. 44: 頼親記, 亀山殿行幸記 : 雅言卿記, 兼基公記. 45: 大嘗會御禊節下次第, 建治三年丁丑日記 : 三善康有, 建治四年正月廿一日 : 徳大寺大相國公孝記, 冬定卿記, 左大史小槻兼文記|内容: 46: 經任卿記, 前豊前守藤憲説記, 實兼公記. 47: 継塵記抄出. 48: 管見記, 公衡公記, 大外記師顕記, 大外記中原師淳記. 49: 真光院禪助僧正記, 吉田内府卿記. 50: 定清記, 叅議雅俊卿記, 太政大臣(公守公)御上表雜事, 仙洞御灌頂日記, 正安二年八月十一日於仙洞被始行熾盛光法, 正安三年御譲位記. 51: 實躬卿記. 52: 公茂公記, 冬平公記, 隆長卿記. 53: 忠教公記, 官記, 正三位長基卿記, 北面秀長記, 大外記中原師右記. 54: 文保元年, 日野中納言資朝卿記, 洞院大納言公敏卿記. 55: 隆蔭卿記, 文保三年記, 尹大納言師賢卿記, 革命記, 立倚子記, 萬里小路中納言藤藤房卿記|内容: 56: 資名卿記, 公秀公記, 一條家記装束抄出, 頼定卿記. 63: 松亞記, 日野大納言時光卿記, 後八條内府實継公記. 74: 成恩寺関白記. 78: 山科家礼記. 82: 諒闇記 : 後成恩寺殿, 宗典僧正記, 綱光公記, 贈従二位宗賢卿記, 義政公記. 84: 長禄二年戊寅正月, 見聞雜記. 87: 言國卿記. 88: 長興宿祢記, 元長卿記, 兼顕卿記, 小槻晴冨記|28末の原奥書に「右山丞記依 仰挍合書冩/享和二年四月 日撿挍保己一」とあり|50「正安二年八月十一日於仙洞被始行熾盛光法」末の原奥書に「文化十五年春二月以南山法曼院藏夲書冩之 撿挍保己一」とあり|横刷毛目表紙を使用|朱点, 朱引, 朱墨筆書き入れあり|付箋あり|蔵書印主信濃須坂藩主堀直格の命によって編集された古記録|他の原本は関東大震災により焼失|極札に「桂壽」(6), 「尚信」(53)との極書, 「武清」(44, 53), 「永海」(51), 「了伴」(52), 「了甫」(74), 「定時」(84, 88)との極印あり|印記: 「花廼家文庫」, 「墨阪十一代主寫藏記」(堀直格(1806-1880)), 「東京大學法理文學部書庫所藏」, 「閲覧室用 FOR USE IN THE READING ROOM」|虫損あり</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -4212,12 +4232,12 @@
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/f48a78a7-0365-73cb-4e46-dd013ef92813.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/a83ab18c-4d05-492c-2121-ec90971ea54a.json</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>f48a78a7-0365-73cb-4e46-dd013ef92813</t>
+          <t>a83ab18c-4d05-492c-2121-ec90971ea54a</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -4227,7 +4247,7 @@
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/f48a78a7-0365-73cb-4e46-dd013ef92813</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/a83ab18c-4d05-492c-2121-ec90971ea54a</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
@@ -4237,12 +4257,12 @@
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/d9d6bd695feea8f0816bee6e991e141accf01cd8.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/b0fe976afebb52b245b298aabead8423fd0d1a6f.jpg</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296193</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296214</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
@@ -4265,7 +4285,7 @@
       <c r="AB31" t="inlineStr"/>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/f48a78a7-0365-73cb-4e46-dd013ef92813/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/a83ab18c-4d05-492c-2121-ec90971ea54a/manifest</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr"/>
@@ -4273,52 +4293,52 @@
       <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="inlineStr"/>
       <c r="AH31" t="n">
-        <v>138</v>
+        <v>59</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>玉蘂 [5]</t>
+          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [12]</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>A00:6067</t>
+          <t>A00:6257</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ギョクズイ</t>
+          <t>レキダイ ザンケツ ニッキ</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>藤原 道家</t>
+          <t>黒川 春村</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>野宮定基 : 久世通夏 [ほか写]</t>
+          <t>[書写者不明]</t>
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr">
         <is>
-          <t>元禄12 [1699]-宝永3 [1706] 奥書</t>
+          <t>[安政5 (1858)]</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
-          <t>写本|書名及び巻冊次は表紙による|奥中の書名: 光明峯寺禅閤道家公記, 峯禅閤記, 峯摂政記, 峯入道摂政記|承元4年の原奥書に「右即位記一卷者光明峯寺禅閤自筆正記也以件本左令吾基春卿透以写之云々加挍正之 ... 永正七年夷則上浣 從一位(花押)」とあり|奥書に「右以或人夲自常州到来令書写之彼夲端書云此冊上下卷 ... 元禄第十二暦仲夏中旬 羽林左衞中郎将藤原定基丗一才」(承元3), 「右光明峯寺禅閤道家公承元二年三月五六月八月四年二三月九月十十一十二月記は借請或人之夲自常州邊来書写之加一挍了/于時元禄第十二端午節也 左中郎将藤原定基丗才」(承元4), 「右玉蘂建暦元年少弟左中将通清朝臣助筆僅加一挍原本文字不正後来得正夲可改之者也/元禄十三年九月十日 松堂閑士(花押)丗二才」(建暦元), 「右玉蘂峯禅閤記建暦二年自二月至九月一冊以或人夲自常州邊来命家僚令書写手自加挍合了/元禄十二年五月六日 左中郎将藤原定基丗一才」(建暦2年上), 「宝永二年十月一日書写畢/承久二春玉蘂以故常州牧權中納言光圀公夲謄写之于時俗務紛擾先請慈兄源亜相公所被写也今以彼夲手自馳禿筆 余識藤(花押)丗七才/同三年二月廿五日一挍了」(承久2年上), 「右峯摂政承久二年記命傭書謄冩之手自一挍了/元禄第十二嵗次著雍単閼蕤賓中旬 羽林軍左衞中郎将藤原定基丗一才」(承久2年下), 「嘉禎四年正月二月閏二月三月四月六月玉蘂先年假借故常州牧前中納言光圀夲無剋力速遂書写之功建暦元年建暦二年下承久二年上及此卷等先献慈兄亜相君写之今及数年申復彼夲謄写之 ... 宝永三年十二月念日 参議從三位行左近衞權中将藤原朝臣定基生年卅八才」(嘉禎4年)とあり|毎半葉11行注文双行|漢文体日記|拠徳川光圀本及び中院通躬鈔本謄写|朱筆書き入れあり|印記: 「定基」(野宮定基), 「野宮書印」|虫損あり (裏打ち補修あり)</t>
+          <t>写本|責任表示及び書写年は『日本古典籍総合目録データベース』による|内容: 6: 光明院御記, 後光嚴院御記, 後小松院宸記, 天聴集. 28: 参議藤定長卿記 : 稱山丞記. 37: 定高卿記, 晴御会部類記, 家光卿御記, 權中納言平範輔卿記. 38: 左大史小槻季継記, 後堀川安貞二年放生會(実基公記), 石清水八幡宮, 弁官拝賀次第. 39: 大外記師光記, 資季卿記, 荒凉記, 忠高卿記. 40: 冷泉公相公記, 勝延法眼記 : 東寺大行事, 後中記 : 小路中納言資頼卿記葉室. 41: 中光記, 師兼記, 陽龍記. 42: 大宮司長則記, 口筆 : 實經, 顕朝卿記, 鴨御幸記. 43: 寳治二年記, 深心院關白記, 藤公親記, 照念院関白兼平公記. 44: 頼親記, 亀山殿行幸記 : 雅言卿記, 兼基公記. 45: 大嘗會御禊節下次第, 建治三年丁丑日記 : 三善康有, 建治四年正月廿一日 : 徳大寺大相國公孝記, 冬定卿記, 左大史小槻兼文記|内容: 46: 經任卿記, 前豊前守藤憲説記, 實兼公記. 47: 継塵記抄出. 48: 管見記, 公衡公記, 大外記師顕記, 大外記中原師淳記. 49: 真光院禪助僧正記, 吉田内府卿記. 50: 定清記, 叅議雅俊卿記, 太政大臣(公守公)御上表雜事, 仙洞御灌頂日記, 正安二年八月十一日於仙洞被始行熾盛光法, 正安三年御譲位記. 51: 實躬卿記. 52: 公茂公記, 冬平公記, 隆長卿記. 53: 忠教公記, 官記, 正三位長基卿記, 北面秀長記, 大外記中原師右記. 54: 文保元年, 日野中納言資朝卿記, 洞院大納言公敏卿記. 55: 隆蔭卿記, 文保三年記, 尹大納言師賢卿記, 革命記, 立倚子記, 萬里小路中納言藤藤房卿記|内容: 56: 資名卿記, 公秀公記, 一條家記装束抄出, 頼定卿記. 63: 松亞記, 日野大納言時光卿記, 後八條内府實継公記. 74: 成恩寺関白記. 78: 山科家礼記. 82: 諒闇記 : 後成恩寺殿, 宗典僧正記, 綱光公記, 贈従二位宗賢卿記, 義政公記. 84: 長禄二年戊寅正月, 見聞雜記. 87: 言國卿記. 88: 長興宿祢記, 元長卿記, 兼顕卿記, 小槻晴冨記|28末の原奥書に「右山丞記依 仰挍合書冩/享和二年四月 日撿挍保己一」とあり|50「正安二年八月十一日於仙洞被始行熾盛光法」末の原奥書に「文化十五年春二月以南山法曼院藏夲書冩之 撿挍保己一」とあり|横刷毛目表紙を使用|朱点, 朱引, 朱墨筆書き入れあり|付箋あり|蔵書印主信濃須坂藩主堀直格の命によって編集された古記録|他の原本は関東大震災により焼失|極札に「桂壽」(6), 「尚信」(53)との極書, 「武清」(44, 53), 「永海」(51), 「了伴」(52), 「了甫」(74), 「定時」(84, 88)との極印あり|印記: 「花廼家文庫」, 「墨阪十一代主寫藏記」(堀直格(1806-1880)), 「東京大學法理文學部書庫所藏」, 「閲覧室用 FOR USE IN THE READING ROOM」|虫損あり</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -4334,12 +4354,12 @@
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/c4ba4bb2-8d3c-7e43-4e3e-e6a6d0c2260f.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/d199046f-6bd4-6ca0-a0bf-c29ad3c19949.json</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>c4ba4bb2-8d3c-7e43-4e3e-e6a6d0c2260f</t>
+          <t>d199046f-6bd4-6ca0-a0bf-c29ad3c19949</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -4349,7 +4369,7 @@
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/c4ba4bb2-8d3c-7e43-4e3e-e6a6d0c2260f</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/d199046f-6bd4-6ca0-a0bf-c29ad3c19949</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
@@ -4359,12 +4379,12 @@
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/58826021e366d49d150087ff3478b98548b97c4a.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/4cbd0825007ec7d3c89014f55d3b6825a8214769.jpg</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296194</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296212</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
@@ -4387,7 +4407,7 @@
       <c r="AB32" t="inlineStr"/>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/c4ba4bb2-8d3c-7e43-4e3e-e6a6d0c2260f/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/d199046f-6bd4-6ca0-a0bf-c29ad3c19949/manifest</t>
         </is>
       </c>
       <c r="AD32" t="inlineStr"/>
@@ -4395,52 +4415,52 @@
       <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="inlineStr"/>
       <c r="AH32" t="n">
-        <v>69</v>
+        <v>77</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>玉蘂 [6]</t>
+          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [13]</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>A00:6067</t>
+          <t>A00:6257</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ギョクズイ</t>
+          <t>レキダイ ザンケツ ニッキ</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>藤原 道家</t>
+          <t>黒川 春村</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>野宮定基 : 久世通夏 [ほか写]</t>
+          <t>[書写者不明]</t>
         </is>
       </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
-          <t>元禄12 [1699]-宝永3 [1706] 奥書</t>
+          <t>[安政5 (1858)]</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
-          <t>写本|書名及び巻冊次は表紙による|奥中の書名: 光明峯寺禅閤道家公記, 峯禅閤記, 峯摂政記, 峯入道摂政記|承元4年の原奥書に「右即位記一卷者光明峯寺禅閤自筆正記也以件本左令吾基春卿透以写之云々加挍正之 ... 永正七年夷則上浣 從一位(花押)」とあり|奥書に「右以或人夲自常州到来令書写之彼夲端書云此冊上下卷 ... 元禄第十二暦仲夏中旬 羽林左衞中郎将藤原定基丗一才」(承元3), 「右光明峯寺禅閤道家公承元二年三月五六月八月四年二三月九月十十一十二月記は借請或人之夲自常州邊来書写之加一挍了/于時元禄第十二端午節也 左中郎将藤原定基丗才」(承元4), 「右玉蘂建暦元年少弟左中将通清朝臣助筆僅加一挍原本文字不正後来得正夲可改之者也/元禄十三年九月十日 松堂閑士(花押)丗二才」(建暦元), 「右玉蘂峯禅閤記建暦二年自二月至九月一冊以或人夲自常州邊来命家僚令書写手自加挍合了/元禄十二年五月六日 左中郎将藤原定基丗一才」(建暦2年上), 「宝永二年十月一日書写畢/承久二春玉蘂以故常州牧權中納言光圀公夲謄写之于時俗務紛擾先請慈兄源亜相公所被写也今以彼夲手自馳禿筆 余識藤(花押)丗七才/同三年二月廿五日一挍了」(承久2年上), 「右峯摂政承久二年記命傭書謄冩之手自一挍了/元禄第十二嵗次著雍単閼蕤賓中旬 羽林軍左衞中郎将藤原定基丗一才」(承久2年下), 「嘉禎四年正月二月閏二月三月四月六月玉蘂先年假借故常州牧前中納言光圀夲無剋力速遂書写之功建暦元年建暦二年下承久二年上及此卷等先献慈兄亜相君写之今及数年申復彼夲謄写之 ... 宝永三年十二月念日 参議從三位行左近衞權中将藤原朝臣定基生年卅八才」(嘉禎4年)とあり|毎半葉11行注文双行|漢文体日記|拠徳川光圀本及び中院通躬鈔本謄写|朱筆書き入れあり|印記: 「定基」(野宮定基), 「野宮書印」|虫損あり (裏打ち補修あり)</t>
+          <t>写本|責任表示及び書写年は『日本古典籍総合目録データベース』による|内容: 6: 光明院御記, 後光嚴院御記, 後小松院宸記, 天聴集. 28: 参議藤定長卿記 : 稱山丞記. 37: 定高卿記, 晴御会部類記, 家光卿御記, 權中納言平範輔卿記. 38: 左大史小槻季継記, 後堀川安貞二年放生會(実基公記), 石清水八幡宮, 弁官拝賀次第. 39: 大外記師光記, 資季卿記, 荒凉記, 忠高卿記. 40: 冷泉公相公記, 勝延法眼記 : 東寺大行事, 後中記 : 小路中納言資頼卿記葉室. 41: 中光記, 師兼記, 陽龍記. 42: 大宮司長則記, 口筆 : 實經, 顕朝卿記, 鴨御幸記. 43: 寳治二年記, 深心院關白記, 藤公親記, 照念院関白兼平公記. 44: 頼親記, 亀山殿行幸記 : 雅言卿記, 兼基公記. 45: 大嘗會御禊節下次第, 建治三年丁丑日記 : 三善康有, 建治四年正月廿一日 : 徳大寺大相國公孝記, 冬定卿記, 左大史小槻兼文記|内容: 46: 經任卿記, 前豊前守藤憲説記, 實兼公記. 47: 継塵記抄出. 48: 管見記, 公衡公記, 大外記師顕記, 大外記中原師淳記. 49: 真光院禪助僧正記, 吉田内府卿記. 50: 定清記, 叅議雅俊卿記, 太政大臣(公守公)御上表雜事, 仙洞御灌頂日記, 正安二年八月十一日於仙洞被始行熾盛光法, 正安三年御譲位記. 51: 實躬卿記. 52: 公茂公記, 冬平公記, 隆長卿記. 53: 忠教公記, 官記, 正三位長基卿記, 北面秀長記, 大外記中原師右記. 54: 文保元年, 日野中納言資朝卿記, 洞院大納言公敏卿記. 55: 隆蔭卿記, 文保三年記, 尹大納言師賢卿記, 革命記, 立倚子記, 萬里小路中納言藤藤房卿記|内容: 56: 資名卿記, 公秀公記, 一條家記装束抄出, 頼定卿記. 63: 松亞記, 日野大納言時光卿記, 後八條内府實継公記. 74: 成恩寺関白記. 78: 山科家礼記. 82: 諒闇記 : 後成恩寺殿, 宗典僧正記, 綱光公記, 贈従二位宗賢卿記, 義政公記. 84: 長禄二年戊寅正月, 見聞雜記. 87: 言國卿記. 88: 長興宿祢記, 元長卿記, 兼顕卿記, 小槻晴冨記|28末の原奥書に「右山丞記依 仰挍合書冩/享和二年四月 日撿挍保己一」とあり|50「正安二年八月十一日於仙洞被始行熾盛光法」末の原奥書に「文化十五年春二月以南山法曼院藏夲書冩之 撿挍保己一」とあり|横刷毛目表紙を使用|朱点, 朱引, 朱墨筆書き入れあり|付箋あり|蔵書印主信濃須坂藩主堀直格の命によって編集された古記録|他の原本は関東大震災により焼失|極札に「桂壽」(6), 「尚信」(53)との極書, 「武清」(44, 53), 「永海」(51), 「了伴」(52), 「了甫」(74), 「定時」(84, 88)との極印あり|印記: 「花廼家文庫」, 「墨阪十一代主寫藏記」(堀直格(1806-1880)), 「東京大學法理文學部書庫所藏」, 「閲覧室用 FOR USE IN THE READING ROOM」|虫損あり</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -4456,12 +4476,12 @@
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/73dc1d4b-7872-a0a3-780c-3c10d2a3758a.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/1b5c5c7f-4892-39f9-4e5e-479a8e921be2.json</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>73dc1d4b-7872-a0a3-780c-3c10d2a3758a</t>
+          <t>1b5c5c7f-4892-39f9-4e5e-479a8e921be2</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -4471,7 +4491,7 @@
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/73dc1d4b-7872-a0a3-780c-3c10d2a3758a</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/1b5c5c7f-4892-39f9-4e5e-479a8e921be2</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
@@ -4481,12 +4501,12 @@
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/6724525552ca8e3c1f42cdc0f0674a54828dc026.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/95aeca9c3732100e9d926fc7a9cb98fba20b6444.jpg</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296195</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296213</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
@@ -4509,7 +4529,7 @@
       <c r="AB33" t="inlineStr"/>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/73dc1d4b-7872-a0a3-780c-3c10d2a3758a/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/1b5c5c7f-4892-39f9-4e5e-479a8e921be2/manifest</t>
         </is>
       </c>
       <c r="AD33" t="inlineStr"/>
@@ -4517,52 +4537,48 @@
       <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="inlineStr"/>
       <c r="AH33" t="n">
-        <v>106</v>
+        <v>74</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>玉蘂 [7]</t>
+          <t>大嘗會悠紀主基鮮味之繪</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>A00:6067</t>
+          <t>A00:6108</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ギョクズイ</t>
+          <t>ダイジョウエ ユキ スキ センミ ノ ズ</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>藤原 道家</t>
-        </is>
-      </c>
+      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>野宮定基 : 久世通夏 [ほか写]</t>
+          <t>[佐伯]</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
-          <t>元禄12 [1699]-宝永3 [1706] 奥書</t>
+          <t>明和元 [1764] 識語</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
-          <t>写本|書名及び巻冊次は表紙による|奥中の書名: 光明峯寺禅閤道家公記, 峯禅閤記, 峯摂政記, 峯入道摂政記|承元4年の原奥書に「右即位記一卷者光明峯寺禅閤自筆正記也以件本左令吾基春卿透以写之云々加挍正之 ... 永正七年夷則上浣 從一位(花押)」とあり|奥書に「右以或人夲自常州到来令書写之彼夲端書云此冊上下卷 ... 元禄第十二暦仲夏中旬 羽林左衞中郎将藤原定基丗一才」(承元3), 「右光明峯寺禅閤道家公承元二年三月五六月八月四年二三月九月十十一十二月記は借請或人之夲自常州邊来書写之加一挍了/于時元禄第十二端午節也 左中郎将藤原定基丗才」(承元4), 「右玉蘂建暦元年少弟左中将通清朝臣助筆僅加一挍原本文字不正後来得正夲可改之者也/元禄十三年九月十日 松堂閑士(花押)丗二才」(建暦元), 「右玉蘂峯禅閤記建暦二年自二月至九月一冊以或人夲自常州邊来命家僚令書写手自加挍合了/元禄十二年五月六日 左中郎将藤原定基丗一才」(建暦2年上), 「宝永二年十月一日書写畢/承久二春玉蘂以故常州牧權中納言光圀公夲謄写之于時俗務紛擾先請慈兄源亜相公所被写也今以彼夲手自馳禿筆 余識藤(花押)丗七才/同三年二月廿五日一挍了」(承久2年上), 「右峯摂政承久二年記命傭書謄冩之手自一挍了/元禄第十二嵗次著雍単閼蕤賓中旬 羽林軍左衞中郎将藤原定基丗一才」(承久2年下), 「嘉禎四年正月二月閏二月三月四月六月玉蘂先年假借故常州牧前中納言光圀夲無剋力速遂書写之功建暦元年建暦二年下承久二年上及此卷等先献慈兄亜相君写之今及数年申復彼夲謄写之 ... 宝永三年十二月念日 参議從三位行左近衞權中将藤原朝臣定基生年卅八才」(嘉禎4年)とあり|毎半葉11行注文双行|漢文体日記|拠徳川光圀本及び中院通躬鈔本謄写|朱筆書き入れあり|印記: 「定基」(野宮定基), 「野宮書印」|虫損あり (裏打ち補修あり)</t>
+          <t>絵巻|書名は識語による|書袋の書名: 悠紀主基鮮味之啚|表紙裏に「元文悠紀主基鮮味之圖 寛延同」とあり|巻末の識語に「右大嘗會悠紀主基鮮味之繪借請御厨子所預紀宗直朝臣令佐伯職房摸冩之畢 明和元年孟冬左少将藤原(花押)」とあり|絵4幅: 梅作枝, 糸作枩, 萩作枝, 萩作枝|紙本著色|彩色あり|帙入り|印記: 「野宮藏書」</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -4578,12 +4594,12 @@
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/e775ea12-9867-70f2-6381-112e31478f75.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/d00e906c-5404-4fc1-44c9-1566cf7f7012.json</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>e775ea12-9867-70f2-6381-112e31478f75</t>
+          <t>d00e906c-5404-4fc1-44c9-1566cf7f7012</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -4593,7 +4609,7 @@
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/e775ea12-9867-70f2-6381-112e31478f75</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/d00e906c-5404-4fc1-44c9-1566cf7f7012</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
@@ -4603,12 +4619,12 @@
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/08e58358a211a53638e77e5431d7fedb34bd5f72.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/51e8aa982b380211852796b36819e6c6c6bf1583.jpg</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296196</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296199</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
@@ -4631,7 +4647,7 @@
       <c r="AB34" t="inlineStr"/>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/e775ea12-9867-70f2-6381-112e31478f75/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/d00e906c-5404-4fc1-44c9-1566cf7f7012/manifest</t>
         </is>
       </c>
       <c r="AD34" t="inlineStr"/>
@@ -4639,52 +4655,48 @@
       <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="inlineStr"/>
       <c r="AH34" t="n">
-        <v>146</v>
+        <v>11</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>玉蘂 [8]</t>
+          <t>真言宗脈啚 : 栂尾夲</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>A00:6067</t>
+          <t>A00:6129</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>ギョクズイ</t>
+          <t>シンゴンシュウ ミャクズ : トガノオボン</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>藤原 道家</t>
-        </is>
-      </c>
+      <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>野宮定基 : 久世通夏 [ほか写]</t>
+          <t>覺心</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
-          <t>元禄12 [1699]-宝永3 [1706] 奥書</t>
+          <t>享保9 [1724] 奥書</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
-          <t>写本|書名及び巻冊次は表紙による|奥中の書名: 光明峯寺禅閤道家公記, 峯禅閤記, 峯摂政記, 峯入道摂政記|承元4年の原奥書に「右即位記一卷者光明峯寺禅閤自筆正記也以件本左令吾基春卿透以写之云々加挍正之 ... 永正七年夷則上浣 從一位(花押)」とあり|奥書に「右以或人夲自常州到来令書写之彼夲端書云此冊上下卷 ... 元禄第十二暦仲夏中旬 羽林左衞中郎将藤原定基丗一才」(承元3), 「右光明峯寺禅閤道家公承元二年三月五六月八月四年二三月九月十十一十二月記は借請或人之夲自常州邊来書写之加一挍了/于時元禄第十二端午節也 左中郎将藤原定基丗才」(承元4), 「右玉蘂建暦元年少弟左中将通清朝臣助筆僅加一挍原本文字不正後来得正夲可改之者也/元禄十三年九月十日 松堂閑士(花押)丗二才」(建暦元), 「右玉蘂峯禅閤記建暦二年自二月至九月一冊以或人夲自常州邊来命家僚令書写手自加挍合了/元禄十二年五月六日 左中郎将藤原定基丗一才」(建暦2年上), 「宝永二年十月一日書写畢/承久二春玉蘂以故常州牧權中納言光圀公夲謄写之于時俗務紛擾先請慈兄源亜相公所被写也今以彼夲手自馳禿筆 余識藤(花押)丗七才/同三年二月廿五日一挍了」(承久2年上), 「右峯摂政承久二年記命傭書謄冩之手自一挍了/元禄第十二嵗次著雍単閼蕤賓中旬 羽林軍左衞中郎将藤原定基丗一才」(承久2年下), 「嘉禎四年正月二月閏二月三月四月六月玉蘂先年假借故常州牧前中納言光圀夲無剋力速遂書写之功建暦元年建暦二年下承久二年上及此卷等先献慈兄亜相君写之今及数年申復彼夲謄写之 ... 宝永三年十二月念日 参議從三位行左近衞權中将藤原朝臣定基生年卅八才」(嘉禎4年)とあり|毎半葉11行注文双行|漢文体日記|拠徳川光圀本及び中院通躬鈔本謄写|朱筆書き入れあり|印記: 「定基」(野宮定基), 「野宮書印」|虫損あり (裏打ち補修あり)</t>
+          <t>写本|書名は題簽による|帙題簽の書名: 真言宗血脈圗|奥書に「正徳二年之春請自性院僧正開栂尾山宮御封之經藏求淂于古聖教若干部是其一也 沙門道空」, 「享保九年甲辰夏寓于洛西御阜草菴以五智山之本冩之訖 南紀護国寺沙門覺心/同年六月晦日以栂尾法鼓臺古本挍合之了」, 「昭和八年四月念三日閲覧砌訂正誤字記入落罫云尒 中野達慧識」とあり|朱筆書き入れあり|印記: 「和學講談所」, 「温故堂文庫」(塙家), 「松平家藏書印」|虫損あり</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -4700,12 +4712,12 @@
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/ca2da620-345c-76fa-9d1d-e7b2c55d757f.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/e6a30e98-5da6-7e0d-7a92-5b26c887309f.json</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>ca2da620-345c-76fa-9d1d-e7b2c55d757f</t>
+          <t>e6a30e98-5da6-7e0d-7a92-5b26c887309f</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -4715,7 +4727,7 @@
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/ca2da620-345c-76fa-9d1d-e7b2c55d757f</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/e6a30e98-5da6-7e0d-7a92-5b26c887309f</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
@@ -4725,12 +4737,12 @@
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/8204e28b4e8f0e2f8abc1b939244f007093f3749.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/10842787f14673fb3729595dd908dde4c4dd6ad8.jpg</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296197</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296200</t>
         </is>
       </c>
       <c r="W35" t="inlineStr">
@@ -4753,7 +4765,7 @@
       <c r="AB35" t="inlineStr"/>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/ca2da620-345c-76fa-9d1d-e7b2c55d757f/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/e6a30e98-5da6-7e0d-7a92-5b26c887309f/manifest</t>
         </is>
       </c>
       <c r="AD35" t="inlineStr"/>
@@ -4761,27 +4773,31 @@
       <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="inlineStr"/>
       <c r="AH35" t="n">
-        <v>63</v>
+        <v>22</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>大明星天子法 : 又名法界虚空蔵法</t>
+          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [1]</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>A00:6097</t>
+          <t>A00:6257</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ダイミョウジョウテンシホウ : マタミョウ ホッカイ コクウゾウホウ</t>
+          <t>レキダイ ザンケツ ニッキ</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>黒川 春村</t>
+        </is>
+      </c>
       <c r="F36" t="inlineStr">
         <is>
           <t>[書写者不明]</t>
@@ -4790,7 +4806,7 @@
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr">
         <is>
-          <t>[天文年間]</t>
+          <t>[安政5 (1858)]</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -4802,7 +4818,7 @@
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
-          <t>写本|巻末の書名: 明星天子法|表紙の書名: 大明皇天子水|大尾に「明星天子法次苐 一交了」とあり|本奥書に「承久三年五月十三日/爲興法利生徃生極樂書冩之/金剛佛子觀照之」とあり|書袋に「天文古筆」, 「天明七未ノ年」とあり|毎半葉8行|押界を施した楮紙打紙を使用|粘葉装|虫損あり</t>
+          <t>写本|責任表示及び書写年は『日本古典籍総合目録データベース』による|内容: 6: 光明院御記, 後光嚴院御記, 後小松院宸記, 天聴集. 28: 参議藤定長卿記 : 稱山丞記. 37: 定高卿記, 晴御会部類記, 家光卿御記, 權中納言平範輔卿記. 38: 左大史小槻季継記, 後堀川安貞二年放生會(実基公記), 石清水八幡宮, 弁官拝賀次第. 39: 大外記師光記, 資季卿記, 荒凉記, 忠高卿記. 40: 冷泉公相公記, 勝延法眼記 : 東寺大行事, 後中記 : 小路中納言資頼卿記葉室. 41: 中光記, 師兼記, 陽龍記. 42: 大宮司長則記, 口筆 : 實經, 顕朝卿記, 鴨御幸記. 43: 寳治二年記, 深心院關白記, 藤公親記, 照念院関白兼平公記. 44: 頼親記, 亀山殿行幸記 : 雅言卿記, 兼基公記. 45: 大嘗會御禊節下次第, 建治三年丁丑日記 : 三善康有, 建治四年正月廿一日 : 徳大寺大相國公孝記, 冬定卿記, 左大史小槻兼文記|内容: 46: 經任卿記, 前豊前守藤憲説記, 實兼公記. 47: 継塵記抄出. 48: 管見記, 公衡公記, 大外記師顕記, 大外記中原師淳記. 49: 真光院禪助僧正記, 吉田内府卿記. 50: 定清記, 叅議雅俊卿記, 太政大臣(公守公)御上表雜事, 仙洞御灌頂日記, 正安二年八月十一日於仙洞被始行熾盛光法, 正安三年御譲位記. 51: 實躬卿記. 52: 公茂公記, 冬平公記, 隆長卿記. 53: 忠教公記, 官記, 正三位長基卿記, 北面秀長記, 大外記中原師右記. 54: 文保元年, 日野中納言資朝卿記, 洞院大納言公敏卿記. 55: 隆蔭卿記, 文保三年記, 尹大納言師賢卿記, 革命記, 立倚子記, 萬里小路中納言藤藤房卿記|内容: 56: 資名卿記, 公秀公記, 一條家記装束抄出, 頼定卿記. 63: 松亞記, 日野大納言時光卿記, 後八條内府實継公記. 74: 成恩寺関白記. 78: 山科家礼記. 82: 諒闇記 : 後成恩寺殿, 宗典僧正記, 綱光公記, 贈従二位宗賢卿記, 義政公記. 84: 長禄二年戊寅正月, 見聞雜記. 87: 言國卿記. 88: 長興宿祢記, 元長卿記, 兼顕卿記, 小槻晴冨記|28末の原奥書に「右山丞記依 仰挍合書冩/享和二年四月 日撿挍保己一」とあり|50「正安二年八月十一日於仙洞被始行熾盛光法」末の原奥書に「文化十五年春二月以南山法曼院藏夲書冩之 撿挍保己一」とあり|横刷毛目表紙を使用|朱点, 朱引, 朱墨筆書き入れあり|付箋あり|蔵書印主信濃須坂藩主堀直格の命によって編集された古記録|他の原本は関東大震災により焼失|極札に「桂壽」(6), 「尚信」(53)との極書, 「武清」(44, 53), 「永海」(51), 「了伴」(52), 「了甫」(74), 「定時」(84, 88)との極印あり|印記: 「花廼家文庫」, 「墨阪十一代主寫藏記」(堀直格(1806-1880)), 「東京大學法理文學部書庫所藏」, 「閲覧室用 FOR USE IN THE READING ROOM」|虫損あり</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -4818,12 +4834,12 @@
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/a1905fc7-4727-0750-41d7-f0ca1df53f47.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/c32632af-9dc0-504a-5437-15a055d52628.json</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>a1905fc7-4727-0750-41d7-f0ca1df53f47</t>
+          <t>c32632af-9dc0-504a-5437-15a055d52628</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -4833,7 +4849,7 @@
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/a1905fc7-4727-0750-41d7-f0ca1df53f47</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/c32632af-9dc0-504a-5437-15a055d52628</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
@@ -4843,12 +4859,12 @@
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/b2590ef4e55f582d8059a5e072e1d6dad33bf996.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/2230dfedd3d91cc8b1c5532de33a8f8559be8357.jpg</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296198</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296201</t>
         </is>
       </c>
       <c r="W36" t="inlineStr">
@@ -4871,7 +4887,7 @@
       <c r="AB36" t="inlineStr"/>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/a1905fc7-4727-0750-41d7-f0ca1df53f47/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/c32632af-9dc0-504a-5437-15a055d52628/manifest</t>
         </is>
       </c>
       <c r="AD36" t="inlineStr"/>
@@ -4879,36 +4895,40 @@
       <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="inlineStr"/>
       <c r="AH36" t="n">
-        <v>9</v>
+        <v>72</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>大嘗會悠紀主基鮮味之繪</t>
+          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [2]</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>A00:6108</t>
+          <t>A00:6257</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ダイジョウエ ユキ スキ センミ ノ ズ</t>
+          <t>レキダイ ザンケツ ニッキ</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>黒川 春村</t>
+        </is>
+      </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>[佐伯]</t>
+          <t>[書写者不明]</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
-          <t>明和元 [1764] 識語</t>
+          <t>[安政5 (1858)]</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -4920,7 +4940,7 @@
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
-          <t>絵巻|書名は識語による|書袋の書名: 悠紀主基鮮味之啚|表紙裏に「元文悠紀主基鮮味之圖 寛延同」とあり|巻末の識語に「右大嘗會悠紀主基鮮味之繪借請御厨子所預紀宗直朝臣令佐伯職房摸冩之畢 明和元年孟冬左少将藤原(花押)」とあり|絵4幅: 梅作枝, 糸作枩, 萩作枝, 萩作枝|紙本著色|彩色あり|帙入り|印記: 「野宮藏書」</t>
+          <t>写本|責任表示及び書写年は『日本古典籍総合目録データベース』による|内容: 6: 光明院御記, 後光嚴院御記, 後小松院宸記, 天聴集. 28: 参議藤定長卿記 : 稱山丞記. 37: 定高卿記, 晴御会部類記, 家光卿御記, 權中納言平範輔卿記. 38: 左大史小槻季継記, 後堀川安貞二年放生會(実基公記), 石清水八幡宮, 弁官拝賀次第. 39: 大外記師光記, 資季卿記, 荒凉記, 忠高卿記. 40: 冷泉公相公記, 勝延法眼記 : 東寺大行事, 後中記 : 小路中納言資頼卿記葉室. 41: 中光記, 師兼記, 陽龍記. 42: 大宮司長則記, 口筆 : 實經, 顕朝卿記, 鴨御幸記. 43: 寳治二年記, 深心院關白記, 藤公親記, 照念院関白兼平公記. 44: 頼親記, 亀山殿行幸記 : 雅言卿記, 兼基公記. 45: 大嘗會御禊節下次第, 建治三年丁丑日記 : 三善康有, 建治四年正月廿一日 : 徳大寺大相國公孝記, 冬定卿記, 左大史小槻兼文記|内容: 46: 經任卿記, 前豊前守藤憲説記, 實兼公記. 47: 継塵記抄出. 48: 管見記, 公衡公記, 大外記師顕記, 大外記中原師淳記. 49: 真光院禪助僧正記, 吉田内府卿記. 50: 定清記, 叅議雅俊卿記, 太政大臣(公守公)御上表雜事, 仙洞御灌頂日記, 正安二年八月十一日於仙洞被始行熾盛光法, 正安三年御譲位記. 51: 實躬卿記. 52: 公茂公記, 冬平公記, 隆長卿記. 53: 忠教公記, 官記, 正三位長基卿記, 北面秀長記, 大外記中原師右記. 54: 文保元年, 日野中納言資朝卿記, 洞院大納言公敏卿記. 55: 隆蔭卿記, 文保三年記, 尹大納言師賢卿記, 革命記, 立倚子記, 萬里小路中納言藤藤房卿記|内容: 56: 資名卿記, 公秀公記, 一條家記装束抄出, 頼定卿記. 63: 松亞記, 日野大納言時光卿記, 後八條内府實継公記. 74: 成恩寺関白記. 78: 山科家礼記. 82: 諒闇記 : 後成恩寺殿, 宗典僧正記, 綱光公記, 贈従二位宗賢卿記, 義政公記. 84: 長禄二年戊寅正月, 見聞雜記. 87: 言國卿記. 88: 長興宿祢記, 元長卿記, 兼顕卿記, 小槻晴冨記|28末の原奥書に「右山丞記依 仰挍合書冩/享和二年四月 日撿挍保己一」とあり|50「正安二年八月十一日於仙洞被始行熾盛光法」末の原奥書に「文化十五年春二月以南山法曼院藏夲書冩之 撿挍保己一」とあり|横刷毛目表紙を使用|朱点, 朱引, 朱墨筆書き入れあり|付箋あり|蔵書印主信濃須坂藩主堀直格の命によって編集された古記録|他の原本は関東大震災により焼失|極札に「桂壽」(6), 「尚信」(53)との極書, 「武清」(44, 53), 「永海」(51), 「了伴」(52), 「了甫」(74), 「定時」(84, 88)との極印あり|印記: 「花廼家文庫」, 「墨阪十一代主寫藏記」(堀直格(1806-1880)), 「東京大學法理文學部書庫所藏」, 「閲覧室用 FOR USE IN THE READING ROOM」|虫損あり</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -4936,12 +4956,12 @@
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/d00e906c-5404-4fc1-44c9-1566cf7f7012.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/f31d474b-60bb-5efd-a570-d8f971a97e5e.json</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>d00e906c-5404-4fc1-44c9-1566cf7f7012</t>
+          <t>f31d474b-60bb-5efd-a570-d8f971a97e5e</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
@@ -4951,7 +4971,7 @@
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/d00e906c-5404-4fc1-44c9-1566cf7f7012</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/f31d474b-60bb-5efd-a570-d8f971a97e5e</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
@@ -4961,12 +4981,12 @@
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/51e8aa982b380211852796b36819e6c6c6bf1583.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/378909456e17de7b588873b8890cd6945bba3cc8.jpg</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296199</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296202</t>
         </is>
       </c>
       <c r="W37" t="inlineStr">
@@ -4989,7 +5009,7 @@
       <c r="AB37" t="inlineStr"/>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/d00e906c-5404-4fc1-44c9-1566cf7f7012/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/f31d474b-60bb-5efd-a570-d8f971a97e5e/manifest</t>
         </is>
       </c>
       <c r="AD37" t="inlineStr"/>
@@ -4997,36 +5017,40 @@
       <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="inlineStr"/>
       <c r="AH37" t="n">
-        <v>11</v>
+        <v>75</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>真言宗脈啚 : 栂尾夲</t>
+          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [3]</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>A00:6129</t>
+          <t>A00:6257</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>シンゴンシュウ ミャクズ : トガノオボン</t>
+          <t>レキダイ ザンケツ ニッキ</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>黒川 春村</t>
+        </is>
+      </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>覺心</t>
+          <t>[書写者不明]</t>
         </is>
       </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
-          <t>享保9 [1724] 奥書</t>
+          <t>[安政5 (1858)]</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -5038,7 +5062,7 @@
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
         <is>
-          <t>写本|書名は題簽による|帙題簽の書名: 真言宗血脈圗|奥書に「正徳二年之春請自性院僧正開栂尾山宮御封之經藏求淂于古聖教若干部是其一也 沙門道空」, 「享保九年甲辰夏寓于洛西御阜草菴以五智山之本冩之訖 南紀護国寺沙門覺心/同年六月晦日以栂尾法鼓臺古本挍合之了」, 「昭和八年四月念三日閲覧砌訂正誤字記入落罫云尒 中野達慧識」とあり|朱筆書き入れあり|印記: 「和學講談所」, 「温故堂文庫」(塙家), 「松平家藏書印」|虫損あり</t>
+          <t>写本|責任表示及び書写年は『日本古典籍総合目録データベース』による|内容: 6: 光明院御記, 後光嚴院御記, 後小松院宸記, 天聴集. 28: 参議藤定長卿記 : 稱山丞記. 37: 定高卿記, 晴御会部類記, 家光卿御記, 權中納言平範輔卿記. 38: 左大史小槻季継記, 後堀川安貞二年放生會(実基公記), 石清水八幡宮, 弁官拝賀次第. 39: 大外記師光記, 資季卿記, 荒凉記, 忠高卿記. 40: 冷泉公相公記, 勝延法眼記 : 東寺大行事, 後中記 : 小路中納言資頼卿記葉室. 41: 中光記, 師兼記, 陽龍記. 42: 大宮司長則記, 口筆 : 實經, 顕朝卿記, 鴨御幸記. 43: 寳治二年記, 深心院關白記, 藤公親記, 照念院関白兼平公記. 44: 頼親記, 亀山殿行幸記 : 雅言卿記, 兼基公記. 45: 大嘗會御禊節下次第, 建治三年丁丑日記 : 三善康有, 建治四年正月廿一日 : 徳大寺大相國公孝記, 冬定卿記, 左大史小槻兼文記|内容: 46: 經任卿記, 前豊前守藤憲説記, 實兼公記. 47: 継塵記抄出. 48: 管見記, 公衡公記, 大外記師顕記, 大外記中原師淳記. 49: 真光院禪助僧正記, 吉田内府卿記. 50: 定清記, 叅議雅俊卿記, 太政大臣(公守公)御上表雜事, 仙洞御灌頂日記, 正安二年八月十一日於仙洞被始行熾盛光法, 正安三年御譲位記. 51: 實躬卿記. 52: 公茂公記, 冬平公記, 隆長卿記. 53: 忠教公記, 官記, 正三位長基卿記, 北面秀長記, 大外記中原師右記. 54: 文保元年, 日野中納言資朝卿記, 洞院大納言公敏卿記. 55: 隆蔭卿記, 文保三年記, 尹大納言師賢卿記, 革命記, 立倚子記, 萬里小路中納言藤藤房卿記|内容: 56: 資名卿記, 公秀公記, 一條家記装束抄出, 頼定卿記. 63: 松亞記, 日野大納言時光卿記, 後八條内府實継公記. 74: 成恩寺関白記. 78: 山科家礼記. 82: 諒闇記 : 後成恩寺殿, 宗典僧正記, 綱光公記, 贈従二位宗賢卿記, 義政公記. 84: 長禄二年戊寅正月, 見聞雜記. 87: 言國卿記. 88: 長興宿祢記, 元長卿記, 兼顕卿記, 小槻晴冨記|28末の原奥書に「右山丞記依 仰挍合書冩/享和二年四月 日撿挍保己一」とあり|50「正安二年八月十一日於仙洞被始行熾盛光法」末の原奥書に「文化十五年春二月以南山法曼院藏夲書冩之 撿挍保己一」とあり|横刷毛目表紙を使用|朱点, 朱引, 朱墨筆書き入れあり|付箋あり|蔵書印主信濃須坂藩主堀直格の命によって編集された古記録|他の原本は関東大震災により焼失|極札に「桂壽」(6), 「尚信」(53)との極書, 「武清」(44, 53), 「永海」(51), 「了伴」(52), 「了甫」(74), 「定時」(84, 88)との極印あり|印記: 「花廼家文庫」, 「墨阪十一代主寫藏記」(堀直格(1806-1880)), 「東京大學法理文學部書庫所藏」, 「閲覧室用 FOR USE IN THE READING ROOM」|虫損あり</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -5054,12 +5078,12 @@
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/e6a30e98-5da6-7e0d-7a92-5b26c887309f.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/0ddf4bea-7e5d-145a-1812-20986271091f.json</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>e6a30e98-5da6-7e0d-7a92-5b26c887309f</t>
+          <t>0ddf4bea-7e5d-145a-1812-20986271091f</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
@@ -5069,7 +5093,7 @@
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/e6a30e98-5da6-7e0d-7a92-5b26c887309f</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/0ddf4bea-7e5d-145a-1812-20986271091f</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
@@ -5079,12 +5103,12 @@
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/10842787f14673fb3729595dd908dde4c4dd6ad8.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/f1d109214b4c636205f357c37df4079371b1c32f.jpg</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296200</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296203</t>
         </is>
       </c>
       <c r="W38" t="inlineStr">
@@ -5107,7 +5131,7 @@
       <c r="AB38" t="inlineStr"/>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/e6a30e98-5da6-7e0d-7a92-5b26c887309f/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/0ddf4bea-7e5d-145a-1812-20986271091f/manifest</t>
         </is>
       </c>
       <c r="AD38" t="inlineStr"/>
@@ -5115,13 +5139,13 @@
       <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="inlineStr"/>
       <c r="AH38" t="n">
-        <v>22</v>
+        <v>50</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [1]</t>
+          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [4]</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -5176,12 +5200,12 @@
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/c32632af-9dc0-504a-5437-15a055d52628.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/5bf3d0ca-0a42-80a4-6959-af4f28d23fa3.json</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>c32632af-9dc0-504a-5437-15a055d52628</t>
+          <t>5bf3d0ca-0a42-80a4-6959-af4f28d23fa3</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
@@ -5191,7 +5215,7 @@
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/c32632af-9dc0-504a-5437-15a055d52628</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/5bf3d0ca-0a42-80a4-6959-af4f28d23fa3</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
@@ -5201,12 +5225,12 @@
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/2230dfedd3d91cc8b1c5532de33a8f8559be8357.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/b3dd61edd0ba78499c058ae1c9d57f1980d4b058.jpg</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296201</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296204</t>
         </is>
       </c>
       <c r="W39" t="inlineStr">
@@ -5229,7 +5253,7 @@
       <c r="AB39" t="inlineStr"/>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/c32632af-9dc0-504a-5437-15a055d52628/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/5bf3d0ca-0a42-80a4-6959-af4f28d23fa3/manifest</t>
         </is>
       </c>
       <c r="AD39" t="inlineStr"/>
@@ -5237,13 +5261,13 @@
       <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="inlineStr"/>
       <c r="AH39" t="n">
-        <v>72</v>
+        <v>52</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [2]</t>
+          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [5]</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -5298,12 +5322,12 @@
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/f31d474b-60bb-5efd-a570-d8f971a97e5e.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/92efd5a7-2a66-1ead-1e71-bdf9c70e12d0.json</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>f31d474b-60bb-5efd-a570-d8f971a97e5e</t>
+          <t>92efd5a7-2a66-1ead-1e71-bdf9c70e12d0</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
@@ -5313,7 +5337,7 @@
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/f31d474b-60bb-5efd-a570-d8f971a97e5e</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/92efd5a7-2a66-1ead-1e71-bdf9c70e12d0</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
@@ -5323,12 +5347,12 @@
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/378909456e17de7b588873b8890cd6945bba3cc8.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/aaef2fe4c4feeefa7fd4fb27983a6dfd085d4a7b.jpg</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296202</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296205</t>
         </is>
       </c>
       <c r="W40" t="inlineStr">
@@ -5351,7 +5375,7 @@
       <c r="AB40" t="inlineStr"/>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/f31d474b-60bb-5efd-a570-d8f971a97e5e/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/92efd5a7-2a66-1ead-1e71-bdf9c70e12d0/manifest</t>
         </is>
       </c>
       <c r="AD40" t="inlineStr"/>
@@ -5359,13 +5383,13 @@
       <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="inlineStr"/>
       <c r="AH40" t="n">
-        <v>75</v>
+        <v>68</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [3]</t>
+          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [6]</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5420,12 +5444,12 @@
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/0ddf4bea-7e5d-145a-1812-20986271091f.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/70ac8e25-6d33-9123-6fb2-0339224b41cc.json</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>0ddf4bea-7e5d-145a-1812-20986271091f</t>
+          <t>70ac8e25-6d33-9123-6fb2-0339224b41cc</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
@@ -5435,7 +5459,7 @@
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/0ddf4bea-7e5d-145a-1812-20986271091f</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/70ac8e25-6d33-9123-6fb2-0339224b41cc</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
@@ -5445,12 +5469,12 @@
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/f1d109214b4c636205f357c37df4079371b1c32f.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/3d36b605983eef3eb9e60d5e9f2d3016a497dd98.jpg</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296203</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296206</t>
         </is>
       </c>
       <c r="W41" t="inlineStr">
@@ -5473,7 +5497,7 @@
       <c r="AB41" t="inlineStr"/>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/0ddf4bea-7e5d-145a-1812-20986271091f/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/70ac8e25-6d33-9123-6fb2-0339224b41cc/manifest</t>
         </is>
       </c>
       <c r="AD41" t="inlineStr"/>
@@ -5481,13 +5505,13 @@
       <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="inlineStr"/>
       <c r="AH41" t="n">
-        <v>50</v>
+        <v>72</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [4]</t>
+          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [7]</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5542,12 +5566,12 @@
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/5bf3d0ca-0a42-80a4-6959-af4f28d23fa3.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/87cadcc3-3c6c-1f0e-a10f-d8c8b16b34e3.json</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>5bf3d0ca-0a42-80a4-6959-af4f28d23fa3</t>
+          <t>87cadcc3-3c6c-1f0e-a10f-d8c8b16b34e3</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
@@ -5557,7 +5581,7 @@
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/5bf3d0ca-0a42-80a4-6959-af4f28d23fa3</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/87cadcc3-3c6c-1f0e-a10f-d8c8b16b34e3</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
@@ -5567,12 +5591,12 @@
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/b3dd61edd0ba78499c058ae1c9d57f1980d4b058.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/60cd75676a83bcd5331212ff419346e6088f81e4.jpg</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296204</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296207</t>
         </is>
       </c>
       <c r="W42" t="inlineStr">
@@ -5595,7 +5619,7 @@
       <c r="AB42" t="inlineStr"/>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/5bf3d0ca-0a42-80a4-6959-af4f28d23fa3/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/87cadcc3-3c6c-1f0e-a10f-d8c8b16b34e3/manifest</t>
         </is>
       </c>
       <c r="AD42" t="inlineStr"/>
@@ -5603,13 +5627,13 @@
       <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="inlineStr"/>
       <c r="AH42" t="n">
-        <v>52</v>
+        <v>67</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [5]</t>
+          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [8]</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5664,12 +5688,12 @@
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/92efd5a7-2a66-1ead-1e71-bdf9c70e12d0.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/d4dc2699-5a8e-7ad5-3160-80d5fae78074.json</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>92efd5a7-2a66-1ead-1e71-bdf9c70e12d0</t>
+          <t>d4dc2699-5a8e-7ad5-3160-80d5fae78074</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
@@ -5679,7 +5703,7 @@
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/92efd5a7-2a66-1ead-1e71-bdf9c70e12d0</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/d4dc2699-5a8e-7ad5-3160-80d5fae78074</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
@@ -5689,12 +5713,12 @@
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/aaef2fe4c4feeefa7fd4fb27983a6dfd085d4a7b.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/596a21f68644c95bd76b3f3600fb73bc78fb9124.jpg</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296205</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296208</t>
         </is>
       </c>
       <c r="W43" t="inlineStr">
@@ -5717,7 +5741,7 @@
       <c r="AB43" t="inlineStr"/>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/92efd5a7-2a66-1ead-1e71-bdf9c70e12d0/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/d4dc2699-5a8e-7ad5-3160-80d5fae78074/manifest</t>
         </is>
       </c>
       <c r="AD43" t="inlineStr"/>
@@ -5725,13 +5749,13 @@
       <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="inlineStr"/>
       <c r="AH43" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [6]</t>
+          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [9]</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5786,12 +5810,12 @@
       <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/70ac8e25-6d33-9123-6fb2-0339224b41cc.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/a5e4d339-47a5-92a8-3fb3-15464db0a1f8.json</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>70ac8e25-6d33-9123-6fb2-0339224b41cc</t>
+          <t>a5e4d339-47a5-92a8-3fb3-15464db0a1f8</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
@@ -5801,7 +5825,7 @@
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/70ac8e25-6d33-9123-6fb2-0339224b41cc</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/a5e4d339-47a5-92a8-3fb3-15464db0a1f8</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
@@ -5811,12 +5835,12 @@
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/3d36b605983eef3eb9e60d5e9f2d3016a497dd98.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/965ce572fe0c064509727c2dbba58751771f36b4.jpg</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296206</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296209</t>
         </is>
       </c>
       <c r="W44" t="inlineStr">
@@ -5839,7 +5863,7 @@
       <c r="AB44" t="inlineStr"/>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/70ac8e25-6d33-9123-6fb2-0339224b41cc/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/a5e4d339-47a5-92a8-3fb3-15464db0a1f8/manifest</t>
         </is>
       </c>
       <c r="AD44" t="inlineStr"/>
@@ -5847,13 +5871,13 @@
       <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="inlineStr"/>
       <c r="AH44" t="n">
-        <v>72</v>
+        <v>64</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [7]</t>
+          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [10]</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5908,12 +5932,12 @@
       <c r="O45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/87cadcc3-3c6c-1f0e-a10f-d8c8b16b34e3.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/941cae96-2884-09d1-316d-978da0fc83f5.json</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>87cadcc3-3c6c-1f0e-a10f-d8c8b16b34e3</t>
+          <t>941cae96-2884-09d1-316d-978da0fc83f5</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
@@ -5923,7 +5947,7 @@
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/87cadcc3-3c6c-1f0e-a10f-d8c8b16b34e3</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/941cae96-2884-09d1-316d-978da0fc83f5</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
@@ -5933,12 +5957,12 @@
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/60cd75676a83bcd5331212ff419346e6088f81e4.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/9b2119b5a8cb266e4d44bebff61cd8b5383a810e.jpg</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296207</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296210</t>
         </is>
       </c>
       <c r="W45" t="inlineStr">
@@ -5961,7 +5985,7 @@
       <c r="AB45" t="inlineStr"/>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/87cadcc3-3c6c-1f0e-a10f-d8c8b16b34e3/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/941cae96-2884-09d1-316d-978da0fc83f5/manifest</t>
         </is>
       </c>
       <c r="AD45" t="inlineStr"/>
@@ -5969,13 +5993,13 @@
       <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="inlineStr"/>
       <c r="AH45" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [8]</t>
+          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [11]</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -6030,12 +6054,12 @@
       <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/d4dc2699-5a8e-7ad5-3160-80d5fae78074.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/b6a83876-30df-48c8-9c3f-3a68e8429d62.json</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>d4dc2699-5a8e-7ad5-3160-80d5fae78074</t>
+          <t>b6a83876-30df-48c8-9c3f-3a68e8429d62</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
@@ -6045,7 +6069,7 @@
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/d4dc2699-5a8e-7ad5-3160-80d5fae78074</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/b6a83876-30df-48c8-9c3f-3a68e8429d62</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
@@ -6055,12 +6079,12 @@
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/596a21f68644c95bd76b3f3600fb73bc78fb9124.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/7f6bf7c4b28ea807212c7ead3da50d50601c8ed1.jpg</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296208</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296211</t>
         </is>
       </c>
       <c r="W46" t="inlineStr">
@@ -6083,7 +6107,7 @@
       <c r="AB46" t="inlineStr"/>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/d4dc2699-5a8e-7ad5-3160-80d5fae78074/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/b6a83876-30df-48c8-9c3f-3a68e8429d62/manifest</t>
         </is>
       </c>
       <c r="AD46" t="inlineStr"/>
@@ -6091,31 +6115,27 @@
       <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="inlineStr"/>
       <c r="AH46" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [9]</t>
+          <t>各種殘經 : 出鄯善縣土峪溝</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>A00:6257</t>
+          <t>A00:4033</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>レキダイ ザンケツ ニッキ</t>
+          <t>カクシュ ザンキョウ : シュツ ゼンゼンケン トヨクコウ</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>黒川 春村</t>
-        </is>
-      </c>
+      <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
           <t>[書写者不明]</t>
@@ -6124,7 +6144,7 @@
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr">
         <is>
-          <t>[安政5 (1858)]</t>
+          <t>[書写年不明]</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -6136,12 +6156,12 @@
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr">
         <is>
-          <t>写本|責任表示及び書写年は『日本古典籍総合目録データベース』による|内容: 6: 光明院御記, 後光嚴院御記, 後小松院宸記, 天聴集. 28: 参議藤定長卿記 : 稱山丞記. 37: 定高卿記, 晴御会部類記, 家光卿御記, 權中納言平範輔卿記. 38: 左大史小槻季継記, 後堀川安貞二年放生會(実基公記), 石清水八幡宮, 弁官拝賀次第. 39: 大外記師光記, 資季卿記, 荒凉記, 忠高卿記. 40: 冷泉公相公記, 勝延法眼記 : 東寺大行事, 後中記 : 小路中納言資頼卿記葉室. 41: 中光記, 師兼記, 陽龍記. 42: 大宮司長則記, 口筆 : 實經, 顕朝卿記, 鴨御幸記. 43: 寳治二年記, 深心院關白記, 藤公親記, 照念院関白兼平公記. 44: 頼親記, 亀山殿行幸記 : 雅言卿記, 兼基公記. 45: 大嘗會御禊節下次第, 建治三年丁丑日記 : 三善康有, 建治四年正月廿一日 : 徳大寺大相國公孝記, 冬定卿記, 左大史小槻兼文記|内容: 46: 經任卿記, 前豊前守藤憲説記, 實兼公記. 47: 継塵記抄出. 48: 管見記, 公衡公記, 大外記師顕記, 大外記中原師淳記. 49: 真光院禪助僧正記, 吉田内府卿記. 50: 定清記, 叅議雅俊卿記, 太政大臣(公守公)御上表雜事, 仙洞御灌頂日記, 正安二年八月十一日於仙洞被始行熾盛光法, 正安三年御譲位記. 51: 實躬卿記. 52: 公茂公記, 冬平公記, 隆長卿記. 53: 忠教公記, 官記, 正三位長基卿記, 北面秀長記, 大外記中原師右記. 54: 文保元年, 日野中納言資朝卿記, 洞院大納言公敏卿記. 55: 隆蔭卿記, 文保三年記, 尹大納言師賢卿記, 革命記, 立倚子記, 萬里小路中納言藤藤房卿記|内容: 56: 資名卿記, 公秀公記, 一條家記装束抄出, 頼定卿記. 63: 松亞記, 日野大納言時光卿記, 後八條内府實継公記. 74: 成恩寺関白記. 78: 山科家礼記. 82: 諒闇記 : 後成恩寺殿, 宗典僧正記, 綱光公記, 贈従二位宗賢卿記, 義政公記. 84: 長禄二年戊寅正月, 見聞雜記. 87: 言國卿記. 88: 長興宿祢記, 元長卿記, 兼顕卿記, 小槻晴冨記|28末の原奥書に「右山丞記依 仰挍合書冩/享和二年四月 日撿挍保己一」とあり|50「正安二年八月十一日於仙洞被始行熾盛光法」末の原奥書に「文化十五年春二月以南山法曼院藏夲書冩之 撿挍保己一」とあり|横刷毛目表紙を使用|朱点, 朱引, 朱墨筆書き入れあり|付箋あり|蔵書印主信濃須坂藩主堀直格の命によって編集された古記録|他の原本は関東大震災により焼失|極札に「桂壽」(6), 「尚信」(53)との極書, 「武清」(44, 53), 「永海」(51), 「了伴」(52), 「了甫」(74), 「定時」(84, 88)との極印あり|印記: 「花廼家文庫」, 「墨阪十一代主寫藏記」(堀直格(1806-1880)), 「東京大學法理文學部書庫所藏」, 「閲覧室用 FOR USE IN THE READING ROOM」|虫損あり</t>
+          <t>写本残片|書名は題簽による|題簽に「出鄯善縣土峪溝 素文珍藏」とあり|識語に「為楊枝甘露滴入紙中展巻把玩但覺異香盈字 晉卿」, 「右二紙係亜利安字 晉卿」, 「右二紙係畏吾児字 晉卿」とあり|蔵書票に「殘經佛像梵字 十五段 鄯善」, 「梵字第一號」とあり|巻子本|箱入|印記: 「臣樹枏印」, 「晉卿」, 「王仲子」, 「王樹枏印」</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>日本語</t>
+          <t>中国語</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -6152,12 +6172,12 @@
       <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/a5e4d339-47a5-92a8-3fb3-15464db0a1f8.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/704d2c7a-4882-6fc8-60d1-94c1e2799bbd.json</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>a5e4d339-47a5-92a8-3fb3-15464db0a1f8</t>
+          <t>704d2c7a-4882-6fc8-60d1-94c1e2799bbd</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
@@ -6167,7 +6187,7 @@
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/a5e4d339-47a5-92a8-3fb3-15464db0a1f8</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/704d2c7a-4882-6fc8-60d1-94c1e2799bbd</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
@@ -6177,12 +6197,12 @@
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/965ce572fe0c064509727c2dbba58751771f36b4.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/4cc89d9a25687c69b3dc3791fd39ac740de2c4a0.jpg</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296209</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296165</t>
         </is>
       </c>
       <c r="W47" t="inlineStr">
@@ -6205,7 +6225,7 @@
       <c r="AB47" t="inlineStr"/>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/a5e4d339-47a5-92a8-3fb3-15464db0a1f8/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/704d2c7a-4882-6fc8-60d1-94c1e2799bbd/manifest</t>
         </is>
       </c>
       <c r="AD47" t="inlineStr"/>
@@ -6213,29 +6233,29 @@
       <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="inlineStr"/>
       <c r="AH47" t="n">
-        <v>64</v>
+        <v>22</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [10]</t>
+          <t>和漢朗詠集 2巻 [1]</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>A00:6257</t>
+          <t>A00:4081</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>レキダイ ザンケツ ニッキ</t>
+          <t>ワカン ロウエイシュウ</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>黒川 春村</t>
+          <t>藤原 公任</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -6246,19 +6266,19 @@
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr">
         <is>
-          <t>[安政5 (1858)]</t>
+          <t>[江戸前期]</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr">
         <is>
-          <t>写本|責任表示及び書写年は『日本古典籍総合目録データベース』による|内容: 6: 光明院御記, 後光嚴院御記, 後小松院宸記, 天聴集. 28: 参議藤定長卿記 : 稱山丞記. 37: 定高卿記, 晴御会部類記, 家光卿御記, 權中納言平範輔卿記. 38: 左大史小槻季継記, 後堀川安貞二年放生會(実基公記), 石清水八幡宮, 弁官拝賀次第. 39: 大外記師光記, 資季卿記, 荒凉記, 忠高卿記. 40: 冷泉公相公記, 勝延法眼記 : 東寺大行事, 後中記 : 小路中納言資頼卿記葉室. 41: 中光記, 師兼記, 陽龍記. 42: 大宮司長則記, 口筆 : 實經, 顕朝卿記, 鴨御幸記. 43: 寳治二年記, 深心院關白記, 藤公親記, 照念院関白兼平公記. 44: 頼親記, 亀山殿行幸記 : 雅言卿記, 兼基公記. 45: 大嘗會御禊節下次第, 建治三年丁丑日記 : 三善康有, 建治四年正月廿一日 : 徳大寺大相國公孝記, 冬定卿記, 左大史小槻兼文記|内容: 46: 經任卿記, 前豊前守藤憲説記, 實兼公記. 47: 継塵記抄出. 48: 管見記, 公衡公記, 大外記師顕記, 大外記中原師淳記. 49: 真光院禪助僧正記, 吉田内府卿記. 50: 定清記, 叅議雅俊卿記, 太政大臣(公守公)御上表雜事, 仙洞御灌頂日記, 正安二年八月十一日於仙洞被始行熾盛光法, 正安三年御譲位記. 51: 實躬卿記. 52: 公茂公記, 冬平公記, 隆長卿記. 53: 忠教公記, 官記, 正三位長基卿記, 北面秀長記, 大外記中原師右記. 54: 文保元年, 日野中納言資朝卿記, 洞院大納言公敏卿記. 55: 隆蔭卿記, 文保三年記, 尹大納言師賢卿記, 革命記, 立倚子記, 萬里小路中納言藤藤房卿記|内容: 56: 資名卿記, 公秀公記, 一條家記装束抄出, 頼定卿記. 63: 松亞記, 日野大納言時光卿記, 後八條内府實継公記. 74: 成恩寺関白記. 78: 山科家礼記. 82: 諒闇記 : 後成恩寺殿, 宗典僧正記, 綱光公記, 贈従二位宗賢卿記, 義政公記. 84: 長禄二年戊寅正月, 見聞雜記. 87: 言國卿記. 88: 長興宿祢記, 元長卿記, 兼顕卿記, 小槻晴冨記|28末の原奥書に「右山丞記依 仰挍合書冩/享和二年四月 日撿挍保己一」とあり|50「正安二年八月十一日於仙洞被始行熾盛光法」末の原奥書に「文化十五年春二月以南山法曼院藏夲書冩之 撿挍保己一」とあり|横刷毛目表紙を使用|朱点, 朱引, 朱墨筆書き入れあり|付箋あり|蔵書印主信濃須坂藩主堀直格の命によって編集された古記録|他の原本は関東大震災により焼失|極札に「桂壽」(6), 「尚信」(53)との極書, 「武清」(44, 53), 「永海」(51), 「了伴」(52), 「了甫」(74), 「定時」(84, 88)との極印あり|印記: 「花廼家文庫」, 「墨阪十一代主寫藏記」(堀直格(1806-1880)), 「東京大學法理文學部書庫所藏」, 「閲覧室用 FOR USE IN THE READING ROOM」|虫損あり</t>
+          <t>写本|書名は目首及び題簽による|外箱の書名: 御本|責任表示は『日本古典籍総合目録データベース』による|巻上: 春, 夏, 秋, 冬. 巻下: 雜|題簽による巻冊次表示: 上, 下|毎半帖8行|漢字平仮名交じり文|鳳凰菱繋ぎ文様緞子表紙, 松葉散しに山雲の金箔見返し, 金泥下絵鳥の子紙を使用|列帖装|二重箱入り</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -6274,12 +6294,12 @@
       <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/941cae96-2884-09d1-316d-978da0fc83f5.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/ba79db36-23e8-1a8a-1ad9-a5809c1109be.json</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>941cae96-2884-09d1-316d-978da0fc83f5</t>
+          <t>ba79db36-23e8-1a8a-1ad9-a5809c1109be</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
@@ -6289,7 +6309,7 @@
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/941cae96-2884-09d1-316d-978da0fc83f5</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/ba79db36-23e8-1a8a-1ad9-a5809c1109be</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
@@ -6299,12 +6319,12 @@
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/9b2119b5a8cb266e4d44bebff61cd8b5383a810e.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/0dbc6905fbe6d7441026c6ec7f4092a564cd7606.jpg</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296210</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296166</t>
         </is>
       </c>
       <c r="W48" t="inlineStr">
@@ -6327,7 +6347,7 @@
       <c r="AB48" t="inlineStr"/>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/941cae96-2884-09d1-316d-978da0fc83f5/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/ba79db36-23e8-1a8a-1ad9-a5809c1109be/manifest</t>
         </is>
       </c>
       <c r="AD48" t="inlineStr"/>
@@ -6335,29 +6355,29 @@
       <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="inlineStr"/>
       <c r="AH48" t="n">
-        <v>70</v>
+        <v>54</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [11]</t>
+          <t>和漢朗詠集 2巻 [2]</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>A00:6257</t>
+          <t>A00:4081</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>レキダイ ザンケツ ニッキ</t>
+          <t>ワカン ロウエイシュウ</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>黒川 春村</t>
+          <t>藤原 公任</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -6368,19 +6388,19 @@
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr">
         <is>
-          <t>[安政5 (1858)]</t>
+          <t>[江戸前期]</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
-          <t>写本|責任表示及び書写年は『日本古典籍総合目録データベース』による|内容: 6: 光明院御記, 後光嚴院御記, 後小松院宸記, 天聴集. 28: 参議藤定長卿記 : 稱山丞記. 37: 定高卿記, 晴御会部類記, 家光卿御記, 權中納言平範輔卿記. 38: 左大史小槻季継記, 後堀川安貞二年放生會(実基公記), 石清水八幡宮, 弁官拝賀次第. 39: 大外記師光記, 資季卿記, 荒凉記, 忠高卿記. 40: 冷泉公相公記, 勝延法眼記 : 東寺大行事, 後中記 : 小路中納言資頼卿記葉室. 41: 中光記, 師兼記, 陽龍記. 42: 大宮司長則記, 口筆 : 實經, 顕朝卿記, 鴨御幸記. 43: 寳治二年記, 深心院關白記, 藤公親記, 照念院関白兼平公記. 44: 頼親記, 亀山殿行幸記 : 雅言卿記, 兼基公記. 45: 大嘗會御禊節下次第, 建治三年丁丑日記 : 三善康有, 建治四年正月廿一日 : 徳大寺大相國公孝記, 冬定卿記, 左大史小槻兼文記|内容: 46: 經任卿記, 前豊前守藤憲説記, 實兼公記. 47: 継塵記抄出. 48: 管見記, 公衡公記, 大外記師顕記, 大外記中原師淳記. 49: 真光院禪助僧正記, 吉田内府卿記. 50: 定清記, 叅議雅俊卿記, 太政大臣(公守公)御上表雜事, 仙洞御灌頂日記, 正安二年八月十一日於仙洞被始行熾盛光法, 正安三年御譲位記. 51: 實躬卿記. 52: 公茂公記, 冬平公記, 隆長卿記. 53: 忠教公記, 官記, 正三位長基卿記, 北面秀長記, 大外記中原師右記. 54: 文保元年, 日野中納言資朝卿記, 洞院大納言公敏卿記. 55: 隆蔭卿記, 文保三年記, 尹大納言師賢卿記, 革命記, 立倚子記, 萬里小路中納言藤藤房卿記|内容: 56: 資名卿記, 公秀公記, 一條家記装束抄出, 頼定卿記. 63: 松亞記, 日野大納言時光卿記, 後八條内府實継公記. 74: 成恩寺関白記. 78: 山科家礼記. 82: 諒闇記 : 後成恩寺殿, 宗典僧正記, 綱光公記, 贈従二位宗賢卿記, 義政公記. 84: 長禄二年戊寅正月, 見聞雜記. 87: 言國卿記. 88: 長興宿祢記, 元長卿記, 兼顕卿記, 小槻晴冨記|28末の原奥書に「右山丞記依 仰挍合書冩/享和二年四月 日撿挍保己一」とあり|50「正安二年八月十一日於仙洞被始行熾盛光法」末の原奥書に「文化十五年春二月以南山法曼院藏夲書冩之 撿挍保己一」とあり|横刷毛目表紙を使用|朱点, 朱引, 朱墨筆書き入れあり|付箋あり|蔵書印主信濃須坂藩主堀直格の命によって編集された古記録|他の原本は関東大震災により焼失|極札に「桂壽」(6), 「尚信」(53)との極書, 「武清」(44, 53), 「永海」(51), 「了伴」(52), 「了甫」(74), 「定時」(84, 88)との極印あり|印記: 「花廼家文庫」, 「墨阪十一代主寫藏記」(堀直格(1806-1880)), 「東京大學法理文學部書庫所藏」, 「閲覧室用 FOR USE IN THE READING ROOM」|虫損あり</t>
+          <t>写本|書名は目首及び題簽による|外箱の書名: 御本|責任表示は『日本古典籍総合目録データベース』による|巻上: 春, 夏, 秋, 冬. 巻下: 雜|題簽による巻冊次表示: 上, 下|毎半帖8行|漢字平仮名交じり文|鳳凰菱繋ぎ文様緞子表紙, 松葉散しに山雲の金箔見返し, 金泥下絵鳥の子紙を使用|列帖装|二重箱入り</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -6396,12 +6416,12 @@
       <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/b6a83876-30df-48c8-9c3f-3a68e8429d62.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/a241b0e6-90d9-46db-1fe8-bf35f1e616c5.json</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>b6a83876-30df-48c8-9c3f-3a68e8429d62</t>
+          <t>a241b0e6-90d9-46db-1fe8-bf35f1e616c5</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
@@ -6411,7 +6431,7 @@
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/b6a83876-30df-48c8-9c3f-3a68e8429d62</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/a241b0e6-90d9-46db-1fe8-bf35f1e616c5</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
@@ -6421,12 +6441,12 @@
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/7f6bf7c4b28ea807212c7ead3da50d50601c8ed1.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/f46b1242e2b77ba4f0d99feac20562f5cd3a0ee2.jpg</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296211</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296167</t>
         </is>
       </c>
       <c r="W49" t="inlineStr">
@@ -6449,7 +6469,7 @@
       <c r="AB49" t="inlineStr"/>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/b6a83876-30df-48c8-9c3f-3a68e8429d62/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/a241b0e6-90d9-46db-1fe8-bf35f1e616c5/manifest</t>
         </is>
       </c>
       <c r="AD49" t="inlineStr"/>
@@ -6457,29 +6477,29 @@
       <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="inlineStr"/>
       <c r="AH49" t="n">
-        <v>64</v>
+        <v>48</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [12]</t>
+          <t>つれつれ草</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>A00:6257</t>
+          <t>A00:4082</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>レキダイ ザンケツ ニッキ</t>
+          <t>ツレズレグサ</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>黒川 春村</t>
+          <t>吉田 兼好</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -6490,7 +6510,7 @@
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr">
         <is>
-          <t>[安政5 (1858)]</t>
+          <t>[江戸前期]</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -6502,7 +6522,7 @@
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr">
         <is>
-          <t>写本|責任表示及び書写年は『日本古典籍総合目録データベース』による|内容: 6: 光明院御記, 後光嚴院御記, 後小松院宸記, 天聴集. 28: 参議藤定長卿記 : 稱山丞記. 37: 定高卿記, 晴御会部類記, 家光卿御記, 權中納言平範輔卿記. 38: 左大史小槻季継記, 後堀川安貞二年放生會(実基公記), 石清水八幡宮, 弁官拝賀次第. 39: 大外記師光記, 資季卿記, 荒凉記, 忠高卿記. 40: 冷泉公相公記, 勝延法眼記 : 東寺大行事, 後中記 : 小路中納言資頼卿記葉室. 41: 中光記, 師兼記, 陽龍記. 42: 大宮司長則記, 口筆 : 實經, 顕朝卿記, 鴨御幸記. 43: 寳治二年記, 深心院關白記, 藤公親記, 照念院関白兼平公記. 44: 頼親記, 亀山殿行幸記 : 雅言卿記, 兼基公記. 45: 大嘗會御禊節下次第, 建治三年丁丑日記 : 三善康有, 建治四年正月廿一日 : 徳大寺大相國公孝記, 冬定卿記, 左大史小槻兼文記|内容: 46: 經任卿記, 前豊前守藤憲説記, 實兼公記. 47: 継塵記抄出. 48: 管見記, 公衡公記, 大外記師顕記, 大外記中原師淳記. 49: 真光院禪助僧正記, 吉田内府卿記. 50: 定清記, 叅議雅俊卿記, 太政大臣(公守公)御上表雜事, 仙洞御灌頂日記, 正安二年八月十一日於仙洞被始行熾盛光法, 正安三年御譲位記. 51: 實躬卿記. 52: 公茂公記, 冬平公記, 隆長卿記. 53: 忠教公記, 官記, 正三位長基卿記, 北面秀長記, 大外記中原師右記. 54: 文保元年, 日野中納言資朝卿記, 洞院大納言公敏卿記. 55: 隆蔭卿記, 文保三年記, 尹大納言師賢卿記, 革命記, 立倚子記, 萬里小路中納言藤藤房卿記|内容: 56: 資名卿記, 公秀公記, 一條家記装束抄出, 頼定卿記. 63: 松亞記, 日野大納言時光卿記, 後八條内府實継公記. 74: 成恩寺関白記. 78: 山科家礼記. 82: 諒闇記 : 後成恩寺殿, 宗典僧正記, 綱光公記, 贈従二位宗賢卿記, 義政公記. 84: 長禄二年戊寅正月, 見聞雜記. 87: 言國卿記. 88: 長興宿祢記, 元長卿記, 兼顕卿記, 小槻晴冨記|28末の原奥書に「右山丞記依 仰挍合書冩/享和二年四月 日撿挍保己一」とあり|50「正安二年八月十一日於仙洞被始行熾盛光法」末の原奥書に「文化十五年春二月以南山法曼院藏夲書冩之 撿挍保己一」とあり|横刷毛目表紙を使用|朱点, 朱引, 朱墨筆書き入れあり|付箋あり|蔵書印主信濃須坂藩主堀直格の命によって編集された古記録|他の原本は関東大震災により焼失|極札に「桂壽」(6), 「尚信」(53)との極書, 「武清」(44, 53), 「永海」(51), 「了伴」(52), 「了甫」(74), 「定時」(84, 88)との極印あり|印記: 「花廼家文庫」, 「墨阪十一代主寫藏記」(堀直格(1806-1880)), 「東京大學法理文學部書庫所藏」, 「閲覧室用 FOR USE IN THE READING ROOM」|虫損あり</t>
+          <t>写本|書名は題簽による|書名の繰返し部分は踊り字|外箱の書名: 御本|責任表示は『日本古典籍総合目録データベース』による|毎半帖10行|漢字平仮名交じり文|花草窠文様緞子表紙, 松葉散しに山雲の金箔見返し, 金泥下絵鳥の子紙を使用|列帖装|二重箱入り</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -6518,12 +6538,12 @@
       <c r="O50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/d199046f-6bd4-6ca0-a0bf-c29ad3c19949.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/d19a62f6-4729-0ee3-3ea7-08f573851a48.json</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>d199046f-6bd4-6ca0-a0bf-c29ad3c19949</t>
+          <t>d19a62f6-4729-0ee3-3ea7-08f573851a48</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
@@ -6533,7 +6553,7 @@
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/d199046f-6bd4-6ca0-a0bf-c29ad3c19949</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/d19a62f6-4729-0ee3-3ea7-08f573851a48</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
@@ -6543,12 +6563,12 @@
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/4cbd0825007ec7d3c89014f55d3b6825a8214769.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/7966b7312c84644ee577a0390937964b1989586d.jpg</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296212</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296168</t>
         </is>
       </c>
       <c r="W50" t="inlineStr">
@@ -6571,7 +6591,7 @@
       <c r="AB50" t="inlineStr"/>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/d199046f-6bd4-6ca0-a0bf-c29ad3c19949/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/d19a62f6-4729-0ee3-3ea7-08f573851a48/manifest</t>
         </is>
       </c>
       <c r="AD50" t="inlineStr"/>
@@ -6579,29 +6599,29 @@
       <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="inlineStr"/>
       <c r="AH50" t="n">
-        <v>77</v>
+        <v>142</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [13]</t>
+          <t>日本廿四孝 6巻 [1]</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>A00:6257</t>
+          <t>A00:4084</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>レキダイ ザンケツ ニッキ</t>
+          <t>ヤマト ニジュウシコウ</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>黒川 春村</t>
+          <t>浅井 了意</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -6612,19 +6632,19 @@
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr">
         <is>
-          <t>[安政5 (1858)]</t>
+          <t>[江戸前期]</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr">
         <is>
-          <t>写本|責任表示及び書写年は『日本古典籍総合目録データベース』による|内容: 6: 光明院御記, 後光嚴院御記, 後小松院宸記, 天聴集. 28: 参議藤定長卿記 : 稱山丞記. 37: 定高卿記, 晴御会部類記, 家光卿御記, 權中納言平範輔卿記. 38: 左大史小槻季継記, 後堀川安貞二年放生會(実基公記), 石清水八幡宮, 弁官拝賀次第. 39: 大外記師光記, 資季卿記, 荒凉記, 忠高卿記. 40: 冷泉公相公記, 勝延法眼記 : 東寺大行事, 後中記 : 小路中納言資頼卿記葉室. 41: 中光記, 師兼記, 陽龍記. 42: 大宮司長則記, 口筆 : 實經, 顕朝卿記, 鴨御幸記. 43: 寳治二年記, 深心院關白記, 藤公親記, 照念院関白兼平公記. 44: 頼親記, 亀山殿行幸記 : 雅言卿記, 兼基公記. 45: 大嘗會御禊節下次第, 建治三年丁丑日記 : 三善康有, 建治四年正月廿一日 : 徳大寺大相國公孝記, 冬定卿記, 左大史小槻兼文記|内容: 46: 經任卿記, 前豊前守藤憲説記, 實兼公記. 47: 継塵記抄出. 48: 管見記, 公衡公記, 大外記師顕記, 大外記中原師淳記. 49: 真光院禪助僧正記, 吉田内府卿記. 50: 定清記, 叅議雅俊卿記, 太政大臣(公守公)御上表雜事, 仙洞御灌頂日記, 正安二年八月十一日於仙洞被始行熾盛光法, 正安三年御譲位記. 51: 實躬卿記. 52: 公茂公記, 冬平公記, 隆長卿記. 53: 忠教公記, 官記, 正三位長基卿記, 北面秀長記, 大外記中原師右記. 54: 文保元年, 日野中納言資朝卿記, 洞院大納言公敏卿記. 55: 隆蔭卿記, 文保三年記, 尹大納言師賢卿記, 革命記, 立倚子記, 萬里小路中納言藤藤房卿記|内容: 56: 資名卿記, 公秀公記, 一條家記装束抄出, 頼定卿記. 63: 松亞記, 日野大納言時光卿記, 後八條内府實継公記. 74: 成恩寺関白記. 78: 山科家礼記. 82: 諒闇記 : 後成恩寺殿, 宗典僧正記, 綱光公記, 贈従二位宗賢卿記, 義政公記. 84: 長禄二年戊寅正月, 見聞雜記. 87: 言國卿記. 88: 長興宿祢記, 元長卿記, 兼顕卿記, 小槻晴冨記|28末の原奥書に「右山丞記依 仰挍合書冩/享和二年四月 日撿挍保己一」とあり|50「正安二年八月十一日於仙洞被始行熾盛光法」末の原奥書に「文化十五年春二月以南山法曼院藏夲書冩之 撿挍保己一」とあり|横刷毛目表紙を使用|朱点, 朱引, 朱墨筆書き入れあり|付箋あり|蔵書印主信濃須坂藩主堀直格の命によって編集された古記録|他の原本は関東大震災により焼失|極札に「桂壽」(6), 「尚信」(53)との極書, 「武清」(44, 53), 「永海」(51), 「了伴」(52), 「了甫」(74), 「定時」(84, 88)との極印あり|印記: 「花廼家文庫」, 「墨阪十一代主寫藏記」(堀直格(1806-1880)), 「東京大學法理文學部書庫所藏」, 「閲覧室用 FOR USE IN THE READING ROOM」|虫損あり</t>
+          <t>写本|書名は目首及び題簽による|内箱の書名: 大和廿四孝|外箱の書名: 御本|責任表示は『日本古典籍総合目録データベース』による|1: 第1-4. 2: 第5-8. 3: 第9-12. 4: 第13-16. 5: 第17-20. 6: 第21-24|毎半帖10行|漢字平仮名交じり文|奈良絵本|梅唐草文様緞子表紙, 松葉散しに山雲の金箔見返し, 金泥下絵鳥の子紙を使用|列帖装|竪本|二重箱入り|糸切れあり</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -6640,12 +6660,12 @@
       <c r="O51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/1b5c5c7f-4892-39f9-4e5e-479a8e921be2.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/bf17bb0e-6d63-718e-218b-614134ee011d.json</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>1b5c5c7f-4892-39f9-4e5e-479a8e921be2</t>
+          <t>bf17bb0e-6d63-718e-218b-614134ee011d</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
@@ -6655,7 +6675,7 @@
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/1b5c5c7f-4892-39f9-4e5e-479a8e921be2</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/bf17bb0e-6d63-718e-218b-614134ee011d</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
@@ -6665,12 +6685,12 @@
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/95aeca9c3732100e9d926fc7a9cb98fba20b6444.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/2c48d85abc93bce026f680cc699c748fb0a877e2.jpg</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296213</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296169</t>
         </is>
       </c>
       <c r="W51" t="inlineStr">
@@ -6693,7 +6713,7 @@
       <c r="AB51" t="inlineStr"/>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/1b5c5c7f-4892-39f9-4e5e-479a8e921be2/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/bf17bb0e-6d63-718e-218b-614134ee011d/manifest</t>
         </is>
       </c>
       <c r="AD51" t="inlineStr"/>
@@ -6701,29 +6721,29 @@
       <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="inlineStr"/>
       <c r="AH51" t="n">
-        <v>74</v>
+        <v>47</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [14]</t>
+          <t>日本廿四孝 6巻 [2]</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>A00:6257</t>
+          <t>A00:4084</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>レキダイ ザンケツ ニッキ</t>
+          <t>ヤマト ニジュウシコウ</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>黒川 春村</t>
+          <t>浅井 了意</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -6734,19 +6754,19 @@
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr">
         <is>
-          <t>[安政5 (1858)]</t>
+          <t>[江戸前期]</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr">
         <is>
-          <t>写本|責任表示及び書写年は『日本古典籍総合目録データベース』による|内容: 6: 光明院御記, 後光嚴院御記, 後小松院宸記, 天聴集. 28: 参議藤定長卿記 : 稱山丞記. 37: 定高卿記, 晴御会部類記, 家光卿御記, 權中納言平範輔卿記. 38: 左大史小槻季継記, 後堀川安貞二年放生會(実基公記), 石清水八幡宮, 弁官拝賀次第. 39: 大外記師光記, 資季卿記, 荒凉記, 忠高卿記. 40: 冷泉公相公記, 勝延法眼記 : 東寺大行事, 後中記 : 小路中納言資頼卿記葉室. 41: 中光記, 師兼記, 陽龍記. 42: 大宮司長則記, 口筆 : 實經, 顕朝卿記, 鴨御幸記. 43: 寳治二年記, 深心院關白記, 藤公親記, 照念院関白兼平公記. 44: 頼親記, 亀山殿行幸記 : 雅言卿記, 兼基公記. 45: 大嘗會御禊節下次第, 建治三年丁丑日記 : 三善康有, 建治四年正月廿一日 : 徳大寺大相國公孝記, 冬定卿記, 左大史小槻兼文記|内容: 46: 經任卿記, 前豊前守藤憲説記, 實兼公記. 47: 継塵記抄出. 48: 管見記, 公衡公記, 大外記師顕記, 大外記中原師淳記. 49: 真光院禪助僧正記, 吉田内府卿記. 50: 定清記, 叅議雅俊卿記, 太政大臣(公守公)御上表雜事, 仙洞御灌頂日記, 正安二年八月十一日於仙洞被始行熾盛光法, 正安三年御譲位記. 51: 實躬卿記. 52: 公茂公記, 冬平公記, 隆長卿記. 53: 忠教公記, 官記, 正三位長基卿記, 北面秀長記, 大外記中原師右記. 54: 文保元年, 日野中納言資朝卿記, 洞院大納言公敏卿記. 55: 隆蔭卿記, 文保三年記, 尹大納言師賢卿記, 革命記, 立倚子記, 萬里小路中納言藤藤房卿記|内容: 56: 資名卿記, 公秀公記, 一條家記装束抄出, 頼定卿記. 63: 松亞記, 日野大納言時光卿記, 後八條内府實継公記. 74: 成恩寺関白記. 78: 山科家礼記. 82: 諒闇記 : 後成恩寺殿, 宗典僧正記, 綱光公記, 贈従二位宗賢卿記, 義政公記. 84: 長禄二年戊寅正月, 見聞雜記. 87: 言國卿記. 88: 長興宿祢記, 元長卿記, 兼顕卿記, 小槻晴冨記|28末の原奥書に「右山丞記依 仰挍合書冩/享和二年四月 日撿挍保己一」とあり|50「正安二年八月十一日於仙洞被始行熾盛光法」末の原奥書に「文化十五年春二月以南山法曼院藏夲書冩之 撿挍保己一」とあり|横刷毛目表紙を使用|朱点, 朱引, 朱墨筆書き入れあり|付箋あり|蔵書印主信濃須坂藩主堀直格の命によって編集された古記録|他の原本は関東大震災により焼失|極札に「桂壽」(6), 「尚信」(53)との極書, 「武清」(44, 53), 「永海」(51), 「了伴」(52), 「了甫」(74), 「定時」(84, 88)との極印あり|印記: 「花廼家文庫」, 「墨阪十一代主寫藏記」(堀直格(1806-1880)), 「東京大學法理文學部書庫所藏」, 「閲覧室用 FOR USE IN THE READING ROOM」|虫損あり</t>
+          <t>写本|書名は目首及び題簽による|内箱の書名: 大和廿四孝|外箱の書名: 御本|責任表示は『日本古典籍総合目録データベース』による|1: 第1-4. 2: 第5-8. 3: 第9-12. 4: 第13-16. 5: 第17-20. 6: 第21-24|毎半帖10行|漢字平仮名交じり文|奈良絵本|梅唐草文様緞子表紙, 松葉散しに山雲の金箔見返し, 金泥下絵鳥の子紙を使用|列帖装|竪本|二重箱入り|糸切れあり</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -6762,12 +6782,12 @@
       <c r="O52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/a83ab18c-4d05-492c-2121-ec90971ea54a.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/c2996e14-8070-09ae-328a-159e60d17016.json</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>a83ab18c-4d05-492c-2121-ec90971ea54a</t>
+          <t>c2996e14-8070-09ae-328a-159e60d17016</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
@@ -6777,7 +6797,7 @@
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/a83ab18c-4d05-492c-2121-ec90971ea54a</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/c2996e14-8070-09ae-328a-159e60d17016</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
@@ -6787,12 +6807,12 @@
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/b0fe976afebb52b245b298aabead8423fd0d1a6f.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/27ba12aa7661321f36193a30b8d8ffb8b32e574c.jpg</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296214</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296170</t>
         </is>
       </c>
       <c r="W52" t="inlineStr">
@@ -6815,7 +6835,7 @@
       <c r="AB52" t="inlineStr"/>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/a83ab18c-4d05-492c-2121-ec90971ea54a/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/c2996e14-8070-09ae-328a-159e60d17016/manifest</t>
         </is>
       </c>
       <c r="AD52" t="inlineStr"/>
@@ -6823,29 +6843,29 @@
       <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="inlineStr"/>
       <c r="AH52" t="n">
-        <v>59</v>
+        <v>103</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [15]</t>
+          <t>日本廿四孝 6巻 [3]</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>A00:6257</t>
+          <t>A00:4084</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>レキダイ ザンケツ ニッキ</t>
+          <t>ヤマト ニジュウシコウ</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>黒川 春村</t>
+          <t>浅井 了意</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -6856,19 +6876,19 @@
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr">
         <is>
-          <t>[安政5 (1858)]</t>
+          <t>[江戸前期]</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr">
         <is>
-          <t>写本|責任表示及び書写年は『日本古典籍総合目録データベース』による|内容: 6: 光明院御記, 後光嚴院御記, 後小松院宸記, 天聴集. 28: 参議藤定長卿記 : 稱山丞記. 37: 定高卿記, 晴御会部類記, 家光卿御記, 權中納言平範輔卿記. 38: 左大史小槻季継記, 後堀川安貞二年放生會(実基公記), 石清水八幡宮, 弁官拝賀次第. 39: 大外記師光記, 資季卿記, 荒凉記, 忠高卿記. 40: 冷泉公相公記, 勝延法眼記 : 東寺大行事, 後中記 : 小路中納言資頼卿記葉室. 41: 中光記, 師兼記, 陽龍記. 42: 大宮司長則記, 口筆 : 實經, 顕朝卿記, 鴨御幸記. 43: 寳治二年記, 深心院關白記, 藤公親記, 照念院関白兼平公記. 44: 頼親記, 亀山殿行幸記 : 雅言卿記, 兼基公記. 45: 大嘗會御禊節下次第, 建治三年丁丑日記 : 三善康有, 建治四年正月廿一日 : 徳大寺大相國公孝記, 冬定卿記, 左大史小槻兼文記|内容: 46: 經任卿記, 前豊前守藤憲説記, 實兼公記. 47: 継塵記抄出. 48: 管見記, 公衡公記, 大外記師顕記, 大外記中原師淳記. 49: 真光院禪助僧正記, 吉田内府卿記. 50: 定清記, 叅議雅俊卿記, 太政大臣(公守公)御上表雜事, 仙洞御灌頂日記, 正安二年八月十一日於仙洞被始行熾盛光法, 正安三年御譲位記. 51: 實躬卿記. 52: 公茂公記, 冬平公記, 隆長卿記. 53: 忠教公記, 官記, 正三位長基卿記, 北面秀長記, 大外記中原師右記. 54: 文保元年, 日野中納言資朝卿記, 洞院大納言公敏卿記. 55: 隆蔭卿記, 文保三年記, 尹大納言師賢卿記, 革命記, 立倚子記, 萬里小路中納言藤藤房卿記|内容: 56: 資名卿記, 公秀公記, 一條家記装束抄出, 頼定卿記. 63: 松亞記, 日野大納言時光卿記, 後八條内府實継公記. 74: 成恩寺関白記. 78: 山科家礼記. 82: 諒闇記 : 後成恩寺殿, 宗典僧正記, 綱光公記, 贈従二位宗賢卿記, 義政公記. 84: 長禄二年戊寅正月, 見聞雜記. 87: 言國卿記. 88: 長興宿祢記, 元長卿記, 兼顕卿記, 小槻晴冨記|28末の原奥書に「右山丞記依 仰挍合書冩/享和二年四月 日撿挍保己一」とあり|50「正安二年八月十一日於仙洞被始行熾盛光法」末の原奥書に「文化十五年春二月以南山法曼院藏夲書冩之 撿挍保己一」とあり|横刷毛目表紙を使用|朱点, 朱引, 朱墨筆書き入れあり|付箋あり|蔵書印主信濃須坂藩主堀直格の命によって編集された古記録|他の原本は関東大震災により焼失|極札に「桂壽」(6), 「尚信」(53)との極書, 「武清」(44, 53), 「永海」(51), 「了伴」(52), 「了甫」(74), 「定時」(84, 88)との極印あり|印記: 「花廼家文庫」, 「墨阪十一代主寫藏記」(堀直格(1806-1880)), 「東京大學法理文學部書庫所藏」, 「閲覧室用 FOR USE IN THE READING ROOM」|虫損あり</t>
+          <t>写本|書名は目首及び題簽による|内箱の書名: 大和廿四孝|外箱の書名: 御本|責任表示は『日本古典籍総合目録データベース』による|1: 第1-4. 2: 第5-8. 3: 第9-12. 4: 第13-16. 5: 第17-20. 6: 第21-24|毎半帖10行|漢字平仮名交じり文|奈良絵本|梅唐草文様緞子表紙, 松葉散しに山雲の金箔見返し, 金泥下絵鳥の子紙を使用|列帖装|竪本|二重箱入り|糸切れあり</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -6884,12 +6904,12 @@
       <c r="O53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/acf20dd5-459a-5438-8dd8-cbc11fe122bf.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/8bf2f649-5d15-2afc-2f36-84e0ac2f513e.json</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>acf20dd5-459a-5438-8dd8-cbc11fe122bf</t>
+          <t>8bf2f649-5d15-2afc-2f36-84e0ac2f513e</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
@@ -6899,7 +6919,7 @@
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/acf20dd5-459a-5438-8dd8-cbc11fe122bf</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/8bf2f649-5d15-2afc-2f36-84e0ac2f513e</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
@@ -6909,12 +6929,12 @@
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/cfeece07d99889e30589237e6d78b4933a56b7d6.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/5841d5cb8d9895d0b483a2f842afc32f67e1719b.jpg</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296215</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296171</t>
         </is>
       </c>
       <c r="W53" t="inlineStr">
@@ -6937,7 +6957,7 @@
       <c r="AB53" t="inlineStr"/>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/acf20dd5-459a-5438-8dd8-cbc11fe122bf/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/8bf2f649-5d15-2afc-2f36-84e0ac2f513e/manifest</t>
         </is>
       </c>
       <c r="AD53" t="inlineStr"/>
@@ -6945,29 +6965,29 @@
       <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="inlineStr"/>
       <c r="AH53" t="n">
-        <v>64</v>
+        <v>47</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [16]</t>
+          <t>日本廿四孝 6巻 [4]</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>A00:6257</t>
+          <t>A00:4084</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>レキダイ ザンケツ ニッキ</t>
+          <t>ヤマト ニジュウシコウ</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>黒川 春村</t>
+          <t>浅井 了意</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -6978,19 +6998,19 @@
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr">
         <is>
-          <t>[安政5 (1858)]</t>
+          <t>[江戸前期]</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr">
         <is>
-          <t>写本|責任表示及び書写年は『日本古典籍総合目録データベース』による|内容: 6: 光明院御記, 後光嚴院御記, 後小松院宸記, 天聴集. 28: 参議藤定長卿記 : 稱山丞記. 37: 定高卿記, 晴御会部類記, 家光卿御記, 權中納言平範輔卿記. 38: 左大史小槻季継記, 後堀川安貞二年放生會(実基公記), 石清水八幡宮, 弁官拝賀次第. 39: 大外記師光記, 資季卿記, 荒凉記, 忠高卿記. 40: 冷泉公相公記, 勝延法眼記 : 東寺大行事, 後中記 : 小路中納言資頼卿記葉室. 41: 中光記, 師兼記, 陽龍記. 42: 大宮司長則記, 口筆 : 實經, 顕朝卿記, 鴨御幸記. 43: 寳治二年記, 深心院關白記, 藤公親記, 照念院関白兼平公記. 44: 頼親記, 亀山殿行幸記 : 雅言卿記, 兼基公記. 45: 大嘗會御禊節下次第, 建治三年丁丑日記 : 三善康有, 建治四年正月廿一日 : 徳大寺大相國公孝記, 冬定卿記, 左大史小槻兼文記|内容: 46: 經任卿記, 前豊前守藤憲説記, 實兼公記. 47: 継塵記抄出. 48: 管見記, 公衡公記, 大外記師顕記, 大外記中原師淳記. 49: 真光院禪助僧正記, 吉田内府卿記. 50: 定清記, 叅議雅俊卿記, 太政大臣(公守公)御上表雜事, 仙洞御灌頂日記, 正安二年八月十一日於仙洞被始行熾盛光法, 正安三年御譲位記. 51: 實躬卿記. 52: 公茂公記, 冬平公記, 隆長卿記. 53: 忠教公記, 官記, 正三位長基卿記, 北面秀長記, 大外記中原師右記. 54: 文保元年, 日野中納言資朝卿記, 洞院大納言公敏卿記. 55: 隆蔭卿記, 文保三年記, 尹大納言師賢卿記, 革命記, 立倚子記, 萬里小路中納言藤藤房卿記|内容: 56: 資名卿記, 公秀公記, 一條家記装束抄出, 頼定卿記. 63: 松亞記, 日野大納言時光卿記, 後八條内府實継公記. 74: 成恩寺関白記. 78: 山科家礼記. 82: 諒闇記 : 後成恩寺殿, 宗典僧正記, 綱光公記, 贈従二位宗賢卿記, 義政公記. 84: 長禄二年戊寅正月, 見聞雜記. 87: 言國卿記. 88: 長興宿祢記, 元長卿記, 兼顕卿記, 小槻晴冨記|28末の原奥書に「右山丞記依 仰挍合書冩/享和二年四月 日撿挍保己一」とあり|50「正安二年八月十一日於仙洞被始行熾盛光法」末の原奥書に「文化十五年春二月以南山法曼院藏夲書冩之 撿挍保己一」とあり|横刷毛目表紙を使用|朱点, 朱引, 朱墨筆書き入れあり|付箋あり|蔵書印主信濃須坂藩主堀直格の命によって編集された古記録|他の原本は関東大震災により焼失|極札に「桂壽」(6), 「尚信」(53)との極書, 「武清」(44, 53), 「永海」(51), 「了伴」(52), 「了甫」(74), 「定時」(84, 88)との極印あり|印記: 「花廼家文庫」, 「墨阪十一代主寫藏記」(堀直格(1806-1880)), 「東京大學法理文學部書庫所藏」, 「閲覧室用 FOR USE IN THE READING ROOM」|虫損あり</t>
+          <t>写本|書名は目首及び題簽による|内箱の書名: 大和廿四孝|外箱の書名: 御本|責任表示は『日本古典籍総合目録データベース』による|1: 第1-4. 2: 第5-8. 3: 第9-12. 4: 第13-16. 5: 第17-20. 6: 第21-24|毎半帖10行|漢字平仮名交じり文|奈良絵本|梅唐草文様緞子表紙, 松葉散しに山雲の金箔見返し, 金泥下絵鳥の子紙を使用|列帖装|竪本|二重箱入り|糸切れあり</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -7006,12 +7026,12 @@
       <c r="O54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/31b47601-839e-83b4-6a49-7d11ed020385.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/59c5b4a7-529d-5e9f-454f-8879e85023eb.json</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>31b47601-839e-83b4-6a49-7d11ed020385</t>
+          <t>59c5b4a7-529d-5e9f-454f-8879e85023eb</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
@@ -7021,7 +7041,7 @@
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/31b47601-839e-83b4-6a49-7d11ed020385</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/59c5b4a7-529d-5e9f-454f-8879e85023eb</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
@@ -7031,12 +7051,12 @@
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/d78a0b64be5f71b37b264b3b2eb8172d4e8a5002.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/e4d2c0aa6489eb2a071834a4a14714fecb372bce.jpg</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296216</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296172</t>
         </is>
       </c>
       <c r="W54" t="inlineStr">
@@ -7059,7 +7079,7 @@
       <c r="AB54" t="inlineStr"/>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/31b47601-839e-83b4-6a49-7d11ed020385/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/59c5b4a7-529d-5e9f-454f-8879e85023eb/manifest</t>
         </is>
       </c>
       <c r="AD54" t="inlineStr"/>
@@ -7067,29 +7087,29 @@
       <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="inlineStr"/>
       <c r="AH54" t="n">
-        <v>58</v>
+        <v>76</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [17]</t>
+          <t>日本廿四孝 6巻 [5]</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>A00:6257</t>
+          <t>A00:4084</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>レキダイ ザンケツ ニッキ</t>
+          <t>ヤマト ニジュウシコウ</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>黒川 春村</t>
+          <t>浅井 了意</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -7100,19 +7120,19 @@
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr">
         <is>
-          <t>[安政5 (1858)]</t>
+          <t>[江戸前期]</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr">
         <is>
-          <t>写本|責任表示及び書写年は『日本古典籍総合目録データベース』による|内容: 6: 光明院御記, 後光嚴院御記, 後小松院宸記, 天聴集. 28: 参議藤定長卿記 : 稱山丞記. 37: 定高卿記, 晴御会部類記, 家光卿御記, 權中納言平範輔卿記. 38: 左大史小槻季継記, 後堀川安貞二年放生會(実基公記), 石清水八幡宮, 弁官拝賀次第. 39: 大外記師光記, 資季卿記, 荒凉記, 忠高卿記. 40: 冷泉公相公記, 勝延法眼記 : 東寺大行事, 後中記 : 小路中納言資頼卿記葉室. 41: 中光記, 師兼記, 陽龍記. 42: 大宮司長則記, 口筆 : 實經, 顕朝卿記, 鴨御幸記. 43: 寳治二年記, 深心院關白記, 藤公親記, 照念院関白兼平公記. 44: 頼親記, 亀山殿行幸記 : 雅言卿記, 兼基公記. 45: 大嘗會御禊節下次第, 建治三年丁丑日記 : 三善康有, 建治四年正月廿一日 : 徳大寺大相國公孝記, 冬定卿記, 左大史小槻兼文記|内容: 46: 經任卿記, 前豊前守藤憲説記, 實兼公記. 47: 継塵記抄出. 48: 管見記, 公衡公記, 大外記師顕記, 大外記中原師淳記. 49: 真光院禪助僧正記, 吉田内府卿記. 50: 定清記, 叅議雅俊卿記, 太政大臣(公守公)御上表雜事, 仙洞御灌頂日記, 正安二年八月十一日於仙洞被始行熾盛光法, 正安三年御譲位記. 51: 實躬卿記. 52: 公茂公記, 冬平公記, 隆長卿記. 53: 忠教公記, 官記, 正三位長基卿記, 北面秀長記, 大外記中原師右記. 54: 文保元年, 日野中納言資朝卿記, 洞院大納言公敏卿記. 55: 隆蔭卿記, 文保三年記, 尹大納言師賢卿記, 革命記, 立倚子記, 萬里小路中納言藤藤房卿記|内容: 56: 資名卿記, 公秀公記, 一條家記装束抄出, 頼定卿記. 63: 松亞記, 日野大納言時光卿記, 後八條内府實継公記. 74: 成恩寺関白記. 78: 山科家礼記. 82: 諒闇記 : 後成恩寺殿, 宗典僧正記, 綱光公記, 贈従二位宗賢卿記, 義政公記. 84: 長禄二年戊寅正月, 見聞雜記. 87: 言國卿記. 88: 長興宿祢記, 元長卿記, 兼顕卿記, 小槻晴冨記|28末の原奥書に「右山丞記依 仰挍合書冩/享和二年四月 日撿挍保己一」とあり|50「正安二年八月十一日於仙洞被始行熾盛光法」末の原奥書に「文化十五年春二月以南山法曼院藏夲書冩之 撿挍保己一」とあり|横刷毛目表紙を使用|朱点, 朱引, 朱墨筆書き入れあり|付箋あり|蔵書印主信濃須坂藩主堀直格の命によって編集された古記録|他の原本は関東大震災により焼失|極札に「桂壽」(6), 「尚信」(53)との極書, 「武清」(44, 53), 「永海」(51), 「了伴」(52), 「了甫」(74), 「定時」(84, 88)との極印あり|印記: 「花廼家文庫」, 「墨阪十一代主寫藏記」(堀直格(1806-1880)), 「東京大學法理文學部書庫所藏」, 「閲覧室用 FOR USE IN THE READING ROOM」|虫損あり</t>
+          <t>写本|書名は目首及び題簽による|内箱の書名: 大和廿四孝|外箱の書名: 御本|責任表示は『日本古典籍総合目録データベース』による|1: 第1-4. 2: 第5-8. 3: 第9-12. 4: 第13-16. 5: 第17-20. 6: 第21-24|毎半帖10行|漢字平仮名交じり文|奈良絵本|梅唐草文様緞子表紙, 松葉散しに山雲の金箔見返し, 金泥下絵鳥の子紙を使用|列帖装|竪本|二重箱入り|糸切れあり</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -7128,12 +7148,12 @@
       <c r="O55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/37d790df-458b-48bf-6b67-3f4755f40f0f.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/ff7eb5a9-8bd0-64c0-3cbf-03a54ac07e65.json</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>37d790df-458b-48bf-6b67-3f4755f40f0f</t>
+          <t>ff7eb5a9-8bd0-64c0-3cbf-03a54ac07e65</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
@@ -7143,7 +7163,7 @@
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/37d790df-458b-48bf-6b67-3f4755f40f0f</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/ff7eb5a9-8bd0-64c0-3cbf-03a54ac07e65</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
@@ -7153,12 +7173,12 @@
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/dae05b3fca02a35e3363b381527ea7a899ca4f74.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/550abdb28c4a764b0c1330b7551c32cee807416f.jpg</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296217</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296173</t>
         </is>
       </c>
       <c r="W55" t="inlineStr">
@@ -7181,7 +7201,7 @@
       <c r="AB55" t="inlineStr"/>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/37d790df-458b-48bf-6b67-3f4755f40f0f/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/ff7eb5a9-8bd0-64c0-3cbf-03a54ac07e65/manifest</t>
         </is>
       </c>
       <c r="AD55" t="inlineStr"/>
@@ -7189,29 +7209,29 @@
       <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="inlineStr"/>
       <c r="AH55" t="n">
-        <v>54</v>
+        <v>87</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [18]</t>
+          <t>日本廿四孝 6巻 [6]</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>A00:6257</t>
+          <t>A00:4084</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>レキダイ ザンケツ ニッキ</t>
+          <t>ヤマト ニジュウシコウ</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>黒川 春村</t>
+          <t>浅井 了意</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -7222,19 +7242,19 @@
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr">
         <is>
-          <t>[安政5 (1858)]</t>
+          <t>[江戸前期]</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr">
         <is>
-          <t>写本|責任表示及び書写年は『日本古典籍総合目録データベース』による|内容: 6: 光明院御記, 後光嚴院御記, 後小松院宸記, 天聴集. 28: 参議藤定長卿記 : 稱山丞記. 37: 定高卿記, 晴御会部類記, 家光卿御記, 權中納言平範輔卿記. 38: 左大史小槻季継記, 後堀川安貞二年放生會(実基公記), 石清水八幡宮, 弁官拝賀次第. 39: 大外記師光記, 資季卿記, 荒凉記, 忠高卿記. 40: 冷泉公相公記, 勝延法眼記 : 東寺大行事, 後中記 : 小路中納言資頼卿記葉室. 41: 中光記, 師兼記, 陽龍記. 42: 大宮司長則記, 口筆 : 實經, 顕朝卿記, 鴨御幸記. 43: 寳治二年記, 深心院關白記, 藤公親記, 照念院関白兼平公記. 44: 頼親記, 亀山殿行幸記 : 雅言卿記, 兼基公記. 45: 大嘗會御禊節下次第, 建治三年丁丑日記 : 三善康有, 建治四年正月廿一日 : 徳大寺大相國公孝記, 冬定卿記, 左大史小槻兼文記|内容: 46: 經任卿記, 前豊前守藤憲説記, 實兼公記. 47: 継塵記抄出. 48: 管見記, 公衡公記, 大外記師顕記, 大外記中原師淳記. 49: 真光院禪助僧正記, 吉田内府卿記. 50: 定清記, 叅議雅俊卿記, 太政大臣(公守公)御上表雜事, 仙洞御灌頂日記, 正安二年八月十一日於仙洞被始行熾盛光法, 正安三年御譲位記. 51: 實躬卿記. 52: 公茂公記, 冬平公記, 隆長卿記. 53: 忠教公記, 官記, 正三位長基卿記, 北面秀長記, 大外記中原師右記. 54: 文保元年, 日野中納言資朝卿記, 洞院大納言公敏卿記. 55: 隆蔭卿記, 文保三年記, 尹大納言師賢卿記, 革命記, 立倚子記, 萬里小路中納言藤藤房卿記|内容: 56: 資名卿記, 公秀公記, 一條家記装束抄出, 頼定卿記. 63: 松亞記, 日野大納言時光卿記, 後八條内府實継公記. 74: 成恩寺関白記. 78: 山科家礼記. 82: 諒闇記 : 後成恩寺殿, 宗典僧正記, 綱光公記, 贈従二位宗賢卿記, 義政公記. 84: 長禄二年戊寅正月, 見聞雜記. 87: 言國卿記. 88: 長興宿祢記, 元長卿記, 兼顕卿記, 小槻晴冨記|28末の原奥書に「右山丞記依 仰挍合書冩/享和二年四月 日撿挍保己一」とあり|50「正安二年八月十一日於仙洞被始行熾盛光法」末の原奥書に「文化十五年春二月以南山法曼院藏夲書冩之 撿挍保己一」とあり|横刷毛目表紙を使用|朱点, 朱引, 朱墨筆書き入れあり|付箋あり|蔵書印主信濃須坂藩主堀直格の命によって編集された古記録|他の原本は関東大震災により焼失|極札に「桂壽」(6), 「尚信」(53)との極書, 「武清」(44, 53), 「永海」(51), 「了伴」(52), 「了甫」(74), 「定時」(84, 88)との極印あり|印記: 「花廼家文庫」, 「墨阪十一代主寫藏記」(堀直格(1806-1880)), 「東京大學法理文學部書庫所藏」, 「閲覧室用 FOR USE IN THE READING ROOM」|虫損あり</t>
+          <t>写本|書名は目首及び題簽による|内箱の書名: 大和廿四孝|外箱の書名: 御本|責任表示は『日本古典籍総合目録データベース』による|1: 第1-4. 2: 第5-8. 3: 第9-12. 4: 第13-16. 5: 第17-20. 6: 第21-24|毎半帖10行|漢字平仮名交じり文|奈良絵本|梅唐草文様緞子表紙, 松葉散しに山雲の金箔見返し, 金泥下絵鳥の子紙を使用|列帖装|竪本|二重箱入り|糸切れあり</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -7250,12 +7270,12 @@
       <c r="O56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/c69854e0-18e9-71b3-a7b1-22422a16688b.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/0106be3f-16cb-3945-1c3c-419a27f26c16.json</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>c69854e0-18e9-71b3-a7b1-22422a16688b</t>
+          <t>0106be3f-16cb-3945-1c3c-419a27f26c16</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
@@ -7265,7 +7285,7 @@
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/c69854e0-18e9-71b3-a7b1-22422a16688b</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/0106be3f-16cb-3945-1c3c-419a27f26c16</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
@@ -7275,12 +7295,12 @@
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/584cfd5ec1bb0f374ab03f25ca3600a8ec2e67bf.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/b1c4cf868676ac5b8b2f574249475349a7a90813.jpg</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296218</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296174</t>
         </is>
       </c>
       <c r="W56" t="inlineStr">
@@ -7303,7 +7323,7 @@
       <c r="AB56" t="inlineStr"/>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/c69854e0-18e9-71b3-a7b1-22422a16688b/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/0106be3f-16cb-3945-1c3c-419a27f26c16/manifest</t>
         </is>
       </c>
       <c r="AD56" t="inlineStr"/>
@@ -7311,29 +7331,29 @@
       <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="inlineStr"/>
       <c r="AH56" t="n">
-        <v>77</v>
+        <v>70</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [19]</t>
+          <t>京ものかたり</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>A00:6257</t>
+          <t>A00:4085</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>レキダイ ザンケツ ニッキ</t>
+          <t>キョウモノガタリ</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>黒川 春村</t>
+          <t>洛陽散人</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -7344,7 +7364,7 @@
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr">
         <is>
-          <t>[安政5 (1858)]</t>
+          <t>[江戸前期]</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -7356,7 +7376,7 @@
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr">
         <is>
-          <t>写本|責任表示及び書写年は『日本古典籍総合目録データベース』による|内容: 6: 光明院御記, 後光嚴院御記, 後小松院宸記, 天聴集. 28: 参議藤定長卿記 : 稱山丞記. 37: 定高卿記, 晴御会部類記, 家光卿御記, 權中納言平範輔卿記. 38: 左大史小槻季継記, 後堀川安貞二年放生會(実基公記), 石清水八幡宮, 弁官拝賀次第. 39: 大外記師光記, 資季卿記, 荒凉記, 忠高卿記. 40: 冷泉公相公記, 勝延法眼記 : 東寺大行事, 後中記 : 小路中納言資頼卿記葉室. 41: 中光記, 師兼記, 陽龍記. 42: 大宮司長則記, 口筆 : 實經, 顕朝卿記, 鴨御幸記. 43: 寳治二年記, 深心院關白記, 藤公親記, 照念院関白兼平公記. 44: 頼親記, 亀山殿行幸記 : 雅言卿記, 兼基公記. 45: 大嘗會御禊節下次第, 建治三年丁丑日記 : 三善康有, 建治四年正月廿一日 : 徳大寺大相國公孝記, 冬定卿記, 左大史小槻兼文記|内容: 46: 經任卿記, 前豊前守藤憲説記, 實兼公記. 47: 継塵記抄出. 48: 管見記, 公衡公記, 大外記師顕記, 大外記中原師淳記. 49: 真光院禪助僧正記, 吉田内府卿記. 50: 定清記, 叅議雅俊卿記, 太政大臣(公守公)御上表雜事, 仙洞御灌頂日記, 正安二年八月十一日於仙洞被始行熾盛光法, 正安三年御譲位記. 51: 實躬卿記. 52: 公茂公記, 冬平公記, 隆長卿記. 53: 忠教公記, 官記, 正三位長基卿記, 北面秀長記, 大外記中原師右記. 54: 文保元年, 日野中納言資朝卿記, 洞院大納言公敏卿記. 55: 隆蔭卿記, 文保三年記, 尹大納言師賢卿記, 革命記, 立倚子記, 萬里小路中納言藤藤房卿記|内容: 56: 資名卿記, 公秀公記, 一條家記装束抄出, 頼定卿記. 63: 松亞記, 日野大納言時光卿記, 後八條内府實継公記. 74: 成恩寺関白記. 78: 山科家礼記. 82: 諒闇記 : 後成恩寺殿, 宗典僧正記, 綱光公記, 贈従二位宗賢卿記, 義政公記. 84: 長禄二年戊寅正月, 見聞雜記. 87: 言國卿記. 88: 長興宿祢記, 元長卿記, 兼顕卿記, 小槻晴冨記|28末の原奥書に「右山丞記依 仰挍合書冩/享和二年四月 日撿挍保己一」とあり|50「正安二年八月十一日於仙洞被始行熾盛光法」末の原奥書に「文化十五年春二月以南山法曼院藏夲書冩之 撿挍保己一」とあり|横刷毛目表紙を使用|朱点, 朱引, 朱墨筆書き入れあり|付箋あり|蔵書印主信濃須坂藩主堀直格の命によって編集された古記録|他の原本は関東大震災により焼失|極札に「桂壽」(6), 「尚信」(53)との極書, 「武清」(44, 53), 「永海」(51), 「了伴」(52), 「了甫」(74), 「定時」(84, 88)との極印あり|印記: 「花廼家文庫」, 「墨阪十一代主寫藏記」(堀直格(1806-1880)), 「東京大學法理文學部書庫所藏」, 「閲覧室用 FOR USE IN THE READING ROOM」|虫損あり</t>
+          <t>写本|書名は題簽による|[跋]中の書名: 見ぬ京ものかたり|外箱の書名: 御本|[跋]に「万治元年の秋夜長きひ ... いぬの年九月の末のはふのなん時 洛陽散人たれ某」とあり|内容: 儒佛の論, など|毎半帖10行|漢字平仮名交じり文|桜唐草文様緞子表紙, 松葉散しに山雲の金箔見返し, 金泥下絵鳥の子紙を使用|列帖装|二重箱入り</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -7372,12 +7392,12 @@
       <c r="O57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/1373f0d8-7cc0-4591-2c18-798fa20f483d.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/13969a60-692e-663a-3a83-97b8168b8fbe.json</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>1373f0d8-7cc0-4591-2c18-798fa20f483d</t>
+          <t>13969a60-692e-663a-3a83-97b8168b8fbe</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
@@ -7387,7 +7407,7 @@
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/1373f0d8-7cc0-4591-2c18-798fa20f483d</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/13969a60-692e-663a-3a83-97b8168b8fbe</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
@@ -7397,12 +7417,12 @@
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/326ed2db044321d7b007462c9ac98badfd7f671a.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/b4c216cdd7c363c063be4e90de6eea21dd1da6e3.jpg</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296219</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296175</t>
         </is>
       </c>
       <c r="W57" t="inlineStr">
@@ -7425,7 +7445,7 @@
       <c r="AB57" t="inlineStr"/>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/1373f0d8-7cc0-4591-2c18-798fa20f483d/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/13969a60-692e-663a-3a83-97b8168b8fbe/manifest</t>
         </is>
       </c>
       <c r="AD57" t="inlineStr"/>
@@ -7433,52 +7453,52 @@
       <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="inlineStr"/>
       <c r="AH57" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [20]</t>
+          <t>北遊漫録 3巻再1巻 [1]</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>A00:6257</t>
+          <t>A00:4099</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>レキダイ ザンケツ ニッキ</t>
+          <t>ホクユウ マンロク</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>黒川 春村</t>
+          <t>久保田 米僊</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>[書写者不明]</t>
+          <t>久保田米僊 [自筆]</t>
         </is>
       </c>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr">
         <is>
-          <t>[安政5 (1858)]</t>
+          <t>明治21 [1888]-明治24 [1891]</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr">
         <is>
-          <t>写本|責任表示及び書写年は『日本古典籍総合目録データベース』による|内容: 6: 光明院御記, 後光嚴院御記, 後小松院宸記, 天聴集. 28: 参議藤定長卿記 : 稱山丞記. 37: 定高卿記, 晴御会部類記, 家光卿御記, 權中納言平範輔卿記. 38: 左大史小槻季継記, 後堀川安貞二年放生會(実基公記), 石清水八幡宮, 弁官拝賀次第. 39: 大外記師光記, 資季卿記, 荒凉記, 忠高卿記. 40: 冷泉公相公記, 勝延法眼記 : 東寺大行事, 後中記 : 小路中納言資頼卿記葉室. 41: 中光記, 師兼記, 陽龍記. 42: 大宮司長則記, 口筆 : 實經, 顕朝卿記, 鴨御幸記. 43: 寳治二年記, 深心院關白記, 藤公親記, 照念院関白兼平公記. 44: 頼親記, 亀山殿行幸記 : 雅言卿記, 兼基公記. 45: 大嘗會御禊節下次第, 建治三年丁丑日記 : 三善康有, 建治四年正月廿一日 : 徳大寺大相國公孝記, 冬定卿記, 左大史小槻兼文記|内容: 46: 經任卿記, 前豊前守藤憲説記, 實兼公記. 47: 継塵記抄出. 48: 管見記, 公衡公記, 大外記師顕記, 大外記中原師淳記. 49: 真光院禪助僧正記, 吉田内府卿記. 50: 定清記, 叅議雅俊卿記, 太政大臣(公守公)御上表雜事, 仙洞御灌頂日記, 正安二年八月十一日於仙洞被始行熾盛光法, 正安三年御譲位記. 51: 實躬卿記. 52: 公茂公記, 冬平公記, 隆長卿記. 53: 忠教公記, 官記, 正三位長基卿記, 北面秀長記, 大外記中原師右記. 54: 文保元年, 日野中納言資朝卿記, 洞院大納言公敏卿記. 55: 隆蔭卿記, 文保三年記, 尹大納言師賢卿記, 革命記, 立倚子記, 萬里小路中納言藤藤房卿記|内容: 56: 資名卿記, 公秀公記, 一條家記装束抄出, 頼定卿記. 63: 松亞記, 日野大納言時光卿記, 後八條内府實継公記. 74: 成恩寺関白記. 78: 山科家礼記. 82: 諒闇記 : 後成恩寺殿, 宗典僧正記, 綱光公記, 贈従二位宗賢卿記, 義政公記. 84: 長禄二年戊寅正月, 見聞雜記. 87: 言國卿記. 88: 長興宿祢記, 元長卿記, 兼顕卿記, 小槻晴冨記|28末の原奥書に「右山丞記依 仰挍合書冩/享和二年四月 日撿挍保己一」とあり|50「正安二年八月十一日於仙洞被始行熾盛光法」末の原奥書に「文化十五年春二月以南山法曼院藏夲書冩之 撿挍保己一」とあり|横刷毛目表紙を使用|朱点, 朱引, 朱墨筆書き入れあり|付箋あり|蔵書印主信濃須坂藩主堀直格の命によって編集された古記録|他の原本は関東大震災により焼失|極札に「桂壽」(6), 「尚信」(53)との極書, 「武清」(44, 53), 「永海」(51), 「了伴」(52), 「了甫」(74), 「定時」(84, 88)との極印あり|印記: 「花廼家文庫」, 「墨阪十一代主寫藏記」(堀直格(1806-1880)), 「東京大學法理文學部書庫所藏」, 「閲覧室用 FOR USE IN THE READING ROOM」|虫損あり</t>
+          <t>写本|書名は扉による|帙題簽に「久保田米僊草稿」とあり|扉に「明治廿一年はる五月」(乾), 「明治廿一年はる六月」(坤), 「明治廿一年はる六月中澣」(瑞啚), 「明治廿四年五月十九日」(再)とあり|乾末に「増補考古畫譜五巻 發兌書肆 有隣堂」とあり|おもに図版|彩色あり|双葉装|印記: 「田寛之印」, 「山脊与弥との」</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -7494,12 +7514,12 @@
       <c r="O58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/d64280ea-576f-4bf3-9413-1b0bf6485e16.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/fdb2f4c7-47bb-0fc6-53e6-e8ffb5796046.json</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>d64280ea-576f-4bf3-9413-1b0bf6485e16</t>
+          <t>fdb2f4c7-47bb-0fc6-53e6-e8ffb5796046</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
@@ -7509,7 +7529,7 @@
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/d64280ea-576f-4bf3-9413-1b0bf6485e16</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/fdb2f4c7-47bb-0fc6-53e6-e8ffb5796046</t>
         </is>
       </c>
       <c r="T58" t="inlineStr">
@@ -7519,12 +7539,12 @@
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/c5e3a0bdc0b67f7429d47677a33485a6a498e20f.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/789ef89fb4fc813de5d276f3c43f982c6760d60b.jpg</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296220</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296176</t>
         </is>
       </c>
       <c r="W58" t="inlineStr">
@@ -7547,7 +7567,7 @@
       <c r="AB58" t="inlineStr"/>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/d64280ea-576f-4bf3-9413-1b0bf6485e16/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/fdb2f4c7-47bb-0fc6-53e6-e8ffb5796046/manifest</t>
         </is>
       </c>
       <c r="AD58" t="inlineStr"/>
@@ -7555,52 +7575,52 @@
       <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="inlineStr"/>
       <c r="AH58" t="n">
-        <v>75</v>
+        <v>31</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [21]</t>
+          <t>北遊漫録 3巻再1巻 [2]</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>A00:6257</t>
+          <t>A00:4099</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>レキダイ ザンケツ ニッキ</t>
+          <t>ホクユウ マンロク</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>黒川 春村</t>
+          <t>久保田 米僊</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>[書写者不明]</t>
+          <t>久保田米僊 [自筆]</t>
         </is>
       </c>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr">
         <is>
-          <t>[安政5 (1858)]</t>
+          <t>明治21 [1888]-明治24 [1891]</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr">
         <is>
-          <t>写本|責任表示及び書写年は『日本古典籍総合目録データベース』による|内容: 6: 光明院御記, 後光嚴院御記, 後小松院宸記, 天聴集. 28: 参議藤定長卿記 : 稱山丞記. 37: 定高卿記, 晴御会部類記, 家光卿御記, 權中納言平範輔卿記. 38: 左大史小槻季継記, 後堀川安貞二年放生會(実基公記), 石清水八幡宮, 弁官拝賀次第. 39: 大外記師光記, 資季卿記, 荒凉記, 忠高卿記. 40: 冷泉公相公記, 勝延法眼記 : 東寺大行事, 後中記 : 小路中納言資頼卿記葉室. 41: 中光記, 師兼記, 陽龍記. 42: 大宮司長則記, 口筆 : 實經, 顕朝卿記, 鴨御幸記. 43: 寳治二年記, 深心院關白記, 藤公親記, 照念院関白兼平公記. 44: 頼親記, 亀山殿行幸記 : 雅言卿記, 兼基公記. 45: 大嘗會御禊節下次第, 建治三年丁丑日記 : 三善康有, 建治四年正月廿一日 : 徳大寺大相國公孝記, 冬定卿記, 左大史小槻兼文記|内容: 46: 經任卿記, 前豊前守藤憲説記, 實兼公記. 47: 継塵記抄出. 48: 管見記, 公衡公記, 大外記師顕記, 大外記中原師淳記. 49: 真光院禪助僧正記, 吉田内府卿記. 50: 定清記, 叅議雅俊卿記, 太政大臣(公守公)御上表雜事, 仙洞御灌頂日記, 正安二年八月十一日於仙洞被始行熾盛光法, 正安三年御譲位記. 51: 實躬卿記. 52: 公茂公記, 冬平公記, 隆長卿記. 53: 忠教公記, 官記, 正三位長基卿記, 北面秀長記, 大外記中原師右記. 54: 文保元年, 日野中納言資朝卿記, 洞院大納言公敏卿記. 55: 隆蔭卿記, 文保三年記, 尹大納言師賢卿記, 革命記, 立倚子記, 萬里小路中納言藤藤房卿記|内容: 56: 資名卿記, 公秀公記, 一條家記装束抄出, 頼定卿記. 63: 松亞記, 日野大納言時光卿記, 後八條内府實継公記. 74: 成恩寺関白記. 78: 山科家礼記. 82: 諒闇記 : 後成恩寺殿, 宗典僧正記, 綱光公記, 贈従二位宗賢卿記, 義政公記. 84: 長禄二年戊寅正月, 見聞雜記. 87: 言國卿記. 88: 長興宿祢記, 元長卿記, 兼顕卿記, 小槻晴冨記|28末の原奥書に「右山丞記依 仰挍合書冩/享和二年四月 日撿挍保己一」とあり|50「正安二年八月十一日於仙洞被始行熾盛光法」末の原奥書に「文化十五年春二月以南山法曼院藏夲書冩之 撿挍保己一」とあり|横刷毛目表紙を使用|朱点, 朱引, 朱墨筆書き入れあり|付箋あり|蔵書印主信濃須坂藩主堀直格の命によって編集された古記録|他の原本は関東大震災により焼失|極札に「桂壽」(6), 「尚信」(53)との極書, 「武清」(44, 53), 「永海」(51), 「了伴」(52), 「了甫」(74), 「定時」(84, 88)との極印あり|印記: 「花廼家文庫」, 「墨阪十一代主寫藏記」(堀直格(1806-1880)), 「東京大學法理文學部書庫所藏」, 「閲覧室用 FOR USE IN THE READING ROOM」|虫損あり</t>
+          <t>写本|書名は扉による|帙題簽に「久保田米僊草稿」とあり|扉に「明治廿一年はる五月」(乾), 「明治廿一年はる六月」(坤), 「明治廿一年はる六月中澣」(瑞啚), 「明治廿四年五月十九日」(再)とあり|乾末に「増補考古畫譜五巻 發兌書肆 有隣堂」とあり|おもに図版|彩色あり|双葉装|印記: 「田寛之印」, 「山脊与弥との」</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -7616,12 +7636,12 @@
       <c r="O59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/decc377c-887e-7362-3bf7-81b1c9c58641.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/01f5e469-1d82-36bd-3e33-34c56a942a2d.json</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>decc377c-887e-7362-3bf7-81b1c9c58641</t>
+          <t>01f5e469-1d82-36bd-3e33-34c56a942a2d</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
@@ -7631,7 +7651,7 @@
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/decc377c-887e-7362-3bf7-81b1c9c58641</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/01f5e469-1d82-36bd-3e33-34c56a942a2d</t>
         </is>
       </c>
       <c r="T59" t="inlineStr">
@@ -7641,12 +7661,12 @@
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/cfd0eab55fb67ed7ab341ab27bc1cb892d7a575c.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/0e331722b5a82ea48f273a6b7465d2784dc8a44c.jpg</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296221</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296177</t>
         </is>
       </c>
       <c r="W59" t="inlineStr">
@@ -7669,7 +7689,7 @@
       <c r="AB59" t="inlineStr"/>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/decc377c-887e-7362-3bf7-81b1c9c58641/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/01f5e469-1d82-36bd-3e33-34c56a942a2d/manifest</t>
         </is>
       </c>
       <c r="AD59" t="inlineStr"/>
@@ -7677,52 +7697,52 @@
       <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="inlineStr"/>
       <c r="AH59" t="n">
-        <v>51</v>
+        <v>31</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [22]</t>
+          <t>北遊漫録 3巻再1巻 [3]</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>A00:6257</t>
+          <t>A00:4099</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>レキダイ ザンケツ ニッキ</t>
+          <t>ホクユウ マンロク</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>黒川 春村</t>
+          <t>久保田 米僊</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>[書写者不明]</t>
+          <t>久保田米僊 [自筆]</t>
         </is>
       </c>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr">
         <is>
-          <t>[安政5 (1858)]</t>
+          <t>明治21 [1888]-明治24 [1891]</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr">
         <is>
-          <t>写本|責任表示及び書写年は『日本古典籍総合目録データベース』による|内容: 6: 光明院御記, 後光嚴院御記, 後小松院宸記, 天聴集. 28: 参議藤定長卿記 : 稱山丞記. 37: 定高卿記, 晴御会部類記, 家光卿御記, 權中納言平範輔卿記. 38: 左大史小槻季継記, 後堀川安貞二年放生會(実基公記), 石清水八幡宮, 弁官拝賀次第. 39: 大外記師光記, 資季卿記, 荒凉記, 忠高卿記. 40: 冷泉公相公記, 勝延法眼記 : 東寺大行事, 後中記 : 小路中納言資頼卿記葉室. 41: 中光記, 師兼記, 陽龍記. 42: 大宮司長則記, 口筆 : 實經, 顕朝卿記, 鴨御幸記. 43: 寳治二年記, 深心院關白記, 藤公親記, 照念院関白兼平公記. 44: 頼親記, 亀山殿行幸記 : 雅言卿記, 兼基公記. 45: 大嘗會御禊節下次第, 建治三年丁丑日記 : 三善康有, 建治四年正月廿一日 : 徳大寺大相國公孝記, 冬定卿記, 左大史小槻兼文記|内容: 46: 經任卿記, 前豊前守藤憲説記, 實兼公記. 47: 継塵記抄出. 48: 管見記, 公衡公記, 大外記師顕記, 大外記中原師淳記. 49: 真光院禪助僧正記, 吉田内府卿記. 50: 定清記, 叅議雅俊卿記, 太政大臣(公守公)御上表雜事, 仙洞御灌頂日記, 正安二年八月十一日於仙洞被始行熾盛光法, 正安三年御譲位記. 51: 實躬卿記. 52: 公茂公記, 冬平公記, 隆長卿記. 53: 忠教公記, 官記, 正三位長基卿記, 北面秀長記, 大外記中原師右記. 54: 文保元年, 日野中納言資朝卿記, 洞院大納言公敏卿記. 55: 隆蔭卿記, 文保三年記, 尹大納言師賢卿記, 革命記, 立倚子記, 萬里小路中納言藤藤房卿記|内容: 56: 資名卿記, 公秀公記, 一條家記装束抄出, 頼定卿記. 63: 松亞記, 日野大納言時光卿記, 後八條内府實継公記. 74: 成恩寺関白記. 78: 山科家礼記. 82: 諒闇記 : 後成恩寺殿, 宗典僧正記, 綱光公記, 贈従二位宗賢卿記, 義政公記. 84: 長禄二年戊寅正月, 見聞雜記. 87: 言國卿記. 88: 長興宿祢記, 元長卿記, 兼顕卿記, 小槻晴冨記|28末の原奥書に「右山丞記依 仰挍合書冩/享和二年四月 日撿挍保己一」とあり|50「正安二年八月十一日於仙洞被始行熾盛光法」末の原奥書に「文化十五年春二月以南山法曼院藏夲書冩之 撿挍保己一」とあり|横刷毛目表紙を使用|朱点, 朱引, 朱墨筆書き入れあり|付箋あり|蔵書印主信濃須坂藩主堀直格の命によって編集された古記録|他の原本は関東大震災により焼失|極札に「桂壽」(6), 「尚信」(53)との極書, 「武清」(44, 53), 「永海」(51), 「了伴」(52), 「了甫」(74), 「定時」(84, 88)との極印あり|印記: 「花廼家文庫」, 「墨阪十一代主寫藏記」(堀直格(1806-1880)), 「東京大學法理文學部書庫所藏」, 「閲覧室用 FOR USE IN THE READING ROOM」|虫損あり</t>
+          <t>写本|書名は扉による|帙題簽に「久保田米僊草稿」とあり|扉に「明治廿一年はる五月」(乾), 「明治廿一年はる六月」(坤), 「明治廿一年はる六月中澣」(瑞啚), 「明治廿四年五月十九日」(再)とあり|乾末に「増補考古畫譜五巻 發兌書肆 有隣堂」とあり|おもに図版|彩色あり|双葉装|印記: 「田寛之印」, 「山脊与弥との」</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -7738,12 +7758,12 @@
       <c r="O60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/b6bde9f3-3f94-81f1-4307-d86d59d90fa3.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/1a4a12a3-0ae7-8858-3851-f3845f60709b.json</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>b6bde9f3-3f94-81f1-4307-d86d59d90fa3</t>
+          <t>1a4a12a3-0ae7-8858-3851-f3845f60709b</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
@@ -7753,7 +7773,7 @@
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/b6bde9f3-3f94-81f1-4307-d86d59d90fa3</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/1a4a12a3-0ae7-8858-3851-f3845f60709b</t>
         </is>
       </c>
       <c r="T60" t="inlineStr">
@@ -7763,12 +7783,12 @@
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/eda09740787be30df4b5cefc348bc2c063c8932c.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/3897bac3ffa751a75c02bb59922c185ca93a9f1e.jpg</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296222</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296178</t>
         </is>
       </c>
       <c r="W60" t="inlineStr">
@@ -7791,7 +7811,7 @@
       <c r="AB60" t="inlineStr"/>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/b6bde9f3-3f94-81f1-4307-d86d59d90fa3/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/1a4a12a3-0ae7-8858-3851-f3845f60709b/manifest</t>
         </is>
       </c>
       <c r="AD60" t="inlineStr"/>
@@ -7799,52 +7819,52 @@
       <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="inlineStr"/>
       <c r="AH60" t="n">
-        <v>62</v>
+        <v>31</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [23]</t>
+          <t>北遊漫録 3巻再1巻 [4]</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>A00:6257</t>
+          <t>A00:4099</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>レキダイ ザンケツ ニッキ</t>
+          <t>ホクユウ マンロク</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>黒川 春村</t>
+          <t>久保田 米僊</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>[書写者不明]</t>
+          <t>久保田米僊 [自筆]</t>
         </is>
       </c>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr">
         <is>
-          <t>[安政5 (1858)]</t>
+          <t>明治21 [1888]-明治24 [1891]</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr">
         <is>
-          <t>写本|責任表示及び書写年は『日本古典籍総合目録データベース』による|内容: 6: 光明院御記, 後光嚴院御記, 後小松院宸記, 天聴集. 28: 参議藤定長卿記 : 稱山丞記. 37: 定高卿記, 晴御会部類記, 家光卿御記, 權中納言平範輔卿記. 38: 左大史小槻季継記, 後堀川安貞二年放生會(実基公記), 石清水八幡宮, 弁官拝賀次第. 39: 大外記師光記, 資季卿記, 荒凉記, 忠高卿記. 40: 冷泉公相公記, 勝延法眼記 : 東寺大行事, 後中記 : 小路中納言資頼卿記葉室. 41: 中光記, 師兼記, 陽龍記. 42: 大宮司長則記, 口筆 : 實經, 顕朝卿記, 鴨御幸記. 43: 寳治二年記, 深心院關白記, 藤公親記, 照念院関白兼平公記. 44: 頼親記, 亀山殿行幸記 : 雅言卿記, 兼基公記. 45: 大嘗會御禊節下次第, 建治三年丁丑日記 : 三善康有, 建治四年正月廿一日 : 徳大寺大相國公孝記, 冬定卿記, 左大史小槻兼文記|内容: 46: 經任卿記, 前豊前守藤憲説記, 實兼公記. 47: 継塵記抄出. 48: 管見記, 公衡公記, 大外記師顕記, 大外記中原師淳記. 49: 真光院禪助僧正記, 吉田内府卿記. 50: 定清記, 叅議雅俊卿記, 太政大臣(公守公)御上表雜事, 仙洞御灌頂日記, 正安二年八月十一日於仙洞被始行熾盛光法, 正安三年御譲位記. 51: 實躬卿記. 52: 公茂公記, 冬平公記, 隆長卿記. 53: 忠教公記, 官記, 正三位長基卿記, 北面秀長記, 大外記中原師右記. 54: 文保元年, 日野中納言資朝卿記, 洞院大納言公敏卿記. 55: 隆蔭卿記, 文保三年記, 尹大納言師賢卿記, 革命記, 立倚子記, 萬里小路中納言藤藤房卿記|内容: 56: 資名卿記, 公秀公記, 一條家記装束抄出, 頼定卿記. 63: 松亞記, 日野大納言時光卿記, 後八條内府實継公記. 74: 成恩寺関白記. 78: 山科家礼記. 82: 諒闇記 : 後成恩寺殿, 宗典僧正記, 綱光公記, 贈従二位宗賢卿記, 義政公記. 84: 長禄二年戊寅正月, 見聞雜記. 87: 言國卿記. 88: 長興宿祢記, 元長卿記, 兼顕卿記, 小槻晴冨記|28末の原奥書に「右山丞記依 仰挍合書冩/享和二年四月 日撿挍保己一」とあり|50「正安二年八月十一日於仙洞被始行熾盛光法」末の原奥書に「文化十五年春二月以南山法曼院藏夲書冩之 撿挍保己一」とあり|横刷毛目表紙を使用|朱点, 朱引, 朱墨筆書き入れあり|付箋あり|蔵書印主信濃須坂藩主堀直格の命によって編集された古記録|他の原本は関東大震災により焼失|極札に「桂壽」(6), 「尚信」(53)との極書, 「武清」(44, 53), 「永海」(51), 「了伴」(52), 「了甫」(74), 「定時」(84, 88)との極印あり|印記: 「花廼家文庫」, 「墨阪十一代主寫藏記」(堀直格(1806-1880)), 「東京大學法理文學部書庫所藏」, 「閲覧室用 FOR USE IN THE READING ROOM」|虫損あり</t>
+          <t>写本|書名は扉による|帙題簽に「久保田米僊草稿」とあり|扉に「明治廿一年はる五月」(乾), 「明治廿一年はる六月」(坤), 「明治廿一年はる六月中澣」(瑞啚), 「明治廿四年五月十九日」(再)とあり|乾末に「増補考古畫譜五巻 發兌書肆 有隣堂」とあり|おもに図版|彩色あり|双葉装|印記: 「田寛之印」, 「山脊与弥との」</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -7860,12 +7880,12 @@
       <c r="O61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/8bd2b968-05d3-77b9-352f-f36fa2260d39.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/73cbda29-23d4-a760-5213-0395cd767491.json</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>8bd2b968-05d3-77b9-352f-f36fa2260d39</t>
+          <t>73cbda29-23d4-a760-5213-0395cd767491</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
@@ -7875,7 +7895,7 @@
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/8bd2b968-05d3-77b9-352f-f36fa2260d39</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/73cbda29-23d4-a760-5213-0395cd767491</t>
         </is>
       </c>
       <c r="T61" t="inlineStr">
@@ -7885,12 +7905,12 @@
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/30225b7ec7795f0c4d6102081bbf79b701183504.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/74a9af6c2a682e260aa96f2ded5a07abfcd3098c.jpg</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296223</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296179</t>
         </is>
       </c>
       <c r="W61" t="inlineStr">
@@ -7913,7 +7933,7 @@
       <c r="AB61" t="inlineStr"/>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/8bd2b968-05d3-77b9-352f-f36fa2260d39/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/73cbda29-23d4-a760-5213-0395cd767491/manifest</t>
         </is>
       </c>
       <c r="AD61" t="inlineStr"/>
@@ -7921,40 +7941,36 @@
       <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="inlineStr"/>
       <c r="AH61" t="n">
-        <v>74</v>
+        <v>22</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [24]</t>
+          <t>蘭主之書翰使節持参叅途中之図</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>A00:6257</t>
+          <t>A00:4146</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>レキダイ ザンケツ ニッキ</t>
+          <t>ランシュ ノ ショカン シセツ ジサン トチュウ ノ ズ</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>黒川 春村</t>
-        </is>
-      </c>
+      <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
-          <t>[書写者不明]</t>
+          <t>[製作者不明]</t>
         </is>
       </c>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr">
         <is>
-          <t>[安政5 (1858)]</t>
+          <t>天保15 [1844] 識語</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -7966,7 +7982,7 @@
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr">
         <is>
-          <t>写本|責任表示及び書写年は『日本古典籍総合目録データベース』による|内容: 6: 光明院御記, 後光嚴院御記, 後小松院宸記, 天聴集. 28: 参議藤定長卿記 : 稱山丞記. 37: 定高卿記, 晴御会部類記, 家光卿御記, 權中納言平範輔卿記. 38: 左大史小槻季継記, 後堀川安貞二年放生會(実基公記), 石清水八幡宮, 弁官拝賀次第. 39: 大外記師光記, 資季卿記, 荒凉記, 忠高卿記. 40: 冷泉公相公記, 勝延法眼記 : 東寺大行事, 後中記 : 小路中納言資頼卿記葉室. 41: 中光記, 師兼記, 陽龍記. 42: 大宮司長則記, 口筆 : 實經, 顕朝卿記, 鴨御幸記. 43: 寳治二年記, 深心院關白記, 藤公親記, 照念院関白兼平公記. 44: 頼親記, 亀山殿行幸記 : 雅言卿記, 兼基公記. 45: 大嘗會御禊節下次第, 建治三年丁丑日記 : 三善康有, 建治四年正月廿一日 : 徳大寺大相國公孝記, 冬定卿記, 左大史小槻兼文記|内容: 46: 經任卿記, 前豊前守藤憲説記, 實兼公記. 47: 継塵記抄出. 48: 管見記, 公衡公記, 大外記師顕記, 大外記中原師淳記. 49: 真光院禪助僧正記, 吉田内府卿記. 50: 定清記, 叅議雅俊卿記, 太政大臣(公守公)御上表雜事, 仙洞御灌頂日記, 正安二年八月十一日於仙洞被始行熾盛光法, 正安三年御譲位記. 51: 實躬卿記. 52: 公茂公記, 冬平公記, 隆長卿記. 53: 忠教公記, 官記, 正三位長基卿記, 北面秀長記, 大外記中原師右記. 54: 文保元年, 日野中納言資朝卿記, 洞院大納言公敏卿記. 55: 隆蔭卿記, 文保三年記, 尹大納言師賢卿記, 革命記, 立倚子記, 萬里小路中納言藤藤房卿記|内容: 56: 資名卿記, 公秀公記, 一條家記装束抄出, 頼定卿記. 63: 松亞記, 日野大納言時光卿記, 後八條内府實継公記. 74: 成恩寺関白記. 78: 山科家礼記. 82: 諒闇記 : 後成恩寺殿, 宗典僧正記, 綱光公記, 贈従二位宗賢卿記, 義政公記. 84: 長禄二年戊寅正月, 見聞雜記. 87: 言國卿記. 88: 長興宿祢記, 元長卿記, 兼顕卿記, 小槻晴冨記|28末の原奥書に「右山丞記依 仰挍合書冩/享和二年四月 日撿挍保己一」とあり|50「正安二年八月十一日於仙洞被始行熾盛光法」末の原奥書に「文化十五年春二月以南山法曼院藏夲書冩之 撿挍保己一」とあり|横刷毛目表紙を使用|朱点, 朱引, 朱墨筆書き入れあり|付箋あり|蔵書印主信濃須坂藩主堀直格の命によって編集された古記録|他の原本は関東大震災により焼失|極札に「桂壽」(6), 「尚信」(53)との極書, 「武清」(44, 53), 「永海」(51), 「了伴」(52), 「了甫」(74), 「定時」(84, 88)との極印あり|印記: 「花廼家文庫」, 「墨阪十一代主寫藏記」(堀直格(1806-1880)), 「東京大學法理文學部書庫所藏」, 「閲覧室用 FOR USE IN THE READING ROOM」|虫損あり</t>
+          <t>書名は題簽による|箱の書名: 和蘭國軍艦人物兵器等図|冒頭に「天保十五年甲辰秋七月二日和蘭國官船奉其主命来進於我﨑嶴茲掲略圖摸其全般及内面結構所備之諸兵器等」との識語あり|絵巻|彩色あり|印記: 「籌海庫」</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -7982,12 +7998,12 @@
       <c r="O62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/c6e97538-22ed-8a51-0e3a-550b7d652860.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/ca3ac8e1-6c03-5832-3987-70b1fa71258a.json</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>c6e97538-22ed-8a51-0e3a-550b7d652860</t>
+          <t>ca3ac8e1-6c03-5832-3987-70b1fa71258a</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
@@ -7997,7 +8013,7 @@
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/c6e97538-22ed-8a51-0e3a-550b7d652860</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/ca3ac8e1-6c03-5832-3987-70b1fa71258a</t>
         </is>
       </c>
       <c r="T62" t="inlineStr">
@@ -8007,12 +8023,12 @@
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/a04dfdaed6c9dc7211358c5ad96c4bc6e9312747.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/32f72c2d68d9e56e4f46528e6997cbb4c330cc23.jpg</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296224</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296180</t>
         </is>
       </c>
       <c r="W62" t="inlineStr">
@@ -8035,7 +8051,7 @@
       <c r="AB62" t="inlineStr"/>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/c6e97538-22ed-8a51-0e3a-550b7d652860/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/ca3ac8e1-6c03-5832-3987-70b1fa71258a/manifest</t>
         </is>
       </c>
       <c r="AD62" t="inlineStr"/>
@@ -8043,40 +8059,36 @@
       <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="inlineStr"/>
       <c r="AH62" t="n">
-        <v>62</v>
+        <v>22</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [25]</t>
+          <t>喎蘭軍艦プレカット並銃劍等之図</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>A00:6257</t>
+          <t>A00:4147</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>レキダイ ザンケツ ニッキ</t>
+          <t>オランダ グンカン プレカット ナラビニ ジュウケン トウ ノ ズ</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>黒川 春村</t>
-        </is>
-      </c>
+      <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
-          <t>[書写者不明]</t>
+          <t>[製作者不明]</t>
         </is>
       </c>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr">
         <is>
-          <t>[安政5 (1858)]</t>
+          <t>[天保弘化年間]</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -8088,7 +8100,7 @@
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr">
         <is>
-          <t>写本|責任表示及び書写年は『日本古典籍総合目録データベース』による|内容: 6: 光明院御記, 後光嚴院御記, 後小松院宸記, 天聴集. 28: 参議藤定長卿記 : 稱山丞記. 37: 定高卿記, 晴御会部類記, 家光卿御記, 權中納言平範輔卿記. 38: 左大史小槻季継記, 後堀川安貞二年放生會(実基公記), 石清水八幡宮, 弁官拝賀次第. 39: 大外記師光記, 資季卿記, 荒凉記, 忠高卿記. 40: 冷泉公相公記, 勝延法眼記 : 東寺大行事, 後中記 : 小路中納言資頼卿記葉室. 41: 中光記, 師兼記, 陽龍記. 42: 大宮司長則記, 口筆 : 實經, 顕朝卿記, 鴨御幸記. 43: 寳治二年記, 深心院關白記, 藤公親記, 照念院関白兼平公記. 44: 頼親記, 亀山殿行幸記 : 雅言卿記, 兼基公記. 45: 大嘗會御禊節下次第, 建治三年丁丑日記 : 三善康有, 建治四年正月廿一日 : 徳大寺大相國公孝記, 冬定卿記, 左大史小槻兼文記|内容: 46: 經任卿記, 前豊前守藤憲説記, 實兼公記. 47: 継塵記抄出. 48: 管見記, 公衡公記, 大外記師顕記, 大外記中原師淳記. 49: 真光院禪助僧正記, 吉田内府卿記. 50: 定清記, 叅議雅俊卿記, 太政大臣(公守公)御上表雜事, 仙洞御灌頂日記, 正安二年八月十一日於仙洞被始行熾盛光法, 正安三年御譲位記. 51: 實躬卿記. 52: 公茂公記, 冬平公記, 隆長卿記. 53: 忠教公記, 官記, 正三位長基卿記, 北面秀長記, 大外記中原師右記. 54: 文保元年, 日野中納言資朝卿記, 洞院大納言公敏卿記. 55: 隆蔭卿記, 文保三年記, 尹大納言師賢卿記, 革命記, 立倚子記, 萬里小路中納言藤藤房卿記|内容: 56: 資名卿記, 公秀公記, 一條家記装束抄出, 頼定卿記. 63: 松亞記, 日野大納言時光卿記, 後八條内府實継公記. 74: 成恩寺関白記. 78: 山科家礼記. 82: 諒闇記 : 後成恩寺殿, 宗典僧正記, 綱光公記, 贈従二位宗賢卿記, 義政公記. 84: 長禄二年戊寅正月, 見聞雜記. 87: 言國卿記. 88: 長興宿祢記, 元長卿記, 兼顕卿記, 小槻晴冨記|28末の原奥書に「右山丞記依 仰挍合書冩/享和二年四月 日撿挍保己一」とあり|50「正安二年八月十一日於仙洞被始行熾盛光法」末の原奥書に「文化十五年春二月以南山法曼院藏夲書冩之 撿挍保己一」とあり|横刷毛目表紙を使用|朱点, 朱引, 朱墨筆書き入れあり|付箋あり|蔵書印主信濃須坂藩主堀直格の命によって編集された古記録|他の原本は関東大震災により焼失|極札に「桂壽」(6), 「尚信」(53)との極書, 「武清」(44, 53), 「永海」(51), 「了伴」(52), 「了甫」(74), 「定時」(84, 88)との極印あり|印記: 「花廼家文庫」, 「墨阪十一代主寫藏記」(堀直格(1806-1880)), 「東京大學法理文學部書庫所藏」, 「閲覧室用 FOR USE IN THE READING ROOM」|虫損あり</t>
+          <t>書名は題簽による|箱の書名: 和蘭國軍艦人物兵器等図|巻末に「圖説」あり|絵巻|彩色あり</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -8104,12 +8116,12 @@
       <c r="O63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/48123112-700b-8619-731b-649449ff034b.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/8509e124-5c2f-173b-2502-4d9cd27f9f85.json</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>48123112-700b-8619-731b-649449ff034b</t>
+          <t>8509e124-5c2f-173b-2502-4d9cd27f9f85</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
@@ -8119,7 +8131,7 @@
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/48123112-700b-8619-731b-649449ff034b</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/8509e124-5c2f-173b-2502-4d9cd27f9f85</t>
         </is>
       </c>
       <c r="T63" t="inlineStr">
@@ -8129,12 +8141,12 @@
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/4c918a15ed3dc97a18f7bc977b4dc2e8c724d774.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/18d2fe489472e7f697dd92568da44185793c8f4d.jpg</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296225</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296181</t>
         </is>
       </c>
       <c r="W63" t="inlineStr">
@@ -8157,7 +8169,7 @@
       <c r="AB63" t="inlineStr"/>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/48123112-700b-8619-731b-649449ff034b/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/8509e124-5c2f-173b-2502-4d9cd27f9f85/manifest</t>
         </is>
       </c>
       <c r="AD63" t="inlineStr"/>
@@ -8165,40 +8177,36 @@
       <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="inlineStr"/>
       <c r="AH63" t="n">
-        <v>78</v>
+        <v>17</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [26]</t>
+          <t>能面圗譜</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>A00:6257</t>
+          <t>A00:4269</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>レキダイ ザンケツ ニッキ</t>
+          <t>ノウメン ズフ</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>黒川 春村</t>
-        </is>
-      </c>
+      <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
-          <t>[書写者不明]</t>
+          <t>[製作者不明]</t>
         </is>
       </c>
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr">
         <is>
-          <t>[安政5 (1858)]</t>
+          <t>[江戸中期以降]</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -8210,7 +8218,7 @@
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr">
         <is>
-          <t>写本|責任表示及び書写年は『日本古典籍総合目録データベース』による|内容: 6: 光明院御記, 後光嚴院御記, 後小松院宸記, 天聴集. 28: 参議藤定長卿記 : 稱山丞記. 37: 定高卿記, 晴御会部類記, 家光卿御記, 權中納言平範輔卿記. 38: 左大史小槻季継記, 後堀川安貞二年放生會(実基公記), 石清水八幡宮, 弁官拝賀次第. 39: 大外記師光記, 資季卿記, 荒凉記, 忠高卿記. 40: 冷泉公相公記, 勝延法眼記 : 東寺大行事, 後中記 : 小路中納言資頼卿記葉室. 41: 中光記, 師兼記, 陽龍記. 42: 大宮司長則記, 口筆 : 實經, 顕朝卿記, 鴨御幸記. 43: 寳治二年記, 深心院關白記, 藤公親記, 照念院関白兼平公記. 44: 頼親記, 亀山殿行幸記 : 雅言卿記, 兼基公記. 45: 大嘗會御禊節下次第, 建治三年丁丑日記 : 三善康有, 建治四年正月廿一日 : 徳大寺大相國公孝記, 冬定卿記, 左大史小槻兼文記|内容: 46: 經任卿記, 前豊前守藤憲説記, 實兼公記. 47: 継塵記抄出. 48: 管見記, 公衡公記, 大外記師顕記, 大外記中原師淳記. 49: 真光院禪助僧正記, 吉田内府卿記. 50: 定清記, 叅議雅俊卿記, 太政大臣(公守公)御上表雜事, 仙洞御灌頂日記, 正安二年八月十一日於仙洞被始行熾盛光法, 正安三年御譲位記. 51: 實躬卿記. 52: 公茂公記, 冬平公記, 隆長卿記. 53: 忠教公記, 官記, 正三位長基卿記, 北面秀長記, 大外記中原師右記. 54: 文保元年, 日野中納言資朝卿記, 洞院大納言公敏卿記. 55: 隆蔭卿記, 文保三年記, 尹大納言師賢卿記, 革命記, 立倚子記, 萬里小路中納言藤藤房卿記|内容: 56: 資名卿記, 公秀公記, 一條家記装束抄出, 頼定卿記. 63: 松亞記, 日野大納言時光卿記, 後八條内府實継公記. 74: 成恩寺関白記. 78: 山科家礼記. 82: 諒闇記 : 後成恩寺殿, 宗典僧正記, 綱光公記, 贈従二位宗賢卿記, 義政公記. 84: 長禄二年戊寅正月, 見聞雜記. 87: 言國卿記. 88: 長興宿祢記, 元長卿記, 兼顕卿記, 小槻晴冨記|28末の原奥書に「右山丞記依 仰挍合書冩/享和二年四月 日撿挍保己一」とあり|50「正安二年八月十一日於仙洞被始行熾盛光法」末の原奥書に「文化十五年春二月以南山法曼院藏夲書冩之 撿挍保己一」とあり|横刷毛目表紙を使用|朱点, 朱引, 朱墨筆書き入れあり|付箋あり|蔵書印主信濃須坂藩主堀直格の命によって編集された古記録|他の原本は関東大震災により焼失|極札に「桂壽」(6), 「尚信」(53)との極書, 「武清」(44, 53), 「永海」(51), 「了伴」(52), 「了甫」(74), 「定時」(84, 88)との極印あり|印記: 「花廼家文庫」, 「墨阪十一代主寫藏記」(堀直格(1806-1880)), 「東京大學法理文學部書庫所藏」, 「閲覧室用 FOR USE IN THE READING ROOM」|虫損あり</t>
+          <t>折本|書名は題簽(墨書)による|帙題簽の書名(墨書): 能面圖譜|絹本彩色|図42幅|本紙: 16×13cm|金切箔散し料紙, 福寿文字布目地表紙を使用</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -8226,12 +8234,12 @@
       <c r="O64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/9b2b928b-4eda-76c6-0dfd-03bde69c046c.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/8b3019c4-7584-208c-0c75-7c855ddc0b9e.json</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>9b2b928b-4eda-76c6-0dfd-03bde69c046c</t>
+          <t>8b3019c4-7584-208c-0c75-7c855ddc0b9e</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
@@ -8241,7 +8249,7 @@
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/9b2b928b-4eda-76c6-0dfd-03bde69c046c</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/8b3019c4-7584-208c-0c75-7c855ddc0b9e</t>
         </is>
       </c>
       <c r="T64" t="inlineStr">
@@ -8251,12 +8259,12 @@
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/7903cd89a232a0d9b4b243d90852d31d93c80300.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/3109e43cd273e3e02f2a227b4f1053cc1d4558bb.jpg</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296226</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296182</t>
         </is>
       </c>
       <c r="W64" t="inlineStr">
@@ -8279,7 +8287,7 @@
       <c r="AB64" t="inlineStr"/>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/9b2b928b-4eda-76c6-0dfd-03bde69c046c/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/8b3019c4-7584-208c-0c75-7c855ddc0b9e/manifest</t>
         </is>
       </c>
       <c r="AD64" t="inlineStr"/>
@@ -8287,29 +8295,29 @@
       <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="inlineStr"/>
       <c r="AH64" t="n">
-        <v>66</v>
+        <v>28</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [27]</t>
+          <t>法蕐經集驗記 2巻</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>A00:6257</t>
+          <t>A00:4273</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>レキダイ ザンケツ ニッキ</t>
+          <t>ホケキョウ シュウゲンキ</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>黒川 春村</t>
+          <t>義寂</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -8320,7 +8328,7 @@
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr">
         <is>
-          <t>[安政5 (1858)]</t>
+          <t>[平安時代]</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -8332,7 +8340,7 @@
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr">
         <is>
-          <t>写本|責任表示及び書写年は『日本古典籍総合目録データベース』による|内容: 6: 光明院御記, 後光嚴院御記, 後小松院宸記, 天聴集. 28: 参議藤定長卿記 : 稱山丞記. 37: 定高卿記, 晴御会部類記, 家光卿御記, 權中納言平範輔卿記. 38: 左大史小槻季継記, 後堀川安貞二年放生會(実基公記), 石清水八幡宮, 弁官拝賀次第. 39: 大外記師光記, 資季卿記, 荒凉記, 忠高卿記. 40: 冷泉公相公記, 勝延法眼記 : 東寺大行事, 後中記 : 小路中納言資頼卿記葉室. 41: 中光記, 師兼記, 陽龍記. 42: 大宮司長則記, 口筆 : 實經, 顕朝卿記, 鴨御幸記. 43: 寳治二年記, 深心院關白記, 藤公親記, 照念院関白兼平公記. 44: 頼親記, 亀山殿行幸記 : 雅言卿記, 兼基公記. 45: 大嘗會御禊節下次第, 建治三年丁丑日記 : 三善康有, 建治四年正月廿一日 : 徳大寺大相國公孝記, 冬定卿記, 左大史小槻兼文記|内容: 46: 經任卿記, 前豊前守藤憲説記, 實兼公記. 47: 継塵記抄出. 48: 管見記, 公衡公記, 大外記師顕記, 大外記中原師淳記. 49: 真光院禪助僧正記, 吉田内府卿記. 50: 定清記, 叅議雅俊卿記, 太政大臣(公守公)御上表雜事, 仙洞御灌頂日記, 正安二年八月十一日於仙洞被始行熾盛光法, 正安三年御譲位記. 51: 實躬卿記. 52: 公茂公記, 冬平公記, 隆長卿記. 53: 忠教公記, 官記, 正三位長基卿記, 北面秀長記, 大外記中原師右記. 54: 文保元年, 日野中納言資朝卿記, 洞院大納言公敏卿記. 55: 隆蔭卿記, 文保三年記, 尹大納言師賢卿記, 革命記, 立倚子記, 萬里小路中納言藤藤房卿記|内容: 56: 資名卿記, 公秀公記, 一條家記装束抄出, 頼定卿記. 63: 松亞記, 日野大納言時光卿記, 後八條内府實継公記. 74: 成恩寺関白記. 78: 山科家礼記. 82: 諒闇記 : 後成恩寺殿, 宗典僧正記, 綱光公記, 贈従二位宗賢卿記, 義政公記. 84: 長禄二年戊寅正月, 見聞雜記. 87: 言國卿記. 88: 長興宿祢記, 元長卿記, 兼顕卿記, 小槻晴冨記|28末の原奥書に「右山丞記依 仰挍合書冩/享和二年四月 日撿挍保己一」とあり|50「正安二年八月十一日於仙洞被始行熾盛光法」末の原奥書に「文化十五年春二月以南山法曼院藏夲書冩之 撿挍保己一」とあり|横刷毛目表紙を使用|朱点, 朱引, 朱墨筆書き入れあり|付箋あり|蔵書印主信濃須坂藩主堀直格の命によって編集された古記録|他の原本は関東大震災により焼失|極札に「桂壽」(6), 「尚信」(53)との極書, 「武清」(44, 53), 「永海」(51), 「了伴」(52), 「了甫」(74), 「定時」(84, 88)との極印あり|印記: 「花廼家文庫」, 「墨阪十一代主寫藏記」(堀直格(1806-1880)), 「東京大學法理文學部書庫所藏」, 「閲覧室用 FOR USE IN THE READING ROOM」|虫損あり</t>
+          <t>鈔本|書名は卷下の巻頭による|大尾の書名: 法蕐集驗記|後付題簽の書名: 法花經集驗記|箱の書名: 法華驗記|卷下の内題下に「并序沙門寂撰」とあり|奥書に「護持僧(花押)夲之」とあり|巻末識語に「嘉應二年庚寅二月十八日傳得之釈子有慶在判」, 「十帋半」とあり|卷上: 諷誦第1. 卷下: 轉讀第2, 書寫第3, 聽聞第4|巻子本|訓点付|卷上の巻頭を欠損|原十紙半を1軸に合綴|朱筆書き入れあり|破損, 虫損あり (裏打ち補修あり)</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -8348,12 +8356,12 @@
       <c r="O65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/ccc6c3da-1648-49f5-91fc-2faaf5400387.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/ec4bceb1-0ab9-74c7-0dc7-f90d0a98a66e.json</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>ccc6c3da-1648-49f5-91fc-2faaf5400387</t>
+          <t>ec4bceb1-0ab9-74c7-0dc7-f90d0a98a66e</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
@@ -8363,7 +8371,7 @@
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/ccc6c3da-1648-49f5-91fc-2faaf5400387</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/ec4bceb1-0ab9-74c7-0dc7-f90d0a98a66e</t>
         </is>
       </c>
       <c r="T65" t="inlineStr">
@@ -8373,12 +8381,12 @@
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/1e476c24ffbe9fd54b432acbf27eb918fc4162d0.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/d1c457097d78f2d8a4b38eebd630ef233026cc5e.jpg</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296227</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296183</t>
         </is>
       </c>
       <c r="W65" t="inlineStr">
@@ -8401,7 +8409,7 @@
       <c r="AB65" t="inlineStr"/>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/ccc6c3da-1648-49f5-91fc-2faaf5400387/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/ec4bceb1-0ab9-74c7-0dc7-f90d0a98a66e/manifest</t>
         </is>
       </c>
       <c r="AD65" t="inlineStr"/>
@@ -8409,40 +8417,36 @@
       <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="inlineStr"/>
       <c r="AH65" t="n">
-        <v>70</v>
+        <v>19</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [28]</t>
+          <t>道成寺</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>A00:6257</t>
+          <t>A00:4276</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>レキダイ ザンケツ ニッキ</t>
+          <t>ドウジョウジ</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>黒川 春村</t>
-        </is>
-      </c>
+      <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
-          <t>[書写者不明]</t>
+          <t>[製作者不明]</t>
         </is>
       </c>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr">
         <is>
-          <t>[安政5 (1858)]</t>
+          <t>天明2 [1782] 識語</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -8454,7 +8458,7 @@
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr">
         <is>
-          <t>写本|責任表示及び書写年は『日本古典籍総合目録データベース』による|内容: 6: 光明院御記, 後光嚴院御記, 後小松院宸記, 天聴集. 28: 参議藤定長卿記 : 稱山丞記. 37: 定高卿記, 晴御会部類記, 家光卿御記, 權中納言平範輔卿記. 38: 左大史小槻季継記, 後堀川安貞二年放生會(実基公記), 石清水八幡宮, 弁官拝賀次第. 39: 大外記師光記, 資季卿記, 荒凉記, 忠高卿記. 40: 冷泉公相公記, 勝延法眼記 : 東寺大行事, 後中記 : 小路中納言資頼卿記葉室. 41: 中光記, 師兼記, 陽龍記. 42: 大宮司長則記, 口筆 : 實經, 顕朝卿記, 鴨御幸記. 43: 寳治二年記, 深心院關白記, 藤公親記, 照念院関白兼平公記. 44: 頼親記, 亀山殿行幸記 : 雅言卿記, 兼基公記. 45: 大嘗會御禊節下次第, 建治三年丁丑日記 : 三善康有, 建治四年正月廿一日 : 徳大寺大相國公孝記, 冬定卿記, 左大史小槻兼文記|内容: 46: 經任卿記, 前豊前守藤憲説記, 實兼公記. 47: 継塵記抄出. 48: 管見記, 公衡公記, 大外記師顕記, 大外記中原師淳記. 49: 真光院禪助僧正記, 吉田内府卿記. 50: 定清記, 叅議雅俊卿記, 太政大臣(公守公)御上表雜事, 仙洞御灌頂日記, 正安二年八月十一日於仙洞被始行熾盛光法, 正安三年御譲位記. 51: 實躬卿記. 52: 公茂公記, 冬平公記, 隆長卿記. 53: 忠教公記, 官記, 正三位長基卿記, 北面秀長記, 大外記中原師右記. 54: 文保元年, 日野中納言資朝卿記, 洞院大納言公敏卿記. 55: 隆蔭卿記, 文保三年記, 尹大納言師賢卿記, 革命記, 立倚子記, 萬里小路中納言藤藤房卿記|内容: 56: 資名卿記, 公秀公記, 一條家記装束抄出, 頼定卿記. 63: 松亞記, 日野大納言時光卿記, 後八條内府實継公記. 74: 成恩寺関白記. 78: 山科家礼記. 82: 諒闇記 : 後成恩寺殿, 宗典僧正記, 綱光公記, 贈従二位宗賢卿記, 義政公記. 84: 長禄二年戊寅正月, 見聞雜記. 87: 言國卿記. 88: 長興宿祢記, 元長卿記, 兼顕卿記, 小槻晴冨記|28末の原奥書に「右山丞記依 仰挍合書冩/享和二年四月 日撿挍保己一」とあり|50「正安二年八月十一日於仙洞被始行熾盛光法」末の原奥書に「文化十五年春二月以南山法曼院藏夲書冩之 撿挍保己一」とあり|横刷毛目表紙を使用|朱点, 朱引, 朱墨筆書き入れあり|付箋あり|蔵書印主信濃須坂藩主堀直格の命によって編集された古記録|他の原本は関東大震災により焼失|極札に「桂壽」(6), 「尚信」(53)との極書, 「武清」(44, 53), 「永海」(51), 「了伴」(52), 「了甫」(74), 「定時」(84, 88)との極印あり|印記: 「花廼家文庫」, 「墨阪十一代主寫藏記」(堀直格(1806-1880)), 「東京大學法理文學部書庫所藏」, 「閲覧室用 FOR USE IN THE READING ROOM」|虫損あり</t>
+          <t>書名は識語による|巻末識語に「道成寺建立年号大長五年三月吉日以後于二百三拾年去テ延長六戊子暦八月十日鐘巻也」, 「時天明二壬寅十月 尚良書之」とあり|絵巻|紙本著色|彩色あり|本紙: 855×28cm|界高: 25.8cm|軸物|軸頭欠損あり|印記: 「尚良印」|破損あり (裏打ち補修あり)</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -8470,12 +8474,12 @@
       <c r="O66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/9f3a126c-84bb-8f96-2916-b65ace30a616.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/79185d0c-7fa3-2efd-863e-93927e137a23.json</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>9f3a126c-84bb-8f96-2916-b65ace30a616</t>
+          <t>79185d0c-7fa3-2efd-863e-93927e137a23</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
@@ -8485,7 +8489,7 @@
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/9f3a126c-84bb-8f96-2916-b65ace30a616</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/79185d0c-7fa3-2efd-863e-93927e137a23</t>
         </is>
       </c>
       <c r="T66" t="inlineStr">
@@ -8495,12 +8499,12 @@
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/fc4844ae32ad2dd582e3570965cb142f5f370f74.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/0c47939e767d716fe085cc41c86d91be28f9df1a.jpg</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296228</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296184</t>
         </is>
       </c>
       <c r="W66" t="inlineStr">
@@ -8523,7 +8527,7 @@
       <c r="AB66" t="inlineStr"/>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/9f3a126c-84bb-8f96-2916-b65ace30a616/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/79185d0c-7fa3-2efd-863e-93927e137a23/manifest</t>
         </is>
       </c>
       <c r="AD66" t="inlineStr"/>
@@ -8531,52 +8535,52 @@
       <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="inlineStr"/>
       <c r="AH66" t="n">
-        <v>70</v>
+        <v>34</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [29]</t>
+          <t>名家短冊 [1]</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>A00:6257</t>
+          <t>A00:4277</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>レキダイ ザンケツ ニッキ</t>
+          <t>メイカ タンザク</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>黒川 春村</t>
+          <t>慶運</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>[書写者不明]</t>
+          <t>慶運 [ほか自筆]</t>
         </is>
       </c>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr">
         <is>
-          <t>[安政5 (1858)]</t>
+          <t>[鎌倉時代-江戸前期]</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr">
         <is>
-          <t>写本|責任表示及び書写年は『日本古典籍総合目録データベース』による|内容: 6: 光明院御記, 後光嚴院御記, 後小松院宸記, 天聴集. 28: 参議藤定長卿記 : 稱山丞記. 37: 定高卿記, 晴御会部類記, 家光卿御記, 權中納言平範輔卿記. 38: 左大史小槻季継記, 後堀川安貞二年放生會(実基公記), 石清水八幡宮, 弁官拝賀次第. 39: 大外記師光記, 資季卿記, 荒凉記, 忠高卿記. 40: 冷泉公相公記, 勝延法眼記 : 東寺大行事, 後中記 : 小路中納言資頼卿記葉室. 41: 中光記, 師兼記, 陽龍記. 42: 大宮司長則記, 口筆 : 實經, 顕朝卿記, 鴨御幸記. 43: 寳治二年記, 深心院關白記, 藤公親記, 照念院関白兼平公記. 44: 頼親記, 亀山殿行幸記 : 雅言卿記, 兼基公記. 45: 大嘗會御禊節下次第, 建治三年丁丑日記 : 三善康有, 建治四年正月廿一日 : 徳大寺大相國公孝記, 冬定卿記, 左大史小槻兼文記|内容: 46: 經任卿記, 前豊前守藤憲説記, 實兼公記. 47: 継塵記抄出. 48: 管見記, 公衡公記, 大外記師顕記, 大外記中原師淳記. 49: 真光院禪助僧正記, 吉田内府卿記. 50: 定清記, 叅議雅俊卿記, 太政大臣(公守公)御上表雜事, 仙洞御灌頂日記, 正安二年八月十一日於仙洞被始行熾盛光法, 正安三年御譲位記. 51: 實躬卿記. 52: 公茂公記, 冬平公記, 隆長卿記. 53: 忠教公記, 官記, 正三位長基卿記, 北面秀長記, 大外記中原師右記. 54: 文保元年, 日野中納言資朝卿記, 洞院大納言公敏卿記. 55: 隆蔭卿記, 文保三年記, 尹大納言師賢卿記, 革命記, 立倚子記, 萬里小路中納言藤藤房卿記|内容: 56: 資名卿記, 公秀公記, 一條家記装束抄出, 頼定卿記. 63: 松亞記, 日野大納言時光卿記, 後八條内府實継公記. 74: 成恩寺関白記. 78: 山科家礼記. 82: 諒闇記 : 後成恩寺殿, 宗典僧正記, 綱光公記, 贈従二位宗賢卿記, 義政公記. 84: 長禄二年戊寅正月, 見聞雜記. 87: 言國卿記. 88: 長興宿祢記, 元長卿記, 兼顕卿記, 小槻晴冨記|28末の原奥書に「右山丞記依 仰挍合書冩/享和二年四月 日撿挍保己一」とあり|50「正安二年八月十一日於仙洞被始行熾盛光法」末の原奥書に「文化十五年春二月以南山法曼院藏夲書冩之 撿挍保己一」とあり|横刷毛目表紙を使用|朱点, 朱引, 朱墨筆書き入れあり|付箋あり|蔵書印主信濃須坂藩主堀直格の命によって編集された古記録|他の原本は関東大震災により焼失|極札に「桂壽」(6), 「尚信」(53)との極書, 「武清」(44, 53), 「永海」(51), 「了伴」(52), 「了甫」(74), 「定時」(84, 88)との極印あり|印記: 「花廼家文庫」, 「墨阪十一代主寫藏記」(堀直格(1806-1880)), 「東京大學法理文學部書庫所藏」, 「閲覧室用 FOR USE IN THE READING ROOM」|虫損あり</t>
+          <t>折本|書名及び巻冊次は題簽による|2の筆者: 慶運 牡丹花, 了流, 宗長, 兼載, 宗碩, 宗牧, 一竿, 正廣, 正般, 祖田, 堯憲, 宗二, 利盛, 増春, 了向, 榮弘, 梅雪, 宗栁, 等惠, 宗訊, 宗養, 乘阿, 兼如, 壽慶, 意運, 本阿彌光悦, 松花堂昭乘, 紹巴, 玄仍, 玄仲, 玄陳, 玄的, 里村玄祥, 昌叱, 昌琢, 昌俔, 昌程, 昌隱, 昌通|3の筆者: 祐守, 祐夏, 詮平, 直國, 興國, 隆國, 武光, 祐範, 宗純, 等貴,  順, 最嶽, 策彦, 幽之, 應其, 堯然, 尊道, 尊應, 尊朝, 道永, 弘覺, 良俊, 道増, 道應, 道興, 藤之, 立承, 性舜, 義俊, 空性, 尊譽, 揚, 道澄, 興意, 道晃|4の筆者: 有三, 他阿, 教, 尊雅, 應猷, 秀順, 可ト, 圓祐, 道順, 実如, 兼俊, 公助, 應祐, 公順, 空慶, 看世, 定信, 玄桂, 道三, 道春, 永喜, 豊永, 葉由, 常弘|2: 古筆切40枚, 極札43枚|3: 古筆切36枚, 極札36枚|4: 古筆切28枚, 極札20枚|毎半面古筆切2枚|原104枚短冊を3帖に合綴|印記: 「順」, 「最嶽」|極印: 「琴山」, 「栄」(古筆了栄)|折り目破損あり</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -8592,12 +8596,12 @@
       <c r="O67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/7cdebe3a-8fb4-14b4-7ddb-3f92f3be9668.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/1469b736-a0ee-61aa-1e00-7a2cfa949411.json</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>7cdebe3a-8fb4-14b4-7ddb-3f92f3be9668</t>
+          <t>1469b736-a0ee-61aa-1e00-7a2cfa949411</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
@@ -8607,7 +8611,7 @@
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/7cdebe3a-8fb4-14b4-7ddb-3f92f3be9668</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/1469b736-a0ee-61aa-1e00-7a2cfa949411</t>
         </is>
       </c>
       <c r="T67" t="inlineStr">
@@ -8617,12 +8621,12 @@
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/08f5648a7b5512a896986520a6449d3620439071.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/7693d9aa48dbd471c84817ef0239807a5e246d64.jpg</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296229</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296185</t>
         </is>
       </c>
       <c r="W67" t="inlineStr">
@@ -8645,7 +8649,7 @@
       <c r="AB67" t="inlineStr"/>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/7cdebe3a-8fb4-14b4-7ddb-3f92f3be9668/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/1469b736-a0ee-61aa-1e00-7a2cfa949411/manifest</t>
         </is>
       </c>
       <c r="AD67" t="inlineStr"/>
@@ -8653,52 +8657,52 @@
       <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="inlineStr"/>
       <c r="AH67" t="n">
-        <v>70</v>
+        <v>27</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>普賢延命</t>
+          <t>名家短冊 [2]</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>A00:6264</t>
+          <t>A00:4277</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>フゲン エンメイ</t>
+          <t>メイカ タンザク</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>興然</t>
+          <t>慶運</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>長円 [写]</t>
+          <t>慶運 [ほか自筆]</t>
         </is>
       </c>
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr">
         <is>
-          <t>嘉禎2 [1236] 奥書</t>
+          <t>[鎌倉時代-江戸前期]</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr">
         <is>
-          <t>写本|内題下に「師 理教」, 「嘉禎二年奥書アリ 長円書」とあり|巻末に「越前闍梨浄与口傳 興然夲」とあり|奥書に「嘉禎二年四月六月奉傳受空達御房ノ長円」とあり|裏に「正和元年壬子八月廿九日於成身院奉伝受之了」とあり|巻子本|送り仮名, 傍訓あり|虫損あり (裏打ち補修あり)</t>
+          <t>折本|書名及び巻冊次は題簽による|2の筆者: 慶運 牡丹花, 了流, 宗長, 兼載, 宗碩, 宗牧, 一竿, 正廣, 正般, 祖田, 堯憲, 宗二, 利盛, 増春, 了向, 榮弘, 梅雪, 宗栁, 等惠, 宗訊, 宗養, 乘阿, 兼如, 壽慶, 意運, 本阿彌光悦, 松花堂昭乘, 紹巴, 玄仍, 玄仲, 玄陳, 玄的, 里村玄祥, 昌叱, 昌琢, 昌俔, 昌程, 昌隱, 昌通|3の筆者: 祐守, 祐夏, 詮平, 直國, 興國, 隆國, 武光, 祐範, 宗純, 等貴,  順, 最嶽, 策彦, 幽之, 應其, 堯然, 尊道, 尊應, 尊朝, 道永, 弘覺, 良俊, 道増, 道應, 道興, 藤之, 立承, 性舜, 義俊, 空性, 尊譽, 揚, 道澄, 興意, 道晃|4の筆者: 有三, 他阿, 教, 尊雅, 應猷, 秀順, 可ト, 圓祐, 道順, 実如, 兼俊, 公助, 應祐, 公順, 空慶, 看世, 定信, 玄桂, 道三, 道春, 永喜, 豊永, 葉由, 常弘|2: 古筆切40枚, 極札43枚|3: 古筆切36枚, 極札36枚|4: 古筆切28枚, 極札20枚|毎半面古筆切2枚|原104枚短冊を3帖に合綴|印記: 「順」, 「最嶽」|極印: 「琴山」, 「栄」(古筆了栄)|折り目破損あり</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -8714,12 +8718,12 @@
       <c r="O68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/e57fef06-5cfd-a602-6a89-f4d7d4360e87.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/53041b9e-294f-71af-3d1a-e305956f5560.json</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>e57fef06-5cfd-a602-6a89-f4d7d4360e87</t>
+          <t>53041b9e-294f-71af-3d1a-e305956f5560</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
@@ -8729,7 +8733,7 @@
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/e57fef06-5cfd-a602-6a89-f4d7d4360e87</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/53041b9e-294f-71af-3d1a-e305956f5560</t>
         </is>
       </c>
       <c r="T68" t="inlineStr">
@@ -8739,12 +8743,12 @@
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/eec20da7736c221a3c86321abead9d8d9429dceb.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/11759cf221ad40925619344bacc4027d06e015ce.jpg</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296230</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296186</t>
         </is>
       </c>
       <c r="W68" t="inlineStr">
@@ -8767,7 +8771,7 @@
       <c r="AB68" t="inlineStr"/>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/e57fef06-5cfd-a602-6a89-f4d7d4360e87/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/53041b9e-294f-71af-3d1a-e305956f5560/manifest</t>
         </is>
       </c>
       <c r="AD68" t="inlineStr"/>
@@ -8775,52 +8779,52 @@
       <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="inlineStr"/>
       <c r="AH68" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>如法愛染王</t>
+          <t>名家短冊 [3]</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>A00:6265</t>
+          <t>A00:4277</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>ニョホウ アイゼンオウ</t>
+          <t>メイカ タンザク</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>仁海</t>
+          <t>慶運</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>禅喜 [写]</t>
+          <t>慶運 [ほか自筆]</t>
         </is>
       </c>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr">
         <is>
-          <t>嘉暦2 [1327] 奥書</t>
+          <t>[鎌倉時代-江戸前期]</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr">
         <is>
-          <t>写本|表紙の書名: 如法愛染|内題下に「付小野大次苐修之」とあり|本奥書に「延慶二年夘月十日於仁和寺真光院書写了 金剛佛子印法 生年卅二」とあり|奥書に「嘉暦二年正月廿二日全写了 禅喜 生年卅一」とあり|巻子本|小野流|淡墨界の料紙を使用(界匡廓: 23.8×2.2cm)|巻頭下部の貼紙に「嘉暦二年巨今五百八十二年鎌倉時代四一ノ六九七号」とあり|破損, 虫損あり (裏打ち補修あり)</t>
+          <t>折本|書名及び巻冊次は題簽による|2の筆者: 慶運 牡丹花, 了流, 宗長, 兼載, 宗碩, 宗牧, 一竿, 正廣, 正般, 祖田, 堯憲, 宗二, 利盛, 増春, 了向, 榮弘, 梅雪, 宗栁, 等惠, 宗訊, 宗養, 乘阿, 兼如, 壽慶, 意運, 本阿彌光悦, 松花堂昭乘, 紹巴, 玄仍, 玄仲, 玄陳, 玄的, 里村玄祥, 昌叱, 昌琢, 昌俔, 昌程, 昌隱, 昌通|3の筆者: 祐守, 祐夏, 詮平, 直國, 興國, 隆國, 武光, 祐範, 宗純, 等貴,  順, 最嶽, 策彦, 幽之, 應其, 堯然, 尊道, 尊應, 尊朝, 道永, 弘覺, 良俊, 道増, 道應, 道興, 藤之, 立承, 性舜, 義俊, 空性, 尊譽, 揚, 道澄, 興意, 道晃|4の筆者: 有三, 他阿, 教, 尊雅, 應猷, 秀順, 可ト, 圓祐, 道順, 実如, 兼俊, 公助, 應祐, 公順, 空慶, 看世, 定信, 玄桂, 道三, 道春, 永喜, 豊永, 葉由, 常弘|2: 古筆切40枚, 極札43枚|3: 古筆切36枚, 極札36枚|4: 古筆切28枚, 極札20枚|毎半面古筆切2枚|原104枚短冊を3帖に合綴|印記: 「順」, 「最嶽」|極印: 「琴山」, 「栄」(古筆了栄)|折り目破損あり</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -8836,12 +8840,12 @@
       <c r="O69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/e321350d-483d-6e38-81a2-a637b8f798fb.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/3d4ceb9b-9516-779a-7ced-f893e9d93b4e.json</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>e321350d-483d-6e38-81a2-a637b8f798fb</t>
+          <t>3d4ceb9b-9516-779a-7ced-f893e9d93b4e</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
@@ -8851,7 +8855,7 @@
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/e321350d-483d-6e38-81a2-a637b8f798fb</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/3d4ceb9b-9516-779a-7ced-f893e9d93b4e</t>
         </is>
       </c>
       <c r="T69" t="inlineStr">
@@ -8861,12 +8865,12 @@
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/355285a0ec0b1cc8f12ae2c98e5215bdc9477998.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/8fd1defea23c7c93fc4d908835c1fea38040580e.jpg</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296231</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296187</t>
         </is>
       </c>
       <c r="W69" t="inlineStr">
@@ -8889,7 +8893,7 @@
       <c r="AB69" t="inlineStr"/>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/e321350d-483d-6e38-81a2-a637b8f798fb/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/3d4ceb9b-9516-779a-7ced-f893e9d93b4e/manifest</t>
         </is>
       </c>
       <c r="AD69" t="inlineStr"/>
@@ -8897,40 +8901,40 @@
       <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="inlineStr"/>
       <c r="AH69" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>三摩耶戒作法 : 東寺</t>
+          <t>御成敗式目絵鈔</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>A00:6266</t>
+          <t>A00:4737</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>サンマヤカイ サホウ : トウジ</t>
+          <t>ゴセイバイ シキモク エショウ</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>聖快</t>
+          <t>岡本 竹籔</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>道快 [自筆]</t>
+          <t>岡夲竹籔 : 松川半山 [書]</t>
         </is>
       </c>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr">
         <is>
-          <t>康暦元 [1379] 奥書</t>
+          <t>[幕末期]</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -8942,7 +8946,7 @@
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr">
         <is>
-          <t>写本|書名は表紙による|本奥書に「康和元年十月廿日午時書了 深禅夲(第三轉)」, 「以小野僧正御夲理趣房書御夲也(初轉)」, 「承暦四年十一月十二日給預又書冩并傳受了 峯大阿闍梨御房事也(第二轉)」とあり|奥書に「康暦元年八月十二日於地藏院以平等坊永嚴自筆夲書冩之訖 東寺沙門道快」, 「同十四日於同院以或夲重挍合入落字注異説削謬詞尤可秘藏而已」とあり|表紙の貼紙に「康暦元年八月十二日於地藏院以平等坊永嚴自筆本書写之訖 東寺沙門道快 南北類」とある|巻子本|朱筆書き入れあり|淡墨界の料紙を使用(界匡廓: 19.5×2.0cm)|印記: 「僧正弘基」|破損, 虫損あり</t>
+          <t>写本|序首の書名: 御成敗式目繪鈔|版心の書名: 式目繪鈔|題簽に「板下本」とあり|巻末に「筆工 岡夲竹籔/画工 松川半山」とあり(「岡本」, 「憲道」, 「義卿」, 「翠宋堂長」との落款朱印あり)|巻末広告に「山田賞月堂先生筆 無雙用文章大成 全一冊」とあり|四周単辺有界2段5行, 内匡廓: 22.3×16.4cm, 白口無魚尾|頭書あり|付訓あり</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -8958,12 +8962,12 @@
       <c r="O70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/2b2562eb-7577-32f6-4c99-462a84e0647c.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/463ab967-60a4-9ff1-3ef2-d2dee79b5315.json</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>2b2562eb-7577-32f6-4c99-462a84e0647c</t>
+          <t>463ab967-60a4-9ff1-3ef2-d2dee79b5315</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
@@ -8973,7 +8977,7 @@
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/2b2562eb-7577-32f6-4c99-462a84e0647c</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/463ab967-60a4-9ff1-3ef2-d2dee79b5315</t>
         </is>
       </c>
       <c r="T70" t="inlineStr">
@@ -8983,12 +8987,12 @@
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/60a9be2785b442f57f54089c594f63b8df5ae1f4.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/e0977d9ba261ea59386ce9f5104a412a5dccaf3f.jpg</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296232</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296188</t>
         </is>
       </c>
       <c r="W70" t="inlineStr">
@@ -9011,7 +9015,7 @@
       <c r="AB70" t="inlineStr"/>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/2b2562eb-7577-32f6-4c99-462a84e0647c/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/463ab967-60a4-9ff1-3ef2-d2dee79b5315/manifest</t>
         </is>
       </c>
       <c r="AD70" t="inlineStr"/>
@@ -9019,52 +9023,52 @@
       <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="inlineStr"/>
       <c r="AH70" t="n">
-        <v>13</v>
+        <v>59</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>騁懐帖 2巻 [1]</t>
+          <t>金界入壇作法</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>A00:6379</t>
+          <t>A00:5975</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>テイカイジョウ</t>
+          <t>コンカイ ニュウダン サホウ</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>芳賀 矢一</t>
+          <t>良円</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>芳賀矢一 [ほか自筆]</t>
+          <t>良円 [写]</t>
         </is>
       </c>
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr">
         <is>
-          <t>[明治-昭和年間]</t>
+          <t>寛元元 [1243] 奥書</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr">
         <is>
-          <t>写本|書名及び巻冊次は題簽による|跋末に「松夲生名ハ百藏東京帝國大學ノ使丁タリ職ヲ山上會議所ニ奉スルコト四十有餘年 ... 頃来マタ諸賢ノ揮毫ヲ乞上名ケテ騁懐帖トイフ ... 帖成リテ予ニ其由来ヲ記セシコトヲ求ム乃チ之ヲ録シテ以テ跋後トス 昭和二年三月 辻善之助識」とあり|折本|書画帖|彩色あり|名録2冊(大和綴)を付す|落款朱印: 「長成」(坪井九馬三), 「圭卿」(市村瓚次郎), 「簣山」(鹽谷時敏), 「維亭」(塚本靖), 「土肥慶藏」, 「忠太」(伊東忠太), 「萬」(和田万吉), 「芳溪」(呉秀三), 「前田慧雲」, 「大澤謙二」, 「南條文雄」, 「有坂氏」(有坂鉊藏), 「博」, 「石亭」(林博太郎), 「長與又郎」, 「宇野哲人」, ほかあり</t>
+          <t>写本|奥書に「寛元々年五月七日以先師法印御夲於常住護国院房以他筆書冩校點了良円」とあり|送り仮名, 返点あり|淡墨界の料紙を使用(界匡廓: 23.7×2.5cm)|貼紙あり|巻子本|箱入り|破損, 虫損あり (裏打ち補修あり)</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -9080,12 +9084,12 @@
       <c r="O71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/bfdc576b-6ce2-9274-914e-8cc9c52c04de.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/ff6e2dd7-8128-3264-2081-15ad4e41857e.json</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>bfdc576b-6ce2-9274-914e-8cc9c52c04de</t>
+          <t>ff6e2dd7-8128-3264-2081-15ad4e41857e</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
@@ -9095,7 +9099,7 @@
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/bfdc576b-6ce2-9274-914e-8cc9c52c04de</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/ff6e2dd7-8128-3264-2081-15ad4e41857e</t>
         </is>
       </c>
       <c r="T71" t="inlineStr">
@@ -9105,12 +9109,12 @@
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/4061afb959aba92577bf3357712e3556cd07cf8e.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/7e2372f45914ea75c8d903fc80f309f16238b39f.jpg</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296233</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296189</t>
         </is>
       </c>
       <c r="W71" t="inlineStr">
@@ -9133,7 +9137,7 @@
       <c r="AB71" t="inlineStr"/>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/bfdc576b-6ce2-9274-914e-8cc9c52c04de/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/ff6e2dd7-8128-3264-2081-15ad4e41857e/manifest</t>
         </is>
       </c>
       <c r="AD71" t="inlineStr"/>
@@ -9141,52 +9145,52 @@
       <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="inlineStr"/>
       <c r="AH71" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>騁懐帖 2巻 [2]</t>
+          <t>玉蘂 [1]</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>A00:6379</t>
+          <t>A00:6067</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>テイカイジョウ</t>
+          <t>ギョクズイ</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>芳賀 矢一</t>
+          <t>藤原 道家</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>芳賀矢一 [ほか自筆]</t>
+          <t>野宮定基 : 久世通夏 [ほか写]</t>
         </is>
       </c>
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr">
         <is>
-          <t>[明治-昭和年間]</t>
+          <t>元禄12 [1699]-宝永3 [1706] 奥書</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr">
         <is>
-          <t>写本|書名及び巻冊次は題簽による|跋末に「松夲生名ハ百藏東京帝國大學ノ使丁タリ職ヲ山上會議所ニ奉スルコト四十有餘年 ... 頃来マタ諸賢ノ揮毫ヲ乞上名ケテ騁懐帖トイフ ... 帖成リテ予ニ其由来ヲ記セシコトヲ求ム乃チ之ヲ録シテ以テ跋後トス 昭和二年三月 辻善之助識」とあり|折本|書画帖|彩色あり|名録2冊(大和綴)を付す|落款朱印: 「長成」(坪井九馬三), 「圭卿」(市村瓚次郎), 「簣山」(鹽谷時敏), 「維亭」(塚本靖), 「土肥慶藏」, 「忠太」(伊東忠太), 「萬」(和田万吉), 「芳溪」(呉秀三), 「前田慧雲」, 「大澤謙二」, 「南條文雄」, 「有坂氏」(有坂鉊藏), 「博」, 「石亭」(林博太郎), 「長與又郎」, 「宇野哲人」, ほかあり</t>
+          <t>写本|書名及び巻冊次は表紙による|奥中の書名: 光明峯寺禅閤道家公記, 峯禅閤記, 峯摂政記, 峯入道摂政記|承元4年の原奥書に「右即位記一卷者光明峯寺禅閤自筆正記也以件本左令吾基春卿透以写之云々加挍正之 ... 永正七年夷則上浣 從一位(花押)」とあり|奥書に「右以或人夲自常州到来令書写之彼夲端書云此冊上下卷 ... 元禄第十二暦仲夏中旬 羽林左衞中郎将藤原定基丗一才」(承元3), 「右光明峯寺禅閤道家公承元二年三月五六月八月四年二三月九月十十一十二月記は借請或人之夲自常州邊来書写之加一挍了/于時元禄第十二端午節也 左中郎将藤原定基丗才」(承元4), 「右玉蘂建暦元年少弟左中将通清朝臣助筆僅加一挍原本文字不正後来得正夲可改之者也/元禄十三年九月十日 松堂閑士(花押)丗二才」(建暦元), 「右玉蘂峯禅閤記建暦二年自二月至九月一冊以或人夲自常州邊来命家僚令書写手自加挍合了/元禄十二年五月六日 左中郎将藤原定基丗一才」(建暦2年上), 「宝永二年十月一日書写畢/承久二春玉蘂以故常州牧權中納言光圀公夲謄写之于時俗務紛擾先請慈兄源亜相公所被写也今以彼夲手自馳禿筆 余識藤(花押)丗七才/同三年二月廿五日一挍了」(承久2年上), 「右峯摂政承久二年記命傭書謄冩之手自一挍了/元禄第十二嵗次著雍単閼蕤賓中旬 羽林軍左衞中郎将藤原定基丗一才」(承久2年下), 「嘉禎四年正月二月閏二月三月四月六月玉蘂先年假借故常州牧前中納言光圀夲無剋力速遂書写之功建暦元年建暦二年下承久二年上及此卷等先献慈兄亜相君写之今及数年申復彼夲謄写之 ... 宝永三年十二月念日 参議從三位行左近衞權中将藤原朝臣定基生年卅八才」(嘉禎4年)とあり|毎半葉11行注文双行|漢文体日記|拠徳川光圀本及び中院通躬鈔本謄写|朱筆書き入れあり|印記: 「定基」(野宮定基), 「野宮書印」|虫損あり (裏打ち補修あり)</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -9202,12 +9206,12 @@
       <c r="O72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/6a4c18fb-90e9-6d15-1234-9cadcc683544.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/b13a7a09-88d0-62d3-44e5-379780395f17.json</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>6a4c18fb-90e9-6d15-1234-9cadcc683544</t>
+          <t>b13a7a09-88d0-62d3-44e5-379780395f17</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
@@ -9217,7 +9221,7 @@
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/6a4c18fb-90e9-6d15-1234-9cadcc683544</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/b13a7a09-88d0-62d3-44e5-379780395f17</t>
         </is>
       </c>
       <c r="T72" t="inlineStr">
@@ -9227,12 +9231,12 @@
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/f705bcd1873bb88e3f1edef2b79dcc86dc2c417b.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/f7ae1bd23dec8f323199a9add81e315f1a653d24.jpg</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296234</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296190</t>
         </is>
       </c>
       <c r="W72" t="inlineStr">
@@ -9255,7 +9259,7 @@
       <c r="AB72" t="inlineStr"/>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/6a4c18fb-90e9-6d15-1234-9cadcc683544/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/b13a7a09-88d0-62d3-44e5-379780395f17/manifest</t>
         </is>
       </c>
       <c r="AD72" t="inlineStr"/>
@@ -9263,52 +9267,52 @@
       <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="inlineStr"/>
       <c r="AH72" t="n">
-        <v>27</v>
+        <v>129</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>清玩書巻</t>
+          <t>玉蘂 [2]</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>A00:6380</t>
+          <t>A00:6067</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>セイガン ショカン</t>
+          <t>ギョクズイ</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>石黒 忠悳</t>
+          <t>藤原 道家</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>石黒忠悳 [ほか自筆]</t>
+          <t>野宮定基 : 久世通夏 [ほか写]</t>
         </is>
       </c>
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr">
         <is>
-          <t>[明治大正年間]</t>
+          <t>元禄12 [1699]-宝永3 [1706] 奥書</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr">
         <is>
-          <t>写本|書名は題簽による|その他の筆者: 市村瓚次郎, 外山正一, 緒方正規, 村上専精, 佐藤進, 菊池大麓, 三宅秀, 箕作佳吉, 三上參次, 箕作元八|冒頭に井上哲の題辞「清玩」あり|巻末に萩野由之の識語あり|収集者は『理翰片影』&lt;BC06713253&gt;の跋による|巻子本|往来書簡貼付集|名録1冊(大和綴)を付す|落款朱印: 「文学博士」, 「井上喆」, 「井上哲印」(井上哲次郎), 「和葊」(萩野由之)</t>
+          <t>写本|書名及び巻冊次は表紙による|奥中の書名: 光明峯寺禅閤道家公記, 峯禅閤記, 峯摂政記, 峯入道摂政記|承元4年の原奥書に「右即位記一卷者光明峯寺禅閤自筆正記也以件本左令吾基春卿透以写之云々加挍正之 ... 永正七年夷則上浣 從一位(花押)」とあり|奥書に「右以或人夲自常州到来令書写之彼夲端書云此冊上下卷 ... 元禄第十二暦仲夏中旬 羽林左衞中郎将藤原定基丗一才」(承元3), 「右光明峯寺禅閤道家公承元二年三月五六月八月四年二三月九月十十一十二月記は借請或人之夲自常州邊来書写之加一挍了/于時元禄第十二端午節也 左中郎将藤原定基丗才」(承元4), 「右玉蘂建暦元年少弟左中将通清朝臣助筆僅加一挍原本文字不正後来得正夲可改之者也/元禄十三年九月十日 松堂閑士(花押)丗二才」(建暦元), 「右玉蘂峯禅閤記建暦二年自二月至九月一冊以或人夲自常州邊来命家僚令書写手自加挍合了/元禄十二年五月六日 左中郎将藤原定基丗一才」(建暦2年上), 「宝永二年十月一日書写畢/承久二春玉蘂以故常州牧權中納言光圀公夲謄写之于時俗務紛擾先請慈兄源亜相公所被写也今以彼夲手自馳禿筆 余識藤(花押)丗七才/同三年二月廿五日一挍了」(承久2年上), 「右峯摂政承久二年記命傭書謄冩之手自一挍了/元禄第十二嵗次著雍単閼蕤賓中旬 羽林軍左衞中郎将藤原定基丗一才」(承久2年下), 「嘉禎四年正月二月閏二月三月四月六月玉蘂先年假借故常州牧前中納言光圀夲無剋力速遂書写之功建暦元年建暦二年下承久二年上及此卷等先献慈兄亜相君写之今及数年申復彼夲謄写之 ... 宝永三年十二月念日 参議從三位行左近衞權中将藤原朝臣定基生年卅八才」(嘉禎4年)とあり|毎半葉11行注文双行|漢文体日記|拠徳川光圀本及び中院通躬鈔本謄写|朱筆書き入れあり|印記: 「定基」(野宮定基), 「野宮書印」|虫損あり (裏打ち補修あり)</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -9324,12 +9328,12 @@
       <c r="O73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/ae3b180b-9cbe-6902-48c2-f0abfdf0a27e.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/20ddaef2-73cc-5ae8-949d-0bdc521924e9.json</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>ae3b180b-9cbe-6902-48c2-f0abfdf0a27e</t>
+          <t>20ddaef2-73cc-5ae8-949d-0bdc521924e9</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
@@ -9339,7 +9343,7 @@
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/ae3b180b-9cbe-6902-48c2-f0abfdf0a27e</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/20ddaef2-73cc-5ae8-949d-0bdc521924e9</t>
         </is>
       </c>
       <c r="T73" t="inlineStr">
@@ -9349,12 +9353,12 @@
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/e799186565cb40d919d91c02eef1308118771dd3.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/e2bfc2adbffcfb9eb459e7863108300f2722cdd2.jpg</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296235</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296191</t>
         </is>
       </c>
       <c r="W73" t="inlineStr">
@@ -9377,7 +9381,7 @@
       <c r="AB73" t="inlineStr"/>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/ae3b180b-9cbe-6902-48c2-f0abfdf0a27e/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/20ddaef2-73cc-5ae8-949d-0bdc521924e9/manifest</t>
         </is>
       </c>
       <c r="AD73" t="inlineStr"/>
@@ -9385,52 +9389,52 @@
       <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="inlineStr"/>
       <c r="AH73" t="n">
-        <v>26</v>
+        <v>104</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>聚珍書巻</t>
+          <t>玉蘂 [3]</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>A00:6381</t>
+          <t>A00:6067</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>シュウチン ショカン</t>
+          <t>ギョクズイ</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>浜尾 新</t>
+          <t>藤原 道家</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>濱尾新 [ほか自筆]</t>
+          <t>野宮定基 : 久世通夏 [ほか写]</t>
         </is>
       </c>
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr">
         <is>
-          <t>[明治年間]</t>
+          <t>元禄12 [1699]-宝永3 [1706] 奥書</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr">
         <is>
-          <t>写本|書名は題簽による|題辞に「聚珍 明治己酉夏八十三老人成斎題」とあり|巻末識語に「松本百蔵為東亰帝國大學厮養二十餘年毎掃故紙籠見有文字者輒収而弆之頃揀其署名氏者十餘紙装潢成卷皆名賢鉅公碩學鴻儒之筆也 ... 明治庚戌二月初夏 豊城陳人恒書時年七十又二」とあり|その他の筆者: 細川潤次郎, 渡邊洪基, 加藤弘之, 川田剛, 辻新次, 中村正直, 古市公威, 小中村清矩, 木村正辭, 島田重禮|巻子本|往来書簡貼付集|名録1冊(大和綴)を付す|落款朱印: 「晩香」, 「徳天」, 「星野恒印」, 「續古堂」, 「重野」, 「重埜士徳」, 「藤原安繹」</t>
+          <t>写本|書名及び巻冊次は表紙による|奥中の書名: 光明峯寺禅閤道家公記, 峯禅閤記, 峯摂政記, 峯入道摂政記|承元4年の原奥書に「右即位記一卷者光明峯寺禅閤自筆正記也以件本左令吾基春卿透以写之云々加挍正之 ... 永正七年夷則上浣 從一位(花押)」とあり|奥書に「右以或人夲自常州到来令書写之彼夲端書云此冊上下卷 ... 元禄第十二暦仲夏中旬 羽林左衞中郎将藤原定基丗一才」(承元3), 「右光明峯寺禅閤道家公承元二年三月五六月八月四年二三月九月十十一十二月記は借請或人之夲自常州邊来書写之加一挍了/于時元禄第十二端午節也 左中郎将藤原定基丗才」(承元4), 「右玉蘂建暦元年少弟左中将通清朝臣助筆僅加一挍原本文字不正後来得正夲可改之者也/元禄十三年九月十日 松堂閑士(花押)丗二才」(建暦元), 「右玉蘂峯禅閤記建暦二年自二月至九月一冊以或人夲自常州邊来命家僚令書写手自加挍合了/元禄十二年五月六日 左中郎将藤原定基丗一才」(建暦2年上), 「宝永二年十月一日書写畢/承久二春玉蘂以故常州牧權中納言光圀公夲謄写之于時俗務紛擾先請慈兄源亜相公所被写也今以彼夲手自馳禿筆 余識藤(花押)丗七才/同三年二月廿五日一挍了」(承久2年上), 「右峯摂政承久二年記命傭書謄冩之手自一挍了/元禄第十二嵗次著雍単閼蕤賓中旬 羽林軍左衞中郎将藤原定基丗一才」(承久2年下), 「嘉禎四年正月二月閏二月三月四月六月玉蘂先年假借故常州牧前中納言光圀夲無剋力速遂書写之功建暦元年建暦二年下承久二年上及此卷等先献慈兄亜相君写之今及数年申復彼夲謄写之 ... 宝永三年十二月念日 参議從三位行左近衞權中将藤原朝臣定基生年卅八才」(嘉禎4年)とあり|毎半葉11行注文双行|漢文体日記|拠徳川光圀本及び中院通躬鈔本謄写|朱筆書き入れあり|印記: 「定基」(野宮定基), 「野宮書印」|虫損あり (裏打ち補修あり)</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -9446,12 +9450,12 @@
       <c r="O74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/4e78ded3-2829-990e-572b-4b5e029a69cc.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/7f62eb7a-844c-22ea-196e-998226c991ea.json</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>4e78ded3-2829-990e-572b-4b5e029a69cc</t>
+          <t>7f62eb7a-844c-22ea-196e-998226c991ea</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
@@ -9461,7 +9465,7 @@
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/4e78ded3-2829-990e-572b-4b5e029a69cc</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/7f62eb7a-844c-22ea-196e-998226c991ea</t>
         </is>
       </c>
       <c r="T74" t="inlineStr">
@@ -9471,12 +9475,12 @@
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/fe6e0e801688014b204ebe9deee8085c19831bc3.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/ac4d01393f2eb0586033bfface43acc61e64021e.jpg</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296236</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296192</t>
         </is>
       </c>
       <c r="W74" t="inlineStr">
@@ -9499,7 +9503,7 @@
       <c r="AB74" t="inlineStr"/>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/4e78ded3-2829-990e-572b-4b5e029a69cc/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/7f62eb7a-844c-22ea-196e-998226c991ea/manifest</t>
         </is>
       </c>
       <c r="AD74" t="inlineStr"/>
@@ -9507,52 +9511,52 @@
       <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="inlineStr"/>
       <c r="AH74" t="n">
-        <v>27</v>
+        <v>77</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>理翰片影</t>
+          <t>玉蘂 [4]</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>A00:6382</t>
+          <t>A00:6067</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>リカン ヘンエイ</t>
+          <t>ギョクズイ</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>井上 毅</t>
+          <t>藤原 道家</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>井上毅 [ほか自筆]</t>
+          <t>野宮定基 : 久世通夏 [ほか写]</t>
         </is>
       </c>
       <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr">
         <is>
-          <t>[明治大正年間]</t>
+          <t>元禄12 [1699]-宝永3 [1706] 奥書</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr">
         <is>
-          <t>写本|書名は題簽による|敘に「松本百藏君我が東京帝國大學に縁故ある諸君の筆蹟を蒐集シ己ニ三卷をなす此卷収む事といわは故子爵井上毅先生をはじめとし神保小虎博士に至るまで十二君の消息なり ... 大正十四年春日三上参次(花押)」とあり|跋に「松本百藏奉職東京帝國大學勞使四十年夙昔不怠其所勤非尋常也大正十四年以古稀辤其軄以平生所収簡牘装潢之得四巻二帖納大學書庫 ... 大正十五年五月於東京帝國大學夲部象軒平野直文識」とあり|その他の筆者: 八代六郎, 垪和爲昌, 鶴田賢次, 長井長義, 久原躬弦, 藤澤利喜太郎, 小藤文次郎, 寺野精一, 青山胤通, 佐藤三吉, 神保小乕|巻子本|往来書簡貼付集|落款朱印: 「士可」, 「虚坣居士」, 「平野直文」</t>
+          <t>写本|書名及び巻冊次は表紙による|奥中の書名: 光明峯寺禅閤道家公記, 峯禅閤記, 峯摂政記, 峯入道摂政記|承元4年の原奥書に「右即位記一卷者光明峯寺禅閤自筆正記也以件本左令吾基春卿透以写之云々加挍正之 ... 永正七年夷則上浣 從一位(花押)」とあり|奥書に「右以或人夲自常州到来令書写之彼夲端書云此冊上下卷 ... 元禄第十二暦仲夏中旬 羽林左衞中郎将藤原定基丗一才」(承元3), 「右光明峯寺禅閤道家公承元二年三月五六月八月四年二三月九月十十一十二月記は借請或人之夲自常州邊来書写之加一挍了/于時元禄第十二端午節也 左中郎将藤原定基丗才」(承元4), 「右玉蘂建暦元年少弟左中将通清朝臣助筆僅加一挍原本文字不正後来得正夲可改之者也/元禄十三年九月十日 松堂閑士(花押)丗二才」(建暦元), 「右玉蘂峯禅閤記建暦二年自二月至九月一冊以或人夲自常州邊来命家僚令書写手自加挍合了/元禄十二年五月六日 左中郎将藤原定基丗一才」(建暦2年上), 「宝永二年十月一日書写畢/承久二春玉蘂以故常州牧權中納言光圀公夲謄写之于時俗務紛擾先請慈兄源亜相公所被写也今以彼夲手自馳禿筆 余識藤(花押)丗七才/同三年二月廿五日一挍了」(承久2年上), 「右峯摂政承久二年記命傭書謄冩之手自一挍了/元禄第十二嵗次著雍単閼蕤賓中旬 羽林軍左衞中郎将藤原定基丗一才」(承久2年下), 「嘉禎四年正月二月閏二月三月四月六月玉蘂先年假借故常州牧前中納言光圀夲無剋力速遂書写之功建暦元年建暦二年下承久二年上及此卷等先献慈兄亜相君写之今及数年申復彼夲謄写之 ... 宝永三年十二月念日 参議從三位行左近衞權中将藤原朝臣定基生年卅八才」(嘉禎4年)とあり|毎半葉11行注文双行|漢文体日記|拠徳川光圀本及び中院通躬鈔本謄写|朱筆書き入れあり|印記: 「定基」(野宮定基), 「野宮書印」|虫損あり (裏打ち補修あり)</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -9568,12 +9572,12 @@
       <c r="O75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/31b15e19-44d8-6c52-9780-873a7f1a2480.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/f48a78a7-0365-73cb-4e46-dd013ef92813.json</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>31b15e19-44d8-6c52-9780-873a7f1a2480</t>
+          <t>f48a78a7-0365-73cb-4e46-dd013ef92813</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
@@ -9583,7 +9587,7 @@
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/31b15e19-44d8-6c52-9780-873a7f1a2480</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/f48a78a7-0365-73cb-4e46-dd013ef92813</t>
         </is>
       </c>
       <c r="T75" t="inlineStr">
@@ -9593,12 +9597,12 @@
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/c34f4eff76edef5a959de5048f588d40ac1cccac.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/d9d6bd695feea8f0816bee6e991e141accf01cd8.jpg</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296237</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296193</t>
         </is>
       </c>
       <c r="W75" t="inlineStr">
@@ -9621,7 +9625,7 @@
       <c r="AB75" t="inlineStr"/>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/31b15e19-44d8-6c52-9780-873a7f1a2480/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/f48a78a7-0365-73cb-4e46-dd013ef92813/manifest</t>
         </is>
       </c>
       <c r="AD75" t="inlineStr"/>
@@ -9629,52 +9633,52 @@
       <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="inlineStr"/>
       <c r="AH75" t="n">
-        <v>21</v>
+        <v>138</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>學海拾遺珠</t>
+          <t>玉蘂 [5]</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>A00:6383</t>
+          <t>A00:6067</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>ガッカイ シュウイシュ</t>
+          <t>ギョクズイ</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>渡辺 渡</t>
+          <t>藤原 道家</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>渡邊渡 [ほか自筆]</t>
+          <t>野宮定基 : 久世通夏 [ほか写]</t>
         </is>
       </c>
       <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr">
         <is>
-          <t>[明治大正年間]</t>
+          <t>元禄12 [1699]-宝永3 [1706] 奥書</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr">
         <is>
-          <t>写本|書名は題簽による|題辞に「學海拾遺珠 大正十二年初夏 讀律書屋主人題」とあり|巻末識語に「東京帝國大學の地小丘有り丘上に會議所有り總長教授等會食聚議の處と為に松本君其の役たると久し親しく碩學大家に接し之を敬するを知る留意して敗紙中に諸家の手跡を索め嵗月を累収て十数家に及へは輙ち裝潢して卷を成す今や第三卷成り文を予に求む松本君孤影孑然會議所に起臥す伴侶は唯名家手簡と手栽の盆柎有るのみ ... 大正十二年二月十九日 隨軒學人」とあり|その他の筆者: 和田垣謙三, 川瀬善太郎, 高松豊吉, 田中義成, 永井久一郎, 中村恭平, 山川健次郎, 松井直吉, 松村任三, 古在由直, 寺尾寿, 櫻井錠二, 清水彦五郎|巻子本|往来書簡貼付集|名録1冊(大和綴)を付す|落款朱印: 「讀經堂主人號随軒」, 「服部宇之吉印記」, 「直文」(平野直文)</t>
+          <t>写本|書名及び巻冊次は表紙による|奥中の書名: 光明峯寺禅閤道家公記, 峯禅閤記, 峯摂政記, 峯入道摂政記|承元4年の原奥書に「右即位記一卷者光明峯寺禅閤自筆正記也以件本左令吾基春卿透以写之云々加挍正之 ... 永正七年夷則上浣 從一位(花押)」とあり|奥書に「右以或人夲自常州到来令書写之彼夲端書云此冊上下卷 ... 元禄第十二暦仲夏中旬 羽林左衞中郎将藤原定基丗一才」(承元3), 「右光明峯寺禅閤道家公承元二年三月五六月八月四年二三月九月十十一十二月記は借請或人之夲自常州邊来書写之加一挍了/于時元禄第十二端午節也 左中郎将藤原定基丗才」(承元4), 「右玉蘂建暦元年少弟左中将通清朝臣助筆僅加一挍原本文字不正後来得正夲可改之者也/元禄十三年九月十日 松堂閑士(花押)丗二才」(建暦元), 「右玉蘂峯禅閤記建暦二年自二月至九月一冊以或人夲自常州邊来命家僚令書写手自加挍合了/元禄十二年五月六日 左中郎将藤原定基丗一才」(建暦2年上), 「宝永二年十月一日書写畢/承久二春玉蘂以故常州牧權中納言光圀公夲謄写之于時俗務紛擾先請慈兄源亜相公所被写也今以彼夲手自馳禿筆 余識藤(花押)丗七才/同三年二月廿五日一挍了」(承久2年上), 「右峯摂政承久二年記命傭書謄冩之手自一挍了/元禄第十二嵗次著雍単閼蕤賓中旬 羽林軍左衞中郎将藤原定基丗一才」(承久2年下), 「嘉禎四年正月二月閏二月三月四月六月玉蘂先年假借故常州牧前中納言光圀夲無剋力速遂書写之功建暦元年建暦二年下承久二年上及此卷等先献慈兄亜相君写之今及数年申復彼夲謄写之 ... 宝永三年十二月念日 参議從三位行左近衞權中将藤原朝臣定基生年卅八才」(嘉禎4年)とあり|毎半葉11行注文双行|漢文体日記|拠徳川光圀本及び中院通躬鈔本謄写|朱筆書き入れあり|印記: 「定基」(野宮定基), 「野宮書印」|虫損あり (裏打ち補修あり)</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -9690,12 +9694,12 @@
       <c r="O76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/9639e5f3-92bd-7423-1bf1-08c4dc087bdf.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/c4ba4bb2-8d3c-7e43-4e3e-e6a6d0c2260f.json</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>9639e5f3-92bd-7423-1bf1-08c4dc087bdf</t>
+          <t>c4ba4bb2-8d3c-7e43-4e3e-e6a6d0c2260f</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
@@ -9705,7 +9709,7 @@
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/9639e5f3-92bd-7423-1bf1-08c4dc087bdf</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/c4ba4bb2-8d3c-7e43-4e3e-e6a6d0c2260f</t>
         </is>
       </c>
       <c r="T76" t="inlineStr">
@@ -9715,12 +9719,12 @@
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/b210fc9854d945b959acd96b0e4fa57d3578ea07.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/58826021e366d49d150087ff3478b98548b97c4a.jpg</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296238</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296194</t>
         </is>
       </c>
       <c r="W76" t="inlineStr">
@@ -9743,7 +9747,7 @@
       <c r="AB76" t="inlineStr"/>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/9639e5f3-92bd-7423-1bf1-08c4dc087bdf/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/c4ba4bb2-8d3c-7e43-4e3e-e6a6d0c2260f/manifest</t>
         </is>
       </c>
       <c r="AD76" t="inlineStr"/>
@@ -9751,52 +9755,52 @@
       <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="inlineStr"/>
       <c r="AH76" t="n">
-        <v>27</v>
+        <v>69</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>御成敗式目</t>
+          <t>玉蘂 [6]</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>A00:6456</t>
+          <t>A00:6067</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>ゴセイバイ シキモク</t>
+          <t>ギョクズイ</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>平泰時 [ほか定]</t>
+          <t>藤原 道家</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>[書写者不明]</t>
+          <t>野宮定基 : 久世通夏 [ほか写]</t>
         </is>
       </c>
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr">
         <is>
-          <t>康永2 [1343] 奥書</t>
+          <t>元禄12 [1699]-宝永3 [1706] 奥書</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr">
         <is>
-          <t>写本|本文末に「貞永元年七月十日 沙弥浄圎/相模大掾藤原業時/玄蕃允三善康連/左衞門少尉藤原朝臣基綱/沙弥行然/散位三善朝臣倫重/加賀守三善朝臣康俊/沙弥行西/前出羽守藤原朝臣家長/前駿河守平義村/前攝津守中原師貟/武蔵守平泰時/相模守平時房」との連署名あり|巻末に「嘉禎三年八月十七日評定之」, 「延應二年五月廾五日評定之」, 「暦仁元年十二月十九日評定之」, 「延應元年九月廾日評定之改嫁事」, 「仁治三十二五評定」, 「嘉禎四年九月二十七日評定之」, 「仁治四二廾五追評定之」, 「延應二年五月廾五日評定之」, 「延應二四廾五評」など追加補抄及び「御式目事」(貞永元八月八日 武蔵守御判/するかの守殿)書簡抄を付す|奥書に「康永二年三月三日於高辻冨小路宿所書冩之訖」とあり|毎葉7行17字注文双行|本文は真字, 送り仮名, 返り点を施し|金砂子散し花菱繋ぎの見返し, 押界を施した楮紙打紙を使用|朱墨筆書き入れあり|軸物(打紙継ぎ)|桐箱入り|印記: 「本立堂記」|汚損, 虫損あり</t>
+          <t>写本|書名及び巻冊次は表紙による|奥中の書名: 光明峯寺禅閤道家公記, 峯禅閤記, 峯摂政記, 峯入道摂政記|承元4年の原奥書に「右即位記一卷者光明峯寺禅閤自筆正記也以件本左令吾基春卿透以写之云々加挍正之 ... 永正七年夷則上浣 從一位(花押)」とあり|奥書に「右以或人夲自常州到来令書写之彼夲端書云此冊上下卷 ... 元禄第十二暦仲夏中旬 羽林左衞中郎将藤原定基丗一才」(承元3), 「右光明峯寺禅閤道家公承元二年三月五六月八月四年二三月九月十十一十二月記は借請或人之夲自常州邊来書写之加一挍了/于時元禄第十二端午節也 左中郎将藤原定基丗才」(承元4), 「右玉蘂建暦元年少弟左中将通清朝臣助筆僅加一挍原本文字不正後来得正夲可改之者也/元禄十三年九月十日 松堂閑士(花押)丗二才」(建暦元), 「右玉蘂峯禅閤記建暦二年自二月至九月一冊以或人夲自常州邊来命家僚令書写手自加挍合了/元禄十二年五月六日 左中郎将藤原定基丗一才」(建暦2年上), 「宝永二年十月一日書写畢/承久二春玉蘂以故常州牧權中納言光圀公夲謄写之于時俗務紛擾先請慈兄源亜相公所被写也今以彼夲手自馳禿筆 余識藤(花押)丗七才/同三年二月廿五日一挍了」(承久2年上), 「右峯摂政承久二年記命傭書謄冩之手自一挍了/元禄第十二嵗次著雍単閼蕤賓中旬 羽林軍左衞中郎将藤原定基丗一才」(承久2年下), 「嘉禎四年正月二月閏二月三月四月六月玉蘂先年假借故常州牧前中納言光圀夲無剋力速遂書写之功建暦元年建暦二年下承久二年上及此卷等先献慈兄亜相君写之今及数年申復彼夲謄写之 ... 宝永三年十二月念日 参議從三位行左近衞權中将藤原朝臣定基生年卅八才」(嘉禎4年)とあり|毎半葉11行注文双行|漢文体日記|拠徳川光圀本及び中院通躬鈔本謄写|朱筆書き入れあり|印記: 「定基」(野宮定基), 「野宮書印」|虫損あり (裏打ち補修あり)</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -9812,12 +9816,12 @@
       <c r="O77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/1dc60eb8-0dd2-1716-521a-8b436e899759.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/73dc1d4b-7872-a0a3-780c-3c10d2a3758a.json</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>1dc60eb8-0dd2-1716-521a-8b436e899759</t>
+          <t>73dc1d4b-7872-a0a3-780c-3c10d2a3758a</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
@@ -9827,7 +9831,7 @@
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/1dc60eb8-0dd2-1716-521a-8b436e899759</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/73dc1d4b-7872-a0a3-780c-3c10d2a3758a</t>
         </is>
       </c>
       <c r="T77" t="inlineStr">
@@ -9837,12 +9841,12 @@
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/8182eba23e72331505a8074acdfe6b5481d358fd.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/6724525552ca8e3c1f42cdc0f0674a54828dc026.jpg</t>
         </is>
       </c>
       <c r="V77" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296239</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296195</t>
         </is>
       </c>
       <c r="W77" t="inlineStr">
@@ -9865,7 +9869,7 @@
       <c r="AB77" t="inlineStr"/>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/1dc60eb8-0dd2-1716-521a-8b436e899759/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/73dc1d4b-7872-a0a3-780c-3c10d2a3758a/manifest</t>
         </is>
       </c>
       <c r="AD77" t="inlineStr"/>
@@ -9873,52 +9877,52 @@
       <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="inlineStr"/>
       <c r="AH77" t="n">
-        <v>45</v>
+        <v>106</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>辨證配劑醫燈 3巻 [1]</t>
+          <t>玉蘂 [7]</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>A00:6517</t>
+          <t>A00:6067</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>ベンショウ ハイザイ イトウ</t>
+          <t>ギョクズイ</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
-          <t>曲直瀬 道三</t>
+          <t>藤原 道家</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>道三 [自筆]</t>
+          <t>野宮定基 : 久世通夏 [ほか写]</t>
         </is>
       </c>
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr">
         <is>
-          <t>元亀2 [1571] 大尾</t>
+          <t>元禄12 [1699]-宝永3 [1706] 奥書</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr">
         <is>
-          <t>写本|巻之2の巻頭書名: 辨證配剤醫燈|大尾に「治病用藥之時欲使侄姪孫一覧如指掌而已/旹元亀第二辛未年冬日南至六十五齢老眼寒窓/日東洛下雖知苦斎盍静翁 道三」とあり|巻末識語に「辨證配劑醫燈全三册壹帙一溪叟道三所親筆也不可忽諸故附一語於後耳」とあり|箱に「和氣道三自書寫配劑醫燈三卷林道春跋之櫻井老人苐一家藏子孫永寶之 葛辰識」との墨書あり|毎半面11行|朱点, 朱引, 朱藍筆書き入れあり|付箋あり|箱入り|印記: 「石堂」, 「昃印」|虫損, 汚損あり</t>
+          <t>写本|書名及び巻冊次は表紙による|奥中の書名: 光明峯寺禅閤道家公記, 峯禅閤記, 峯摂政記, 峯入道摂政記|承元4年の原奥書に「右即位記一卷者光明峯寺禅閤自筆正記也以件本左令吾基春卿透以写之云々加挍正之 ... 永正七年夷則上浣 從一位(花押)」とあり|奥書に「右以或人夲自常州到来令書写之彼夲端書云此冊上下卷 ... 元禄第十二暦仲夏中旬 羽林左衞中郎将藤原定基丗一才」(承元3), 「右光明峯寺禅閤道家公承元二年三月五六月八月四年二三月九月十十一十二月記は借請或人之夲自常州邊来書写之加一挍了/于時元禄第十二端午節也 左中郎将藤原定基丗才」(承元4), 「右玉蘂建暦元年少弟左中将通清朝臣助筆僅加一挍原本文字不正後来得正夲可改之者也/元禄十三年九月十日 松堂閑士(花押)丗二才」(建暦元), 「右玉蘂峯禅閤記建暦二年自二月至九月一冊以或人夲自常州邊来命家僚令書写手自加挍合了/元禄十二年五月六日 左中郎将藤原定基丗一才」(建暦2年上), 「宝永二年十月一日書写畢/承久二春玉蘂以故常州牧權中納言光圀公夲謄写之于時俗務紛擾先請慈兄源亜相公所被写也今以彼夲手自馳禿筆 余識藤(花押)丗七才/同三年二月廿五日一挍了」(承久2年上), 「右峯摂政承久二年記命傭書謄冩之手自一挍了/元禄第十二嵗次著雍単閼蕤賓中旬 羽林軍左衞中郎将藤原定基丗一才」(承久2年下), 「嘉禎四年正月二月閏二月三月四月六月玉蘂先年假借故常州牧前中納言光圀夲無剋力速遂書写之功建暦元年建暦二年下承久二年上及此卷等先献慈兄亜相君写之今及数年申復彼夲謄写之 ... 宝永三年十二月念日 参議從三位行左近衞權中将藤原朝臣定基生年卅八才」(嘉禎4年)とあり|毎半葉11行注文双行|漢文体日記|拠徳川光圀本及び中院通躬鈔本謄写|朱筆書き入れあり|印記: 「定基」(野宮定基), 「野宮書印」|虫損あり (裏打ち補修あり)</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -9934,12 +9938,12 @@
       <c r="O78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/ede81088-3a4b-221d-711c-889d446e8d7e.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/e775ea12-9867-70f2-6381-112e31478f75.json</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>ede81088-3a4b-221d-711c-889d446e8d7e</t>
+          <t>e775ea12-9867-70f2-6381-112e31478f75</t>
         </is>
       </c>
       <c r="R78" t="inlineStr">
@@ -9949,7 +9953,7 @@
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/ede81088-3a4b-221d-711c-889d446e8d7e</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/e775ea12-9867-70f2-6381-112e31478f75</t>
         </is>
       </c>
       <c r="T78" t="inlineStr">
@@ -9959,12 +9963,12 @@
       </c>
       <c r="U78" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/1089675f22f8a9e5e8d856bf42c0b3fa7e2b5168.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/08e58358a211a53638e77e5431d7fedb34bd5f72.jpg</t>
         </is>
       </c>
       <c r="V78" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296240</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296196</t>
         </is>
       </c>
       <c r="W78" t="inlineStr">
@@ -9987,7 +9991,7 @@
       <c r="AB78" t="inlineStr"/>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/ede81088-3a4b-221d-711c-889d446e8d7e/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/e775ea12-9867-70f2-6381-112e31478f75/manifest</t>
         </is>
       </c>
       <c r="AD78" t="inlineStr"/>
@@ -9995,52 +9999,52 @@
       <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="inlineStr"/>
       <c r="AH78" t="n">
-        <v>61</v>
+        <v>146</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>辨證配劑醫燈 3巻 [2]</t>
+          <t>玉蘂 [8]</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>A00:6517</t>
+          <t>A00:6067</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>ベンショウ ハイザイ イトウ</t>
+          <t>ギョクズイ</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>曲直瀬 道三</t>
+          <t>藤原 道家</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>道三 [自筆]</t>
+          <t>野宮定基 : 久世通夏 [ほか写]</t>
         </is>
       </c>
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr">
         <is>
-          <t>元亀2 [1571] 大尾</t>
+          <t>元禄12 [1699]-宝永3 [1706] 奥書</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr">
         <is>
-          <t>写本|巻之2の巻頭書名: 辨證配剤醫燈|大尾に「治病用藥之時欲使侄姪孫一覧如指掌而已/旹元亀第二辛未年冬日南至六十五齢老眼寒窓/日東洛下雖知苦斎盍静翁 道三」とあり|巻末識語に「辨證配劑醫燈全三册壹帙一溪叟道三所親筆也不可忽諸故附一語於後耳」とあり|箱に「和氣道三自書寫配劑醫燈三卷林道春跋之櫻井老人苐一家藏子孫永寶之 葛辰識」との墨書あり|毎半面11行|朱点, 朱引, 朱藍筆書き入れあり|付箋あり|箱入り|印記: 「石堂」, 「昃印」|虫損, 汚損あり</t>
+          <t>写本|書名及び巻冊次は表紙による|奥中の書名: 光明峯寺禅閤道家公記, 峯禅閤記, 峯摂政記, 峯入道摂政記|承元4年の原奥書に「右即位記一卷者光明峯寺禅閤自筆正記也以件本左令吾基春卿透以写之云々加挍正之 ... 永正七年夷則上浣 從一位(花押)」とあり|奥書に「右以或人夲自常州到来令書写之彼夲端書云此冊上下卷 ... 元禄第十二暦仲夏中旬 羽林左衞中郎将藤原定基丗一才」(承元3), 「右光明峯寺禅閤道家公承元二年三月五六月八月四年二三月九月十十一十二月記は借請或人之夲自常州邊来書写之加一挍了/于時元禄第十二端午節也 左中郎将藤原定基丗才」(承元4), 「右玉蘂建暦元年少弟左中将通清朝臣助筆僅加一挍原本文字不正後来得正夲可改之者也/元禄十三年九月十日 松堂閑士(花押)丗二才」(建暦元), 「右玉蘂峯禅閤記建暦二年自二月至九月一冊以或人夲自常州邊来命家僚令書写手自加挍合了/元禄十二年五月六日 左中郎将藤原定基丗一才」(建暦2年上), 「宝永二年十月一日書写畢/承久二春玉蘂以故常州牧權中納言光圀公夲謄写之于時俗務紛擾先請慈兄源亜相公所被写也今以彼夲手自馳禿筆 余識藤(花押)丗七才/同三年二月廿五日一挍了」(承久2年上), 「右峯摂政承久二年記命傭書謄冩之手自一挍了/元禄第十二嵗次著雍単閼蕤賓中旬 羽林軍左衞中郎将藤原定基丗一才」(承久2年下), 「嘉禎四年正月二月閏二月三月四月六月玉蘂先年假借故常州牧前中納言光圀夲無剋力速遂書写之功建暦元年建暦二年下承久二年上及此卷等先献慈兄亜相君写之今及数年申復彼夲謄写之 ... 宝永三年十二月念日 参議從三位行左近衞權中将藤原朝臣定基生年卅八才」(嘉禎4年)とあり|毎半葉11行注文双行|漢文体日記|拠徳川光圀本及び中院通躬鈔本謄写|朱筆書き入れあり|印記: 「定基」(野宮定基), 「野宮書印」|虫損あり (裏打ち補修あり)</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -10056,12 +10060,12 @@
       <c r="O79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/93511b52-3de6-4102-980b-24d00b6c5851.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/ca2da620-345c-76fa-9d1d-e7b2c55d757f.json</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>93511b52-3de6-4102-980b-24d00b6c5851</t>
+          <t>ca2da620-345c-76fa-9d1d-e7b2c55d757f</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
@@ -10071,7 +10075,7 @@
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/93511b52-3de6-4102-980b-24d00b6c5851</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/ca2da620-345c-76fa-9d1d-e7b2c55d757f</t>
         </is>
       </c>
       <c r="T79" t="inlineStr">
@@ -10081,12 +10085,12 @@
       </c>
       <c r="U79" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/a82992bab1da44c99dc71e9ac8ef6ff3d626dc4d.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/8204e28b4e8f0e2f8abc1b939244f007093f3749.jpg</t>
         </is>
       </c>
       <c r="V79" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296241</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296197</t>
         </is>
       </c>
       <c r="W79" t="inlineStr">
@@ -10109,7 +10113,7 @@
       <c r="AB79" t="inlineStr"/>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/93511b52-3de6-4102-980b-24d00b6c5851/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/ca2da620-345c-76fa-9d1d-e7b2c55d757f/manifest</t>
         </is>
       </c>
       <c r="AD79" t="inlineStr"/>
@@ -10117,52 +10121,48 @@
       <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="inlineStr"/>
       <c r="AH79" t="n">
-        <v>52</v>
+        <v>63</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>辨證配劑醫燈 3巻 [3]</t>
+          <t>大明星天子法 : 又名法界虚空蔵法</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>A00:6517</t>
+          <t>A00:6097</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>ベンショウ ハイザイ イトウ</t>
+          <t>ダイミョウジョウテンシホウ : マタミョウ ホッカイ コクウゾウホウ</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>曲直瀬 道三</t>
-        </is>
-      </c>
+      <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr">
         <is>
-          <t>道三 [自筆]</t>
+          <t>[書写者不明]</t>
         </is>
       </c>
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr">
         <is>
-          <t>元亀2 [1571] 大尾</t>
+          <t>[天文年間]</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr">
         <is>
-          <t>写本|巻之2の巻頭書名: 辨證配剤醫燈|大尾に「治病用藥之時欲使侄姪孫一覧如指掌而已/旹元亀第二辛未年冬日南至六十五齢老眼寒窓/日東洛下雖知苦斎盍静翁 道三」とあり|巻末識語に「辨證配劑醫燈全三册壹帙一溪叟道三所親筆也不可忽諸故附一語於後耳」とあり|箱に「和氣道三自書寫配劑醫燈三卷林道春跋之櫻井老人苐一家藏子孫永寶之 葛辰識」との墨書あり|毎半面11行|朱点, 朱引, 朱藍筆書き入れあり|付箋あり|箱入り|印記: 「石堂」, 「昃印」|虫損, 汚損あり</t>
+          <t>写本|巻末の書名: 明星天子法|表紙の書名: 大明皇天子水|大尾に「明星天子法次苐 一交了」とあり|本奥書に「承久三年五月十三日/爲興法利生徃生極樂書冩之/金剛佛子觀照之」とあり|書袋に「天文古筆」, 「天明七未ノ年」とあり|毎半葉8行|押界を施した楮紙打紙を使用|粘葉装|虫損あり</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -10178,12 +10178,12 @@
       <c r="O80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/a23dae2e-701a-8d7c-1359-fe786c2e2cdd.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/a1905fc7-4727-0750-41d7-f0ca1df53f47.json</t>
         </is>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>a23dae2e-701a-8d7c-1359-fe786c2e2cdd</t>
+          <t>a1905fc7-4727-0750-41d7-f0ca1df53f47</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
@@ -10193,7 +10193,7 @@
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/a23dae2e-701a-8d7c-1359-fe786c2e2cdd</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/a1905fc7-4727-0750-41d7-f0ca1df53f47</t>
         </is>
       </c>
       <c r="T80" t="inlineStr">
@@ -10203,12 +10203,12 @@
       </c>
       <c r="U80" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/21b02bac7c065db97c214037acfa4b232d2ddc89.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/b2590ef4e55f582d8059a5e072e1d6dad33bf996.jpg</t>
         </is>
       </c>
       <c r="V80" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296242</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296198</t>
         </is>
       </c>
       <c r="W80" t="inlineStr">
@@ -10231,7 +10231,7 @@
       <c r="AB80" t="inlineStr"/>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/a23dae2e-701a-8d7c-1359-fe786c2e2cdd/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/a1905fc7-4727-0750-41d7-f0ca1df53f47/manifest</t>
         </is>
       </c>
       <c r="AD80" t="inlineStr"/>
@@ -10239,7 +10239,7 @@
       <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="inlineStr"/>
       <c r="AH80" t="n">
-        <v>63</v>
+        <v>9</v>
       </c>
     </row>
     <row r="81">

--- a/docs/collections/koten/metadata/data.xlsx
+++ b/docs/collections/koten/metadata/data.xlsx
@@ -761,7 +761,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [17]</t>
+          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [20]</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -816,12 +816,12 @@
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/37d790df-458b-48bf-6b67-3f4755f40f0f.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/d64280ea-576f-4bf3-9413-1b0bf6485e16.json</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>37d790df-458b-48bf-6b67-3f4755f40f0f</t>
+          <t>d64280ea-576f-4bf3-9413-1b0bf6485e16</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -831,7 +831,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/37d790df-458b-48bf-6b67-3f4755f40f0f</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/d64280ea-576f-4bf3-9413-1b0bf6485e16</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -841,12 +841,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/dae05b3fca02a35e3363b381527ea7a899ca4f74.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/c5e3a0bdc0b67f7429d47677a33485a6a498e20f.jpg</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296217</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296220</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -869,7 +869,7 @@
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/37d790df-458b-48bf-6b67-3f4755f40f0f/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/d64280ea-576f-4bf3-9413-1b0bf6485e16/manifest</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr"/>
@@ -877,13 +877,13 @@
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="n">
-        <v>54</v>
+        <v>75</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [18]</t>
+          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [21]</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -938,12 +938,12 @@
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/c69854e0-18e9-71b3-a7b1-22422a16688b.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/decc377c-887e-7362-3bf7-81b1c9c58641.json</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>c69854e0-18e9-71b3-a7b1-22422a16688b</t>
+          <t>decc377c-887e-7362-3bf7-81b1c9c58641</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/c69854e0-18e9-71b3-a7b1-22422a16688b</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/decc377c-887e-7362-3bf7-81b1c9c58641</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -963,12 +963,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/584cfd5ec1bb0f374ab03f25ca3600a8ec2e67bf.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/cfd0eab55fb67ed7ab341ab27bc1cb892d7a575c.jpg</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296218</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296221</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -991,7 +991,7 @@
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/c69854e0-18e9-71b3-a7b1-22422a16688b/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/decc377c-887e-7362-3bf7-81b1c9c58641/manifest</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr"/>
@@ -999,13 +999,13 @@
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="n">
-        <v>77</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [19]</t>
+          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [22]</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1060,12 +1060,12 @@
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/1373f0d8-7cc0-4591-2c18-798fa20f483d.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/b6bde9f3-3f94-81f1-4307-d86d59d90fa3.json</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>1373f0d8-7cc0-4591-2c18-798fa20f483d</t>
+          <t>b6bde9f3-3f94-81f1-4307-d86d59d90fa3</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/1373f0d8-7cc0-4591-2c18-798fa20f483d</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/b6bde9f3-3f94-81f1-4307-d86d59d90fa3</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/326ed2db044321d7b007462c9ac98badfd7f671a.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/eda09740787be30df4b5cefc348bc2c063c8932c.jpg</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296219</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296222</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1113,7 +1113,7 @@
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/1373f0d8-7cc0-4591-2c18-798fa20f483d/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/b6bde9f3-3f94-81f1-4307-d86d59d90fa3/manifest</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr"/>
@@ -1121,13 +1121,13 @@
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="n">
-        <v>69</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [20]</t>
+          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [23]</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1182,12 +1182,12 @@
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/d64280ea-576f-4bf3-9413-1b0bf6485e16.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/8bd2b968-05d3-77b9-352f-f36fa2260d39.json</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>d64280ea-576f-4bf3-9413-1b0bf6485e16</t>
+          <t>8bd2b968-05d3-77b9-352f-f36fa2260d39</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/d64280ea-576f-4bf3-9413-1b0bf6485e16</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/8bd2b968-05d3-77b9-352f-f36fa2260d39</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1207,12 +1207,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/c5e3a0bdc0b67f7429d47677a33485a6a498e20f.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/30225b7ec7795f0c4d6102081bbf79b701183504.jpg</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296220</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296223</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1235,7 +1235,7 @@
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/d64280ea-576f-4bf3-9413-1b0bf6485e16/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/8bd2b968-05d3-77b9-352f-f36fa2260d39/manifest</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr"/>
@@ -1243,13 +1243,13 @@
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="inlineStr"/>
       <c r="AH6" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [21]</t>
+          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [24]</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1304,12 +1304,12 @@
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/decc377c-887e-7362-3bf7-81b1c9c58641.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/c6e97538-22ed-8a51-0e3a-550b7d652860.json</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>decc377c-887e-7362-3bf7-81b1c9c58641</t>
+          <t>c6e97538-22ed-8a51-0e3a-550b7d652860</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/decc377c-887e-7362-3bf7-81b1c9c58641</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/c6e97538-22ed-8a51-0e3a-550b7d652860</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/cfd0eab55fb67ed7ab341ab27bc1cb892d7a575c.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/a04dfdaed6c9dc7211358c5ad96c4bc6e9312747.jpg</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296221</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296224</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1357,7 +1357,7 @@
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/decc377c-887e-7362-3bf7-81b1c9c58641/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/c6e97538-22ed-8a51-0e3a-550b7d652860/manifest</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr"/>
@@ -1365,13 +1365,13 @@
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="inlineStr"/>
       <c r="AH7" t="n">
-        <v>51</v>
+        <v>62</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [22]</t>
+          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [25]</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1426,12 +1426,12 @@
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/b6bde9f3-3f94-81f1-4307-d86d59d90fa3.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/48123112-700b-8619-731b-649449ff034b.json</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>b6bde9f3-3f94-81f1-4307-d86d59d90fa3</t>
+          <t>48123112-700b-8619-731b-649449ff034b</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/b6bde9f3-3f94-81f1-4307-d86d59d90fa3</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/48123112-700b-8619-731b-649449ff034b</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/eda09740787be30df4b5cefc348bc2c063c8932c.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/4c918a15ed3dc97a18f7bc977b4dc2e8c724d774.jpg</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296222</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296225</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -1479,7 +1479,7 @@
       <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/b6bde9f3-3f94-81f1-4307-d86d59d90fa3/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/48123112-700b-8619-731b-649449ff034b/manifest</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr"/>
@@ -1487,13 +1487,13 @@
       <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="inlineStr"/>
       <c r="AH8" t="n">
-        <v>62</v>
+        <v>78</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [23]</t>
+          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [26]</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1548,12 +1548,12 @@
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/8bd2b968-05d3-77b9-352f-f36fa2260d39.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/9b2b928b-4eda-76c6-0dfd-03bde69c046c.json</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>8bd2b968-05d3-77b9-352f-f36fa2260d39</t>
+          <t>9b2b928b-4eda-76c6-0dfd-03bde69c046c</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/8bd2b968-05d3-77b9-352f-f36fa2260d39</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/9b2b928b-4eda-76c6-0dfd-03bde69c046c</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
@@ -1573,12 +1573,12 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/30225b7ec7795f0c4d6102081bbf79b701183504.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/7903cd89a232a0d9b4b243d90852d31d93c80300.jpg</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296223</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296226</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -1601,7 +1601,7 @@
       <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/8bd2b968-05d3-77b9-352f-f36fa2260d39/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/9b2b928b-4eda-76c6-0dfd-03bde69c046c/manifest</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr"/>
@@ -1609,13 +1609,13 @@
       <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="inlineStr"/>
       <c r="AH9" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [24]</t>
+          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [27]</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1670,12 +1670,12 @@
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/c6e97538-22ed-8a51-0e3a-550b7d652860.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/ccc6c3da-1648-49f5-91fc-2faaf5400387.json</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>c6e97538-22ed-8a51-0e3a-550b7d652860</t>
+          <t>ccc6c3da-1648-49f5-91fc-2faaf5400387</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1685,7 +1685,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/c6e97538-22ed-8a51-0e3a-550b7d652860</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/ccc6c3da-1648-49f5-91fc-2faaf5400387</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/a04dfdaed6c9dc7211358c5ad96c4bc6e9312747.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/1e476c24ffbe9fd54b432acbf27eb918fc4162d0.jpg</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296224</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296227</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
@@ -1723,7 +1723,7 @@
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/c6e97538-22ed-8a51-0e3a-550b7d652860/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/ccc6c3da-1648-49f5-91fc-2faaf5400387/manifest</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr"/>
@@ -1731,13 +1731,13 @@
       <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="inlineStr"/>
       <c r="AH10" t="n">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [25]</t>
+          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [28]</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1792,12 +1792,12 @@
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/48123112-700b-8619-731b-649449ff034b.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/9f3a126c-84bb-8f96-2916-b65ace30a616.json</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>48123112-700b-8619-731b-649449ff034b</t>
+          <t>9f3a126c-84bb-8f96-2916-b65ace30a616</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1807,7 +1807,7 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/48123112-700b-8619-731b-649449ff034b</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/9f3a126c-84bb-8f96-2916-b65ace30a616</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
@@ -1817,12 +1817,12 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/4c918a15ed3dc97a18f7bc977b4dc2e8c724d774.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/fc4844ae32ad2dd582e3570965cb142f5f370f74.jpg</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296225</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296228</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
@@ -1845,7 +1845,7 @@
       <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/48123112-700b-8619-731b-649449ff034b/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/9f3a126c-84bb-8f96-2916-b65ace30a616/manifest</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr"/>
@@ -1853,13 +1853,13 @@
       <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="inlineStr"/>
       <c r="AH11" t="n">
-        <v>78</v>
+        <v>70</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [26]</t>
+          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [29]</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1914,12 +1914,12 @@
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/9b2b928b-4eda-76c6-0dfd-03bde69c046c.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/7cdebe3a-8fb4-14b4-7ddb-3f92f3be9668.json</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>9b2b928b-4eda-76c6-0dfd-03bde69c046c</t>
+          <t>7cdebe3a-8fb4-14b4-7ddb-3f92f3be9668</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1929,7 +1929,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/9b2b928b-4eda-76c6-0dfd-03bde69c046c</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/7cdebe3a-8fb4-14b4-7ddb-3f92f3be9668</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
@@ -1939,12 +1939,12 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/7903cd89a232a0d9b4b243d90852d31d93c80300.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/08f5648a7b5512a896986520a6449d3620439071.jpg</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296226</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296229</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
@@ -1967,7 +1967,7 @@
       <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/9b2b928b-4eda-76c6-0dfd-03bde69c046c/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/7cdebe3a-8fb4-14b4-7ddb-3f92f3be9668/manifest</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr"/>
@@ -1975,40 +1975,40 @@
       <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="inlineStr"/>
       <c r="AH12" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [27]</t>
+          <t>普賢延命</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>A00:6257</t>
+          <t>A00:6264</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>レキダイ ザンケツ ニッキ</t>
+          <t>フゲン エンメイ</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>黒川 春村</t>
+          <t>興然</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>[書写者不明]</t>
+          <t>長円 [写]</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>[安政5 (1858)]</t>
+          <t>嘉禎2 [1236] 奥書</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2020,7 +2020,7 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>写本|責任表示及び書写年は『日本古典籍総合目録データベース』による|内容: 6: 光明院御記, 後光嚴院御記, 後小松院宸記, 天聴集. 28: 参議藤定長卿記 : 稱山丞記. 37: 定高卿記, 晴御会部類記, 家光卿御記, 權中納言平範輔卿記. 38: 左大史小槻季継記, 後堀川安貞二年放生會(実基公記), 石清水八幡宮, 弁官拝賀次第. 39: 大外記師光記, 資季卿記, 荒凉記, 忠高卿記. 40: 冷泉公相公記, 勝延法眼記 : 東寺大行事, 後中記 : 小路中納言資頼卿記葉室. 41: 中光記, 師兼記, 陽龍記. 42: 大宮司長則記, 口筆 : 實經, 顕朝卿記, 鴨御幸記. 43: 寳治二年記, 深心院關白記, 藤公親記, 照念院関白兼平公記. 44: 頼親記, 亀山殿行幸記 : 雅言卿記, 兼基公記. 45: 大嘗會御禊節下次第, 建治三年丁丑日記 : 三善康有, 建治四年正月廿一日 : 徳大寺大相國公孝記, 冬定卿記, 左大史小槻兼文記|内容: 46: 經任卿記, 前豊前守藤憲説記, 實兼公記. 47: 継塵記抄出. 48: 管見記, 公衡公記, 大外記師顕記, 大外記中原師淳記. 49: 真光院禪助僧正記, 吉田内府卿記. 50: 定清記, 叅議雅俊卿記, 太政大臣(公守公)御上表雜事, 仙洞御灌頂日記, 正安二年八月十一日於仙洞被始行熾盛光法, 正安三年御譲位記. 51: 實躬卿記. 52: 公茂公記, 冬平公記, 隆長卿記. 53: 忠教公記, 官記, 正三位長基卿記, 北面秀長記, 大外記中原師右記. 54: 文保元年, 日野中納言資朝卿記, 洞院大納言公敏卿記. 55: 隆蔭卿記, 文保三年記, 尹大納言師賢卿記, 革命記, 立倚子記, 萬里小路中納言藤藤房卿記|内容: 56: 資名卿記, 公秀公記, 一條家記装束抄出, 頼定卿記. 63: 松亞記, 日野大納言時光卿記, 後八條内府實継公記. 74: 成恩寺関白記. 78: 山科家礼記. 82: 諒闇記 : 後成恩寺殿, 宗典僧正記, 綱光公記, 贈従二位宗賢卿記, 義政公記. 84: 長禄二年戊寅正月, 見聞雜記. 87: 言國卿記. 88: 長興宿祢記, 元長卿記, 兼顕卿記, 小槻晴冨記|28末の原奥書に「右山丞記依 仰挍合書冩/享和二年四月 日撿挍保己一」とあり|50「正安二年八月十一日於仙洞被始行熾盛光法」末の原奥書に「文化十五年春二月以南山法曼院藏夲書冩之 撿挍保己一」とあり|横刷毛目表紙を使用|朱点, 朱引, 朱墨筆書き入れあり|付箋あり|蔵書印主信濃須坂藩主堀直格の命によって編集された古記録|他の原本は関東大震災により焼失|極札に「桂壽」(6), 「尚信」(53)との極書, 「武清」(44, 53), 「永海」(51), 「了伴」(52), 「了甫」(74), 「定時」(84, 88)との極印あり|印記: 「花廼家文庫」, 「墨阪十一代主寫藏記」(堀直格(1806-1880)), 「東京大學法理文學部書庫所藏」, 「閲覧室用 FOR USE IN THE READING ROOM」|虫損あり</t>
+          <t>写本|内題下に「師 理教」, 「嘉禎二年奥書アリ 長円書」とあり|巻末に「越前闍梨浄与口傳 興然夲」とあり|奥書に「嘉禎二年四月六月奉傳受空達御房ノ長円」とあり|裏に「正和元年壬子八月廿九日於成身院奉伝受之了」とあり|巻子本|送り仮名, 傍訓あり|虫損あり (裏打ち補修あり)</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -2036,12 +2036,12 @@
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/ccc6c3da-1648-49f5-91fc-2faaf5400387.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/e57fef06-5cfd-a602-6a89-f4d7d4360e87.json</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>ccc6c3da-1648-49f5-91fc-2faaf5400387</t>
+          <t>e57fef06-5cfd-a602-6a89-f4d7d4360e87</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/ccc6c3da-1648-49f5-91fc-2faaf5400387</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/e57fef06-5cfd-a602-6a89-f4d7d4360e87</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/1e476c24ffbe9fd54b432acbf27eb918fc4162d0.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/eec20da7736c221a3c86321abead9d8d9429dceb.jpg</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296227</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296230</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -2089,7 +2089,7 @@
       <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/ccc6c3da-1648-49f5-91fc-2faaf5400387/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/e57fef06-5cfd-a602-6a89-f4d7d4360e87/manifest</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr"/>
@@ -2097,40 +2097,40 @@
       <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="inlineStr"/>
       <c r="AH13" t="n">
-        <v>70</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [28]</t>
+          <t>如法愛染王</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>A00:6257</t>
+          <t>A00:6265</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>レキダイ ザンケツ ニッキ</t>
+          <t>ニョホウ アイゼンオウ</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>黒川 春村</t>
+          <t>仁海</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>[書写者不明]</t>
+          <t>禅喜 [写]</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>[安政5 (1858)]</t>
+          <t>嘉暦2 [1327] 奥書</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2142,7 +2142,7 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>写本|責任表示及び書写年は『日本古典籍総合目録データベース』による|内容: 6: 光明院御記, 後光嚴院御記, 後小松院宸記, 天聴集. 28: 参議藤定長卿記 : 稱山丞記. 37: 定高卿記, 晴御会部類記, 家光卿御記, 權中納言平範輔卿記. 38: 左大史小槻季継記, 後堀川安貞二年放生會(実基公記), 石清水八幡宮, 弁官拝賀次第. 39: 大外記師光記, 資季卿記, 荒凉記, 忠高卿記. 40: 冷泉公相公記, 勝延法眼記 : 東寺大行事, 後中記 : 小路中納言資頼卿記葉室. 41: 中光記, 師兼記, 陽龍記. 42: 大宮司長則記, 口筆 : 實經, 顕朝卿記, 鴨御幸記. 43: 寳治二年記, 深心院關白記, 藤公親記, 照念院関白兼平公記. 44: 頼親記, 亀山殿行幸記 : 雅言卿記, 兼基公記. 45: 大嘗會御禊節下次第, 建治三年丁丑日記 : 三善康有, 建治四年正月廿一日 : 徳大寺大相國公孝記, 冬定卿記, 左大史小槻兼文記|内容: 46: 經任卿記, 前豊前守藤憲説記, 實兼公記. 47: 継塵記抄出. 48: 管見記, 公衡公記, 大外記師顕記, 大外記中原師淳記. 49: 真光院禪助僧正記, 吉田内府卿記. 50: 定清記, 叅議雅俊卿記, 太政大臣(公守公)御上表雜事, 仙洞御灌頂日記, 正安二年八月十一日於仙洞被始行熾盛光法, 正安三年御譲位記. 51: 實躬卿記. 52: 公茂公記, 冬平公記, 隆長卿記. 53: 忠教公記, 官記, 正三位長基卿記, 北面秀長記, 大外記中原師右記. 54: 文保元年, 日野中納言資朝卿記, 洞院大納言公敏卿記. 55: 隆蔭卿記, 文保三年記, 尹大納言師賢卿記, 革命記, 立倚子記, 萬里小路中納言藤藤房卿記|内容: 56: 資名卿記, 公秀公記, 一條家記装束抄出, 頼定卿記. 63: 松亞記, 日野大納言時光卿記, 後八條内府實継公記. 74: 成恩寺関白記. 78: 山科家礼記. 82: 諒闇記 : 後成恩寺殿, 宗典僧正記, 綱光公記, 贈従二位宗賢卿記, 義政公記. 84: 長禄二年戊寅正月, 見聞雜記. 87: 言國卿記. 88: 長興宿祢記, 元長卿記, 兼顕卿記, 小槻晴冨記|28末の原奥書に「右山丞記依 仰挍合書冩/享和二年四月 日撿挍保己一」とあり|50「正安二年八月十一日於仙洞被始行熾盛光法」末の原奥書に「文化十五年春二月以南山法曼院藏夲書冩之 撿挍保己一」とあり|横刷毛目表紙を使用|朱点, 朱引, 朱墨筆書き入れあり|付箋あり|蔵書印主信濃須坂藩主堀直格の命によって編集された古記録|他の原本は関東大震災により焼失|極札に「桂壽」(6), 「尚信」(53)との極書, 「武清」(44, 53), 「永海」(51), 「了伴」(52), 「了甫」(74), 「定時」(84, 88)との極印あり|印記: 「花廼家文庫」, 「墨阪十一代主寫藏記」(堀直格(1806-1880)), 「東京大學法理文學部書庫所藏」, 「閲覧室用 FOR USE IN THE READING ROOM」|虫損あり</t>
+          <t>写本|表紙の書名: 如法愛染|内題下に「付小野大次苐修之」とあり|本奥書に「延慶二年夘月十日於仁和寺真光院書写了 金剛佛子印法 生年卅二」とあり|奥書に「嘉暦二年正月廿二日全写了 禅喜 生年卅一」とあり|巻子本|小野流|淡墨界の料紙を使用(界匡廓: 23.8×2.2cm)|巻頭下部の貼紙に「嘉暦二年巨今五百八十二年鎌倉時代四一ノ六九七号」とあり|破損, 虫損あり (裏打ち補修あり)</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -2158,12 +2158,12 @@
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/9f3a126c-84bb-8f96-2916-b65ace30a616.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/e321350d-483d-6e38-81a2-a637b8f798fb.json</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>9f3a126c-84bb-8f96-2916-b65ace30a616</t>
+          <t>e321350d-483d-6e38-81a2-a637b8f798fb</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -2173,7 +2173,7 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/9f3a126c-84bb-8f96-2916-b65ace30a616</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/e321350d-483d-6e38-81a2-a637b8f798fb</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
@@ -2183,12 +2183,12 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/fc4844ae32ad2dd582e3570965cb142f5f370f74.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/355285a0ec0b1cc8f12ae2c98e5215bdc9477998.jpg</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296228</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296231</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -2211,7 +2211,7 @@
       <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/9f3a126c-84bb-8f96-2916-b65ace30a616/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/e321350d-483d-6e38-81a2-a637b8f798fb/manifest</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr"/>
@@ -2219,40 +2219,40 @@
       <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="inlineStr"/>
       <c r="AH14" t="n">
-        <v>70</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [29]</t>
+          <t>三摩耶戒作法 : 東寺</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>A00:6257</t>
+          <t>A00:6266</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>レキダイ ザンケツ ニッキ</t>
+          <t>サンマヤカイ サホウ : トウジ</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>黒川 春村</t>
+          <t>聖快</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>[書写者不明]</t>
+          <t>道快 [自筆]</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>[安政5 (1858)]</t>
+          <t>康暦元 [1379] 奥書</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2264,7 +2264,7 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>写本|責任表示及び書写年は『日本古典籍総合目録データベース』による|内容: 6: 光明院御記, 後光嚴院御記, 後小松院宸記, 天聴集. 28: 参議藤定長卿記 : 稱山丞記. 37: 定高卿記, 晴御会部類記, 家光卿御記, 權中納言平範輔卿記. 38: 左大史小槻季継記, 後堀川安貞二年放生會(実基公記), 石清水八幡宮, 弁官拝賀次第. 39: 大外記師光記, 資季卿記, 荒凉記, 忠高卿記. 40: 冷泉公相公記, 勝延法眼記 : 東寺大行事, 後中記 : 小路中納言資頼卿記葉室. 41: 中光記, 師兼記, 陽龍記. 42: 大宮司長則記, 口筆 : 實經, 顕朝卿記, 鴨御幸記. 43: 寳治二年記, 深心院關白記, 藤公親記, 照念院関白兼平公記. 44: 頼親記, 亀山殿行幸記 : 雅言卿記, 兼基公記. 45: 大嘗會御禊節下次第, 建治三年丁丑日記 : 三善康有, 建治四年正月廿一日 : 徳大寺大相國公孝記, 冬定卿記, 左大史小槻兼文記|内容: 46: 經任卿記, 前豊前守藤憲説記, 實兼公記. 47: 継塵記抄出. 48: 管見記, 公衡公記, 大外記師顕記, 大外記中原師淳記. 49: 真光院禪助僧正記, 吉田内府卿記. 50: 定清記, 叅議雅俊卿記, 太政大臣(公守公)御上表雜事, 仙洞御灌頂日記, 正安二年八月十一日於仙洞被始行熾盛光法, 正安三年御譲位記. 51: 實躬卿記. 52: 公茂公記, 冬平公記, 隆長卿記. 53: 忠教公記, 官記, 正三位長基卿記, 北面秀長記, 大外記中原師右記. 54: 文保元年, 日野中納言資朝卿記, 洞院大納言公敏卿記. 55: 隆蔭卿記, 文保三年記, 尹大納言師賢卿記, 革命記, 立倚子記, 萬里小路中納言藤藤房卿記|内容: 56: 資名卿記, 公秀公記, 一條家記装束抄出, 頼定卿記. 63: 松亞記, 日野大納言時光卿記, 後八條内府實継公記. 74: 成恩寺関白記. 78: 山科家礼記. 82: 諒闇記 : 後成恩寺殿, 宗典僧正記, 綱光公記, 贈従二位宗賢卿記, 義政公記. 84: 長禄二年戊寅正月, 見聞雜記. 87: 言國卿記. 88: 長興宿祢記, 元長卿記, 兼顕卿記, 小槻晴冨記|28末の原奥書に「右山丞記依 仰挍合書冩/享和二年四月 日撿挍保己一」とあり|50「正安二年八月十一日於仙洞被始行熾盛光法」末の原奥書に「文化十五年春二月以南山法曼院藏夲書冩之 撿挍保己一」とあり|横刷毛目表紙を使用|朱点, 朱引, 朱墨筆書き入れあり|付箋あり|蔵書印主信濃須坂藩主堀直格の命によって編集された古記録|他の原本は関東大震災により焼失|極札に「桂壽」(6), 「尚信」(53)との極書, 「武清」(44, 53), 「永海」(51), 「了伴」(52), 「了甫」(74), 「定時」(84, 88)との極印あり|印記: 「花廼家文庫」, 「墨阪十一代主寫藏記」(堀直格(1806-1880)), 「東京大學法理文學部書庫所藏」, 「閲覧室用 FOR USE IN THE READING ROOM」|虫損あり</t>
+          <t>写本|書名は表紙による|本奥書に「康和元年十月廿日午時書了 深禅夲(第三轉)」, 「以小野僧正御夲理趣房書御夲也(初轉)」, 「承暦四年十一月十二日給預又書冩并傳受了 峯大阿闍梨御房事也(第二轉)」とあり|奥書に「康暦元年八月十二日於地藏院以平等坊永嚴自筆夲書冩之訖 東寺沙門道快」, 「同十四日於同院以或夲重挍合入落字注異説削謬詞尤可秘藏而已」とあり|表紙の貼紙に「康暦元年八月十二日於地藏院以平等坊永嚴自筆本書写之訖 東寺沙門道快 南北類」とある|巻子本|朱筆書き入れあり|淡墨界の料紙を使用(界匡廓: 19.5×2.0cm)|印記: 「僧正弘基」|破損, 虫損あり</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -2280,12 +2280,12 @@
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/7cdebe3a-8fb4-14b4-7ddb-3f92f3be9668.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/2b2562eb-7577-32f6-4c99-462a84e0647c.json</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>7cdebe3a-8fb4-14b4-7ddb-3f92f3be9668</t>
+          <t>2b2562eb-7577-32f6-4c99-462a84e0647c</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -2295,7 +2295,7 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/7cdebe3a-8fb4-14b4-7ddb-3f92f3be9668</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/2b2562eb-7577-32f6-4c99-462a84e0647c</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
@@ -2305,12 +2305,12 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/08f5648a7b5512a896986520a6449d3620439071.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/60a9be2785b442f57f54089c594f63b8df5ae1f4.jpg</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296229</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296232</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
@@ -2333,7 +2333,7 @@
       <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/7cdebe3a-8fb4-14b4-7ddb-3f92f3be9668/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/2b2562eb-7577-32f6-4c99-462a84e0647c/manifest</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr"/>
@@ -2341,52 +2341,48 @@
       <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="inlineStr"/>
       <c r="AH15" t="n">
-        <v>70</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>普賢延命</t>
+          <t>騁懐帖 2巻 [1]</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>A00:6264</t>
+          <t>A00:6379</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>フゲン エンメイ</t>
+          <t>テイカイジョウ</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>興然</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>長円 [写]</t>
-        </is>
-      </c>
+          <t>芳賀矢一[ほか自筆] ; 松本百藏 [集]</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>嘉禎2 [1236] 奥書</t>
+          <t>[明治-昭和年間]</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>写本|内題下に「師 理教」, 「嘉禎二年奥書アリ 長円書」とあり|巻末に「越前闍梨浄与口傳 興然夲」とあり|奥書に「嘉禎二年四月六月奉傳受空達御房ノ長円」とあり|裏に「正和元年壬子八月廿九日於成身院奉伝受之了」とあり|巻子本|送り仮名, 傍訓あり|虫損あり (裏打ち補修あり)</t>
+          <t>写本|書名及び巻冊次は題簽による|跋末に「松夲生名ハ百藏東京帝國大學ノ使丁タリ職ヲ山上會議所ニ奉スルコト四十有餘年 ... 頃来マタ諸賢ノ揮毫ヲ乞上名ケテ騁懐帖トイフ ... 帖成リテ予ニ其由来ヲ記セシコトヲ求ム乃チ之ヲ録シテ以テ跋後トス 昭和二年三月 辻善之助識」とあり|折本|書画帖|彩色あり|名録2冊(大和綴)を付す|落款朱印: 「長成」(坪井九馬三), 「圭卿」(市村瓚次郎), 「簣山」(鹽谷時敏), 「維亭」(塚本靖), 「土肥慶藏」, 「忠太」(伊東忠太), 「萬」(和田万吉), 「芳溪」(呉秀三), 「前田慧雲」, 「大澤謙二」, 「南條文雄」, 「有坂氏」(有坂鉊藏), 「博」, 「石亭」(林博太郎), 「長與又郎」, 「宇野哲人」, ほかあり</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2402,12 +2398,12 @@
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/e57fef06-5cfd-a602-6a89-f4d7d4360e87.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/bfdc576b-6ce2-9274-914e-8cc9c52c04de.json</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>e57fef06-5cfd-a602-6a89-f4d7d4360e87</t>
+          <t>bfdc576b-6ce2-9274-914e-8cc9c52c04de</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -2417,7 +2413,7 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/e57fef06-5cfd-a602-6a89-f4d7d4360e87</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/bfdc576b-6ce2-9274-914e-8cc9c52c04de</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
@@ -2427,12 +2423,12 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/eec20da7736c221a3c86321abead9d8d9429dceb.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/4061afb959aba92577bf3357712e3556cd07cf8e.jpg</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296230</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296233</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
@@ -2455,7 +2451,7 @@
       <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/e57fef06-5cfd-a602-6a89-f4d7d4360e87/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/bfdc576b-6ce2-9274-914e-8cc9c52c04de/manifest</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr"/>
@@ -2463,52 +2459,48 @@
       <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="inlineStr"/>
       <c r="AH16" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>如法愛染王</t>
+          <t>騁懐帖 2巻 [2]</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>A00:6265</t>
+          <t>A00:6379</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ニョホウ アイゼンオウ</t>
+          <t>テイカイジョウ</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>仁海</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>禅喜 [写]</t>
-        </is>
-      </c>
+          <t>芳賀矢一[ほか自筆] ; 松本百藏 [集]</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>嘉暦2 [1327] 奥書</t>
+          <t>[明治-昭和年間]</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>写本|表紙の書名: 如法愛染|内題下に「付小野大次苐修之」とあり|本奥書に「延慶二年夘月十日於仁和寺真光院書写了 金剛佛子印法 生年卅二」とあり|奥書に「嘉暦二年正月廿二日全写了 禅喜 生年卅一」とあり|巻子本|小野流|淡墨界の料紙を使用(界匡廓: 23.8×2.2cm)|巻頭下部の貼紙に「嘉暦二年巨今五百八十二年鎌倉時代四一ノ六九七号」とあり|破損, 虫損あり (裏打ち補修あり)</t>
+          <t>写本|書名及び巻冊次は題簽による|跋末に「松夲生名ハ百藏東京帝國大學ノ使丁タリ職ヲ山上會議所ニ奉スルコト四十有餘年 ... 頃来マタ諸賢ノ揮毫ヲ乞上名ケテ騁懐帖トイフ ... 帖成リテ予ニ其由来ヲ記セシコトヲ求ム乃チ之ヲ録シテ以テ跋後トス 昭和二年三月 辻善之助識」とあり|折本|書画帖|彩色あり|名録2冊(大和綴)を付す|落款朱印: 「長成」(坪井九馬三), 「圭卿」(市村瓚次郎), 「簣山」(鹽谷時敏), 「維亭」(塚本靖), 「土肥慶藏」, 「忠太」(伊東忠太), 「萬」(和田万吉), 「芳溪」(呉秀三), 「前田慧雲」, 「大澤謙二」, 「南條文雄」, 「有坂氏」(有坂鉊藏), 「博」, 「石亭」(林博太郎), 「長與又郎」, 「宇野哲人」, ほかあり</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2524,12 +2516,12 @@
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/e321350d-483d-6e38-81a2-a637b8f798fb.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/6a4c18fb-90e9-6d15-1234-9cadcc683544.json</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>e321350d-483d-6e38-81a2-a637b8f798fb</t>
+          <t>6a4c18fb-90e9-6d15-1234-9cadcc683544</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -2539,7 +2531,7 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/e321350d-483d-6e38-81a2-a637b8f798fb</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/6a4c18fb-90e9-6d15-1234-9cadcc683544</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
@@ -2549,12 +2541,12 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/355285a0ec0b1cc8f12ae2c98e5215bdc9477998.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/f705bcd1873bb88e3f1edef2b79dcc86dc2c417b.jpg</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296231</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296234</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
@@ -2577,7 +2569,7 @@
       <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/e321350d-483d-6e38-81a2-a637b8f798fb/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/6a4c18fb-90e9-6d15-1234-9cadcc683544/manifest</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr"/>
@@ -2585,40 +2577,36 @@
       <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="inlineStr"/>
       <c r="AH17" t="n">
-        <v>7</v>
+        <v>27</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>三摩耶戒作法 : 東寺</t>
+          <t>清玩書巻</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>A00:6266</t>
+          <t>A00:6380</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>サンマヤカイ サホウ : トウジ</t>
+          <t>セイガン ショカン</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>聖快</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>道快 [自筆]</t>
-        </is>
-      </c>
+          <t>石黒忠悳[ほか自筆] ; [松本百藏収集]</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>康暦元 [1379] 奥書</t>
+          <t>[明治大正年間]</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2630,7 +2618,7 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>写本|書名は表紙による|本奥書に「康和元年十月廿日午時書了 深禅夲(第三轉)」, 「以小野僧正御夲理趣房書御夲也(初轉)」, 「承暦四年十一月十二日給預又書冩并傳受了 峯大阿闍梨御房事也(第二轉)」とあり|奥書に「康暦元年八月十二日於地藏院以平等坊永嚴自筆夲書冩之訖 東寺沙門道快」, 「同十四日於同院以或夲重挍合入落字注異説削謬詞尤可秘藏而已」とあり|表紙の貼紙に「康暦元年八月十二日於地藏院以平等坊永嚴自筆本書写之訖 東寺沙門道快 南北類」とある|巻子本|朱筆書き入れあり|淡墨界の料紙を使用(界匡廓: 19.5×2.0cm)|印記: 「僧正弘基」|破損, 虫損あり</t>
+          <t>写本|書名は題簽による|その他の筆者: 市村瓚次郎, 外山正一, 緒方正規, 村上専精, 佐藤進, 菊池大麓, 三宅秀, 箕作佳吉, 三上參次, 箕作元八|冒頭に井上哲の題辞「清玩」あり|巻末に萩野由之の識語あり|収集者は『理翰片影』&lt;BC06713253&gt;の跋による|巻子本|往来書簡貼付集|名録1冊(大和綴)を付す|落款朱印: 「文学博士」, 「井上喆」, 「井上哲印」(井上哲次郎), 「和葊」(萩野由之)</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2646,12 +2634,12 @@
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/2b2562eb-7577-32f6-4c99-462a84e0647c.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/ae3b180b-9cbe-6902-48c2-f0abfdf0a27e.json</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2b2562eb-7577-32f6-4c99-462a84e0647c</t>
+          <t>ae3b180b-9cbe-6902-48c2-f0abfdf0a27e</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -2661,7 +2649,7 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/2b2562eb-7577-32f6-4c99-462a84e0647c</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/ae3b180b-9cbe-6902-48c2-f0abfdf0a27e</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
@@ -2671,12 +2659,12 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/60a9be2785b442f57f54089c594f63b8df5ae1f4.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/e799186565cb40d919d91c02eef1308118771dd3.jpg</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296232</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296235</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
@@ -2699,7 +2687,7 @@
       <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/2b2562eb-7577-32f6-4c99-462a84e0647c/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/ae3b180b-9cbe-6902-48c2-f0abfdf0a27e/manifest</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr"/>
@@ -2707,52 +2695,48 @@
       <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="inlineStr"/>
       <c r="AH18" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>騁懐帖 2巻 [1]</t>
+          <t>聚珍書巻</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>A00:6379</t>
+          <t>A00:6381</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>テイカイジョウ</t>
+          <t>シュウチン ショカン</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>芳賀 矢一</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>芳賀矢一 [ほか自筆]</t>
-        </is>
-      </c>
+          <t>濱尾新 [ほか自筆] ; 松本百藏 [収集]</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>[明治-昭和年間]</t>
+          <t>[明治年間]</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
-          <t>写本|書名及び巻冊次は題簽による|跋末に「松夲生名ハ百藏東京帝國大學ノ使丁タリ職ヲ山上會議所ニ奉スルコト四十有餘年 ... 頃来マタ諸賢ノ揮毫ヲ乞上名ケテ騁懐帖トイフ ... 帖成リテ予ニ其由来ヲ記セシコトヲ求ム乃チ之ヲ録シテ以テ跋後トス 昭和二年三月 辻善之助識」とあり|折本|書画帖|彩色あり|名録2冊(大和綴)を付す|落款朱印: 「長成」(坪井九馬三), 「圭卿」(市村瓚次郎), 「簣山」(鹽谷時敏), 「維亭」(塚本靖), 「土肥慶藏」, 「忠太」(伊東忠太), 「萬」(和田万吉), 「芳溪」(呉秀三), 「前田慧雲」, 「大澤謙二」, 「南條文雄」, 「有坂氏」(有坂鉊藏), 「博」, 「石亭」(林博太郎), 「長與又郎」, 「宇野哲人」, ほかあり</t>
+          <t>写本|書名は題簽による|題辞に「聚珍 明治己酉夏八十三老人成斎題」とあり|巻末識語に「松本百蔵為東亰帝國大學厮養二十餘年毎掃故紙籠見有文字者輒収而弆之頃揀其署名氏者十餘紙装潢成卷皆名賢鉅公碩學鴻儒之筆也 ... 明治庚戌二月初夏 豊城陳人恒書時年七十又二」とあり|その他の筆者: 細川潤次郎, 渡邊洪基, 加藤弘之, 川田剛, 辻新次, 中村正直, 古市公威, 小中村清矩, 木村正辭, 島田重禮|巻子本|往来書簡貼付集|名録1冊(大和綴)を付す|落款朱印: 「晩香」, 「徳天」, 「星野恒印」, 「續古堂」, 「重野」, 「重埜士徳」, 「藤原安繹」</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2768,12 +2752,12 @@
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/bfdc576b-6ce2-9274-914e-8cc9c52c04de.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/4e78ded3-2829-990e-572b-4b5e029a69cc.json</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>bfdc576b-6ce2-9274-914e-8cc9c52c04de</t>
+          <t>4e78ded3-2829-990e-572b-4b5e029a69cc</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -2783,7 +2767,7 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/bfdc576b-6ce2-9274-914e-8cc9c52c04de</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/4e78ded3-2829-990e-572b-4b5e029a69cc</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
@@ -2793,12 +2777,12 @@
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/4061afb959aba92577bf3357712e3556cd07cf8e.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/fe6e0e801688014b204ebe9deee8085c19831bc3.jpg</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296233</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296236</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
@@ -2821,7 +2805,7 @@
       <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/bfdc576b-6ce2-9274-914e-8cc9c52c04de/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/4e78ded3-2829-990e-572b-4b5e029a69cc/manifest</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr"/>
@@ -2829,52 +2813,48 @@
       <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="inlineStr"/>
       <c r="AH19" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>騁懐帖 2巻 [2]</t>
+          <t>理翰片影</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>A00:6379</t>
+          <t>A00:6382</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>テイカイジョウ</t>
+          <t>リカン ヘンエイ</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>芳賀 矢一</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>芳賀矢一 [ほか自筆]</t>
-        </is>
-      </c>
+          <t>井上毅 [ほか自筆] ; 松本百藏 [蒐集]</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>[明治-昭和年間]</t>
+          <t>[明治大正年間]</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
-          <t>写本|書名及び巻冊次は題簽による|跋末に「松夲生名ハ百藏東京帝國大學ノ使丁タリ職ヲ山上會議所ニ奉スルコト四十有餘年 ... 頃来マタ諸賢ノ揮毫ヲ乞上名ケテ騁懐帖トイフ ... 帖成リテ予ニ其由来ヲ記セシコトヲ求ム乃チ之ヲ録シテ以テ跋後トス 昭和二年三月 辻善之助識」とあり|折本|書画帖|彩色あり|名録2冊(大和綴)を付す|落款朱印: 「長成」(坪井九馬三), 「圭卿」(市村瓚次郎), 「簣山」(鹽谷時敏), 「維亭」(塚本靖), 「土肥慶藏」, 「忠太」(伊東忠太), 「萬」(和田万吉), 「芳溪」(呉秀三), 「前田慧雲」, 「大澤謙二」, 「南條文雄」, 「有坂氏」(有坂鉊藏), 「博」, 「石亭」(林博太郎), 「長與又郎」, 「宇野哲人」, ほかあり</t>
+          <t>写本|書名は題簽による|敘に「松本百藏君我が東京帝國大學に縁故ある諸君の筆蹟を蒐集シ己ニ三卷をなす此卷収む事といわは故子爵井上毅先生をはじめとし神保小虎博士に至るまで十二君の消息なり ... 大正十四年春日三上参次(花押)」とあり|跋に「松本百藏奉職東京帝國大學勞使四十年夙昔不怠其所勤非尋常也大正十四年以古稀辤其軄以平生所収簡牘装潢之得四巻二帖納大學書庫 ... 大正十五年五月於東京帝國大學夲部象軒平野直文識」とあり|その他の筆者: 八代六郎, 垪和爲昌, 鶴田賢次, 長井長義, 久原躬弦, 藤澤利喜太郎, 小藤文次郎, 寺野精一, 青山胤通, 佐藤三吉, 神保小乕|巻子本|往来書簡貼付集|落款朱印: 「士可」, 「虚坣居士」, 「平野直文」</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2890,12 +2870,12 @@
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/6a4c18fb-90e9-6d15-1234-9cadcc683544.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/31b15e19-44d8-6c52-9780-873a7f1a2480.json</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>6a4c18fb-90e9-6d15-1234-9cadcc683544</t>
+          <t>31b15e19-44d8-6c52-9780-873a7f1a2480</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -2905,7 +2885,7 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/6a4c18fb-90e9-6d15-1234-9cadcc683544</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/31b15e19-44d8-6c52-9780-873a7f1a2480</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
@@ -2915,12 +2895,12 @@
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/f705bcd1873bb88e3f1edef2b79dcc86dc2c417b.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/c34f4eff76edef5a959de5048f588d40ac1cccac.jpg</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296234</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296237</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
@@ -2943,7 +2923,7 @@
       <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/6a4c18fb-90e9-6d15-1234-9cadcc683544/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/31b15e19-44d8-6c52-9780-873a7f1a2480/manifest</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr"/>
@@ -2951,36 +2931,32 @@
       <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="inlineStr"/>
       <c r="AH20" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>清玩書巻</t>
+          <t>學海拾遺珠</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>A00:6380</t>
+          <t>A00:6383</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>セイガン ショカン</t>
+          <t>ガッカイ シュウイシュ</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>石黒 忠悳</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>石黒忠悳 [ほか自筆]</t>
-        </is>
-      </c>
+          <t>渡邊渡 [ほか自筆] ; 松本[百藏 集]</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
@@ -2996,7 +2972,7 @@
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
-          <t>写本|書名は題簽による|その他の筆者: 市村瓚次郎, 外山正一, 緒方正規, 村上専精, 佐藤進, 菊池大麓, 三宅秀, 箕作佳吉, 三上參次, 箕作元八|冒頭に井上哲の題辞「清玩」あり|巻末に萩野由之の識語あり|収集者は『理翰片影』&lt;BC06713253&gt;の跋による|巻子本|往来書簡貼付集|名録1冊(大和綴)を付す|落款朱印: 「文学博士」, 「井上喆」, 「井上哲印」(井上哲次郎), 「和葊」(萩野由之)</t>
+          <t>写本|書名は題簽による|題辞に「學海拾遺珠 大正十二年初夏 讀律書屋主人題」とあり|巻末識語に「東京帝國大學の地小丘有り丘上に會議所有り總長教授等會食聚議の處と為に松本君其の役たると久し親しく碩學大家に接し之を敬するを知る留意して敗紙中に諸家の手跡を索め嵗月を累収て十数家に及へは輙ち裝潢して卷を成す今や第三卷成り文を予に求む松本君孤影孑然會議所に起臥す伴侶は唯名家手簡と手栽の盆柎有るのみ ... 大正十二年二月十九日 隨軒學人」とあり|その他の筆者: 和田垣謙三, 川瀬善太郎, 高松豊吉, 田中義成, 永井久一郎, 中村恭平, 山川健次郎, 松井直吉, 松村任三, 古在由直, 寺尾寿, 櫻井錠二, 清水彦五郎|巻子本|往来書簡貼付集|名録1冊(大和綴)を付す|落款朱印: 「讀經堂主人號随軒」, 「服部宇之吉印記」, 「直文」(平野直文)</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -3012,12 +2988,12 @@
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/ae3b180b-9cbe-6902-48c2-f0abfdf0a27e.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/9639e5f3-92bd-7423-1bf1-08c4dc087bdf.json</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>ae3b180b-9cbe-6902-48c2-f0abfdf0a27e</t>
+          <t>9639e5f3-92bd-7423-1bf1-08c4dc087bdf</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -3027,7 +3003,7 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/ae3b180b-9cbe-6902-48c2-f0abfdf0a27e</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/9639e5f3-92bd-7423-1bf1-08c4dc087bdf</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
@@ -3037,12 +3013,12 @@
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/e799186565cb40d919d91c02eef1308118771dd3.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/b210fc9854d945b959acd96b0e4fa57d3578ea07.jpg</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296235</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296238</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
@@ -3065,7 +3041,7 @@
       <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/ae3b180b-9cbe-6902-48c2-f0abfdf0a27e/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/9639e5f3-92bd-7423-1bf1-08c4dc087bdf/manifest</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr"/>
@@ -3073,40 +3049,40 @@
       <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="inlineStr"/>
       <c r="AH21" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>聚珍書巻</t>
+          <t>御成敗式目</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>A00:6381</t>
+          <t>A00:6456</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>シュウチン ショカン</t>
+          <t>ゴセイバイ シキモク</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>浜尾 新</t>
+          <t>平泰時 [ほか定]</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>濱尾新 [ほか自筆]</t>
+          <t>[書写者不明]</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
-          <t>[明治年間]</t>
+          <t>康永2 [1343] 奥書</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -3118,7 +3094,7 @@
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
-          <t>写本|書名は題簽による|題辞に「聚珍 明治己酉夏八十三老人成斎題」とあり|巻末識語に「松本百蔵為東亰帝國大學厮養二十餘年毎掃故紙籠見有文字者輒収而弆之頃揀其署名氏者十餘紙装潢成卷皆名賢鉅公碩學鴻儒之筆也 ... 明治庚戌二月初夏 豊城陳人恒書時年七十又二」とあり|その他の筆者: 細川潤次郎, 渡邊洪基, 加藤弘之, 川田剛, 辻新次, 中村正直, 古市公威, 小中村清矩, 木村正辭, 島田重禮|巻子本|往来書簡貼付集|名録1冊(大和綴)を付す|落款朱印: 「晩香」, 「徳天」, 「星野恒印」, 「續古堂」, 「重野」, 「重埜士徳」, 「藤原安繹」</t>
+          <t>写本|本文末に「貞永元年七月十日 沙弥浄圎/相模大掾藤原業時/玄蕃允三善康連/左衞門少尉藤原朝臣基綱/沙弥行然/散位三善朝臣倫重/加賀守三善朝臣康俊/沙弥行西/前出羽守藤原朝臣家長/前駿河守平義村/前攝津守中原師貟/武蔵守平泰時/相模守平時房」との連署名あり|巻末に「嘉禎三年八月十七日評定之」, 「延應二年五月廾五日評定之」, 「暦仁元年十二月十九日評定之」, 「延應元年九月廾日評定之改嫁事」, 「仁治三十二五評定」, 「嘉禎四年九月二十七日評定之」, 「仁治四二廾五追評定之」, 「延應二年五月廾五日評定之」, 「延應二四廾五評」など追加補抄及び「御式目事」(貞永元八月八日 武蔵守御判/するかの守殿)書簡抄を付す|奥書に「康永二年三月三日於高辻冨小路宿所書冩之訖」とあり|毎葉7行17字注文双行|本文は真字, 送り仮名, 返り点を施し|金砂子散し花菱繋ぎの見返し, 押界を施した楮紙打紙を使用|朱墨筆書き入れあり|軸物(打紙継ぎ)|桐箱入り|印記: 「本立堂記」|汚損, 虫損あり</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -3134,12 +3110,12 @@
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/4e78ded3-2829-990e-572b-4b5e029a69cc.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/1dc60eb8-0dd2-1716-521a-8b436e899759.json</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>4e78ded3-2829-990e-572b-4b5e029a69cc</t>
+          <t>1dc60eb8-0dd2-1716-521a-8b436e899759</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -3149,7 +3125,7 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/4e78ded3-2829-990e-572b-4b5e029a69cc</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/1dc60eb8-0dd2-1716-521a-8b436e899759</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
@@ -3159,12 +3135,12 @@
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/fe6e0e801688014b204ebe9deee8085c19831bc3.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/8182eba23e72331505a8074acdfe6b5481d358fd.jpg</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296236</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296239</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
@@ -3187,7 +3163,7 @@
       <c r="AB22" t="inlineStr"/>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/4e78ded3-2829-990e-572b-4b5e029a69cc/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/1dc60eb8-0dd2-1716-521a-8b436e899759/manifest</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr"/>
@@ -3195,52 +3171,52 @@
       <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="inlineStr"/>
       <c r="AH22" t="n">
-        <v>27</v>
+        <v>45</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>理翰片影</t>
+          <t>辨證配劑醫燈 3巻 [1]</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>A00:6382</t>
+          <t>A00:6517</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>リカン ヘンエイ</t>
+          <t>ベンショウ ハイザイ イトウ</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>井上 毅</t>
+          <t>曲直瀬 道三</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>井上毅 [ほか自筆]</t>
+          <t>道三 [自筆]</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
-          <t>[明治大正年間]</t>
+          <t>元亀2 [1571] 大尾</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
-          <t>写本|書名は題簽による|敘に「松本百藏君我が東京帝國大學に縁故ある諸君の筆蹟を蒐集シ己ニ三卷をなす此卷収む事といわは故子爵井上毅先生をはじめとし神保小虎博士に至るまで十二君の消息なり ... 大正十四年春日三上参次(花押)」とあり|跋に「松本百藏奉職東京帝國大學勞使四十年夙昔不怠其所勤非尋常也大正十四年以古稀辤其軄以平生所収簡牘装潢之得四巻二帖納大學書庫 ... 大正十五年五月於東京帝國大學夲部象軒平野直文識」とあり|その他の筆者: 八代六郎, 垪和爲昌, 鶴田賢次, 長井長義, 久原躬弦, 藤澤利喜太郎, 小藤文次郎, 寺野精一, 青山胤通, 佐藤三吉, 神保小乕|巻子本|往来書簡貼付集|落款朱印: 「士可」, 「虚坣居士」, 「平野直文」</t>
+          <t>写本|巻之2の巻頭書名: 辨證配剤醫燈|大尾に「治病用藥之時欲使侄姪孫一覧如指掌而已/旹元亀第二辛未年冬日南至六十五齢老眼寒窓/日東洛下雖知苦斎盍静翁 道三」とあり|巻末識語に「辨證配劑醫燈全三册壹帙一溪叟道三所親筆也不可忽諸故附一語於後耳」とあり|箱に「和氣道三自書寫配劑醫燈三卷林道春跋之櫻井老人苐一家藏子孫永寶之 葛辰識」との墨書あり|毎半面11行|朱点, 朱引, 朱藍筆書き入れあり|付箋あり|箱入り|印記: 「石堂」, 「昃印」|虫損, 汚損あり</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -3256,12 +3232,12 @@
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/31b15e19-44d8-6c52-9780-873a7f1a2480.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/ede81088-3a4b-221d-711c-889d446e8d7e.json</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>31b15e19-44d8-6c52-9780-873a7f1a2480</t>
+          <t>ede81088-3a4b-221d-711c-889d446e8d7e</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -3271,7 +3247,7 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/31b15e19-44d8-6c52-9780-873a7f1a2480</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/ede81088-3a4b-221d-711c-889d446e8d7e</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
@@ -3281,12 +3257,12 @@
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/c34f4eff76edef5a959de5048f588d40ac1cccac.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/1089675f22f8a9e5e8d856bf42c0b3fa7e2b5168.jpg</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296237</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296240</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
@@ -3309,7 +3285,7 @@
       <c r="AB23" t="inlineStr"/>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/31b15e19-44d8-6c52-9780-873a7f1a2480/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/ede81088-3a4b-221d-711c-889d446e8d7e/manifest</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr"/>
@@ -3317,52 +3293,52 @@
       <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="inlineStr"/>
       <c r="AH23" t="n">
-        <v>21</v>
+        <v>61</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>學海拾遺珠</t>
+          <t>辨證配劑醫燈 3巻 [2]</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>A00:6383</t>
+          <t>A00:6517</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ガッカイ シュウイシュ</t>
+          <t>ベンショウ ハイザイ イトウ</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>渡辺 渡</t>
+          <t>曲直瀬 道三</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>渡邊渡 [ほか自筆]</t>
+          <t>道三 [自筆]</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
-          <t>[明治大正年間]</t>
+          <t>元亀2 [1571] 大尾</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
-          <t>写本|書名は題簽による|題辞に「學海拾遺珠 大正十二年初夏 讀律書屋主人題」とあり|巻末識語に「東京帝國大學の地小丘有り丘上に會議所有り總長教授等會食聚議の處と為に松本君其の役たると久し親しく碩學大家に接し之を敬するを知る留意して敗紙中に諸家の手跡を索め嵗月を累収て十数家に及へは輙ち裝潢して卷を成す今や第三卷成り文を予に求む松本君孤影孑然會議所に起臥す伴侶は唯名家手簡と手栽の盆柎有るのみ ... 大正十二年二月十九日 隨軒學人」とあり|その他の筆者: 和田垣謙三, 川瀬善太郎, 高松豊吉, 田中義成, 永井久一郎, 中村恭平, 山川健次郎, 松井直吉, 松村任三, 古在由直, 寺尾寿, 櫻井錠二, 清水彦五郎|巻子本|往来書簡貼付集|名録1冊(大和綴)を付す|落款朱印: 「讀經堂主人號随軒」, 「服部宇之吉印記」, 「直文」(平野直文)</t>
+          <t>写本|巻之2の巻頭書名: 辨證配剤醫燈|大尾に「治病用藥之時欲使侄姪孫一覧如指掌而已/旹元亀第二辛未年冬日南至六十五齢老眼寒窓/日東洛下雖知苦斎盍静翁 道三」とあり|巻末識語に「辨證配劑醫燈全三册壹帙一溪叟道三所親筆也不可忽諸故附一語於後耳」とあり|箱に「和氣道三自書寫配劑醫燈三卷林道春跋之櫻井老人苐一家藏子孫永寶之 葛辰識」との墨書あり|毎半面11行|朱点, 朱引, 朱藍筆書き入れあり|付箋あり|箱入り|印記: 「石堂」, 「昃印」|虫損, 汚損あり</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -3378,12 +3354,12 @@
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/9639e5f3-92bd-7423-1bf1-08c4dc087bdf.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/93511b52-3de6-4102-980b-24d00b6c5851.json</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>9639e5f3-92bd-7423-1bf1-08c4dc087bdf</t>
+          <t>93511b52-3de6-4102-980b-24d00b6c5851</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -3393,7 +3369,7 @@
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/9639e5f3-92bd-7423-1bf1-08c4dc087bdf</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/93511b52-3de6-4102-980b-24d00b6c5851</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
@@ -3403,12 +3379,12 @@
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/b210fc9854d945b959acd96b0e4fa57d3578ea07.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/a82992bab1da44c99dc71e9ac8ef6ff3d626dc4d.jpg</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296238</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296241</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
@@ -3431,7 +3407,7 @@
       <c r="AB24" t="inlineStr"/>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/9639e5f3-92bd-7423-1bf1-08c4dc087bdf/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/93511b52-3de6-4102-980b-24d00b6c5851/manifest</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr"/>
@@ -3439,52 +3415,52 @@
       <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="inlineStr"/>
       <c r="AH24" t="n">
-        <v>27</v>
+        <v>52</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>御成敗式目</t>
+          <t>辨證配劑醫燈 3巻 [3]</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>A00:6456</t>
+          <t>A00:6517</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ゴセイバイ シキモク</t>
+          <t>ベンショウ ハイザイ イトウ</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>平泰時 [ほか定]</t>
+          <t>曲直瀬 道三</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>[書写者不明]</t>
+          <t>道三 [自筆]</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
-          <t>康永2 [1343] 奥書</t>
+          <t>元亀2 [1571] 大尾</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
-          <t>写本|本文末に「貞永元年七月十日 沙弥浄圎/相模大掾藤原業時/玄蕃允三善康連/左衞門少尉藤原朝臣基綱/沙弥行然/散位三善朝臣倫重/加賀守三善朝臣康俊/沙弥行西/前出羽守藤原朝臣家長/前駿河守平義村/前攝津守中原師貟/武蔵守平泰時/相模守平時房」との連署名あり|巻末に「嘉禎三年八月十七日評定之」, 「延應二年五月廾五日評定之」, 「暦仁元年十二月十九日評定之」, 「延應元年九月廾日評定之改嫁事」, 「仁治三十二五評定」, 「嘉禎四年九月二十七日評定之」, 「仁治四二廾五追評定之」, 「延應二年五月廾五日評定之」, 「延應二四廾五評」など追加補抄及び「御式目事」(貞永元八月八日 武蔵守御判/するかの守殿)書簡抄を付す|奥書に「康永二年三月三日於高辻冨小路宿所書冩之訖」とあり|毎葉7行17字注文双行|本文は真字, 送り仮名, 返り点を施し|金砂子散し花菱繋ぎの見返し, 押界を施した楮紙打紙を使用|朱墨筆書き入れあり|軸物(打紙継ぎ)|桐箱入り|印記: 「本立堂記」|汚損, 虫損あり</t>
+          <t>写本|巻之2の巻頭書名: 辨證配剤醫燈|大尾に「治病用藥之時欲使侄姪孫一覧如指掌而已/旹元亀第二辛未年冬日南至六十五齢老眼寒窓/日東洛下雖知苦斎盍静翁 道三」とあり|巻末識語に「辨證配劑醫燈全三册壹帙一溪叟道三所親筆也不可忽諸故附一語於後耳」とあり|箱に「和氣道三自書寫配劑醫燈三卷林道春跋之櫻井老人苐一家藏子孫永寶之 葛辰識」との墨書あり|毎半面11行|朱点, 朱引, 朱藍筆書き入れあり|付箋あり|箱入り|印記: 「石堂」, 「昃印」|虫損, 汚損あり</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -3500,12 +3476,12 @@
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/1dc60eb8-0dd2-1716-521a-8b436e899759.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/a23dae2e-701a-8d7c-1359-fe786c2e2cdd.json</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>1dc60eb8-0dd2-1716-521a-8b436e899759</t>
+          <t>a23dae2e-701a-8d7c-1359-fe786c2e2cdd</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -3515,7 +3491,7 @@
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/1dc60eb8-0dd2-1716-521a-8b436e899759</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/a23dae2e-701a-8d7c-1359-fe786c2e2cdd</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
@@ -3525,12 +3501,12 @@
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/8182eba23e72331505a8074acdfe6b5481d358fd.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/21b02bac7c065db97c214037acfa4b232d2ddc89.jpg</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296239</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296242</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
@@ -3553,7 +3529,7 @@
       <c r="AB25" t="inlineStr"/>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/1dc60eb8-0dd2-1716-521a-8b436e899759/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/a23dae2e-701a-8d7c-1359-fe786c2e2cdd/manifest</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr"/>
@@ -3561,52 +3537,52 @@
       <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="inlineStr"/>
       <c r="AH25" t="n">
-        <v>45</v>
+        <v>63</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>辨證配劑醫燈 3巻 [1]</t>
+          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [19]</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>A00:6517</t>
+          <t>A00:6257</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ベンショウ ハイザイ イトウ</t>
+          <t>レキダイ ザンケツ ニッキ</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>曲直瀬 道三</t>
+          <t>黒川 春村</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>道三 [自筆]</t>
+          <t>[書写者不明]</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
-          <t>元亀2 [1571] 大尾</t>
+          <t>[安政5 (1858)]</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
-          <t>写本|巻之2の巻頭書名: 辨證配剤醫燈|大尾に「治病用藥之時欲使侄姪孫一覧如指掌而已/旹元亀第二辛未年冬日南至六十五齢老眼寒窓/日東洛下雖知苦斎盍静翁 道三」とあり|巻末識語に「辨證配劑醫燈全三册壹帙一溪叟道三所親筆也不可忽諸故附一語於後耳」とあり|箱に「和氣道三自書寫配劑醫燈三卷林道春跋之櫻井老人苐一家藏子孫永寶之 葛辰識」との墨書あり|毎半面11行|朱点, 朱引, 朱藍筆書き入れあり|付箋あり|箱入り|印記: 「石堂」, 「昃印」|虫損, 汚損あり</t>
+          <t>写本|責任表示及び書写年は『日本古典籍総合目録データベース』による|内容: 6: 光明院御記, 後光嚴院御記, 後小松院宸記, 天聴集. 28: 参議藤定長卿記 : 稱山丞記. 37: 定高卿記, 晴御会部類記, 家光卿御記, 權中納言平範輔卿記. 38: 左大史小槻季継記, 後堀川安貞二年放生會(実基公記), 石清水八幡宮, 弁官拝賀次第. 39: 大外記師光記, 資季卿記, 荒凉記, 忠高卿記. 40: 冷泉公相公記, 勝延法眼記 : 東寺大行事, 後中記 : 小路中納言資頼卿記葉室. 41: 中光記, 師兼記, 陽龍記. 42: 大宮司長則記, 口筆 : 實經, 顕朝卿記, 鴨御幸記. 43: 寳治二年記, 深心院關白記, 藤公親記, 照念院関白兼平公記. 44: 頼親記, 亀山殿行幸記 : 雅言卿記, 兼基公記. 45: 大嘗會御禊節下次第, 建治三年丁丑日記 : 三善康有, 建治四年正月廿一日 : 徳大寺大相國公孝記, 冬定卿記, 左大史小槻兼文記|内容: 46: 經任卿記, 前豊前守藤憲説記, 實兼公記. 47: 継塵記抄出. 48: 管見記, 公衡公記, 大外記師顕記, 大外記中原師淳記. 49: 真光院禪助僧正記, 吉田内府卿記. 50: 定清記, 叅議雅俊卿記, 太政大臣(公守公)御上表雜事, 仙洞御灌頂日記, 正安二年八月十一日於仙洞被始行熾盛光法, 正安三年御譲位記. 51: 實躬卿記. 52: 公茂公記, 冬平公記, 隆長卿記. 53: 忠教公記, 官記, 正三位長基卿記, 北面秀長記, 大外記中原師右記. 54: 文保元年, 日野中納言資朝卿記, 洞院大納言公敏卿記. 55: 隆蔭卿記, 文保三年記, 尹大納言師賢卿記, 革命記, 立倚子記, 萬里小路中納言藤藤房卿記|内容: 56: 資名卿記, 公秀公記, 一條家記装束抄出, 頼定卿記. 63: 松亞記, 日野大納言時光卿記, 後八條内府實継公記. 74: 成恩寺関白記. 78: 山科家礼記. 82: 諒闇記 : 後成恩寺殿, 宗典僧正記, 綱光公記, 贈従二位宗賢卿記, 義政公記. 84: 長禄二年戊寅正月, 見聞雜記. 87: 言國卿記. 88: 長興宿祢記, 元長卿記, 兼顕卿記, 小槻晴冨記|28末の原奥書に「右山丞記依 仰挍合書冩/享和二年四月 日撿挍保己一」とあり|50「正安二年八月十一日於仙洞被始行熾盛光法」末の原奥書に「文化十五年春二月以南山法曼院藏夲書冩之 撿挍保己一」とあり|横刷毛目表紙を使用|朱点, 朱引, 朱墨筆書き入れあり|付箋あり|蔵書印主信濃須坂藩主堀直格の命によって編集された古記録|他の原本は関東大震災により焼失|極札に「桂壽」(6), 「尚信」(53)との極書, 「武清」(44, 53), 「永海」(51), 「了伴」(52), 「了甫」(74), 「定時」(84, 88)との極印あり|印記: 「花廼家文庫」, 「墨阪十一代主寫藏記」(堀直格(1806-1880)), 「東京大學法理文學部書庫所藏」, 「閲覧室用 FOR USE IN THE READING ROOM」|虫損あり</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -3622,12 +3598,12 @@
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/ede81088-3a4b-221d-711c-889d446e8d7e.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/1373f0d8-7cc0-4591-2c18-798fa20f483d.json</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>ede81088-3a4b-221d-711c-889d446e8d7e</t>
+          <t>1373f0d8-7cc0-4591-2c18-798fa20f483d</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -3637,7 +3613,7 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/ede81088-3a4b-221d-711c-889d446e8d7e</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/1373f0d8-7cc0-4591-2c18-798fa20f483d</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
@@ -3647,12 +3623,12 @@
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/1089675f22f8a9e5e8d856bf42c0b3fa7e2b5168.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/326ed2db044321d7b007462c9ac98badfd7f671a.jpg</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296240</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296219</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
@@ -3675,7 +3651,7 @@
       <c r="AB26" t="inlineStr"/>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/ede81088-3a4b-221d-711c-889d446e8d7e/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/1373f0d8-7cc0-4591-2c18-798fa20f483d/manifest</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr"/>
@@ -3683,52 +3659,52 @@
       <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="inlineStr"/>
       <c r="AH26" t="n">
-        <v>61</v>
+        <v>69</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>辨證配劑醫燈 3巻 [2]</t>
+          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [18]</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>A00:6517</t>
+          <t>A00:6257</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ベンショウ ハイザイ イトウ</t>
+          <t>レキダイ ザンケツ ニッキ</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>曲直瀬 道三</t>
+          <t>黒川 春村</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>道三 [自筆]</t>
+          <t>[書写者不明]</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
-          <t>元亀2 [1571] 大尾</t>
+          <t>[安政5 (1858)]</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
-          <t>写本|巻之2の巻頭書名: 辨證配剤醫燈|大尾に「治病用藥之時欲使侄姪孫一覧如指掌而已/旹元亀第二辛未年冬日南至六十五齢老眼寒窓/日東洛下雖知苦斎盍静翁 道三」とあり|巻末識語に「辨證配劑醫燈全三册壹帙一溪叟道三所親筆也不可忽諸故附一語於後耳」とあり|箱に「和氣道三自書寫配劑醫燈三卷林道春跋之櫻井老人苐一家藏子孫永寶之 葛辰識」との墨書あり|毎半面11行|朱点, 朱引, 朱藍筆書き入れあり|付箋あり|箱入り|印記: 「石堂」, 「昃印」|虫損, 汚損あり</t>
+          <t>写本|責任表示及び書写年は『日本古典籍総合目録データベース』による|内容: 6: 光明院御記, 後光嚴院御記, 後小松院宸記, 天聴集. 28: 参議藤定長卿記 : 稱山丞記. 37: 定高卿記, 晴御会部類記, 家光卿御記, 權中納言平範輔卿記. 38: 左大史小槻季継記, 後堀川安貞二年放生會(実基公記), 石清水八幡宮, 弁官拝賀次第. 39: 大外記師光記, 資季卿記, 荒凉記, 忠高卿記. 40: 冷泉公相公記, 勝延法眼記 : 東寺大行事, 後中記 : 小路中納言資頼卿記葉室. 41: 中光記, 師兼記, 陽龍記. 42: 大宮司長則記, 口筆 : 實經, 顕朝卿記, 鴨御幸記. 43: 寳治二年記, 深心院關白記, 藤公親記, 照念院関白兼平公記. 44: 頼親記, 亀山殿行幸記 : 雅言卿記, 兼基公記. 45: 大嘗會御禊節下次第, 建治三年丁丑日記 : 三善康有, 建治四年正月廿一日 : 徳大寺大相國公孝記, 冬定卿記, 左大史小槻兼文記|内容: 46: 經任卿記, 前豊前守藤憲説記, 實兼公記. 47: 継塵記抄出. 48: 管見記, 公衡公記, 大外記師顕記, 大外記中原師淳記. 49: 真光院禪助僧正記, 吉田内府卿記. 50: 定清記, 叅議雅俊卿記, 太政大臣(公守公)御上表雜事, 仙洞御灌頂日記, 正安二年八月十一日於仙洞被始行熾盛光法, 正安三年御譲位記. 51: 實躬卿記. 52: 公茂公記, 冬平公記, 隆長卿記. 53: 忠教公記, 官記, 正三位長基卿記, 北面秀長記, 大外記中原師右記. 54: 文保元年, 日野中納言資朝卿記, 洞院大納言公敏卿記. 55: 隆蔭卿記, 文保三年記, 尹大納言師賢卿記, 革命記, 立倚子記, 萬里小路中納言藤藤房卿記|内容: 56: 資名卿記, 公秀公記, 一條家記装束抄出, 頼定卿記. 63: 松亞記, 日野大納言時光卿記, 後八條内府實継公記. 74: 成恩寺関白記. 78: 山科家礼記. 82: 諒闇記 : 後成恩寺殿, 宗典僧正記, 綱光公記, 贈従二位宗賢卿記, 義政公記. 84: 長禄二年戊寅正月, 見聞雜記. 87: 言國卿記. 88: 長興宿祢記, 元長卿記, 兼顕卿記, 小槻晴冨記|28末の原奥書に「右山丞記依 仰挍合書冩/享和二年四月 日撿挍保己一」とあり|50「正安二年八月十一日於仙洞被始行熾盛光法」末の原奥書に「文化十五年春二月以南山法曼院藏夲書冩之 撿挍保己一」とあり|横刷毛目表紙を使用|朱点, 朱引, 朱墨筆書き入れあり|付箋あり|蔵書印主信濃須坂藩主堀直格の命によって編集された古記録|他の原本は関東大震災により焼失|極札に「桂壽」(6), 「尚信」(53)との極書, 「武清」(44, 53), 「永海」(51), 「了伴」(52), 「了甫」(74), 「定時」(84, 88)との極印あり|印記: 「花廼家文庫」, 「墨阪十一代主寫藏記」(堀直格(1806-1880)), 「東京大學法理文學部書庫所藏」, 「閲覧室用 FOR USE IN THE READING ROOM」|虫損あり</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -3744,12 +3720,12 @@
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/93511b52-3de6-4102-980b-24d00b6c5851.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/c69854e0-18e9-71b3-a7b1-22422a16688b.json</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>93511b52-3de6-4102-980b-24d00b6c5851</t>
+          <t>c69854e0-18e9-71b3-a7b1-22422a16688b</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -3759,7 +3735,7 @@
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/93511b52-3de6-4102-980b-24d00b6c5851</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/c69854e0-18e9-71b3-a7b1-22422a16688b</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
@@ -3769,12 +3745,12 @@
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/a82992bab1da44c99dc71e9ac8ef6ff3d626dc4d.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/584cfd5ec1bb0f374ab03f25ca3600a8ec2e67bf.jpg</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296241</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296218</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
@@ -3797,7 +3773,7 @@
       <c r="AB27" t="inlineStr"/>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/93511b52-3de6-4102-980b-24d00b6c5851/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/c69854e0-18e9-71b3-a7b1-22422a16688b/manifest</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr"/>
@@ -3805,52 +3781,52 @@
       <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="inlineStr"/>
       <c r="AH27" t="n">
-        <v>52</v>
+        <v>77</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>辨證配劑醫燈 3巻 [3]</t>
+          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [17]</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>A00:6517</t>
+          <t>A00:6257</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ベンショウ ハイザイ イトウ</t>
+          <t>レキダイ ザンケツ ニッキ</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>曲直瀬 道三</t>
+          <t>黒川 春村</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>道三 [自筆]</t>
+          <t>[書写者不明]</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
-          <t>元亀2 [1571] 大尾</t>
+          <t>[安政5 (1858)]</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
-          <t>写本|巻之2の巻頭書名: 辨證配剤醫燈|大尾に「治病用藥之時欲使侄姪孫一覧如指掌而已/旹元亀第二辛未年冬日南至六十五齢老眼寒窓/日東洛下雖知苦斎盍静翁 道三」とあり|巻末識語に「辨證配劑醫燈全三册壹帙一溪叟道三所親筆也不可忽諸故附一語於後耳」とあり|箱に「和氣道三自書寫配劑醫燈三卷林道春跋之櫻井老人苐一家藏子孫永寶之 葛辰識」との墨書あり|毎半面11行|朱点, 朱引, 朱藍筆書き入れあり|付箋あり|箱入り|印記: 「石堂」, 「昃印」|虫損, 汚損あり</t>
+          <t>写本|責任表示及び書写年は『日本古典籍総合目録データベース』による|内容: 6: 光明院御記, 後光嚴院御記, 後小松院宸記, 天聴集. 28: 参議藤定長卿記 : 稱山丞記. 37: 定高卿記, 晴御会部類記, 家光卿御記, 權中納言平範輔卿記. 38: 左大史小槻季継記, 後堀川安貞二年放生會(実基公記), 石清水八幡宮, 弁官拝賀次第. 39: 大外記師光記, 資季卿記, 荒凉記, 忠高卿記. 40: 冷泉公相公記, 勝延法眼記 : 東寺大行事, 後中記 : 小路中納言資頼卿記葉室. 41: 中光記, 師兼記, 陽龍記. 42: 大宮司長則記, 口筆 : 實經, 顕朝卿記, 鴨御幸記. 43: 寳治二年記, 深心院關白記, 藤公親記, 照念院関白兼平公記. 44: 頼親記, 亀山殿行幸記 : 雅言卿記, 兼基公記. 45: 大嘗會御禊節下次第, 建治三年丁丑日記 : 三善康有, 建治四年正月廿一日 : 徳大寺大相國公孝記, 冬定卿記, 左大史小槻兼文記|内容: 46: 經任卿記, 前豊前守藤憲説記, 實兼公記. 47: 継塵記抄出. 48: 管見記, 公衡公記, 大外記師顕記, 大外記中原師淳記. 49: 真光院禪助僧正記, 吉田内府卿記. 50: 定清記, 叅議雅俊卿記, 太政大臣(公守公)御上表雜事, 仙洞御灌頂日記, 正安二年八月十一日於仙洞被始行熾盛光法, 正安三年御譲位記. 51: 實躬卿記. 52: 公茂公記, 冬平公記, 隆長卿記. 53: 忠教公記, 官記, 正三位長基卿記, 北面秀長記, 大外記中原師右記. 54: 文保元年, 日野中納言資朝卿記, 洞院大納言公敏卿記. 55: 隆蔭卿記, 文保三年記, 尹大納言師賢卿記, 革命記, 立倚子記, 萬里小路中納言藤藤房卿記|内容: 56: 資名卿記, 公秀公記, 一條家記装束抄出, 頼定卿記. 63: 松亞記, 日野大納言時光卿記, 後八條内府實継公記. 74: 成恩寺関白記. 78: 山科家礼記. 82: 諒闇記 : 後成恩寺殿, 宗典僧正記, 綱光公記, 贈従二位宗賢卿記, 義政公記. 84: 長禄二年戊寅正月, 見聞雜記. 87: 言國卿記. 88: 長興宿祢記, 元長卿記, 兼顕卿記, 小槻晴冨記|28末の原奥書に「右山丞記依 仰挍合書冩/享和二年四月 日撿挍保己一」とあり|50「正安二年八月十一日於仙洞被始行熾盛光法」末の原奥書に「文化十五年春二月以南山法曼院藏夲書冩之 撿挍保己一」とあり|横刷毛目表紙を使用|朱点, 朱引, 朱墨筆書き入れあり|付箋あり|蔵書印主信濃須坂藩主堀直格の命によって編集された古記録|他の原本は関東大震災により焼失|極札に「桂壽」(6), 「尚信」(53)との極書, 「武清」(44, 53), 「永海」(51), 「了伴」(52), 「了甫」(74), 「定時」(84, 88)との極印あり|印記: 「花廼家文庫」, 「墨阪十一代主寫藏記」(堀直格(1806-1880)), 「東京大學法理文學部書庫所藏」, 「閲覧室用 FOR USE IN THE READING ROOM」|虫損あり</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -3866,12 +3842,12 @@
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/a23dae2e-701a-8d7c-1359-fe786c2e2cdd.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/37d790df-458b-48bf-6b67-3f4755f40f0f.json</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>a23dae2e-701a-8d7c-1359-fe786c2e2cdd</t>
+          <t>37d790df-458b-48bf-6b67-3f4755f40f0f</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -3881,7 +3857,7 @@
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/a23dae2e-701a-8d7c-1359-fe786c2e2cdd</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/37d790df-458b-48bf-6b67-3f4755f40f0f</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
@@ -3891,12 +3867,12 @@
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/21b02bac7c065db97c214037acfa4b232d2ddc89.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/dae05b3fca02a35e3363b381527ea7a899ca4f74.jpg</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296242</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296217</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
@@ -3919,7 +3895,7 @@
       <c r="AB28" t="inlineStr"/>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/a23dae2e-701a-8d7c-1359-fe786c2e2cdd/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/37d790df-458b-48bf-6b67-3f4755f40f0f/manifest</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr"/>
@@ -3927,13 +3903,13 @@
       <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="inlineStr"/>
       <c r="AH28" t="n">
-        <v>63</v>
+        <v>54</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [16]</t>
+          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [15]</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3988,12 +3964,12 @@
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/31b47601-839e-83b4-6a49-7d11ed020385.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/acf20dd5-459a-5438-8dd8-cbc11fe122bf.json</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>31b47601-839e-83b4-6a49-7d11ed020385</t>
+          <t>acf20dd5-459a-5438-8dd8-cbc11fe122bf</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -4003,7 +3979,7 @@
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/31b47601-839e-83b4-6a49-7d11ed020385</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/acf20dd5-459a-5438-8dd8-cbc11fe122bf</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
@@ -4013,12 +3989,12 @@
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/d78a0b64be5f71b37b264b3b2eb8172d4e8a5002.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/cfeece07d99889e30589237e6d78b4933a56b7d6.jpg</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296216</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296215</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
@@ -4041,7 +4017,7 @@
       <c r="AB29" t="inlineStr"/>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/31b47601-839e-83b4-6a49-7d11ed020385/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/acf20dd5-459a-5438-8dd8-cbc11fe122bf/manifest</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr"/>
@@ -4049,13 +4025,13 @@
       <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="inlineStr"/>
       <c r="AH29" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [15]</t>
+          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [16]</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -4110,12 +4086,12 @@
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/acf20dd5-459a-5438-8dd8-cbc11fe122bf.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/31b47601-839e-83b4-6a49-7d11ed020385.json</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>acf20dd5-459a-5438-8dd8-cbc11fe122bf</t>
+          <t>31b47601-839e-83b4-6a49-7d11ed020385</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -4125,7 +4101,7 @@
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/acf20dd5-459a-5438-8dd8-cbc11fe122bf</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/31b47601-839e-83b4-6a49-7d11ed020385</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
@@ -4135,12 +4111,12 @@
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/cfeece07d99889e30589237e6d78b4933a56b7d6.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/d78a0b64be5f71b37b264b3b2eb8172d4e8a5002.jpg</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296215</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296216</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
@@ -4163,7 +4139,7 @@
       <c r="AB30" t="inlineStr"/>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/acf20dd5-459a-5438-8dd8-cbc11fe122bf/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/31b47601-839e-83b4-6a49-7d11ed020385/manifest</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr"/>
@@ -4171,13 +4147,13 @@
       <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="inlineStr"/>
       <c r="AH30" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [14]</t>
+          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [2]</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -4232,12 +4208,12 @@
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/a83ab18c-4d05-492c-2121-ec90971ea54a.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/f31d474b-60bb-5efd-a570-d8f971a97e5e.json</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>a83ab18c-4d05-492c-2121-ec90971ea54a</t>
+          <t>f31d474b-60bb-5efd-a570-d8f971a97e5e</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -4247,7 +4223,7 @@
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/a83ab18c-4d05-492c-2121-ec90971ea54a</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/f31d474b-60bb-5efd-a570-d8f971a97e5e</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
@@ -4257,12 +4233,12 @@
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/b0fe976afebb52b245b298aabead8423fd0d1a6f.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/378909456e17de7b588873b8890cd6945bba3cc8.jpg</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296214</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296202</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
@@ -4285,7 +4261,7 @@
       <c r="AB31" t="inlineStr"/>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/a83ab18c-4d05-492c-2121-ec90971ea54a/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/f31d474b-60bb-5efd-a570-d8f971a97e5e/manifest</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr"/>
@@ -4293,13 +4269,13 @@
       <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="inlineStr"/>
       <c r="AH31" t="n">
-        <v>59</v>
+        <v>75</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [12]</t>
+          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [3]</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -4354,12 +4330,12 @@
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/d199046f-6bd4-6ca0-a0bf-c29ad3c19949.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/0ddf4bea-7e5d-145a-1812-20986271091f.json</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>d199046f-6bd4-6ca0-a0bf-c29ad3c19949</t>
+          <t>0ddf4bea-7e5d-145a-1812-20986271091f</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -4369,7 +4345,7 @@
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/d199046f-6bd4-6ca0-a0bf-c29ad3c19949</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/0ddf4bea-7e5d-145a-1812-20986271091f</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
@@ -4379,12 +4355,12 @@
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/4cbd0825007ec7d3c89014f55d3b6825a8214769.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/f1d109214b4c636205f357c37df4079371b1c32f.jpg</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296212</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296203</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
@@ -4407,7 +4383,7 @@
       <c r="AB32" t="inlineStr"/>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/d199046f-6bd4-6ca0-a0bf-c29ad3c19949/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/0ddf4bea-7e5d-145a-1812-20986271091f/manifest</t>
         </is>
       </c>
       <c r="AD32" t="inlineStr"/>
@@ -4415,13 +4391,13 @@
       <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="inlineStr"/>
       <c r="AH32" t="n">
-        <v>77</v>
+        <v>50</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [13]</t>
+          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [4]</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4476,12 +4452,12 @@
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/1b5c5c7f-4892-39f9-4e5e-479a8e921be2.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/5bf3d0ca-0a42-80a4-6959-af4f28d23fa3.json</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>1b5c5c7f-4892-39f9-4e5e-479a8e921be2</t>
+          <t>5bf3d0ca-0a42-80a4-6959-af4f28d23fa3</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -4491,7 +4467,7 @@
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/1b5c5c7f-4892-39f9-4e5e-479a8e921be2</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/5bf3d0ca-0a42-80a4-6959-af4f28d23fa3</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
@@ -4501,12 +4477,12 @@
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/95aeca9c3732100e9d926fc7a9cb98fba20b6444.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/b3dd61edd0ba78499c058ae1c9d57f1980d4b058.jpg</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296213</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296204</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
@@ -4529,7 +4505,7 @@
       <c r="AB33" t="inlineStr"/>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/1b5c5c7f-4892-39f9-4e5e-479a8e921be2/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/5bf3d0ca-0a42-80a4-6959-af4f28d23fa3/manifest</t>
         </is>
       </c>
       <c r="AD33" t="inlineStr"/>
@@ -4537,36 +4513,40 @@
       <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="inlineStr"/>
       <c r="AH33" t="n">
-        <v>74</v>
+        <v>52</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>大嘗會悠紀主基鮮味之繪</t>
+          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [5]</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>A00:6108</t>
+          <t>A00:6257</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ダイジョウエ ユキ スキ センミ ノ ズ</t>
+          <t>レキダイ ザンケツ ニッキ</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>黒川 春村</t>
+        </is>
+      </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>[佐伯]</t>
+          <t>[書写者不明]</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
-          <t>明和元 [1764] 識語</t>
+          <t>[安政5 (1858)]</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -4578,7 +4558,7 @@
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
-          <t>絵巻|書名は識語による|書袋の書名: 悠紀主基鮮味之啚|表紙裏に「元文悠紀主基鮮味之圖 寛延同」とあり|巻末の識語に「右大嘗會悠紀主基鮮味之繪借請御厨子所預紀宗直朝臣令佐伯職房摸冩之畢 明和元年孟冬左少将藤原(花押)」とあり|絵4幅: 梅作枝, 糸作枩, 萩作枝, 萩作枝|紙本著色|彩色あり|帙入り|印記: 「野宮藏書」</t>
+          <t>写本|責任表示及び書写年は『日本古典籍総合目録データベース』による|内容: 6: 光明院御記, 後光嚴院御記, 後小松院宸記, 天聴集. 28: 参議藤定長卿記 : 稱山丞記. 37: 定高卿記, 晴御会部類記, 家光卿御記, 權中納言平範輔卿記. 38: 左大史小槻季継記, 後堀川安貞二年放生會(実基公記), 石清水八幡宮, 弁官拝賀次第. 39: 大外記師光記, 資季卿記, 荒凉記, 忠高卿記. 40: 冷泉公相公記, 勝延法眼記 : 東寺大行事, 後中記 : 小路中納言資頼卿記葉室. 41: 中光記, 師兼記, 陽龍記. 42: 大宮司長則記, 口筆 : 實經, 顕朝卿記, 鴨御幸記. 43: 寳治二年記, 深心院關白記, 藤公親記, 照念院関白兼平公記. 44: 頼親記, 亀山殿行幸記 : 雅言卿記, 兼基公記. 45: 大嘗會御禊節下次第, 建治三年丁丑日記 : 三善康有, 建治四年正月廿一日 : 徳大寺大相國公孝記, 冬定卿記, 左大史小槻兼文記|内容: 46: 經任卿記, 前豊前守藤憲説記, 實兼公記. 47: 継塵記抄出. 48: 管見記, 公衡公記, 大外記師顕記, 大外記中原師淳記. 49: 真光院禪助僧正記, 吉田内府卿記. 50: 定清記, 叅議雅俊卿記, 太政大臣(公守公)御上表雜事, 仙洞御灌頂日記, 正安二年八月十一日於仙洞被始行熾盛光法, 正安三年御譲位記. 51: 實躬卿記. 52: 公茂公記, 冬平公記, 隆長卿記. 53: 忠教公記, 官記, 正三位長基卿記, 北面秀長記, 大外記中原師右記. 54: 文保元年, 日野中納言資朝卿記, 洞院大納言公敏卿記. 55: 隆蔭卿記, 文保三年記, 尹大納言師賢卿記, 革命記, 立倚子記, 萬里小路中納言藤藤房卿記|内容: 56: 資名卿記, 公秀公記, 一條家記装束抄出, 頼定卿記. 63: 松亞記, 日野大納言時光卿記, 後八條内府實継公記. 74: 成恩寺関白記. 78: 山科家礼記. 82: 諒闇記 : 後成恩寺殿, 宗典僧正記, 綱光公記, 贈従二位宗賢卿記, 義政公記. 84: 長禄二年戊寅正月, 見聞雜記. 87: 言國卿記. 88: 長興宿祢記, 元長卿記, 兼顕卿記, 小槻晴冨記|28末の原奥書に「右山丞記依 仰挍合書冩/享和二年四月 日撿挍保己一」とあり|50「正安二年八月十一日於仙洞被始行熾盛光法」末の原奥書に「文化十五年春二月以南山法曼院藏夲書冩之 撿挍保己一」とあり|横刷毛目表紙を使用|朱点, 朱引, 朱墨筆書き入れあり|付箋あり|蔵書印主信濃須坂藩主堀直格の命によって編集された古記録|他の原本は関東大震災により焼失|極札に「桂壽」(6), 「尚信」(53)との極書, 「武清」(44, 53), 「永海」(51), 「了伴」(52), 「了甫」(74), 「定時」(84, 88)との極印あり|印記: 「花廼家文庫」, 「墨阪十一代主寫藏記」(堀直格(1806-1880)), 「東京大學法理文學部書庫所藏」, 「閲覧室用 FOR USE IN THE READING ROOM」|虫損あり</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -4594,12 +4574,12 @@
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/d00e906c-5404-4fc1-44c9-1566cf7f7012.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/92efd5a7-2a66-1ead-1e71-bdf9c70e12d0.json</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>d00e906c-5404-4fc1-44c9-1566cf7f7012</t>
+          <t>92efd5a7-2a66-1ead-1e71-bdf9c70e12d0</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -4609,7 +4589,7 @@
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/d00e906c-5404-4fc1-44c9-1566cf7f7012</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/92efd5a7-2a66-1ead-1e71-bdf9c70e12d0</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
@@ -4619,12 +4599,12 @@
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/51e8aa982b380211852796b36819e6c6c6bf1583.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/aaef2fe4c4feeefa7fd4fb27983a6dfd085d4a7b.jpg</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296199</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296205</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
@@ -4647,7 +4627,7 @@
       <c r="AB34" t="inlineStr"/>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/d00e906c-5404-4fc1-44c9-1566cf7f7012/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/92efd5a7-2a66-1ead-1e71-bdf9c70e12d0/manifest</t>
         </is>
       </c>
       <c r="AD34" t="inlineStr"/>
@@ -4655,36 +4635,40 @@
       <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="inlineStr"/>
       <c r="AH34" t="n">
-        <v>11</v>
+        <v>68</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>真言宗脈啚 : 栂尾夲</t>
+          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [6]</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>A00:6129</t>
+          <t>A00:6257</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>シンゴンシュウ ミャクズ : トガノオボン</t>
+          <t>レキダイ ザンケツ ニッキ</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>黒川 春村</t>
+        </is>
+      </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>覺心</t>
+          <t>[書写者不明]</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
-          <t>享保9 [1724] 奥書</t>
+          <t>[安政5 (1858)]</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -4696,7 +4680,7 @@
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
-          <t>写本|書名は題簽による|帙題簽の書名: 真言宗血脈圗|奥書に「正徳二年之春請自性院僧正開栂尾山宮御封之經藏求淂于古聖教若干部是其一也 沙門道空」, 「享保九年甲辰夏寓于洛西御阜草菴以五智山之本冩之訖 南紀護国寺沙門覺心/同年六月晦日以栂尾法鼓臺古本挍合之了」, 「昭和八年四月念三日閲覧砌訂正誤字記入落罫云尒 中野達慧識」とあり|朱筆書き入れあり|印記: 「和學講談所」, 「温故堂文庫」(塙家), 「松平家藏書印」|虫損あり</t>
+          <t>写本|責任表示及び書写年は『日本古典籍総合目録データベース』による|内容: 6: 光明院御記, 後光嚴院御記, 後小松院宸記, 天聴集. 28: 参議藤定長卿記 : 稱山丞記. 37: 定高卿記, 晴御会部類記, 家光卿御記, 權中納言平範輔卿記. 38: 左大史小槻季継記, 後堀川安貞二年放生會(実基公記), 石清水八幡宮, 弁官拝賀次第. 39: 大外記師光記, 資季卿記, 荒凉記, 忠高卿記. 40: 冷泉公相公記, 勝延法眼記 : 東寺大行事, 後中記 : 小路中納言資頼卿記葉室. 41: 中光記, 師兼記, 陽龍記. 42: 大宮司長則記, 口筆 : 實經, 顕朝卿記, 鴨御幸記. 43: 寳治二年記, 深心院關白記, 藤公親記, 照念院関白兼平公記. 44: 頼親記, 亀山殿行幸記 : 雅言卿記, 兼基公記. 45: 大嘗會御禊節下次第, 建治三年丁丑日記 : 三善康有, 建治四年正月廿一日 : 徳大寺大相國公孝記, 冬定卿記, 左大史小槻兼文記|内容: 46: 經任卿記, 前豊前守藤憲説記, 實兼公記. 47: 継塵記抄出. 48: 管見記, 公衡公記, 大外記師顕記, 大外記中原師淳記. 49: 真光院禪助僧正記, 吉田内府卿記. 50: 定清記, 叅議雅俊卿記, 太政大臣(公守公)御上表雜事, 仙洞御灌頂日記, 正安二年八月十一日於仙洞被始行熾盛光法, 正安三年御譲位記. 51: 實躬卿記. 52: 公茂公記, 冬平公記, 隆長卿記. 53: 忠教公記, 官記, 正三位長基卿記, 北面秀長記, 大外記中原師右記. 54: 文保元年, 日野中納言資朝卿記, 洞院大納言公敏卿記. 55: 隆蔭卿記, 文保三年記, 尹大納言師賢卿記, 革命記, 立倚子記, 萬里小路中納言藤藤房卿記|内容: 56: 資名卿記, 公秀公記, 一條家記装束抄出, 頼定卿記. 63: 松亞記, 日野大納言時光卿記, 後八條内府實継公記. 74: 成恩寺関白記. 78: 山科家礼記. 82: 諒闇記 : 後成恩寺殿, 宗典僧正記, 綱光公記, 贈従二位宗賢卿記, 義政公記. 84: 長禄二年戊寅正月, 見聞雜記. 87: 言國卿記. 88: 長興宿祢記, 元長卿記, 兼顕卿記, 小槻晴冨記|28末の原奥書に「右山丞記依 仰挍合書冩/享和二年四月 日撿挍保己一」とあり|50「正安二年八月十一日於仙洞被始行熾盛光法」末の原奥書に「文化十五年春二月以南山法曼院藏夲書冩之 撿挍保己一」とあり|横刷毛目表紙を使用|朱点, 朱引, 朱墨筆書き入れあり|付箋あり|蔵書印主信濃須坂藩主堀直格の命によって編集された古記録|他の原本は関東大震災により焼失|極札に「桂壽」(6), 「尚信」(53)との極書, 「武清」(44, 53), 「永海」(51), 「了伴」(52), 「了甫」(74), 「定時」(84, 88)との極印あり|印記: 「花廼家文庫」, 「墨阪十一代主寫藏記」(堀直格(1806-1880)), 「東京大學法理文學部書庫所藏」, 「閲覧室用 FOR USE IN THE READING ROOM」|虫損あり</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -4712,12 +4696,12 @@
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/e6a30e98-5da6-7e0d-7a92-5b26c887309f.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/70ac8e25-6d33-9123-6fb2-0339224b41cc.json</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>e6a30e98-5da6-7e0d-7a92-5b26c887309f</t>
+          <t>70ac8e25-6d33-9123-6fb2-0339224b41cc</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -4727,7 +4711,7 @@
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/e6a30e98-5da6-7e0d-7a92-5b26c887309f</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/70ac8e25-6d33-9123-6fb2-0339224b41cc</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
@@ -4737,12 +4721,12 @@
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/10842787f14673fb3729595dd908dde4c4dd6ad8.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/3d36b605983eef3eb9e60d5e9f2d3016a497dd98.jpg</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296200</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296206</t>
         </is>
       </c>
       <c r="W35" t="inlineStr">
@@ -4765,7 +4749,7 @@
       <c r="AB35" t="inlineStr"/>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/e6a30e98-5da6-7e0d-7a92-5b26c887309f/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/70ac8e25-6d33-9123-6fb2-0339224b41cc/manifest</t>
         </is>
       </c>
       <c r="AD35" t="inlineStr"/>
@@ -4773,13 +4757,13 @@
       <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="inlineStr"/>
       <c r="AH35" t="n">
-        <v>22</v>
+        <v>72</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [1]</t>
+          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [7]</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4834,12 +4818,12 @@
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/c32632af-9dc0-504a-5437-15a055d52628.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/87cadcc3-3c6c-1f0e-a10f-d8c8b16b34e3.json</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>c32632af-9dc0-504a-5437-15a055d52628</t>
+          <t>87cadcc3-3c6c-1f0e-a10f-d8c8b16b34e3</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -4849,7 +4833,7 @@
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/c32632af-9dc0-504a-5437-15a055d52628</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/87cadcc3-3c6c-1f0e-a10f-d8c8b16b34e3</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
@@ -4859,12 +4843,12 @@
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/2230dfedd3d91cc8b1c5532de33a8f8559be8357.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/60cd75676a83bcd5331212ff419346e6088f81e4.jpg</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296201</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296207</t>
         </is>
       </c>
       <c r="W36" t="inlineStr">
@@ -4887,7 +4871,7 @@
       <c r="AB36" t="inlineStr"/>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/c32632af-9dc0-504a-5437-15a055d52628/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/87cadcc3-3c6c-1f0e-a10f-d8c8b16b34e3/manifest</t>
         </is>
       </c>
       <c r="AD36" t="inlineStr"/>
@@ -4895,13 +4879,13 @@
       <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="inlineStr"/>
       <c r="AH36" t="n">
-        <v>72</v>
+        <v>67</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [2]</t>
+          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [8]</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4956,12 +4940,12 @@
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/f31d474b-60bb-5efd-a570-d8f971a97e5e.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/d4dc2699-5a8e-7ad5-3160-80d5fae78074.json</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>f31d474b-60bb-5efd-a570-d8f971a97e5e</t>
+          <t>d4dc2699-5a8e-7ad5-3160-80d5fae78074</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
@@ -4971,7 +4955,7 @@
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/f31d474b-60bb-5efd-a570-d8f971a97e5e</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/d4dc2699-5a8e-7ad5-3160-80d5fae78074</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
@@ -4981,12 +4965,12 @@
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/378909456e17de7b588873b8890cd6945bba3cc8.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/596a21f68644c95bd76b3f3600fb73bc78fb9124.jpg</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296202</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296208</t>
         </is>
       </c>
       <c r="W37" t="inlineStr">
@@ -5009,7 +4993,7 @@
       <c r="AB37" t="inlineStr"/>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/f31d474b-60bb-5efd-a570-d8f971a97e5e/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/d4dc2699-5a8e-7ad5-3160-80d5fae78074/manifest</t>
         </is>
       </c>
       <c r="AD37" t="inlineStr"/>
@@ -5017,13 +5001,13 @@
       <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="inlineStr"/>
       <c r="AH37" t="n">
-        <v>75</v>
+        <v>67</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [3]</t>
+          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [9]</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -5078,12 +5062,12 @@
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/0ddf4bea-7e5d-145a-1812-20986271091f.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/a5e4d339-47a5-92a8-3fb3-15464db0a1f8.json</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>0ddf4bea-7e5d-145a-1812-20986271091f</t>
+          <t>a5e4d339-47a5-92a8-3fb3-15464db0a1f8</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
@@ -5093,7 +5077,7 @@
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/0ddf4bea-7e5d-145a-1812-20986271091f</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/a5e4d339-47a5-92a8-3fb3-15464db0a1f8</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
@@ -5103,12 +5087,12 @@
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/f1d109214b4c636205f357c37df4079371b1c32f.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/965ce572fe0c064509727c2dbba58751771f36b4.jpg</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296203</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296209</t>
         </is>
       </c>
       <c r="W38" t="inlineStr">
@@ -5131,7 +5115,7 @@
       <c r="AB38" t="inlineStr"/>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/0ddf4bea-7e5d-145a-1812-20986271091f/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/a5e4d339-47a5-92a8-3fb3-15464db0a1f8/manifest</t>
         </is>
       </c>
       <c r="AD38" t="inlineStr"/>
@@ -5139,13 +5123,13 @@
       <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="inlineStr"/>
       <c r="AH38" t="n">
-        <v>50</v>
+        <v>64</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [4]</t>
+          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [10]</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -5200,12 +5184,12 @@
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/5bf3d0ca-0a42-80a4-6959-af4f28d23fa3.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/941cae96-2884-09d1-316d-978da0fc83f5.json</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>5bf3d0ca-0a42-80a4-6959-af4f28d23fa3</t>
+          <t>941cae96-2884-09d1-316d-978da0fc83f5</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
@@ -5215,7 +5199,7 @@
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/5bf3d0ca-0a42-80a4-6959-af4f28d23fa3</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/941cae96-2884-09d1-316d-978da0fc83f5</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
@@ -5225,12 +5209,12 @@
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/b3dd61edd0ba78499c058ae1c9d57f1980d4b058.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/9b2119b5a8cb266e4d44bebff61cd8b5383a810e.jpg</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296204</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296210</t>
         </is>
       </c>
       <c r="W39" t="inlineStr">
@@ -5253,7 +5237,7 @@
       <c r="AB39" t="inlineStr"/>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/5bf3d0ca-0a42-80a4-6959-af4f28d23fa3/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/941cae96-2884-09d1-316d-978da0fc83f5/manifest</t>
         </is>
       </c>
       <c r="AD39" t="inlineStr"/>
@@ -5261,13 +5245,13 @@
       <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="inlineStr"/>
       <c r="AH39" t="n">
-        <v>52</v>
+        <v>70</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [5]</t>
+          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [11]</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -5322,12 +5306,12 @@
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/92efd5a7-2a66-1ead-1e71-bdf9c70e12d0.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/b6a83876-30df-48c8-9c3f-3a68e8429d62.json</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>92efd5a7-2a66-1ead-1e71-bdf9c70e12d0</t>
+          <t>b6a83876-30df-48c8-9c3f-3a68e8429d62</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
@@ -5337,7 +5321,7 @@
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/92efd5a7-2a66-1ead-1e71-bdf9c70e12d0</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/b6a83876-30df-48c8-9c3f-3a68e8429d62</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
@@ -5347,12 +5331,12 @@
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/aaef2fe4c4feeefa7fd4fb27983a6dfd085d4a7b.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/7f6bf7c4b28ea807212c7ead3da50d50601c8ed1.jpg</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296205</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296211</t>
         </is>
       </c>
       <c r="W40" t="inlineStr">
@@ -5375,7 +5359,7 @@
       <c r="AB40" t="inlineStr"/>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/92efd5a7-2a66-1ead-1e71-bdf9c70e12d0/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/b6a83876-30df-48c8-9c3f-3a68e8429d62/manifest</t>
         </is>
       </c>
       <c r="AD40" t="inlineStr"/>
@@ -5383,13 +5367,13 @@
       <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="inlineStr"/>
       <c r="AH40" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [6]</t>
+          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [12]</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5444,12 +5428,12 @@
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/70ac8e25-6d33-9123-6fb2-0339224b41cc.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/d199046f-6bd4-6ca0-a0bf-c29ad3c19949.json</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>70ac8e25-6d33-9123-6fb2-0339224b41cc</t>
+          <t>d199046f-6bd4-6ca0-a0bf-c29ad3c19949</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
@@ -5459,7 +5443,7 @@
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/70ac8e25-6d33-9123-6fb2-0339224b41cc</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/d199046f-6bd4-6ca0-a0bf-c29ad3c19949</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
@@ -5469,12 +5453,12 @@
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/3d36b605983eef3eb9e60d5e9f2d3016a497dd98.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/4cbd0825007ec7d3c89014f55d3b6825a8214769.jpg</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296206</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296212</t>
         </is>
       </c>
       <c r="W41" t="inlineStr">
@@ -5497,7 +5481,7 @@
       <c r="AB41" t="inlineStr"/>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/70ac8e25-6d33-9123-6fb2-0339224b41cc/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/d199046f-6bd4-6ca0-a0bf-c29ad3c19949/manifest</t>
         </is>
       </c>
       <c r="AD41" t="inlineStr"/>
@@ -5505,13 +5489,13 @@
       <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="inlineStr"/>
       <c r="AH41" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [7]</t>
+          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [13]</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5566,12 +5550,12 @@
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/87cadcc3-3c6c-1f0e-a10f-d8c8b16b34e3.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/1b5c5c7f-4892-39f9-4e5e-479a8e921be2.json</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>87cadcc3-3c6c-1f0e-a10f-d8c8b16b34e3</t>
+          <t>1b5c5c7f-4892-39f9-4e5e-479a8e921be2</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
@@ -5581,7 +5565,7 @@
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/87cadcc3-3c6c-1f0e-a10f-d8c8b16b34e3</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/1b5c5c7f-4892-39f9-4e5e-479a8e921be2</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
@@ -5591,12 +5575,12 @@
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/60cd75676a83bcd5331212ff419346e6088f81e4.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/95aeca9c3732100e9d926fc7a9cb98fba20b6444.jpg</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296207</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296213</t>
         </is>
       </c>
       <c r="W42" t="inlineStr">
@@ -5619,7 +5603,7 @@
       <c r="AB42" t="inlineStr"/>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/87cadcc3-3c6c-1f0e-a10f-d8c8b16b34e3/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/1b5c5c7f-4892-39f9-4e5e-479a8e921be2/manifest</t>
         </is>
       </c>
       <c r="AD42" t="inlineStr"/>
@@ -5627,13 +5611,13 @@
       <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="inlineStr"/>
       <c r="AH42" t="n">
-        <v>67</v>
+        <v>74</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [8]</t>
+          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [14]</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5688,12 +5672,12 @@
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/d4dc2699-5a8e-7ad5-3160-80d5fae78074.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/a83ab18c-4d05-492c-2121-ec90971ea54a.json</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>d4dc2699-5a8e-7ad5-3160-80d5fae78074</t>
+          <t>a83ab18c-4d05-492c-2121-ec90971ea54a</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
@@ -5703,7 +5687,7 @@
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/d4dc2699-5a8e-7ad5-3160-80d5fae78074</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/a83ab18c-4d05-492c-2121-ec90971ea54a</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
@@ -5713,12 +5697,12 @@
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/596a21f68644c95bd76b3f3600fb73bc78fb9124.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/b0fe976afebb52b245b298aabead8423fd0d1a6f.jpg</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296208</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296214</t>
         </is>
       </c>
       <c r="W43" t="inlineStr">
@@ -5741,7 +5725,7 @@
       <c r="AB43" t="inlineStr"/>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/d4dc2699-5a8e-7ad5-3160-80d5fae78074/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/a83ab18c-4d05-492c-2121-ec90971ea54a/manifest</t>
         </is>
       </c>
       <c r="AD43" t="inlineStr"/>
@@ -5749,29 +5733,29 @@
       <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="inlineStr"/>
       <c r="AH43" t="n">
-        <v>67</v>
+        <v>59</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [9]</t>
+          <t>和漢朗詠集 2巻 [2]</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>A00:6257</t>
+          <t>A00:4081</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>レキダイ ザンケツ ニッキ</t>
+          <t>ワカン ロウエイシュウ</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>黒川 春村</t>
+          <t>藤原 公任</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -5782,19 +5766,19 @@
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr">
         <is>
-          <t>[安政5 (1858)]</t>
+          <t>[江戸前期]</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr">
         <is>
-          <t>写本|責任表示及び書写年は『日本古典籍総合目録データベース』による|内容: 6: 光明院御記, 後光嚴院御記, 後小松院宸記, 天聴集. 28: 参議藤定長卿記 : 稱山丞記. 37: 定高卿記, 晴御会部類記, 家光卿御記, 權中納言平範輔卿記. 38: 左大史小槻季継記, 後堀川安貞二年放生會(実基公記), 石清水八幡宮, 弁官拝賀次第. 39: 大外記師光記, 資季卿記, 荒凉記, 忠高卿記. 40: 冷泉公相公記, 勝延法眼記 : 東寺大行事, 後中記 : 小路中納言資頼卿記葉室. 41: 中光記, 師兼記, 陽龍記. 42: 大宮司長則記, 口筆 : 實經, 顕朝卿記, 鴨御幸記. 43: 寳治二年記, 深心院關白記, 藤公親記, 照念院関白兼平公記. 44: 頼親記, 亀山殿行幸記 : 雅言卿記, 兼基公記. 45: 大嘗會御禊節下次第, 建治三年丁丑日記 : 三善康有, 建治四年正月廿一日 : 徳大寺大相國公孝記, 冬定卿記, 左大史小槻兼文記|内容: 46: 經任卿記, 前豊前守藤憲説記, 實兼公記. 47: 継塵記抄出. 48: 管見記, 公衡公記, 大外記師顕記, 大外記中原師淳記. 49: 真光院禪助僧正記, 吉田内府卿記. 50: 定清記, 叅議雅俊卿記, 太政大臣(公守公)御上表雜事, 仙洞御灌頂日記, 正安二年八月十一日於仙洞被始行熾盛光法, 正安三年御譲位記. 51: 實躬卿記. 52: 公茂公記, 冬平公記, 隆長卿記. 53: 忠教公記, 官記, 正三位長基卿記, 北面秀長記, 大外記中原師右記. 54: 文保元年, 日野中納言資朝卿記, 洞院大納言公敏卿記. 55: 隆蔭卿記, 文保三年記, 尹大納言師賢卿記, 革命記, 立倚子記, 萬里小路中納言藤藤房卿記|内容: 56: 資名卿記, 公秀公記, 一條家記装束抄出, 頼定卿記. 63: 松亞記, 日野大納言時光卿記, 後八條内府實継公記. 74: 成恩寺関白記. 78: 山科家礼記. 82: 諒闇記 : 後成恩寺殿, 宗典僧正記, 綱光公記, 贈従二位宗賢卿記, 義政公記. 84: 長禄二年戊寅正月, 見聞雜記. 87: 言國卿記. 88: 長興宿祢記, 元長卿記, 兼顕卿記, 小槻晴冨記|28末の原奥書に「右山丞記依 仰挍合書冩/享和二年四月 日撿挍保己一」とあり|50「正安二年八月十一日於仙洞被始行熾盛光法」末の原奥書に「文化十五年春二月以南山法曼院藏夲書冩之 撿挍保己一」とあり|横刷毛目表紙を使用|朱点, 朱引, 朱墨筆書き入れあり|付箋あり|蔵書印主信濃須坂藩主堀直格の命によって編集された古記録|他の原本は関東大震災により焼失|極札に「桂壽」(6), 「尚信」(53)との極書, 「武清」(44, 53), 「永海」(51), 「了伴」(52), 「了甫」(74), 「定時」(84, 88)との極印あり|印記: 「花廼家文庫」, 「墨阪十一代主寫藏記」(堀直格(1806-1880)), 「東京大學法理文學部書庫所藏」, 「閲覧室用 FOR USE IN THE READING ROOM」|虫損あり</t>
+          <t>写本|書名は目首及び題簽による|外箱の書名: 御本|責任表示は『日本古典籍総合目録データベース』による|巻上: 春, 夏, 秋, 冬. 巻下: 雜|題簽による巻冊次表示: 上, 下|毎半帖8行|漢字平仮名交じり文|鳳凰菱繋ぎ文様緞子表紙, 松葉散しに山雲の金箔見返し, 金泥下絵鳥の子紙を使用|列帖装|二重箱入り</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -5810,12 +5794,12 @@
       <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/a5e4d339-47a5-92a8-3fb3-15464db0a1f8.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/a241b0e6-90d9-46db-1fe8-bf35f1e616c5.json</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>a5e4d339-47a5-92a8-3fb3-15464db0a1f8</t>
+          <t>a241b0e6-90d9-46db-1fe8-bf35f1e616c5</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
@@ -5825,7 +5809,7 @@
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/a5e4d339-47a5-92a8-3fb3-15464db0a1f8</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/a241b0e6-90d9-46db-1fe8-bf35f1e616c5</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
@@ -5835,12 +5819,12 @@
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/965ce572fe0c064509727c2dbba58751771f36b4.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/f46b1242e2b77ba4f0d99feac20562f5cd3a0ee2.jpg</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296209</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296167</t>
         </is>
       </c>
       <c r="W44" t="inlineStr">
@@ -5863,7 +5847,7 @@
       <c r="AB44" t="inlineStr"/>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/a5e4d339-47a5-92a8-3fb3-15464db0a1f8/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/a241b0e6-90d9-46db-1fe8-bf35f1e616c5/manifest</t>
         </is>
       </c>
       <c r="AD44" t="inlineStr"/>
@@ -5871,29 +5855,29 @@
       <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="inlineStr"/>
       <c r="AH44" t="n">
-        <v>64</v>
+        <v>48</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [10]</t>
+          <t>つれつれ草</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>A00:6257</t>
+          <t>A00:4082</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>レキダイ ザンケツ ニッキ</t>
+          <t>ツレズレグサ</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>黒川 春村</t>
+          <t>吉田 兼好</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -5904,7 +5888,7 @@
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr">
         <is>
-          <t>[安政5 (1858)]</t>
+          <t>[江戸前期]</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -5916,7 +5900,7 @@
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr">
         <is>
-          <t>写本|責任表示及び書写年は『日本古典籍総合目録データベース』による|内容: 6: 光明院御記, 後光嚴院御記, 後小松院宸記, 天聴集. 28: 参議藤定長卿記 : 稱山丞記. 37: 定高卿記, 晴御会部類記, 家光卿御記, 權中納言平範輔卿記. 38: 左大史小槻季継記, 後堀川安貞二年放生會(実基公記), 石清水八幡宮, 弁官拝賀次第. 39: 大外記師光記, 資季卿記, 荒凉記, 忠高卿記. 40: 冷泉公相公記, 勝延法眼記 : 東寺大行事, 後中記 : 小路中納言資頼卿記葉室. 41: 中光記, 師兼記, 陽龍記. 42: 大宮司長則記, 口筆 : 實經, 顕朝卿記, 鴨御幸記. 43: 寳治二年記, 深心院關白記, 藤公親記, 照念院関白兼平公記. 44: 頼親記, 亀山殿行幸記 : 雅言卿記, 兼基公記. 45: 大嘗會御禊節下次第, 建治三年丁丑日記 : 三善康有, 建治四年正月廿一日 : 徳大寺大相國公孝記, 冬定卿記, 左大史小槻兼文記|内容: 46: 經任卿記, 前豊前守藤憲説記, 實兼公記. 47: 継塵記抄出. 48: 管見記, 公衡公記, 大外記師顕記, 大外記中原師淳記. 49: 真光院禪助僧正記, 吉田内府卿記. 50: 定清記, 叅議雅俊卿記, 太政大臣(公守公)御上表雜事, 仙洞御灌頂日記, 正安二年八月十一日於仙洞被始行熾盛光法, 正安三年御譲位記. 51: 實躬卿記. 52: 公茂公記, 冬平公記, 隆長卿記. 53: 忠教公記, 官記, 正三位長基卿記, 北面秀長記, 大外記中原師右記. 54: 文保元年, 日野中納言資朝卿記, 洞院大納言公敏卿記. 55: 隆蔭卿記, 文保三年記, 尹大納言師賢卿記, 革命記, 立倚子記, 萬里小路中納言藤藤房卿記|内容: 56: 資名卿記, 公秀公記, 一條家記装束抄出, 頼定卿記. 63: 松亞記, 日野大納言時光卿記, 後八條内府實継公記. 74: 成恩寺関白記. 78: 山科家礼記. 82: 諒闇記 : 後成恩寺殿, 宗典僧正記, 綱光公記, 贈従二位宗賢卿記, 義政公記. 84: 長禄二年戊寅正月, 見聞雜記. 87: 言國卿記. 88: 長興宿祢記, 元長卿記, 兼顕卿記, 小槻晴冨記|28末の原奥書に「右山丞記依 仰挍合書冩/享和二年四月 日撿挍保己一」とあり|50「正安二年八月十一日於仙洞被始行熾盛光法」末の原奥書に「文化十五年春二月以南山法曼院藏夲書冩之 撿挍保己一」とあり|横刷毛目表紙を使用|朱点, 朱引, 朱墨筆書き入れあり|付箋あり|蔵書印主信濃須坂藩主堀直格の命によって編集された古記録|他の原本は関東大震災により焼失|極札に「桂壽」(6), 「尚信」(53)との極書, 「武清」(44, 53), 「永海」(51), 「了伴」(52), 「了甫」(74), 「定時」(84, 88)との極印あり|印記: 「花廼家文庫」, 「墨阪十一代主寫藏記」(堀直格(1806-1880)), 「東京大學法理文學部書庫所藏」, 「閲覧室用 FOR USE IN THE READING ROOM」|虫損あり</t>
+          <t>写本|書名は題簽による|書名の繰返し部分は踊り字|外箱の書名: 御本|責任表示は『日本古典籍総合目録データベース』による|毎半帖10行|漢字平仮名交じり文|花草窠文様緞子表紙, 松葉散しに山雲の金箔見返し, 金泥下絵鳥の子紙を使用|列帖装|二重箱入り</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -5932,12 +5916,12 @@
       <c r="O45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/941cae96-2884-09d1-316d-978da0fc83f5.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/d19a62f6-4729-0ee3-3ea7-08f573851a48.json</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>941cae96-2884-09d1-316d-978da0fc83f5</t>
+          <t>d19a62f6-4729-0ee3-3ea7-08f573851a48</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
@@ -5947,7 +5931,7 @@
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/941cae96-2884-09d1-316d-978da0fc83f5</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/d19a62f6-4729-0ee3-3ea7-08f573851a48</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
@@ -5957,12 +5941,12 @@
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/9b2119b5a8cb266e4d44bebff61cd8b5383a810e.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/7966b7312c84644ee577a0390937964b1989586d.jpg</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296210</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296168</t>
         </is>
       </c>
       <c r="W45" t="inlineStr">
@@ -5985,7 +5969,7 @@
       <c r="AB45" t="inlineStr"/>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/941cae96-2884-09d1-316d-978da0fc83f5/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/d19a62f6-4729-0ee3-3ea7-08f573851a48/manifest</t>
         </is>
       </c>
       <c r="AD45" t="inlineStr"/>
@@ -5993,29 +5977,29 @@
       <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="inlineStr"/>
       <c r="AH45" t="n">
-        <v>70</v>
+        <v>142</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [11]</t>
+          <t>日本廿四孝 6巻 [1]</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>A00:6257</t>
+          <t>A00:4084</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>レキダイ ザンケツ ニッキ</t>
+          <t>ヤマト ニジュウシコウ</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>黒川 春村</t>
+          <t>浅井 了意</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -6026,19 +6010,19 @@
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr">
         <is>
-          <t>[安政5 (1858)]</t>
+          <t>[江戸前期]</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr">
         <is>
-          <t>写本|責任表示及び書写年は『日本古典籍総合目録データベース』による|内容: 6: 光明院御記, 後光嚴院御記, 後小松院宸記, 天聴集. 28: 参議藤定長卿記 : 稱山丞記. 37: 定高卿記, 晴御会部類記, 家光卿御記, 權中納言平範輔卿記. 38: 左大史小槻季継記, 後堀川安貞二年放生會(実基公記), 石清水八幡宮, 弁官拝賀次第. 39: 大外記師光記, 資季卿記, 荒凉記, 忠高卿記. 40: 冷泉公相公記, 勝延法眼記 : 東寺大行事, 後中記 : 小路中納言資頼卿記葉室. 41: 中光記, 師兼記, 陽龍記. 42: 大宮司長則記, 口筆 : 實經, 顕朝卿記, 鴨御幸記. 43: 寳治二年記, 深心院關白記, 藤公親記, 照念院関白兼平公記. 44: 頼親記, 亀山殿行幸記 : 雅言卿記, 兼基公記. 45: 大嘗會御禊節下次第, 建治三年丁丑日記 : 三善康有, 建治四年正月廿一日 : 徳大寺大相國公孝記, 冬定卿記, 左大史小槻兼文記|内容: 46: 經任卿記, 前豊前守藤憲説記, 實兼公記. 47: 継塵記抄出. 48: 管見記, 公衡公記, 大外記師顕記, 大外記中原師淳記. 49: 真光院禪助僧正記, 吉田内府卿記. 50: 定清記, 叅議雅俊卿記, 太政大臣(公守公)御上表雜事, 仙洞御灌頂日記, 正安二年八月十一日於仙洞被始行熾盛光法, 正安三年御譲位記. 51: 實躬卿記. 52: 公茂公記, 冬平公記, 隆長卿記. 53: 忠教公記, 官記, 正三位長基卿記, 北面秀長記, 大外記中原師右記. 54: 文保元年, 日野中納言資朝卿記, 洞院大納言公敏卿記. 55: 隆蔭卿記, 文保三年記, 尹大納言師賢卿記, 革命記, 立倚子記, 萬里小路中納言藤藤房卿記|内容: 56: 資名卿記, 公秀公記, 一條家記装束抄出, 頼定卿記. 63: 松亞記, 日野大納言時光卿記, 後八條内府實継公記. 74: 成恩寺関白記. 78: 山科家礼記. 82: 諒闇記 : 後成恩寺殿, 宗典僧正記, 綱光公記, 贈従二位宗賢卿記, 義政公記. 84: 長禄二年戊寅正月, 見聞雜記. 87: 言國卿記. 88: 長興宿祢記, 元長卿記, 兼顕卿記, 小槻晴冨記|28末の原奥書に「右山丞記依 仰挍合書冩/享和二年四月 日撿挍保己一」とあり|50「正安二年八月十一日於仙洞被始行熾盛光法」末の原奥書に「文化十五年春二月以南山法曼院藏夲書冩之 撿挍保己一」とあり|横刷毛目表紙を使用|朱点, 朱引, 朱墨筆書き入れあり|付箋あり|蔵書印主信濃須坂藩主堀直格の命によって編集された古記録|他の原本は関東大震災により焼失|極札に「桂壽」(6), 「尚信」(53)との極書, 「武清」(44, 53), 「永海」(51), 「了伴」(52), 「了甫」(74), 「定時」(84, 88)との極印あり|印記: 「花廼家文庫」, 「墨阪十一代主寫藏記」(堀直格(1806-1880)), 「東京大學法理文學部書庫所藏」, 「閲覧室用 FOR USE IN THE READING ROOM」|虫損あり</t>
+          <t>写本|書名は目首及び題簽による|内箱の書名: 大和廿四孝|外箱の書名: 御本|責任表示は『日本古典籍総合目録データベース』による|1: 第1-4. 2: 第5-8. 3: 第9-12. 4: 第13-16. 5: 第17-20. 6: 第21-24|毎半帖10行|漢字平仮名交じり文|奈良絵本|梅唐草文様緞子表紙, 松葉散しに山雲の金箔見返し, 金泥下絵鳥の子紙を使用|列帖装|竪本|二重箱入り|糸切れあり</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -6054,12 +6038,12 @@
       <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/b6a83876-30df-48c8-9c3f-3a68e8429d62.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/bf17bb0e-6d63-718e-218b-614134ee011d.json</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>b6a83876-30df-48c8-9c3f-3a68e8429d62</t>
+          <t>bf17bb0e-6d63-718e-218b-614134ee011d</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
@@ -6069,7 +6053,7 @@
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/b6a83876-30df-48c8-9c3f-3a68e8429d62</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/bf17bb0e-6d63-718e-218b-614134ee011d</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
@@ -6079,12 +6063,12 @@
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/7f6bf7c4b28ea807212c7ead3da50d50601c8ed1.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/2c48d85abc93bce026f680cc699c748fb0a877e2.jpg</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296211</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296169</t>
         </is>
       </c>
       <c r="W46" t="inlineStr">
@@ -6107,7 +6091,7 @@
       <c r="AB46" t="inlineStr"/>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/b6a83876-30df-48c8-9c3f-3a68e8429d62/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/bf17bb0e-6d63-718e-218b-614134ee011d/manifest</t>
         </is>
       </c>
       <c r="AD46" t="inlineStr"/>
@@ -6115,27 +6099,31 @@
       <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="inlineStr"/>
       <c r="AH46" t="n">
-        <v>64</v>
+        <v>47</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>各種殘經 : 出鄯善縣土峪溝</t>
+          <t>日本廿四孝 6巻 [2]</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>A00:4033</t>
+          <t>A00:4084</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>カクシュ ザンキョウ : シュツ ゼンゼンケン トヨクコウ</t>
+          <t>ヤマト ニジュウシコウ</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>浅井 了意</t>
+        </is>
+      </c>
       <c r="F47" t="inlineStr">
         <is>
           <t>[書写者不明]</t>
@@ -6144,24 +6132,24 @@
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr">
         <is>
-          <t>[書写年不明]</t>
+          <t>[江戸前期]</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr">
         <is>
-          <t>写本残片|書名は題簽による|題簽に「出鄯善縣土峪溝 素文珍藏」とあり|識語に「為楊枝甘露滴入紙中展巻把玩但覺異香盈字 晉卿」, 「右二紙係亜利安字 晉卿」, 「右二紙係畏吾児字 晉卿」とあり|蔵書票に「殘經佛像梵字 十五段 鄯善」, 「梵字第一號」とあり|巻子本|箱入|印記: 「臣樹枏印」, 「晉卿」, 「王仲子」, 「王樹枏印」</t>
+          <t>写本|書名は目首及び題簽による|内箱の書名: 大和廿四孝|外箱の書名: 御本|責任表示は『日本古典籍総合目録データベース』による|1: 第1-4. 2: 第5-8. 3: 第9-12. 4: 第13-16. 5: 第17-20. 6: 第21-24|毎半帖10行|漢字平仮名交じり文|奈良絵本|梅唐草文様緞子表紙, 松葉散しに山雲の金箔見返し, 金泥下絵鳥の子紙を使用|列帖装|竪本|二重箱入り|糸切れあり</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>中国語</t>
+          <t>日本語</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -6172,12 +6160,12 @@
       <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/704d2c7a-4882-6fc8-60d1-94c1e2799bbd.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/c2996e14-8070-09ae-328a-159e60d17016.json</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>704d2c7a-4882-6fc8-60d1-94c1e2799bbd</t>
+          <t>c2996e14-8070-09ae-328a-159e60d17016</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
@@ -6187,7 +6175,7 @@
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/704d2c7a-4882-6fc8-60d1-94c1e2799bbd</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/c2996e14-8070-09ae-328a-159e60d17016</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
@@ -6197,12 +6185,12 @@
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/4cc89d9a25687c69b3dc3791fd39ac740de2c4a0.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/27ba12aa7661321f36193a30b8d8ffb8b32e574c.jpg</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296165</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296170</t>
         </is>
       </c>
       <c r="W47" t="inlineStr">
@@ -6225,7 +6213,7 @@
       <c r="AB47" t="inlineStr"/>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/704d2c7a-4882-6fc8-60d1-94c1e2799bbd/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/c2996e14-8070-09ae-328a-159e60d17016/manifest</t>
         </is>
       </c>
       <c r="AD47" t="inlineStr"/>
@@ -6233,29 +6221,29 @@
       <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="inlineStr"/>
       <c r="AH47" t="n">
-        <v>22</v>
+        <v>103</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>和漢朗詠集 2巻 [1]</t>
+          <t>日本廿四孝 6巻 [3]</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>A00:4081</t>
+          <t>A00:4084</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>ワカン ロウエイシュウ</t>
+          <t>ヤマト ニジュウシコウ</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>藤原 公任</t>
+          <t>浅井 了意</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -6271,14 +6259,14 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr">
         <is>
-          <t>写本|書名は目首及び題簽による|外箱の書名: 御本|責任表示は『日本古典籍総合目録データベース』による|巻上: 春, 夏, 秋, 冬. 巻下: 雜|題簽による巻冊次表示: 上, 下|毎半帖8行|漢字平仮名交じり文|鳳凰菱繋ぎ文様緞子表紙, 松葉散しに山雲の金箔見返し, 金泥下絵鳥の子紙を使用|列帖装|二重箱入り</t>
+          <t>写本|書名は目首及び題簽による|内箱の書名: 大和廿四孝|外箱の書名: 御本|責任表示は『日本古典籍総合目録データベース』による|1: 第1-4. 2: 第5-8. 3: 第9-12. 4: 第13-16. 5: 第17-20. 6: 第21-24|毎半帖10行|漢字平仮名交じり文|奈良絵本|梅唐草文様緞子表紙, 松葉散しに山雲の金箔見返し, 金泥下絵鳥の子紙を使用|列帖装|竪本|二重箱入り|糸切れあり</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -6294,12 +6282,12 @@
       <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/ba79db36-23e8-1a8a-1ad9-a5809c1109be.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/8bf2f649-5d15-2afc-2f36-84e0ac2f513e.json</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>ba79db36-23e8-1a8a-1ad9-a5809c1109be</t>
+          <t>8bf2f649-5d15-2afc-2f36-84e0ac2f513e</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
@@ -6309,7 +6297,7 @@
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/ba79db36-23e8-1a8a-1ad9-a5809c1109be</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/8bf2f649-5d15-2afc-2f36-84e0ac2f513e</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
@@ -6319,12 +6307,12 @@
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/0dbc6905fbe6d7441026c6ec7f4092a564cd7606.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/5841d5cb8d9895d0b483a2f842afc32f67e1719b.jpg</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296166</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296171</t>
         </is>
       </c>
       <c r="W48" t="inlineStr">
@@ -6347,7 +6335,7 @@
       <c r="AB48" t="inlineStr"/>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/ba79db36-23e8-1a8a-1ad9-a5809c1109be/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/8bf2f649-5d15-2afc-2f36-84e0ac2f513e/manifest</t>
         </is>
       </c>
       <c r="AD48" t="inlineStr"/>
@@ -6355,29 +6343,29 @@
       <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="inlineStr"/>
       <c r="AH48" t="n">
-        <v>54</v>
+        <v>47</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>和漢朗詠集 2巻 [2]</t>
+          <t>日本廿四孝 6巻 [4]</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>A00:4081</t>
+          <t>A00:4084</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ワカン ロウエイシュウ</t>
+          <t>ヤマト ニジュウシコウ</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>藤原 公任</t>
+          <t>浅井 了意</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -6393,14 +6381,14 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
-          <t>写本|書名は目首及び題簽による|外箱の書名: 御本|責任表示は『日本古典籍総合目録データベース』による|巻上: 春, 夏, 秋, 冬. 巻下: 雜|題簽による巻冊次表示: 上, 下|毎半帖8行|漢字平仮名交じり文|鳳凰菱繋ぎ文様緞子表紙, 松葉散しに山雲の金箔見返し, 金泥下絵鳥の子紙を使用|列帖装|二重箱入り</t>
+          <t>写本|書名は目首及び題簽による|内箱の書名: 大和廿四孝|外箱の書名: 御本|責任表示は『日本古典籍総合目録データベース』による|1: 第1-4. 2: 第5-8. 3: 第9-12. 4: 第13-16. 5: 第17-20. 6: 第21-24|毎半帖10行|漢字平仮名交じり文|奈良絵本|梅唐草文様緞子表紙, 松葉散しに山雲の金箔見返し, 金泥下絵鳥の子紙を使用|列帖装|竪本|二重箱入り|糸切れあり</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -6416,12 +6404,12 @@
       <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/a241b0e6-90d9-46db-1fe8-bf35f1e616c5.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/59c5b4a7-529d-5e9f-454f-8879e85023eb.json</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>a241b0e6-90d9-46db-1fe8-bf35f1e616c5</t>
+          <t>59c5b4a7-529d-5e9f-454f-8879e85023eb</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
@@ -6431,7 +6419,7 @@
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/a241b0e6-90d9-46db-1fe8-bf35f1e616c5</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/59c5b4a7-529d-5e9f-454f-8879e85023eb</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
@@ -6441,12 +6429,12 @@
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/f46b1242e2b77ba4f0d99feac20562f5cd3a0ee2.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/e4d2c0aa6489eb2a071834a4a14714fecb372bce.jpg</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296167</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296172</t>
         </is>
       </c>
       <c r="W49" t="inlineStr">
@@ -6469,7 +6457,7 @@
       <c r="AB49" t="inlineStr"/>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/a241b0e6-90d9-46db-1fe8-bf35f1e616c5/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/59c5b4a7-529d-5e9f-454f-8879e85023eb/manifest</t>
         </is>
       </c>
       <c r="AD49" t="inlineStr"/>
@@ -6477,29 +6465,29 @@
       <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="inlineStr"/>
       <c r="AH49" t="n">
-        <v>48</v>
+        <v>76</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>つれつれ草</t>
+          <t>日本廿四孝 6巻 [5]</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>A00:4082</t>
+          <t>A00:4084</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>ツレズレグサ</t>
+          <t>ヤマト ニジュウシコウ</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>吉田 兼好</t>
+          <t>浅井 了意</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -6515,14 +6503,14 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr">
         <is>
-          <t>写本|書名は題簽による|書名の繰返し部分は踊り字|外箱の書名: 御本|責任表示は『日本古典籍総合目録データベース』による|毎半帖10行|漢字平仮名交じり文|花草窠文様緞子表紙, 松葉散しに山雲の金箔見返し, 金泥下絵鳥の子紙を使用|列帖装|二重箱入り</t>
+          <t>写本|書名は目首及び題簽による|内箱の書名: 大和廿四孝|外箱の書名: 御本|責任表示は『日本古典籍総合目録データベース』による|1: 第1-4. 2: 第5-8. 3: 第9-12. 4: 第13-16. 5: 第17-20. 6: 第21-24|毎半帖10行|漢字平仮名交じり文|奈良絵本|梅唐草文様緞子表紙, 松葉散しに山雲の金箔見返し, 金泥下絵鳥の子紙を使用|列帖装|竪本|二重箱入り|糸切れあり</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -6538,12 +6526,12 @@
       <c r="O50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/d19a62f6-4729-0ee3-3ea7-08f573851a48.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/ff7eb5a9-8bd0-64c0-3cbf-03a54ac07e65.json</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>d19a62f6-4729-0ee3-3ea7-08f573851a48</t>
+          <t>ff7eb5a9-8bd0-64c0-3cbf-03a54ac07e65</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
@@ -6553,7 +6541,7 @@
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/d19a62f6-4729-0ee3-3ea7-08f573851a48</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/ff7eb5a9-8bd0-64c0-3cbf-03a54ac07e65</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
@@ -6563,12 +6551,12 @@
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/7966b7312c84644ee577a0390937964b1989586d.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/550abdb28c4a764b0c1330b7551c32cee807416f.jpg</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296168</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296173</t>
         </is>
       </c>
       <c r="W50" t="inlineStr">
@@ -6591,7 +6579,7 @@
       <c r="AB50" t="inlineStr"/>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/d19a62f6-4729-0ee3-3ea7-08f573851a48/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/ff7eb5a9-8bd0-64c0-3cbf-03a54ac07e65/manifest</t>
         </is>
       </c>
       <c r="AD50" t="inlineStr"/>
@@ -6599,13 +6587,13 @@
       <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="inlineStr"/>
       <c r="AH50" t="n">
-        <v>142</v>
+        <v>87</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>日本廿四孝 6巻 [1]</t>
+          <t>日本廿四孝 6巻 [6]</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -6660,12 +6648,12 @@
       <c r="O51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/bf17bb0e-6d63-718e-218b-614134ee011d.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/0106be3f-16cb-3945-1c3c-419a27f26c16.json</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>bf17bb0e-6d63-718e-218b-614134ee011d</t>
+          <t>0106be3f-16cb-3945-1c3c-419a27f26c16</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
@@ -6675,7 +6663,7 @@
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/bf17bb0e-6d63-718e-218b-614134ee011d</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/0106be3f-16cb-3945-1c3c-419a27f26c16</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
@@ -6685,12 +6673,12 @@
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/2c48d85abc93bce026f680cc699c748fb0a877e2.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/b1c4cf868676ac5b8b2f574249475349a7a90813.jpg</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296169</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296174</t>
         </is>
       </c>
       <c r="W51" t="inlineStr">
@@ -6713,7 +6701,7 @@
       <c r="AB51" t="inlineStr"/>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/bf17bb0e-6d63-718e-218b-614134ee011d/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/0106be3f-16cb-3945-1c3c-419a27f26c16/manifest</t>
         </is>
       </c>
       <c r="AD51" t="inlineStr"/>
@@ -6721,29 +6709,29 @@
       <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="inlineStr"/>
       <c r="AH51" t="n">
-        <v>47</v>
+        <v>70</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>日本廿四孝 6巻 [2]</t>
+          <t>京ものかたり</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>A00:4084</t>
+          <t>A00:4085</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>ヤマト ニジュウシコウ</t>
+          <t>キョウモノガタリ</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>浅井 了意</t>
+          <t>洛陽散人</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -6759,14 +6747,14 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr">
         <is>
-          <t>写本|書名は目首及び題簽による|内箱の書名: 大和廿四孝|外箱の書名: 御本|責任表示は『日本古典籍総合目録データベース』による|1: 第1-4. 2: 第5-8. 3: 第9-12. 4: 第13-16. 5: 第17-20. 6: 第21-24|毎半帖10行|漢字平仮名交じり文|奈良絵本|梅唐草文様緞子表紙, 松葉散しに山雲の金箔見返し, 金泥下絵鳥の子紙を使用|列帖装|竪本|二重箱入り|糸切れあり</t>
+          <t>写本|書名は題簽による|[跋]中の書名: 見ぬ京ものかたり|外箱の書名: 御本|[跋]に「万治元年の秋夜長きひ ... いぬの年九月の末のはふのなん時 洛陽散人たれ某」とあり|内容: 儒佛の論, など|毎半帖10行|漢字平仮名交じり文|桜唐草文様緞子表紙, 松葉散しに山雲の金箔見返し, 金泥下絵鳥の子紙を使用|列帖装|二重箱入り</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -6782,12 +6770,12 @@
       <c r="O52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/c2996e14-8070-09ae-328a-159e60d17016.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/13969a60-692e-663a-3a83-97b8168b8fbe.json</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>c2996e14-8070-09ae-328a-159e60d17016</t>
+          <t>13969a60-692e-663a-3a83-97b8168b8fbe</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
@@ -6797,7 +6785,7 @@
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/c2996e14-8070-09ae-328a-159e60d17016</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/13969a60-692e-663a-3a83-97b8168b8fbe</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
@@ -6807,12 +6795,12 @@
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/27ba12aa7661321f36193a30b8d8ffb8b32e574c.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/b4c216cdd7c363c063be4e90de6eea21dd1da6e3.jpg</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296170</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296175</t>
         </is>
       </c>
       <c r="W52" t="inlineStr">
@@ -6835,7 +6823,7 @@
       <c r="AB52" t="inlineStr"/>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/c2996e14-8070-09ae-328a-159e60d17016/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/13969a60-692e-663a-3a83-97b8168b8fbe/manifest</t>
         </is>
       </c>
       <c r="AD52" t="inlineStr"/>
@@ -6843,52 +6831,52 @@
       <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="inlineStr"/>
       <c r="AH52" t="n">
-        <v>103</v>
+        <v>68</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>日本廿四孝 6巻 [3]</t>
+          <t>北遊漫録 3巻再1巻 [1]</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>A00:4084</t>
+          <t>A00:4099</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>ヤマト ニジュウシコウ</t>
+          <t>ホクユウ マンロク</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>浅井 了意</t>
+          <t>久保田 米僊</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>[書写者不明]</t>
+          <t>久保田米僊 [自筆]</t>
         </is>
       </c>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr">
         <is>
-          <t>[江戸前期]</t>
+          <t>明治21 [1888]-明治24 [1891]</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr">
         <is>
-          <t>写本|書名は目首及び題簽による|内箱の書名: 大和廿四孝|外箱の書名: 御本|責任表示は『日本古典籍総合目録データベース』による|1: 第1-4. 2: 第5-8. 3: 第9-12. 4: 第13-16. 5: 第17-20. 6: 第21-24|毎半帖10行|漢字平仮名交じり文|奈良絵本|梅唐草文様緞子表紙, 松葉散しに山雲の金箔見返し, 金泥下絵鳥の子紙を使用|列帖装|竪本|二重箱入り|糸切れあり</t>
+          <t>写本|書名は扉による|帙題簽に「久保田米僊草稿」とあり|扉に「明治廿一年はる五月」(乾), 「明治廿一年はる六月」(坤), 「明治廿一年はる六月中澣」(瑞啚), 「明治廿四年五月十九日」(再)とあり|乾末に「増補考古畫譜五巻 發兌書肆 有隣堂」とあり|おもに図版|彩色あり|双葉装|印記: 「田寛之印」, 「山脊与弥との」</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -6904,12 +6892,12 @@
       <c r="O53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/8bf2f649-5d15-2afc-2f36-84e0ac2f513e.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/fdb2f4c7-47bb-0fc6-53e6-e8ffb5796046.json</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>8bf2f649-5d15-2afc-2f36-84e0ac2f513e</t>
+          <t>fdb2f4c7-47bb-0fc6-53e6-e8ffb5796046</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
@@ -6919,7 +6907,7 @@
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/8bf2f649-5d15-2afc-2f36-84e0ac2f513e</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/fdb2f4c7-47bb-0fc6-53e6-e8ffb5796046</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
@@ -6929,12 +6917,12 @@
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/5841d5cb8d9895d0b483a2f842afc32f67e1719b.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/789ef89fb4fc813de5d276f3c43f982c6760d60b.jpg</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296171</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296176</t>
         </is>
       </c>
       <c r="W53" t="inlineStr">
@@ -6957,7 +6945,7 @@
       <c r="AB53" t="inlineStr"/>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/8bf2f649-5d15-2afc-2f36-84e0ac2f513e/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/fdb2f4c7-47bb-0fc6-53e6-e8ffb5796046/manifest</t>
         </is>
       </c>
       <c r="AD53" t="inlineStr"/>
@@ -6965,52 +6953,52 @@
       <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="inlineStr"/>
       <c r="AH53" t="n">
-        <v>47</v>
+        <v>31</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>日本廿四孝 6巻 [4]</t>
+          <t>北遊漫録 3巻再1巻 [2]</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>A00:4084</t>
+          <t>A00:4099</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>ヤマト ニジュウシコウ</t>
+          <t>ホクユウ マンロク</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>浅井 了意</t>
+          <t>久保田 米僊</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>[書写者不明]</t>
+          <t>久保田米僊 [自筆]</t>
         </is>
       </c>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr">
         <is>
-          <t>[江戸前期]</t>
+          <t>明治21 [1888]-明治24 [1891]</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr">
         <is>
-          <t>写本|書名は目首及び題簽による|内箱の書名: 大和廿四孝|外箱の書名: 御本|責任表示は『日本古典籍総合目録データベース』による|1: 第1-4. 2: 第5-8. 3: 第9-12. 4: 第13-16. 5: 第17-20. 6: 第21-24|毎半帖10行|漢字平仮名交じり文|奈良絵本|梅唐草文様緞子表紙, 松葉散しに山雲の金箔見返し, 金泥下絵鳥の子紙を使用|列帖装|竪本|二重箱入り|糸切れあり</t>
+          <t>写本|書名は扉による|帙題簽に「久保田米僊草稿」とあり|扉に「明治廿一年はる五月」(乾), 「明治廿一年はる六月」(坤), 「明治廿一年はる六月中澣」(瑞啚), 「明治廿四年五月十九日」(再)とあり|乾末に「増補考古畫譜五巻 發兌書肆 有隣堂」とあり|おもに図版|彩色あり|双葉装|印記: 「田寛之印」, 「山脊与弥との」</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -7026,12 +7014,12 @@
       <c r="O54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/59c5b4a7-529d-5e9f-454f-8879e85023eb.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/01f5e469-1d82-36bd-3e33-34c56a942a2d.json</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>59c5b4a7-529d-5e9f-454f-8879e85023eb</t>
+          <t>01f5e469-1d82-36bd-3e33-34c56a942a2d</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
@@ -7041,7 +7029,7 @@
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/59c5b4a7-529d-5e9f-454f-8879e85023eb</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/01f5e469-1d82-36bd-3e33-34c56a942a2d</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
@@ -7051,12 +7039,12 @@
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/e4d2c0aa6489eb2a071834a4a14714fecb372bce.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/0e331722b5a82ea48f273a6b7465d2784dc8a44c.jpg</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296172</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296177</t>
         </is>
       </c>
       <c r="W54" t="inlineStr">
@@ -7079,7 +7067,7 @@
       <c r="AB54" t="inlineStr"/>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/59c5b4a7-529d-5e9f-454f-8879e85023eb/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/01f5e469-1d82-36bd-3e33-34c56a942a2d/manifest</t>
         </is>
       </c>
       <c r="AD54" t="inlineStr"/>
@@ -7087,52 +7075,52 @@
       <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="inlineStr"/>
       <c r="AH54" t="n">
-        <v>76</v>
+        <v>31</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>日本廿四孝 6巻 [5]</t>
+          <t>北遊漫録 3巻再1巻 [3]</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>A00:4084</t>
+          <t>A00:4099</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>ヤマト ニジュウシコウ</t>
+          <t>ホクユウ マンロク</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>浅井 了意</t>
+          <t>久保田 米僊</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>[書写者不明]</t>
+          <t>久保田米僊 [自筆]</t>
         </is>
       </c>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr">
         <is>
-          <t>[江戸前期]</t>
+          <t>明治21 [1888]-明治24 [1891]</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr">
         <is>
-          <t>写本|書名は目首及び題簽による|内箱の書名: 大和廿四孝|外箱の書名: 御本|責任表示は『日本古典籍総合目録データベース』による|1: 第1-4. 2: 第5-8. 3: 第9-12. 4: 第13-16. 5: 第17-20. 6: 第21-24|毎半帖10行|漢字平仮名交じり文|奈良絵本|梅唐草文様緞子表紙, 松葉散しに山雲の金箔見返し, 金泥下絵鳥の子紙を使用|列帖装|竪本|二重箱入り|糸切れあり</t>
+          <t>写本|書名は扉による|帙題簽に「久保田米僊草稿」とあり|扉に「明治廿一年はる五月」(乾), 「明治廿一年はる六月」(坤), 「明治廿一年はる六月中澣」(瑞啚), 「明治廿四年五月十九日」(再)とあり|乾末に「増補考古畫譜五巻 發兌書肆 有隣堂」とあり|おもに図版|彩色あり|双葉装|印記: 「田寛之印」, 「山脊与弥との」</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -7148,12 +7136,12 @@
       <c r="O55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/ff7eb5a9-8bd0-64c0-3cbf-03a54ac07e65.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/1a4a12a3-0ae7-8858-3851-f3845f60709b.json</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>ff7eb5a9-8bd0-64c0-3cbf-03a54ac07e65</t>
+          <t>1a4a12a3-0ae7-8858-3851-f3845f60709b</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
@@ -7163,7 +7151,7 @@
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/ff7eb5a9-8bd0-64c0-3cbf-03a54ac07e65</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/1a4a12a3-0ae7-8858-3851-f3845f60709b</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
@@ -7173,12 +7161,12 @@
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/550abdb28c4a764b0c1330b7551c32cee807416f.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/3897bac3ffa751a75c02bb59922c185ca93a9f1e.jpg</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296173</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296178</t>
         </is>
       </c>
       <c r="W55" t="inlineStr">
@@ -7201,7 +7189,7 @@
       <c r="AB55" t="inlineStr"/>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/ff7eb5a9-8bd0-64c0-3cbf-03a54ac07e65/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/1a4a12a3-0ae7-8858-3851-f3845f60709b/manifest</t>
         </is>
       </c>
       <c r="AD55" t="inlineStr"/>
@@ -7209,52 +7197,52 @@
       <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="inlineStr"/>
       <c r="AH55" t="n">
-        <v>87</v>
+        <v>31</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>日本廿四孝 6巻 [6]</t>
+          <t>北遊漫録 3巻再1巻 [4]</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>A00:4084</t>
+          <t>A00:4099</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>ヤマト ニジュウシコウ</t>
+          <t>ホクユウ マンロク</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>浅井 了意</t>
+          <t>久保田 米僊</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>[書写者不明]</t>
+          <t>久保田米僊 [自筆]</t>
         </is>
       </c>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr">
         <is>
-          <t>[江戸前期]</t>
+          <t>明治21 [1888]-明治24 [1891]</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr">
         <is>
-          <t>写本|書名は目首及び題簽による|内箱の書名: 大和廿四孝|外箱の書名: 御本|責任表示は『日本古典籍総合目録データベース』による|1: 第1-4. 2: 第5-8. 3: 第9-12. 4: 第13-16. 5: 第17-20. 6: 第21-24|毎半帖10行|漢字平仮名交じり文|奈良絵本|梅唐草文様緞子表紙, 松葉散しに山雲の金箔見返し, 金泥下絵鳥の子紙を使用|列帖装|竪本|二重箱入り|糸切れあり</t>
+          <t>写本|書名は扉による|帙題簽に「久保田米僊草稿」とあり|扉に「明治廿一年はる五月」(乾), 「明治廿一年はる六月」(坤), 「明治廿一年はる六月中澣」(瑞啚), 「明治廿四年五月十九日」(再)とあり|乾末に「増補考古畫譜五巻 發兌書肆 有隣堂」とあり|おもに図版|彩色あり|双葉装|印記: 「田寛之印」, 「山脊与弥との」</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -7270,12 +7258,12 @@
       <c r="O56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/0106be3f-16cb-3945-1c3c-419a27f26c16.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/73cbda29-23d4-a760-5213-0395cd767491.json</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>0106be3f-16cb-3945-1c3c-419a27f26c16</t>
+          <t>73cbda29-23d4-a760-5213-0395cd767491</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
@@ -7285,7 +7273,7 @@
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/0106be3f-16cb-3945-1c3c-419a27f26c16</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/73cbda29-23d4-a760-5213-0395cd767491</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
@@ -7295,12 +7283,12 @@
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/b1c4cf868676ac5b8b2f574249475349a7a90813.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/74a9af6c2a682e260aa96f2ded5a07abfcd3098c.jpg</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296174</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296179</t>
         </is>
       </c>
       <c r="W56" t="inlineStr">
@@ -7323,7 +7311,7 @@
       <c r="AB56" t="inlineStr"/>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/0106be3f-16cb-3945-1c3c-419a27f26c16/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/73cbda29-23d4-a760-5213-0395cd767491/manifest</t>
         </is>
       </c>
       <c r="AD56" t="inlineStr"/>
@@ -7331,40 +7319,36 @@
       <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="inlineStr"/>
       <c r="AH56" t="n">
-        <v>70</v>
+        <v>22</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>京ものかたり</t>
+          <t>蘭主之書翰使節持参叅途中之図</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>A00:4085</t>
+          <t>A00:4146</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>キョウモノガタリ</t>
+          <t>ランシュ ノ ショカン シセツ ジサン トチュウ ノ ズ</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>洛陽散人</t>
-        </is>
-      </c>
+      <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
-          <t>[書写者不明]</t>
+          <t>[製作者不明]</t>
         </is>
       </c>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr">
         <is>
-          <t>[江戸前期]</t>
+          <t>天保15 [1844] 識語</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -7376,7 +7360,7 @@
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr">
         <is>
-          <t>写本|書名は題簽による|[跋]中の書名: 見ぬ京ものかたり|外箱の書名: 御本|[跋]に「万治元年の秋夜長きひ ... いぬの年九月の末のはふのなん時 洛陽散人たれ某」とあり|内容: 儒佛の論, など|毎半帖10行|漢字平仮名交じり文|桜唐草文様緞子表紙, 松葉散しに山雲の金箔見返し, 金泥下絵鳥の子紙を使用|列帖装|二重箱入り</t>
+          <t>書名は題簽による|箱の書名: 和蘭國軍艦人物兵器等図|冒頭に「天保十五年甲辰秋七月二日和蘭國官船奉其主命来進於我﨑嶴茲掲略圖摸其全般及内面結構所備之諸兵器等」との識語あり|絵巻|彩色あり|印記: 「籌海庫」</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -7392,12 +7376,12 @@
       <c r="O57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/13969a60-692e-663a-3a83-97b8168b8fbe.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/ca3ac8e1-6c03-5832-3987-70b1fa71258a.json</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>13969a60-692e-663a-3a83-97b8168b8fbe</t>
+          <t>ca3ac8e1-6c03-5832-3987-70b1fa71258a</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
@@ -7407,7 +7391,7 @@
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/13969a60-692e-663a-3a83-97b8168b8fbe</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/ca3ac8e1-6c03-5832-3987-70b1fa71258a</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
@@ -7417,12 +7401,12 @@
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/b4c216cdd7c363c063be4e90de6eea21dd1da6e3.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/32f72c2d68d9e56e4f46528e6997cbb4c330cc23.jpg</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296175</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296180</t>
         </is>
       </c>
       <c r="W57" t="inlineStr">
@@ -7445,7 +7429,7 @@
       <c r="AB57" t="inlineStr"/>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/13969a60-692e-663a-3a83-97b8168b8fbe/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/ca3ac8e1-6c03-5832-3987-70b1fa71258a/manifest</t>
         </is>
       </c>
       <c r="AD57" t="inlineStr"/>
@@ -7453,52 +7437,48 @@
       <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="inlineStr"/>
       <c r="AH57" t="n">
-        <v>68</v>
+        <v>22</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>北遊漫録 3巻再1巻 [1]</t>
+          <t>喎蘭軍艦プレカット並銃劍等之図</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>A00:4099</t>
+          <t>A00:4147</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>ホクユウ マンロク</t>
+          <t>オランダ グンカン プレカット ナラビニ ジュウケン トウ ノ ズ</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>久保田 米僊</t>
-        </is>
-      </c>
+      <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
-          <t>久保田米僊 [自筆]</t>
+          <t>[製作者不明]</t>
         </is>
       </c>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr">
         <is>
-          <t>明治21 [1888]-明治24 [1891]</t>
+          <t>[天保弘化年間]</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr">
         <is>
-          <t>写本|書名は扉による|帙題簽に「久保田米僊草稿」とあり|扉に「明治廿一年はる五月」(乾), 「明治廿一年はる六月」(坤), 「明治廿一年はる六月中澣」(瑞啚), 「明治廿四年五月十九日」(再)とあり|乾末に「増補考古畫譜五巻 發兌書肆 有隣堂」とあり|おもに図版|彩色あり|双葉装|印記: 「田寛之印」, 「山脊与弥との」</t>
+          <t>書名は題簽による|箱の書名: 和蘭國軍艦人物兵器等図|巻末に「圖説」あり|絵巻|彩色あり</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -7514,12 +7494,12 @@
       <c r="O58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/fdb2f4c7-47bb-0fc6-53e6-e8ffb5796046.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/8509e124-5c2f-173b-2502-4d9cd27f9f85.json</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>fdb2f4c7-47bb-0fc6-53e6-e8ffb5796046</t>
+          <t>8509e124-5c2f-173b-2502-4d9cd27f9f85</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
@@ -7529,7 +7509,7 @@
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/fdb2f4c7-47bb-0fc6-53e6-e8ffb5796046</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/8509e124-5c2f-173b-2502-4d9cd27f9f85</t>
         </is>
       </c>
       <c r="T58" t="inlineStr">
@@ -7539,12 +7519,12 @@
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/789ef89fb4fc813de5d276f3c43f982c6760d60b.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/18d2fe489472e7f697dd92568da44185793c8f4d.jpg</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296176</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296181</t>
         </is>
       </c>
       <c r="W58" t="inlineStr">
@@ -7567,7 +7547,7 @@
       <c r="AB58" t="inlineStr"/>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/fdb2f4c7-47bb-0fc6-53e6-e8ffb5796046/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/8509e124-5c2f-173b-2502-4d9cd27f9f85/manifest</t>
         </is>
       </c>
       <c r="AD58" t="inlineStr"/>
@@ -7575,52 +7555,48 @@
       <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="inlineStr"/>
       <c r="AH58" t="n">
-        <v>31</v>
+        <v>17</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>北遊漫録 3巻再1巻 [2]</t>
+          <t>能面圗譜</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>A00:4099</t>
+          <t>A00:4269</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>ホクユウ マンロク</t>
+          <t>ノウメン ズフ</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>久保田 米僊</t>
-        </is>
-      </c>
+      <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>久保田米僊 [自筆]</t>
+          <t>[製作者不明]</t>
         </is>
       </c>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr">
         <is>
-          <t>明治21 [1888]-明治24 [1891]</t>
+          <t>[江戸中期以降]</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr">
         <is>
-          <t>写本|書名は扉による|帙題簽に「久保田米僊草稿」とあり|扉に「明治廿一年はる五月」(乾), 「明治廿一年はる六月」(坤), 「明治廿一年はる六月中澣」(瑞啚), 「明治廿四年五月十九日」(再)とあり|乾末に「増補考古畫譜五巻 發兌書肆 有隣堂」とあり|おもに図版|彩色あり|双葉装|印記: 「田寛之印」, 「山脊与弥との」</t>
+          <t>折本|書名は題簽(墨書)による|帙題簽の書名(墨書): 能面圖譜|絹本彩色|図42幅|本紙: 16×13cm|金切箔散し料紙, 福寿文字布目地表紙を使用</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -7636,12 +7612,12 @@
       <c r="O59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/01f5e469-1d82-36bd-3e33-34c56a942a2d.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/8b3019c4-7584-208c-0c75-7c855ddc0b9e.json</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>01f5e469-1d82-36bd-3e33-34c56a942a2d</t>
+          <t>8b3019c4-7584-208c-0c75-7c855ddc0b9e</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
@@ -7651,7 +7627,7 @@
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/01f5e469-1d82-36bd-3e33-34c56a942a2d</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/8b3019c4-7584-208c-0c75-7c855ddc0b9e</t>
         </is>
       </c>
       <c r="T59" t="inlineStr">
@@ -7661,12 +7637,12 @@
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/0e331722b5a82ea48f273a6b7465d2784dc8a44c.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/3109e43cd273e3e02f2a227b4f1053cc1d4558bb.jpg</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296177</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296182</t>
         </is>
       </c>
       <c r="W59" t="inlineStr">
@@ -7689,7 +7665,7 @@
       <c r="AB59" t="inlineStr"/>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/01f5e469-1d82-36bd-3e33-34c56a942a2d/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/8b3019c4-7584-208c-0c75-7c855ddc0b9e/manifest</t>
         </is>
       </c>
       <c r="AD59" t="inlineStr"/>
@@ -7697,52 +7673,52 @@
       <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="inlineStr"/>
       <c r="AH59" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>北遊漫録 3巻再1巻 [3]</t>
+          <t>法蕐經集驗記 2巻</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>A00:4099</t>
+          <t>A00:4273</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>ホクユウ マンロク</t>
+          <t>ホケキョウ シュウゲンキ</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>久保田 米僊</t>
+          <t>義寂</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>久保田米僊 [自筆]</t>
+          <t>[書写者不明]</t>
         </is>
       </c>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr">
         <is>
-          <t>明治21 [1888]-明治24 [1891]</t>
+          <t>[平安時代]</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr">
         <is>
-          <t>写本|書名は扉による|帙題簽に「久保田米僊草稿」とあり|扉に「明治廿一年はる五月」(乾), 「明治廿一年はる六月」(坤), 「明治廿一年はる六月中澣」(瑞啚), 「明治廿四年五月十九日」(再)とあり|乾末に「増補考古畫譜五巻 發兌書肆 有隣堂」とあり|おもに図版|彩色あり|双葉装|印記: 「田寛之印」, 「山脊与弥との」</t>
+          <t>鈔本|書名は卷下の巻頭による|大尾の書名: 法蕐集驗記|後付題簽の書名: 法花經集驗記|箱の書名: 法華驗記|卷下の内題下に「并序沙門寂撰」とあり|奥書に「護持僧(花押)夲之」とあり|巻末識語に「嘉應二年庚寅二月十八日傳得之釈子有慶在判」, 「十帋半」とあり|卷上: 諷誦第1. 卷下: 轉讀第2, 書寫第3, 聽聞第4|巻子本|訓点付|卷上の巻頭を欠損|原十紙半を1軸に合綴|朱筆書き入れあり|破損, 虫損あり (裏打ち補修あり)</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -7758,12 +7734,12 @@
       <c r="O60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/1a4a12a3-0ae7-8858-3851-f3845f60709b.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/ec4bceb1-0ab9-74c7-0dc7-f90d0a98a66e.json</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>1a4a12a3-0ae7-8858-3851-f3845f60709b</t>
+          <t>ec4bceb1-0ab9-74c7-0dc7-f90d0a98a66e</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
@@ -7773,7 +7749,7 @@
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/1a4a12a3-0ae7-8858-3851-f3845f60709b</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/ec4bceb1-0ab9-74c7-0dc7-f90d0a98a66e</t>
         </is>
       </c>
       <c r="T60" t="inlineStr">
@@ -7783,12 +7759,12 @@
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/3897bac3ffa751a75c02bb59922c185ca93a9f1e.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/d1c457097d78f2d8a4b38eebd630ef233026cc5e.jpg</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296178</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296183</t>
         </is>
       </c>
       <c r="W60" t="inlineStr">
@@ -7811,7 +7787,7 @@
       <c r="AB60" t="inlineStr"/>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/1a4a12a3-0ae7-8858-3851-f3845f60709b/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/ec4bceb1-0ab9-74c7-0dc7-f90d0a98a66e/manifest</t>
         </is>
       </c>
       <c r="AD60" t="inlineStr"/>
@@ -7819,52 +7795,48 @@
       <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="inlineStr"/>
       <c r="AH60" t="n">
-        <v>31</v>
+        <v>19</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>北遊漫録 3巻再1巻 [4]</t>
+          <t>道成寺</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>A00:4099</t>
+          <t>A00:4276</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>ホクユウ マンロク</t>
+          <t>ドウジョウジ</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>久保田 米僊</t>
-        </is>
-      </c>
+      <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
-          <t>久保田米僊 [自筆]</t>
+          <t>[製作者不明]</t>
         </is>
       </c>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr">
         <is>
-          <t>明治21 [1888]-明治24 [1891]</t>
+          <t>天明2 [1782] 識語</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr">
         <is>
-          <t>写本|書名は扉による|帙題簽に「久保田米僊草稿」とあり|扉に「明治廿一年はる五月」(乾), 「明治廿一年はる六月」(坤), 「明治廿一年はる六月中澣」(瑞啚), 「明治廿四年五月十九日」(再)とあり|乾末に「増補考古畫譜五巻 發兌書肆 有隣堂」とあり|おもに図版|彩色あり|双葉装|印記: 「田寛之印」, 「山脊与弥との」</t>
+          <t>書名は識語による|巻末識語に「道成寺建立年号大長五年三月吉日以後于二百三拾年去テ延長六戊子暦八月十日鐘巻也」, 「時天明二壬寅十月 尚良書之」とあり|絵巻|紙本著色|彩色あり|本紙: 855×28cm|界高: 25.8cm|軸物|軸頭欠損あり|印記: 「尚良印」|破損あり (裏打ち補修あり)</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -7880,12 +7852,12 @@
       <c r="O61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/73cbda29-23d4-a760-5213-0395cd767491.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/79185d0c-7fa3-2efd-863e-93927e137a23.json</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>73cbda29-23d4-a760-5213-0395cd767491</t>
+          <t>79185d0c-7fa3-2efd-863e-93927e137a23</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
@@ -7895,7 +7867,7 @@
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/73cbda29-23d4-a760-5213-0395cd767491</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/79185d0c-7fa3-2efd-863e-93927e137a23</t>
         </is>
       </c>
       <c r="T61" t="inlineStr">
@@ -7905,12 +7877,12 @@
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/74a9af6c2a682e260aa96f2ded5a07abfcd3098c.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/0c47939e767d716fe085cc41c86d91be28f9df1a.jpg</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296179</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296184</t>
         </is>
       </c>
       <c r="W61" t="inlineStr">
@@ -7933,7 +7905,7 @@
       <c r="AB61" t="inlineStr"/>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/73cbda29-23d4-a760-5213-0395cd767491/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/79185d0c-7fa3-2efd-863e-93927e137a23/manifest</t>
         </is>
       </c>
       <c r="AD61" t="inlineStr"/>
@@ -7941,48 +7913,52 @@
       <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="inlineStr"/>
       <c r="AH61" t="n">
-        <v>22</v>
+        <v>34</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>蘭主之書翰使節持参叅途中之図</t>
+          <t>名家短冊 [1]</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>A00:4146</t>
+          <t>A00:4277</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>ランシュ ノ ショカン シセツ ジサン トチュウ ノ ズ</t>
+          <t>メイカ タンザク</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>慶運</t>
+        </is>
+      </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>[製作者不明]</t>
+          <t>慶運 [ほか自筆]</t>
         </is>
       </c>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr">
         <is>
-          <t>天保15 [1844] 識語</t>
+          <t>[鎌倉時代-江戸前期]</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr">
         <is>
-          <t>書名は題簽による|箱の書名: 和蘭國軍艦人物兵器等図|冒頭に「天保十五年甲辰秋七月二日和蘭國官船奉其主命来進於我﨑嶴茲掲略圖摸其全般及内面結構所備之諸兵器等」との識語あり|絵巻|彩色あり|印記: 「籌海庫」</t>
+          <t>折本|書名及び巻冊次は題簽による|2の筆者: 慶運 牡丹花, 了流, 宗長, 兼載, 宗碩, 宗牧, 一竿, 正廣, 正般, 祖田, 堯憲, 宗二, 利盛, 増春, 了向, 榮弘, 梅雪, 宗栁, 等惠, 宗訊, 宗養, 乘阿, 兼如, 壽慶, 意運, 本阿彌光悦, 松花堂昭乘, 紹巴, 玄仍, 玄仲, 玄陳, 玄的, 里村玄祥, 昌叱, 昌琢, 昌俔, 昌程, 昌隱, 昌通|3の筆者: 祐守, 祐夏, 詮平, 直國, 興國, 隆國, 武光, 祐範, 宗純, 等貴,  順, 最嶽, 策彦, 幽之, 應其, 堯然, 尊道, 尊應, 尊朝, 道永, 弘覺, 良俊, 道増, 道應, 道興, 藤之, 立承, 性舜, 義俊, 空性, 尊譽, 揚, 道澄, 興意, 道晃|4の筆者: 有三, 他阿, 教, 尊雅, 應猷, 秀順, 可ト, 圓祐, 道順, 実如, 兼俊, 公助, 應祐, 公順, 空慶, 看世, 定信, 玄桂, 道三, 道春, 永喜, 豊永, 葉由, 常弘|2: 古筆切40枚, 極札43枚|3: 古筆切36枚, 極札36枚|4: 古筆切28枚, 極札20枚|毎半面古筆切2枚|原104枚短冊を3帖に合綴|印記: 「順」, 「最嶽」|極印: 「琴山」, 「栄」(古筆了栄)|折り目破損あり</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -7998,12 +7974,12 @@
       <c r="O62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/ca3ac8e1-6c03-5832-3987-70b1fa71258a.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/1469b736-a0ee-61aa-1e00-7a2cfa949411.json</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>ca3ac8e1-6c03-5832-3987-70b1fa71258a</t>
+          <t>1469b736-a0ee-61aa-1e00-7a2cfa949411</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
@@ -8013,7 +7989,7 @@
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/ca3ac8e1-6c03-5832-3987-70b1fa71258a</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/1469b736-a0ee-61aa-1e00-7a2cfa949411</t>
         </is>
       </c>
       <c r="T62" t="inlineStr">
@@ -8023,12 +7999,12 @@
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/32f72c2d68d9e56e4f46528e6997cbb4c330cc23.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/7693d9aa48dbd471c84817ef0239807a5e246d64.jpg</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296180</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296185</t>
         </is>
       </c>
       <c r="W62" t="inlineStr">
@@ -8051,7 +8027,7 @@
       <c r="AB62" t="inlineStr"/>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/ca3ac8e1-6c03-5832-3987-70b1fa71258a/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/1469b736-a0ee-61aa-1e00-7a2cfa949411/manifest</t>
         </is>
       </c>
       <c r="AD62" t="inlineStr"/>
@@ -8059,48 +8035,52 @@
       <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="inlineStr"/>
       <c r="AH62" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>喎蘭軍艦プレカット並銃劍等之図</t>
+          <t>名家短冊 [2]</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>A00:4147</t>
+          <t>A00:4277</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>オランダ グンカン プレカット ナラビニ ジュウケン トウ ノ ズ</t>
+          <t>メイカ タンザク</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>慶運</t>
+        </is>
+      </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>[製作者不明]</t>
+          <t>慶運 [ほか自筆]</t>
         </is>
       </c>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr">
         <is>
-          <t>[天保弘化年間]</t>
+          <t>[鎌倉時代-江戸前期]</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr">
         <is>
-          <t>書名は題簽による|箱の書名: 和蘭國軍艦人物兵器等図|巻末に「圖説」あり|絵巻|彩色あり</t>
+          <t>折本|書名及び巻冊次は題簽による|2の筆者: 慶運 牡丹花, 了流, 宗長, 兼載, 宗碩, 宗牧, 一竿, 正廣, 正般, 祖田, 堯憲, 宗二, 利盛, 増春, 了向, 榮弘, 梅雪, 宗栁, 等惠, 宗訊, 宗養, 乘阿, 兼如, 壽慶, 意運, 本阿彌光悦, 松花堂昭乘, 紹巴, 玄仍, 玄仲, 玄陳, 玄的, 里村玄祥, 昌叱, 昌琢, 昌俔, 昌程, 昌隱, 昌通|3の筆者: 祐守, 祐夏, 詮平, 直國, 興國, 隆國, 武光, 祐範, 宗純, 等貴,  順, 最嶽, 策彦, 幽之, 應其, 堯然, 尊道, 尊應, 尊朝, 道永, 弘覺, 良俊, 道増, 道應, 道興, 藤之, 立承, 性舜, 義俊, 空性, 尊譽, 揚, 道澄, 興意, 道晃|4の筆者: 有三, 他阿, 教, 尊雅, 應猷, 秀順, 可ト, 圓祐, 道順, 実如, 兼俊, 公助, 應祐, 公順, 空慶, 看世, 定信, 玄桂, 道三, 道春, 永喜, 豊永, 葉由, 常弘|2: 古筆切40枚, 極札43枚|3: 古筆切36枚, 極札36枚|4: 古筆切28枚, 極札20枚|毎半面古筆切2枚|原104枚短冊を3帖に合綴|印記: 「順」, 「最嶽」|極印: 「琴山」, 「栄」(古筆了栄)|折り目破損あり</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -8116,12 +8096,12 @@
       <c r="O63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/8509e124-5c2f-173b-2502-4d9cd27f9f85.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/53041b9e-294f-71af-3d1a-e305956f5560.json</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>8509e124-5c2f-173b-2502-4d9cd27f9f85</t>
+          <t>53041b9e-294f-71af-3d1a-e305956f5560</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
@@ -8131,7 +8111,7 @@
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/8509e124-5c2f-173b-2502-4d9cd27f9f85</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/53041b9e-294f-71af-3d1a-e305956f5560</t>
         </is>
       </c>
       <c r="T63" t="inlineStr">
@@ -8141,12 +8121,12 @@
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/18d2fe489472e7f697dd92568da44185793c8f4d.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/11759cf221ad40925619344bacc4027d06e015ce.jpg</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296181</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296186</t>
         </is>
       </c>
       <c r="W63" t="inlineStr">
@@ -8169,7 +8149,7 @@
       <c r="AB63" t="inlineStr"/>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/8509e124-5c2f-173b-2502-4d9cd27f9f85/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/53041b9e-294f-71af-3d1a-e305956f5560/manifest</t>
         </is>
       </c>
       <c r="AD63" t="inlineStr"/>
@@ -8177,48 +8157,52 @@
       <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="inlineStr"/>
       <c r="AH63" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>能面圗譜</t>
+          <t>名家短冊 [3]</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>A00:4269</t>
+          <t>A00:4277</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>ノウメン ズフ</t>
+          <t>メイカ タンザク</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>慶運</t>
+        </is>
+      </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>[製作者不明]</t>
+          <t>慶運 [ほか自筆]</t>
         </is>
       </c>
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr">
         <is>
-          <t>[江戸中期以降]</t>
+          <t>[鎌倉時代-江戸前期]</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr">
         <is>
-          <t>折本|書名は題簽(墨書)による|帙題簽の書名(墨書): 能面圖譜|絹本彩色|図42幅|本紙: 16×13cm|金切箔散し料紙, 福寿文字布目地表紙を使用</t>
+          <t>折本|書名及び巻冊次は題簽による|2の筆者: 慶運 牡丹花, 了流, 宗長, 兼載, 宗碩, 宗牧, 一竿, 正廣, 正般, 祖田, 堯憲, 宗二, 利盛, 増春, 了向, 榮弘, 梅雪, 宗栁, 等惠, 宗訊, 宗養, 乘阿, 兼如, 壽慶, 意運, 本阿彌光悦, 松花堂昭乘, 紹巴, 玄仍, 玄仲, 玄陳, 玄的, 里村玄祥, 昌叱, 昌琢, 昌俔, 昌程, 昌隱, 昌通|3の筆者: 祐守, 祐夏, 詮平, 直國, 興國, 隆國, 武光, 祐範, 宗純, 等貴,  順, 最嶽, 策彦, 幽之, 應其, 堯然, 尊道, 尊應, 尊朝, 道永, 弘覺, 良俊, 道増, 道應, 道興, 藤之, 立承, 性舜, 義俊, 空性, 尊譽, 揚, 道澄, 興意, 道晃|4の筆者: 有三, 他阿, 教, 尊雅, 應猷, 秀順, 可ト, 圓祐, 道順, 実如, 兼俊, 公助, 應祐, 公順, 空慶, 看世, 定信, 玄桂, 道三, 道春, 永喜, 豊永, 葉由, 常弘|2: 古筆切40枚, 極札43枚|3: 古筆切36枚, 極札36枚|4: 古筆切28枚, 極札20枚|毎半面古筆切2枚|原104枚短冊を3帖に合綴|印記: 「順」, 「最嶽」|極印: 「琴山」, 「栄」(古筆了栄)|折り目破損あり</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -8234,12 +8218,12 @@
       <c r="O64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/8b3019c4-7584-208c-0c75-7c855ddc0b9e.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/3d4ceb9b-9516-779a-7ced-f893e9d93b4e.json</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>8b3019c4-7584-208c-0c75-7c855ddc0b9e</t>
+          <t>3d4ceb9b-9516-779a-7ced-f893e9d93b4e</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
@@ -8249,7 +8233,7 @@
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/8b3019c4-7584-208c-0c75-7c855ddc0b9e</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/3d4ceb9b-9516-779a-7ced-f893e9d93b4e</t>
         </is>
       </c>
       <c r="T64" t="inlineStr">
@@ -8259,12 +8243,12 @@
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/3109e43cd273e3e02f2a227b4f1053cc1d4558bb.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/8fd1defea23c7c93fc4d908835c1fea38040580e.jpg</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296182</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296187</t>
         </is>
       </c>
       <c r="W64" t="inlineStr">
@@ -8287,7 +8271,7 @@
       <c r="AB64" t="inlineStr"/>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/8b3019c4-7584-208c-0c75-7c855ddc0b9e/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/3d4ceb9b-9516-779a-7ced-f893e9d93b4e/manifest</t>
         </is>
       </c>
       <c r="AD64" t="inlineStr"/>
@@ -8295,40 +8279,40 @@
       <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="inlineStr"/>
       <c r="AH64" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>法蕐經集驗記 2巻</t>
+          <t>御成敗式目絵鈔</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>A00:4273</t>
+          <t>A00:4737</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>ホケキョウ シュウゲンキ</t>
+          <t>ゴセイバイ シキモク エショウ</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>義寂</t>
+          <t>岡本 竹籔</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>[書写者不明]</t>
+          <t>岡夲竹籔 : 松川半山 [書]</t>
         </is>
       </c>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr">
         <is>
-          <t>[平安時代]</t>
+          <t>[幕末期]</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -8340,7 +8324,7 @@
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr">
         <is>
-          <t>鈔本|書名は卷下の巻頭による|大尾の書名: 法蕐集驗記|後付題簽の書名: 法花經集驗記|箱の書名: 法華驗記|卷下の内題下に「并序沙門寂撰」とあり|奥書に「護持僧(花押)夲之」とあり|巻末識語に「嘉應二年庚寅二月十八日傳得之釈子有慶在判」, 「十帋半」とあり|卷上: 諷誦第1. 卷下: 轉讀第2, 書寫第3, 聽聞第4|巻子本|訓点付|卷上の巻頭を欠損|原十紙半を1軸に合綴|朱筆書き入れあり|破損, 虫損あり (裏打ち補修あり)</t>
+          <t>写本|序首の書名: 御成敗式目繪鈔|版心の書名: 式目繪鈔|題簽に「板下本」とあり|巻末に「筆工 岡夲竹籔/画工 松川半山」とあり(「岡本」, 「憲道」, 「義卿」, 「翠宋堂長」との落款朱印あり)|巻末広告に「山田賞月堂先生筆 無雙用文章大成 全一冊」とあり|四周単辺有界2段5行, 内匡廓: 22.3×16.4cm, 白口無魚尾|頭書あり|付訓あり</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -8356,12 +8340,12 @@
       <c r="O65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/ec4bceb1-0ab9-74c7-0dc7-f90d0a98a66e.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/463ab967-60a4-9ff1-3ef2-d2dee79b5315.json</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>ec4bceb1-0ab9-74c7-0dc7-f90d0a98a66e</t>
+          <t>463ab967-60a4-9ff1-3ef2-d2dee79b5315</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
@@ -8371,7 +8355,7 @@
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/ec4bceb1-0ab9-74c7-0dc7-f90d0a98a66e</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/463ab967-60a4-9ff1-3ef2-d2dee79b5315</t>
         </is>
       </c>
       <c r="T65" t="inlineStr">
@@ -8381,12 +8365,12 @@
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/d1c457097d78f2d8a4b38eebd630ef233026cc5e.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/e0977d9ba261ea59386ce9f5104a412a5dccaf3f.jpg</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296183</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296188</t>
         </is>
       </c>
       <c r="W65" t="inlineStr">
@@ -8409,7 +8393,7 @@
       <c r="AB65" t="inlineStr"/>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/ec4bceb1-0ab9-74c7-0dc7-f90d0a98a66e/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/463ab967-60a4-9ff1-3ef2-d2dee79b5315/manifest</t>
         </is>
       </c>
       <c r="AD65" t="inlineStr"/>
@@ -8417,36 +8401,40 @@
       <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="inlineStr"/>
       <c r="AH65" t="n">
-        <v>19</v>
+        <v>59</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>道成寺</t>
+          <t>金界入壇作法</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>A00:4276</t>
+          <t>A00:5975</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>ドウジョウジ</t>
+          <t>コンカイ ニュウダン サホウ</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>良円</t>
+        </is>
+      </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>[製作者不明]</t>
+          <t>良円 [写]</t>
         </is>
       </c>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr">
         <is>
-          <t>天明2 [1782] 識語</t>
+          <t>寛元元 [1243] 奥書</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -8458,7 +8446,7 @@
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr">
         <is>
-          <t>書名は識語による|巻末識語に「道成寺建立年号大長五年三月吉日以後于二百三拾年去テ延長六戊子暦八月十日鐘巻也」, 「時天明二壬寅十月 尚良書之」とあり|絵巻|紙本著色|彩色あり|本紙: 855×28cm|界高: 25.8cm|軸物|軸頭欠損あり|印記: 「尚良印」|破損あり (裏打ち補修あり)</t>
+          <t>写本|奥書に「寛元々年五月七日以先師法印御夲於常住護国院房以他筆書冩校點了良円」とあり|送り仮名, 返点あり|淡墨界の料紙を使用(界匡廓: 23.7×2.5cm)|貼紙あり|巻子本|箱入り|破損, 虫損あり (裏打ち補修あり)</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -8474,12 +8462,12 @@
       <c r="O66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/79185d0c-7fa3-2efd-863e-93927e137a23.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/ff6e2dd7-8128-3264-2081-15ad4e41857e.json</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>79185d0c-7fa3-2efd-863e-93927e137a23</t>
+          <t>ff6e2dd7-8128-3264-2081-15ad4e41857e</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
@@ -8489,7 +8477,7 @@
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/79185d0c-7fa3-2efd-863e-93927e137a23</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/ff6e2dd7-8128-3264-2081-15ad4e41857e</t>
         </is>
       </c>
       <c r="T66" t="inlineStr">
@@ -8499,12 +8487,12 @@
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/0c47939e767d716fe085cc41c86d91be28f9df1a.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/7e2372f45914ea75c8d903fc80f309f16238b39f.jpg</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296184</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296189</t>
         </is>
       </c>
       <c r="W66" t="inlineStr">
@@ -8527,7 +8515,7 @@
       <c r="AB66" t="inlineStr"/>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/79185d0c-7fa3-2efd-863e-93927e137a23/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/ff6e2dd7-8128-3264-2081-15ad4e41857e/manifest</t>
         </is>
       </c>
       <c r="AD66" t="inlineStr"/>
@@ -8535,52 +8523,52 @@
       <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="inlineStr"/>
       <c r="AH66" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>名家短冊 [1]</t>
+          <t>玉蘂 [1]</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>A00:4277</t>
+          <t>A00:6067</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>メイカ タンザク</t>
+          <t>ギョクズイ</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>慶運</t>
+          <t>藤原 道家</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>慶運 [ほか自筆]</t>
+          <t>野宮定基 : 久世通夏 [ほか写]</t>
         </is>
       </c>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr">
         <is>
-          <t>[鎌倉時代-江戸前期]</t>
+          <t>元禄12 [1699]-宝永3 [1706] 奥書</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr">
         <is>
-          <t>折本|書名及び巻冊次は題簽による|2の筆者: 慶運 牡丹花, 了流, 宗長, 兼載, 宗碩, 宗牧, 一竿, 正廣, 正般, 祖田, 堯憲, 宗二, 利盛, 増春, 了向, 榮弘, 梅雪, 宗栁, 等惠, 宗訊, 宗養, 乘阿, 兼如, 壽慶, 意運, 本阿彌光悦, 松花堂昭乘, 紹巴, 玄仍, 玄仲, 玄陳, 玄的, 里村玄祥, 昌叱, 昌琢, 昌俔, 昌程, 昌隱, 昌通|3の筆者: 祐守, 祐夏, 詮平, 直國, 興國, 隆國, 武光, 祐範, 宗純, 等貴,  順, 最嶽, 策彦, 幽之, 應其, 堯然, 尊道, 尊應, 尊朝, 道永, 弘覺, 良俊, 道増, 道應, 道興, 藤之, 立承, 性舜, 義俊, 空性, 尊譽, 揚, 道澄, 興意, 道晃|4の筆者: 有三, 他阿, 教, 尊雅, 應猷, 秀順, 可ト, 圓祐, 道順, 実如, 兼俊, 公助, 應祐, 公順, 空慶, 看世, 定信, 玄桂, 道三, 道春, 永喜, 豊永, 葉由, 常弘|2: 古筆切40枚, 極札43枚|3: 古筆切36枚, 極札36枚|4: 古筆切28枚, 極札20枚|毎半面古筆切2枚|原104枚短冊を3帖に合綴|印記: 「順」, 「最嶽」|極印: 「琴山」, 「栄」(古筆了栄)|折り目破損あり</t>
+          <t>写本|書名及び巻冊次は表紙による|奥中の書名: 光明峯寺禅閤道家公記, 峯禅閤記, 峯摂政記, 峯入道摂政記|承元4年の原奥書に「右即位記一卷者光明峯寺禅閤自筆正記也以件本左令吾基春卿透以写之云々加挍正之 ... 永正七年夷則上浣 從一位(花押)」とあり|奥書に「右以或人夲自常州到来令書写之彼夲端書云此冊上下卷 ... 元禄第十二暦仲夏中旬 羽林左衞中郎将藤原定基丗一才」(承元3), 「右光明峯寺禅閤道家公承元二年三月五六月八月四年二三月九月十十一十二月記は借請或人之夲自常州邊来書写之加一挍了/于時元禄第十二端午節也 左中郎将藤原定基丗才」(承元4), 「右玉蘂建暦元年少弟左中将通清朝臣助筆僅加一挍原本文字不正後来得正夲可改之者也/元禄十三年九月十日 松堂閑士(花押)丗二才」(建暦元), 「右玉蘂峯禅閤記建暦二年自二月至九月一冊以或人夲自常州邊来命家僚令書写手自加挍合了/元禄十二年五月六日 左中郎将藤原定基丗一才」(建暦2年上), 「宝永二年十月一日書写畢/承久二春玉蘂以故常州牧權中納言光圀公夲謄写之于時俗務紛擾先請慈兄源亜相公所被写也今以彼夲手自馳禿筆 余識藤(花押)丗七才/同三年二月廿五日一挍了」(承久2年上), 「右峯摂政承久二年記命傭書謄冩之手自一挍了/元禄第十二嵗次著雍単閼蕤賓中旬 羽林軍左衞中郎将藤原定基丗一才」(承久2年下), 「嘉禎四年正月二月閏二月三月四月六月玉蘂先年假借故常州牧前中納言光圀夲無剋力速遂書写之功建暦元年建暦二年下承久二年上及此卷等先献慈兄亜相君写之今及数年申復彼夲謄写之 ... 宝永三年十二月念日 参議從三位行左近衞權中将藤原朝臣定基生年卅八才」(嘉禎4年)とあり|毎半葉11行注文双行|漢文体日記|拠徳川光圀本及び中院通躬鈔本謄写|朱筆書き入れあり|印記: 「定基」(野宮定基), 「野宮書印」|虫損あり (裏打ち補修あり)</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -8596,12 +8584,12 @@
       <c r="O67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/1469b736-a0ee-61aa-1e00-7a2cfa949411.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/b13a7a09-88d0-62d3-44e5-379780395f17.json</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>1469b736-a0ee-61aa-1e00-7a2cfa949411</t>
+          <t>b13a7a09-88d0-62d3-44e5-379780395f17</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
@@ -8611,7 +8599,7 @@
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/1469b736-a0ee-61aa-1e00-7a2cfa949411</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/b13a7a09-88d0-62d3-44e5-379780395f17</t>
         </is>
       </c>
       <c r="T67" t="inlineStr">
@@ -8621,12 +8609,12 @@
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/7693d9aa48dbd471c84817ef0239807a5e246d64.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/f7ae1bd23dec8f323199a9add81e315f1a653d24.jpg</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296185</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296190</t>
         </is>
       </c>
       <c r="W67" t="inlineStr">
@@ -8649,7 +8637,7 @@
       <c r="AB67" t="inlineStr"/>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/1469b736-a0ee-61aa-1e00-7a2cfa949411/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/b13a7a09-88d0-62d3-44e5-379780395f17/manifest</t>
         </is>
       </c>
       <c r="AD67" t="inlineStr"/>
@@ -8657,52 +8645,52 @@
       <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="inlineStr"/>
       <c r="AH67" t="n">
-        <v>27</v>
+        <v>129</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>名家短冊 [2]</t>
+          <t>玉蘂 [2]</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>A00:4277</t>
+          <t>A00:6067</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>メイカ タンザク</t>
+          <t>ギョクズイ</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>慶運</t>
+          <t>藤原 道家</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>慶運 [ほか自筆]</t>
+          <t>野宮定基 : 久世通夏 [ほか写]</t>
         </is>
       </c>
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr">
         <is>
-          <t>[鎌倉時代-江戸前期]</t>
+          <t>元禄12 [1699]-宝永3 [1706] 奥書</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr">
         <is>
-          <t>折本|書名及び巻冊次は題簽による|2の筆者: 慶運 牡丹花, 了流, 宗長, 兼載, 宗碩, 宗牧, 一竿, 正廣, 正般, 祖田, 堯憲, 宗二, 利盛, 増春, 了向, 榮弘, 梅雪, 宗栁, 等惠, 宗訊, 宗養, 乘阿, 兼如, 壽慶, 意運, 本阿彌光悦, 松花堂昭乘, 紹巴, 玄仍, 玄仲, 玄陳, 玄的, 里村玄祥, 昌叱, 昌琢, 昌俔, 昌程, 昌隱, 昌通|3の筆者: 祐守, 祐夏, 詮平, 直國, 興國, 隆國, 武光, 祐範, 宗純, 等貴,  順, 最嶽, 策彦, 幽之, 應其, 堯然, 尊道, 尊應, 尊朝, 道永, 弘覺, 良俊, 道増, 道應, 道興, 藤之, 立承, 性舜, 義俊, 空性, 尊譽, 揚, 道澄, 興意, 道晃|4の筆者: 有三, 他阿, 教, 尊雅, 應猷, 秀順, 可ト, 圓祐, 道順, 実如, 兼俊, 公助, 應祐, 公順, 空慶, 看世, 定信, 玄桂, 道三, 道春, 永喜, 豊永, 葉由, 常弘|2: 古筆切40枚, 極札43枚|3: 古筆切36枚, 極札36枚|4: 古筆切28枚, 極札20枚|毎半面古筆切2枚|原104枚短冊を3帖に合綴|印記: 「順」, 「最嶽」|極印: 「琴山」, 「栄」(古筆了栄)|折り目破損あり</t>
+          <t>写本|書名及び巻冊次は表紙による|奥中の書名: 光明峯寺禅閤道家公記, 峯禅閤記, 峯摂政記, 峯入道摂政記|承元4年の原奥書に「右即位記一卷者光明峯寺禅閤自筆正記也以件本左令吾基春卿透以写之云々加挍正之 ... 永正七年夷則上浣 從一位(花押)」とあり|奥書に「右以或人夲自常州到来令書写之彼夲端書云此冊上下卷 ... 元禄第十二暦仲夏中旬 羽林左衞中郎将藤原定基丗一才」(承元3), 「右光明峯寺禅閤道家公承元二年三月五六月八月四年二三月九月十十一十二月記は借請或人之夲自常州邊来書写之加一挍了/于時元禄第十二端午節也 左中郎将藤原定基丗才」(承元4), 「右玉蘂建暦元年少弟左中将通清朝臣助筆僅加一挍原本文字不正後来得正夲可改之者也/元禄十三年九月十日 松堂閑士(花押)丗二才」(建暦元), 「右玉蘂峯禅閤記建暦二年自二月至九月一冊以或人夲自常州邊来命家僚令書写手自加挍合了/元禄十二年五月六日 左中郎将藤原定基丗一才」(建暦2年上), 「宝永二年十月一日書写畢/承久二春玉蘂以故常州牧權中納言光圀公夲謄写之于時俗務紛擾先請慈兄源亜相公所被写也今以彼夲手自馳禿筆 余識藤(花押)丗七才/同三年二月廿五日一挍了」(承久2年上), 「右峯摂政承久二年記命傭書謄冩之手自一挍了/元禄第十二嵗次著雍単閼蕤賓中旬 羽林軍左衞中郎将藤原定基丗一才」(承久2年下), 「嘉禎四年正月二月閏二月三月四月六月玉蘂先年假借故常州牧前中納言光圀夲無剋力速遂書写之功建暦元年建暦二年下承久二年上及此卷等先献慈兄亜相君写之今及数年申復彼夲謄写之 ... 宝永三年十二月念日 参議從三位行左近衞權中将藤原朝臣定基生年卅八才」(嘉禎4年)とあり|毎半葉11行注文双行|漢文体日記|拠徳川光圀本及び中院通躬鈔本謄写|朱筆書き入れあり|印記: 「定基」(野宮定基), 「野宮書印」|虫損あり (裏打ち補修あり)</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -8718,12 +8706,12 @@
       <c r="O68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/53041b9e-294f-71af-3d1a-e305956f5560.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/20ddaef2-73cc-5ae8-949d-0bdc521924e9.json</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>53041b9e-294f-71af-3d1a-e305956f5560</t>
+          <t>20ddaef2-73cc-5ae8-949d-0bdc521924e9</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
@@ -8733,7 +8721,7 @@
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/53041b9e-294f-71af-3d1a-e305956f5560</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/20ddaef2-73cc-5ae8-949d-0bdc521924e9</t>
         </is>
       </c>
       <c r="T68" t="inlineStr">
@@ -8743,12 +8731,12 @@
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/11759cf221ad40925619344bacc4027d06e015ce.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/e2bfc2adbffcfb9eb459e7863108300f2722cdd2.jpg</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296186</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296191</t>
         </is>
       </c>
       <c r="W68" t="inlineStr">
@@ -8771,7 +8759,7 @@
       <c r="AB68" t="inlineStr"/>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/53041b9e-294f-71af-3d1a-e305956f5560/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/20ddaef2-73cc-5ae8-949d-0bdc521924e9/manifest</t>
         </is>
       </c>
       <c r="AD68" t="inlineStr"/>
@@ -8779,52 +8767,52 @@
       <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="inlineStr"/>
       <c r="AH68" t="n">
-        <v>24</v>
+        <v>104</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>名家短冊 [3]</t>
+          <t>玉蘂 [3]</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>A00:4277</t>
+          <t>A00:6067</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>メイカ タンザク</t>
+          <t>ギョクズイ</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>慶運</t>
+          <t>藤原 道家</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>慶運 [ほか自筆]</t>
+          <t>野宮定基 : 久世通夏 [ほか写]</t>
         </is>
       </c>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr">
         <is>
-          <t>[鎌倉時代-江戸前期]</t>
+          <t>元禄12 [1699]-宝永3 [1706] 奥書</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr">
         <is>
-          <t>折本|書名及び巻冊次は題簽による|2の筆者: 慶運 牡丹花, 了流, 宗長, 兼載, 宗碩, 宗牧, 一竿, 正廣, 正般, 祖田, 堯憲, 宗二, 利盛, 増春, 了向, 榮弘, 梅雪, 宗栁, 等惠, 宗訊, 宗養, 乘阿, 兼如, 壽慶, 意運, 本阿彌光悦, 松花堂昭乘, 紹巴, 玄仍, 玄仲, 玄陳, 玄的, 里村玄祥, 昌叱, 昌琢, 昌俔, 昌程, 昌隱, 昌通|3の筆者: 祐守, 祐夏, 詮平, 直國, 興國, 隆國, 武光, 祐範, 宗純, 等貴,  順, 最嶽, 策彦, 幽之, 應其, 堯然, 尊道, 尊應, 尊朝, 道永, 弘覺, 良俊, 道増, 道應, 道興, 藤之, 立承, 性舜, 義俊, 空性, 尊譽, 揚, 道澄, 興意, 道晃|4の筆者: 有三, 他阿, 教, 尊雅, 應猷, 秀順, 可ト, 圓祐, 道順, 実如, 兼俊, 公助, 應祐, 公順, 空慶, 看世, 定信, 玄桂, 道三, 道春, 永喜, 豊永, 葉由, 常弘|2: 古筆切40枚, 極札43枚|3: 古筆切36枚, 極札36枚|4: 古筆切28枚, 極札20枚|毎半面古筆切2枚|原104枚短冊を3帖に合綴|印記: 「順」, 「最嶽」|極印: 「琴山」, 「栄」(古筆了栄)|折り目破損あり</t>
+          <t>写本|書名及び巻冊次は表紙による|奥中の書名: 光明峯寺禅閤道家公記, 峯禅閤記, 峯摂政記, 峯入道摂政記|承元4年の原奥書に「右即位記一卷者光明峯寺禅閤自筆正記也以件本左令吾基春卿透以写之云々加挍正之 ... 永正七年夷則上浣 從一位(花押)」とあり|奥書に「右以或人夲自常州到来令書写之彼夲端書云此冊上下卷 ... 元禄第十二暦仲夏中旬 羽林左衞中郎将藤原定基丗一才」(承元3), 「右光明峯寺禅閤道家公承元二年三月五六月八月四年二三月九月十十一十二月記は借請或人之夲自常州邊来書写之加一挍了/于時元禄第十二端午節也 左中郎将藤原定基丗才」(承元4), 「右玉蘂建暦元年少弟左中将通清朝臣助筆僅加一挍原本文字不正後来得正夲可改之者也/元禄十三年九月十日 松堂閑士(花押)丗二才」(建暦元), 「右玉蘂峯禅閤記建暦二年自二月至九月一冊以或人夲自常州邊来命家僚令書写手自加挍合了/元禄十二年五月六日 左中郎将藤原定基丗一才」(建暦2年上), 「宝永二年十月一日書写畢/承久二春玉蘂以故常州牧權中納言光圀公夲謄写之于時俗務紛擾先請慈兄源亜相公所被写也今以彼夲手自馳禿筆 余識藤(花押)丗七才/同三年二月廿五日一挍了」(承久2年上), 「右峯摂政承久二年記命傭書謄冩之手自一挍了/元禄第十二嵗次著雍単閼蕤賓中旬 羽林軍左衞中郎将藤原定基丗一才」(承久2年下), 「嘉禎四年正月二月閏二月三月四月六月玉蘂先年假借故常州牧前中納言光圀夲無剋力速遂書写之功建暦元年建暦二年下承久二年上及此卷等先献慈兄亜相君写之今及数年申復彼夲謄写之 ... 宝永三年十二月念日 参議從三位行左近衞權中将藤原朝臣定基生年卅八才」(嘉禎4年)とあり|毎半葉11行注文双行|漢文体日記|拠徳川光圀本及び中院通躬鈔本謄写|朱筆書き入れあり|印記: 「定基」(野宮定基), 「野宮書印」|虫損あり (裏打ち補修あり)</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -8840,12 +8828,12 @@
       <c r="O69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/3d4ceb9b-9516-779a-7ced-f893e9d93b4e.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/7f62eb7a-844c-22ea-196e-998226c991ea.json</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>3d4ceb9b-9516-779a-7ced-f893e9d93b4e</t>
+          <t>7f62eb7a-844c-22ea-196e-998226c991ea</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
@@ -8855,7 +8843,7 @@
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/3d4ceb9b-9516-779a-7ced-f893e9d93b4e</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/7f62eb7a-844c-22ea-196e-998226c991ea</t>
         </is>
       </c>
       <c r="T69" t="inlineStr">
@@ -8865,12 +8853,12 @@
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/8fd1defea23c7c93fc4d908835c1fea38040580e.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/ac4d01393f2eb0586033bfface43acc61e64021e.jpg</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296187</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296192</t>
         </is>
       </c>
       <c r="W69" t="inlineStr">
@@ -8893,7 +8881,7 @@
       <c r="AB69" t="inlineStr"/>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/3d4ceb9b-9516-779a-7ced-f893e9d93b4e/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/7f62eb7a-844c-22ea-196e-998226c991ea/manifest</t>
         </is>
       </c>
       <c r="AD69" t="inlineStr"/>
@@ -8901,52 +8889,52 @@
       <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="inlineStr"/>
       <c r="AH69" t="n">
-        <v>24</v>
+        <v>77</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>御成敗式目絵鈔</t>
+          <t>玉蘂 [4]</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>A00:4737</t>
+          <t>A00:6067</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>ゴセイバイ シキモク エショウ</t>
+          <t>ギョクズイ</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>岡本 竹籔</t>
+          <t>藤原 道家</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>岡夲竹籔 : 松川半山 [書]</t>
+          <t>野宮定基 : 久世通夏 [ほか写]</t>
         </is>
       </c>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr">
         <is>
-          <t>[幕末期]</t>
+          <t>元禄12 [1699]-宝永3 [1706] 奥書</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr">
         <is>
-          <t>写本|序首の書名: 御成敗式目繪鈔|版心の書名: 式目繪鈔|題簽に「板下本」とあり|巻末に「筆工 岡夲竹籔/画工 松川半山」とあり(「岡本」, 「憲道」, 「義卿」, 「翠宋堂長」との落款朱印あり)|巻末広告に「山田賞月堂先生筆 無雙用文章大成 全一冊」とあり|四周単辺有界2段5行, 内匡廓: 22.3×16.4cm, 白口無魚尾|頭書あり|付訓あり</t>
+          <t>写本|書名及び巻冊次は表紙による|奥中の書名: 光明峯寺禅閤道家公記, 峯禅閤記, 峯摂政記, 峯入道摂政記|承元4年の原奥書に「右即位記一卷者光明峯寺禅閤自筆正記也以件本左令吾基春卿透以写之云々加挍正之 ... 永正七年夷則上浣 從一位(花押)」とあり|奥書に「右以或人夲自常州到来令書写之彼夲端書云此冊上下卷 ... 元禄第十二暦仲夏中旬 羽林左衞中郎将藤原定基丗一才」(承元3), 「右光明峯寺禅閤道家公承元二年三月五六月八月四年二三月九月十十一十二月記は借請或人之夲自常州邊来書写之加一挍了/于時元禄第十二端午節也 左中郎将藤原定基丗才」(承元4), 「右玉蘂建暦元年少弟左中将通清朝臣助筆僅加一挍原本文字不正後来得正夲可改之者也/元禄十三年九月十日 松堂閑士(花押)丗二才」(建暦元), 「右玉蘂峯禅閤記建暦二年自二月至九月一冊以或人夲自常州邊来命家僚令書写手自加挍合了/元禄十二年五月六日 左中郎将藤原定基丗一才」(建暦2年上), 「宝永二年十月一日書写畢/承久二春玉蘂以故常州牧權中納言光圀公夲謄写之于時俗務紛擾先請慈兄源亜相公所被写也今以彼夲手自馳禿筆 余識藤(花押)丗七才/同三年二月廿五日一挍了」(承久2年上), 「右峯摂政承久二年記命傭書謄冩之手自一挍了/元禄第十二嵗次著雍単閼蕤賓中旬 羽林軍左衞中郎将藤原定基丗一才」(承久2年下), 「嘉禎四年正月二月閏二月三月四月六月玉蘂先年假借故常州牧前中納言光圀夲無剋力速遂書写之功建暦元年建暦二年下承久二年上及此卷等先献慈兄亜相君写之今及数年申復彼夲謄写之 ... 宝永三年十二月念日 参議從三位行左近衞權中将藤原朝臣定基生年卅八才」(嘉禎4年)とあり|毎半葉11行注文双行|漢文体日記|拠徳川光圀本及び中院通躬鈔本謄写|朱筆書き入れあり|印記: 「定基」(野宮定基), 「野宮書印」|虫損あり (裏打ち補修あり)</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -8962,12 +8950,12 @@
       <c r="O70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/463ab967-60a4-9ff1-3ef2-d2dee79b5315.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/f48a78a7-0365-73cb-4e46-dd013ef92813.json</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>463ab967-60a4-9ff1-3ef2-d2dee79b5315</t>
+          <t>f48a78a7-0365-73cb-4e46-dd013ef92813</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
@@ -8977,7 +8965,7 @@
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/463ab967-60a4-9ff1-3ef2-d2dee79b5315</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/f48a78a7-0365-73cb-4e46-dd013ef92813</t>
         </is>
       </c>
       <c r="T70" t="inlineStr">
@@ -8987,12 +8975,12 @@
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/e0977d9ba261ea59386ce9f5104a412a5dccaf3f.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/d9d6bd695feea8f0816bee6e991e141accf01cd8.jpg</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296188</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296193</t>
         </is>
       </c>
       <c r="W70" t="inlineStr">
@@ -9015,7 +9003,7 @@
       <c r="AB70" t="inlineStr"/>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/463ab967-60a4-9ff1-3ef2-d2dee79b5315/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/f48a78a7-0365-73cb-4e46-dd013ef92813/manifest</t>
         </is>
       </c>
       <c r="AD70" t="inlineStr"/>
@@ -9023,52 +9011,52 @@
       <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="inlineStr"/>
       <c r="AH70" t="n">
-        <v>59</v>
+        <v>138</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>金界入壇作法</t>
+          <t>玉蘂 [5]</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>A00:5975</t>
+          <t>A00:6067</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>コンカイ ニュウダン サホウ</t>
+          <t>ギョクズイ</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>良円</t>
+          <t>藤原 道家</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>良円 [写]</t>
+          <t>野宮定基 : 久世通夏 [ほか写]</t>
         </is>
       </c>
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr">
         <is>
-          <t>寛元元 [1243] 奥書</t>
+          <t>元禄12 [1699]-宝永3 [1706] 奥書</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr">
         <is>
-          <t>写本|奥書に「寛元々年五月七日以先師法印御夲於常住護国院房以他筆書冩校點了良円」とあり|送り仮名, 返点あり|淡墨界の料紙を使用(界匡廓: 23.7×2.5cm)|貼紙あり|巻子本|箱入り|破損, 虫損あり (裏打ち補修あり)</t>
+          <t>写本|書名及び巻冊次は表紙による|奥中の書名: 光明峯寺禅閤道家公記, 峯禅閤記, 峯摂政記, 峯入道摂政記|承元4年の原奥書に「右即位記一卷者光明峯寺禅閤自筆正記也以件本左令吾基春卿透以写之云々加挍正之 ... 永正七年夷則上浣 從一位(花押)」とあり|奥書に「右以或人夲自常州到来令書写之彼夲端書云此冊上下卷 ... 元禄第十二暦仲夏中旬 羽林左衞中郎将藤原定基丗一才」(承元3), 「右光明峯寺禅閤道家公承元二年三月五六月八月四年二三月九月十十一十二月記は借請或人之夲自常州邊来書写之加一挍了/于時元禄第十二端午節也 左中郎将藤原定基丗才」(承元4), 「右玉蘂建暦元年少弟左中将通清朝臣助筆僅加一挍原本文字不正後来得正夲可改之者也/元禄十三年九月十日 松堂閑士(花押)丗二才」(建暦元), 「右玉蘂峯禅閤記建暦二年自二月至九月一冊以或人夲自常州邊来命家僚令書写手自加挍合了/元禄十二年五月六日 左中郎将藤原定基丗一才」(建暦2年上), 「宝永二年十月一日書写畢/承久二春玉蘂以故常州牧權中納言光圀公夲謄写之于時俗務紛擾先請慈兄源亜相公所被写也今以彼夲手自馳禿筆 余識藤(花押)丗七才/同三年二月廿五日一挍了」(承久2年上), 「右峯摂政承久二年記命傭書謄冩之手自一挍了/元禄第十二嵗次著雍単閼蕤賓中旬 羽林軍左衞中郎将藤原定基丗一才」(承久2年下), 「嘉禎四年正月二月閏二月三月四月六月玉蘂先年假借故常州牧前中納言光圀夲無剋力速遂書写之功建暦元年建暦二年下承久二年上及此卷等先献慈兄亜相君写之今及数年申復彼夲謄写之 ... 宝永三年十二月念日 参議從三位行左近衞權中将藤原朝臣定基生年卅八才」(嘉禎4年)とあり|毎半葉11行注文双行|漢文体日記|拠徳川光圀本及び中院通躬鈔本謄写|朱筆書き入れあり|印記: 「定基」(野宮定基), 「野宮書印」|虫損あり (裏打ち補修あり)</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -9084,12 +9072,12 @@
       <c r="O71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/ff6e2dd7-8128-3264-2081-15ad4e41857e.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/c4ba4bb2-8d3c-7e43-4e3e-e6a6d0c2260f.json</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>ff6e2dd7-8128-3264-2081-15ad4e41857e</t>
+          <t>c4ba4bb2-8d3c-7e43-4e3e-e6a6d0c2260f</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
@@ -9099,7 +9087,7 @@
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/ff6e2dd7-8128-3264-2081-15ad4e41857e</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/c4ba4bb2-8d3c-7e43-4e3e-e6a6d0c2260f</t>
         </is>
       </c>
       <c r="T71" t="inlineStr">
@@ -9109,12 +9097,12 @@
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/7e2372f45914ea75c8d903fc80f309f16238b39f.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/58826021e366d49d150087ff3478b98548b97c4a.jpg</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296189</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296194</t>
         </is>
       </c>
       <c r="W71" t="inlineStr">
@@ -9137,7 +9125,7 @@
       <c r="AB71" t="inlineStr"/>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/ff6e2dd7-8128-3264-2081-15ad4e41857e/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/c4ba4bb2-8d3c-7e43-4e3e-e6a6d0c2260f/manifest</t>
         </is>
       </c>
       <c r="AD71" t="inlineStr"/>
@@ -9145,13 +9133,13 @@
       <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="inlineStr"/>
       <c r="AH71" t="n">
-        <v>39</v>
+        <v>69</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>玉蘂 [1]</t>
+          <t>玉蘂 [6]</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -9206,12 +9194,12 @@
       <c r="O72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/b13a7a09-88d0-62d3-44e5-379780395f17.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/73dc1d4b-7872-a0a3-780c-3c10d2a3758a.json</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>b13a7a09-88d0-62d3-44e5-379780395f17</t>
+          <t>73dc1d4b-7872-a0a3-780c-3c10d2a3758a</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
@@ -9221,7 +9209,7 @@
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/b13a7a09-88d0-62d3-44e5-379780395f17</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/73dc1d4b-7872-a0a3-780c-3c10d2a3758a</t>
         </is>
       </c>
       <c r="T72" t="inlineStr">
@@ -9231,12 +9219,12 @@
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/f7ae1bd23dec8f323199a9add81e315f1a653d24.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/6724525552ca8e3c1f42cdc0f0674a54828dc026.jpg</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296190</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296195</t>
         </is>
       </c>
       <c r="W72" t="inlineStr">
@@ -9259,7 +9247,7 @@
       <c r="AB72" t="inlineStr"/>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/b13a7a09-88d0-62d3-44e5-379780395f17/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/73dc1d4b-7872-a0a3-780c-3c10d2a3758a/manifest</t>
         </is>
       </c>
       <c r="AD72" t="inlineStr"/>
@@ -9267,13 +9255,13 @@
       <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="inlineStr"/>
       <c r="AH72" t="n">
-        <v>129</v>
+        <v>106</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>玉蘂 [2]</t>
+          <t>玉蘂 [7]</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -9328,12 +9316,12 @@
       <c r="O73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/20ddaef2-73cc-5ae8-949d-0bdc521924e9.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/e775ea12-9867-70f2-6381-112e31478f75.json</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>20ddaef2-73cc-5ae8-949d-0bdc521924e9</t>
+          <t>e775ea12-9867-70f2-6381-112e31478f75</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
@@ -9343,7 +9331,7 @@
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/20ddaef2-73cc-5ae8-949d-0bdc521924e9</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/e775ea12-9867-70f2-6381-112e31478f75</t>
         </is>
       </c>
       <c r="T73" t="inlineStr">
@@ -9353,12 +9341,12 @@
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/e2bfc2adbffcfb9eb459e7863108300f2722cdd2.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/08e58358a211a53638e77e5431d7fedb34bd5f72.jpg</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296191</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296196</t>
         </is>
       </c>
       <c r="W73" t="inlineStr">
@@ -9381,7 +9369,7 @@
       <c r="AB73" t="inlineStr"/>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/20ddaef2-73cc-5ae8-949d-0bdc521924e9/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/e775ea12-9867-70f2-6381-112e31478f75/manifest</t>
         </is>
       </c>
       <c r="AD73" t="inlineStr"/>
@@ -9389,13 +9377,13 @@
       <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="inlineStr"/>
       <c r="AH73" t="n">
-        <v>104</v>
+        <v>146</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>玉蘂 [3]</t>
+          <t>玉蘂 [8]</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -9450,12 +9438,12 @@
       <c r="O74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/7f62eb7a-844c-22ea-196e-998226c991ea.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/ca2da620-345c-76fa-9d1d-e7b2c55d757f.json</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>7f62eb7a-844c-22ea-196e-998226c991ea</t>
+          <t>ca2da620-345c-76fa-9d1d-e7b2c55d757f</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
@@ -9465,7 +9453,7 @@
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/7f62eb7a-844c-22ea-196e-998226c991ea</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/ca2da620-345c-76fa-9d1d-e7b2c55d757f</t>
         </is>
       </c>
       <c r="T74" t="inlineStr">
@@ -9475,12 +9463,12 @@
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/ac4d01393f2eb0586033bfface43acc61e64021e.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/8204e28b4e8f0e2f8abc1b939244f007093f3749.jpg</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296192</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296197</t>
         </is>
       </c>
       <c r="W74" t="inlineStr">
@@ -9503,7 +9491,7 @@
       <c r="AB74" t="inlineStr"/>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/7f62eb7a-844c-22ea-196e-998226c991ea/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/ca2da620-345c-76fa-9d1d-e7b2c55d757f/manifest</t>
         </is>
       </c>
       <c r="AD74" t="inlineStr"/>
@@ -9511,52 +9499,48 @@
       <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="inlineStr"/>
       <c r="AH74" t="n">
-        <v>77</v>
+        <v>63</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>玉蘂 [4]</t>
+          <t>大明星天子法 : 又名法界虚空蔵法</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>A00:6067</t>
+          <t>A00:6097</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>ギョクズイ</t>
+          <t>ダイミョウジョウテンシホウ : マタミョウ ホッカイ コクウゾウホウ</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>藤原 道家</t>
-        </is>
-      </c>
+      <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
-          <t>野宮定基 : 久世通夏 [ほか写]</t>
+          <t>[書写者不明]</t>
         </is>
       </c>
       <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr">
         <is>
-          <t>元禄12 [1699]-宝永3 [1706] 奥書</t>
+          <t>[天文年間]</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr">
         <is>
-          <t>写本|書名及び巻冊次は表紙による|奥中の書名: 光明峯寺禅閤道家公記, 峯禅閤記, 峯摂政記, 峯入道摂政記|承元4年の原奥書に「右即位記一卷者光明峯寺禅閤自筆正記也以件本左令吾基春卿透以写之云々加挍正之 ... 永正七年夷則上浣 從一位(花押)」とあり|奥書に「右以或人夲自常州到来令書写之彼夲端書云此冊上下卷 ... 元禄第十二暦仲夏中旬 羽林左衞中郎将藤原定基丗一才」(承元3), 「右光明峯寺禅閤道家公承元二年三月五六月八月四年二三月九月十十一十二月記は借請或人之夲自常州邊来書写之加一挍了/于時元禄第十二端午節也 左中郎将藤原定基丗才」(承元4), 「右玉蘂建暦元年少弟左中将通清朝臣助筆僅加一挍原本文字不正後来得正夲可改之者也/元禄十三年九月十日 松堂閑士(花押)丗二才」(建暦元), 「右玉蘂峯禅閤記建暦二年自二月至九月一冊以或人夲自常州邊来命家僚令書写手自加挍合了/元禄十二年五月六日 左中郎将藤原定基丗一才」(建暦2年上), 「宝永二年十月一日書写畢/承久二春玉蘂以故常州牧權中納言光圀公夲謄写之于時俗務紛擾先請慈兄源亜相公所被写也今以彼夲手自馳禿筆 余識藤(花押)丗七才/同三年二月廿五日一挍了」(承久2年上), 「右峯摂政承久二年記命傭書謄冩之手自一挍了/元禄第十二嵗次著雍単閼蕤賓中旬 羽林軍左衞中郎将藤原定基丗一才」(承久2年下), 「嘉禎四年正月二月閏二月三月四月六月玉蘂先年假借故常州牧前中納言光圀夲無剋力速遂書写之功建暦元年建暦二年下承久二年上及此卷等先献慈兄亜相君写之今及数年申復彼夲謄写之 ... 宝永三年十二月念日 参議從三位行左近衞權中将藤原朝臣定基生年卅八才」(嘉禎4年)とあり|毎半葉11行注文双行|漢文体日記|拠徳川光圀本及び中院通躬鈔本謄写|朱筆書き入れあり|印記: 「定基」(野宮定基), 「野宮書印」|虫損あり (裏打ち補修あり)</t>
+          <t>写本|巻末の書名: 明星天子法|表紙の書名: 大明皇天子水|大尾に「明星天子法次苐 一交了」とあり|本奥書に「承久三年五月十三日/爲興法利生徃生極樂書冩之/金剛佛子觀照之」とあり|書袋に「天文古筆」, 「天明七未ノ年」とあり|毎半葉8行|押界を施した楮紙打紙を使用|粘葉装|虫損あり</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -9572,12 +9556,12 @@
       <c r="O75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/f48a78a7-0365-73cb-4e46-dd013ef92813.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/a1905fc7-4727-0750-41d7-f0ca1df53f47.json</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>f48a78a7-0365-73cb-4e46-dd013ef92813</t>
+          <t>a1905fc7-4727-0750-41d7-f0ca1df53f47</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
@@ -9587,7 +9571,7 @@
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/f48a78a7-0365-73cb-4e46-dd013ef92813</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/a1905fc7-4727-0750-41d7-f0ca1df53f47</t>
         </is>
       </c>
       <c r="T75" t="inlineStr">
@@ -9597,12 +9581,12 @@
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/d9d6bd695feea8f0816bee6e991e141accf01cd8.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/b2590ef4e55f582d8059a5e072e1d6dad33bf996.jpg</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296193</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296198</t>
         </is>
       </c>
       <c r="W75" t="inlineStr">
@@ -9625,7 +9609,7 @@
       <c r="AB75" t="inlineStr"/>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/f48a78a7-0365-73cb-4e46-dd013ef92813/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/a1905fc7-4727-0750-41d7-f0ca1df53f47/manifest</t>
         </is>
       </c>
       <c r="AD75" t="inlineStr"/>
@@ -9633,52 +9617,48 @@
       <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="inlineStr"/>
       <c r="AH75" t="n">
-        <v>138</v>
+        <v>9</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>玉蘂 [5]</t>
+          <t>大嘗會悠紀主基鮮味之繪</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>A00:6067</t>
+          <t>A00:6108</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>ギョクズイ</t>
+          <t>ダイジョウエ ユキ スキ センミ ノ ズ</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>藤原 道家</t>
-        </is>
-      </c>
+      <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
-          <t>野宮定基 : 久世通夏 [ほか写]</t>
+          <t>[佐伯]</t>
         </is>
       </c>
       <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr">
         <is>
-          <t>元禄12 [1699]-宝永3 [1706] 奥書</t>
+          <t>明和元 [1764] 識語</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr">
         <is>
-          <t>写本|書名及び巻冊次は表紙による|奥中の書名: 光明峯寺禅閤道家公記, 峯禅閤記, 峯摂政記, 峯入道摂政記|承元4年の原奥書に「右即位記一卷者光明峯寺禅閤自筆正記也以件本左令吾基春卿透以写之云々加挍正之 ... 永正七年夷則上浣 從一位(花押)」とあり|奥書に「右以或人夲自常州到来令書写之彼夲端書云此冊上下卷 ... 元禄第十二暦仲夏中旬 羽林左衞中郎将藤原定基丗一才」(承元3), 「右光明峯寺禅閤道家公承元二年三月五六月八月四年二三月九月十十一十二月記は借請或人之夲自常州邊来書写之加一挍了/于時元禄第十二端午節也 左中郎将藤原定基丗才」(承元4), 「右玉蘂建暦元年少弟左中将通清朝臣助筆僅加一挍原本文字不正後来得正夲可改之者也/元禄十三年九月十日 松堂閑士(花押)丗二才」(建暦元), 「右玉蘂峯禅閤記建暦二年自二月至九月一冊以或人夲自常州邊来命家僚令書写手自加挍合了/元禄十二年五月六日 左中郎将藤原定基丗一才」(建暦2年上), 「宝永二年十月一日書写畢/承久二春玉蘂以故常州牧權中納言光圀公夲謄写之于時俗務紛擾先請慈兄源亜相公所被写也今以彼夲手自馳禿筆 余識藤(花押)丗七才/同三年二月廿五日一挍了」(承久2年上), 「右峯摂政承久二年記命傭書謄冩之手自一挍了/元禄第十二嵗次著雍単閼蕤賓中旬 羽林軍左衞中郎将藤原定基丗一才」(承久2年下), 「嘉禎四年正月二月閏二月三月四月六月玉蘂先年假借故常州牧前中納言光圀夲無剋力速遂書写之功建暦元年建暦二年下承久二年上及此卷等先献慈兄亜相君写之今及数年申復彼夲謄写之 ... 宝永三年十二月念日 参議從三位行左近衞權中将藤原朝臣定基生年卅八才」(嘉禎4年)とあり|毎半葉11行注文双行|漢文体日記|拠徳川光圀本及び中院通躬鈔本謄写|朱筆書き入れあり|印記: 「定基」(野宮定基), 「野宮書印」|虫損あり (裏打ち補修あり)</t>
+          <t>絵巻|書名は識語による|書袋の書名: 悠紀主基鮮味之啚|表紙裏に「元文悠紀主基鮮味之圖 寛延同」とあり|巻末の識語に「右大嘗會悠紀主基鮮味之繪借請御厨子所預紀宗直朝臣令佐伯職房摸冩之畢 明和元年孟冬左少将藤原(花押)」とあり|絵4幅: 梅作枝, 糸作枩, 萩作枝, 萩作枝|紙本著色|彩色あり|帙入り|印記: 「野宮藏書」</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -9694,12 +9674,12 @@
       <c r="O76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/c4ba4bb2-8d3c-7e43-4e3e-e6a6d0c2260f.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/d00e906c-5404-4fc1-44c9-1566cf7f7012.json</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>c4ba4bb2-8d3c-7e43-4e3e-e6a6d0c2260f</t>
+          <t>d00e906c-5404-4fc1-44c9-1566cf7f7012</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
@@ -9709,7 +9689,7 @@
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/c4ba4bb2-8d3c-7e43-4e3e-e6a6d0c2260f</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/d00e906c-5404-4fc1-44c9-1566cf7f7012</t>
         </is>
       </c>
       <c r="T76" t="inlineStr">
@@ -9719,12 +9699,12 @@
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/58826021e366d49d150087ff3478b98548b97c4a.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/51e8aa982b380211852796b36819e6c6c6bf1583.jpg</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296194</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296199</t>
         </is>
       </c>
       <c r="W76" t="inlineStr">
@@ -9747,7 +9727,7 @@
       <c r="AB76" t="inlineStr"/>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/c4ba4bb2-8d3c-7e43-4e3e-e6a6d0c2260f/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/d00e906c-5404-4fc1-44c9-1566cf7f7012/manifest</t>
         </is>
       </c>
       <c r="AD76" t="inlineStr"/>
@@ -9755,52 +9735,48 @@
       <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="inlineStr"/>
       <c r="AH76" t="n">
-        <v>69</v>
+        <v>11</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>玉蘂 [6]</t>
+          <t>真言宗脈啚 : 栂尾夲</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>A00:6067</t>
+          <t>A00:6129</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>ギョクズイ</t>
+          <t>シンゴンシュウ ミャクズ : トガノオボン</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>藤原 道家</t>
-        </is>
-      </c>
+      <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
-          <t>野宮定基 : 久世通夏 [ほか写]</t>
+          <t>覺心</t>
         </is>
       </c>
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr">
         <is>
-          <t>元禄12 [1699]-宝永3 [1706] 奥書</t>
+          <t>享保9 [1724] 奥書</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr">
         <is>
-          <t>写本|書名及び巻冊次は表紙による|奥中の書名: 光明峯寺禅閤道家公記, 峯禅閤記, 峯摂政記, 峯入道摂政記|承元4年の原奥書に「右即位記一卷者光明峯寺禅閤自筆正記也以件本左令吾基春卿透以写之云々加挍正之 ... 永正七年夷則上浣 從一位(花押)」とあり|奥書に「右以或人夲自常州到来令書写之彼夲端書云此冊上下卷 ... 元禄第十二暦仲夏中旬 羽林左衞中郎将藤原定基丗一才」(承元3), 「右光明峯寺禅閤道家公承元二年三月五六月八月四年二三月九月十十一十二月記は借請或人之夲自常州邊来書写之加一挍了/于時元禄第十二端午節也 左中郎将藤原定基丗才」(承元4), 「右玉蘂建暦元年少弟左中将通清朝臣助筆僅加一挍原本文字不正後来得正夲可改之者也/元禄十三年九月十日 松堂閑士(花押)丗二才」(建暦元), 「右玉蘂峯禅閤記建暦二年自二月至九月一冊以或人夲自常州邊来命家僚令書写手自加挍合了/元禄十二年五月六日 左中郎将藤原定基丗一才」(建暦2年上), 「宝永二年十月一日書写畢/承久二春玉蘂以故常州牧權中納言光圀公夲謄写之于時俗務紛擾先請慈兄源亜相公所被写也今以彼夲手自馳禿筆 余識藤(花押)丗七才/同三年二月廿五日一挍了」(承久2年上), 「右峯摂政承久二年記命傭書謄冩之手自一挍了/元禄第十二嵗次著雍単閼蕤賓中旬 羽林軍左衞中郎将藤原定基丗一才」(承久2年下), 「嘉禎四年正月二月閏二月三月四月六月玉蘂先年假借故常州牧前中納言光圀夲無剋力速遂書写之功建暦元年建暦二年下承久二年上及此卷等先献慈兄亜相君写之今及数年申復彼夲謄写之 ... 宝永三年十二月念日 参議從三位行左近衞權中将藤原朝臣定基生年卅八才」(嘉禎4年)とあり|毎半葉11行注文双行|漢文体日記|拠徳川光圀本及び中院通躬鈔本謄写|朱筆書き入れあり|印記: 「定基」(野宮定基), 「野宮書印」|虫損あり (裏打ち補修あり)</t>
+          <t>写本|書名は題簽による|帙題簽の書名: 真言宗血脈圗|奥書に「正徳二年之春請自性院僧正開栂尾山宮御封之經藏求淂于古聖教若干部是其一也 沙門道空」, 「享保九年甲辰夏寓于洛西御阜草菴以五智山之本冩之訖 南紀護国寺沙門覺心/同年六月晦日以栂尾法鼓臺古本挍合之了」, 「昭和八年四月念三日閲覧砌訂正誤字記入落罫云尒 中野達慧識」とあり|朱筆書き入れあり|印記: 「和學講談所」, 「温故堂文庫」(塙家), 「松平家藏書印」|虫損あり</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -9816,12 +9792,12 @@
       <c r="O77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/73dc1d4b-7872-a0a3-780c-3c10d2a3758a.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/e6a30e98-5da6-7e0d-7a92-5b26c887309f.json</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>73dc1d4b-7872-a0a3-780c-3c10d2a3758a</t>
+          <t>e6a30e98-5da6-7e0d-7a92-5b26c887309f</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
@@ -9831,7 +9807,7 @@
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/73dc1d4b-7872-a0a3-780c-3c10d2a3758a</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/e6a30e98-5da6-7e0d-7a92-5b26c887309f</t>
         </is>
       </c>
       <c r="T77" t="inlineStr">
@@ -9841,12 +9817,12 @@
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/6724525552ca8e3c1f42cdc0f0674a54828dc026.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/10842787f14673fb3729595dd908dde4c4dd6ad8.jpg</t>
         </is>
       </c>
       <c r="V77" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296195</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296200</t>
         </is>
       </c>
       <c r="W77" t="inlineStr">
@@ -9869,7 +9845,7 @@
       <c r="AB77" t="inlineStr"/>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/73dc1d4b-7872-a0a3-780c-3c10d2a3758a/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/e6a30e98-5da6-7e0d-7a92-5b26c887309f/manifest</t>
         </is>
       </c>
       <c r="AD77" t="inlineStr"/>
@@ -9877,52 +9853,52 @@
       <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="inlineStr"/>
       <c r="AH77" t="n">
-        <v>106</v>
+        <v>22</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>玉蘂 [7]</t>
+          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [1]</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>A00:6067</t>
+          <t>A00:6257</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>ギョクズイ</t>
+          <t>レキダイ ザンケツ ニッキ</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
-          <t>藤原 道家</t>
+          <t>黒川 春村</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>野宮定基 : 久世通夏 [ほか写]</t>
+          <t>[書写者不明]</t>
         </is>
       </c>
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr">
         <is>
-          <t>元禄12 [1699]-宝永3 [1706] 奥書</t>
+          <t>[安政5 (1858)]</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr">
         <is>
-          <t>写本|書名及び巻冊次は表紙による|奥中の書名: 光明峯寺禅閤道家公記, 峯禅閤記, 峯摂政記, 峯入道摂政記|承元4年の原奥書に「右即位記一卷者光明峯寺禅閤自筆正記也以件本左令吾基春卿透以写之云々加挍正之 ... 永正七年夷則上浣 從一位(花押)」とあり|奥書に「右以或人夲自常州到来令書写之彼夲端書云此冊上下卷 ... 元禄第十二暦仲夏中旬 羽林左衞中郎将藤原定基丗一才」(承元3), 「右光明峯寺禅閤道家公承元二年三月五六月八月四年二三月九月十十一十二月記は借請或人之夲自常州邊来書写之加一挍了/于時元禄第十二端午節也 左中郎将藤原定基丗才」(承元4), 「右玉蘂建暦元年少弟左中将通清朝臣助筆僅加一挍原本文字不正後来得正夲可改之者也/元禄十三年九月十日 松堂閑士(花押)丗二才」(建暦元), 「右玉蘂峯禅閤記建暦二年自二月至九月一冊以或人夲自常州邊来命家僚令書写手自加挍合了/元禄十二年五月六日 左中郎将藤原定基丗一才」(建暦2年上), 「宝永二年十月一日書写畢/承久二春玉蘂以故常州牧權中納言光圀公夲謄写之于時俗務紛擾先請慈兄源亜相公所被写也今以彼夲手自馳禿筆 余識藤(花押)丗七才/同三年二月廿五日一挍了」(承久2年上), 「右峯摂政承久二年記命傭書謄冩之手自一挍了/元禄第十二嵗次著雍単閼蕤賓中旬 羽林軍左衞中郎将藤原定基丗一才」(承久2年下), 「嘉禎四年正月二月閏二月三月四月六月玉蘂先年假借故常州牧前中納言光圀夲無剋力速遂書写之功建暦元年建暦二年下承久二年上及此卷等先献慈兄亜相君写之今及数年申復彼夲謄写之 ... 宝永三年十二月念日 参議從三位行左近衞權中将藤原朝臣定基生年卅八才」(嘉禎4年)とあり|毎半葉11行注文双行|漢文体日記|拠徳川光圀本及び中院通躬鈔本謄写|朱筆書き入れあり|印記: 「定基」(野宮定基), 「野宮書印」|虫損あり (裏打ち補修あり)</t>
+          <t>写本|責任表示及び書写年は『日本古典籍総合目録データベース』による|内容: 6: 光明院御記, 後光嚴院御記, 後小松院宸記, 天聴集. 28: 参議藤定長卿記 : 稱山丞記. 37: 定高卿記, 晴御会部類記, 家光卿御記, 權中納言平範輔卿記. 38: 左大史小槻季継記, 後堀川安貞二年放生會(実基公記), 石清水八幡宮, 弁官拝賀次第. 39: 大外記師光記, 資季卿記, 荒凉記, 忠高卿記. 40: 冷泉公相公記, 勝延法眼記 : 東寺大行事, 後中記 : 小路中納言資頼卿記葉室. 41: 中光記, 師兼記, 陽龍記. 42: 大宮司長則記, 口筆 : 實經, 顕朝卿記, 鴨御幸記. 43: 寳治二年記, 深心院關白記, 藤公親記, 照念院関白兼平公記. 44: 頼親記, 亀山殿行幸記 : 雅言卿記, 兼基公記. 45: 大嘗會御禊節下次第, 建治三年丁丑日記 : 三善康有, 建治四年正月廿一日 : 徳大寺大相國公孝記, 冬定卿記, 左大史小槻兼文記|内容: 46: 經任卿記, 前豊前守藤憲説記, 實兼公記. 47: 継塵記抄出. 48: 管見記, 公衡公記, 大外記師顕記, 大外記中原師淳記. 49: 真光院禪助僧正記, 吉田内府卿記. 50: 定清記, 叅議雅俊卿記, 太政大臣(公守公)御上表雜事, 仙洞御灌頂日記, 正安二年八月十一日於仙洞被始行熾盛光法, 正安三年御譲位記. 51: 實躬卿記. 52: 公茂公記, 冬平公記, 隆長卿記. 53: 忠教公記, 官記, 正三位長基卿記, 北面秀長記, 大外記中原師右記. 54: 文保元年, 日野中納言資朝卿記, 洞院大納言公敏卿記. 55: 隆蔭卿記, 文保三年記, 尹大納言師賢卿記, 革命記, 立倚子記, 萬里小路中納言藤藤房卿記|内容: 56: 資名卿記, 公秀公記, 一條家記装束抄出, 頼定卿記. 63: 松亞記, 日野大納言時光卿記, 後八條内府實継公記. 74: 成恩寺関白記. 78: 山科家礼記. 82: 諒闇記 : 後成恩寺殿, 宗典僧正記, 綱光公記, 贈従二位宗賢卿記, 義政公記. 84: 長禄二年戊寅正月, 見聞雜記. 87: 言國卿記. 88: 長興宿祢記, 元長卿記, 兼顕卿記, 小槻晴冨記|28末の原奥書に「右山丞記依 仰挍合書冩/享和二年四月 日撿挍保己一」とあり|50「正安二年八月十一日於仙洞被始行熾盛光法」末の原奥書に「文化十五年春二月以南山法曼院藏夲書冩之 撿挍保己一」とあり|横刷毛目表紙を使用|朱点, 朱引, 朱墨筆書き入れあり|付箋あり|蔵書印主信濃須坂藩主堀直格の命によって編集された古記録|他の原本は関東大震災により焼失|極札に「桂壽」(6), 「尚信」(53)との極書, 「武清」(44, 53), 「永海」(51), 「了伴」(52), 「了甫」(74), 「定時」(84, 88)との極印あり|印記: 「花廼家文庫」, 「墨阪十一代主寫藏記」(堀直格(1806-1880)), 「東京大學法理文學部書庫所藏」, 「閲覧室用 FOR USE IN THE READING ROOM」|虫損あり</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -9938,12 +9914,12 @@
       <c r="O78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/e775ea12-9867-70f2-6381-112e31478f75.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/c32632af-9dc0-504a-5437-15a055d52628.json</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>e775ea12-9867-70f2-6381-112e31478f75</t>
+          <t>c32632af-9dc0-504a-5437-15a055d52628</t>
         </is>
       </c>
       <c r="R78" t="inlineStr">
@@ -9953,7 +9929,7 @@
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/e775ea12-9867-70f2-6381-112e31478f75</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/c32632af-9dc0-504a-5437-15a055d52628</t>
         </is>
       </c>
       <c r="T78" t="inlineStr">
@@ -9963,12 +9939,12 @@
       </c>
       <c r="U78" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/08e58358a211a53638e77e5431d7fedb34bd5f72.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/2230dfedd3d91cc8b1c5532de33a8f8559be8357.jpg</t>
         </is>
       </c>
       <c r="V78" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296196</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296201</t>
         </is>
       </c>
       <c r="W78" t="inlineStr">
@@ -9991,7 +9967,7 @@
       <c r="AB78" t="inlineStr"/>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/e775ea12-9867-70f2-6381-112e31478f75/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/c32632af-9dc0-504a-5437-15a055d52628/manifest</t>
         </is>
       </c>
       <c r="AD78" t="inlineStr"/>
@@ -9999,52 +9975,56 @@
       <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="inlineStr"/>
       <c r="AH78" t="n">
-        <v>146</v>
+        <v>72</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>玉蘂 [8]</t>
+          <t>おちくほのさうし</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>A00:6067</t>
+          <t>A00:4083</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>ギョクズイ</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr"/>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>藤原 道家</t>
-        </is>
-      </c>
+          <t>オチクボ ノ ソウシ</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>おちくほ物語|御本</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
         <is>
-          <t>野宮定基 : 久世通夏 [ほか写]</t>
+          <t>[書写者不明]</t>
         </is>
       </c>
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr">
         <is>
-          <t>元禄12 [1699]-宝永3 [1706] 奥書</t>
+          <t>[江戸前期]</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>写本</t>
+        </is>
+      </c>
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr">
         <is>
-          <t>写本|書名及び巻冊次は表紙による|奥中の書名: 光明峯寺禅閤道家公記, 峯禅閤記, 峯摂政記, 峯入道摂政記|承元4年の原奥書に「右即位記一卷者光明峯寺禅閤自筆正記也以件本左令吾基春卿透以写之云々加挍正之 ... 永正七年夷則上浣 從一位(花押)」とあり|奥書に「右以或人夲自常州到来令書写之彼夲端書云此冊上下卷 ... 元禄第十二暦仲夏中旬 羽林左衞中郎将藤原定基丗一才」(承元3), 「右光明峯寺禅閤道家公承元二年三月五六月八月四年二三月九月十十一十二月記は借請或人之夲自常州邊来書写之加一挍了/于時元禄第十二端午節也 左中郎将藤原定基丗才」(承元4), 「右玉蘂建暦元年少弟左中将通清朝臣助筆僅加一挍原本文字不正後来得正夲可改之者也/元禄十三年九月十日 松堂閑士(花押)丗二才」(建暦元), 「右玉蘂峯禅閤記建暦二年自二月至九月一冊以或人夲自常州邊来命家僚令書写手自加挍合了/元禄十二年五月六日 左中郎将藤原定基丗一才」(建暦2年上), 「宝永二年十月一日書写畢/承久二春玉蘂以故常州牧權中納言光圀公夲謄写之于時俗務紛擾先請慈兄源亜相公所被写也今以彼夲手自馳禿筆 余識藤(花押)丗七才/同三年二月廿五日一挍了」(承久2年上), 「右峯摂政承久二年記命傭書謄冩之手自一挍了/元禄第十二嵗次著雍単閼蕤賓中旬 羽林軍左衞中郎将藤原定基丗一才」(承久2年下), 「嘉禎四年正月二月閏二月三月四月六月玉蘂先年假借故常州牧前中納言光圀夲無剋力速遂書写之功建暦元年建暦二年下承久二年上及此卷等先献慈兄亜相君写之今及数年申復彼夲謄写之 ... 宝永三年十二月念日 参議從三位行左近衞權中将藤原朝臣定基生年卅八才」(嘉禎4年)とあり|毎半葉11行注文双行|漢文体日記|拠徳川光圀本及び中院通躬鈔本謄写|朱筆書き入れあり|印記: 「定基」(野宮定基), 「野宮書印」|虫損あり (裏打ち補修あり)</t>
+          <t>書名は題簽による|毎半帖10行|漢字平仮名交じり文|奈良絵本|桜唐草文様緞子表紙, 松葉散しに山雲の金箔見返し, 金泥下絵鳥の子紙を使用|列帖装|二重箱入り</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -10054,28 +10034,28 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>図書</t>
+          <t>和古書</t>
         </is>
       </c>
       <c r="O79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/ca2da620-345c-76fa-9d1d-e7b2c55d757f.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/8aa19100-0937-5fd9-29f1-ba41ad8d1830.json</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>ca2da620-345c-76fa-9d1d-e7b2c55d757f</t>
+          <t>8aa19100-0937-5fd9-29f1-ba41ad8d1830</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/ca2da620-345c-76fa-9d1d-e7b2c55d757f</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/8aa19100-0937-5fd9-29f1-ba41ad8d1830</t>
         </is>
       </c>
       <c r="T79" t="inlineStr">
@@ -10085,12 +10065,12 @@
       </c>
       <c r="U79" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/8204e28b4e8f0e2f8abc1b939244f007093f3749.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/124815802d3a78d8f78dd4fbb98d24d55e5c3b34.jpg</t>
         </is>
       </c>
       <c r="V79" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296197</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1182819</t>
         </is>
       </c>
       <c r="W79" t="inlineStr">
@@ -10113,7 +10093,7 @@
       <c r="AB79" t="inlineStr"/>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/ca2da620-345c-76fa-9d1d-e7b2c55d757f/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/8aa19100-0937-5fd9-29f1-ba41ad8d1830/manifest</t>
         </is>
       </c>
       <c r="AD79" t="inlineStr"/>
@@ -10121,36 +10101,48 @@
       <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="inlineStr"/>
       <c r="AH79" t="n">
-        <v>63</v>
+        <v>33</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>大明星天子法 : 又名法界虚空蔵法</t>
+          <t>甲午日記 : 天保五年正月吉日</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>A00:6097</t>
+          <t>A00:4613</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>ダイミョウジョウテンシホウ : マタミョウ ホッカイ コクウゾウホウ</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr"/>
-      <c r="E80" t="inlineStr"/>
+          <t>コウゴ ニッキ : テンポウ ゴネン ショウガツ キチジツ</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>天保五年馬琴日記</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>滝沢 馬琴</t>
+        </is>
+      </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>[書写者不明]</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr"/>
+          <t>瀧澤馬琴 [自筆]</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>1834</t>
+        </is>
+      </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>[天文年間]</t>
+          <t>天保5</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -10158,11 +10150,15 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J80" t="inlineStr"/>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>写本</t>
+        </is>
+      </c>
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr">
         <is>
-          <t>写本|巻末の書名: 明星天子法|表紙の書名: 大明皇天子水|大尾に「明星天子法次苐 一交了」とあり|本奥書に「承久三年五月十三日/爲興法利生徃生極樂書冩之/金剛佛子觀照之」とあり|書袋に「天文古筆」, 「天明七未ノ年」とあり|毎半葉8行|押界を施した楮紙打紙を使用|粘葉装|虫損あり</t>
+          <t>書名は扉による|巻末に「已上午年日記畢」とあり|裏表紙に「神田 瀧澤」とあり|内容: 天保五甲午年春正月-12月|墨抹, 胡粉による修正あり|巻末の識語末に「昭和五年十二月に至って脩覆を了せり」とあり|虫損あり (裏打ち補修あり)</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -10172,28 +10168,28 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>図書</t>
+          <t>和古書</t>
         </is>
       </c>
       <c r="O80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/a1905fc7-4727-0750-41d7-f0ca1df53f47.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/c91cb308-03bd-94f5-3c56-9d0fac9424d3.json</t>
         </is>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>a1905fc7-4727-0750-41d7-f0ca1df53f47</t>
+          <t>c91cb308-03bd-94f5-3c56-9d0fac9424d3</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/a1905fc7-4727-0750-41d7-f0ca1df53f47</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/c91cb308-03bd-94f5-3c56-9d0fac9424d3</t>
         </is>
       </c>
       <c r="T80" t="inlineStr">
@@ -10203,12 +10199,12 @@
       </c>
       <c r="U80" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/b2590ef4e55f582d8059a5e072e1d6dad33bf996.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/92f1a1f83433e8cf04243d82fb0811e6cf653db2.jpg</t>
         </is>
       </c>
       <c r="V80" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296198</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1182820</t>
         </is>
       </c>
       <c r="W80" t="inlineStr">
@@ -10231,7 +10227,7 @@
       <c r="AB80" t="inlineStr"/>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/a1905fc7-4727-0750-41d7-f0ca1df53f47/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/c91cb308-03bd-94f5-3c56-9d0fac9424d3/manifest</t>
         </is>
       </c>
       <c r="AD80" t="inlineStr"/>
@@ -10239,30 +10235,26 @@
       <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="inlineStr"/>
       <c r="AH80" t="n">
-        <v>9</v>
+        <v>172</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>おちくほのさうし</t>
+          <t>天神記</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>A00:4083</t>
+          <t>A00:5770</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>オチクボ ノ ソウシ</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>おちくほ物語|御本</t>
-        </is>
-      </c>
+          <t>テンジンキ</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
         <is>
@@ -10272,7 +10264,7 @@
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr">
         <is>
-          <t>[江戸前期]</t>
+          <t>[室町末期-江戸前期]</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -10288,7 +10280,7 @@
       <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr">
         <is>
-          <t>書名は題簽による|毎半帖10行|漢字平仮名交じり文|奈良絵本|桜唐草文様緞子表紙, 松葉散しに山雲の金箔見返し, 金泥下絵鳥の子紙を使用|列帖装|二重箱入り</t>
+          <t>書名は表紙( 朱書)による|毎半葉13行|奈良絵本|秋草に籬の紺紙金泥表紙, 麻の葉繋ぎに丸龍文様の銀箔見返しを使用|印記: 「渡郶文庫珍藏書印」(渡部信)</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -10304,12 +10296,12 @@
       <c r="O81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/8aa19100-0937-5fd9-29f1-ba41ad8d1830.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/f7abc34f-6ff4-1309-4e13-cd69cce698b7.json</t>
         </is>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>8aa19100-0937-5fd9-29f1-ba41ad8d1830</t>
+          <t>f7abc34f-6ff4-1309-4e13-cd69cce698b7</t>
         </is>
       </c>
       <c r="R81" t="inlineStr">
@@ -10319,7 +10311,7 @@
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/8aa19100-0937-5fd9-29f1-ba41ad8d1830</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/f7abc34f-6ff4-1309-4e13-cd69cce698b7</t>
         </is>
       </c>
       <c r="T81" t="inlineStr">
@@ -10329,12 +10321,12 @@
       </c>
       <c r="U81" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/124815802d3a78d8f78dd4fbb98d24d55e5c3b34.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/b6b3dd9c0e350f9b1b14c1a2ba0d012e6762e42c.jpg</t>
         </is>
       </c>
       <c r="V81" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1182819</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1182821</t>
         </is>
       </c>
       <c r="W81" t="inlineStr">
@@ -10357,7 +10349,7 @@
       <c r="AB81" t="inlineStr"/>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/8aa19100-0937-5fd9-29f1-ba41ad8d1830/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/f7abc34f-6ff4-1309-4e13-cd69cce698b7/manifest</t>
         </is>
       </c>
       <c r="AD81" t="inlineStr"/>
@@ -10365,48 +10357,36 @@
       <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="inlineStr"/>
       <c r="AH81" t="n">
-        <v>33</v>
+        <v>14</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>甲午日記 : 天保五年正月吉日</t>
+          <t>各種殘經 : 出鄯善縣土峪溝</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>A00:4613</t>
+          <t>A00:4033</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>コウゴ ニッキ : テンポウ ゴネン ショウガツ キチジツ</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>天保五年馬琴日記</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>滝沢 馬琴</t>
-        </is>
-      </c>
+          <t>カクシュ ザンキョウ : シュツ ゼンゼンケン トヨクコウ</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr">
         <is>
-          <t>瀧澤馬琴 [自筆]</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>1834</t>
-        </is>
-      </c>
+          <t>[書写者不明]</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr">
         <is>
-          <t>天保5</t>
+          <t>[書写年不明]</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -10414,46 +10394,42 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>写本</t>
-        </is>
-      </c>
+      <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr">
         <is>
-          <t>書名は扉による|巻末に「已上午年日記畢」とあり|裏表紙に「神田 瀧澤」とあり|内容: 天保五甲午年春正月-12月|墨抹, 胡粉による修正あり|巻末の識語末に「昭和五年十二月に至って脩覆を了せり」とあり|虫損あり (裏打ち補修あり)</t>
+          <t>写本残片|書名は題簽による|題簽に「出鄯善縣土峪溝 素文珍藏」とあり|識語に「為楊枝甘露滴入紙中展巻把玩但覺異香盈字 晉卿」, 「右二紙係亜利安字 晉卿」, 「右二紙係畏吾児字 晉卿」とあり|蔵書票に「殘經佛像梵字 十五段 鄯善」, 「梵字第一號」とあり|巻子本|箱入|印記: 「臣樹枏印」, 「晉卿」, 「王仲子」, 「王樹枏印」</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>日本語</t>
+          <t>中国語</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>和古書</t>
+          <t>図書</t>
         </is>
       </c>
       <c r="O82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/c91cb308-03bd-94f5-3c56-9d0fac9424d3.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/704d2c7a-4882-6fc8-60d1-94c1e2799bbd.json</t>
         </is>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>c91cb308-03bd-94f5-3c56-9d0fac9424d3</t>
+          <t>704d2c7a-4882-6fc8-60d1-94c1e2799bbd</t>
         </is>
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/</t>
         </is>
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/c91cb308-03bd-94f5-3c56-9d0fac9424d3</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/704d2c7a-4882-6fc8-60d1-94c1e2799bbd</t>
         </is>
       </c>
       <c r="T82" t="inlineStr">
@@ -10463,12 +10439,12 @@
       </c>
       <c r="U82" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/92f1a1f83433e8cf04243d82fb0811e6cf653db2.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/4cc89d9a25687c69b3dc3791fd39ac740de2c4a0.jpg</t>
         </is>
       </c>
       <c r="V82" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1182820</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296165</t>
         </is>
       </c>
       <c r="W82" t="inlineStr">
@@ -10491,7 +10467,7 @@
       <c r="AB82" t="inlineStr"/>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/c91cb308-03bd-94f5-3c56-9d0fac9424d3/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/704d2c7a-4882-6fc8-60d1-94c1e2799bbd/manifest</t>
         </is>
       </c>
       <c r="AD82" t="inlineStr"/>
@@ -10499,27 +10475,31 @@
       <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="inlineStr"/>
       <c r="AH82" t="n">
-        <v>172</v>
+        <v>22</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>天神記</t>
+          <t>和漢朗詠集 2巻 [1]</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>A00:5770</t>
+          <t>A00:4081</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>テンジンキ</t>
+          <t>ワカン ロウエイシュウ</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
-      <c r="E83" t="inlineStr"/>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>藤原 公任</t>
+        </is>
+      </c>
       <c r="F83" t="inlineStr">
         <is>
           <t>[書写者不明]</t>
@@ -10528,23 +10508,19 @@
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr">
         <is>
-          <t>[室町末期-江戸前期]</t>
+          <t>[江戸前期]</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>写本</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
       <c r="L83" t="inlineStr">
         <is>
-          <t>書名は表紙( 朱書)による|毎半葉13行|奈良絵本|秋草に籬の紺紙金泥表紙, 麻の葉繋ぎに丸龍文様の銀箔見返しを使用|印記: 「渡郶文庫珍藏書印」(渡部信)</t>
+          <t>写本|書名は目首及び題簽による|外箱の書名: 御本|責任表示は『日本古典籍総合目録データベース』による|巻上: 春, 夏, 秋, 冬. 巻下: 雜|題簽による巻冊次表示: 上, 下|毎半帖8行|漢字平仮名交じり文|鳳凰菱繋ぎ文様緞子表紙, 松葉散しに山雲の金箔見返し, 金泥下絵鳥の子紙を使用|列帖装|二重箱入り</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -10554,28 +10530,28 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>和古書</t>
+          <t>図書</t>
         </is>
       </c>
       <c r="O83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/f7abc34f-6ff4-1309-4e13-cd69cce698b7.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/ba79db36-23e8-1a8a-1ad9-a5809c1109be.json</t>
         </is>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>f7abc34f-6ff4-1309-4e13-cd69cce698b7</t>
+          <t>ba79db36-23e8-1a8a-1ad9-a5809c1109be</t>
         </is>
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/f7abc34f-6ff4-1309-4e13-cd69cce698b7</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/ba79db36-23e8-1a8a-1ad9-a5809c1109be</t>
         </is>
       </c>
       <c r="T83" t="inlineStr">
@@ -10585,12 +10561,12 @@
       </c>
       <c r="U83" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/b6b3dd9c0e350f9b1b14c1a2ba0d012e6762e42c.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/0dbc6905fbe6d7441026c6ec7f4092a564cd7606.jpg</t>
         </is>
       </c>
       <c r="V83" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1182821</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296166</t>
         </is>
       </c>
       <c r="W83" t="inlineStr">
@@ -10613,7 +10589,7 @@
       <c r="AB83" t="inlineStr"/>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/f7abc34f-6ff4-1309-4e13-cd69cce698b7/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/ba79db36-23e8-1a8a-1ad9-a5809c1109be/manifest</t>
         </is>
       </c>
       <c r="AD83" t="inlineStr"/>
@@ -10621,7 +10597,7 @@
       <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="inlineStr"/>
       <c r="AH83" t="n">
-        <v>14</v>
+        <v>54</v>
       </c>
     </row>
     <row r="84">

--- a/docs/collections/koten/metadata/data.xlsx
+++ b/docs/collections/koten/metadata/data.xlsx
@@ -761,34 +761,34 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [20]</t>
+          <t>三摩耶戒作法 : 東寺</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>A00:6257</t>
+          <t>A00:6266</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>レキダイ ザンケツ ニッキ</t>
+          <t>サンマヤカイ サホウ : トウジ</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>黒川 春村</t>
+          <t>聖快</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>[書写者不明]</t>
+          <t>道快 [自筆]</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>[安政5 (1858)]</t>
+          <t>康暦元 [1379] 奥書</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -800,7 +800,7 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>写本|責任表示及び書写年は『日本古典籍総合目録データベース』による|内容: 6: 光明院御記, 後光嚴院御記, 後小松院宸記, 天聴集. 28: 参議藤定長卿記 : 稱山丞記. 37: 定高卿記, 晴御会部類記, 家光卿御記, 權中納言平範輔卿記. 38: 左大史小槻季継記, 後堀川安貞二年放生會(実基公記), 石清水八幡宮, 弁官拝賀次第. 39: 大外記師光記, 資季卿記, 荒凉記, 忠高卿記. 40: 冷泉公相公記, 勝延法眼記 : 東寺大行事, 後中記 : 小路中納言資頼卿記葉室. 41: 中光記, 師兼記, 陽龍記. 42: 大宮司長則記, 口筆 : 實經, 顕朝卿記, 鴨御幸記. 43: 寳治二年記, 深心院關白記, 藤公親記, 照念院関白兼平公記. 44: 頼親記, 亀山殿行幸記 : 雅言卿記, 兼基公記. 45: 大嘗會御禊節下次第, 建治三年丁丑日記 : 三善康有, 建治四年正月廿一日 : 徳大寺大相國公孝記, 冬定卿記, 左大史小槻兼文記|内容: 46: 經任卿記, 前豊前守藤憲説記, 實兼公記. 47: 継塵記抄出. 48: 管見記, 公衡公記, 大外記師顕記, 大外記中原師淳記. 49: 真光院禪助僧正記, 吉田内府卿記. 50: 定清記, 叅議雅俊卿記, 太政大臣(公守公)御上表雜事, 仙洞御灌頂日記, 正安二年八月十一日於仙洞被始行熾盛光法, 正安三年御譲位記. 51: 實躬卿記. 52: 公茂公記, 冬平公記, 隆長卿記. 53: 忠教公記, 官記, 正三位長基卿記, 北面秀長記, 大外記中原師右記. 54: 文保元年, 日野中納言資朝卿記, 洞院大納言公敏卿記. 55: 隆蔭卿記, 文保三年記, 尹大納言師賢卿記, 革命記, 立倚子記, 萬里小路中納言藤藤房卿記|内容: 56: 資名卿記, 公秀公記, 一條家記装束抄出, 頼定卿記. 63: 松亞記, 日野大納言時光卿記, 後八條内府實継公記. 74: 成恩寺関白記. 78: 山科家礼記. 82: 諒闇記 : 後成恩寺殿, 宗典僧正記, 綱光公記, 贈従二位宗賢卿記, 義政公記. 84: 長禄二年戊寅正月, 見聞雜記. 87: 言國卿記. 88: 長興宿祢記, 元長卿記, 兼顕卿記, 小槻晴冨記|28末の原奥書に「右山丞記依 仰挍合書冩/享和二年四月 日撿挍保己一」とあり|50「正安二年八月十一日於仙洞被始行熾盛光法」末の原奥書に「文化十五年春二月以南山法曼院藏夲書冩之 撿挍保己一」とあり|横刷毛目表紙を使用|朱点, 朱引, 朱墨筆書き入れあり|付箋あり|蔵書印主信濃須坂藩主堀直格の命によって編集された古記録|他の原本は関東大震災により焼失|極札に「桂壽」(6), 「尚信」(53)との極書, 「武清」(44, 53), 「永海」(51), 「了伴」(52), 「了甫」(74), 「定時」(84, 88)との極印あり|印記: 「花廼家文庫」, 「墨阪十一代主寫藏記」(堀直格(1806-1880)), 「東京大學法理文學部書庫所藏」, 「閲覧室用 FOR USE IN THE READING ROOM」|虫損あり</t>
+          <t>写本|書名は表紙による|本奥書に「康和元年十月廿日午時書了 深禅夲(第三轉)」, 「以小野僧正御夲理趣房書御夲也(初轉)」, 「承暦四年十一月十二日給預又書冩并傳受了 峯大阿闍梨御房事也(第二轉)」とあり|奥書に「康暦元年八月十二日於地藏院以平等坊永嚴自筆夲書冩之訖 東寺沙門道快」, 「同十四日於同院以或夲重挍合入落字注異説削謬詞尤可秘藏而已」とあり|表紙の貼紙に「康暦元年八月十二日於地藏院以平等坊永嚴自筆本書写之訖 東寺沙門道快 南北類」とある|巻子本|朱筆書き入れあり|淡墨界の料紙を使用(界匡廓: 19.5×2.0cm)|印記: 「僧正弘基」|破損, 虫損あり</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -816,12 +816,12 @@
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/d64280ea-576f-4bf3-9413-1b0bf6485e16.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/2b2562eb-7577-32f6-4c99-462a84e0647c.json</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>d64280ea-576f-4bf3-9413-1b0bf6485e16</t>
+          <t>2b2562eb-7577-32f6-4c99-462a84e0647c</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -831,7 +831,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/d64280ea-576f-4bf3-9413-1b0bf6485e16</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/2b2562eb-7577-32f6-4c99-462a84e0647c</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -841,12 +841,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/c5e3a0bdc0b67f7429d47677a33485a6a498e20f.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/60a9be2785b442f57f54089c594f63b8df5ae1f4.jpg</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296220</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296232</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -869,7 +869,7 @@
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/d64280ea-576f-4bf3-9413-1b0bf6485e16/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/2b2562eb-7577-32f6-4c99-462a84e0647c/manifest</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr"/>
@@ -877,52 +877,48 @@
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="n">
-        <v>75</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [21]</t>
+          <t>騁懐帖 2巻 [1]</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>A00:6257</t>
+          <t>A00:6379</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>レキダイ ザンケツ ニッキ</t>
+          <t>テイカイジョウ</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>黒川 春村</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>[書写者不明]</t>
-        </is>
-      </c>
+          <t>芳賀矢一[ほか自筆] ; 松本百藏 [集]</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>[安政5 (1858)]</t>
+          <t>[明治-昭和年間]</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>写本|責任表示及び書写年は『日本古典籍総合目録データベース』による|内容: 6: 光明院御記, 後光嚴院御記, 後小松院宸記, 天聴集. 28: 参議藤定長卿記 : 稱山丞記. 37: 定高卿記, 晴御会部類記, 家光卿御記, 權中納言平範輔卿記. 38: 左大史小槻季継記, 後堀川安貞二年放生會(実基公記), 石清水八幡宮, 弁官拝賀次第. 39: 大外記師光記, 資季卿記, 荒凉記, 忠高卿記. 40: 冷泉公相公記, 勝延法眼記 : 東寺大行事, 後中記 : 小路中納言資頼卿記葉室. 41: 中光記, 師兼記, 陽龍記. 42: 大宮司長則記, 口筆 : 實經, 顕朝卿記, 鴨御幸記. 43: 寳治二年記, 深心院關白記, 藤公親記, 照念院関白兼平公記. 44: 頼親記, 亀山殿行幸記 : 雅言卿記, 兼基公記. 45: 大嘗會御禊節下次第, 建治三年丁丑日記 : 三善康有, 建治四年正月廿一日 : 徳大寺大相國公孝記, 冬定卿記, 左大史小槻兼文記|内容: 46: 經任卿記, 前豊前守藤憲説記, 實兼公記. 47: 継塵記抄出. 48: 管見記, 公衡公記, 大外記師顕記, 大外記中原師淳記. 49: 真光院禪助僧正記, 吉田内府卿記. 50: 定清記, 叅議雅俊卿記, 太政大臣(公守公)御上表雜事, 仙洞御灌頂日記, 正安二年八月十一日於仙洞被始行熾盛光法, 正安三年御譲位記. 51: 實躬卿記. 52: 公茂公記, 冬平公記, 隆長卿記. 53: 忠教公記, 官記, 正三位長基卿記, 北面秀長記, 大外記中原師右記. 54: 文保元年, 日野中納言資朝卿記, 洞院大納言公敏卿記. 55: 隆蔭卿記, 文保三年記, 尹大納言師賢卿記, 革命記, 立倚子記, 萬里小路中納言藤藤房卿記|内容: 56: 資名卿記, 公秀公記, 一條家記装束抄出, 頼定卿記. 63: 松亞記, 日野大納言時光卿記, 後八條内府實継公記. 74: 成恩寺関白記. 78: 山科家礼記. 82: 諒闇記 : 後成恩寺殿, 宗典僧正記, 綱光公記, 贈従二位宗賢卿記, 義政公記. 84: 長禄二年戊寅正月, 見聞雜記. 87: 言國卿記. 88: 長興宿祢記, 元長卿記, 兼顕卿記, 小槻晴冨記|28末の原奥書に「右山丞記依 仰挍合書冩/享和二年四月 日撿挍保己一」とあり|50「正安二年八月十一日於仙洞被始行熾盛光法」末の原奥書に「文化十五年春二月以南山法曼院藏夲書冩之 撿挍保己一」とあり|横刷毛目表紙を使用|朱点, 朱引, 朱墨筆書き入れあり|付箋あり|蔵書印主信濃須坂藩主堀直格の命によって編集された古記録|他の原本は関東大震災により焼失|極札に「桂壽」(6), 「尚信」(53)との極書, 「武清」(44, 53), 「永海」(51), 「了伴」(52), 「了甫」(74), 「定時」(84, 88)との極印あり|印記: 「花廼家文庫」, 「墨阪十一代主寫藏記」(堀直格(1806-1880)), 「東京大學法理文學部書庫所藏」, 「閲覧室用 FOR USE IN THE READING ROOM」|虫損あり</t>
+          <t>写本|書名及び巻冊次は題簽による|跋末に「松夲生名ハ百藏東京帝國大學ノ使丁タリ職ヲ山上會議所ニ奉スルコト四十有餘年 ... 頃来マタ諸賢ノ揮毫ヲ乞上名ケテ騁懐帖トイフ ... 帖成リテ予ニ其由来ヲ記セシコトヲ求ム乃チ之ヲ録シテ以テ跋後トス 昭和二年三月 辻善之助識」とあり|折本|書画帖|彩色あり|名録2冊(大和綴)を付す|落款朱印: 「長成」(坪井九馬三), 「圭卿」(市村瓚次郎), 「簣山」(鹽谷時敏), 「維亭」(塚本靖), 「土肥慶藏」, 「忠太」(伊東忠太), 「萬」(和田万吉), 「芳溪」(呉秀三), 「前田慧雲」, 「大澤謙二」, 「南條文雄」, 「有坂氏」(有坂鉊藏), 「博」, 「石亭」(林博太郎), 「長與又郎」, 「宇野哲人」, ほかあり</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -938,12 +934,12 @@
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/decc377c-887e-7362-3bf7-81b1c9c58641.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/bfdc576b-6ce2-9274-914e-8cc9c52c04de.json</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>decc377c-887e-7362-3bf7-81b1c9c58641</t>
+          <t>bfdc576b-6ce2-9274-914e-8cc9c52c04de</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -953,7 +949,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/decc377c-887e-7362-3bf7-81b1c9c58641</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/bfdc576b-6ce2-9274-914e-8cc9c52c04de</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -963,12 +959,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/cfd0eab55fb67ed7ab341ab27bc1cb892d7a575c.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/4061afb959aba92577bf3357712e3556cd07cf8e.jpg</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296221</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296233</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -991,7 +987,7 @@
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/decc377c-887e-7362-3bf7-81b1c9c58641/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/bfdc576b-6ce2-9274-914e-8cc9c52c04de/manifest</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr"/>
@@ -999,52 +995,48 @@
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="n">
-        <v>51</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [22]</t>
+          <t>騁懐帖 2巻 [2]</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>A00:6257</t>
+          <t>A00:6379</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>レキダイ ザンケツ ニッキ</t>
+          <t>テイカイジョウ</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>黒川 春村</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>[書写者不明]</t>
-        </is>
-      </c>
+          <t>芳賀矢一[ほか自筆] ; 松本百藏 [集]</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>[安政5 (1858)]</t>
+          <t>[明治-昭和年間]</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>写本|責任表示及び書写年は『日本古典籍総合目録データベース』による|内容: 6: 光明院御記, 後光嚴院御記, 後小松院宸記, 天聴集. 28: 参議藤定長卿記 : 稱山丞記. 37: 定高卿記, 晴御会部類記, 家光卿御記, 權中納言平範輔卿記. 38: 左大史小槻季継記, 後堀川安貞二年放生會(実基公記), 石清水八幡宮, 弁官拝賀次第. 39: 大外記師光記, 資季卿記, 荒凉記, 忠高卿記. 40: 冷泉公相公記, 勝延法眼記 : 東寺大行事, 後中記 : 小路中納言資頼卿記葉室. 41: 中光記, 師兼記, 陽龍記. 42: 大宮司長則記, 口筆 : 實經, 顕朝卿記, 鴨御幸記. 43: 寳治二年記, 深心院關白記, 藤公親記, 照念院関白兼平公記. 44: 頼親記, 亀山殿行幸記 : 雅言卿記, 兼基公記. 45: 大嘗會御禊節下次第, 建治三年丁丑日記 : 三善康有, 建治四年正月廿一日 : 徳大寺大相國公孝記, 冬定卿記, 左大史小槻兼文記|内容: 46: 經任卿記, 前豊前守藤憲説記, 實兼公記. 47: 継塵記抄出. 48: 管見記, 公衡公記, 大外記師顕記, 大外記中原師淳記. 49: 真光院禪助僧正記, 吉田内府卿記. 50: 定清記, 叅議雅俊卿記, 太政大臣(公守公)御上表雜事, 仙洞御灌頂日記, 正安二年八月十一日於仙洞被始行熾盛光法, 正安三年御譲位記. 51: 實躬卿記. 52: 公茂公記, 冬平公記, 隆長卿記. 53: 忠教公記, 官記, 正三位長基卿記, 北面秀長記, 大外記中原師右記. 54: 文保元年, 日野中納言資朝卿記, 洞院大納言公敏卿記. 55: 隆蔭卿記, 文保三年記, 尹大納言師賢卿記, 革命記, 立倚子記, 萬里小路中納言藤藤房卿記|内容: 56: 資名卿記, 公秀公記, 一條家記装束抄出, 頼定卿記. 63: 松亞記, 日野大納言時光卿記, 後八條内府實継公記. 74: 成恩寺関白記. 78: 山科家礼記. 82: 諒闇記 : 後成恩寺殿, 宗典僧正記, 綱光公記, 贈従二位宗賢卿記, 義政公記. 84: 長禄二年戊寅正月, 見聞雜記. 87: 言國卿記. 88: 長興宿祢記, 元長卿記, 兼顕卿記, 小槻晴冨記|28末の原奥書に「右山丞記依 仰挍合書冩/享和二年四月 日撿挍保己一」とあり|50「正安二年八月十一日於仙洞被始行熾盛光法」末の原奥書に「文化十五年春二月以南山法曼院藏夲書冩之 撿挍保己一」とあり|横刷毛目表紙を使用|朱点, 朱引, 朱墨筆書き入れあり|付箋あり|蔵書印主信濃須坂藩主堀直格の命によって編集された古記録|他の原本は関東大震災により焼失|極札に「桂壽」(6), 「尚信」(53)との極書, 「武清」(44, 53), 「永海」(51), 「了伴」(52), 「了甫」(74), 「定時」(84, 88)との極印あり|印記: 「花廼家文庫」, 「墨阪十一代主寫藏記」(堀直格(1806-1880)), 「東京大學法理文學部書庫所藏」, 「閲覧室用 FOR USE IN THE READING ROOM」|虫損あり</t>
+          <t>写本|書名及び巻冊次は題簽による|跋末に「松夲生名ハ百藏東京帝國大學ノ使丁タリ職ヲ山上會議所ニ奉スルコト四十有餘年 ... 頃来マタ諸賢ノ揮毫ヲ乞上名ケテ騁懐帖トイフ ... 帖成リテ予ニ其由来ヲ記セシコトヲ求ム乃チ之ヲ録シテ以テ跋後トス 昭和二年三月 辻善之助識」とあり|折本|書画帖|彩色あり|名録2冊(大和綴)を付す|落款朱印: 「長成」(坪井九馬三), 「圭卿」(市村瓚次郎), 「簣山」(鹽谷時敏), 「維亭」(塚本靖), 「土肥慶藏」, 「忠太」(伊東忠太), 「萬」(和田万吉), 「芳溪」(呉秀三), 「前田慧雲」, 「大澤謙二」, 「南條文雄」, 「有坂氏」(有坂鉊藏), 「博」, 「石亭」(林博太郎), 「長與又郎」, 「宇野哲人」, ほかあり</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -1060,12 +1052,12 @@
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/b6bde9f3-3f94-81f1-4307-d86d59d90fa3.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/6a4c18fb-90e9-6d15-1234-9cadcc683544.json</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>b6bde9f3-3f94-81f1-4307-d86d59d90fa3</t>
+          <t>6a4c18fb-90e9-6d15-1234-9cadcc683544</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -1075,7 +1067,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/b6bde9f3-3f94-81f1-4307-d86d59d90fa3</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/6a4c18fb-90e9-6d15-1234-9cadcc683544</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1085,12 +1077,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/eda09740787be30df4b5cefc348bc2c063c8932c.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/f705bcd1873bb88e3f1edef2b79dcc86dc2c417b.jpg</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296222</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296234</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1113,7 +1105,7 @@
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/b6bde9f3-3f94-81f1-4307-d86d59d90fa3/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/6a4c18fb-90e9-6d15-1234-9cadcc683544/manifest</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr"/>
@@ -1121,40 +1113,36 @@
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="n">
-        <v>62</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [23]</t>
+          <t>清玩書巻</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>A00:6257</t>
+          <t>A00:6380</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>レキダイ ザンケツ ニッキ</t>
+          <t>セイガン ショカン</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>黒川 春村</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>[書写者不明]</t>
-        </is>
-      </c>
+          <t>石黒忠悳[ほか自筆] ; [松本百藏収集]</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>[安政5 (1858)]</t>
+          <t>[明治大正年間]</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1166,7 +1154,7 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>写本|責任表示及び書写年は『日本古典籍総合目録データベース』による|内容: 6: 光明院御記, 後光嚴院御記, 後小松院宸記, 天聴集. 28: 参議藤定長卿記 : 稱山丞記. 37: 定高卿記, 晴御会部類記, 家光卿御記, 權中納言平範輔卿記. 38: 左大史小槻季継記, 後堀川安貞二年放生會(実基公記), 石清水八幡宮, 弁官拝賀次第. 39: 大外記師光記, 資季卿記, 荒凉記, 忠高卿記. 40: 冷泉公相公記, 勝延法眼記 : 東寺大行事, 後中記 : 小路中納言資頼卿記葉室. 41: 中光記, 師兼記, 陽龍記. 42: 大宮司長則記, 口筆 : 實經, 顕朝卿記, 鴨御幸記. 43: 寳治二年記, 深心院關白記, 藤公親記, 照念院関白兼平公記. 44: 頼親記, 亀山殿行幸記 : 雅言卿記, 兼基公記. 45: 大嘗會御禊節下次第, 建治三年丁丑日記 : 三善康有, 建治四年正月廿一日 : 徳大寺大相國公孝記, 冬定卿記, 左大史小槻兼文記|内容: 46: 經任卿記, 前豊前守藤憲説記, 實兼公記. 47: 継塵記抄出. 48: 管見記, 公衡公記, 大外記師顕記, 大外記中原師淳記. 49: 真光院禪助僧正記, 吉田内府卿記. 50: 定清記, 叅議雅俊卿記, 太政大臣(公守公)御上表雜事, 仙洞御灌頂日記, 正安二年八月十一日於仙洞被始行熾盛光法, 正安三年御譲位記. 51: 實躬卿記. 52: 公茂公記, 冬平公記, 隆長卿記. 53: 忠教公記, 官記, 正三位長基卿記, 北面秀長記, 大外記中原師右記. 54: 文保元年, 日野中納言資朝卿記, 洞院大納言公敏卿記. 55: 隆蔭卿記, 文保三年記, 尹大納言師賢卿記, 革命記, 立倚子記, 萬里小路中納言藤藤房卿記|内容: 56: 資名卿記, 公秀公記, 一條家記装束抄出, 頼定卿記. 63: 松亞記, 日野大納言時光卿記, 後八條内府實継公記. 74: 成恩寺関白記. 78: 山科家礼記. 82: 諒闇記 : 後成恩寺殿, 宗典僧正記, 綱光公記, 贈従二位宗賢卿記, 義政公記. 84: 長禄二年戊寅正月, 見聞雜記. 87: 言國卿記. 88: 長興宿祢記, 元長卿記, 兼顕卿記, 小槻晴冨記|28末の原奥書に「右山丞記依 仰挍合書冩/享和二年四月 日撿挍保己一」とあり|50「正安二年八月十一日於仙洞被始行熾盛光法」末の原奥書に「文化十五年春二月以南山法曼院藏夲書冩之 撿挍保己一」とあり|横刷毛目表紙を使用|朱点, 朱引, 朱墨筆書き入れあり|付箋あり|蔵書印主信濃須坂藩主堀直格の命によって編集された古記録|他の原本は関東大震災により焼失|極札に「桂壽」(6), 「尚信」(53)との極書, 「武清」(44, 53), 「永海」(51), 「了伴」(52), 「了甫」(74), 「定時」(84, 88)との極印あり|印記: 「花廼家文庫」, 「墨阪十一代主寫藏記」(堀直格(1806-1880)), 「東京大學法理文學部書庫所藏」, 「閲覧室用 FOR USE IN THE READING ROOM」|虫損あり</t>
+          <t>写本|書名は題簽による|その他の筆者: 市村瓚次郎, 外山正一, 緒方正規, 村上専精, 佐藤進, 菊池大麓, 三宅秀, 箕作佳吉, 三上參次, 箕作元八|冒頭に井上哲の題辞「清玩」あり|巻末に萩野由之の識語あり|収集者は『理翰片影』&lt;BC06713253&gt;の跋による|巻子本|往来書簡貼付集|名録1冊(大和綴)を付す|落款朱印: 「文学博士」, 「井上喆」, 「井上哲印」(井上哲次郎), 「和葊」(萩野由之)</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1182,12 +1170,12 @@
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/8bd2b968-05d3-77b9-352f-f36fa2260d39.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/ae3b180b-9cbe-6902-48c2-f0abfdf0a27e.json</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>8bd2b968-05d3-77b9-352f-f36fa2260d39</t>
+          <t>ae3b180b-9cbe-6902-48c2-f0abfdf0a27e</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1197,7 +1185,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/8bd2b968-05d3-77b9-352f-f36fa2260d39</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/ae3b180b-9cbe-6902-48c2-f0abfdf0a27e</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1207,12 +1195,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/30225b7ec7795f0c4d6102081bbf79b701183504.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/e799186565cb40d919d91c02eef1308118771dd3.jpg</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296223</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296235</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1235,7 +1223,7 @@
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/8bd2b968-05d3-77b9-352f-f36fa2260d39/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/ae3b180b-9cbe-6902-48c2-f0abfdf0a27e/manifest</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr"/>
@@ -1243,40 +1231,36 @@
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="inlineStr"/>
       <c r="AH6" t="n">
-        <v>74</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [24]</t>
+          <t>聚珍書巻</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>A00:6257</t>
+          <t>A00:6381</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>レキダイ ザンケツ ニッキ</t>
+          <t>シュウチン ショカン</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>黒川 春村</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>[書写者不明]</t>
-        </is>
-      </c>
+          <t>濱尾新 [ほか自筆] ; 松本百藏 [収集]</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>[安政5 (1858)]</t>
+          <t>[明治年間]</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1288,7 +1272,7 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>写本|責任表示及び書写年は『日本古典籍総合目録データベース』による|内容: 6: 光明院御記, 後光嚴院御記, 後小松院宸記, 天聴集. 28: 参議藤定長卿記 : 稱山丞記. 37: 定高卿記, 晴御会部類記, 家光卿御記, 權中納言平範輔卿記. 38: 左大史小槻季継記, 後堀川安貞二年放生會(実基公記), 石清水八幡宮, 弁官拝賀次第. 39: 大外記師光記, 資季卿記, 荒凉記, 忠高卿記. 40: 冷泉公相公記, 勝延法眼記 : 東寺大行事, 後中記 : 小路中納言資頼卿記葉室. 41: 中光記, 師兼記, 陽龍記. 42: 大宮司長則記, 口筆 : 實經, 顕朝卿記, 鴨御幸記. 43: 寳治二年記, 深心院關白記, 藤公親記, 照念院関白兼平公記. 44: 頼親記, 亀山殿行幸記 : 雅言卿記, 兼基公記. 45: 大嘗會御禊節下次第, 建治三年丁丑日記 : 三善康有, 建治四年正月廿一日 : 徳大寺大相國公孝記, 冬定卿記, 左大史小槻兼文記|内容: 46: 經任卿記, 前豊前守藤憲説記, 實兼公記. 47: 継塵記抄出. 48: 管見記, 公衡公記, 大外記師顕記, 大外記中原師淳記. 49: 真光院禪助僧正記, 吉田内府卿記. 50: 定清記, 叅議雅俊卿記, 太政大臣(公守公)御上表雜事, 仙洞御灌頂日記, 正安二年八月十一日於仙洞被始行熾盛光法, 正安三年御譲位記. 51: 實躬卿記. 52: 公茂公記, 冬平公記, 隆長卿記. 53: 忠教公記, 官記, 正三位長基卿記, 北面秀長記, 大外記中原師右記. 54: 文保元年, 日野中納言資朝卿記, 洞院大納言公敏卿記. 55: 隆蔭卿記, 文保三年記, 尹大納言師賢卿記, 革命記, 立倚子記, 萬里小路中納言藤藤房卿記|内容: 56: 資名卿記, 公秀公記, 一條家記装束抄出, 頼定卿記. 63: 松亞記, 日野大納言時光卿記, 後八條内府實継公記. 74: 成恩寺関白記. 78: 山科家礼記. 82: 諒闇記 : 後成恩寺殿, 宗典僧正記, 綱光公記, 贈従二位宗賢卿記, 義政公記. 84: 長禄二年戊寅正月, 見聞雜記. 87: 言國卿記. 88: 長興宿祢記, 元長卿記, 兼顕卿記, 小槻晴冨記|28末の原奥書に「右山丞記依 仰挍合書冩/享和二年四月 日撿挍保己一」とあり|50「正安二年八月十一日於仙洞被始行熾盛光法」末の原奥書に「文化十五年春二月以南山法曼院藏夲書冩之 撿挍保己一」とあり|横刷毛目表紙を使用|朱点, 朱引, 朱墨筆書き入れあり|付箋あり|蔵書印主信濃須坂藩主堀直格の命によって編集された古記録|他の原本は関東大震災により焼失|極札に「桂壽」(6), 「尚信」(53)との極書, 「武清」(44, 53), 「永海」(51), 「了伴」(52), 「了甫」(74), 「定時」(84, 88)との極印あり|印記: 「花廼家文庫」, 「墨阪十一代主寫藏記」(堀直格(1806-1880)), 「東京大學法理文學部書庫所藏」, 「閲覧室用 FOR USE IN THE READING ROOM」|虫損あり</t>
+          <t>写本|書名は題簽による|題辞に「聚珍 明治己酉夏八十三老人成斎題」とあり|巻末識語に「松本百蔵為東亰帝國大學厮養二十餘年毎掃故紙籠見有文字者輒収而弆之頃揀其署名氏者十餘紙装潢成卷皆名賢鉅公碩學鴻儒之筆也 ... 明治庚戌二月初夏 豊城陳人恒書時年七十又二」とあり|その他の筆者: 細川潤次郎, 渡邊洪基, 加藤弘之, 川田剛, 辻新次, 中村正直, 古市公威, 小中村清矩, 木村正辭, 島田重禮|巻子本|往来書簡貼付集|名録1冊(大和綴)を付す|落款朱印: 「晩香」, 「徳天」, 「星野恒印」, 「續古堂」, 「重野」, 「重埜士徳」, 「藤原安繹」</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1304,12 +1288,12 @@
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/c6e97538-22ed-8a51-0e3a-550b7d652860.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/4e78ded3-2829-990e-572b-4b5e029a69cc.json</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>c6e97538-22ed-8a51-0e3a-550b7d652860</t>
+          <t>4e78ded3-2829-990e-572b-4b5e029a69cc</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1319,7 +1303,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/c6e97538-22ed-8a51-0e3a-550b7d652860</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/4e78ded3-2829-990e-572b-4b5e029a69cc</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1329,12 +1313,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/a04dfdaed6c9dc7211358c5ad96c4bc6e9312747.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/fe6e0e801688014b204ebe9deee8085c19831bc3.jpg</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296224</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296236</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1357,7 +1341,7 @@
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/c6e97538-22ed-8a51-0e3a-550b7d652860/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/4e78ded3-2829-990e-572b-4b5e029a69cc/manifest</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr"/>
@@ -1365,40 +1349,36 @@
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="inlineStr"/>
       <c r="AH7" t="n">
-        <v>62</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [25]</t>
+          <t>理翰片影</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>A00:6257</t>
+          <t>A00:6382</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>レキダイ ザンケツ ニッキ</t>
+          <t>リカン ヘンエイ</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>黒川 春村</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>[書写者不明]</t>
-        </is>
-      </c>
+          <t>井上毅 [ほか自筆] ; 松本百藏 [蒐集]</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>[安政5 (1858)]</t>
+          <t>[明治大正年間]</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1410,7 +1390,7 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>写本|責任表示及び書写年は『日本古典籍総合目録データベース』による|内容: 6: 光明院御記, 後光嚴院御記, 後小松院宸記, 天聴集. 28: 参議藤定長卿記 : 稱山丞記. 37: 定高卿記, 晴御会部類記, 家光卿御記, 權中納言平範輔卿記. 38: 左大史小槻季継記, 後堀川安貞二年放生會(実基公記), 石清水八幡宮, 弁官拝賀次第. 39: 大外記師光記, 資季卿記, 荒凉記, 忠高卿記. 40: 冷泉公相公記, 勝延法眼記 : 東寺大行事, 後中記 : 小路中納言資頼卿記葉室. 41: 中光記, 師兼記, 陽龍記. 42: 大宮司長則記, 口筆 : 實經, 顕朝卿記, 鴨御幸記. 43: 寳治二年記, 深心院關白記, 藤公親記, 照念院関白兼平公記. 44: 頼親記, 亀山殿行幸記 : 雅言卿記, 兼基公記. 45: 大嘗會御禊節下次第, 建治三年丁丑日記 : 三善康有, 建治四年正月廿一日 : 徳大寺大相國公孝記, 冬定卿記, 左大史小槻兼文記|内容: 46: 經任卿記, 前豊前守藤憲説記, 實兼公記. 47: 継塵記抄出. 48: 管見記, 公衡公記, 大外記師顕記, 大外記中原師淳記. 49: 真光院禪助僧正記, 吉田内府卿記. 50: 定清記, 叅議雅俊卿記, 太政大臣(公守公)御上表雜事, 仙洞御灌頂日記, 正安二年八月十一日於仙洞被始行熾盛光法, 正安三年御譲位記. 51: 實躬卿記. 52: 公茂公記, 冬平公記, 隆長卿記. 53: 忠教公記, 官記, 正三位長基卿記, 北面秀長記, 大外記中原師右記. 54: 文保元年, 日野中納言資朝卿記, 洞院大納言公敏卿記. 55: 隆蔭卿記, 文保三年記, 尹大納言師賢卿記, 革命記, 立倚子記, 萬里小路中納言藤藤房卿記|内容: 56: 資名卿記, 公秀公記, 一條家記装束抄出, 頼定卿記. 63: 松亞記, 日野大納言時光卿記, 後八條内府實継公記. 74: 成恩寺関白記. 78: 山科家礼記. 82: 諒闇記 : 後成恩寺殿, 宗典僧正記, 綱光公記, 贈従二位宗賢卿記, 義政公記. 84: 長禄二年戊寅正月, 見聞雜記. 87: 言國卿記. 88: 長興宿祢記, 元長卿記, 兼顕卿記, 小槻晴冨記|28末の原奥書に「右山丞記依 仰挍合書冩/享和二年四月 日撿挍保己一」とあり|50「正安二年八月十一日於仙洞被始行熾盛光法」末の原奥書に「文化十五年春二月以南山法曼院藏夲書冩之 撿挍保己一」とあり|横刷毛目表紙を使用|朱点, 朱引, 朱墨筆書き入れあり|付箋あり|蔵書印主信濃須坂藩主堀直格の命によって編集された古記録|他の原本は関東大震災により焼失|極札に「桂壽」(6), 「尚信」(53)との極書, 「武清」(44, 53), 「永海」(51), 「了伴」(52), 「了甫」(74), 「定時」(84, 88)との極印あり|印記: 「花廼家文庫」, 「墨阪十一代主寫藏記」(堀直格(1806-1880)), 「東京大學法理文學部書庫所藏」, 「閲覧室用 FOR USE IN THE READING ROOM」|虫損あり</t>
+          <t>写本|書名は題簽による|敘に「松本百藏君我が東京帝國大學に縁故ある諸君の筆蹟を蒐集シ己ニ三卷をなす此卷収む事といわは故子爵井上毅先生をはじめとし神保小虎博士に至るまで十二君の消息なり ... 大正十四年春日三上参次(花押)」とあり|跋に「松本百藏奉職東京帝國大學勞使四十年夙昔不怠其所勤非尋常也大正十四年以古稀辤其軄以平生所収簡牘装潢之得四巻二帖納大學書庫 ... 大正十五年五月於東京帝國大學夲部象軒平野直文識」とあり|その他の筆者: 八代六郎, 垪和爲昌, 鶴田賢次, 長井長義, 久原躬弦, 藤澤利喜太郎, 小藤文次郎, 寺野精一, 青山胤通, 佐藤三吉, 神保小乕|巻子本|往来書簡貼付集|落款朱印: 「士可」, 「虚坣居士」, 「平野直文」</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1426,12 +1406,12 @@
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/48123112-700b-8619-731b-649449ff034b.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/31b15e19-44d8-6c52-9780-873a7f1a2480.json</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>48123112-700b-8619-731b-649449ff034b</t>
+          <t>31b15e19-44d8-6c52-9780-873a7f1a2480</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1441,7 +1421,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/48123112-700b-8619-731b-649449ff034b</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/31b15e19-44d8-6c52-9780-873a7f1a2480</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -1451,12 +1431,12 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/4c918a15ed3dc97a18f7bc977b4dc2e8c724d774.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/c34f4eff76edef5a959de5048f588d40ac1cccac.jpg</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296225</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296237</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -1479,7 +1459,7 @@
       <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/48123112-700b-8619-731b-649449ff034b/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/31b15e19-44d8-6c52-9780-873a7f1a2480/manifest</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr"/>
@@ -1487,40 +1467,36 @@
       <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="inlineStr"/>
       <c r="AH8" t="n">
-        <v>78</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [26]</t>
+          <t>學海拾遺珠</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>A00:6257</t>
+          <t>A00:6383</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>レキダイ ザンケツ ニッキ</t>
+          <t>ガッカイ シュウイシュ</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>黒川 春村</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>[書写者不明]</t>
-        </is>
-      </c>
+          <t>渡邊渡 [ほか自筆] ; 松本[百藏 集]</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>[安政5 (1858)]</t>
+          <t>[明治大正年間]</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1532,7 +1508,7 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>写本|責任表示及び書写年は『日本古典籍総合目録データベース』による|内容: 6: 光明院御記, 後光嚴院御記, 後小松院宸記, 天聴集. 28: 参議藤定長卿記 : 稱山丞記. 37: 定高卿記, 晴御会部類記, 家光卿御記, 權中納言平範輔卿記. 38: 左大史小槻季継記, 後堀川安貞二年放生會(実基公記), 石清水八幡宮, 弁官拝賀次第. 39: 大外記師光記, 資季卿記, 荒凉記, 忠高卿記. 40: 冷泉公相公記, 勝延法眼記 : 東寺大行事, 後中記 : 小路中納言資頼卿記葉室. 41: 中光記, 師兼記, 陽龍記. 42: 大宮司長則記, 口筆 : 實經, 顕朝卿記, 鴨御幸記. 43: 寳治二年記, 深心院關白記, 藤公親記, 照念院関白兼平公記. 44: 頼親記, 亀山殿行幸記 : 雅言卿記, 兼基公記. 45: 大嘗會御禊節下次第, 建治三年丁丑日記 : 三善康有, 建治四年正月廿一日 : 徳大寺大相國公孝記, 冬定卿記, 左大史小槻兼文記|内容: 46: 經任卿記, 前豊前守藤憲説記, 實兼公記. 47: 継塵記抄出. 48: 管見記, 公衡公記, 大外記師顕記, 大外記中原師淳記. 49: 真光院禪助僧正記, 吉田内府卿記. 50: 定清記, 叅議雅俊卿記, 太政大臣(公守公)御上表雜事, 仙洞御灌頂日記, 正安二年八月十一日於仙洞被始行熾盛光法, 正安三年御譲位記. 51: 實躬卿記. 52: 公茂公記, 冬平公記, 隆長卿記. 53: 忠教公記, 官記, 正三位長基卿記, 北面秀長記, 大外記中原師右記. 54: 文保元年, 日野中納言資朝卿記, 洞院大納言公敏卿記. 55: 隆蔭卿記, 文保三年記, 尹大納言師賢卿記, 革命記, 立倚子記, 萬里小路中納言藤藤房卿記|内容: 56: 資名卿記, 公秀公記, 一條家記装束抄出, 頼定卿記. 63: 松亞記, 日野大納言時光卿記, 後八條内府實継公記. 74: 成恩寺関白記. 78: 山科家礼記. 82: 諒闇記 : 後成恩寺殿, 宗典僧正記, 綱光公記, 贈従二位宗賢卿記, 義政公記. 84: 長禄二年戊寅正月, 見聞雜記. 87: 言國卿記. 88: 長興宿祢記, 元長卿記, 兼顕卿記, 小槻晴冨記|28末の原奥書に「右山丞記依 仰挍合書冩/享和二年四月 日撿挍保己一」とあり|50「正安二年八月十一日於仙洞被始行熾盛光法」末の原奥書に「文化十五年春二月以南山法曼院藏夲書冩之 撿挍保己一」とあり|横刷毛目表紙を使用|朱点, 朱引, 朱墨筆書き入れあり|付箋あり|蔵書印主信濃須坂藩主堀直格の命によって編集された古記録|他の原本は関東大震災により焼失|極札に「桂壽」(6), 「尚信」(53)との極書, 「武清」(44, 53), 「永海」(51), 「了伴」(52), 「了甫」(74), 「定時」(84, 88)との極印あり|印記: 「花廼家文庫」, 「墨阪十一代主寫藏記」(堀直格(1806-1880)), 「東京大學法理文學部書庫所藏」, 「閲覧室用 FOR USE IN THE READING ROOM」|虫損あり</t>
+          <t>写本|書名は題簽による|題辞に「學海拾遺珠 大正十二年初夏 讀律書屋主人題」とあり|巻末識語に「東京帝國大學の地小丘有り丘上に會議所有り總長教授等會食聚議の處と為に松本君其の役たると久し親しく碩學大家に接し之を敬するを知る留意して敗紙中に諸家の手跡を索め嵗月を累収て十数家に及へは輙ち裝潢して卷を成す今や第三卷成り文を予に求む松本君孤影孑然會議所に起臥す伴侶は唯名家手簡と手栽の盆柎有るのみ ... 大正十二年二月十九日 隨軒學人」とあり|その他の筆者: 和田垣謙三, 川瀬善太郎, 高松豊吉, 田中義成, 永井久一郎, 中村恭平, 山川健次郎, 松井直吉, 松村任三, 古在由直, 寺尾寿, 櫻井錠二, 清水彦五郎|巻子本|往来書簡貼付集|名録1冊(大和綴)を付す|落款朱印: 「讀經堂主人號随軒」, 「服部宇之吉印記」, 「直文」(平野直文)</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1548,12 +1524,12 @@
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/9b2b928b-4eda-76c6-0dfd-03bde69c046c.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/9639e5f3-92bd-7423-1bf1-08c4dc087bdf.json</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>9b2b928b-4eda-76c6-0dfd-03bde69c046c</t>
+          <t>9639e5f3-92bd-7423-1bf1-08c4dc087bdf</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1563,7 +1539,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/9b2b928b-4eda-76c6-0dfd-03bde69c046c</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/9639e5f3-92bd-7423-1bf1-08c4dc087bdf</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
@@ -1573,12 +1549,12 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/7903cd89a232a0d9b4b243d90852d31d93c80300.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/b210fc9854d945b959acd96b0e4fa57d3578ea07.jpg</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296226</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296238</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -1601,7 +1577,7 @@
       <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/9b2b928b-4eda-76c6-0dfd-03bde69c046c/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/9639e5f3-92bd-7423-1bf1-08c4dc087bdf/manifest</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr"/>
@@ -1609,29 +1585,29 @@
       <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="inlineStr"/>
       <c r="AH9" t="n">
-        <v>66</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [27]</t>
+          <t>御成敗式目</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A00:6257</t>
+          <t>A00:6456</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>レキダイ ザンケツ ニッキ</t>
+          <t>ゴセイバイ シキモク</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>黒川 春村</t>
+          <t>平泰時 [ほか定]</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1642,7 +1618,7 @@
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>[安政5 (1858)]</t>
+          <t>康永2 [1343] 奥書</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1654,7 +1630,7 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>写本|責任表示及び書写年は『日本古典籍総合目録データベース』による|内容: 6: 光明院御記, 後光嚴院御記, 後小松院宸記, 天聴集. 28: 参議藤定長卿記 : 稱山丞記. 37: 定高卿記, 晴御会部類記, 家光卿御記, 權中納言平範輔卿記. 38: 左大史小槻季継記, 後堀川安貞二年放生會(実基公記), 石清水八幡宮, 弁官拝賀次第. 39: 大外記師光記, 資季卿記, 荒凉記, 忠高卿記. 40: 冷泉公相公記, 勝延法眼記 : 東寺大行事, 後中記 : 小路中納言資頼卿記葉室. 41: 中光記, 師兼記, 陽龍記. 42: 大宮司長則記, 口筆 : 實經, 顕朝卿記, 鴨御幸記. 43: 寳治二年記, 深心院關白記, 藤公親記, 照念院関白兼平公記. 44: 頼親記, 亀山殿行幸記 : 雅言卿記, 兼基公記. 45: 大嘗會御禊節下次第, 建治三年丁丑日記 : 三善康有, 建治四年正月廿一日 : 徳大寺大相國公孝記, 冬定卿記, 左大史小槻兼文記|内容: 46: 經任卿記, 前豊前守藤憲説記, 實兼公記. 47: 継塵記抄出. 48: 管見記, 公衡公記, 大外記師顕記, 大外記中原師淳記. 49: 真光院禪助僧正記, 吉田内府卿記. 50: 定清記, 叅議雅俊卿記, 太政大臣(公守公)御上表雜事, 仙洞御灌頂日記, 正安二年八月十一日於仙洞被始行熾盛光法, 正安三年御譲位記. 51: 實躬卿記. 52: 公茂公記, 冬平公記, 隆長卿記. 53: 忠教公記, 官記, 正三位長基卿記, 北面秀長記, 大外記中原師右記. 54: 文保元年, 日野中納言資朝卿記, 洞院大納言公敏卿記. 55: 隆蔭卿記, 文保三年記, 尹大納言師賢卿記, 革命記, 立倚子記, 萬里小路中納言藤藤房卿記|内容: 56: 資名卿記, 公秀公記, 一條家記装束抄出, 頼定卿記. 63: 松亞記, 日野大納言時光卿記, 後八條内府實継公記. 74: 成恩寺関白記. 78: 山科家礼記. 82: 諒闇記 : 後成恩寺殿, 宗典僧正記, 綱光公記, 贈従二位宗賢卿記, 義政公記. 84: 長禄二年戊寅正月, 見聞雜記. 87: 言國卿記. 88: 長興宿祢記, 元長卿記, 兼顕卿記, 小槻晴冨記|28末の原奥書に「右山丞記依 仰挍合書冩/享和二年四月 日撿挍保己一」とあり|50「正安二年八月十一日於仙洞被始行熾盛光法」末の原奥書に「文化十五年春二月以南山法曼院藏夲書冩之 撿挍保己一」とあり|横刷毛目表紙を使用|朱点, 朱引, 朱墨筆書き入れあり|付箋あり|蔵書印主信濃須坂藩主堀直格の命によって編集された古記録|他の原本は関東大震災により焼失|極札に「桂壽」(6), 「尚信」(53)との極書, 「武清」(44, 53), 「永海」(51), 「了伴」(52), 「了甫」(74), 「定時」(84, 88)との極印あり|印記: 「花廼家文庫」, 「墨阪十一代主寫藏記」(堀直格(1806-1880)), 「東京大學法理文學部書庫所藏」, 「閲覧室用 FOR USE IN THE READING ROOM」|虫損あり</t>
+          <t>写本|本文末に「貞永元年七月十日 沙弥浄圎/相模大掾藤原業時/玄蕃允三善康連/左衞門少尉藤原朝臣基綱/沙弥行然/散位三善朝臣倫重/加賀守三善朝臣康俊/沙弥行西/前出羽守藤原朝臣家長/前駿河守平義村/前攝津守中原師貟/武蔵守平泰時/相模守平時房」との連署名あり|巻末に「嘉禎三年八月十七日評定之」, 「延應二年五月廾五日評定之」, 「暦仁元年十二月十九日評定之」, 「延應元年九月廾日評定之改嫁事」, 「仁治三十二五評定」, 「嘉禎四年九月二十七日評定之」, 「仁治四二廾五追評定之」, 「延應二年五月廾五日評定之」, 「延應二四廾五評」など追加補抄及び「御式目事」(貞永元八月八日 武蔵守御判/するかの守殿)書簡抄を付す|奥書に「康永二年三月三日於高辻冨小路宿所書冩之訖」とあり|毎葉7行17字注文双行|本文は真字, 送り仮名, 返り点を施し|金砂子散し花菱繋ぎの見返し, 押界を施した楮紙打紙を使用|朱墨筆書き入れあり|軸物(打紙継ぎ)|桐箱入り|印記: 「本立堂記」|汚損, 虫損あり</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1670,12 +1646,12 @@
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/ccc6c3da-1648-49f5-91fc-2faaf5400387.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/1dc60eb8-0dd2-1716-521a-8b436e899759.json</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>ccc6c3da-1648-49f5-91fc-2faaf5400387</t>
+          <t>1dc60eb8-0dd2-1716-521a-8b436e899759</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1685,7 +1661,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/ccc6c3da-1648-49f5-91fc-2faaf5400387</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/1dc60eb8-0dd2-1716-521a-8b436e899759</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
@@ -1695,12 +1671,12 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/1e476c24ffbe9fd54b432acbf27eb918fc4162d0.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/8182eba23e72331505a8074acdfe6b5481d358fd.jpg</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296227</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296239</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
@@ -1723,7 +1699,7 @@
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/ccc6c3da-1648-49f5-91fc-2faaf5400387/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/1dc60eb8-0dd2-1716-521a-8b436e899759/manifest</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr"/>
@@ -1731,52 +1707,52 @@
       <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="inlineStr"/>
       <c r="AH10" t="n">
-        <v>70</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [28]</t>
+          <t>辨證配劑醫燈 3巻 [1]</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A00:6257</t>
+          <t>A00:6517</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>レキダイ ザンケツ ニッキ</t>
+          <t>ベンショウ ハイザイ イトウ</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>黒川 春村</t>
+          <t>曲直瀬 道三</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>[書写者不明]</t>
+          <t>道三 [自筆]</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>[安政5 (1858)]</t>
+          <t>元亀2 [1571] 大尾</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>写本|責任表示及び書写年は『日本古典籍総合目録データベース』による|内容: 6: 光明院御記, 後光嚴院御記, 後小松院宸記, 天聴集. 28: 参議藤定長卿記 : 稱山丞記. 37: 定高卿記, 晴御会部類記, 家光卿御記, 權中納言平範輔卿記. 38: 左大史小槻季継記, 後堀川安貞二年放生會(実基公記), 石清水八幡宮, 弁官拝賀次第. 39: 大外記師光記, 資季卿記, 荒凉記, 忠高卿記. 40: 冷泉公相公記, 勝延法眼記 : 東寺大行事, 後中記 : 小路中納言資頼卿記葉室. 41: 中光記, 師兼記, 陽龍記. 42: 大宮司長則記, 口筆 : 實經, 顕朝卿記, 鴨御幸記. 43: 寳治二年記, 深心院關白記, 藤公親記, 照念院関白兼平公記. 44: 頼親記, 亀山殿行幸記 : 雅言卿記, 兼基公記. 45: 大嘗會御禊節下次第, 建治三年丁丑日記 : 三善康有, 建治四年正月廿一日 : 徳大寺大相國公孝記, 冬定卿記, 左大史小槻兼文記|内容: 46: 經任卿記, 前豊前守藤憲説記, 實兼公記. 47: 継塵記抄出. 48: 管見記, 公衡公記, 大外記師顕記, 大外記中原師淳記. 49: 真光院禪助僧正記, 吉田内府卿記. 50: 定清記, 叅議雅俊卿記, 太政大臣(公守公)御上表雜事, 仙洞御灌頂日記, 正安二年八月十一日於仙洞被始行熾盛光法, 正安三年御譲位記. 51: 實躬卿記. 52: 公茂公記, 冬平公記, 隆長卿記. 53: 忠教公記, 官記, 正三位長基卿記, 北面秀長記, 大外記中原師右記. 54: 文保元年, 日野中納言資朝卿記, 洞院大納言公敏卿記. 55: 隆蔭卿記, 文保三年記, 尹大納言師賢卿記, 革命記, 立倚子記, 萬里小路中納言藤藤房卿記|内容: 56: 資名卿記, 公秀公記, 一條家記装束抄出, 頼定卿記. 63: 松亞記, 日野大納言時光卿記, 後八條内府實継公記. 74: 成恩寺関白記. 78: 山科家礼記. 82: 諒闇記 : 後成恩寺殿, 宗典僧正記, 綱光公記, 贈従二位宗賢卿記, 義政公記. 84: 長禄二年戊寅正月, 見聞雜記. 87: 言國卿記. 88: 長興宿祢記, 元長卿記, 兼顕卿記, 小槻晴冨記|28末の原奥書に「右山丞記依 仰挍合書冩/享和二年四月 日撿挍保己一」とあり|50「正安二年八月十一日於仙洞被始行熾盛光法」末の原奥書に「文化十五年春二月以南山法曼院藏夲書冩之 撿挍保己一」とあり|横刷毛目表紙を使用|朱点, 朱引, 朱墨筆書き入れあり|付箋あり|蔵書印主信濃須坂藩主堀直格の命によって編集された古記録|他の原本は関東大震災により焼失|極札に「桂壽」(6), 「尚信」(53)との極書, 「武清」(44, 53), 「永海」(51), 「了伴」(52), 「了甫」(74), 「定時」(84, 88)との極印あり|印記: 「花廼家文庫」, 「墨阪十一代主寫藏記」(堀直格(1806-1880)), 「東京大學法理文學部書庫所藏」, 「閲覧室用 FOR USE IN THE READING ROOM」|虫損あり</t>
+          <t>写本|巻之2の巻頭書名: 辨證配剤醫燈|大尾に「治病用藥之時欲使侄姪孫一覧如指掌而已/旹元亀第二辛未年冬日南至六十五齢老眼寒窓/日東洛下雖知苦斎盍静翁 道三」とあり|巻末識語に「辨證配劑醫燈全三册壹帙一溪叟道三所親筆也不可忽諸故附一語於後耳」とあり|箱に「和氣道三自書寫配劑醫燈三卷林道春跋之櫻井老人苐一家藏子孫永寶之 葛辰識」との墨書あり|毎半面11行|朱点, 朱引, 朱藍筆書き入れあり|付箋あり|箱入り|印記: 「石堂」, 「昃印」|虫損, 汚損あり</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1792,12 +1768,12 @@
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/9f3a126c-84bb-8f96-2916-b65ace30a616.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/ede81088-3a4b-221d-711c-889d446e8d7e.json</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>9f3a126c-84bb-8f96-2916-b65ace30a616</t>
+          <t>ede81088-3a4b-221d-711c-889d446e8d7e</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1807,7 +1783,7 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/9f3a126c-84bb-8f96-2916-b65ace30a616</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/ede81088-3a4b-221d-711c-889d446e8d7e</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
@@ -1817,12 +1793,12 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/fc4844ae32ad2dd582e3570965cb142f5f370f74.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/1089675f22f8a9e5e8d856bf42c0b3fa7e2b5168.jpg</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296228</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296240</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
@@ -1845,7 +1821,7 @@
       <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/9f3a126c-84bb-8f96-2916-b65ace30a616/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/ede81088-3a4b-221d-711c-889d446e8d7e/manifest</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr"/>
@@ -1853,52 +1829,52 @@
       <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="inlineStr"/>
       <c r="AH11" t="n">
-        <v>70</v>
+        <v>61</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [29]</t>
+          <t>辨證配劑醫燈 3巻 [2]</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>A00:6257</t>
+          <t>A00:6517</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>レキダイ ザンケツ ニッキ</t>
+          <t>ベンショウ ハイザイ イトウ</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>黒川 春村</t>
+          <t>曲直瀬 道三</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>[書写者不明]</t>
+          <t>道三 [自筆]</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>[安政5 (1858)]</t>
+          <t>元亀2 [1571] 大尾</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>写本|責任表示及び書写年は『日本古典籍総合目録データベース』による|内容: 6: 光明院御記, 後光嚴院御記, 後小松院宸記, 天聴集. 28: 参議藤定長卿記 : 稱山丞記. 37: 定高卿記, 晴御会部類記, 家光卿御記, 權中納言平範輔卿記. 38: 左大史小槻季継記, 後堀川安貞二年放生會(実基公記), 石清水八幡宮, 弁官拝賀次第. 39: 大外記師光記, 資季卿記, 荒凉記, 忠高卿記. 40: 冷泉公相公記, 勝延法眼記 : 東寺大行事, 後中記 : 小路中納言資頼卿記葉室. 41: 中光記, 師兼記, 陽龍記. 42: 大宮司長則記, 口筆 : 實經, 顕朝卿記, 鴨御幸記. 43: 寳治二年記, 深心院關白記, 藤公親記, 照念院関白兼平公記. 44: 頼親記, 亀山殿行幸記 : 雅言卿記, 兼基公記. 45: 大嘗會御禊節下次第, 建治三年丁丑日記 : 三善康有, 建治四年正月廿一日 : 徳大寺大相國公孝記, 冬定卿記, 左大史小槻兼文記|内容: 46: 經任卿記, 前豊前守藤憲説記, 實兼公記. 47: 継塵記抄出. 48: 管見記, 公衡公記, 大外記師顕記, 大外記中原師淳記. 49: 真光院禪助僧正記, 吉田内府卿記. 50: 定清記, 叅議雅俊卿記, 太政大臣(公守公)御上表雜事, 仙洞御灌頂日記, 正安二年八月十一日於仙洞被始行熾盛光法, 正安三年御譲位記. 51: 實躬卿記. 52: 公茂公記, 冬平公記, 隆長卿記. 53: 忠教公記, 官記, 正三位長基卿記, 北面秀長記, 大外記中原師右記. 54: 文保元年, 日野中納言資朝卿記, 洞院大納言公敏卿記. 55: 隆蔭卿記, 文保三年記, 尹大納言師賢卿記, 革命記, 立倚子記, 萬里小路中納言藤藤房卿記|内容: 56: 資名卿記, 公秀公記, 一條家記装束抄出, 頼定卿記. 63: 松亞記, 日野大納言時光卿記, 後八條内府實継公記. 74: 成恩寺関白記. 78: 山科家礼記. 82: 諒闇記 : 後成恩寺殿, 宗典僧正記, 綱光公記, 贈従二位宗賢卿記, 義政公記. 84: 長禄二年戊寅正月, 見聞雜記. 87: 言國卿記. 88: 長興宿祢記, 元長卿記, 兼顕卿記, 小槻晴冨記|28末の原奥書に「右山丞記依 仰挍合書冩/享和二年四月 日撿挍保己一」とあり|50「正安二年八月十一日於仙洞被始行熾盛光法」末の原奥書に「文化十五年春二月以南山法曼院藏夲書冩之 撿挍保己一」とあり|横刷毛目表紙を使用|朱点, 朱引, 朱墨筆書き入れあり|付箋あり|蔵書印主信濃須坂藩主堀直格の命によって編集された古記録|他の原本は関東大震災により焼失|極札に「桂壽」(6), 「尚信」(53)との極書, 「武清」(44, 53), 「永海」(51), 「了伴」(52), 「了甫」(74), 「定時」(84, 88)との極印あり|印記: 「花廼家文庫」, 「墨阪十一代主寫藏記」(堀直格(1806-1880)), 「東京大學法理文學部書庫所藏」, 「閲覧室用 FOR USE IN THE READING ROOM」|虫損あり</t>
+          <t>写本|巻之2の巻頭書名: 辨證配剤醫燈|大尾に「治病用藥之時欲使侄姪孫一覧如指掌而已/旹元亀第二辛未年冬日南至六十五齢老眼寒窓/日東洛下雖知苦斎盍静翁 道三」とあり|巻末識語に「辨證配劑醫燈全三册壹帙一溪叟道三所親筆也不可忽諸故附一語於後耳」とあり|箱に「和氣道三自書寫配劑醫燈三卷林道春跋之櫻井老人苐一家藏子孫永寶之 葛辰識」との墨書あり|毎半面11行|朱点, 朱引, 朱藍筆書き入れあり|付箋あり|箱入り|印記: 「石堂」, 「昃印」|虫損, 汚損あり</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1914,12 +1890,12 @@
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/7cdebe3a-8fb4-14b4-7ddb-3f92f3be9668.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/93511b52-3de6-4102-980b-24d00b6c5851.json</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>7cdebe3a-8fb4-14b4-7ddb-3f92f3be9668</t>
+          <t>93511b52-3de6-4102-980b-24d00b6c5851</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1929,7 +1905,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/7cdebe3a-8fb4-14b4-7ddb-3f92f3be9668</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/93511b52-3de6-4102-980b-24d00b6c5851</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
@@ -1939,12 +1915,12 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/08f5648a7b5512a896986520a6449d3620439071.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/a82992bab1da44c99dc71e9ac8ef6ff3d626dc4d.jpg</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296229</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296241</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
@@ -1967,7 +1943,7 @@
       <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/7cdebe3a-8fb4-14b4-7ddb-3f92f3be9668/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/93511b52-3de6-4102-980b-24d00b6c5851/manifest</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr"/>
@@ -1975,52 +1951,52 @@
       <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="inlineStr"/>
       <c r="AH12" t="n">
-        <v>70</v>
+        <v>52</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>普賢延命</t>
+          <t>辨證配劑醫燈 3巻 [3]</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>A00:6264</t>
+          <t>A00:6517</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>フゲン エンメイ</t>
+          <t>ベンショウ ハイザイ イトウ</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>興然</t>
+          <t>曲直瀬 道三</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>長円 [写]</t>
+          <t>道三 [自筆]</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>嘉禎2 [1236] 奥書</t>
+          <t>元亀2 [1571] 大尾</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>写本|内題下に「師 理教」, 「嘉禎二年奥書アリ 長円書」とあり|巻末に「越前闍梨浄与口傳 興然夲」とあり|奥書に「嘉禎二年四月六月奉傳受空達御房ノ長円」とあり|裏に「正和元年壬子八月廿九日於成身院奉伝受之了」とあり|巻子本|送り仮名, 傍訓あり|虫損あり (裏打ち補修あり)</t>
+          <t>写本|巻之2の巻頭書名: 辨證配剤醫燈|大尾に「治病用藥之時欲使侄姪孫一覧如指掌而已/旹元亀第二辛未年冬日南至六十五齢老眼寒窓/日東洛下雖知苦斎盍静翁 道三」とあり|巻末識語に「辨證配劑醫燈全三册壹帙一溪叟道三所親筆也不可忽諸故附一語於後耳」とあり|箱に「和氣道三自書寫配劑醫燈三卷林道春跋之櫻井老人苐一家藏子孫永寶之 葛辰識」との墨書あり|毎半面11行|朱点, 朱引, 朱藍筆書き入れあり|付箋あり|箱入り|印記: 「石堂」, 「昃印」|虫損, 汚損あり</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -2036,12 +2012,12 @@
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/e57fef06-5cfd-a602-6a89-f4d7d4360e87.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/a23dae2e-701a-8d7c-1359-fe786c2e2cdd.json</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>e57fef06-5cfd-a602-6a89-f4d7d4360e87</t>
+          <t>a23dae2e-701a-8d7c-1359-fe786c2e2cdd</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -2051,7 +2027,7 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/e57fef06-5cfd-a602-6a89-f4d7d4360e87</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/a23dae2e-701a-8d7c-1359-fe786c2e2cdd</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
@@ -2061,12 +2037,12 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/eec20da7736c221a3c86321abead9d8d9429dceb.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/21b02bac7c065db97c214037acfa4b232d2ddc89.jpg</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296230</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296242</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -2089,7 +2065,7 @@
       <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/e57fef06-5cfd-a602-6a89-f4d7d4360e87/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/a23dae2e-701a-8d7c-1359-fe786c2e2cdd/manifest</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr"/>
@@ -2097,40 +2073,40 @@
       <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="inlineStr"/>
       <c r="AH13" t="n">
-        <v>7</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>如法愛染王</t>
+          <t>おちくほのさうし</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>A00:6265</t>
+          <t>A00:4083</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ニョホウ アイゼンオウ</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>仁海</t>
-        </is>
-      </c>
+          <t>オチクボ ノ ソウシ</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>おちくほ物語|御本</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>禅喜 [写]</t>
+          <t>[書写者不明]</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>嘉暦2 [1327] 奥書</t>
+          <t>[江戸前期]</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2138,11 +2114,15 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>写本</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>写本|表紙の書名: 如法愛染|内題下に「付小野大次苐修之」とあり|本奥書に「延慶二年夘月十日於仁和寺真光院書写了 金剛佛子印法 生年卅二」とあり|奥書に「嘉暦二年正月廿二日全写了 禅喜 生年卅一」とあり|巻子本|小野流|淡墨界の料紙を使用(界匡廓: 23.8×2.2cm)|巻頭下部の貼紙に「嘉暦二年巨今五百八十二年鎌倉時代四一ノ六九七号」とあり|破損, 虫損あり (裏打ち補修あり)</t>
+          <t>書名は題簽による|毎半帖10行|漢字平仮名交じり文|奈良絵本|桜唐草文様緞子表紙, 松葉散しに山雲の金箔見返し, 金泥下絵鳥の子紙を使用|列帖装|二重箱入り</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -2152,28 +2132,28 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>図書</t>
+          <t>和古書</t>
         </is>
       </c>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/e321350d-483d-6e38-81a2-a637b8f798fb.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/8aa19100-0937-5fd9-29f1-ba41ad8d1830.json</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>e321350d-483d-6e38-81a2-a637b8f798fb</t>
+          <t>8aa19100-0937-5fd9-29f1-ba41ad8d1830</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/e321350d-483d-6e38-81a2-a637b8f798fb</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/8aa19100-0937-5fd9-29f1-ba41ad8d1830</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
@@ -2183,12 +2163,12 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/355285a0ec0b1cc8f12ae2c98e5215bdc9477998.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/124815802d3a78d8f78dd4fbb98d24d55e5c3b34.jpg</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296231</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1182819</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -2211,7 +2191,7 @@
       <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/e321350d-483d-6e38-81a2-a637b8f798fb/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/8aa19100-0937-5fd9-29f1-ba41ad8d1830/manifest</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr"/>
@@ -2219,40 +2199,48 @@
       <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="inlineStr"/>
       <c r="AH14" t="n">
-        <v>7</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>三摩耶戒作法 : 東寺</t>
+          <t>甲午日記 : 天保五年正月吉日</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>A00:6266</t>
+          <t>A00:4613</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>サンマヤカイ サホウ : トウジ</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>コウゴ ニッキ : テンポウ ゴネン ショウガツ キチジツ</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>天保五年馬琴日記</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>聖快</t>
+          <t>滝沢 馬琴</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>道快 [自筆]</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr"/>
+          <t>瀧澤馬琴 [自筆]</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>1834</t>
+        </is>
+      </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>康暦元 [1379] 奥書</t>
+          <t>天保5</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2260,11 +2248,15 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>写本</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>写本|書名は表紙による|本奥書に「康和元年十月廿日午時書了 深禅夲(第三轉)」, 「以小野僧正御夲理趣房書御夲也(初轉)」, 「承暦四年十一月十二日給預又書冩并傳受了 峯大阿闍梨御房事也(第二轉)」とあり|奥書に「康暦元年八月十二日於地藏院以平等坊永嚴自筆夲書冩之訖 東寺沙門道快」, 「同十四日於同院以或夲重挍合入落字注異説削謬詞尤可秘藏而已」とあり|表紙の貼紙に「康暦元年八月十二日於地藏院以平等坊永嚴自筆本書写之訖 東寺沙門道快 南北類」とある|巻子本|朱筆書き入れあり|淡墨界の料紙を使用(界匡廓: 19.5×2.0cm)|印記: 「僧正弘基」|破損, 虫損あり</t>
+          <t>書名は扉による|巻末に「已上午年日記畢」とあり|裏表紙に「神田 瀧澤」とあり|内容: 天保五甲午年春正月-12月|墨抹, 胡粉による修正あり|巻末の識語末に「昭和五年十二月に至って脩覆を了せり」とあり|虫損あり (裏打ち補修あり)</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -2274,28 +2266,28 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>図書</t>
+          <t>和古書</t>
         </is>
       </c>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/2b2562eb-7577-32f6-4c99-462a84e0647c.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/c91cb308-03bd-94f5-3c56-9d0fac9424d3.json</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2b2562eb-7577-32f6-4c99-462a84e0647c</t>
+          <t>c91cb308-03bd-94f5-3c56-9d0fac9424d3</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/2b2562eb-7577-32f6-4c99-462a84e0647c</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/c91cb308-03bd-94f5-3c56-9d0fac9424d3</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
@@ -2305,12 +2297,12 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/60a9be2785b442f57f54089c594f63b8df5ae1f4.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/92f1a1f83433e8cf04243d82fb0811e6cf653db2.jpg</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296232</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1182820</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
@@ -2333,7 +2325,7 @@
       <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/2b2562eb-7577-32f6-4c99-462a84e0647c/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/c91cb308-03bd-94f5-3c56-9d0fac9424d3/manifest</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr"/>
@@ -2341,48 +2333,52 @@
       <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="inlineStr"/>
       <c r="AH15" t="n">
-        <v>13</v>
+        <v>172</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>騁懐帖 2巻 [1]</t>
+          <t>天神記</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>A00:6379</t>
+          <t>A00:5770</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>テイカイジョウ</t>
+          <t>テンジンキ</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>芳賀矢一[ほか自筆] ; 松本百藏 [集]</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>[書写者不明]</t>
+        </is>
+      </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>[明治-昭和年間]</t>
+          <t>[室町末期-江戸前期]</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>写本</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>写本|書名及び巻冊次は題簽による|跋末に「松夲生名ハ百藏東京帝國大學ノ使丁タリ職ヲ山上會議所ニ奉スルコト四十有餘年 ... 頃来マタ諸賢ノ揮毫ヲ乞上名ケテ騁懐帖トイフ ... 帖成リテ予ニ其由来ヲ記セシコトヲ求ム乃チ之ヲ録シテ以テ跋後トス 昭和二年三月 辻善之助識」とあり|折本|書画帖|彩色あり|名録2冊(大和綴)を付す|落款朱印: 「長成」(坪井九馬三), 「圭卿」(市村瓚次郎), 「簣山」(鹽谷時敏), 「維亭」(塚本靖), 「土肥慶藏」, 「忠太」(伊東忠太), 「萬」(和田万吉), 「芳溪」(呉秀三), 「前田慧雲」, 「大澤謙二」, 「南條文雄」, 「有坂氏」(有坂鉊藏), 「博」, 「石亭」(林博太郎), 「長與又郎」, 「宇野哲人」, ほかあり</t>
+          <t>書名は表紙( 朱書)による|毎半葉13行|奈良絵本|秋草に籬の紺紙金泥表紙, 麻の葉繋ぎに丸龍文様の銀箔見返しを使用|印記: 「渡郶文庫珍藏書印」(渡部信)</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2392,28 +2388,28 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>図書</t>
+          <t>和古書</t>
         </is>
       </c>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/bfdc576b-6ce2-9274-914e-8cc9c52c04de.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/f7abc34f-6ff4-1309-4e13-cd69cce698b7.json</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>bfdc576b-6ce2-9274-914e-8cc9c52c04de</t>
+          <t>f7abc34f-6ff4-1309-4e13-cd69cce698b7</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/bfdc576b-6ce2-9274-914e-8cc9c52c04de</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/f7abc34f-6ff4-1309-4e13-cd69cce698b7</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
@@ -2423,12 +2419,12 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/4061afb959aba92577bf3357712e3556cd07cf8e.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/b6b3dd9c0e350f9b1b14c1a2ba0d012e6762e42c.jpg</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296233</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1182821</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
@@ -2451,7 +2447,7 @@
       <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/bfdc576b-6ce2-9274-914e-8cc9c52c04de/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/f7abc34f-6ff4-1309-4e13-cd69cce698b7/manifest</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr"/>
@@ -2459,53 +2455,53 @@
       <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="inlineStr"/>
       <c r="AH16" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>騁懐帖 2巻 [2]</t>
+          <t>各種殘經 : 出鄯善縣土峪溝</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>A00:6379</t>
+          <t>A00:4033</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>テイカイジョウ</t>
+          <t>カクシュ ザンキョウ : シュツ ゼンゼンケン トヨクコウ</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>芳賀矢一[ほか自筆] ; 松本百藏 [集]</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>[書写者不明]</t>
+        </is>
+      </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>[明治-昭和年間]</t>
+          <t>[書写年不明]</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>写本|書名及び巻冊次は題簽による|跋末に「松夲生名ハ百藏東京帝國大學ノ使丁タリ職ヲ山上會議所ニ奉スルコト四十有餘年 ... 頃来マタ諸賢ノ揮毫ヲ乞上名ケテ騁懐帖トイフ ... 帖成リテ予ニ其由来ヲ記セシコトヲ求ム乃チ之ヲ録シテ以テ跋後トス 昭和二年三月 辻善之助識」とあり|折本|書画帖|彩色あり|名録2冊(大和綴)を付す|落款朱印: 「長成」(坪井九馬三), 「圭卿」(市村瓚次郎), 「簣山」(鹽谷時敏), 「維亭」(塚本靖), 「土肥慶藏」, 「忠太」(伊東忠太), 「萬」(和田万吉), 「芳溪」(呉秀三), 「前田慧雲」, 「大澤謙二」, 「南條文雄」, 「有坂氏」(有坂鉊藏), 「博」, 「石亭」(林博太郎), 「長與又郎」, 「宇野哲人」, ほかあり</t>
+          <t>写本残片|書名は題簽による|題簽に「出鄯善縣土峪溝 素文珍藏」とあり|識語に「為楊枝甘露滴入紙中展巻把玩但覺異香盈字 晉卿」, 「右二紙係亜利安字 晉卿」, 「右二紙係畏吾児字 晉卿」とあり|蔵書票に「殘經佛像梵字 十五段 鄯善」, 「梵字第一號」とあり|巻子本|箱入|印記: 「臣樹枏印」, 「晉卿」, 「王仲子」, 「王樹枏印」</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>日本語</t>
+          <t>中国語</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2516,12 +2512,12 @@
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/6a4c18fb-90e9-6d15-1234-9cadcc683544.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/704d2c7a-4882-6fc8-60d1-94c1e2799bbd.json</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>6a4c18fb-90e9-6d15-1234-9cadcc683544</t>
+          <t>704d2c7a-4882-6fc8-60d1-94c1e2799bbd</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -2531,7 +2527,7 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/6a4c18fb-90e9-6d15-1234-9cadcc683544</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/704d2c7a-4882-6fc8-60d1-94c1e2799bbd</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
@@ -2541,12 +2537,12 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/f705bcd1873bb88e3f1edef2b79dcc86dc2c417b.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/4cc89d9a25687c69b3dc3791fd39ac740de2c4a0.jpg</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296234</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296165</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
@@ -2569,7 +2565,7 @@
       <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/6a4c18fb-90e9-6d15-1234-9cadcc683544/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/704d2c7a-4882-6fc8-60d1-94c1e2799bbd/manifest</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr"/>
@@ -2577,48 +2573,52 @@
       <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="inlineStr"/>
       <c r="AH17" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>清玩書巻</t>
+          <t>和漢朗詠集 2巻 [1]</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>A00:6380</t>
+          <t>A00:4081</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>セイガン ショカン</t>
+          <t>ワカン ロウエイシュウ</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>石黒忠悳[ほか自筆] ; [松本百藏収集]</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr"/>
+          <t>藤原 公任</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>[書写者不明]</t>
+        </is>
+      </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>[明治大正年間]</t>
+          <t>[江戸前期]</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>写本|書名は題簽による|その他の筆者: 市村瓚次郎, 外山正一, 緒方正規, 村上専精, 佐藤進, 菊池大麓, 三宅秀, 箕作佳吉, 三上參次, 箕作元八|冒頭に井上哲の題辞「清玩」あり|巻末に萩野由之の識語あり|収集者は『理翰片影』&lt;BC06713253&gt;の跋による|巻子本|往来書簡貼付集|名録1冊(大和綴)を付す|落款朱印: 「文学博士」, 「井上喆」, 「井上哲印」(井上哲次郎), 「和葊」(萩野由之)</t>
+          <t>写本|書名は目首及び題簽による|外箱の書名: 御本|責任表示は『日本古典籍総合目録データベース』による|巻上: 春, 夏, 秋, 冬. 巻下: 雜|題簽による巻冊次表示: 上, 下|毎半帖8行|漢字平仮名交じり文|鳳凰菱繋ぎ文様緞子表紙, 松葉散しに山雲の金箔見返し, 金泥下絵鳥の子紙を使用|列帖装|二重箱入り</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2634,12 +2634,12 @@
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/ae3b180b-9cbe-6902-48c2-f0abfdf0a27e.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/ba79db36-23e8-1a8a-1ad9-a5809c1109be.json</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>ae3b180b-9cbe-6902-48c2-f0abfdf0a27e</t>
+          <t>ba79db36-23e8-1a8a-1ad9-a5809c1109be</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -2649,7 +2649,7 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/ae3b180b-9cbe-6902-48c2-f0abfdf0a27e</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/ba79db36-23e8-1a8a-1ad9-a5809c1109be</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
@@ -2659,12 +2659,12 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/e799186565cb40d919d91c02eef1308118771dd3.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/0dbc6905fbe6d7441026c6ec7f4092a564cd7606.jpg</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296235</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296166</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
@@ -2687,7 +2687,7 @@
       <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/ae3b180b-9cbe-6902-48c2-f0abfdf0a27e/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/ba79db36-23e8-1a8a-1ad9-a5809c1109be/manifest</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr"/>
@@ -2695,48 +2695,52 @@
       <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="inlineStr"/>
       <c r="AH18" t="n">
-        <v>26</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>聚珍書巻</t>
+          <t>和漢朗詠集 2巻 [2]</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>A00:6381</t>
+          <t>A00:4081</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>シュウチン ショカン</t>
+          <t>ワカン ロウエイシュウ</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>濱尾新 [ほか自筆] ; 松本百藏 [収集]</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr"/>
+          <t>藤原 公任</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>[書写者不明]</t>
+        </is>
+      </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>[明治年間]</t>
+          <t>[江戸前期]</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
-          <t>写本|書名は題簽による|題辞に「聚珍 明治己酉夏八十三老人成斎題」とあり|巻末識語に「松本百蔵為東亰帝國大學厮養二十餘年毎掃故紙籠見有文字者輒収而弆之頃揀其署名氏者十餘紙装潢成卷皆名賢鉅公碩學鴻儒之筆也 ... 明治庚戌二月初夏 豊城陳人恒書時年七十又二」とあり|その他の筆者: 細川潤次郎, 渡邊洪基, 加藤弘之, 川田剛, 辻新次, 中村正直, 古市公威, 小中村清矩, 木村正辭, 島田重禮|巻子本|往来書簡貼付集|名録1冊(大和綴)を付す|落款朱印: 「晩香」, 「徳天」, 「星野恒印」, 「續古堂」, 「重野」, 「重埜士徳」, 「藤原安繹」</t>
+          <t>写本|書名は目首及び題簽による|外箱の書名: 御本|責任表示は『日本古典籍総合目録データベース』による|巻上: 春, 夏, 秋, 冬. 巻下: 雜|題簽による巻冊次表示: 上, 下|毎半帖8行|漢字平仮名交じり文|鳳凰菱繋ぎ文様緞子表紙, 松葉散しに山雲の金箔見返し, 金泥下絵鳥の子紙を使用|列帖装|二重箱入り</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2752,12 +2756,12 @@
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/4e78ded3-2829-990e-572b-4b5e029a69cc.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/a241b0e6-90d9-46db-1fe8-bf35f1e616c5.json</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>4e78ded3-2829-990e-572b-4b5e029a69cc</t>
+          <t>a241b0e6-90d9-46db-1fe8-bf35f1e616c5</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -2767,7 +2771,7 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/4e78ded3-2829-990e-572b-4b5e029a69cc</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/a241b0e6-90d9-46db-1fe8-bf35f1e616c5</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
@@ -2777,12 +2781,12 @@
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/fe6e0e801688014b204ebe9deee8085c19831bc3.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/f46b1242e2b77ba4f0d99feac20562f5cd3a0ee2.jpg</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296236</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296167</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
@@ -2805,7 +2809,7 @@
       <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/4e78ded3-2829-990e-572b-4b5e029a69cc/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/a241b0e6-90d9-46db-1fe8-bf35f1e616c5/manifest</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr"/>
@@ -2813,36 +2817,40 @@
       <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="inlineStr"/>
       <c r="AH19" t="n">
-        <v>27</v>
+        <v>48</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>理翰片影</t>
+          <t>つれつれ草</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>A00:6382</t>
+          <t>A00:4082</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>リカン ヘンエイ</t>
+          <t>ツレズレグサ</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>井上毅 [ほか自筆] ; 松本百藏 [蒐集]</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr"/>
+          <t>吉田 兼好</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>[書写者不明]</t>
+        </is>
+      </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>[明治大正年間]</t>
+          <t>[江戸前期]</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2854,7 +2862,7 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
-          <t>写本|書名は題簽による|敘に「松本百藏君我が東京帝國大學に縁故ある諸君の筆蹟を蒐集シ己ニ三卷をなす此卷収む事といわは故子爵井上毅先生をはじめとし神保小虎博士に至るまで十二君の消息なり ... 大正十四年春日三上参次(花押)」とあり|跋に「松本百藏奉職東京帝國大學勞使四十年夙昔不怠其所勤非尋常也大正十四年以古稀辤其軄以平生所収簡牘装潢之得四巻二帖納大學書庫 ... 大正十五年五月於東京帝國大學夲部象軒平野直文識」とあり|その他の筆者: 八代六郎, 垪和爲昌, 鶴田賢次, 長井長義, 久原躬弦, 藤澤利喜太郎, 小藤文次郎, 寺野精一, 青山胤通, 佐藤三吉, 神保小乕|巻子本|往来書簡貼付集|落款朱印: 「士可」, 「虚坣居士」, 「平野直文」</t>
+          <t>写本|書名は題簽による|書名の繰返し部分は踊り字|外箱の書名: 御本|責任表示は『日本古典籍総合目録データベース』による|毎半帖10行|漢字平仮名交じり文|花草窠文様緞子表紙, 松葉散しに山雲の金箔見返し, 金泥下絵鳥の子紙を使用|列帖装|二重箱入り</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2870,12 +2878,12 @@
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/31b15e19-44d8-6c52-9780-873a7f1a2480.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/d19a62f6-4729-0ee3-3ea7-08f573851a48.json</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>31b15e19-44d8-6c52-9780-873a7f1a2480</t>
+          <t>d19a62f6-4729-0ee3-3ea7-08f573851a48</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -2885,7 +2893,7 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/31b15e19-44d8-6c52-9780-873a7f1a2480</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/d19a62f6-4729-0ee3-3ea7-08f573851a48</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
@@ -2895,12 +2903,12 @@
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/c34f4eff76edef5a959de5048f588d40ac1cccac.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/7966b7312c84644ee577a0390937964b1989586d.jpg</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296237</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296168</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
@@ -2923,7 +2931,7 @@
       <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/31b15e19-44d8-6c52-9780-873a7f1a2480/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/d19a62f6-4729-0ee3-3ea7-08f573851a48/manifest</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr"/>
@@ -2931,48 +2939,52 @@
       <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="inlineStr"/>
       <c r="AH20" t="n">
-        <v>21</v>
+        <v>142</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>學海拾遺珠</t>
+          <t>日本廿四孝 6巻 [1]</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>A00:6383</t>
+          <t>A00:4084</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ガッカイ シュウイシュ</t>
+          <t>ヤマト ニジュウシコウ</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>渡邊渡 [ほか自筆] ; 松本[百藏 集]</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr"/>
+          <t>浅井 了意</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>[書写者不明]</t>
+        </is>
+      </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
-          <t>[明治大正年間]</t>
+          <t>[江戸前期]</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
-          <t>写本|書名は題簽による|題辞に「學海拾遺珠 大正十二年初夏 讀律書屋主人題」とあり|巻末識語に「東京帝國大學の地小丘有り丘上に會議所有り總長教授等會食聚議の處と為に松本君其の役たると久し親しく碩學大家に接し之を敬するを知る留意して敗紙中に諸家の手跡を索め嵗月を累収て十数家に及へは輙ち裝潢して卷を成す今や第三卷成り文を予に求む松本君孤影孑然會議所に起臥す伴侶は唯名家手簡と手栽の盆柎有るのみ ... 大正十二年二月十九日 隨軒學人」とあり|その他の筆者: 和田垣謙三, 川瀬善太郎, 高松豊吉, 田中義成, 永井久一郎, 中村恭平, 山川健次郎, 松井直吉, 松村任三, 古在由直, 寺尾寿, 櫻井錠二, 清水彦五郎|巻子本|往来書簡貼付集|名録1冊(大和綴)を付す|落款朱印: 「讀經堂主人號随軒」, 「服部宇之吉印記」, 「直文」(平野直文)</t>
+          <t>写本|書名は目首及び題簽による|内箱の書名: 大和廿四孝|外箱の書名: 御本|責任表示は『日本古典籍総合目録データベース』による|1: 第1-4. 2: 第5-8. 3: 第9-12. 4: 第13-16. 5: 第17-20. 6: 第21-24|毎半帖10行|漢字平仮名交じり文|奈良絵本|梅唐草文様緞子表紙, 松葉散しに山雲の金箔見返し, 金泥下絵鳥の子紙を使用|列帖装|竪本|二重箱入り|糸切れあり</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2988,12 +3000,12 @@
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/9639e5f3-92bd-7423-1bf1-08c4dc087bdf.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/bf17bb0e-6d63-718e-218b-614134ee011d.json</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>9639e5f3-92bd-7423-1bf1-08c4dc087bdf</t>
+          <t>bf17bb0e-6d63-718e-218b-614134ee011d</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -3003,7 +3015,7 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/9639e5f3-92bd-7423-1bf1-08c4dc087bdf</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/bf17bb0e-6d63-718e-218b-614134ee011d</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
@@ -3013,12 +3025,12 @@
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/b210fc9854d945b959acd96b0e4fa57d3578ea07.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/2c48d85abc93bce026f680cc699c748fb0a877e2.jpg</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296238</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296169</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
@@ -3041,7 +3053,7 @@
       <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/9639e5f3-92bd-7423-1bf1-08c4dc087bdf/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/bf17bb0e-6d63-718e-218b-614134ee011d/manifest</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr"/>
@@ -3049,29 +3061,29 @@
       <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="inlineStr"/>
       <c r="AH21" t="n">
-        <v>27</v>
+        <v>47</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>御成敗式目</t>
+          <t>日本廿四孝 6巻 [2]</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>A00:6456</t>
+          <t>A00:4084</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ゴセイバイ シキモク</t>
+          <t>ヤマト ニジュウシコウ</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>平泰時 [ほか定]</t>
+          <t>浅井 了意</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -3082,19 +3094,19 @@
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
-          <t>康永2 [1343] 奥書</t>
+          <t>[江戸前期]</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
-          <t>写本|本文末に「貞永元年七月十日 沙弥浄圎/相模大掾藤原業時/玄蕃允三善康連/左衞門少尉藤原朝臣基綱/沙弥行然/散位三善朝臣倫重/加賀守三善朝臣康俊/沙弥行西/前出羽守藤原朝臣家長/前駿河守平義村/前攝津守中原師貟/武蔵守平泰時/相模守平時房」との連署名あり|巻末に「嘉禎三年八月十七日評定之」, 「延應二年五月廾五日評定之」, 「暦仁元年十二月十九日評定之」, 「延應元年九月廾日評定之改嫁事」, 「仁治三十二五評定」, 「嘉禎四年九月二十七日評定之」, 「仁治四二廾五追評定之」, 「延應二年五月廾五日評定之」, 「延應二四廾五評」など追加補抄及び「御式目事」(貞永元八月八日 武蔵守御判/するかの守殿)書簡抄を付す|奥書に「康永二年三月三日於高辻冨小路宿所書冩之訖」とあり|毎葉7行17字注文双行|本文は真字, 送り仮名, 返り点を施し|金砂子散し花菱繋ぎの見返し, 押界を施した楮紙打紙を使用|朱墨筆書き入れあり|軸物(打紙継ぎ)|桐箱入り|印記: 「本立堂記」|汚損, 虫損あり</t>
+          <t>写本|書名は目首及び題簽による|内箱の書名: 大和廿四孝|外箱の書名: 御本|責任表示は『日本古典籍総合目録データベース』による|1: 第1-4. 2: 第5-8. 3: 第9-12. 4: 第13-16. 5: 第17-20. 6: 第21-24|毎半帖10行|漢字平仮名交じり文|奈良絵本|梅唐草文様緞子表紙, 松葉散しに山雲の金箔見返し, 金泥下絵鳥の子紙を使用|列帖装|竪本|二重箱入り|糸切れあり</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -3110,12 +3122,12 @@
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/1dc60eb8-0dd2-1716-521a-8b436e899759.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/c2996e14-8070-09ae-328a-159e60d17016.json</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>1dc60eb8-0dd2-1716-521a-8b436e899759</t>
+          <t>c2996e14-8070-09ae-328a-159e60d17016</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -3125,7 +3137,7 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/1dc60eb8-0dd2-1716-521a-8b436e899759</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/c2996e14-8070-09ae-328a-159e60d17016</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
@@ -3135,12 +3147,12 @@
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/8182eba23e72331505a8074acdfe6b5481d358fd.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/27ba12aa7661321f36193a30b8d8ffb8b32e574c.jpg</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296239</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296170</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
@@ -3163,7 +3175,7 @@
       <c r="AB22" t="inlineStr"/>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/1dc60eb8-0dd2-1716-521a-8b436e899759/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/c2996e14-8070-09ae-328a-159e60d17016/manifest</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr"/>
@@ -3171,52 +3183,52 @@
       <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="inlineStr"/>
       <c r="AH22" t="n">
-        <v>45</v>
+        <v>103</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>辨證配劑醫燈 3巻 [1]</t>
+          <t>日本廿四孝 6巻 [3]</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>A00:6517</t>
+          <t>A00:4084</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ベンショウ ハイザイ イトウ</t>
+          <t>ヤマト ニジュウシコウ</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>曲直瀬 道三</t>
+          <t>浅井 了意</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>道三 [自筆]</t>
+          <t>[書写者不明]</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
-          <t>元亀2 [1571] 大尾</t>
+          <t>[江戸前期]</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
-          <t>写本|巻之2の巻頭書名: 辨證配剤醫燈|大尾に「治病用藥之時欲使侄姪孫一覧如指掌而已/旹元亀第二辛未年冬日南至六十五齢老眼寒窓/日東洛下雖知苦斎盍静翁 道三」とあり|巻末識語に「辨證配劑醫燈全三册壹帙一溪叟道三所親筆也不可忽諸故附一語於後耳」とあり|箱に「和氣道三自書寫配劑醫燈三卷林道春跋之櫻井老人苐一家藏子孫永寶之 葛辰識」との墨書あり|毎半面11行|朱点, 朱引, 朱藍筆書き入れあり|付箋あり|箱入り|印記: 「石堂」, 「昃印」|虫損, 汚損あり</t>
+          <t>写本|書名は目首及び題簽による|内箱の書名: 大和廿四孝|外箱の書名: 御本|責任表示は『日本古典籍総合目録データベース』による|1: 第1-4. 2: 第5-8. 3: 第9-12. 4: 第13-16. 5: 第17-20. 6: 第21-24|毎半帖10行|漢字平仮名交じり文|奈良絵本|梅唐草文様緞子表紙, 松葉散しに山雲の金箔見返し, 金泥下絵鳥の子紙を使用|列帖装|竪本|二重箱入り|糸切れあり</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -3232,12 +3244,12 @@
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/ede81088-3a4b-221d-711c-889d446e8d7e.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/8bf2f649-5d15-2afc-2f36-84e0ac2f513e.json</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>ede81088-3a4b-221d-711c-889d446e8d7e</t>
+          <t>8bf2f649-5d15-2afc-2f36-84e0ac2f513e</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -3247,7 +3259,7 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/ede81088-3a4b-221d-711c-889d446e8d7e</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/8bf2f649-5d15-2afc-2f36-84e0ac2f513e</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
@@ -3257,12 +3269,12 @@
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/1089675f22f8a9e5e8d856bf42c0b3fa7e2b5168.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/5841d5cb8d9895d0b483a2f842afc32f67e1719b.jpg</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296240</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296171</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
@@ -3285,7 +3297,7 @@
       <c r="AB23" t="inlineStr"/>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/ede81088-3a4b-221d-711c-889d446e8d7e/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/8bf2f649-5d15-2afc-2f36-84e0ac2f513e/manifest</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr"/>
@@ -3293,52 +3305,52 @@
       <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="inlineStr"/>
       <c r="AH23" t="n">
-        <v>61</v>
+        <v>47</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>辨證配劑醫燈 3巻 [2]</t>
+          <t>日本廿四孝 6巻 [4]</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>A00:6517</t>
+          <t>A00:4084</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ベンショウ ハイザイ イトウ</t>
+          <t>ヤマト ニジュウシコウ</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>曲直瀬 道三</t>
+          <t>浅井 了意</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>道三 [自筆]</t>
+          <t>[書写者不明]</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
-          <t>元亀2 [1571] 大尾</t>
+          <t>[江戸前期]</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
-          <t>写本|巻之2の巻頭書名: 辨證配剤醫燈|大尾に「治病用藥之時欲使侄姪孫一覧如指掌而已/旹元亀第二辛未年冬日南至六十五齢老眼寒窓/日東洛下雖知苦斎盍静翁 道三」とあり|巻末識語に「辨證配劑醫燈全三册壹帙一溪叟道三所親筆也不可忽諸故附一語於後耳」とあり|箱に「和氣道三自書寫配劑醫燈三卷林道春跋之櫻井老人苐一家藏子孫永寶之 葛辰識」との墨書あり|毎半面11行|朱点, 朱引, 朱藍筆書き入れあり|付箋あり|箱入り|印記: 「石堂」, 「昃印」|虫損, 汚損あり</t>
+          <t>写本|書名は目首及び題簽による|内箱の書名: 大和廿四孝|外箱の書名: 御本|責任表示は『日本古典籍総合目録データベース』による|1: 第1-4. 2: 第5-8. 3: 第9-12. 4: 第13-16. 5: 第17-20. 6: 第21-24|毎半帖10行|漢字平仮名交じり文|奈良絵本|梅唐草文様緞子表紙, 松葉散しに山雲の金箔見返し, 金泥下絵鳥の子紙を使用|列帖装|竪本|二重箱入り|糸切れあり</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -3354,12 +3366,12 @@
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/93511b52-3de6-4102-980b-24d00b6c5851.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/59c5b4a7-529d-5e9f-454f-8879e85023eb.json</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>93511b52-3de6-4102-980b-24d00b6c5851</t>
+          <t>59c5b4a7-529d-5e9f-454f-8879e85023eb</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -3369,7 +3381,7 @@
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/93511b52-3de6-4102-980b-24d00b6c5851</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/59c5b4a7-529d-5e9f-454f-8879e85023eb</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
@@ -3379,12 +3391,12 @@
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/a82992bab1da44c99dc71e9ac8ef6ff3d626dc4d.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/e4d2c0aa6489eb2a071834a4a14714fecb372bce.jpg</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296241</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296172</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
@@ -3407,7 +3419,7 @@
       <c r="AB24" t="inlineStr"/>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/93511b52-3de6-4102-980b-24d00b6c5851/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/59c5b4a7-529d-5e9f-454f-8879e85023eb/manifest</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr"/>
@@ -3415,52 +3427,52 @@
       <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="inlineStr"/>
       <c r="AH24" t="n">
-        <v>52</v>
+        <v>76</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>辨證配劑醫燈 3巻 [3]</t>
+          <t>日本廿四孝 6巻 [5]</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>A00:6517</t>
+          <t>A00:4084</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ベンショウ ハイザイ イトウ</t>
+          <t>ヤマト ニジュウシコウ</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>曲直瀬 道三</t>
+          <t>浅井 了意</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>道三 [自筆]</t>
+          <t>[書写者不明]</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
-          <t>元亀2 [1571] 大尾</t>
+          <t>[江戸前期]</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
-          <t>写本|巻之2の巻頭書名: 辨證配剤醫燈|大尾に「治病用藥之時欲使侄姪孫一覧如指掌而已/旹元亀第二辛未年冬日南至六十五齢老眼寒窓/日東洛下雖知苦斎盍静翁 道三」とあり|巻末識語に「辨證配劑醫燈全三册壹帙一溪叟道三所親筆也不可忽諸故附一語於後耳」とあり|箱に「和氣道三自書寫配劑醫燈三卷林道春跋之櫻井老人苐一家藏子孫永寶之 葛辰識」との墨書あり|毎半面11行|朱点, 朱引, 朱藍筆書き入れあり|付箋あり|箱入り|印記: 「石堂」, 「昃印」|虫損, 汚損あり</t>
+          <t>写本|書名は目首及び題簽による|内箱の書名: 大和廿四孝|外箱の書名: 御本|責任表示は『日本古典籍総合目録データベース』による|1: 第1-4. 2: 第5-8. 3: 第9-12. 4: 第13-16. 5: 第17-20. 6: 第21-24|毎半帖10行|漢字平仮名交じり文|奈良絵本|梅唐草文様緞子表紙, 松葉散しに山雲の金箔見返し, 金泥下絵鳥の子紙を使用|列帖装|竪本|二重箱入り|糸切れあり</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -3476,12 +3488,12 @@
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/a23dae2e-701a-8d7c-1359-fe786c2e2cdd.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/ff7eb5a9-8bd0-64c0-3cbf-03a54ac07e65.json</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>a23dae2e-701a-8d7c-1359-fe786c2e2cdd</t>
+          <t>ff7eb5a9-8bd0-64c0-3cbf-03a54ac07e65</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -3491,7 +3503,7 @@
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/a23dae2e-701a-8d7c-1359-fe786c2e2cdd</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/ff7eb5a9-8bd0-64c0-3cbf-03a54ac07e65</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
@@ -3501,12 +3513,12 @@
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/21b02bac7c065db97c214037acfa4b232d2ddc89.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/550abdb28c4a764b0c1330b7551c32cee807416f.jpg</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296242</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296173</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
@@ -3529,7 +3541,7 @@
       <c r="AB25" t="inlineStr"/>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/a23dae2e-701a-8d7c-1359-fe786c2e2cdd/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/ff7eb5a9-8bd0-64c0-3cbf-03a54ac07e65/manifest</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr"/>
@@ -3537,29 +3549,29 @@
       <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="inlineStr"/>
       <c r="AH25" t="n">
-        <v>63</v>
+        <v>87</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [19]</t>
+          <t>日本廿四孝 6巻 [6]</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>A00:6257</t>
+          <t>A00:4084</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>レキダイ ザンケツ ニッキ</t>
+          <t>ヤマト ニジュウシコウ</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>黒川 春村</t>
+          <t>浅井 了意</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -3570,19 +3582,19 @@
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
-          <t>[安政5 (1858)]</t>
+          <t>[江戸前期]</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
-          <t>写本|責任表示及び書写年は『日本古典籍総合目録データベース』による|内容: 6: 光明院御記, 後光嚴院御記, 後小松院宸記, 天聴集. 28: 参議藤定長卿記 : 稱山丞記. 37: 定高卿記, 晴御会部類記, 家光卿御記, 權中納言平範輔卿記. 38: 左大史小槻季継記, 後堀川安貞二年放生會(実基公記), 石清水八幡宮, 弁官拝賀次第. 39: 大外記師光記, 資季卿記, 荒凉記, 忠高卿記. 40: 冷泉公相公記, 勝延法眼記 : 東寺大行事, 後中記 : 小路中納言資頼卿記葉室. 41: 中光記, 師兼記, 陽龍記. 42: 大宮司長則記, 口筆 : 實經, 顕朝卿記, 鴨御幸記. 43: 寳治二年記, 深心院關白記, 藤公親記, 照念院関白兼平公記. 44: 頼親記, 亀山殿行幸記 : 雅言卿記, 兼基公記. 45: 大嘗會御禊節下次第, 建治三年丁丑日記 : 三善康有, 建治四年正月廿一日 : 徳大寺大相國公孝記, 冬定卿記, 左大史小槻兼文記|内容: 46: 經任卿記, 前豊前守藤憲説記, 實兼公記. 47: 継塵記抄出. 48: 管見記, 公衡公記, 大外記師顕記, 大外記中原師淳記. 49: 真光院禪助僧正記, 吉田内府卿記. 50: 定清記, 叅議雅俊卿記, 太政大臣(公守公)御上表雜事, 仙洞御灌頂日記, 正安二年八月十一日於仙洞被始行熾盛光法, 正安三年御譲位記. 51: 實躬卿記. 52: 公茂公記, 冬平公記, 隆長卿記. 53: 忠教公記, 官記, 正三位長基卿記, 北面秀長記, 大外記中原師右記. 54: 文保元年, 日野中納言資朝卿記, 洞院大納言公敏卿記. 55: 隆蔭卿記, 文保三年記, 尹大納言師賢卿記, 革命記, 立倚子記, 萬里小路中納言藤藤房卿記|内容: 56: 資名卿記, 公秀公記, 一條家記装束抄出, 頼定卿記. 63: 松亞記, 日野大納言時光卿記, 後八條内府實継公記. 74: 成恩寺関白記. 78: 山科家礼記. 82: 諒闇記 : 後成恩寺殿, 宗典僧正記, 綱光公記, 贈従二位宗賢卿記, 義政公記. 84: 長禄二年戊寅正月, 見聞雜記. 87: 言國卿記. 88: 長興宿祢記, 元長卿記, 兼顕卿記, 小槻晴冨記|28末の原奥書に「右山丞記依 仰挍合書冩/享和二年四月 日撿挍保己一」とあり|50「正安二年八月十一日於仙洞被始行熾盛光法」末の原奥書に「文化十五年春二月以南山法曼院藏夲書冩之 撿挍保己一」とあり|横刷毛目表紙を使用|朱点, 朱引, 朱墨筆書き入れあり|付箋あり|蔵書印主信濃須坂藩主堀直格の命によって編集された古記録|他の原本は関東大震災により焼失|極札に「桂壽」(6), 「尚信」(53)との極書, 「武清」(44, 53), 「永海」(51), 「了伴」(52), 「了甫」(74), 「定時」(84, 88)との極印あり|印記: 「花廼家文庫」, 「墨阪十一代主寫藏記」(堀直格(1806-1880)), 「東京大學法理文學部書庫所藏」, 「閲覧室用 FOR USE IN THE READING ROOM」|虫損あり</t>
+          <t>写本|書名は目首及び題簽による|内箱の書名: 大和廿四孝|外箱の書名: 御本|責任表示は『日本古典籍総合目録データベース』による|1: 第1-4. 2: 第5-8. 3: 第9-12. 4: 第13-16. 5: 第17-20. 6: 第21-24|毎半帖10行|漢字平仮名交じり文|奈良絵本|梅唐草文様緞子表紙, 松葉散しに山雲の金箔見返し, 金泥下絵鳥の子紙を使用|列帖装|竪本|二重箱入り|糸切れあり</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -3598,12 +3610,12 @@
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/1373f0d8-7cc0-4591-2c18-798fa20f483d.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/0106be3f-16cb-3945-1c3c-419a27f26c16.json</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>1373f0d8-7cc0-4591-2c18-798fa20f483d</t>
+          <t>0106be3f-16cb-3945-1c3c-419a27f26c16</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -3613,7 +3625,7 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/1373f0d8-7cc0-4591-2c18-798fa20f483d</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/0106be3f-16cb-3945-1c3c-419a27f26c16</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
@@ -3623,12 +3635,12 @@
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/326ed2db044321d7b007462c9ac98badfd7f671a.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/b1c4cf868676ac5b8b2f574249475349a7a90813.jpg</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296219</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296174</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
@@ -3651,7 +3663,7 @@
       <c r="AB26" t="inlineStr"/>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/1373f0d8-7cc0-4591-2c18-798fa20f483d/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/0106be3f-16cb-3945-1c3c-419a27f26c16/manifest</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr"/>
@@ -3659,29 +3671,29 @@
       <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="inlineStr"/>
       <c r="AH26" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [18]</t>
+          <t>京ものかたり</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>A00:6257</t>
+          <t>A00:4085</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>レキダイ ザンケツ ニッキ</t>
+          <t>キョウモノガタリ</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>黒川 春村</t>
+          <t>洛陽散人</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -3692,7 +3704,7 @@
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
-          <t>[安政5 (1858)]</t>
+          <t>[江戸前期]</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3704,7 +3716,7 @@
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
-          <t>写本|責任表示及び書写年は『日本古典籍総合目録データベース』による|内容: 6: 光明院御記, 後光嚴院御記, 後小松院宸記, 天聴集. 28: 参議藤定長卿記 : 稱山丞記. 37: 定高卿記, 晴御会部類記, 家光卿御記, 權中納言平範輔卿記. 38: 左大史小槻季継記, 後堀川安貞二年放生會(実基公記), 石清水八幡宮, 弁官拝賀次第. 39: 大外記師光記, 資季卿記, 荒凉記, 忠高卿記. 40: 冷泉公相公記, 勝延法眼記 : 東寺大行事, 後中記 : 小路中納言資頼卿記葉室. 41: 中光記, 師兼記, 陽龍記. 42: 大宮司長則記, 口筆 : 實經, 顕朝卿記, 鴨御幸記. 43: 寳治二年記, 深心院關白記, 藤公親記, 照念院関白兼平公記. 44: 頼親記, 亀山殿行幸記 : 雅言卿記, 兼基公記. 45: 大嘗會御禊節下次第, 建治三年丁丑日記 : 三善康有, 建治四年正月廿一日 : 徳大寺大相國公孝記, 冬定卿記, 左大史小槻兼文記|内容: 46: 經任卿記, 前豊前守藤憲説記, 實兼公記. 47: 継塵記抄出. 48: 管見記, 公衡公記, 大外記師顕記, 大外記中原師淳記. 49: 真光院禪助僧正記, 吉田内府卿記. 50: 定清記, 叅議雅俊卿記, 太政大臣(公守公)御上表雜事, 仙洞御灌頂日記, 正安二年八月十一日於仙洞被始行熾盛光法, 正安三年御譲位記. 51: 實躬卿記. 52: 公茂公記, 冬平公記, 隆長卿記. 53: 忠教公記, 官記, 正三位長基卿記, 北面秀長記, 大外記中原師右記. 54: 文保元年, 日野中納言資朝卿記, 洞院大納言公敏卿記. 55: 隆蔭卿記, 文保三年記, 尹大納言師賢卿記, 革命記, 立倚子記, 萬里小路中納言藤藤房卿記|内容: 56: 資名卿記, 公秀公記, 一條家記装束抄出, 頼定卿記. 63: 松亞記, 日野大納言時光卿記, 後八條内府實継公記. 74: 成恩寺関白記. 78: 山科家礼記. 82: 諒闇記 : 後成恩寺殿, 宗典僧正記, 綱光公記, 贈従二位宗賢卿記, 義政公記. 84: 長禄二年戊寅正月, 見聞雜記. 87: 言國卿記. 88: 長興宿祢記, 元長卿記, 兼顕卿記, 小槻晴冨記|28末の原奥書に「右山丞記依 仰挍合書冩/享和二年四月 日撿挍保己一」とあり|50「正安二年八月十一日於仙洞被始行熾盛光法」末の原奥書に「文化十五年春二月以南山法曼院藏夲書冩之 撿挍保己一」とあり|横刷毛目表紙を使用|朱点, 朱引, 朱墨筆書き入れあり|付箋あり|蔵書印主信濃須坂藩主堀直格の命によって編集された古記録|他の原本は関東大震災により焼失|極札に「桂壽」(6), 「尚信」(53)との極書, 「武清」(44, 53), 「永海」(51), 「了伴」(52), 「了甫」(74), 「定時」(84, 88)との極印あり|印記: 「花廼家文庫」, 「墨阪十一代主寫藏記」(堀直格(1806-1880)), 「東京大學法理文學部書庫所藏」, 「閲覧室用 FOR USE IN THE READING ROOM」|虫損あり</t>
+          <t>写本|書名は題簽による|[跋]中の書名: 見ぬ京ものかたり|外箱の書名: 御本|[跋]に「万治元年の秋夜長きひ ... いぬの年九月の末のはふのなん時 洛陽散人たれ某」とあり|内容: 儒佛の論, など|毎半帖10行|漢字平仮名交じり文|桜唐草文様緞子表紙, 松葉散しに山雲の金箔見返し, 金泥下絵鳥の子紙を使用|列帖装|二重箱入り</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -3720,12 +3732,12 @@
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/c69854e0-18e9-71b3-a7b1-22422a16688b.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/13969a60-692e-663a-3a83-97b8168b8fbe.json</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>c69854e0-18e9-71b3-a7b1-22422a16688b</t>
+          <t>13969a60-692e-663a-3a83-97b8168b8fbe</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -3735,7 +3747,7 @@
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/c69854e0-18e9-71b3-a7b1-22422a16688b</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/13969a60-692e-663a-3a83-97b8168b8fbe</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
@@ -3745,12 +3757,12 @@
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/584cfd5ec1bb0f374ab03f25ca3600a8ec2e67bf.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/b4c216cdd7c363c063be4e90de6eea21dd1da6e3.jpg</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296218</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296175</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
@@ -3773,7 +3785,7 @@
       <c r="AB27" t="inlineStr"/>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/c69854e0-18e9-71b3-a7b1-22422a16688b/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/13969a60-692e-663a-3a83-97b8168b8fbe/manifest</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr"/>
@@ -3781,52 +3793,52 @@
       <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="inlineStr"/>
       <c r="AH27" t="n">
-        <v>77</v>
+        <v>68</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [17]</t>
+          <t>北遊漫録 3巻再1巻 [1]</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>A00:6257</t>
+          <t>A00:4099</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>レキダイ ザンケツ ニッキ</t>
+          <t>ホクユウ マンロク</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>黒川 春村</t>
+          <t>久保田 米僊</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>[書写者不明]</t>
+          <t>久保田米僊 [自筆]</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
-          <t>[安政5 (1858)]</t>
+          <t>明治21 [1888]-明治24 [1891]</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
-          <t>写本|責任表示及び書写年は『日本古典籍総合目録データベース』による|内容: 6: 光明院御記, 後光嚴院御記, 後小松院宸記, 天聴集. 28: 参議藤定長卿記 : 稱山丞記. 37: 定高卿記, 晴御会部類記, 家光卿御記, 權中納言平範輔卿記. 38: 左大史小槻季継記, 後堀川安貞二年放生會(実基公記), 石清水八幡宮, 弁官拝賀次第. 39: 大外記師光記, 資季卿記, 荒凉記, 忠高卿記. 40: 冷泉公相公記, 勝延法眼記 : 東寺大行事, 後中記 : 小路中納言資頼卿記葉室. 41: 中光記, 師兼記, 陽龍記. 42: 大宮司長則記, 口筆 : 實經, 顕朝卿記, 鴨御幸記. 43: 寳治二年記, 深心院關白記, 藤公親記, 照念院関白兼平公記. 44: 頼親記, 亀山殿行幸記 : 雅言卿記, 兼基公記. 45: 大嘗會御禊節下次第, 建治三年丁丑日記 : 三善康有, 建治四年正月廿一日 : 徳大寺大相國公孝記, 冬定卿記, 左大史小槻兼文記|内容: 46: 經任卿記, 前豊前守藤憲説記, 實兼公記. 47: 継塵記抄出. 48: 管見記, 公衡公記, 大外記師顕記, 大外記中原師淳記. 49: 真光院禪助僧正記, 吉田内府卿記. 50: 定清記, 叅議雅俊卿記, 太政大臣(公守公)御上表雜事, 仙洞御灌頂日記, 正安二年八月十一日於仙洞被始行熾盛光法, 正安三年御譲位記. 51: 實躬卿記. 52: 公茂公記, 冬平公記, 隆長卿記. 53: 忠教公記, 官記, 正三位長基卿記, 北面秀長記, 大外記中原師右記. 54: 文保元年, 日野中納言資朝卿記, 洞院大納言公敏卿記. 55: 隆蔭卿記, 文保三年記, 尹大納言師賢卿記, 革命記, 立倚子記, 萬里小路中納言藤藤房卿記|内容: 56: 資名卿記, 公秀公記, 一條家記装束抄出, 頼定卿記. 63: 松亞記, 日野大納言時光卿記, 後八條内府實継公記. 74: 成恩寺関白記. 78: 山科家礼記. 82: 諒闇記 : 後成恩寺殿, 宗典僧正記, 綱光公記, 贈従二位宗賢卿記, 義政公記. 84: 長禄二年戊寅正月, 見聞雜記. 87: 言國卿記. 88: 長興宿祢記, 元長卿記, 兼顕卿記, 小槻晴冨記|28末の原奥書に「右山丞記依 仰挍合書冩/享和二年四月 日撿挍保己一」とあり|50「正安二年八月十一日於仙洞被始行熾盛光法」末の原奥書に「文化十五年春二月以南山法曼院藏夲書冩之 撿挍保己一」とあり|横刷毛目表紙を使用|朱点, 朱引, 朱墨筆書き入れあり|付箋あり|蔵書印主信濃須坂藩主堀直格の命によって編集された古記録|他の原本は関東大震災により焼失|極札に「桂壽」(6), 「尚信」(53)との極書, 「武清」(44, 53), 「永海」(51), 「了伴」(52), 「了甫」(74), 「定時」(84, 88)との極印あり|印記: 「花廼家文庫」, 「墨阪十一代主寫藏記」(堀直格(1806-1880)), 「東京大學法理文學部書庫所藏」, 「閲覧室用 FOR USE IN THE READING ROOM」|虫損あり</t>
+          <t>写本|書名は扉による|帙題簽に「久保田米僊草稿」とあり|扉に「明治廿一年はる五月」(乾), 「明治廿一年はる六月」(坤), 「明治廿一年はる六月中澣」(瑞啚), 「明治廿四年五月十九日」(再)とあり|乾末に「増補考古畫譜五巻 發兌書肆 有隣堂」とあり|おもに図版|彩色あり|双葉装|印記: 「田寛之印」, 「山脊与弥との」</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -3842,12 +3854,12 @@
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/37d790df-458b-48bf-6b67-3f4755f40f0f.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/fdb2f4c7-47bb-0fc6-53e6-e8ffb5796046.json</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>37d790df-458b-48bf-6b67-3f4755f40f0f</t>
+          <t>fdb2f4c7-47bb-0fc6-53e6-e8ffb5796046</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -3857,7 +3869,7 @@
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/37d790df-458b-48bf-6b67-3f4755f40f0f</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/fdb2f4c7-47bb-0fc6-53e6-e8ffb5796046</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
@@ -3867,12 +3879,12 @@
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/dae05b3fca02a35e3363b381527ea7a899ca4f74.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/789ef89fb4fc813de5d276f3c43f982c6760d60b.jpg</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296217</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296176</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
@@ -3895,7 +3907,7 @@
       <c r="AB28" t="inlineStr"/>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/37d790df-458b-48bf-6b67-3f4755f40f0f/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/fdb2f4c7-47bb-0fc6-53e6-e8ffb5796046/manifest</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr"/>
@@ -3903,52 +3915,52 @@
       <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="inlineStr"/>
       <c r="AH28" t="n">
-        <v>54</v>
+        <v>31</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [15]</t>
+          <t>北遊漫録 3巻再1巻 [2]</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>A00:6257</t>
+          <t>A00:4099</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>レキダイ ザンケツ ニッキ</t>
+          <t>ホクユウ マンロク</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>黒川 春村</t>
+          <t>久保田 米僊</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>[書写者不明]</t>
+          <t>久保田米僊 [自筆]</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
-          <t>[安政5 (1858)]</t>
+          <t>明治21 [1888]-明治24 [1891]</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
-          <t>写本|責任表示及び書写年は『日本古典籍総合目録データベース』による|内容: 6: 光明院御記, 後光嚴院御記, 後小松院宸記, 天聴集. 28: 参議藤定長卿記 : 稱山丞記. 37: 定高卿記, 晴御会部類記, 家光卿御記, 權中納言平範輔卿記. 38: 左大史小槻季継記, 後堀川安貞二年放生會(実基公記), 石清水八幡宮, 弁官拝賀次第. 39: 大外記師光記, 資季卿記, 荒凉記, 忠高卿記. 40: 冷泉公相公記, 勝延法眼記 : 東寺大行事, 後中記 : 小路中納言資頼卿記葉室. 41: 中光記, 師兼記, 陽龍記. 42: 大宮司長則記, 口筆 : 實經, 顕朝卿記, 鴨御幸記. 43: 寳治二年記, 深心院關白記, 藤公親記, 照念院関白兼平公記. 44: 頼親記, 亀山殿行幸記 : 雅言卿記, 兼基公記. 45: 大嘗會御禊節下次第, 建治三年丁丑日記 : 三善康有, 建治四年正月廿一日 : 徳大寺大相國公孝記, 冬定卿記, 左大史小槻兼文記|内容: 46: 經任卿記, 前豊前守藤憲説記, 實兼公記. 47: 継塵記抄出. 48: 管見記, 公衡公記, 大外記師顕記, 大外記中原師淳記. 49: 真光院禪助僧正記, 吉田内府卿記. 50: 定清記, 叅議雅俊卿記, 太政大臣(公守公)御上表雜事, 仙洞御灌頂日記, 正安二年八月十一日於仙洞被始行熾盛光法, 正安三年御譲位記. 51: 實躬卿記. 52: 公茂公記, 冬平公記, 隆長卿記. 53: 忠教公記, 官記, 正三位長基卿記, 北面秀長記, 大外記中原師右記. 54: 文保元年, 日野中納言資朝卿記, 洞院大納言公敏卿記. 55: 隆蔭卿記, 文保三年記, 尹大納言師賢卿記, 革命記, 立倚子記, 萬里小路中納言藤藤房卿記|内容: 56: 資名卿記, 公秀公記, 一條家記装束抄出, 頼定卿記. 63: 松亞記, 日野大納言時光卿記, 後八條内府實継公記. 74: 成恩寺関白記. 78: 山科家礼記. 82: 諒闇記 : 後成恩寺殿, 宗典僧正記, 綱光公記, 贈従二位宗賢卿記, 義政公記. 84: 長禄二年戊寅正月, 見聞雜記. 87: 言國卿記. 88: 長興宿祢記, 元長卿記, 兼顕卿記, 小槻晴冨記|28末の原奥書に「右山丞記依 仰挍合書冩/享和二年四月 日撿挍保己一」とあり|50「正安二年八月十一日於仙洞被始行熾盛光法」末の原奥書に「文化十五年春二月以南山法曼院藏夲書冩之 撿挍保己一」とあり|横刷毛目表紙を使用|朱点, 朱引, 朱墨筆書き入れあり|付箋あり|蔵書印主信濃須坂藩主堀直格の命によって編集された古記録|他の原本は関東大震災により焼失|極札に「桂壽」(6), 「尚信」(53)との極書, 「武清」(44, 53), 「永海」(51), 「了伴」(52), 「了甫」(74), 「定時」(84, 88)との極印あり|印記: 「花廼家文庫」, 「墨阪十一代主寫藏記」(堀直格(1806-1880)), 「東京大學法理文學部書庫所藏」, 「閲覧室用 FOR USE IN THE READING ROOM」|虫損あり</t>
+          <t>写本|書名は扉による|帙題簽に「久保田米僊草稿」とあり|扉に「明治廿一年はる五月」(乾), 「明治廿一年はる六月」(坤), 「明治廿一年はる六月中澣」(瑞啚), 「明治廿四年五月十九日」(再)とあり|乾末に「増補考古畫譜五巻 發兌書肆 有隣堂」とあり|おもに図版|彩色あり|双葉装|印記: 「田寛之印」, 「山脊与弥との」</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -3964,12 +3976,12 @@
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/acf20dd5-459a-5438-8dd8-cbc11fe122bf.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/01f5e469-1d82-36bd-3e33-34c56a942a2d.json</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>acf20dd5-459a-5438-8dd8-cbc11fe122bf</t>
+          <t>01f5e469-1d82-36bd-3e33-34c56a942a2d</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -3979,7 +3991,7 @@
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/acf20dd5-459a-5438-8dd8-cbc11fe122bf</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/01f5e469-1d82-36bd-3e33-34c56a942a2d</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
@@ -3989,12 +4001,12 @@
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/cfeece07d99889e30589237e6d78b4933a56b7d6.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/0e331722b5a82ea48f273a6b7465d2784dc8a44c.jpg</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296215</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296177</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
@@ -4017,7 +4029,7 @@
       <c r="AB29" t="inlineStr"/>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/acf20dd5-459a-5438-8dd8-cbc11fe122bf/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/01f5e469-1d82-36bd-3e33-34c56a942a2d/manifest</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr"/>
@@ -4025,52 +4037,52 @@
       <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="inlineStr"/>
       <c r="AH29" t="n">
-        <v>64</v>
+        <v>31</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [16]</t>
+          <t>北遊漫録 3巻再1巻 [3]</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>A00:6257</t>
+          <t>A00:4099</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>レキダイ ザンケツ ニッキ</t>
+          <t>ホクユウ マンロク</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>黒川 春村</t>
+          <t>久保田 米僊</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>[書写者不明]</t>
+          <t>久保田米僊 [自筆]</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
-          <t>[安政5 (1858)]</t>
+          <t>明治21 [1888]-明治24 [1891]</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
-          <t>写本|責任表示及び書写年は『日本古典籍総合目録データベース』による|内容: 6: 光明院御記, 後光嚴院御記, 後小松院宸記, 天聴集. 28: 参議藤定長卿記 : 稱山丞記. 37: 定高卿記, 晴御会部類記, 家光卿御記, 權中納言平範輔卿記. 38: 左大史小槻季継記, 後堀川安貞二年放生會(実基公記), 石清水八幡宮, 弁官拝賀次第. 39: 大外記師光記, 資季卿記, 荒凉記, 忠高卿記. 40: 冷泉公相公記, 勝延法眼記 : 東寺大行事, 後中記 : 小路中納言資頼卿記葉室. 41: 中光記, 師兼記, 陽龍記. 42: 大宮司長則記, 口筆 : 實經, 顕朝卿記, 鴨御幸記. 43: 寳治二年記, 深心院關白記, 藤公親記, 照念院関白兼平公記. 44: 頼親記, 亀山殿行幸記 : 雅言卿記, 兼基公記. 45: 大嘗會御禊節下次第, 建治三年丁丑日記 : 三善康有, 建治四年正月廿一日 : 徳大寺大相國公孝記, 冬定卿記, 左大史小槻兼文記|内容: 46: 經任卿記, 前豊前守藤憲説記, 實兼公記. 47: 継塵記抄出. 48: 管見記, 公衡公記, 大外記師顕記, 大外記中原師淳記. 49: 真光院禪助僧正記, 吉田内府卿記. 50: 定清記, 叅議雅俊卿記, 太政大臣(公守公)御上表雜事, 仙洞御灌頂日記, 正安二年八月十一日於仙洞被始行熾盛光法, 正安三年御譲位記. 51: 實躬卿記. 52: 公茂公記, 冬平公記, 隆長卿記. 53: 忠教公記, 官記, 正三位長基卿記, 北面秀長記, 大外記中原師右記. 54: 文保元年, 日野中納言資朝卿記, 洞院大納言公敏卿記. 55: 隆蔭卿記, 文保三年記, 尹大納言師賢卿記, 革命記, 立倚子記, 萬里小路中納言藤藤房卿記|内容: 56: 資名卿記, 公秀公記, 一條家記装束抄出, 頼定卿記. 63: 松亞記, 日野大納言時光卿記, 後八條内府實継公記. 74: 成恩寺関白記. 78: 山科家礼記. 82: 諒闇記 : 後成恩寺殿, 宗典僧正記, 綱光公記, 贈従二位宗賢卿記, 義政公記. 84: 長禄二年戊寅正月, 見聞雜記. 87: 言國卿記. 88: 長興宿祢記, 元長卿記, 兼顕卿記, 小槻晴冨記|28末の原奥書に「右山丞記依 仰挍合書冩/享和二年四月 日撿挍保己一」とあり|50「正安二年八月十一日於仙洞被始行熾盛光法」末の原奥書に「文化十五年春二月以南山法曼院藏夲書冩之 撿挍保己一」とあり|横刷毛目表紙を使用|朱点, 朱引, 朱墨筆書き入れあり|付箋あり|蔵書印主信濃須坂藩主堀直格の命によって編集された古記録|他の原本は関東大震災により焼失|極札に「桂壽」(6), 「尚信」(53)との極書, 「武清」(44, 53), 「永海」(51), 「了伴」(52), 「了甫」(74), 「定時」(84, 88)との極印あり|印記: 「花廼家文庫」, 「墨阪十一代主寫藏記」(堀直格(1806-1880)), 「東京大學法理文學部書庫所藏」, 「閲覧室用 FOR USE IN THE READING ROOM」|虫損あり</t>
+          <t>写本|書名は扉による|帙題簽に「久保田米僊草稿」とあり|扉に「明治廿一年はる五月」(乾), 「明治廿一年はる六月」(坤), 「明治廿一年はる六月中澣」(瑞啚), 「明治廿四年五月十九日」(再)とあり|乾末に「増補考古畫譜五巻 發兌書肆 有隣堂」とあり|おもに図版|彩色あり|双葉装|印記: 「田寛之印」, 「山脊与弥との」</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -4086,12 +4098,12 @@
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/31b47601-839e-83b4-6a49-7d11ed020385.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/1a4a12a3-0ae7-8858-3851-f3845f60709b.json</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>31b47601-839e-83b4-6a49-7d11ed020385</t>
+          <t>1a4a12a3-0ae7-8858-3851-f3845f60709b</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -4101,7 +4113,7 @@
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/31b47601-839e-83b4-6a49-7d11ed020385</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/1a4a12a3-0ae7-8858-3851-f3845f60709b</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
@@ -4111,12 +4123,12 @@
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/d78a0b64be5f71b37b264b3b2eb8172d4e8a5002.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/3897bac3ffa751a75c02bb59922c185ca93a9f1e.jpg</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296216</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296178</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
@@ -4139,7 +4151,7 @@
       <c r="AB30" t="inlineStr"/>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/31b47601-839e-83b4-6a49-7d11ed020385/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/1a4a12a3-0ae7-8858-3851-f3845f60709b/manifest</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr"/>
@@ -4147,52 +4159,52 @@
       <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="inlineStr"/>
       <c r="AH30" t="n">
-        <v>58</v>
+        <v>31</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [2]</t>
+          <t>北遊漫録 3巻再1巻 [4]</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>A00:6257</t>
+          <t>A00:4099</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>レキダイ ザンケツ ニッキ</t>
+          <t>ホクユウ マンロク</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>黒川 春村</t>
+          <t>久保田 米僊</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>[書写者不明]</t>
+          <t>久保田米僊 [自筆]</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
-          <t>[安政5 (1858)]</t>
+          <t>明治21 [1888]-明治24 [1891]</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
-          <t>写本|責任表示及び書写年は『日本古典籍総合目録データベース』による|内容: 6: 光明院御記, 後光嚴院御記, 後小松院宸記, 天聴集. 28: 参議藤定長卿記 : 稱山丞記. 37: 定高卿記, 晴御会部類記, 家光卿御記, 權中納言平範輔卿記. 38: 左大史小槻季継記, 後堀川安貞二年放生會(実基公記), 石清水八幡宮, 弁官拝賀次第. 39: 大外記師光記, 資季卿記, 荒凉記, 忠高卿記. 40: 冷泉公相公記, 勝延法眼記 : 東寺大行事, 後中記 : 小路中納言資頼卿記葉室. 41: 中光記, 師兼記, 陽龍記. 42: 大宮司長則記, 口筆 : 實經, 顕朝卿記, 鴨御幸記. 43: 寳治二年記, 深心院關白記, 藤公親記, 照念院関白兼平公記. 44: 頼親記, 亀山殿行幸記 : 雅言卿記, 兼基公記. 45: 大嘗會御禊節下次第, 建治三年丁丑日記 : 三善康有, 建治四年正月廿一日 : 徳大寺大相國公孝記, 冬定卿記, 左大史小槻兼文記|内容: 46: 經任卿記, 前豊前守藤憲説記, 實兼公記. 47: 継塵記抄出. 48: 管見記, 公衡公記, 大外記師顕記, 大外記中原師淳記. 49: 真光院禪助僧正記, 吉田内府卿記. 50: 定清記, 叅議雅俊卿記, 太政大臣(公守公)御上表雜事, 仙洞御灌頂日記, 正安二年八月十一日於仙洞被始行熾盛光法, 正安三年御譲位記. 51: 實躬卿記. 52: 公茂公記, 冬平公記, 隆長卿記. 53: 忠教公記, 官記, 正三位長基卿記, 北面秀長記, 大外記中原師右記. 54: 文保元年, 日野中納言資朝卿記, 洞院大納言公敏卿記. 55: 隆蔭卿記, 文保三年記, 尹大納言師賢卿記, 革命記, 立倚子記, 萬里小路中納言藤藤房卿記|内容: 56: 資名卿記, 公秀公記, 一條家記装束抄出, 頼定卿記. 63: 松亞記, 日野大納言時光卿記, 後八條内府實継公記. 74: 成恩寺関白記. 78: 山科家礼記. 82: 諒闇記 : 後成恩寺殿, 宗典僧正記, 綱光公記, 贈従二位宗賢卿記, 義政公記. 84: 長禄二年戊寅正月, 見聞雜記. 87: 言國卿記. 88: 長興宿祢記, 元長卿記, 兼顕卿記, 小槻晴冨記|28末の原奥書に「右山丞記依 仰挍合書冩/享和二年四月 日撿挍保己一」とあり|50「正安二年八月十一日於仙洞被始行熾盛光法」末の原奥書に「文化十五年春二月以南山法曼院藏夲書冩之 撿挍保己一」とあり|横刷毛目表紙を使用|朱点, 朱引, 朱墨筆書き入れあり|付箋あり|蔵書印主信濃須坂藩主堀直格の命によって編集された古記録|他の原本は関東大震災により焼失|極札に「桂壽」(6), 「尚信」(53)との極書, 「武清」(44, 53), 「永海」(51), 「了伴」(52), 「了甫」(74), 「定時」(84, 88)との極印あり|印記: 「花廼家文庫」, 「墨阪十一代主寫藏記」(堀直格(1806-1880)), 「東京大學法理文學部書庫所藏」, 「閲覧室用 FOR USE IN THE READING ROOM」|虫損あり</t>
+          <t>写本|書名は扉による|帙題簽に「久保田米僊草稿」とあり|扉に「明治廿一年はる五月」(乾), 「明治廿一年はる六月」(坤), 「明治廿一年はる六月中澣」(瑞啚), 「明治廿四年五月十九日」(再)とあり|乾末に「増補考古畫譜五巻 發兌書肆 有隣堂」とあり|おもに図版|彩色あり|双葉装|印記: 「田寛之印」, 「山脊与弥との」</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -4208,12 +4220,12 @@
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/f31d474b-60bb-5efd-a570-d8f971a97e5e.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/73cbda29-23d4-a760-5213-0395cd767491.json</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>f31d474b-60bb-5efd-a570-d8f971a97e5e</t>
+          <t>73cbda29-23d4-a760-5213-0395cd767491</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -4223,7 +4235,7 @@
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/f31d474b-60bb-5efd-a570-d8f971a97e5e</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/73cbda29-23d4-a760-5213-0395cd767491</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
@@ -4233,12 +4245,12 @@
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/378909456e17de7b588873b8890cd6945bba3cc8.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/74a9af6c2a682e260aa96f2ded5a07abfcd3098c.jpg</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296202</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296179</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
@@ -4261,7 +4273,7 @@
       <c r="AB31" t="inlineStr"/>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/f31d474b-60bb-5efd-a570-d8f971a97e5e/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/73cbda29-23d4-a760-5213-0395cd767491/manifest</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr"/>
@@ -4269,40 +4281,36 @@
       <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="inlineStr"/>
       <c r="AH31" t="n">
-        <v>75</v>
+        <v>22</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [3]</t>
+          <t>蘭主之書翰使節持参叅途中之図</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>A00:6257</t>
+          <t>A00:4146</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>レキダイ ザンケツ ニッキ</t>
+          <t>ランシュ ノ ショカン シセツ ジサン トチュウ ノ ズ</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>黒川 春村</t>
-        </is>
-      </c>
+      <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>[書写者不明]</t>
+          <t>[製作者不明]</t>
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr">
         <is>
-          <t>[安政5 (1858)]</t>
+          <t>天保15 [1844] 識語</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -4314,7 +4322,7 @@
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
-          <t>写本|責任表示及び書写年は『日本古典籍総合目録データベース』による|内容: 6: 光明院御記, 後光嚴院御記, 後小松院宸記, 天聴集. 28: 参議藤定長卿記 : 稱山丞記. 37: 定高卿記, 晴御会部類記, 家光卿御記, 權中納言平範輔卿記. 38: 左大史小槻季継記, 後堀川安貞二年放生會(実基公記), 石清水八幡宮, 弁官拝賀次第. 39: 大外記師光記, 資季卿記, 荒凉記, 忠高卿記. 40: 冷泉公相公記, 勝延法眼記 : 東寺大行事, 後中記 : 小路中納言資頼卿記葉室. 41: 中光記, 師兼記, 陽龍記. 42: 大宮司長則記, 口筆 : 實經, 顕朝卿記, 鴨御幸記. 43: 寳治二年記, 深心院關白記, 藤公親記, 照念院関白兼平公記. 44: 頼親記, 亀山殿行幸記 : 雅言卿記, 兼基公記. 45: 大嘗會御禊節下次第, 建治三年丁丑日記 : 三善康有, 建治四年正月廿一日 : 徳大寺大相國公孝記, 冬定卿記, 左大史小槻兼文記|内容: 46: 經任卿記, 前豊前守藤憲説記, 實兼公記. 47: 継塵記抄出. 48: 管見記, 公衡公記, 大外記師顕記, 大外記中原師淳記. 49: 真光院禪助僧正記, 吉田内府卿記. 50: 定清記, 叅議雅俊卿記, 太政大臣(公守公)御上表雜事, 仙洞御灌頂日記, 正安二年八月十一日於仙洞被始行熾盛光法, 正安三年御譲位記. 51: 實躬卿記. 52: 公茂公記, 冬平公記, 隆長卿記. 53: 忠教公記, 官記, 正三位長基卿記, 北面秀長記, 大外記中原師右記. 54: 文保元年, 日野中納言資朝卿記, 洞院大納言公敏卿記. 55: 隆蔭卿記, 文保三年記, 尹大納言師賢卿記, 革命記, 立倚子記, 萬里小路中納言藤藤房卿記|内容: 56: 資名卿記, 公秀公記, 一條家記装束抄出, 頼定卿記. 63: 松亞記, 日野大納言時光卿記, 後八條内府實継公記. 74: 成恩寺関白記. 78: 山科家礼記. 82: 諒闇記 : 後成恩寺殿, 宗典僧正記, 綱光公記, 贈従二位宗賢卿記, 義政公記. 84: 長禄二年戊寅正月, 見聞雜記. 87: 言國卿記. 88: 長興宿祢記, 元長卿記, 兼顕卿記, 小槻晴冨記|28末の原奥書に「右山丞記依 仰挍合書冩/享和二年四月 日撿挍保己一」とあり|50「正安二年八月十一日於仙洞被始行熾盛光法」末の原奥書に「文化十五年春二月以南山法曼院藏夲書冩之 撿挍保己一」とあり|横刷毛目表紙を使用|朱点, 朱引, 朱墨筆書き入れあり|付箋あり|蔵書印主信濃須坂藩主堀直格の命によって編集された古記録|他の原本は関東大震災により焼失|極札に「桂壽」(6), 「尚信」(53)との極書, 「武清」(44, 53), 「永海」(51), 「了伴」(52), 「了甫」(74), 「定時」(84, 88)との極印あり|印記: 「花廼家文庫」, 「墨阪十一代主寫藏記」(堀直格(1806-1880)), 「東京大學法理文學部書庫所藏」, 「閲覧室用 FOR USE IN THE READING ROOM」|虫損あり</t>
+          <t>書名は題簽による|箱の書名: 和蘭國軍艦人物兵器等図|冒頭に「天保十五年甲辰秋七月二日和蘭國官船奉其主命来進於我﨑嶴茲掲略圖摸其全般及内面結構所備之諸兵器等」との識語あり|絵巻|彩色あり|印記: 「籌海庫」</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -4330,12 +4338,12 @@
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/0ddf4bea-7e5d-145a-1812-20986271091f.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/ca3ac8e1-6c03-5832-3987-70b1fa71258a.json</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0ddf4bea-7e5d-145a-1812-20986271091f</t>
+          <t>ca3ac8e1-6c03-5832-3987-70b1fa71258a</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -4345,7 +4353,7 @@
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/0ddf4bea-7e5d-145a-1812-20986271091f</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/ca3ac8e1-6c03-5832-3987-70b1fa71258a</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
@@ -4355,12 +4363,12 @@
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/f1d109214b4c636205f357c37df4079371b1c32f.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/32f72c2d68d9e56e4f46528e6997cbb4c330cc23.jpg</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296203</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296180</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
@@ -4383,7 +4391,7 @@
       <c r="AB32" t="inlineStr"/>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/0ddf4bea-7e5d-145a-1812-20986271091f/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/ca3ac8e1-6c03-5832-3987-70b1fa71258a/manifest</t>
         </is>
       </c>
       <c r="AD32" t="inlineStr"/>
@@ -4391,40 +4399,36 @@
       <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="inlineStr"/>
       <c r="AH32" t="n">
-        <v>50</v>
+        <v>22</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [4]</t>
+          <t>喎蘭軍艦プレカット並銃劍等之図</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>A00:6257</t>
+          <t>A00:4147</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>レキダイ ザンケツ ニッキ</t>
+          <t>オランダ グンカン プレカット ナラビニ ジュウケン トウ ノ ズ</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>黒川 春村</t>
-        </is>
-      </c>
+      <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>[書写者不明]</t>
+          <t>[製作者不明]</t>
         </is>
       </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
-          <t>[安政5 (1858)]</t>
+          <t>[天保弘化年間]</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4436,7 +4440,7 @@
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
-          <t>写本|責任表示及び書写年は『日本古典籍総合目録データベース』による|内容: 6: 光明院御記, 後光嚴院御記, 後小松院宸記, 天聴集. 28: 参議藤定長卿記 : 稱山丞記. 37: 定高卿記, 晴御会部類記, 家光卿御記, 權中納言平範輔卿記. 38: 左大史小槻季継記, 後堀川安貞二年放生會(実基公記), 石清水八幡宮, 弁官拝賀次第. 39: 大外記師光記, 資季卿記, 荒凉記, 忠高卿記. 40: 冷泉公相公記, 勝延法眼記 : 東寺大行事, 後中記 : 小路中納言資頼卿記葉室. 41: 中光記, 師兼記, 陽龍記. 42: 大宮司長則記, 口筆 : 實經, 顕朝卿記, 鴨御幸記. 43: 寳治二年記, 深心院關白記, 藤公親記, 照念院関白兼平公記. 44: 頼親記, 亀山殿行幸記 : 雅言卿記, 兼基公記. 45: 大嘗會御禊節下次第, 建治三年丁丑日記 : 三善康有, 建治四年正月廿一日 : 徳大寺大相國公孝記, 冬定卿記, 左大史小槻兼文記|内容: 46: 經任卿記, 前豊前守藤憲説記, 實兼公記. 47: 継塵記抄出. 48: 管見記, 公衡公記, 大外記師顕記, 大外記中原師淳記. 49: 真光院禪助僧正記, 吉田内府卿記. 50: 定清記, 叅議雅俊卿記, 太政大臣(公守公)御上表雜事, 仙洞御灌頂日記, 正安二年八月十一日於仙洞被始行熾盛光法, 正安三年御譲位記. 51: 實躬卿記. 52: 公茂公記, 冬平公記, 隆長卿記. 53: 忠教公記, 官記, 正三位長基卿記, 北面秀長記, 大外記中原師右記. 54: 文保元年, 日野中納言資朝卿記, 洞院大納言公敏卿記. 55: 隆蔭卿記, 文保三年記, 尹大納言師賢卿記, 革命記, 立倚子記, 萬里小路中納言藤藤房卿記|内容: 56: 資名卿記, 公秀公記, 一條家記装束抄出, 頼定卿記. 63: 松亞記, 日野大納言時光卿記, 後八條内府實継公記. 74: 成恩寺関白記. 78: 山科家礼記. 82: 諒闇記 : 後成恩寺殿, 宗典僧正記, 綱光公記, 贈従二位宗賢卿記, 義政公記. 84: 長禄二年戊寅正月, 見聞雜記. 87: 言國卿記. 88: 長興宿祢記, 元長卿記, 兼顕卿記, 小槻晴冨記|28末の原奥書に「右山丞記依 仰挍合書冩/享和二年四月 日撿挍保己一」とあり|50「正安二年八月十一日於仙洞被始行熾盛光法」末の原奥書に「文化十五年春二月以南山法曼院藏夲書冩之 撿挍保己一」とあり|横刷毛目表紙を使用|朱点, 朱引, 朱墨筆書き入れあり|付箋あり|蔵書印主信濃須坂藩主堀直格の命によって編集された古記録|他の原本は関東大震災により焼失|極札に「桂壽」(6), 「尚信」(53)との極書, 「武清」(44, 53), 「永海」(51), 「了伴」(52), 「了甫」(74), 「定時」(84, 88)との極印あり|印記: 「花廼家文庫」, 「墨阪十一代主寫藏記」(堀直格(1806-1880)), 「東京大學法理文學部書庫所藏」, 「閲覧室用 FOR USE IN THE READING ROOM」|虫損あり</t>
+          <t>書名は題簽による|箱の書名: 和蘭國軍艦人物兵器等図|巻末に「圖説」あり|絵巻|彩色あり</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -4452,12 +4456,12 @@
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/5bf3d0ca-0a42-80a4-6959-af4f28d23fa3.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/8509e124-5c2f-173b-2502-4d9cd27f9f85.json</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>5bf3d0ca-0a42-80a4-6959-af4f28d23fa3</t>
+          <t>8509e124-5c2f-173b-2502-4d9cd27f9f85</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -4467,7 +4471,7 @@
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/5bf3d0ca-0a42-80a4-6959-af4f28d23fa3</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/8509e124-5c2f-173b-2502-4d9cd27f9f85</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
@@ -4477,12 +4481,12 @@
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/b3dd61edd0ba78499c058ae1c9d57f1980d4b058.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/18d2fe489472e7f697dd92568da44185793c8f4d.jpg</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296204</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296181</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
@@ -4505,7 +4509,7 @@
       <c r="AB33" t="inlineStr"/>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/5bf3d0ca-0a42-80a4-6959-af4f28d23fa3/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/8509e124-5c2f-173b-2502-4d9cd27f9f85/manifest</t>
         </is>
       </c>
       <c r="AD33" t="inlineStr"/>
@@ -4513,40 +4517,36 @@
       <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="inlineStr"/>
       <c r="AH33" t="n">
-        <v>52</v>
+        <v>17</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [5]</t>
+          <t>能面圗譜</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>A00:6257</t>
+          <t>A00:4269</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>レキダイ ザンケツ ニッキ</t>
+          <t>ノウメン ズフ</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>黒川 春村</t>
-        </is>
-      </c>
+      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>[書写者不明]</t>
+          <t>[製作者不明]</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
-          <t>[安政5 (1858)]</t>
+          <t>[江戸中期以降]</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -4558,7 +4558,7 @@
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
-          <t>写本|責任表示及び書写年は『日本古典籍総合目録データベース』による|内容: 6: 光明院御記, 後光嚴院御記, 後小松院宸記, 天聴集. 28: 参議藤定長卿記 : 稱山丞記. 37: 定高卿記, 晴御会部類記, 家光卿御記, 權中納言平範輔卿記. 38: 左大史小槻季継記, 後堀川安貞二年放生會(実基公記), 石清水八幡宮, 弁官拝賀次第. 39: 大外記師光記, 資季卿記, 荒凉記, 忠高卿記. 40: 冷泉公相公記, 勝延法眼記 : 東寺大行事, 後中記 : 小路中納言資頼卿記葉室. 41: 中光記, 師兼記, 陽龍記. 42: 大宮司長則記, 口筆 : 實經, 顕朝卿記, 鴨御幸記. 43: 寳治二年記, 深心院關白記, 藤公親記, 照念院関白兼平公記. 44: 頼親記, 亀山殿行幸記 : 雅言卿記, 兼基公記. 45: 大嘗會御禊節下次第, 建治三年丁丑日記 : 三善康有, 建治四年正月廿一日 : 徳大寺大相國公孝記, 冬定卿記, 左大史小槻兼文記|内容: 46: 經任卿記, 前豊前守藤憲説記, 實兼公記. 47: 継塵記抄出. 48: 管見記, 公衡公記, 大外記師顕記, 大外記中原師淳記. 49: 真光院禪助僧正記, 吉田内府卿記. 50: 定清記, 叅議雅俊卿記, 太政大臣(公守公)御上表雜事, 仙洞御灌頂日記, 正安二年八月十一日於仙洞被始行熾盛光法, 正安三年御譲位記. 51: 實躬卿記. 52: 公茂公記, 冬平公記, 隆長卿記. 53: 忠教公記, 官記, 正三位長基卿記, 北面秀長記, 大外記中原師右記. 54: 文保元年, 日野中納言資朝卿記, 洞院大納言公敏卿記. 55: 隆蔭卿記, 文保三年記, 尹大納言師賢卿記, 革命記, 立倚子記, 萬里小路中納言藤藤房卿記|内容: 56: 資名卿記, 公秀公記, 一條家記装束抄出, 頼定卿記. 63: 松亞記, 日野大納言時光卿記, 後八條内府實継公記. 74: 成恩寺関白記. 78: 山科家礼記. 82: 諒闇記 : 後成恩寺殿, 宗典僧正記, 綱光公記, 贈従二位宗賢卿記, 義政公記. 84: 長禄二年戊寅正月, 見聞雜記. 87: 言國卿記. 88: 長興宿祢記, 元長卿記, 兼顕卿記, 小槻晴冨記|28末の原奥書に「右山丞記依 仰挍合書冩/享和二年四月 日撿挍保己一」とあり|50「正安二年八月十一日於仙洞被始行熾盛光法」末の原奥書に「文化十五年春二月以南山法曼院藏夲書冩之 撿挍保己一」とあり|横刷毛目表紙を使用|朱点, 朱引, 朱墨筆書き入れあり|付箋あり|蔵書印主信濃須坂藩主堀直格の命によって編集された古記録|他の原本は関東大震災により焼失|極札に「桂壽」(6), 「尚信」(53)との極書, 「武清」(44, 53), 「永海」(51), 「了伴」(52), 「了甫」(74), 「定時」(84, 88)との極印あり|印記: 「花廼家文庫」, 「墨阪十一代主寫藏記」(堀直格(1806-1880)), 「東京大學法理文學部書庫所藏」, 「閲覧室用 FOR USE IN THE READING ROOM」|虫損あり</t>
+          <t>折本|書名は題簽(墨書)による|帙題簽の書名(墨書): 能面圖譜|絹本彩色|図42幅|本紙: 16×13cm|金切箔散し料紙, 福寿文字布目地表紙を使用</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -4574,12 +4574,12 @@
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/92efd5a7-2a66-1ead-1e71-bdf9c70e12d0.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/8b3019c4-7584-208c-0c75-7c855ddc0b9e.json</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>92efd5a7-2a66-1ead-1e71-bdf9c70e12d0</t>
+          <t>8b3019c4-7584-208c-0c75-7c855ddc0b9e</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -4589,7 +4589,7 @@
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/92efd5a7-2a66-1ead-1e71-bdf9c70e12d0</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/8b3019c4-7584-208c-0c75-7c855ddc0b9e</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
@@ -4599,12 +4599,12 @@
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/aaef2fe4c4feeefa7fd4fb27983a6dfd085d4a7b.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/3109e43cd273e3e02f2a227b4f1053cc1d4558bb.jpg</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296205</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296182</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
@@ -4627,7 +4627,7 @@
       <c r="AB34" t="inlineStr"/>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/92efd5a7-2a66-1ead-1e71-bdf9c70e12d0/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/8b3019c4-7584-208c-0c75-7c855ddc0b9e/manifest</t>
         </is>
       </c>
       <c r="AD34" t="inlineStr"/>
@@ -4635,29 +4635,29 @@
       <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="inlineStr"/>
       <c r="AH34" t="n">
-        <v>68</v>
+        <v>28</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [6]</t>
+          <t>法蕐經集驗記 2巻</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>A00:6257</t>
+          <t>A00:4273</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>レキダイ ザンケツ ニッキ</t>
+          <t>ホケキョウ シュウゲンキ</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>黒川 春村</t>
+          <t>義寂</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -4668,7 +4668,7 @@
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
-          <t>[安政5 (1858)]</t>
+          <t>[平安時代]</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -4680,7 +4680,7 @@
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
-          <t>写本|責任表示及び書写年は『日本古典籍総合目録データベース』による|内容: 6: 光明院御記, 後光嚴院御記, 後小松院宸記, 天聴集. 28: 参議藤定長卿記 : 稱山丞記. 37: 定高卿記, 晴御会部類記, 家光卿御記, 權中納言平範輔卿記. 38: 左大史小槻季継記, 後堀川安貞二年放生會(実基公記), 石清水八幡宮, 弁官拝賀次第. 39: 大外記師光記, 資季卿記, 荒凉記, 忠高卿記. 40: 冷泉公相公記, 勝延法眼記 : 東寺大行事, 後中記 : 小路中納言資頼卿記葉室. 41: 中光記, 師兼記, 陽龍記. 42: 大宮司長則記, 口筆 : 實經, 顕朝卿記, 鴨御幸記. 43: 寳治二年記, 深心院關白記, 藤公親記, 照念院関白兼平公記. 44: 頼親記, 亀山殿行幸記 : 雅言卿記, 兼基公記. 45: 大嘗會御禊節下次第, 建治三年丁丑日記 : 三善康有, 建治四年正月廿一日 : 徳大寺大相國公孝記, 冬定卿記, 左大史小槻兼文記|内容: 46: 經任卿記, 前豊前守藤憲説記, 實兼公記. 47: 継塵記抄出. 48: 管見記, 公衡公記, 大外記師顕記, 大外記中原師淳記. 49: 真光院禪助僧正記, 吉田内府卿記. 50: 定清記, 叅議雅俊卿記, 太政大臣(公守公)御上表雜事, 仙洞御灌頂日記, 正安二年八月十一日於仙洞被始行熾盛光法, 正安三年御譲位記. 51: 實躬卿記. 52: 公茂公記, 冬平公記, 隆長卿記. 53: 忠教公記, 官記, 正三位長基卿記, 北面秀長記, 大外記中原師右記. 54: 文保元年, 日野中納言資朝卿記, 洞院大納言公敏卿記. 55: 隆蔭卿記, 文保三年記, 尹大納言師賢卿記, 革命記, 立倚子記, 萬里小路中納言藤藤房卿記|内容: 56: 資名卿記, 公秀公記, 一條家記装束抄出, 頼定卿記. 63: 松亞記, 日野大納言時光卿記, 後八條内府實継公記. 74: 成恩寺関白記. 78: 山科家礼記. 82: 諒闇記 : 後成恩寺殿, 宗典僧正記, 綱光公記, 贈従二位宗賢卿記, 義政公記. 84: 長禄二年戊寅正月, 見聞雜記. 87: 言國卿記. 88: 長興宿祢記, 元長卿記, 兼顕卿記, 小槻晴冨記|28末の原奥書に「右山丞記依 仰挍合書冩/享和二年四月 日撿挍保己一」とあり|50「正安二年八月十一日於仙洞被始行熾盛光法」末の原奥書に「文化十五年春二月以南山法曼院藏夲書冩之 撿挍保己一」とあり|横刷毛目表紙を使用|朱点, 朱引, 朱墨筆書き入れあり|付箋あり|蔵書印主信濃須坂藩主堀直格の命によって編集された古記録|他の原本は関東大震災により焼失|極札に「桂壽」(6), 「尚信」(53)との極書, 「武清」(44, 53), 「永海」(51), 「了伴」(52), 「了甫」(74), 「定時」(84, 88)との極印あり|印記: 「花廼家文庫」, 「墨阪十一代主寫藏記」(堀直格(1806-1880)), 「東京大學法理文學部書庫所藏」, 「閲覧室用 FOR USE IN THE READING ROOM」|虫損あり</t>
+          <t>鈔本|書名は卷下の巻頭による|大尾の書名: 法蕐集驗記|後付題簽の書名: 法花經集驗記|箱の書名: 法華驗記|卷下の内題下に「并序沙門寂撰」とあり|奥書に「護持僧(花押)夲之」とあり|巻末識語に「嘉應二年庚寅二月十八日傳得之釈子有慶在判」, 「十帋半」とあり|卷上: 諷誦第1. 卷下: 轉讀第2, 書寫第3, 聽聞第4|巻子本|訓点付|卷上の巻頭を欠損|原十紙半を1軸に合綴|朱筆書き入れあり|破損, 虫損あり (裏打ち補修あり)</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -4696,12 +4696,12 @@
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/70ac8e25-6d33-9123-6fb2-0339224b41cc.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/ec4bceb1-0ab9-74c7-0dc7-f90d0a98a66e.json</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>70ac8e25-6d33-9123-6fb2-0339224b41cc</t>
+          <t>ec4bceb1-0ab9-74c7-0dc7-f90d0a98a66e</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -4711,7 +4711,7 @@
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/70ac8e25-6d33-9123-6fb2-0339224b41cc</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/ec4bceb1-0ab9-74c7-0dc7-f90d0a98a66e</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
@@ -4721,12 +4721,12 @@
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/3d36b605983eef3eb9e60d5e9f2d3016a497dd98.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/d1c457097d78f2d8a4b38eebd630ef233026cc5e.jpg</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296206</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296183</t>
         </is>
       </c>
       <c r="W35" t="inlineStr">
@@ -4749,7 +4749,7 @@
       <c r="AB35" t="inlineStr"/>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/70ac8e25-6d33-9123-6fb2-0339224b41cc/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/ec4bceb1-0ab9-74c7-0dc7-f90d0a98a66e/manifest</t>
         </is>
       </c>
       <c r="AD35" t="inlineStr"/>
@@ -4757,40 +4757,36 @@
       <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="inlineStr"/>
       <c r="AH35" t="n">
-        <v>72</v>
+        <v>19</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [7]</t>
+          <t>道成寺</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>A00:6257</t>
+          <t>A00:4276</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>レキダイ ザンケツ ニッキ</t>
+          <t>ドウジョウジ</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>黒川 春村</t>
-        </is>
-      </c>
+      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>[書写者不明]</t>
+          <t>[製作者不明]</t>
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr">
         <is>
-          <t>[安政5 (1858)]</t>
+          <t>天明2 [1782] 識語</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -4802,7 +4798,7 @@
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
-          <t>写本|責任表示及び書写年は『日本古典籍総合目録データベース』による|内容: 6: 光明院御記, 後光嚴院御記, 後小松院宸記, 天聴集. 28: 参議藤定長卿記 : 稱山丞記. 37: 定高卿記, 晴御会部類記, 家光卿御記, 權中納言平範輔卿記. 38: 左大史小槻季継記, 後堀川安貞二年放生會(実基公記), 石清水八幡宮, 弁官拝賀次第. 39: 大外記師光記, 資季卿記, 荒凉記, 忠高卿記. 40: 冷泉公相公記, 勝延法眼記 : 東寺大行事, 後中記 : 小路中納言資頼卿記葉室. 41: 中光記, 師兼記, 陽龍記. 42: 大宮司長則記, 口筆 : 實經, 顕朝卿記, 鴨御幸記. 43: 寳治二年記, 深心院關白記, 藤公親記, 照念院関白兼平公記. 44: 頼親記, 亀山殿行幸記 : 雅言卿記, 兼基公記. 45: 大嘗會御禊節下次第, 建治三年丁丑日記 : 三善康有, 建治四年正月廿一日 : 徳大寺大相國公孝記, 冬定卿記, 左大史小槻兼文記|内容: 46: 經任卿記, 前豊前守藤憲説記, 實兼公記. 47: 継塵記抄出. 48: 管見記, 公衡公記, 大外記師顕記, 大外記中原師淳記. 49: 真光院禪助僧正記, 吉田内府卿記. 50: 定清記, 叅議雅俊卿記, 太政大臣(公守公)御上表雜事, 仙洞御灌頂日記, 正安二年八月十一日於仙洞被始行熾盛光法, 正安三年御譲位記. 51: 實躬卿記. 52: 公茂公記, 冬平公記, 隆長卿記. 53: 忠教公記, 官記, 正三位長基卿記, 北面秀長記, 大外記中原師右記. 54: 文保元年, 日野中納言資朝卿記, 洞院大納言公敏卿記. 55: 隆蔭卿記, 文保三年記, 尹大納言師賢卿記, 革命記, 立倚子記, 萬里小路中納言藤藤房卿記|内容: 56: 資名卿記, 公秀公記, 一條家記装束抄出, 頼定卿記. 63: 松亞記, 日野大納言時光卿記, 後八條内府實継公記. 74: 成恩寺関白記. 78: 山科家礼記. 82: 諒闇記 : 後成恩寺殿, 宗典僧正記, 綱光公記, 贈従二位宗賢卿記, 義政公記. 84: 長禄二年戊寅正月, 見聞雜記. 87: 言國卿記. 88: 長興宿祢記, 元長卿記, 兼顕卿記, 小槻晴冨記|28末の原奥書に「右山丞記依 仰挍合書冩/享和二年四月 日撿挍保己一」とあり|50「正安二年八月十一日於仙洞被始行熾盛光法」末の原奥書に「文化十五年春二月以南山法曼院藏夲書冩之 撿挍保己一」とあり|横刷毛目表紙を使用|朱点, 朱引, 朱墨筆書き入れあり|付箋あり|蔵書印主信濃須坂藩主堀直格の命によって編集された古記録|他の原本は関東大震災により焼失|極札に「桂壽」(6), 「尚信」(53)との極書, 「武清」(44, 53), 「永海」(51), 「了伴」(52), 「了甫」(74), 「定時」(84, 88)との極印あり|印記: 「花廼家文庫」, 「墨阪十一代主寫藏記」(堀直格(1806-1880)), 「東京大學法理文學部書庫所藏」, 「閲覧室用 FOR USE IN THE READING ROOM」|虫損あり</t>
+          <t>書名は識語による|巻末識語に「道成寺建立年号大長五年三月吉日以後于二百三拾年去テ延長六戊子暦八月十日鐘巻也」, 「時天明二壬寅十月 尚良書之」とあり|絵巻|紙本著色|彩色あり|本紙: 855×28cm|界高: 25.8cm|軸物|軸頭欠損あり|印記: 「尚良印」|破損あり (裏打ち補修あり)</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -4818,12 +4814,12 @@
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/87cadcc3-3c6c-1f0e-a10f-d8c8b16b34e3.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/79185d0c-7fa3-2efd-863e-93927e137a23.json</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>87cadcc3-3c6c-1f0e-a10f-d8c8b16b34e3</t>
+          <t>79185d0c-7fa3-2efd-863e-93927e137a23</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -4833,7 +4829,7 @@
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/87cadcc3-3c6c-1f0e-a10f-d8c8b16b34e3</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/79185d0c-7fa3-2efd-863e-93927e137a23</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
@@ -4843,12 +4839,12 @@
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/60cd75676a83bcd5331212ff419346e6088f81e4.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/0c47939e767d716fe085cc41c86d91be28f9df1a.jpg</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296207</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296184</t>
         </is>
       </c>
       <c r="W36" t="inlineStr">
@@ -4871,7 +4867,7 @@
       <c r="AB36" t="inlineStr"/>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/87cadcc3-3c6c-1f0e-a10f-d8c8b16b34e3/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/79185d0c-7fa3-2efd-863e-93927e137a23/manifest</t>
         </is>
       </c>
       <c r="AD36" t="inlineStr"/>
@@ -4879,52 +4875,52 @@
       <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="inlineStr"/>
       <c r="AH36" t="n">
-        <v>67</v>
+        <v>34</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [8]</t>
+          <t>名家短冊 [1]</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>A00:6257</t>
+          <t>A00:4277</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>レキダイ ザンケツ ニッキ</t>
+          <t>メイカ タンザク</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>黒川 春村</t>
+          <t>慶運</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>[書写者不明]</t>
+          <t>慶運 [ほか自筆]</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
-          <t>[安政5 (1858)]</t>
+          <t>[鎌倉時代-江戸前期]</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
-          <t>写本|責任表示及び書写年は『日本古典籍総合目録データベース』による|内容: 6: 光明院御記, 後光嚴院御記, 後小松院宸記, 天聴集. 28: 参議藤定長卿記 : 稱山丞記. 37: 定高卿記, 晴御会部類記, 家光卿御記, 權中納言平範輔卿記. 38: 左大史小槻季継記, 後堀川安貞二年放生會(実基公記), 石清水八幡宮, 弁官拝賀次第. 39: 大外記師光記, 資季卿記, 荒凉記, 忠高卿記. 40: 冷泉公相公記, 勝延法眼記 : 東寺大行事, 後中記 : 小路中納言資頼卿記葉室. 41: 中光記, 師兼記, 陽龍記. 42: 大宮司長則記, 口筆 : 實經, 顕朝卿記, 鴨御幸記. 43: 寳治二年記, 深心院關白記, 藤公親記, 照念院関白兼平公記. 44: 頼親記, 亀山殿行幸記 : 雅言卿記, 兼基公記. 45: 大嘗會御禊節下次第, 建治三年丁丑日記 : 三善康有, 建治四年正月廿一日 : 徳大寺大相國公孝記, 冬定卿記, 左大史小槻兼文記|内容: 46: 經任卿記, 前豊前守藤憲説記, 實兼公記. 47: 継塵記抄出. 48: 管見記, 公衡公記, 大外記師顕記, 大外記中原師淳記. 49: 真光院禪助僧正記, 吉田内府卿記. 50: 定清記, 叅議雅俊卿記, 太政大臣(公守公)御上表雜事, 仙洞御灌頂日記, 正安二年八月十一日於仙洞被始行熾盛光法, 正安三年御譲位記. 51: 實躬卿記. 52: 公茂公記, 冬平公記, 隆長卿記. 53: 忠教公記, 官記, 正三位長基卿記, 北面秀長記, 大外記中原師右記. 54: 文保元年, 日野中納言資朝卿記, 洞院大納言公敏卿記. 55: 隆蔭卿記, 文保三年記, 尹大納言師賢卿記, 革命記, 立倚子記, 萬里小路中納言藤藤房卿記|内容: 56: 資名卿記, 公秀公記, 一條家記装束抄出, 頼定卿記. 63: 松亞記, 日野大納言時光卿記, 後八條内府實継公記. 74: 成恩寺関白記. 78: 山科家礼記. 82: 諒闇記 : 後成恩寺殿, 宗典僧正記, 綱光公記, 贈従二位宗賢卿記, 義政公記. 84: 長禄二年戊寅正月, 見聞雜記. 87: 言國卿記. 88: 長興宿祢記, 元長卿記, 兼顕卿記, 小槻晴冨記|28末の原奥書に「右山丞記依 仰挍合書冩/享和二年四月 日撿挍保己一」とあり|50「正安二年八月十一日於仙洞被始行熾盛光法」末の原奥書に「文化十五年春二月以南山法曼院藏夲書冩之 撿挍保己一」とあり|横刷毛目表紙を使用|朱点, 朱引, 朱墨筆書き入れあり|付箋あり|蔵書印主信濃須坂藩主堀直格の命によって編集された古記録|他の原本は関東大震災により焼失|極札に「桂壽」(6), 「尚信」(53)との極書, 「武清」(44, 53), 「永海」(51), 「了伴」(52), 「了甫」(74), 「定時」(84, 88)との極印あり|印記: 「花廼家文庫」, 「墨阪十一代主寫藏記」(堀直格(1806-1880)), 「東京大學法理文學部書庫所藏」, 「閲覧室用 FOR USE IN THE READING ROOM」|虫損あり</t>
+          <t>折本|書名及び巻冊次は題簽による|2の筆者: 慶運 牡丹花, 了流, 宗長, 兼載, 宗碩, 宗牧, 一竿, 正廣, 正般, 祖田, 堯憲, 宗二, 利盛, 増春, 了向, 榮弘, 梅雪, 宗栁, 等惠, 宗訊, 宗養, 乘阿, 兼如, 壽慶, 意運, 本阿彌光悦, 松花堂昭乘, 紹巴, 玄仍, 玄仲, 玄陳, 玄的, 里村玄祥, 昌叱, 昌琢, 昌俔, 昌程, 昌隱, 昌通|3の筆者: 祐守, 祐夏, 詮平, 直國, 興國, 隆國, 武光, 祐範, 宗純, 等貴,  順, 最嶽, 策彦, 幽之, 應其, 堯然, 尊道, 尊應, 尊朝, 道永, 弘覺, 良俊, 道増, 道應, 道興, 藤之, 立承, 性舜, 義俊, 空性, 尊譽, 揚, 道澄, 興意, 道晃|4の筆者: 有三, 他阿, 教, 尊雅, 應猷, 秀順, 可ト, 圓祐, 道順, 実如, 兼俊, 公助, 應祐, 公順, 空慶, 看世, 定信, 玄桂, 道三, 道春, 永喜, 豊永, 葉由, 常弘|2: 古筆切40枚, 極札43枚|3: 古筆切36枚, 極札36枚|4: 古筆切28枚, 極札20枚|毎半面古筆切2枚|原104枚短冊を3帖に合綴|印記: 「順」, 「最嶽」|極印: 「琴山」, 「栄」(古筆了栄)|折り目破損あり</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -4940,12 +4936,12 @@
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/d4dc2699-5a8e-7ad5-3160-80d5fae78074.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/1469b736-a0ee-61aa-1e00-7a2cfa949411.json</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>d4dc2699-5a8e-7ad5-3160-80d5fae78074</t>
+          <t>1469b736-a0ee-61aa-1e00-7a2cfa949411</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
@@ -4955,7 +4951,7 @@
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/d4dc2699-5a8e-7ad5-3160-80d5fae78074</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/1469b736-a0ee-61aa-1e00-7a2cfa949411</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
@@ -4965,12 +4961,12 @@
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/596a21f68644c95bd76b3f3600fb73bc78fb9124.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/7693d9aa48dbd471c84817ef0239807a5e246d64.jpg</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296208</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296185</t>
         </is>
       </c>
       <c r="W37" t="inlineStr">
@@ -4993,7 +4989,7 @@
       <c r="AB37" t="inlineStr"/>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/d4dc2699-5a8e-7ad5-3160-80d5fae78074/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/1469b736-a0ee-61aa-1e00-7a2cfa949411/manifest</t>
         </is>
       </c>
       <c r="AD37" t="inlineStr"/>
@@ -5001,52 +4997,52 @@
       <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="inlineStr"/>
       <c r="AH37" t="n">
-        <v>67</v>
+        <v>27</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [9]</t>
+          <t>名家短冊 [2]</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>A00:6257</t>
+          <t>A00:4277</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>レキダイ ザンケツ ニッキ</t>
+          <t>メイカ タンザク</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>黒川 春村</t>
+          <t>慶運</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>[書写者不明]</t>
+          <t>慶運 [ほか自筆]</t>
         </is>
       </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
-          <t>[安政5 (1858)]</t>
+          <t>[鎌倉時代-江戸前期]</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
         <is>
-          <t>写本|責任表示及び書写年は『日本古典籍総合目録データベース』による|内容: 6: 光明院御記, 後光嚴院御記, 後小松院宸記, 天聴集. 28: 参議藤定長卿記 : 稱山丞記. 37: 定高卿記, 晴御会部類記, 家光卿御記, 權中納言平範輔卿記. 38: 左大史小槻季継記, 後堀川安貞二年放生會(実基公記), 石清水八幡宮, 弁官拝賀次第. 39: 大外記師光記, 資季卿記, 荒凉記, 忠高卿記. 40: 冷泉公相公記, 勝延法眼記 : 東寺大行事, 後中記 : 小路中納言資頼卿記葉室. 41: 中光記, 師兼記, 陽龍記. 42: 大宮司長則記, 口筆 : 實經, 顕朝卿記, 鴨御幸記. 43: 寳治二年記, 深心院關白記, 藤公親記, 照念院関白兼平公記. 44: 頼親記, 亀山殿行幸記 : 雅言卿記, 兼基公記. 45: 大嘗會御禊節下次第, 建治三年丁丑日記 : 三善康有, 建治四年正月廿一日 : 徳大寺大相國公孝記, 冬定卿記, 左大史小槻兼文記|内容: 46: 經任卿記, 前豊前守藤憲説記, 實兼公記. 47: 継塵記抄出. 48: 管見記, 公衡公記, 大外記師顕記, 大外記中原師淳記. 49: 真光院禪助僧正記, 吉田内府卿記. 50: 定清記, 叅議雅俊卿記, 太政大臣(公守公)御上表雜事, 仙洞御灌頂日記, 正安二年八月十一日於仙洞被始行熾盛光法, 正安三年御譲位記. 51: 實躬卿記. 52: 公茂公記, 冬平公記, 隆長卿記. 53: 忠教公記, 官記, 正三位長基卿記, 北面秀長記, 大外記中原師右記. 54: 文保元年, 日野中納言資朝卿記, 洞院大納言公敏卿記. 55: 隆蔭卿記, 文保三年記, 尹大納言師賢卿記, 革命記, 立倚子記, 萬里小路中納言藤藤房卿記|内容: 56: 資名卿記, 公秀公記, 一條家記装束抄出, 頼定卿記. 63: 松亞記, 日野大納言時光卿記, 後八條内府實継公記. 74: 成恩寺関白記. 78: 山科家礼記. 82: 諒闇記 : 後成恩寺殿, 宗典僧正記, 綱光公記, 贈従二位宗賢卿記, 義政公記. 84: 長禄二年戊寅正月, 見聞雜記. 87: 言國卿記. 88: 長興宿祢記, 元長卿記, 兼顕卿記, 小槻晴冨記|28末の原奥書に「右山丞記依 仰挍合書冩/享和二年四月 日撿挍保己一」とあり|50「正安二年八月十一日於仙洞被始行熾盛光法」末の原奥書に「文化十五年春二月以南山法曼院藏夲書冩之 撿挍保己一」とあり|横刷毛目表紙を使用|朱点, 朱引, 朱墨筆書き入れあり|付箋あり|蔵書印主信濃須坂藩主堀直格の命によって編集された古記録|他の原本は関東大震災により焼失|極札に「桂壽」(6), 「尚信」(53)との極書, 「武清」(44, 53), 「永海」(51), 「了伴」(52), 「了甫」(74), 「定時」(84, 88)との極印あり|印記: 「花廼家文庫」, 「墨阪十一代主寫藏記」(堀直格(1806-1880)), 「東京大學法理文學部書庫所藏」, 「閲覧室用 FOR USE IN THE READING ROOM」|虫損あり</t>
+          <t>折本|書名及び巻冊次は題簽による|2の筆者: 慶運 牡丹花, 了流, 宗長, 兼載, 宗碩, 宗牧, 一竿, 正廣, 正般, 祖田, 堯憲, 宗二, 利盛, 増春, 了向, 榮弘, 梅雪, 宗栁, 等惠, 宗訊, 宗養, 乘阿, 兼如, 壽慶, 意運, 本阿彌光悦, 松花堂昭乘, 紹巴, 玄仍, 玄仲, 玄陳, 玄的, 里村玄祥, 昌叱, 昌琢, 昌俔, 昌程, 昌隱, 昌通|3の筆者: 祐守, 祐夏, 詮平, 直國, 興國, 隆國, 武光, 祐範, 宗純, 等貴,  順, 最嶽, 策彦, 幽之, 應其, 堯然, 尊道, 尊應, 尊朝, 道永, 弘覺, 良俊, 道増, 道應, 道興, 藤之, 立承, 性舜, 義俊, 空性, 尊譽, 揚, 道澄, 興意, 道晃|4の筆者: 有三, 他阿, 教, 尊雅, 應猷, 秀順, 可ト, 圓祐, 道順, 実如, 兼俊, 公助, 應祐, 公順, 空慶, 看世, 定信, 玄桂, 道三, 道春, 永喜, 豊永, 葉由, 常弘|2: 古筆切40枚, 極札43枚|3: 古筆切36枚, 極札36枚|4: 古筆切28枚, 極札20枚|毎半面古筆切2枚|原104枚短冊を3帖に合綴|印記: 「順」, 「最嶽」|極印: 「琴山」, 「栄」(古筆了栄)|折り目破損あり</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -5062,12 +5058,12 @@
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/a5e4d339-47a5-92a8-3fb3-15464db0a1f8.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/53041b9e-294f-71af-3d1a-e305956f5560.json</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>a5e4d339-47a5-92a8-3fb3-15464db0a1f8</t>
+          <t>53041b9e-294f-71af-3d1a-e305956f5560</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
@@ -5077,7 +5073,7 @@
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/a5e4d339-47a5-92a8-3fb3-15464db0a1f8</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/53041b9e-294f-71af-3d1a-e305956f5560</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
@@ -5087,12 +5083,12 @@
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/965ce572fe0c064509727c2dbba58751771f36b4.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/11759cf221ad40925619344bacc4027d06e015ce.jpg</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296209</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296186</t>
         </is>
       </c>
       <c r="W38" t="inlineStr">
@@ -5115,7 +5111,7 @@
       <c r="AB38" t="inlineStr"/>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/a5e4d339-47a5-92a8-3fb3-15464db0a1f8/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/53041b9e-294f-71af-3d1a-e305956f5560/manifest</t>
         </is>
       </c>
       <c r="AD38" t="inlineStr"/>
@@ -5123,52 +5119,52 @@
       <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="inlineStr"/>
       <c r="AH38" t="n">
-        <v>64</v>
+        <v>24</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [10]</t>
+          <t>名家短冊 [3]</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>A00:6257</t>
+          <t>A00:4277</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>レキダイ ザンケツ ニッキ</t>
+          <t>メイカ タンザク</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>黒川 春村</t>
+          <t>慶運</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>[書写者不明]</t>
+          <t>慶運 [ほか自筆]</t>
         </is>
       </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
-          <t>[安政5 (1858)]</t>
+          <t>[鎌倉時代-江戸前期]</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
         <is>
-          <t>写本|責任表示及び書写年は『日本古典籍総合目録データベース』による|内容: 6: 光明院御記, 後光嚴院御記, 後小松院宸記, 天聴集. 28: 参議藤定長卿記 : 稱山丞記. 37: 定高卿記, 晴御会部類記, 家光卿御記, 權中納言平範輔卿記. 38: 左大史小槻季継記, 後堀川安貞二年放生會(実基公記), 石清水八幡宮, 弁官拝賀次第. 39: 大外記師光記, 資季卿記, 荒凉記, 忠高卿記. 40: 冷泉公相公記, 勝延法眼記 : 東寺大行事, 後中記 : 小路中納言資頼卿記葉室. 41: 中光記, 師兼記, 陽龍記. 42: 大宮司長則記, 口筆 : 實經, 顕朝卿記, 鴨御幸記. 43: 寳治二年記, 深心院關白記, 藤公親記, 照念院関白兼平公記. 44: 頼親記, 亀山殿行幸記 : 雅言卿記, 兼基公記. 45: 大嘗會御禊節下次第, 建治三年丁丑日記 : 三善康有, 建治四年正月廿一日 : 徳大寺大相國公孝記, 冬定卿記, 左大史小槻兼文記|内容: 46: 經任卿記, 前豊前守藤憲説記, 實兼公記. 47: 継塵記抄出. 48: 管見記, 公衡公記, 大外記師顕記, 大外記中原師淳記. 49: 真光院禪助僧正記, 吉田内府卿記. 50: 定清記, 叅議雅俊卿記, 太政大臣(公守公)御上表雜事, 仙洞御灌頂日記, 正安二年八月十一日於仙洞被始行熾盛光法, 正安三年御譲位記. 51: 實躬卿記. 52: 公茂公記, 冬平公記, 隆長卿記. 53: 忠教公記, 官記, 正三位長基卿記, 北面秀長記, 大外記中原師右記. 54: 文保元年, 日野中納言資朝卿記, 洞院大納言公敏卿記. 55: 隆蔭卿記, 文保三年記, 尹大納言師賢卿記, 革命記, 立倚子記, 萬里小路中納言藤藤房卿記|内容: 56: 資名卿記, 公秀公記, 一條家記装束抄出, 頼定卿記. 63: 松亞記, 日野大納言時光卿記, 後八條内府實継公記. 74: 成恩寺関白記. 78: 山科家礼記. 82: 諒闇記 : 後成恩寺殿, 宗典僧正記, 綱光公記, 贈従二位宗賢卿記, 義政公記. 84: 長禄二年戊寅正月, 見聞雜記. 87: 言國卿記. 88: 長興宿祢記, 元長卿記, 兼顕卿記, 小槻晴冨記|28末の原奥書に「右山丞記依 仰挍合書冩/享和二年四月 日撿挍保己一」とあり|50「正安二年八月十一日於仙洞被始行熾盛光法」末の原奥書に「文化十五年春二月以南山法曼院藏夲書冩之 撿挍保己一」とあり|横刷毛目表紙を使用|朱点, 朱引, 朱墨筆書き入れあり|付箋あり|蔵書印主信濃須坂藩主堀直格の命によって編集された古記録|他の原本は関東大震災により焼失|極札に「桂壽」(6), 「尚信」(53)との極書, 「武清」(44, 53), 「永海」(51), 「了伴」(52), 「了甫」(74), 「定時」(84, 88)との極印あり|印記: 「花廼家文庫」, 「墨阪十一代主寫藏記」(堀直格(1806-1880)), 「東京大學法理文學部書庫所藏」, 「閲覧室用 FOR USE IN THE READING ROOM」|虫損あり</t>
+          <t>折本|書名及び巻冊次は題簽による|2の筆者: 慶運 牡丹花, 了流, 宗長, 兼載, 宗碩, 宗牧, 一竿, 正廣, 正般, 祖田, 堯憲, 宗二, 利盛, 増春, 了向, 榮弘, 梅雪, 宗栁, 等惠, 宗訊, 宗養, 乘阿, 兼如, 壽慶, 意運, 本阿彌光悦, 松花堂昭乘, 紹巴, 玄仍, 玄仲, 玄陳, 玄的, 里村玄祥, 昌叱, 昌琢, 昌俔, 昌程, 昌隱, 昌通|3の筆者: 祐守, 祐夏, 詮平, 直國, 興國, 隆國, 武光, 祐範, 宗純, 等貴,  順, 最嶽, 策彦, 幽之, 應其, 堯然, 尊道, 尊應, 尊朝, 道永, 弘覺, 良俊, 道増, 道應, 道興, 藤之, 立承, 性舜, 義俊, 空性, 尊譽, 揚, 道澄, 興意, 道晃|4の筆者: 有三, 他阿, 教, 尊雅, 應猷, 秀順, 可ト, 圓祐, 道順, 実如, 兼俊, 公助, 應祐, 公順, 空慶, 看世, 定信, 玄桂, 道三, 道春, 永喜, 豊永, 葉由, 常弘|2: 古筆切40枚, 極札43枚|3: 古筆切36枚, 極札36枚|4: 古筆切28枚, 極札20枚|毎半面古筆切2枚|原104枚短冊を3帖に合綴|印記: 「順」, 「最嶽」|極印: 「琴山」, 「栄」(古筆了栄)|折り目破損あり</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -5184,12 +5180,12 @@
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/941cae96-2884-09d1-316d-978da0fc83f5.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/3d4ceb9b-9516-779a-7ced-f893e9d93b4e.json</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>941cae96-2884-09d1-316d-978da0fc83f5</t>
+          <t>3d4ceb9b-9516-779a-7ced-f893e9d93b4e</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
@@ -5199,7 +5195,7 @@
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/941cae96-2884-09d1-316d-978da0fc83f5</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/3d4ceb9b-9516-779a-7ced-f893e9d93b4e</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
@@ -5209,12 +5205,12 @@
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/9b2119b5a8cb266e4d44bebff61cd8b5383a810e.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/8fd1defea23c7c93fc4d908835c1fea38040580e.jpg</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296210</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296187</t>
         </is>
       </c>
       <c r="W39" t="inlineStr">
@@ -5237,7 +5233,7 @@
       <c r="AB39" t="inlineStr"/>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/941cae96-2884-09d1-316d-978da0fc83f5/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/3d4ceb9b-9516-779a-7ced-f893e9d93b4e/manifest</t>
         </is>
       </c>
       <c r="AD39" t="inlineStr"/>
@@ -5245,40 +5241,40 @@
       <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="inlineStr"/>
       <c r="AH39" t="n">
-        <v>70</v>
+        <v>24</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [11]</t>
+          <t>御成敗式目絵鈔</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>A00:6257</t>
+          <t>A00:4737</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>レキダイ ザンケツ ニッキ</t>
+          <t>ゴセイバイ シキモク エショウ</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>黒川 春村</t>
+          <t>岡本 竹籔</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>[書写者不明]</t>
+          <t>岡夲竹籔 : 松川半山 [書]</t>
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
-          <t>[安政5 (1858)]</t>
+          <t>[幕末期]</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -5290,7 +5286,7 @@
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
-          <t>写本|責任表示及び書写年は『日本古典籍総合目録データベース』による|内容: 6: 光明院御記, 後光嚴院御記, 後小松院宸記, 天聴集. 28: 参議藤定長卿記 : 稱山丞記. 37: 定高卿記, 晴御会部類記, 家光卿御記, 權中納言平範輔卿記. 38: 左大史小槻季継記, 後堀川安貞二年放生會(実基公記), 石清水八幡宮, 弁官拝賀次第. 39: 大外記師光記, 資季卿記, 荒凉記, 忠高卿記. 40: 冷泉公相公記, 勝延法眼記 : 東寺大行事, 後中記 : 小路中納言資頼卿記葉室. 41: 中光記, 師兼記, 陽龍記. 42: 大宮司長則記, 口筆 : 實經, 顕朝卿記, 鴨御幸記. 43: 寳治二年記, 深心院關白記, 藤公親記, 照念院関白兼平公記. 44: 頼親記, 亀山殿行幸記 : 雅言卿記, 兼基公記. 45: 大嘗會御禊節下次第, 建治三年丁丑日記 : 三善康有, 建治四年正月廿一日 : 徳大寺大相國公孝記, 冬定卿記, 左大史小槻兼文記|内容: 46: 經任卿記, 前豊前守藤憲説記, 實兼公記. 47: 継塵記抄出. 48: 管見記, 公衡公記, 大外記師顕記, 大外記中原師淳記. 49: 真光院禪助僧正記, 吉田内府卿記. 50: 定清記, 叅議雅俊卿記, 太政大臣(公守公)御上表雜事, 仙洞御灌頂日記, 正安二年八月十一日於仙洞被始行熾盛光法, 正安三年御譲位記. 51: 實躬卿記. 52: 公茂公記, 冬平公記, 隆長卿記. 53: 忠教公記, 官記, 正三位長基卿記, 北面秀長記, 大外記中原師右記. 54: 文保元年, 日野中納言資朝卿記, 洞院大納言公敏卿記. 55: 隆蔭卿記, 文保三年記, 尹大納言師賢卿記, 革命記, 立倚子記, 萬里小路中納言藤藤房卿記|内容: 56: 資名卿記, 公秀公記, 一條家記装束抄出, 頼定卿記. 63: 松亞記, 日野大納言時光卿記, 後八條内府實継公記. 74: 成恩寺関白記. 78: 山科家礼記. 82: 諒闇記 : 後成恩寺殿, 宗典僧正記, 綱光公記, 贈従二位宗賢卿記, 義政公記. 84: 長禄二年戊寅正月, 見聞雜記. 87: 言國卿記. 88: 長興宿祢記, 元長卿記, 兼顕卿記, 小槻晴冨記|28末の原奥書に「右山丞記依 仰挍合書冩/享和二年四月 日撿挍保己一」とあり|50「正安二年八月十一日於仙洞被始行熾盛光法」末の原奥書に「文化十五年春二月以南山法曼院藏夲書冩之 撿挍保己一」とあり|横刷毛目表紙を使用|朱点, 朱引, 朱墨筆書き入れあり|付箋あり|蔵書印主信濃須坂藩主堀直格の命によって編集された古記録|他の原本は関東大震災により焼失|極札に「桂壽」(6), 「尚信」(53)との極書, 「武清」(44, 53), 「永海」(51), 「了伴」(52), 「了甫」(74), 「定時」(84, 88)との極印あり|印記: 「花廼家文庫」, 「墨阪十一代主寫藏記」(堀直格(1806-1880)), 「東京大學法理文學部書庫所藏」, 「閲覧室用 FOR USE IN THE READING ROOM」|虫損あり</t>
+          <t>写本|序首の書名: 御成敗式目繪鈔|版心の書名: 式目繪鈔|題簽に「板下本」とあり|巻末に「筆工 岡夲竹籔/画工 松川半山」とあり(「岡本」, 「憲道」, 「義卿」, 「翠宋堂長」との落款朱印あり)|巻末広告に「山田賞月堂先生筆 無雙用文章大成 全一冊」とあり|四周単辺有界2段5行, 内匡廓: 22.3×16.4cm, 白口無魚尾|頭書あり|付訓あり</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -5306,12 +5302,12 @@
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/b6a83876-30df-48c8-9c3f-3a68e8429d62.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/463ab967-60a4-9ff1-3ef2-d2dee79b5315.json</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>b6a83876-30df-48c8-9c3f-3a68e8429d62</t>
+          <t>463ab967-60a4-9ff1-3ef2-d2dee79b5315</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
@@ -5321,7 +5317,7 @@
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/b6a83876-30df-48c8-9c3f-3a68e8429d62</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/463ab967-60a4-9ff1-3ef2-d2dee79b5315</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
@@ -5331,12 +5327,12 @@
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/7f6bf7c4b28ea807212c7ead3da50d50601c8ed1.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/e0977d9ba261ea59386ce9f5104a412a5dccaf3f.jpg</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296211</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296188</t>
         </is>
       </c>
       <c r="W40" t="inlineStr">
@@ -5359,7 +5355,7 @@
       <c r="AB40" t="inlineStr"/>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/b6a83876-30df-48c8-9c3f-3a68e8429d62/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/463ab967-60a4-9ff1-3ef2-d2dee79b5315/manifest</t>
         </is>
       </c>
       <c r="AD40" t="inlineStr"/>
@@ -5367,40 +5363,40 @@
       <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="inlineStr"/>
       <c r="AH40" t="n">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [12]</t>
+          <t>金界入壇作法</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>A00:6257</t>
+          <t>A00:5975</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>レキダイ ザンケツ ニッキ</t>
+          <t>コンカイ ニュウダン サホウ</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>黒川 春村</t>
+          <t>良円</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>[書写者不明]</t>
+          <t>良円 [写]</t>
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
-          <t>[安政5 (1858)]</t>
+          <t>寛元元 [1243] 奥書</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -5412,7 +5408,7 @@
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
-          <t>写本|責任表示及び書写年は『日本古典籍総合目録データベース』による|内容: 6: 光明院御記, 後光嚴院御記, 後小松院宸記, 天聴集. 28: 参議藤定長卿記 : 稱山丞記. 37: 定高卿記, 晴御会部類記, 家光卿御記, 權中納言平範輔卿記. 38: 左大史小槻季継記, 後堀川安貞二年放生會(実基公記), 石清水八幡宮, 弁官拝賀次第. 39: 大外記師光記, 資季卿記, 荒凉記, 忠高卿記. 40: 冷泉公相公記, 勝延法眼記 : 東寺大行事, 後中記 : 小路中納言資頼卿記葉室. 41: 中光記, 師兼記, 陽龍記. 42: 大宮司長則記, 口筆 : 實經, 顕朝卿記, 鴨御幸記. 43: 寳治二年記, 深心院關白記, 藤公親記, 照念院関白兼平公記. 44: 頼親記, 亀山殿行幸記 : 雅言卿記, 兼基公記. 45: 大嘗會御禊節下次第, 建治三年丁丑日記 : 三善康有, 建治四年正月廿一日 : 徳大寺大相國公孝記, 冬定卿記, 左大史小槻兼文記|内容: 46: 經任卿記, 前豊前守藤憲説記, 實兼公記. 47: 継塵記抄出. 48: 管見記, 公衡公記, 大外記師顕記, 大外記中原師淳記. 49: 真光院禪助僧正記, 吉田内府卿記. 50: 定清記, 叅議雅俊卿記, 太政大臣(公守公)御上表雜事, 仙洞御灌頂日記, 正安二年八月十一日於仙洞被始行熾盛光法, 正安三年御譲位記. 51: 實躬卿記. 52: 公茂公記, 冬平公記, 隆長卿記. 53: 忠教公記, 官記, 正三位長基卿記, 北面秀長記, 大外記中原師右記. 54: 文保元年, 日野中納言資朝卿記, 洞院大納言公敏卿記. 55: 隆蔭卿記, 文保三年記, 尹大納言師賢卿記, 革命記, 立倚子記, 萬里小路中納言藤藤房卿記|内容: 56: 資名卿記, 公秀公記, 一條家記装束抄出, 頼定卿記. 63: 松亞記, 日野大納言時光卿記, 後八條内府實継公記. 74: 成恩寺関白記. 78: 山科家礼記. 82: 諒闇記 : 後成恩寺殿, 宗典僧正記, 綱光公記, 贈従二位宗賢卿記, 義政公記. 84: 長禄二年戊寅正月, 見聞雜記. 87: 言國卿記. 88: 長興宿祢記, 元長卿記, 兼顕卿記, 小槻晴冨記|28末の原奥書に「右山丞記依 仰挍合書冩/享和二年四月 日撿挍保己一」とあり|50「正安二年八月十一日於仙洞被始行熾盛光法」末の原奥書に「文化十五年春二月以南山法曼院藏夲書冩之 撿挍保己一」とあり|横刷毛目表紙を使用|朱点, 朱引, 朱墨筆書き入れあり|付箋あり|蔵書印主信濃須坂藩主堀直格の命によって編集された古記録|他の原本は関東大震災により焼失|極札に「桂壽」(6), 「尚信」(53)との極書, 「武清」(44, 53), 「永海」(51), 「了伴」(52), 「了甫」(74), 「定時」(84, 88)との極印あり|印記: 「花廼家文庫」, 「墨阪十一代主寫藏記」(堀直格(1806-1880)), 「東京大學法理文學部書庫所藏」, 「閲覧室用 FOR USE IN THE READING ROOM」|虫損あり</t>
+          <t>写本|奥書に「寛元々年五月七日以先師法印御夲於常住護国院房以他筆書冩校點了良円」とあり|送り仮名, 返点あり|淡墨界の料紙を使用(界匡廓: 23.7×2.5cm)|貼紙あり|巻子本|箱入り|破損, 虫損あり (裏打ち補修あり)</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -5428,12 +5424,12 @@
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/d199046f-6bd4-6ca0-a0bf-c29ad3c19949.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/ff6e2dd7-8128-3264-2081-15ad4e41857e.json</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>d199046f-6bd4-6ca0-a0bf-c29ad3c19949</t>
+          <t>ff6e2dd7-8128-3264-2081-15ad4e41857e</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
@@ -5443,7 +5439,7 @@
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/d199046f-6bd4-6ca0-a0bf-c29ad3c19949</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/ff6e2dd7-8128-3264-2081-15ad4e41857e</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
@@ -5453,12 +5449,12 @@
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/4cbd0825007ec7d3c89014f55d3b6825a8214769.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/7e2372f45914ea75c8d903fc80f309f16238b39f.jpg</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296212</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296189</t>
         </is>
       </c>
       <c r="W41" t="inlineStr">
@@ -5481,7 +5477,7 @@
       <c r="AB41" t="inlineStr"/>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/d199046f-6bd4-6ca0-a0bf-c29ad3c19949/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/ff6e2dd7-8128-3264-2081-15ad4e41857e/manifest</t>
         </is>
       </c>
       <c r="AD41" t="inlineStr"/>
@@ -5489,52 +5485,52 @@
       <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="inlineStr"/>
       <c r="AH41" t="n">
-        <v>77</v>
+        <v>39</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [13]</t>
+          <t>玉蘂 [1]</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>A00:6257</t>
+          <t>A00:6067</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>レキダイ ザンケツ ニッキ</t>
+          <t>ギョクズイ</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>黒川 春村</t>
+          <t>藤原 道家</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>[書写者不明]</t>
+          <t>野宮定基 : 久世通夏 [ほか写]</t>
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr">
         <is>
-          <t>[安政5 (1858)]</t>
+          <t>元禄12 [1699]-宝永3 [1706] 奥書</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
-          <t>写本|責任表示及び書写年は『日本古典籍総合目録データベース』による|内容: 6: 光明院御記, 後光嚴院御記, 後小松院宸記, 天聴集. 28: 参議藤定長卿記 : 稱山丞記. 37: 定高卿記, 晴御会部類記, 家光卿御記, 權中納言平範輔卿記. 38: 左大史小槻季継記, 後堀川安貞二年放生會(実基公記), 石清水八幡宮, 弁官拝賀次第. 39: 大外記師光記, 資季卿記, 荒凉記, 忠高卿記. 40: 冷泉公相公記, 勝延法眼記 : 東寺大行事, 後中記 : 小路中納言資頼卿記葉室. 41: 中光記, 師兼記, 陽龍記. 42: 大宮司長則記, 口筆 : 實經, 顕朝卿記, 鴨御幸記. 43: 寳治二年記, 深心院關白記, 藤公親記, 照念院関白兼平公記. 44: 頼親記, 亀山殿行幸記 : 雅言卿記, 兼基公記. 45: 大嘗會御禊節下次第, 建治三年丁丑日記 : 三善康有, 建治四年正月廿一日 : 徳大寺大相國公孝記, 冬定卿記, 左大史小槻兼文記|内容: 46: 經任卿記, 前豊前守藤憲説記, 實兼公記. 47: 継塵記抄出. 48: 管見記, 公衡公記, 大外記師顕記, 大外記中原師淳記. 49: 真光院禪助僧正記, 吉田内府卿記. 50: 定清記, 叅議雅俊卿記, 太政大臣(公守公)御上表雜事, 仙洞御灌頂日記, 正安二年八月十一日於仙洞被始行熾盛光法, 正安三年御譲位記. 51: 實躬卿記. 52: 公茂公記, 冬平公記, 隆長卿記. 53: 忠教公記, 官記, 正三位長基卿記, 北面秀長記, 大外記中原師右記. 54: 文保元年, 日野中納言資朝卿記, 洞院大納言公敏卿記. 55: 隆蔭卿記, 文保三年記, 尹大納言師賢卿記, 革命記, 立倚子記, 萬里小路中納言藤藤房卿記|内容: 56: 資名卿記, 公秀公記, 一條家記装束抄出, 頼定卿記. 63: 松亞記, 日野大納言時光卿記, 後八條内府實継公記. 74: 成恩寺関白記. 78: 山科家礼記. 82: 諒闇記 : 後成恩寺殿, 宗典僧正記, 綱光公記, 贈従二位宗賢卿記, 義政公記. 84: 長禄二年戊寅正月, 見聞雜記. 87: 言國卿記. 88: 長興宿祢記, 元長卿記, 兼顕卿記, 小槻晴冨記|28末の原奥書に「右山丞記依 仰挍合書冩/享和二年四月 日撿挍保己一」とあり|50「正安二年八月十一日於仙洞被始行熾盛光法」末の原奥書に「文化十五年春二月以南山法曼院藏夲書冩之 撿挍保己一」とあり|横刷毛目表紙を使用|朱点, 朱引, 朱墨筆書き入れあり|付箋あり|蔵書印主信濃須坂藩主堀直格の命によって編集された古記録|他の原本は関東大震災により焼失|極札に「桂壽」(6), 「尚信」(53)との極書, 「武清」(44, 53), 「永海」(51), 「了伴」(52), 「了甫」(74), 「定時」(84, 88)との極印あり|印記: 「花廼家文庫」, 「墨阪十一代主寫藏記」(堀直格(1806-1880)), 「東京大學法理文學部書庫所藏」, 「閲覧室用 FOR USE IN THE READING ROOM」|虫損あり</t>
+          <t>写本|書名及び巻冊次は表紙による|奥中の書名: 光明峯寺禅閤道家公記, 峯禅閤記, 峯摂政記, 峯入道摂政記|承元4年の原奥書に「右即位記一卷者光明峯寺禅閤自筆正記也以件本左令吾基春卿透以写之云々加挍正之 ... 永正七年夷則上浣 從一位(花押)」とあり|奥書に「右以或人夲自常州到来令書写之彼夲端書云此冊上下卷 ... 元禄第十二暦仲夏中旬 羽林左衞中郎将藤原定基丗一才」(承元3), 「右光明峯寺禅閤道家公承元二年三月五六月八月四年二三月九月十十一十二月記は借請或人之夲自常州邊来書写之加一挍了/于時元禄第十二端午節也 左中郎将藤原定基丗才」(承元4), 「右玉蘂建暦元年少弟左中将通清朝臣助筆僅加一挍原本文字不正後来得正夲可改之者也/元禄十三年九月十日 松堂閑士(花押)丗二才」(建暦元), 「右玉蘂峯禅閤記建暦二年自二月至九月一冊以或人夲自常州邊来命家僚令書写手自加挍合了/元禄十二年五月六日 左中郎将藤原定基丗一才」(建暦2年上), 「宝永二年十月一日書写畢/承久二春玉蘂以故常州牧權中納言光圀公夲謄写之于時俗務紛擾先請慈兄源亜相公所被写也今以彼夲手自馳禿筆 余識藤(花押)丗七才/同三年二月廿五日一挍了」(承久2年上), 「右峯摂政承久二年記命傭書謄冩之手自一挍了/元禄第十二嵗次著雍単閼蕤賓中旬 羽林軍左衞中郎将藤原定基丗一才」(承久2年下), 「嘉禎四年正月二月閏二月三月四月六月玉蘂先年假借故常州牧前中納言光圀夲無剋力速遂書写之功建暦元年建暦二年下承久二年上及此卷等先献慈兄亜相君写之今及数年申復彼夲謄写之 ... 宝永三年十二月念日 参議從三位行左近衞權中将藤原朝臣定基生年卅八才」(嘉禎4年)とあり|毎半葉11行注文双行|漢文体日記|拠徳川光圀本及び中院通躬鈔本謄写|朱筆書き入れあり|印記: 「定基」(野宮定基), 「野宮書印」|虫損あり (裏打ち補修あり)</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -5550,12 +5546,12 @@
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/1b5c5c7f-4892-39f9-4e5e-479a8e921be2.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/b13a7a09-88d0-62d3-44e5-379780395f17.json</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>1b5c5c7f-4892-39f9-4e5e-479a8e921be2</t>
+          <t>b13a7a09-88d0-62d3-44e5-379780395f17</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
@@ -5565,7 +5561,7 @@
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/1b5c5c7f-4892-39f9-4e5e-479a8e921be2</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/b13a7a09-88d0-62d3-44e5-379780395f17</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
@@ -5575,12 +5571,12 @@
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/95aeca9c3732100e9d926fc7a9cb98fba20b6444.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/f7ae1bd23dec8f323199a9add81e315f1a653d24.jpg</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296213</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296190</t>
         </is>
       </c>
       <c r="W42" t="inlineStr">
@@ -5603,7 +5599,7 @@
       <c r="AB42" t="inlineStr"/>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/1b5c5c7f-4892-39f9-4e5e-479a8e921be2/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/b13a7a09-88d0-62d3-44e5-379780395f17/manifest</t>
         </is>
       </c>
       <c r="AD42" t="inlineStr"/>
@@ -5611,52 +5607,52 @@
       <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="inlineStr"/>
       <c r="AH42" t="n">
-        <v>74</v>
+        <v>129</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [14]</t>
+          <t>玉蘂 [2]</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>A00:6257</t>
+          <t>A00:6067</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>レキダイ ザンケツ ニッキ</t>
+          <t>ギョクズイ</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>黒川 春村</t>
+          <t>藤原 道家</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>[書写者不明]</t>
+          <t>野宮定基 : 久世通夏 [ほか写]</t>
         </is>
       </c>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
-          <t>[安政5 (1858)]</t>
+          <t>元禄12 [1699]-宝永3 [1706] 奥書</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr">
         <is>
-          <t>写本|責任表示及び書写年は『日本古典籍総合目録データベース』による|内容: 6: 光明院御記, 後光嚴院御記, 後小松院宸記, 天聴集. 28: 参議藤定長卿記 : 稱山丞記. 37: 定高卿記, 晴御会部類記, 家光卿御記, 權中納言平範輔卿記. 38: 左大史小槻季継記, 後堀川安貞二年放生會(実基公記), 石清水八幡宮, 弁官拝賀次第. 39: 大外記師光記, 資季卿記, 荒凉記, 忠高卿記. 40: 冷泉公相公記, 勝延法眼記 : 東寺大行事, 後中記 : 小路中納言資頼卿記葉室. 41: 中光記, 師兼記, 陽龍記. 42: 大宮司長則記, 口筆 : 實經, 顕朝卿記, 鴨御幸記. 43: 寳治二年記, 深心院關白記, 藤公親記, 照念院関白兼平公記. 44: 頼親記, 亀山殿行幸記 : 雅言卿記, 兼基公記. 45: 大嘗會御禊節下次第, 建治三年丁丑日記 : 三善康有, 建治四年正月廿一日 : 徳大寺大相國公孝記, 冬定卿記, 左大史小槻兼文記|内容: 46: 經任卿記, 前豊前守藤憲説記, 實兼公記. 47: 継塵記抄出. 48: 管見記, 公衡公記, 大外記師顕記, 大外記中原師淳記. 49: 真光院禪助僧正記, 吉田内府卿記. 50: 定清記, 叅議雅俊卿記, 太政大臣(公守公)御上表雜事, 仙洞御灌頂日記, 正安二年八月十一日於仙洞被始行熾盛光法, 正安三年御譲位記. 51: 實躬卿記. 52: 公茂公記, 冬平公記, 隆長卿記. 53: 忠教公記, 官記, 正三位長基卿記, 北面秀長記, 大外記中原師右記. 54: 文保元年, 日野中納言資朝卿記, 洞院大納言公敏卿記. 55: 隆蔭卿記, 文保三年記, 尹大納言師賢卿記, 革命記, 立倚子記, 萬里小路中納言藤藤房卿記|内容: 56: 資名卿記, 公秀公記, 一條家記装束抄出, 頼定卿記. 63: 松亞記, 日野大納言時光卿記, 後八條内府實継公記. 74: 成恩寺関白記. 78: 山科家礼記. 82: 諒闇記 : 後成恩寺殿, 宗典僧正記, 綱光公記, 贈従二位宗賢卿記, 義政公記. 84: 長禄二年戊寅正月, 見聞雜記. 87: 言國卿記. 88: 長興宿祢記, 元長卿記, 兼顕卿記, 小槻晴冨記|28末の原奥書に「右山丞記依 仰挍合書冩/享和二年四月 日撿挍保己一」とあり|50「正安二年八月十一日於仙洞被始行熾盛光法」末の原奥書に「文化十五年春二月以南山法曼院藏夲書冩之 撿挍保己一」とあり|横刷毛目表紙を使用|朱点, 朱引, 朱墨筆書き入れあり|付箋あり|蔵書印主信濃須坂藩主堀直格の命によって編集された古記録|他の原本は関東大震災により焼失|極札に「桂壽」(6), 「尚信」(53)との極書, 「武清」(44, 53), 「永海」(51), 「了伴」(52), 「了甫」(74), 「定時」(84, 88)との極印あり|印記: 「花廼家文庫」, 「墨阪十一代主寫藏記」(堀直格(1806-1880)), 「東京大學法理文學部書庫所藏」, 「閲覧室用 FOR USE IN THE READING ROOM」|虫損あり</t>
+          <t>写本|書名及び巻冊次は表紙による|奥中の書名: 光明峯寺禅閤道家公記, 峯禅閤記, 峯摂政記, 峯入道摂政記|承元4年の原奥書に「右即位記一卷者光明峯寺禅閤自筆正記也以件本左令吾基春卿透以写之云々加挍正之 ... 永正七年夷則上浣 從一位(花押)」とあり|奥書に「右以或人夲自常州到来令書写之彼夲端書云此冊上下卷 ... 元禄第十二暦仲夏中旬 羽林左衞中郎将藤原定基丗一才」(承元3), 「右光明峯寺禅閤道家公承元二年三月五六月八月四年二三月九月十十一十二月記は借請或人之夲自常州邊来書写之加一挍了/于時元禄第十二端午節也 左中郎将藤原定基丗才」(承元4), 「右玉蘂建暦元年少弟左中将通清朝臣助筆僅加一挍原本文字不正後来得正夲可改之者也/元禄十三年九月十日 松堂閑士(花押)丗二才」(建暦元), 「右玉蘂峯禅閤記建暦二年自二月至九月一冊以或人夲自常州邊来命家僚令書写手自加挍合了/元禄十二年五月六日 左中郎将藤原定基丗一才」(建暦2年上), 「宝永二年十月一日書写畢/承久二春玉蘂以故常州牧權中納言光圀公夲謄写之于時俗務紛擾先請慈兄源亜相公所被写也今以彼夲手自馳禿筆 余識藤(花押)丗七才/同三年二月廿五日一挍了」(承久2年上), 「右峯摂政承久二年記命傭書謄冩之手自一挍了/元禄第十二嵗次著雍単閼蕤賓中旬 羽林軍左衞中郎将藤原定基丗一才」(承久2年下), 「嘉禎四年正月二月閏二月三月四月六月玉蘂先年假借故常州牧前中納言光圀夲無剋力速遂書写之功建暦元年建暦二年下承久二年上及此卷等先献慈兄亜相君写之今及数年申復彼夲謄写之 ... 宝永三年十二月念日 参議從三位行左近衞權中将藤原朝臣定基生年卅八才」(嘉禎4年)とあり|毎半葉11行注文双行|漢文体日記|拠徳川光圀本及び中院通躬鈔本謄写|朱筆書き入れあり|印記: 「定基」(野宮定基), 「野宮書印」|虫損あり (裏打ち補修あり)</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -5672,12 +5668,12 @@
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/a83ab18c-4d05-492c-2121-ec90971ea54a.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/20ddaef2-73cc-5ae8-949d-0bdc521924e9.json</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>a83ab18c-4d05-492c-2121-ec90971ea54a</t>
+          <t>20ddaef2-73cc-5ae8-949d-0bdc521924e9</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
@@ -5687,7 +5683,7 @@
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/a83ab18c-4d05-492c-2121-ec90971ea54a</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/20ddaef2-73cc-5ae8-949d-0bdc521924e9</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
@@ -5697,12 +5693,12 @@
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/b0fe976afebb52b245b298aabead8423fd0d1a6f.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/e2bfc2adbffcfb9eb459e7863108300f2722cdd2.jpg</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296214</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296191</t>
         </is>
       </c>
       <c r="W43" t="inlineStr">
@@ -5725,7 +5721,7 @@
       <c r="AB43" t="inlineStr"/>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/a83ab18c-4d05-492c-2121-ec90971ea54a/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/20ddaef2-73cc-5ae8-949d-0bdc521924e9/manifest</t>
         </is>
       </c>
       <c r="AD43" t="inlineStr"/>
@@ -5733,52 +5729,52 @@
       <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="inlineStr"/>
       <c r="AH43" t="n">
-        <v>59</v>
+        <v>104</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>和漢朗詠集 2巻 [2]</t>
+          <t>玉蘂 [3]</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>A00:4081</t>
+          <t>A00:6067</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>ワカン ロウエイシュウ</t>
+          <t>ギョクズイ</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>藤原 公任</t>
+          <t>藤原 道家</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>[書写者不明]</t>
+          <t>野宮定基 : 久世通夏 [ほか写]</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr">
         <is>
-          <t>[江戸前期]</t>
+          <t>元禄12 [1699]-宝永3 [1706] 奥書</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr">
         <is>
-          <t>写本|書名は目首及び題簽による|外箱の書名: 御本|責任表示は『日本古典籍総合目録データベース』による|巻上: 春, 夏, 秋, 冬. 巻下: 雜|題簽による巻冊次表示: 上, 下|毎半帖8行|漢字平仮名交じり文|鳳凰菱繋ぎ文様緞子表紙, 松葉散しに山雲の金箔見返し, 金泥下絵鳥の子紙を使用|列帖装|二重箱入り</t>
+          <t>写本|書名及び巻冊次は表紙による|奥中の書名: 光明峯寺禅閤道家公記, 峯禅閤記, 峯摂政記, 峯入道摂政記|承元4年の原奥書に「右即位記一卷者光明峯寺禅閤自筆正記也以件本左令吾基春卿透以写之云々加挍正之 ... 永正七年夷則上浣 從一位(花押)」とあり|奥書に「右以或人夲自常州到来令書写之彼夲端書云此冊上下卷 ... 元禄第十二暦仲夏中旬 羽林左衞中郎将藤原定基丗一才」(承元3), 「右光明峯寺禅閤道家公承元二年三月五六月八月四年二三月九月十十一十二月記は借請或人之夲自常州邊来書写之加一挍了/于時元禄第十二端午節也 左中郎将藤原定基丗才」(承元4), 「右玉蘂建暦元年少弟左中将通清朝臣助筆僅加一挍原本文字不正後来得正夲可改之者也/元禄十三年九月十日 松堂閑士(花押)丗二才」(建暦元), 「右玉蘂峯禅閤記建暦二年自二月至九月一冊以或人夲自常州邊来命家僚令書写手自加挍合了/元禄十二年五月六日 左中郎将藤原定基丗一才」(建暦2年上), 「宝永二年十月一日書写畢/承久二春玉蘂以故常州牧權中納言光圀公夲謄写之于時俗務紛擾先請慈兄源亜相公所被写也今以彼夲手自馳禿筆 余識藤(花押)丗七才/同三年二月廿五日一挍了」(承久2年上), 「右峯摂政承久二年記命傭書謄冩之手自一挍了/元禄第十二嵗次著雍単閼蕤賓中旬 羽林軍左衞中郎将藤原定基丗一才」(承久2年下), 「嘉禎四年正月二月閏二月三月四月六月玉蘂先年假借故常州牧前中納言光圀夲無剋力速遂書写之功建暦元年建暦二年下承久二年上及此卷等先献慈兄亜相君写之今及数年申復彼夲謄写之 ... 宝永三年十二月念日 参議從三位行左近衞權中将藤原朝臣定基生年卅八才」(嘉禎4年)とあり|毎半葉11行注文双行|漢文体日記|拠徳川光圀本及び中院通躬鈔本謄写|朱筆書き入れあり|印記: 「定基」(野宮定基), 「野宮書印」|虫損あり (裏打ち補修あり)</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -5794,12 +5790,12 @@
       <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/a241b0e6-90d9-46db-1fe8-bf35f1e616c5.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/7f62eb7a-844c-22ea-196e-998226c991ea.json</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>a241b0e6-90d9-46db-1fe8-bf35f1e616c5</t>
+          <t>7f62eb7a-844c-22ea-196e-998226c991ea</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
@@ -5809,7 +5805,7 @@
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/a241b0e6-90d9-46db-1fe8-bf35f1e616c5</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/7f62eb7a-844c-22ea-196e-998226c991ea</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
@@ -5819,12 +5815,12 @@
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/f46b1242e2b77ba4f0d99feac20562f5cd3a0ee2.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/ac4d01393f2eb0586033bfface43acc61e64021e.jpg</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296167</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296192</t>
         </is>
       </c>
       <c r="W44" t="inlineStr">
@@ -5847,7 +5843,7 @@
       <c r="AB44" t="inlineStr"/>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/a241b0e6-90d9-46db-1fe8-bf35f1e616c5/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/7f62eb7a-844c-22ea-196e-998226c991ea/manifest</t>
         </is>
       </c>
       <c r="AD44" t="inlineStr"/>
@@ -5855,52 +5851,52 @@
       <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="inlineStr"/>
       <c r="AH44" t="n">
-        <v>48</v>
+        <v>77</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>つれつれ草</t>
+          <t>玉蘂 [4]</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>A00:4082</t>
+          <t>A00:6067</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>ツレズレグサ</t>
+          <t>ギョクズイ</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>吉田 兼好</t>
+          <t>藤原 道家</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>[書写者不明]</t>
+          <t>野宮定基 : 久世通夏 [ほか写]</t>
         </is>
       </c>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr">
         <is>
-          <t>[江戸前期]</t>
+          <t>元禄12 [1699]-宝永3 [1706] 奥書</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr">
         <is>
-          <t>写本|書名は題簽による|書名の繰返し部分は踊り字|外箱の書名: 御本|責任表示は『日本古典籍総合目録データベース』による|毎半帖10行|漢字平仮名交じり文|花草窠文様緞子表紙, 松葉散しに山雲の金箔見返し, 金泥下絵鳥の子紙を使用|列帖装|二重箱入り</t>
+          <t>写本|書名及び巻冊次は表紙による|奥中の書名: 光明峯寺禅閤道家公記, 峯禅閤記, 峯摂政記, 峯入道摂政記|承元4年の原奥書に「右即位記一卷者光明峯寺禅閤自筆正記也以件本左令吾基春卿透以写之云々加挍正之 ... 永正七年夷則上浣 從一位(花押)」とあり|奥書に「右以或人夲自常州到来令書写之彼夲端書云此冊上下卷 ... 元禄第十二暦仲夏中旬 羽林左衞中郎将藤原定基丗一才」(承元3), 「右光明峯寺禅閤道家公承元二年三月五六月八月四年二三月九月十十一十二月記は借請或人之夲自常州邊来書写之加一挍了/于時元禄第十二端午節也 左中郎将藤原定基丗才」(承元4), 「右玉蘂建暦元年少弟左中将通清朝臣助筆僅加一挍原本文字不正後来得正夲可改之者也/元禄十三年九月十日 松堂閑士(花押)丗二才」(建暦元), 「右玉蘂峯禅閤記建暦二年自二月至九月一冊以或人夲自常州邊来命家僚令書写手自加挍合了/元禄十二年五月六日 左中郎将藤原定基丗一才」(建暦2年上), 「宝永二年十月一日書写畢/承久二春玉蘂以故常州牧權中納言光圀公夲謄写之于時俗務紛擾先請慈兄源亜相公所被写也今以彼夲手自馳禿筆 余識藤(花押)丗七才/同三年二月廿五日一挍了」(承久2年上), 「右峯摂政承久二年記命傭書謄冩之手自一挍了/元禄第十二嵗次著雍単閼蕤賓中旬 羽林軍左衞中郎将藤原定基丗一才」(承久2年下), 「嘉禎四年正月二月閏二月三月四月六月玉蘂先年假借故常州牧前中納言光圀夲無剋力速遂書写之功建暦元年建暦二年下承久二年上及此卷等先献慈兄亜相君写之今及数年申復彼夲謄写之 ... 宝永三年十二月念日 参議從三位行左近衞權中将藤原朝臣定基生年卅八才」(嘉禎4年)とあり|毎半葉11行注文双行|漢文体日記|拠徳川光圀本及び中院通躬鈔本謄写|朱筆書き入れあり|印記: 「定基」(野宮定基), 「野宮書印」|虫損あり (裏打ち補修あり)</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -5916,12 +5912,12 @@
       <c r="O45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/d19a62f6-4729-0ee3-3ea7-08f573851a48.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/f48a78a7-0365-73cb-4e46-dd013ef92813.json</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>d19a62f6-4729-0ee3-3ea7-08f573851a48</t>
+          <t>f48a78a7-0365-73cb-4e46-dd013ef92813</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
@@ -5931,7 +5927,7 @@
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/d19a62f6-4729-0ee3-3ea7-08f573851a48</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/f48a78a7-0365-73cb-4e46-dd013ef92813</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
@@ -5941,12 +5937,12 @@
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/7966b7312c84644ee577a0390937964b1989586d.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/d9d6bd695feea8f0816bee6e991e141accf01cd8.jpg</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296168</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296193</t>
         </is>
       </c>
       <c r="W45" t="inlineStr">
@@ -5969,7 +5965,7 @@
       <c r="AB45" t="inlineStr"/>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/d19a62f6-4729-0ee3-3ea7-08f573851a48/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/f48a78a7-0365-73cb-4e46-dd013ef92813/manifest</t>
         </is>
       </c>
       <c r="AD45" t="inlineStr"/>
@@ -5977,52 +5973,52 @@
       <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="inlineStr"/>
       <c r="AH45" t="n">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>日本廿四孝 6巻 [1]</t>
+          <t>玉蘂 [5]</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>A00:4084</t>
+          <t>A00:6067</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>ヤマト ニジュウシコウ</t>
+          <t>ギョクズイ</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>浅井 了意</t>
+          <t>藤原 道家</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>[書写者不明]</t>
+          <t>野宮定基 : 久世通夏 [ほか写]</t>
         </is>
       </c>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr">
         <is>
-          <t>[江戸前期]</t>
+          <t>元禄12 [1699]-宝永3 [1706] 奥書</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr">
         <is>
-          <t>写本|書名は目首及び題簽による|内箱の書名: 大和廿四孝|外箱の書名: 御本|責任表示は『日本古典籍総合目録データベース』による|1: 第1-4. 2: 第5-8. 3: 第9-12. 4: 第13-16. 5: 第17-20. 6: 第21-24|毎半帖10行|漢字平仮名交じり文|奈良絵本|梅唐草文様緞子表紙, 松葉散しに山雲の金箔見返し, 金泥下絵鳥の子紙を使用|列帖装|竪本|二重箱入り|糸切れあり</t>
+          <t>写本|書名及び巻冊次は表紙による|奥中の書名: 光明峯寺禅閤道家公記, 峯禅閤記, 峯摂政記, 峯入道摂政記|承元4年の原奥書に「右即位記一卷者光明峯寺禅閤自筆正記也以件本左令吾基春卿透以写之云々加挍正之 ... 永正七年夷則上浣 從一位(花押)」とあり|奥書に「右以或人夲自常州到来令書写之彼夲端書云此冊上下卷 ... 元禄第十二暦仲夏中旬 羽林左衞中郎将藤原定基丗一才」(承元3), 「右光明峯寺禅閤道家公承元二年三月五六月八月四年二三月九月十十一十二月記は借請或人之夲自常州邊来書写之加一挍了/于時元禄第十二端午節也 左中郎将藤原定基丗才」(承元4), 「右玉蘂建暦元年少弟左中将通清朝臣助筆僅加一挍原本文字不正後来得正夲可改之者也/元禄十三年九月十日 松堂閑士(花押)丗二才」(建暦元), 「右玉蘂峯禅閤記建暦二年自二月至九月一冊以或人夲自常州邊来命家僚令書写手自加挍合了/元禄十二年五月六日 左中郎将藤原定基丗一才」(建暦2年上), 「宝永二年十月一日書写畢/承久二春玉蘂以故常州牧權中納言光圀公夲謄写之于時俗務紛擾先請慈兄源亜相公所被写也今以彼夲手自馳禿筆 余識藤(花押)丗七才/同三年二月廿五日一挍了」(承久2年上), 「右峯摂政承久二年記命傭書謄冩之手自一挍了/元禄第十二嵗次著雍単閼蕤賓中旬 羽林軍左衞中郎将藤原定基丗一才」(承久2年下), 「嘉禎四年正月二月閏二月三月四月六月玉蘂先年假借故常州牧前中納言光圀夲無剋力速遂書写之功建暦元年建暦二年下承久二年上及此卷等先献慈兄亜相君写之今及数年申復彼夲謄写之 ... 宝永三年十二月念日 参議從三位行左近衞權中将藤原朝臣定基生年卅八才」(嘉禎4年)とあり|毎半葉11行注文双行|漢文体日記|拠徳川光圀本及び中院通躬鈔本謄写|朱筆書き入れあり|印記: 「定基」(野宮定基), 「野宮書印」|虫損あり (裏打ち補修あり)</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -6038,12 +6034,12 @@
       <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/bf17bb0e-6d63-718e-218b-614134ee011d.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/c4ba4bb2-8d3c-7e43-4e3e-e6a6d0c2260f.json</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>bf17bb0e-6d63-718e-218b-614134ee011d</t>
+          <t>c4ba4bb2-8d3c-7e43-4e3e-e6a6d0c2260f</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
@@ -6053,7 +6049,7 @@
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/bf17bb0e-6d63-718e-218b-614134ee011d</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/c4ba4bb2-8d3c-7e43-4e3e-e6a6d0c2260f</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
@@ -6063,12 +6059,12 @@
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/2c48d85abc93bce026f680cc699c748fb0a877e2.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/58826021e366d49d150087ff3478b98548b97c4a.jpg</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296169</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296194</t>
         </is>
       </c>
       <c r="W46" t="inlineStr">
@@ -6091,7 +6087,7 @@
       <c r="AB46" t="inlineStr"/>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/bf17bb0e-6d63-718e-218b-614134ee011d/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/c4ba4bb2-8d3c-7e43-4e3e-e6a6d0c2260f/manifest</t>
         </is>
       </c>
       <c r="AD46" t="inlineStr"/>
@@ -6099,52 +6095,52 @@
       <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="inlineStr"/>
       <c r="AH46" t="n">
-        <v>47</v>
+        <v>69</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>日本廿四孝 6巻 [2]</t>
+          <t>玉蘂 [6]</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>A00:4084</t>
+          <t>A00:6067</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ヤマト ニジュウシコウ</t>
+          <t>ギョクズイ</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>浅井 了意</t>
+          <t>藤原 道家</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>[書写者不明]</t>
+          <t>野宮定基 : 久世通夏 [ほか写]</t>
         </is>
       </c>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr">
         <is>
-          <t>[江戸前期]</t>
+          <t>元禄12 [1699]-宝永3 [1706] 奥書</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr">
         <is>
-          <t>写本|書名は目首及び題簽による|内箱の書名: 大和廿四孝|外箱の書名: 御本|責任表示は『日本古典籍総合目録データベース』による|1: 第1-4. 2: 第5-8. 3: 第9-12. 4: 第13-16. 5: 第17-20. 6: 第21-24|毎半帖10行|漢字平仮名交じり文|奈良絵本|梅唐草文様緞子表紙, 松葉散しに山雲の金箔見返し, 金泥下絵鳥の子紙を使用|列帖装|竪本|二重箱入り|糸切れあり</t>
+          <t>写本|書名及び巻冊次は表紙による|奥中の書名: 光明峯寺禅閤道家公記, 峯禅閤記, 峯摂政記, 峯入道摂政記|承元4年の原奥書に「右即位記一卷者光明峯寺禅閤自筆正記也以件本左令吾基春卿透以写之云々加挍正之 ... 永正七年夷則上浣 從一位(花押)」とあり|奥書に「右以或人夲自常州到来令書写之彼夲端書云此冊上下卷 ... 元禄第十二暦仲夏中旬 羽林左衞中郎将藤原定基丗一才」(承元3), 「右光明峯寺禅閤道家公承元二年三月五六月八月四年二三月九月十十一十二月記は借請或人之夲自常州邊来書写之加一挍了/于時元禄第十二端午節也 左中郎将藤原定基丗才」(承元4), 「右玉蘂建暦元年少弟左中将通清朝臣助筆僅加一挍原本文字不正後来得正夲可改之者也/元禄十三年九月十日 松堂閑士(花押)丗二才」(建暦元), 「右玉蘂峯禅閤記建暦二年自二月至九月一冊以或人夲自常州邊来命家僚令書写手自加挍合了/元禄十二年五月六日 左中郎将藤原定基丗一才」(建暦2年上), 「宝永二年十月一日書写畢/承久二春玉蘂以故常州牧權中納言光圀公夲謄写之于時俗務紛擾先請慈兄源亜相公所被写也今以彼夲手自馳禿筆 余識藤(花押)丗七才/同三年二月廿五日一挍了」(承久2年上), 「右峯摂政承久二年記命傭書謄冩之手自一挍了/元禄第十二嵗次著雍単閼蕤賓中旬 羽林軍左衞中郎将藤原定基丗一才」(承久2年下), 「嘉禎四年正月二月閏二月三月四月六月玉蘂先年假借故常州牧前中納言光圀夲無剋力速遂書写之功建暦元年建暦二年下承久二年上及此卷等先献慈兄亜相君写之今及数年申復彼夲謄写之 ... 宝永三年十二月念日 参議從三位行左近衞權中将藤原朝臣定基生年卅八才」(嘉禎4年)とあり|毎半葉11行注文双行|漢文体日記|拠徳川光圀本及び中院通躬鈔本謄写|朱筆書き入れあり|印記: 「定基」(野宮定基), 「野宮書印」|虫損あり (裏打ち補修あり)</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -6160,12 +6156,12 @@
       <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/c2996e14-8070-09ae-328a-159e60d17016.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/73dc1d4b-7872-a0a3-780c-3c10d2a3758a.json</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>c2996e14-8070-09ae-328a-159e60d17016</t>
+          <t>73dc1d4b-7872-a0a3-780c-3c10d2a3758a</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
@@ -6175,7 +6171,7 @@
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/c2996e14-8070-09ae-328a-159e60d17016</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/73dc1d4b-7872-a0a3-780c-3c10d2a3758a</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
@@ -6185,12 +6181,12 @@
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/27ba12aa7661321f36193a30b8d8ffb8b32e574c.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/6724525552ca8e3c1f42cdc0f0674a54828dc026.jpg</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296170</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296195</t>
         </is>
       </c>
       <c r="W47" t="inlineStr">
@@ -6213,7 +6209,7 @@
       <c r="AB47" t="inlineStr"/>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/c2996e14-8070-09ae-328a-159e60d17016/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/73dc1d4b-7872-a0a3-780c-3c10d2a3758a/manifest</t>
         </is>
       </c>
       <c r="AD47" t="inlineStr"/>
@@ -6221,52 +6217,52 @@
       <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="inlineStr"/>
       <c r="AH47" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>日本廿四孝 6巻 [3]</t>
+          <t>玉蘂 [7]</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>A00:4084</t>
+          <t>A00:6067</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>ヤマト ニジュウシコウ</t>
+          <t>ギョクズイ</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>浅井 了意</t>
+          <t>藤原 道家</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>[書写者不明]</t>
+          <t>野宮定基 : 久世通夏 [ほか写]</t>
         </is>
       </c>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr">
         <is>
-          <t>[江戸前期]</t>
+          <t>元禄12 [1699]-宝永3 [1706] 奥書</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr">
         <is>
-          <t>写本|書名は目首及び題簽による|内箱の書名: 大和廿四孝|外箱の書名: 御本|責任表示は『日本古典籍総合目録データベース』による|1: 第1-4. 2: 第5-8. 3: 第9-12. 4: 第13-16. 5: 第17-20. 6: 第21-24|毎半帖10行|漢字平仮名交じり文|奈良絵本|梅唐草文様緞子表紙, 松葉散しに山雲の金箔見返し, 金泥下絵鳥の子紙を使用|列帖装|竪本|二重箱入り|糸切れあり</t>
+          <t>写本|書名及び巻冊次は表紙による|奥中の書名: 光明峯寺禅閤道家公記, 峯禅閤記, 峯摂政記, 峯入道摂政記|承元4年の原奥書に「右即位記一卷者光明峯寺禅閤自筆正記也以件本左令吾基春卿透以写之云々加挍正之 ... 永正七年夷則上浣 從一位(花押)」とあり|奥書に「右以或人夲自常州到来令書写之彼夲端書云此冊上下卷 ... 元禄第十二暦仲夏中旬 羽林左衞中郎将藤原定基丗一才」(承元3), 「右光明峯寺禅閤道家公承元二年三月五六月八月四年二三月九月十十一十二月記は借請或人之夲自常州邊来書写之加一挍了/于時元禄第十二端午節也 左中郎将藤原定基丗才」(承元4), 「右玉蘂建暦元年少弟左中将通清朝臣助筆僅加一挍原本文字不正後来得正夲可改之者也/元禄十三年九月十日 松堂閑士(花押)丗二才」(建暦元), 「右玉蘂峯禅閤記建暦二年自二月至九月一冊以或人夲自常州邊来命家僚令書写手自加挍合了/元禄十二年五月六日 左中郎将藤原定基丗一才」(建暦2年上), 「宝永二年十月一日書写畢/承久二春玉蘂以故常州牧權中納言光圀公夲謄写之于時俗務紛擾先請慈兄源亜相公所被写也今以彼夲手自馳禿筆 余識藤(花押)丗七才/同三年二月廿五日一挍了」(承久2年上), 「右峯摂政承久二年記命傭書謄冩之手自一挍了/元禄第十二嵗次著雍単閼蕤賓中旬 羽林軍左衞中郎将藤原定基丗一才」(承久2年下), 「嘉禎四年正月二月閏二月三月四月六月玉蘂先年假借故常州牧前中納言光圀夲無剋力速遂書写之功建暦元年建暦二年下承久二年上及此卷等先献慈兄亜相君写之今及数年申復彼夲謄写之 ... 宝永三年十二月念日 参議從三位行左近衞權中将藤原朝臣定基生年卅八才」(嘉禎4年)とあり|毎半葉11行注文双行|漢文体日記|拠徳川光圀本及び中院通躬鈔本謄写|朱筆書き入れあり|印記: 「定基」(野宮定基), 「野宮書印」|虫損あり (裏打ち補修あり)</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -6282,12 +6278,12 @@
       <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/8bf2f649-5d15-2afc-2f36-84e0ac2f513e.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/e775ea12-9867-70f2-6381-112e31478f75.json</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>8bf2f649-5d15-2afc-2f36-84e0ac2f513e</t>
+          <t>e775ea12-9867-70f2-6381-112e31478f75</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
@@ -6297,7 +6293,7 @@
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/8bf2f649-5d15-2afc-2f36-84e0ac2f513e</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/e775ea12-9867-70f2-6381-112e31478f75</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
@@ -6307,12 +6303,12 @@
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/5841d5cb8d9895d0b483a2f842afc32f67e1719b.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/08e58358a211a53638e77e5431d7fedb34bd5f72.jpg</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296171</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296196</t>
         </is>
       </c>
       <c r="W48" t="inlineStr">
@@ -6335,7 +6331,7 @@
       <c r="AB48" t="inlineStr"/>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/8bf2f649-5d15-2afc-2f36-84e0ac2f513e/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/e775ea12-9867-70f2-6381-112e31478f75/manifest</t>
         </is>
       </c>
       <c r="AD48" t="inlineStr"/>
@@ -6343,52 +6339,52 @@
       <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="inlineStr"/>
       <c r="AH48" t="n">
-        <v>47</v>
+        <v>146</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>日本廿四孝 6巻 [4]</t>
+          <t>玉蘂 [8]</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>A00:4084</t>
+          <t>A00:6067</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ヤマト ニジュウシコウ</t>
+          <t>ギョクズイ</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>浅井 了意</t>
+          <t>藤原 道家</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>[書写者不明]</t>
+          <t>野宮定基 : 久世通夏 [ほか写]</t>
         </is>
       </c>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr">
         <is>
-          <t>[江戸前期]</t>
+          <t>元禄12 [1699]-宝永3 [1706] 奥書</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
-          <t>写本|書名は目首及び題簽による|内箱の書名: 大和廿四孝|外箱の書名: 御本|責任表示は『日本古典籍総合目録データベース』による|1: 第1-4. 2: 第5-8. 3: 第9-12. 4: 第13-16. 5: 第17-20. 6: 第21-24|毎半帖10行|漢字平仮名交じり文|奈良絵本|梅唐草文様緞子表紙, 松葉散しに山雲の金箔見返し, 金泥下絵鳥の子紙を使用|列帖装|竪本|二重箱入り|糸切れあり</t>
+          <t>写本|書名及び巻冊次は表紙による|奥中の書名: 光明峯寺禅閤道家公記, 峯禅閤記, 峯摂政記, 峯入道摂政記|承元4年の原奥書に「右即位記一卷者光明峯寺禅閤自筆正記也以件本左令吾基春卿透以写之云々加挍正之 ... 永正七年夷則上浣 從一位(花押)」とあり|奥書に「右以或人夲自常州到来令書写之彼夲端書云此冊上下卷 ... 元禄第十二暦仲夏中旬 羽林左衞中郎将藤原定基丗一才」(承元3), 「右光明峯寺禅閤道家公承元二年三月五六月八月四年二三月九月十十一十二月記は借請或人之夲自常州邊来書写之加一挍了/于時元禄第十二端午節也 左中郎将藤原定基丗才」(承元4), 「右玉蘂建暦元年少弟左中将通清朝臣助筆僅加一挍原本文字不正後来得正夲可改之者也/元禄十三年九月十日 松堂閑士(花押)丗二才」(建暦元), 「右玉蘂峯禅閤記建暦二年自二月至九月一冊以或人夲自常州邊来命家僚令書写手自加挍合了/元禄十二年五月六日 左中郎将藤原定基丗一才」(建暦2年上), 「宝永二年十月一日書写畢/承久二春玉蘂以故常州牧權中納言光圀公夲謄写之于時俗務紛擾先請慈兄源亜相公所被写也今以彼夲手自馳禿筆 余識藤(花押)丗七才/同三年二月廿五日一挍了」(承久2年上), 「右峯摂政承久二年記命傭書謄冩之手自一挍了/元禄第十二嵗次著雍単閼蕤賓中旬 羽林軍左衞中郎将藤原定基丗一才」(承久2年下), 「嘉禎四年正月二月閏二月三月四月六月玉蘂先年假借故常州牧前中納言光圀夲無剋力速遂書写之功建暦元年建暦二年下承久二年上及此卷等先献慈兄亜相君写之今及数年申復彼夲謄写之 ... 宝永三年十二月念日 参議從三位行左近衞權中将藤原朝臣定基生年卅八才」(嘉禎4年)とあり|毎半葉11行注文双行|漢文体日記|拠徳川光圀本及び中院通躬鈔本謄写|朱筆書き入れあり|印記: 「定基」(野宮定基), 「野宮書印」|虫損あり (裏打ち補修あり)</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -6404,12 +6400,12 @@
       <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/59c5b4a7-529d-5e9f-454f-8879e85023eb.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/ca2da620-345c-76fa-9d1d-e7b2c55d757f.json</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>59c5b4a7-529d-5e9f-454f-8879e85023eb</t>
+          <t>ca2da620-345c-76fa-9d1d-e7b2c55d757f</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
@@ -6419,7 +6415,7 @@
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/59c5b4a7-529d-5e9f-454f-8879e85023eb</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/ca2da620-345c-76fa-9d1d-e7b2c55d757f</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
@@ -6429,12 +6425,12 @@
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/e4d2c0aa6489eb2a071834a4a14714fecb372bce.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/8204e28b4e8f0e2f8abc1b939244f007093f3749.jpg</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296172</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296197</t>
         </is>
       </c>
       <c r="W49" t="inlineStr">
@@ -6457,7 +6453,7 @@
       <c r="AB49" t="inlineStr"/>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/59c5b4a7-529d-5e9f-454f-8879e85023eb/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/ca2da620-345c-76fa-9d1d-e7b2c55d757f/manifest</t>
         </is>
       </c>
       <c r="AD49" t="inlineStr"/>
@@ -6465,31 +6461,27 @@
       <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="inlineStr"/>
       <c r="AH49" t="n">
-        <v>76</v>
+        <v>63</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>日本廿四孝 6巻 [5]</t>
+          <t>大明星天子法 : 又名法界虚空蔵法</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>A00:4084</t>
+          <t>A00:6097</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>ヤマト ニジュウシコウ</t>
+          <t>ダイミョウジョウテンシホウ : マタミョウ ホッカイ コクウゾウホウ</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>浅井 了意</t>
-        </is>
-      </c>
+      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
           <t>[書写者不明]</t>
@@ -6498,19 +6490,19 @@
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr">
         <is>
-          <t>[江戸前期]</t>
+          <t>[天文年間]</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr">
         <is>
-          <t>写本|書名は目首及び題簽による|内箱の書名: 大和廿四孝|外箱の書名: 御本|責任表示は『日本古典籍総合目録データベース』による|1: 第1-4. 2: 第5-8. 3: 第9-12. 4: 第13-16. 5: 第17-20. 6: 第21-24|毎半帖10行|漢字平仮名交じり文|奈良絵本|梅唐草文様緞子表紙, 松葉散しに山雲の金箔見返し, 金泥下絵鳥の子紙を使用|列帖装|竪本|二重箱入り|糸切れあり</t>
+          <t>写本|巻末の書名: 明星天子法|表紙の書名: 大明皇天子水|大尾に「明星天子法次苐 一交了」とあり|本奥書に「承久三年五月十三日/爲興法利生徃生極樂書冩之/金剛佛子觀照之」とあり|書袋に「天文古筆」, 「天明七未ノ年」とあり|毎半葉8行|押界を施した楮紙打紙を使用|粘葉装|虫損あり</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -6526,12 +6518,12 @@
       <c r="O50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/ff7eb5a9-8bd0-64c0-3cbf-03a54ac07e65.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/a1905fc7-4727-0750-41d7-f0ca1df53f47.json</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>ff7eb5a9-8bd0-64c0-3cbf-03a54ac07e65</t>
+          <t>a1905fc7-4727-0750-41d7-f0ca1df53f47</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
@@ -6541,7 +6533,7 @@
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/ff7eb5a9-8bd0-64c0-3cbf-03a54ac07e65</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/a1905fc7-4727-0750-41d7-f0ca1df53f47</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
@@ -6551,12 +6543,12 @@
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/550abdb28c4a764b0c1330b7551c32cee807416f.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/b2590ef4e55f582d8059a5e072e1d6dad33bf996.jpg</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296173</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296198</t>
         </is>
       </c>
       <c r="W50" t="inlineStr">
@@ -6579,7 +6571,7 @@
       <c r="AB50" t="inlineStr"/>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/ff7eb5a9-8bd0-64c0-3cbf-03a54ac07e65/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/a1905fc7-4727-0750-41d7-f0ca1df53f47/manifest</t>
         </is>
       </c>
       <c r="AD50" t="inlineStr"/>
@@ -6587,52 +6579,48 @@
       <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="inlineStr"/>
       <c r="AH50" t="n">
-        <v>87</v>
+        <v>9</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>日本廿四孝 6巻 [6]</t>
+          <t>大嘗會悠紀主基鮮味之繪</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>A00:4084</t>
+          <t>A00:6108</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>ヤマト ニジュウシコウ</t>
+          <t>ダイジョウエ ユキ スキ センミ ノ ズ</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>浅井 了意</t>
-        </is>
-      </c>
+      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
-          <t>[書写者不明]</t>
+          <t>[佐伯]</t>
         </is>
       </c>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr">
         <is>
-          <t>[江戸前期]</t>
+          <t>明和元 [1764] 識語</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr">
         <is>
-          <t>写本|書名は目首及び題簽による|内箱の書名: 大和廿四孝|外箱の書名: 御本|責任表示は『日本古典籍総合目録データベース』による|1: 第1-4. 2: 第5-8. 3: 第9-12. 4: 第13-16. 5: 第17-20. 6: 第21-24|毎半帖10行|漢字平仮名交じり文|奈良絵本|梅唐草文様緞子表紙, 松葉散しに山雲の金箔見返し, 金泥下絵鳥の子紙を使用|列帖装|竪本|二重箱入り|糸切れあり</t>
+          <t>絵巻|書名は識語による|書袋の書名: 悠紀主基鮮味之啚|表紙裏に「元文悠紀主基鮮味之圖 寛延同」とあり|巻末の識語に「右大嘗會悠紀主基鮮味之繪借請御厨子所預紀宗直朝臣令佐伯職房摸冩之畢 明和元年孟冬左少将藤原(花押)」とあり|絵4幅: 梅作枝, 糸作枩, 萩作枝, 萩作枝|紙本著色|彩色あり|帙入り|印記: 「野宮藏書」</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -6648,12 +6636,12 @@
       <c r="O51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/0106be3f-16cb-3945-1c3c-419a27f26c16.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/d00e906c-5404-4fc1-44c9-1566cf7f7012.json</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>0106be3f-16cb-3945-1c3c-419a27f26c16</t>
+          <t>d00e906c-5404-4fc1-44c9-1566cf7f7012</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
@@ -6663,7 +6651,7 @@
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/0106be3f-16cb-3945-1c3c-419a27f26c16</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/d00e906c-5404-4fc1-44c9-1566cf7f7012</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
@@ -6673,12 +6661,12 @@
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/b1c4cf868676ac5b8b2f574249475349a7a90813.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/51e8aa982b380211852796b36819e6c6c6bf1583.jpg</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296174</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296199</t>
         </is>
       </c>
       <c r="W51" t="inlineStr">
@@ -6701,7 +6689,7 @@
       <c r="AB51" t="inlineStr"/>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/0106be3f-16cb-3945-1c3c-419a27f26c16/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/d00e906c-5404-4fc1-44c9-1566cf7f7012/manifest</t>
         </is>
       </c>
       <c r="AD51" t="inlineStr"/>
@@ -6709,40 +6697,36 @@
       <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="inlineStr"/>
       <c r="AH51" t="n">
-        <v>70</v>
+        <v>11</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>京ものかたり</t>
+          <t>真言宗脈啚 : 栂尾夲</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>A00:4085</t>
+          <t>A00:6129</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>キョウモノガタリ</t>
+          <t>シンゴンシュウ ミャクズ : トガノオボン</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>洛陽散人</t>
-        </is>
-      </c>
+      <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
-          <t>[書写者不明]</t>
+          <t>覺心</t>
         </is>
       </c>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr">
         <is>
-          <t>[江戸前期]</t>
+          <t>享保9 [1724] 奥書</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -6754,7 +6738,7 @@
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr">
         <is>
-          <t>写本|書名は題簽による|[跋]中の書名: 見ぬ京ものかたり|外箱の書名: 御本|[跋]に「万治元年の秋夜長きひ ... いぬの年九月の末のはふのなん時 洛陽散人たれ某」とあり|内容: 儒佛の論, など|毎半帖10行|漢字平仮名交じり文|桜唐草文様緞子表紙, 松葉散しに山雲の金箔見返し, 金泥下絵鳥の子紙を使用|列帖装|二重箱入り</t>
+          <t>写本|書名は題簽による|帙題簽の書名: 真言宗血脈圗|奥書に「正徳二年之春請自性院僧正開栂尾山宮御封之經藏求淂于古聖教若干部是其一也 沙門道空」, 「享保九年甲辰夏寓于洛西御阜草菴以五智山之本冩之訖 南紀護国寺沙門覺心/同年六月晦日以栂尾法鼓臺古本挍合之了」, 「昭和八年四月念三日閲覧砌訂正誤字記入落罫云尒 中野達慧識」とあり|朱筆書き入れあり|印記: 「和學講談所」, 「温故堂文庫」(塙家), 「松平家藏書印」|虫損あり</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -6770,12 +6754,12 @@
       <c r="O52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/13969a60-692e-663a-3a83-97b8168b8fbe.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/e6a30e98-5da6-7e0d-7a92-5b26c887309f.json</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>13969a60-692e-663a-3a83-97b8168b8fbe</t>
+          <t>e6a30e98-5da6-7e0d-7a92-5b26c887309f</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
@@ -6785,7 +6769,7 @@
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/13969a60-692e-663a-3a83-97b8168b8fbe</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/e6a30e98-5da6-7e0d-7a92-5b26c887309f</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
@@ -6795,12 +6779,12 @@
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/b4c216cdd7c363c063be4e90de6eea21dd1da6e3.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/10842787f14673fb3729595dd908dde4c4dd6ad8.jpg</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296175</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296200</t>
         </is>
       </c>
       <c r="W52" t="inlineStr">
@@ -6823,7 +6807,7 @@
       <c r="AB52" t="inlineStr"/>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/13969a60-692e-663a-3a83-97b8168b8fbe/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/e6a30e98-5da6-7e0d-7a92-5b26c887309f/manifest</t>
         </is>
       </c>
       <c r="AD52" t="inlineStr"/>
@@ -6831,52 +6815,52 @@
       <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="inlineStr"/>
       <c r="AH52" t="n">
-        <v>68</v>
+        <v>22</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>北遊漫録 3巻再1巻 [1]</t>
+          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [1]</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>A00:4099</t>
+          <t>A00:6257</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>ホクユウ マンロク</t>
+          <t>レキダイ ザンケツ ニッキ</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>久保田 米僊</t>
+          <t>黒川 春村</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>久保田米僊 [自筆]</t>
+          <t>[書写者不明]</t>
         </is>
       </c>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr">
         <is>
-          <t>明治21 [1888]-明治24 [1891]</t>
+          <t>[安政5 (1858)]</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr">
         <is>
-          <t>写本|書名は扉による|帙題簽に「久保田米僊草稿」とあり|扉に「明治廿一年はる五月」(乾), 「明治廿一年はる六月」(坤), 「明治廿一年はる六月中澣」(瑞啚), 「明治廿四年五月十九日」(再)とあり|乾末に「増補考古畫譜五巻 發兌書肆 有隣堂」とあり|おもに図版|彩色あり|双葉装|印記: 「田寛之印」, 「山脊与弥との」</t>
+          <t>写本|責任表示及び書写年は『日本古典籍総合目録データベース』による|内容: 6: 光明院御記, 後光嚴院御記, 後小松院宸記, 天聴集. 28: 参議藤定長卿記 : 稱山丞記. 37: 定高卿記, 晴御会部類記, 家光卿御記, 權中納言平範輔卿記. 38: 左大史小槻季継記, 後堀川安貞二年放生會(実基公記), 石清水八幡宮, 弁官拝賀次第. 39: 大外記師光記, 資季卿記, 荒凉記, 忠高卿記. 40: 冷泉公相公記, 勝延法眼記 : 東寺大行事, 後中記 : 小路中納言資頼卿記葉室. 41: 中光記, 師兼記, 陽龍記. 42: 大宮司長則記, 口筆 : 實經, 顕朝卿記, 鴨御幸記. 43: 寳治二年記, 深心院關白記, 藤公親記, 照念院関白兼平公記. 44: 頼親記, 亀山殿行幸記 : 雅言卿記, 兼基公記. 45: 大嘗會御禊節下次第, 建治三年丁丑日記 : 三善康有, 建治四年正月廿一日 : 徳大寺大相國公孝記, 冬定卿記, 左大史小槻兼文記|内容: 46: 經任卿記, 前豊前守藤憲説記, 實兼公記. 47: 継塵記抄出. 48: 管見記, 公衡公記, 大外記師顕記, 大外記中原師淳記. 49: 真光院禪助僧正記, 吉田内府卿記. 50: 定清記, 叅議雅俊卿記, 太政大臣(公守公)御上表雜事, 仙洞御灌頂日記, 正安二年八月十一日於仙洞被始行熾盛光法, 正安三年御譲位記. 51: 實躬卿記. 52: 公茂公記, 冬平公記, 隆長卿記. 53: 忠教公記, 官記, 正三位長基卿記, 北面秀長記, 大外記中原師右記. 54: 文保元年, 日野中納言資朝卿記, 洞院大納言公敏卿記. 55: 隆蔭卿記, 文保三年記, 尹大納言師賢卿記, 革命記, 立倚子記, 萬里小路中納言藤藤房卿記|内容: 56: 資名卿記, 公秀公記, 一條家記装束抄出, 頼定卿記. 63: 松亞記, 日野大納言時光卿記, 後八條内府實継公記. 74: 成恩寺関白記. 78: 山科家礼記. 82: 諒闇記 : 後成恩寺殿, 宗典僧正記, 綱光公記, 贈従二位宗賢卿記, 義政公記. 84: 長禄二年戊寅正月, 見聞雜記. 87: 言國卿記. 88: 長興宿祢記, 元長卿記, 兼顕卿記, 小槻晴冨記|28末の原奥書に「右山丞記依 仰挍合書冩/享和二年四月 日撿挍保己一」とあり|50「正安二年八月十一日於仙洞被始行熾盛光法」末の原奥書に「文化十五年春二月以南山法曼院藏夲書冩之 撿挍保己一」とあり|横刷毛目表紙を使用|朱点, 朱引, 朱墨筆書き入れあり|付箋あり|蔵書印主信濃須坂藩主堀直格の命によって編集された古記録|他の原本は関東大震災により焼失|極札に「桂壽」(6), 「尚信」(53)との極書, 「武清」(44, 53), 「永海」(51), 「了伴」(52), 「了甫」(74), 「定時」(84, 88)との極印あり|印記: 「花廼家文庫」, 「墨阪十一代主寫藏記」(堀直格(1806-1880)), 「東京大學法理文學部書庫所藏」, 「閲覧室用 FOR USE IN THE READING ROOM」|虫損あり</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -6892,12 +6876,12 @@
       <c r="O53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/fdb2f4c7-47bb-0fc6-53e6-e8ffb5796046.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/c32632af-9dc0-504a-5437-15a055d52628.json</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>fdb2f4c7-47bb-0fc6-53e6-e8ffb5796046</t>
+          <t>c32632af-9dc0-504a-5437-15a055d52628</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
@@ -6907,7 +6891,7 @@
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/fdb2f4c7-47bb-0fc6-53e6-e8ffb5796046</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/c32632af-9dc0-504a-5437-15a055d52628</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
@@ -6917,12 +6901,12 @@
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/789ef89fb4fc813de5d276f3c43f982c6760d60b.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/2230dfedd3d91cc8b1c5532de33a8f8559be8357.jpg</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296176</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296201</t>
         </is>
       </c>
       <c r="W53" t="inlineStr">
@@ -6945,7 +6929,7 @@
       <c r="AB53" t="inlineStr"/>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/fdb2f4c7-47bb-0fc6-53e6-e8ffb5796046/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/c32632af-9dc0-504a-5437-15a055d52628/manifest</t>
         </is>
       </c>
       <c r="AD53" t="inlineStr"/>
@@ -6953,52 +6937,52 @@
       <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="inlineStr"/>
       <c r="AH53" t="n">
-        <v>31</v>
+        <v>72</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>北遊漫録 3巻再1巻 [2]</t>
+          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [2]</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>A00:4099</t>
+          <t>A00:6257</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>ホクユウ マンロク</t>
+          <t>レキダイ ザンケツ ニッキ</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>久保田 米僊</t>
+          <t>黒川 春村</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>久保田米僊 [自筆]</t>
+          <t>[書写者不明]</t>
         </is>
       </c>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr">
         <is>
-          <t>明治21 [1888]-明治24 [1891]</t>
+          <t>[安政5 (1858)]</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr">
         <is>
-          <t>写本|書名は扉による|帙題簽に「久保田米僊草稿」とあり|扉に「明治廿一年はる五月」(乾), 「明治廿一年はる六月」(坤), 「明治廿一年はる六月中澣」(瑞啚), 「明治廿四年五月十九日」(再)とあり|乾末に「増補考古畫譜五巻 發兌書肆 有隣堂」とあり|おもに図版|彩色あり|双葉装|印記: 「田寛之印」, 「山脊与弥との」</t>
+          <t>写本|責任表示及び書写年は『日本古典籍総合目録データベース』による|内容: 6: 光明院御記, 後光嚴院御記, 後小松院宸記, 天聴集. 28: 参議藤定長卿記 : 稱山丞記. 37: 定高卿記, 晴御会部類記, 家光卿御記, 權中納言平範輔卿記. 38: 左大史小槻季継記, 後堀川安貞二年放生會(実基公記), 石清水八幡宮, 弁官拝賀次第. 39: 大外記師光記, 資季卿記, 荒凉記, 忠高卿記. 40: 冷泉公相公記, 勝延法眼記 : 東寺大行事, 後中記 : 小路中納言資頼卿記葉室. 41: 中光記, 師兼記, 陽龍記. 42: 大宮司長則記, 口筆 : 實經, 顕朝卿記, 鴨御幸記. 43: 寳治二年記, 深心院關白記, 藤公親記, 照念院関白兼平公記. 44: 頼親記, 亀山殿行幸記 : 雅言卿記, 兼基公記. 45: 大嘗會御禊節下次第, 建治三年丁丑日記 : 三善康有, 建治四年正月廿一日 : 徳大寺大相國公孝記, 冬定卿記, 左大史小槻兼文記|内容: 46: 經任卿記, 前豊前守藤憲説記, 實兼公記. 47: 継塵記抄出. 48: 管見記, 公衡公記, 大外記師顕記, 大外記中原師淳記. 49: 真光院禪助僧正記, 吉田内府卿記. 50: 定清記, 叅議雅俊卿記, 太政大臣(公守公)御上表雜事, 仙洞御灌頂日記, 正安二年八月十一日於仙洞被始行熾盛光法, 正安三年御譲位記. 51: 實躬卿記. 52: 公茂公記, 冬平公記, 隆長卿記. 53: 忠教公記, 官記, 正三位長基卿記, 北面秀長記, 大外記中原師右記. 54: 文保元年, 日野中納言資朝卿記, 洞院大納言公敏卿記. 55: 隆蔭卿記, 文保三年記, 尹大納言師賢卿記, 革命記, 立倚子記, 萬里小路中納言藤藤房卿記|内容: 56: 資名卿記, 公秀公記, 一條家記装束抄出, 頼定卿記. 63: 松亞記, 日野大納言時光卿記, 後八條内府實継公記. 74: 成恩寺関白記. 78: 山科家礼記. 82: 諒闇記 : 後成恩寺殿, 宗典僧正記, 綱光公記, 贈従二位宗賢卿記, 義政公記. 84: 長禄二年戊寅正月, 見聞雜記. 87: 言國卿記. 88: 長興宿祢記, 元長卿記, 兼顕卿記, 小槻晴冨記|28末の原奥書に「右山丞記依 仰挍合書冩/享和二年四月 日撿挍保己一」とあり|50「正安二年八月十一日於仙洞被始行熾盛光法」末の原奥書に「文化十五年春二月以南山法曼院藏夲書冩之 撿挍保己一」とあり|横刷毛目表紙を使用|朱点, 朱引, 朱墨筆書き入れあり|付箋あり|蔵書印主信濃須坂藩主堀直格の命によって編集された古記録|他の原本は関東大震災により焼失|極札に「桂壽」(6), 「尚信」(53)との極書, 「武清」(44, 53), 「永海」(51), 「了伴」(52), 「了甫」(74), 「定時」(84, 88)との極印あり|印記: 「花廼家文庫」, 「墨阪十一代主寫藏記」(堀直格(1806-1880)), 「東京大學法理文學部書庫所藏」, 「閲覧室用 FOR USE IN THE READING ROOM」|虫損あり</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -7014,12 +6998,12 @@
       <c r="O54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/01f5e469-1d82-36bd-3e33-34c56a942a2d.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/f31d474b-60bb-5efd-a570-d8f971a97e5e.json</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>01f5e469-1d82-36bd-3e33-34c56a942a2d</t>
+          <t>f31d474b-60bb-5efd-a570-d8f971a97e5e</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
@@ -7029,7 +7013,7 @@
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/01f5e469-1d82-36bd-3e33-34c56a942a2d</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/f31d474b-60bb-5efd-a570-d8f971a97e5e</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
@@ -7039,12 +7023,12 @@
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/0e331722b5a82ea48f273a6b7465d2784dc8a44c.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/378909456e17de7b588873b8890cd6945bba3cc8.jpg</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296177</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296202</t>
         </is>
       </c>
       <c r="W54" t="inlineStr">
@@ -7067,7 +7051,7 @@
       <c r="AB54" t="inlineStr"/>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/01f5e469-1d82-36bd-3e33-34c56a942a2d/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/f31d474b-60bb-5efd-a570-d8f971a97e5e/manifest</t>
         </is>
       </c>
       <c r="AD54" t="inlineStr"/>
@@ -7075,52 +7059,52 @@
       <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="inlineStr"/>
       <c r="AH54" t="n">
-        <v>31</v>
+        <v>75</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>北遊漫録 3巻再1巻 [3]</t>
+          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [3]</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>A00:4099</t>
+          <t>A00:6257</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>ホクユウ マンロク</t>
+          <t>レキダイ ザンケツ ニッキ</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>久保田 米僊</t>
+          <t>黒川 春村</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>久保田米僊 [自筆]</t>
+          <t>[書写者不明]</t>
         </is>
       </c>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr">
         <is>
-          <t>明治21 [1888]-明治24 [1891]</t>
+          <t>[安政5 (1858)]</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr">
         <is>
-          <t>写本|書名は扉による|帙題簽に「久保田米僊草稿」とあり|扉に「明治廿一年はる五月」(乾), 「明治廿一年はる六月」(坤), 「明治廿一年はる六月中澣」(瑞啚), 「明治廿四年五月十九日」(再)とあり|乾末に「増補考古畫譜五巻 發兌書肆 有隣堂」とあり|おもに図版|彩色あり|双葉装|印記: 「田寛之印」, 「山脊与弥との」</t>
+          <t>写本|責任表示及び書写年は『日本古典籍総合目録データベース』による|内容: 6: 光明院御記, 後光嚴院御記, 後小松院宸記, 天聴集. 28: 参議藤定長卿記 : 稱山丞記. 37: 定高卿記, 晴御会部類記, 家光卿御記, 權中納言平範輔卿記. 38: 左大史小槻季継記, 後堀川安貞二年放生會(実基公記), 石清水八幡宮, 弁官拝賀次第. 39: 大外記師光記, 資季卿記, 荒凉記, 忠高卿記. 40: 冷泉公相公記, 勝延法眼記 : 東寺大行事, 後中記 : 小路中納言資頼卿記葉室. 41: 中光記, 師兼記, 陽龍記. 42: 大宮司長則記, 口筆 : 實經, 顕朝卿記, 鴨御幸記. 43: 寳治二年記, 深心院關白記, 藤公親記, 照念院関白兼平公記. 44: 頼親記, 亀山殿行幸記 : 雅言卿記, 兼基公記. 45: 大嘗會御禊節下次第, 建治三年丁丑日記 : 三善康有, 建治四年正月廿一日 : 徳大寺大相國公孝記, 冬定卿記, 左大史小槻兼文記|内容: 46: 經任卿記, 前豊前守藤憲説記, 實兼公記. 47: 継塵記抄出. 48: 管見記, 公衡公記, 大外記師顕記, 大外記中原師淳記. 49: 真光院禪助僧正記, 吉田内府卿記. 50: 定清記, 叅議雅俊卿記, 太政大臣(公守公)御上表雜事, 仙洞御灌頂日記, 正安二年八月十一日於仙洞被始行熾盛光法, 正安三年御譲位記. 51: 實躬卿記. 52: 公茂公記, 冬平公記, 隆長卿記. 53: 忠教公記, 官記, 正三位長基卿記, 北面秀長記, 大外記中原師右記. 54: 文保元年, 日野中納言資朝卿記, 洞院大納言公敏卿記. 55: 隆蔭卿記, 文保三年記, 尹大納言師賢卿記, 革命記, 立倚子記, 萬里小路中納言藤藤房卿記|内容: 56: 資名卿記, 公秀公記, 一條家記装束抄出, 頼定卿記. 63: 松亞記, 日野大納言時光卿記, 後八條内府實継公記. 74: 成恩寺関白記. 78: 山科家礼記. 82: 諒闇記 : 後成恩寺殿, 宗典僧正記, 綱光公記, 贈従二位宗賢卿記, 義政公記. 84: 長禄二年戊寅正月, 見聞雜記. 87: 言國卿記. 88: 長興宿祢記, 元長卿記, 兼顕卿記, 小槻晴冨記|28末の原奥書に「右山丞記依 仰挍合書冩/享和二年四月 日撿挍保己一」とあり|50「正安二年八月十一日於仙洞被始行熾盛光法」末の原奥書に「文化十五年春二月以南山法曼院藏夲書冩之 撿挍保己一」とあり|横刷毛目表紙を使用|朱点, 朱引, 朱墨筆書き入れあり|付箋あり|蔵書印主信濃須坂藩主堀直格の命によって編集された古記録|他の原本は関東大震災により焼失|極札に「桂壽」(6), 「尚信」(53)との極書, 「武清」(44, 53), 「永海」(51), 「了伴」(52), 「了甫」(74), 「定時」(84, 88)との極印あり|印記: 「花廼家文庫」, 「墨阪十一代主寫藏記」(堀直格(1806-1880)), 「東京大學法理文學部書庫所藏」, 「閲覧室用 FOR USE IN THE READING ROOM」|虫損あり</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -7136,12 +7120,12 @@
       <c r="O55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/1a4a12a3-0ae7-8858-3851-f3845f60709b.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/0ddf4bea-7e5d-145a-1812-20986271091f.json</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>1a4a12a3-0ae7-8858-3851-f3845f60709b</t>
+          <t>0ddf4bea-7e5d-145a-1812-20986271091f</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
@@ -7151,7 +7135,7 @@
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/1a4a12a3-0ae7-8858-3851-f3845f60709b</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/0ddf4bea-7e5d-145a-1812-20986271091f</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
@@ -7161,12 +7145,12 @@
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/3897bac3ffa751a75c02bb59922c185ca93a9f1e.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/f1d109214b4c636205f357c37df4079371b1c32f.jpg</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296178</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296203</t>
         </is>
       </c>
       <c r="W55" t="inlineStr">
@@ -7189,7 +7173,7 @@
       <c r="AB55" t="inlineStr"/>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/1a4a12a3-0ae7-8858-3851-f3845f60709b/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/0ddf4bea-7e5d-145a-1812-20986271091f/manifest</t>
         </is>
       </c>
       <c r="AD55" t="inlineStr"/>
@@ -7197,52 +7181,52 @@
       <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="inlineStr"/>
       <c r="AH55" t="n">
-        <v>31</v>
+        <v>50</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>北遊漫録 3巻再1巻 [4]</t>
+          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [4]</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>A00:4099</t>
+          <t>A00:6257</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>ホクユウ マンロク</t>
+          <t>レキダイ ザンケツ ニッキ</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>久保田 米僊</t>
+          <t>黒川 春村</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>久保田米僊 [自筆]</t>
+          <t>[書写者不明]</t>
         </is>
       </c>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr">
         <is>
-          <t>明治21 [1888]-明治24 [1891]</t>
+          <t>[安政5 (1858)]</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr">
         <is>
-          <t>写本|書名は扉による|帙題簽に「久保田米僊草稿」とあり|扉に「明治廿一年はる五月」(乾), 「明治廿一年はる六月」(坤), 「明治廿一年はる六月中澣」(瑞啚), 「明治廿四年五月十九日」(再)とあり|乾末に「増補考古畫譜五巻 發兌書肆 有隣堂」とあり|おもに図版|彩色あり|双葉装|印記: 「田寛之印」, 「山脊与弥との」</t>
+          <t>写本|責任表示及び書写年は『日本古典籍総合目録データベース』による|内容: 6: 光明院御記, 後光嚴院御記, 後小松院宸記, 天聴集. 28: 参議藤定長卿記 : 稱山丞記. 37: 定高卿記, 晴御会部類記, 家光卿御記, 權中納言平範輔卿記. 38: 左大史小槻季継記, 後堀川安貞二年放生會(実基公記), 石清水八幡宮, 弁官拝賀次第. 39: 大外記師光記, 資季卿記, 荒凉記, 忠高卿記. 40: 冷泉公相公記, 勝延法眼記 : 東寺大行事, 後中記 : 小路中納言資頼卿記葉室. 41: 中光記, 師兼記, 陽龍記. 42: 大宮司長則記, 口筆 : 實經, 顕朝卿記, 鴨御幸記. 43: 寳治二年記, 深心院關白記, 藤公親記, 照念院関白兼平公記. 44: 頼親記, 亀山殿行幸記 : 雅言卿記, 兼基公記. 45: 大嘗會御禊節下次第, 建治三年丁丑日記 : 三善康有, 建治四年正月廿一日 : 徳大寺大相國公孝記, 冬定卿記, 左大史小槻兼文記|内容: 46: 經任卿記, 前豊前守藤憲説記, 實兼公記. 47: 継塵記抄出. 48: 管見記, 公衡公記, 大外記師顕記, 大外記中原師淳記. 49: 真光院禪助僧正記, 吉田内府卿記. 50: 定清記, 叅議雅俊卿記, 太政大臣(公守公)御上表雜事, 仙洞御灌頂日記, 正安二年八月十一日於仙洞被始行熾盛光法, 正安三年御譲位記. 51: 實躬卿記. 52: 公茂公記, 冬平公記, 隆長卿記. 53: 忠教公記, 官記, 正三位長基卿記, 北面秀長記, 大外記中原師右記. 54: 文保元年, 日野中納言資朝卿記, 洞院大納言公敏卿記. 55: 隆蔭卿記, 文保三年記, 尹大納言師賢卿記, 革命記, 立倚子記, 萬里小路中納言藤藤房卿記|内容: 56: 資名卿記, 公秀公記, 一條家記装束抄出, 頼定卿記. 63: 松亞記, 日野大納言時光卿記, 後八條内府實継公記. 74: 成恩寺関白記. 78: 山科家礼記. 82: 諒闇記 : 後成恩寺殿, 宗典僧正記, 綱光公記, 贈従二位宗賢卿記, 義政公記. 84: 長禄二年戊寅正月, 見聞雜記. 87: 言國卿記. 88: 長興宿祢記, 元長卿記, 兼顕卿記, 小槻晴冨記|28末の原奥書に「右山丞記依 仰挍合書冩/享和二年四月 日撿挍保己一」とあり|50「正安二年八月十一日於仙洞被始行熾盛光法」末の原奥書に「文化十五年春二月以南山法曼院藏夲書冩之 撿挍保己一」とあり|横刷毛目表紙を使用|朱点, 朱引, 朱墨筆書き入れあり|付箋あり|蔵書印主信濃須坂藩主堀直格の命によって編集された古記録|他の原本は関東大震災により焼失|極札に「桂壽」(6), 「尚信」(53)との極書, 「武清」(44, 53), 「永海」(51), 「了伴」(52), 「了甫」(74), 「定時」(84, 88)との極印あり|印記: 「花廼家文庫」, 「墨阪十一代主寫藏記」(堀直格(1806-1880)), 「東京大學法理文學部書庫所藏」, 「閲覧室用 FOR USE IN THE READING ROOM」|虫損あり</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -7258,12 +7242,12 @@
       <c r="O56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/73cbda29-23d4-a760-5213-0395cd767491.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/5bf3d0ca-0a42-80a4-6959-af4f28d23fa3.json</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>73cbda29-23d4-a760-5213-0395cd767491</t>
+          <t>5bf3d0ca-0a42-80a4-6959-af4f28d23fa3</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
@@ -7273,7 +7257,7 @@
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/73cbda29-23d4-a760-5213-0395cd767491</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/5bf3d0ca-0a42-80a4-6959-af4f28d23fa3</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
@@ -7283,12 +7267,12 @@
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/74a9af6c2a682e260aa96f2ded5a07abfcd3098c.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/b3dd61edd0ba78499c058ae1c9d57f1980d4b058.jpg</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296179</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296204</t>
         </is>
       </c>
       <c r="W56" t="inlineStr">
@@ -7311,7 +7295,7 @@
       <c r="AB56" t="inlineStr"/>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/73cbda29-23d4-a760-5213-0395cd767491/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/5bf3d0ca-0a42-80a4-6959-af4f28d23fa3/manifest</t>
         </is>
       </c>
       <c r="AD56" t="inlineStr"/>
@@ -7319,36 +7303,40 @@
       <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="inlineStr"/>
       <c r="AH56" t="n">
-        <v>22</v>
+        <v>52</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>蘭主之書翰使節持参叅途中之図</t>
+          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [5]</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>A00:4146</t>
+          <t>A00:6257</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>ランシュ ノ ショカン シセツ ジサン トチュウ ノ ズ</t>
+          <t>レキダイ ザンケツ ニッキ</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>黒川 春村</t>
+        </is>
+      </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>[製作者不明]</t>
+          <t>[書写者不明]</t>
         </is>
       </c>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr">
         <is>
-          <t>天保15 [1844] 識語</t>
+          <t>[安政5 (1858)]</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -7360,7 +7348,7 @@
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr">
         <is>
-          <t>書名は題簽による|箱の書名: 和蘭國軍艦人物兵器等図|冒頭に「天保十五年甲辰秋七月二日和蘭國官船奉其主命来進於我﨑嶴茲掲略圖摸其全般及内面結構所備之諸兵器等」との識語あり|絵巻|彩色あり|印記: 「籌海庫」</t>
+          <t>写本|責任表示及び書写年は『日本古典籍総合目録データベース』による|内容: 6: 光明院御記, 後光嚴院御記, 後小松院宸記, 天聴集. 28: 参議藤定長卿記 : 稱山丞記. 37: 定高卿記, 晴御会部類記, 家光卿御記, 權中納言平範輔卿記. 38: 左大史小槻季継記, 後堀川安貞二年放生會(実基公記), 石清水八幡宮, 弁官拝賀次第. 39: 大外記師光記, 資季卿記, 荒凉記, 忠高卿記. 40: 冷泉公相公記, 勝延法眼記 : 東寺大行事, 後中記 : 小路中納言資頼卿記葉室. 41: 中光記, 師兼記, 陽龍記. 42: 大宮司長則記, 口筆 : 實經, 顕朝卿記, 鴨御幸記. 43: 寳治二年記, 深心院關白記, 藤公親記, 照念院関白兼平公記. 44: 頼親記, 亀山殿行幸記 : 雅言卿記, 兼基公記. 45: 大嘗會御禊節下次第, 建治三年丁丑日記 : 三善康有, 建治四年正月廿一日 : 徳大寺大相國公孝記, 冬定卿記, 左大史小槻兼文記|内容: 46: 經任卿記, 前豊前守藤憲説記, 實兼公記. 47: 継塵記抄出. 48: 管見記, 公衡公記, 大外記師顕記, 大外記中原師淳記. 49: 真光院禪助僧正記, 吉田内府卿記. 50: 定清記, 叅議雅俊卿記, 太政大臣(公守公)御上表雜事, 仙洞御灌頂日記, 正安二年八月十一日於仙洞被始行熾盛光法, 正安三年御譲位記. 51: 實躬卿記. 52: 公茂公記, 冬平公記, 隆長卿記. 53: 忠教公記, 官記, 正三位長基卿記, 北面秀長記, 大外記中原師右記. 54: 文保元年, 日野中納言資朝卿記, 洞院大納言公敏卿記. 55: 隆蔭卿記, 文保三年記, 尹大納言師賢卿記, 革命記, 立倚子記, 萬里小路中納言藤藤房卿記|内容: 56: 資名卿記, 公秀公記, 一條家記装束抄出, 頼定卿記. 63: 松亞記, 日野大納言時光卿記, 後八條内府實継公記. 74: 成恩寺関白記. 78: 山科家礼記. 82: 諒闇記 : 後成恩寺殿, 宗典僧正記, 綱光公記, 贈従二位宗賢卿記, 義政公記. 84: 長禄二年戊寅正月, 見聞雜記. 87: 言國卿記. 88: 長興宿祢記, 元長卿記, 兼顕卿記, 小槻晴冨記|28末の原奥書に「右山丞記依 仰挍合書冩/享和二年四月 日撿挍保己一」とあり|50「正安二年八月十一日於仙洞被始行熾盛光法」末の原奥書に「文化十五年春二月以南山法曼院藏夲書冩之 撿挍保己一」とあり|横刷毛目表紙を使用|朱点, 朱引, 朱墨筆書き入れあり|付箋あり|蔵書印主信濃須坂藩主堀直格の命によって編集された古記録|他の原本は関東大震災により焼失|極札に「桂壽」(6), 「尚信」(53)との極書, 「武清」(44, 53), 「永海」(51), 「了伴」(52), 「了甫」(74), 「定時」(84, 88)との極印あり|印記: 「花廼家文庫」, 「墨阪十一代主寫藏記」(堀直格(1806-1880)), 「東京大學法理文學部書庫所藏」, 「閲覧室用 FOR USE IN THE READING ROOM」|虫損あり</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -7376,12 +7364,12 @@
       <c r="O57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/ca3ac8e1-6c03-5832-3987-70b1fa71258a.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/92efd5a7-2a66-1ead-1e71-bdf9c70e12d0.json</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>ca3ac8e1-6c03-5832-3987-70b1fa71258a</t>
+          <t>92efd5a7-2a66-1ead-1e71-bdf9c70e12d0</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
@@ -7391,7 +7379,7 @@
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/ca3ac8e1-6c03-5832-3987-70b1fa71258a</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/92efd5a7-2a66-1ead-1e71-bdf9c70e12d0</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
@@ -7401,12 +7389,12 @@
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/32f72c2d68d9e56e4f46528e6997cbb4c330cc23.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/aaef2fe4c4feeefa7fd4fb27983a6dfd085d4a7b.jpg</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296180</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296205</t>
         </is>
       </c>
       <c r="W57" t="inlineStr">
@@ -7429,7 +7417,7 @@
       <c r="AB57" t="inlineStr"/>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/ca3ac8e1-6c03-5832-3987-70b1fa71258a/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/92efd5a7-2a66-1ead-1e71-bdf9c70e12d0/manifest</t>
         </is>
       </c>
       <c r="AD57" t="inlineStr"/>
@@ -7437,36 +7425,40 @@
       <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="inlineStr"/>
       <c r="AH57" t="n">
-        <v>22</v>
+        <v>68</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>喎蘭軍艦プレカット並銃劍等之図</t>
+          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [6]</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>A00:4147</t>
+          <t>A00:6257</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>オランダ グンカン プレカット ナラビニ ジュウケン トウ ノ ズ</t>
+          <t>レキダイ ザンケツ ニッキ</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>黒川 春村</t>
+        </is>
+      </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>[製作者不明]</t>
+          <t>[書写者不明]</t>
         </is>
       </c>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr">
         <is>
-          <t>[天保弘化年間]</t>
+          <t>[安政5 (1858)]</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -7478,7 +7470,7 @@
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr">
         <is>
-          <t>書名は題簽による|箱の書名: 和蘭國軍艦人物兵器等図|巻末に「圖説」あり|絵巻|彩色あり</t>
+          <t>写本|責任表示及び書写年は『日本古典籍総合目録データベース』による|内容: 6: 光明院御記, 後光嚴院御記, 後小松院宸記, 天聴集. 28: 参議藤定長卿記 : 稱山丞記. 37: 定高卿記, 晴御会部類記, 家光卿御記, 權中納言平範輔卿記. 38: 左大史小槻季継記, 後堀川安貞二年放生會(実基公記), 石清水八幡宮, 弁官拝賀次第. 39: 大外記師光記, 資季卿記, 荒凉記, 忠高卿記. 40: 冷泉公相公記, 勝延法眼記 : 東寺大行事, 後中記 : 小路中納言資頼卿記葉室. 41: 中光記, 師兼記, 陽龍記. 42: 大宮司長則記, 口筆 : 實經, 顕朝卿記, 鴨御幸記. 43: 寳治二年記, 深心院關白記, 藤公親記, 照念院関白兼平公記. 44: 頼親記, 亀山殿行幸記 : 雅言卿記, 兼基公記. 45: 大嘗會御禊節下次第, 建治三年丁丑日記 : 三善康有, 建治四年正月廿一日 : 徳大寺大相國公孝記, 冬定卿記, 左大史小槻兼文記|内容: 46: 經任卿記, 前豊前守藤憲説記, 實兼公記. 47: 継塵記抄出. 48: 管見記, 公衡公記, 大外記師顕記, 大外記中原師淳記. 49: 真光院禪助僧正記, 吉田内府卿記. 50: 定清記, 叅議雅俊卿記, 太政大臣(公守公)御上表雜事, 仙洞御灌頂日記, 正安二年八月十一日於仙洞被始行熾盛光法, 正安三年御譲位記. 51: 實躬卿記. 52: 公茂公記, 冬平公記, 隆長卿記. 53: 忠教公記, 官記, 正三位長基卿記, 北面秀長記, 大外記中原師右記. 54: 文保元年, 日野中納言資朝卿記, 洞院大納言公敏卿記. 55: 隆蔭卿記, 文保三年記, 尹大納言師賢卿記, 革命記, 立倚子記, 萬里小路中納言藤藤房卿記|内容: 56: 資名卿記, 公秀公記, 一條家記装束抄出, 頼定卿記. 63: 松亞記, 日野大納言時光卿記, 後八條内府實継公記. 74: 成恩寺関白記. 78: 山科家礼記. 82: 諒闇記 : 後成恩寺殿, 宗典僧正記, 綱光公記, 贈従二位宗賢卿記, 義政公記. 84: 長禄二年戊寅正月, 見聞雜記. 87: 言國卿記. 88: 長興宿祢記, 元長卿記, 兼顕卿記, 小槻晴冨記|28末の原奥書に「右山丞記依 仰挍合書冩/享和二年四月 日撿挍保己一」とあり|50「正安二年八月十一日於仙洞被始行熾盛光法」末の原奥書に「文化十五年春二月以南山法曼院藏夲書冩之 撿挍保己一」とあり|横刷毛目表紙を使用|朱点, 朱引, 朱墨筆書き入れあり|付箋あり|蔵書印主信濃須坂藩主堀直格の命によって編集された古記録|他の原本は関東大震災により焼失|極札に「桂壽」(6), 「尚信」(53)との極書, 「武清」(44, 53), 「永海」(51), 「了伴」(52), 「了甫」(74), 「定時」(84, 88)との極印あり|印記: 「花廼家文庫」, 「墨阪十一代主寫藏記」(堀直格(1806-1880)), 「東京大學法理文學部書庫所藏」, 「閲覧室用 FOR USE IN THE READING ROOM」|虫損あり</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -7494,12 +7486,12 @@
       <c r="O58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/8509e124-5c2f-173b-2502-4d9cd27f9f85.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/70ac8e25-6d33-9123-6fb2-0339224b41cc.json</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>8509e124-5c2f-173b-2502-4d9cd27f9f85</t>
+          <t>70ac8e25-6d33-9123-6fb2-0339224b41cc</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
@@ -7509,7 +7501,7 @@
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/8509e124-5c2f-173b-2502-4d9cd27f9f85</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/70ac8e25-6d33-9123-6fb2-0339224b41cc</t>
         </is>
       </c>
       <c r="T58" t="inlineStr">
@@ -7519,12 +7511,12 @@
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/18d2fe489472e7f697dd92568da44185793c8f4d.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/3d36b605983eef3eb9e60d5e9f2d3016a497dd98.jpg</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296181</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296206</t>
         </is>
       </c>
       <c r="W58" t="inlineStr">
@@ -7547,7 +7539,7 @@
       <c r="AB58" t="inlineStr"/>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/8509e124-5c2f-173b-2502-4d9cd27f9f85/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/70ac8e25-6d33-9123-6fb2-0339224b41cc/manifest</t>
         </is>
       </c>
       <c r="AD58" t="inlineStr"/>
@@ -7555,36 +7547,40 @@
       <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="inlineStr"/>
       <c r="AH58" t="n">
-        <v>17</v>
+        <v>72</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>能面圗譜</t>
+          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [7]</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>A00:4269</t>
+          <t>A00:6257</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>ノウメン ズフ</t>
+          <t>レキダイ ザンケツ ニッキ</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>黒川 春村</t>
+        </is>
+      </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>[製作者不明]</t>
+          <t>[書写者不明]</t>
         </is>
       </c>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr">
         <is>
-          <t>[江戸中期以降]</t>
+          <t>[安政5 (1858)]</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -7596,7 +7592,7 @@
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr">
         <is>
-          <t>折本|書名は題簽(墨書)による|帙題簽の書名(墨書): 能面圖譜|絹本彩色|図42幅|本紙: 16×13cm|金切箔散し料紙, 福寿文字布目地表紙を使用</t>
+          <t>写本|責任表示及び書写年は『日本古典籍総合目録データベース』による|内容: 6: 光明院御記, 後光嚴院御記, 後小松院宸記, 天聴集. 28: 参議藤定長卿記 : 稱山丞記. 37: 定高卿記, 晴御会部類記, 家光卿御記, 權中納言平範輔卿記. 38: 左大史小槻季継記, 後堀川安貞二年放生會(実基公記), 石清水八幡宮, 弁官拝賀次第. 39: 大外記師光記, 資季卿記, 荒凉記, 忠高卿記. 40: 冷泉公相公記, 勝延法眼記 : 東寺大行事, 後中記 : 小路中納言資頼卿記葉室. 41: 中光記, 師兼記, 陽龍記. 42: 大宮司長則記, 口筆 : 實經, 顕朝卿記, 鴨御幸記. 43: 寳治二年記, 深心院關白記, 藤公親記, 照念院関白兼平公記. 44: 頼親記, 亀山殿行幸記 : 雅言卿記, 兼基公記. 45: 大嘗會御禊節下次第, 建治三年丁丑日記 : 三善康有, 建治四年正月廿一日 : 徳大寺大相國公孝記, 冬定卿記, 左大史小槻兼文記|内容: 46: 經任卿記, 前豊前守藤憲説記, 實兼公記. 47: 継塵記抄出. 48: 管見記, 公衡公記, 大外記師顕記, 大外記中原師淳記. 49: 真光院禪助僧正記, 吉田内府卿記. 50: 定清記, 叅議雅俊卿記, 太政大臣(公守公)御上表雜事, 仙洞御灌頂日記, 正安二年八月十一日於仙洞被始行熾盛光法, 正安三年御譲位記. 51: 實躬卿記. 52: 公茂公記, 冬平公記, 隆長卿記. 53: 忠教公記, 官記, 正三位長基卿記, 北面秀長記, 大外記中原師右記. 54: 文保元年, 日野中納言資朝卿記, 洞院大納言公敏卿記. 55: 隆蔭卿記, 文保三年記, 尹大納言師賢卿記, 革命記, 立倚子記, 萬里小路中納言藤藤房卿記|内容: 56: 資名卿記, 公秀公記, 一條家記装束抄出, 頼定卿記. 63: 松亞記, 日野大納言時光卿記, 後八條内府實継公記. 74: 成恩寺関白記. 78: 山科家礼記. 82: 諒闇記 : 後成恩寺殿, 宗典僧正記, 綱光公記, 贈従二位宗賢卿記, 義政公記. 84: 長禄二年戊寅正月, 見聞雜記. 87: 言國卿記. 88: 長興宿祢記, 元長卿記, 兼顕卿記, 小槻晴冨記|28末の原奥書に「右山丞記依 仰挍合書冩/享和二年四月 日撿挍保己一」とあり|50「正安二年八月十一日於仙洞被始行熾盛光法」末の原奥書に「文化十五年春二月以南山法曼院藏夲書冩之 撿挍保己一」とあり|横刷毛目表紙を使用|朱点, 朱引, 朱墨筆書き入れあり|付箋あり|蔵書印主信濃須坂藩主堀直格の命によって編集された古記録|他の原本は関東大震災により焼失|極札に「桂壽」(6), 「尚信」(53)との極書, 「武清」(44, 53), 「永海」(51), 「了伴」(52), 「了甫」(74), 「定時」(84, 88)との極印あり|印記: 「花廼家文庫」, 「墨阪十一代主寫藏記」(堀直格(1806-1880)), 「東京大學法理文學部書庫所藏」, 「閲覧室用 FOR USE IN THE READING ROOM」|虫損あり</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -7612,12 +7608,12 @@
       <c r="O59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/8b3019c4-7584-208c-0c75-7c855ddc0b9e.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/87cadcc3-3c6c-1f0e-a10f-d8c8b16b34e3.json</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>8b3019c4-7584-208c-0c75-7c855ddc0b9e</t>
+          <t>87cadcc3-3c6c-1f0e-a10f-d8c8b16b34e3</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
@@ -7627,7 +7623,7 @@
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/8b3019c4-7584-208c-0c75-7c855ddc0b9e</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/87cadcc3-3c6c-1f0e-a10f-d8c8b16b34e3</t>
         </is>
       </c>
       <c r="T59" t="inlineStr">
@@ -7637,12 +7633,12 @@
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/3109e43cd273e3e02f2a227b4f1053cc1d4558bb.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/60cd75676a83bcd5331212ff419346e6088f81e4.jpg</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296182</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296207</t>
         </is>
       </c>
       <c r="W59" t="inlineStr">
@@ -7665,7 +7661,7 @@
       <c r="AB59" t="inlineStr"/>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/8b3019c4-7584-208c-0c75-7c855ddc0b9e/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/87cadcc3-3c6c-1f0e-a10f-d8c8b16b34e3/manifest</t>
         </is>
       </c>
       <c r="AD59" t="inlineStr"/>
@@ -7673,29 +7669,29 @@
       <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="inlineStr"/>
       <c r="AH59" t="n">
-        <v>28</v>
+        <v>67</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>法蕐經集驗記 2巻</t>
+          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [8]</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>A00:4273</t>
+          <t>A00:6257</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>ホケキョウ シュウゲンキ</t>
+          <t>レキダイ ザンケツ ニッキ</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>義寂</t>
+          <t>黒川 春村</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -7706,7 +7702,7 @@
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr">
         <is>
-          <t>[平安時代]</t>
+          <t>[安政5 (1858)]</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -7718,7 +7714,7 @@
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr">
         <is>
-          <t>鈔本|書名は卷下の巻頭による|大尾の書名: 法蕐集驗記|後付題簽の書名: 法花經集驗記|箱の書名: 法華驗記|卷下の内題下に「并序沙門寂撰」とあり|奥書に「護持僧(花押)夲之」とあり|巻末識語に「嘉應二年庚寅二月十八日傳得之釈子有慶在判」, 「十帋半」とあり|卷上: 諷誦第1. 卷下: 轉讀第2, 書寫第3, 聽聞第4|巻子本|訓点付|卷上の巻頭を欠損|原十紙半を1軸に合綴|朱筆書き入れあり|破損, 虫損あり (裏打ち補修あり)</t>
+          <t>写本|責任表示及び書写年は『日本古典籍総合目録データベース』による|内容: 6: 光明院御記, 後光嚴院御記, 後小松院宸記, 天聴集. 28: 参議藤定長卿記 : 稱山丞記. 37: 定高卿記, 晴御会部類記, 家光卿御記, 權中納言平範輔卿記. 38: 左大史小槻季継記, 後堀川安貞二年放生會(実基公記), 石清水八幡宮, 弁官拝賀次第. 39: 大外記師光記, 資季卿記, 荒凉記, 忠高卿記. 40: 冷泉公相公記, 勝延法眼記 : 東寺大行事, 後中記 : 小路中納言資頼卿記葉室. 41: 中光記, 師兼記, 陽龍記. 42: 大宮司長則記, 口筆 : 實經, 顕朝卿記, 鴨御幸記. 43: 寳治二年記, 深心院關白記, 藤公親記, 照念院関白兼平公記. 44: 頼親記, 亀山殿行幸記 : 雅言卿記, 兼基公記. 45: 大嘗會御禊節下次第, 建治三年丁丑日記 : 三善康有, 建治四年正月廿一日 : 徳大寺大相國公孝記, 冬定卿記, 左大史小槻兼文記|内容: 46: 經任卿記, 前豊前守藤憲説記, 實兼公記. 47: 継塵記抄出. 48: 管見記, 公衡公記, 大外記師顕記, 大外記中原師淳記. 49: 真光院禪助僧正記, 吉田内府卿記. 50: 定清記, 叅議雅俊卿記, 太政大臣(公守公)御上表雜事, 仙洞御灌頂日記, 正安二年八月十一日於仙洞被始行熾盛光法, 正安三年御譲位記. 51: 實躬卿記. 52: 公茂公記, 冬平公記, 隆長卿記. 53: 忠教公記, 官記, 正三位長基卿記, 北面秀長記, 大外記中原師右記. 54: 文保元年, 日野中納言資朝卿記, 洞院大納言公敏卿記. 55: 隆蔭卿記, 文保三年記, 尹大納言師賢卿記, 革命記, 立倚子記, 萬里小路中納言藤藤房卿記|内容: 56: 資名卿記, 公秀公記, 一條家記装束抄出, 頼定卿記. 63: 松亞記, 日野大納言時光卿記, 後八條内府實継公記. 74: 成恩寺関白記. 78: 山科家礼記. 82: 諒闇記 : 後成恩寺殿, 宗典僧正記, 綱光公記, 贈従二位宗賢卿記, 義政公記. 84: 長禄二年戊寅正月, 見聞雜記. 87: 言國卿記. 88: 長興宿祢記, 元長卿記, 兼顕卿記, 小槻晴冨記|28末の原奥書に「右山丞記依 仰挍合書冩/享和二年四月 日撿挍保己一」とあり|50「正安二年八月十一日於仙洞被始行熾盛光法」末の原奥書に「文化十五年春二月以南山法曼院藏夲書冩之 撿挍保己一」とあり|横刷毛目表紙を使用|朱点, 朱引, 朱墨筆書き入れあり|付箋あり|蔵書印主信濃須坂藩主堀直格の命によって編集された古記録|他の原本は関東大震災により焼失|極札に「桂壽」(6), 「尚信」(53)との極書, 「武清」(44, 53), 「永海」(51), 「了伴」(52), 「了甫」(74), 「定時」(84, 88)との極印あり|印記: 「花廼家文庫」, 「墨阪十一代主寫藏記」(堀直格(1806-1880)), 「東京大學法理文學部書庫所藏」, 「閲覧室用 FOR USE IN THE READING ROOM」|虫損あり</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -7734,12 +7730,12 @@
       <c r="O60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/ec4bceb1-0ab9-74c7-0dc7-f90d0a98a66e.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/d4dc2699-5a8e-7ad5-3160-80d5fae78074.json</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>ec4bceb1-0ab9-74c7-0dc7-f90d0a98a66e</t>
+          <t>d4dc2699-5a8e-7ad5-3160-80d5fae78074</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
@@ -7749,7 +7745,7 @@
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/ec4bceb1-0ab9-74c7-0dc7-f90d0a98a66e</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/d4dc2699-5a8e-7ad5-3160-80d5fae78074</t>
         </is>
       </c>
       <c r="T60" t="inlineStr">
@@ -7759,12 +7755,12 @@
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/d1c457097d78f2d8a4b38eebd630ef233026cc5e.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/596a21f68644c95bd76b3f3600fb73bc78fb9124.jpg</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296183</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296208</t>
         </is>
       </c>
       <c r="W60" t="inlineStr">
@@ -7787,7 +7783,7 @@
       <c r="AB60" t="inlineStr"/>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/ec4bceb1-0ab9-74c7-0dc7-f90d0a98a66e/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/d4dc2699-5a8e-7ad5-3160-80d5fae78074/manifest</t>
         </is>
       </c>
       <c r="AD60" t="inlineStr"/>
@@ -7795,36 +7791,40 @@
       <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="inlineStr"/>
       <c r="AH60" t="n">
-        <v>19</v>
+        <v>67</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>道成寺</t>
+          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [9]</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>A00:4276</t>
+          <t>A00:6257</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>ドウジョウジ</t>
+          <t>レキダイ ザンケツ ニッキ</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>黒川 春村</t>
+        </is>
+      </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>[製作者不明]</t>
+          <t>[書写者不明]</t>
         </is>
       </c>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr">
         <is>
-          <t>天明2 [1782] 識語</t>
+          <t>[安政5 (1858)]</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -7836,7 +7836,7 @@
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr">
         <is>
-          <t>書名は識語による|巻末識語に「道成寺建立年号大長五年三月吉日以後于二百三拾年去テ延長六戊子暦八月十日鐘巻也」, 「時天明二壬寅十月 尚良書之」とあり|絵巻|紙本著色|彩色あり|本紙: 855×28cm|界高: 25.8cm|軸物|軸頭欠損あり|印記: 「尚良印」|破損あり (裏打ち補修あり)</t>
+          <t>写本|責任表示及び書写年は『日本古典籍総合目録データベース』による|内容: 6: 光明院御記, 後光嚴院御記, 後小松院宸記, 天聴集. 28: 参議藤定長卿記 : 稱山丞記. 37: 定高卿記, 晴御会部類記, 家光卿御記, 權中納言平範輔卿記. 38: 左大史小槻季継記, 後堀川安貞二年放生會(実基公記), 石清水八幡宮, 弁官拝賀次第. 39: 大外記師光記, 資季卿記, 荒凉記, 忠高卿記. 40: 冷泉公相公記, 勝延法眼記 : 東寺大行事, 後中記 : 小路中納言資頼卿記葉室. 41: 中光記, 師兼記, 陽龍記. 42: 大宮司長則記, 口筆 : 實經, 顕朝卿記, 鴨御幸記. 43: 寳治二年記, 深心院關白記, 藤公親記, 照念院関白兼平公記. 44: 頼親記, 亀山殿行幸記 : 雅言卿記, 兼基公記. 45: 大嘗會御禊節下次第, 建治三年丁丑日記 : 三善康有, 建治四年正月廿一日 : 徳大寺大相國公孝記, 冬定卿記, 左大史小槻兼文記|内容: 46: 經任卿記, 前豊前守藤憲説記, 實兼公記. 47: 継塵記抄出. 48: 管見記, 公衡公記, 大外記師顕記, 大外記中原師淳記. 49: 真光院禪助僧正記, 吉田内府卿記. 50: 定清記, 叅議雅俊卿記, 太政大臣(公守公)御上表雜事, 仙洞御灌頂日記, 正安二年八月十一日於仙洞被始行熾盛光法, 正安三年御譲位記. 51: 實躬卿記. 52: 公茂公記, 冬平公記, 隆長卿記. 53: 忠教公記, 官記, 正三位長基卿記, 北面秀長記, 大外記中原師右記. 54: 文保元年, 日野中納言資朝卿記, 洞院大納言公敏卿記. 55: 隆蔭卿記, 文保三年記, 尹大納言師賢卿記, 革命記, 立倚子記, 萬里小路中納言藤藤房卿記|内容: 56: 資名卿記, 公秀公記, 一條家記装束抄出, 頼定卿記. 63: 松亞記, 日野大納言時光卿記, 後八條内府實継公記. 74: 成恩寺関白記. 78: 山科家礼記. 82: 諒闇記 : 後成恩寺殿, 宗典僧正記, 綱光公記, 贈従二位宗賢卿記, 義政公記. 84: 長禄二年戊寅正月, 見聞雜記. 87: 言國卿記. 88: 長興宿祢記, 元長卿記, 兼顕卿記, 小槻晴冨記|28末の原奥書に「右山丞記依 仰挍合書冩/享和二年四月 日撿挍保己一」とあり|50「正安二年八月十一日於仙洞被始行熾盛光法」末の原奥書に「文化十五年春二月以南山法曼院藏夲書冩之 撿挍保己一」とあり|横刷毛目表紙を使用|朱点, 朱引, 朱墨筆書き入れあり|付箋あり|蔵書印主信濃須坂藩主堀直格の命によって編集された古記録|他の原本は関東大震災により焼失|極札に「桂壽」(6), 「尚信」(53)との極書, 「武清」(44, 53), 「永海」(51), 「了伴」(52), 「了甫」(74), 「定時」(84, 88)との極印あり|印記: 「花廼家文庫」, 「墨阪十一代主寫藏記」(堀直格(1806-1880)), 「東京大學法理文學部書庫所藏」, 「閲覧室用 FOR USE IN THE READING ROOM」|虫損あり</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -7852,12 +7852,12 @@
       <c r="O61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/79185d0c-7fa3-2efd-863e-93927e137a23.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/a5e4d339-47a5-92a8-3fb3-15464db0a1f8.json</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>79185d0c-7fa3-2efd-863e-93927e137a23</t>
+          <t>a5e4d339-47a5-92a8-3fb3-15464db0a1f8</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
@@ -7867,7 +7867,7 @@
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/79185d0c-7fa3-2efd-863e-93927e137a23</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/a5e4d339-47a5-92a8-3fb3-15464db0a1f8</t>
         </is>
       </c>
       <c r="T61" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/0c47939e767d716fe085cc41c86d91be28f9df1a.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/965ce572fe0c064509727c2dbba58751771f36b4.jpg</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296184</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296209</t>
         </is>
       </c>
       <c r="W61" t="inlineStr">
@@ -7905,7 +7905,7 @@
       <c r="AB61" t="inlineStr"/>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/79185d0c-7fa3-2efd-863e-93927e137a23/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/a5e4d339-47a5-92a8-3fb3-15464db0a1f8/manifest</t>
         </is>
       </c>
       <c r="AD61" t="inlineStr"/>
@@ -7913,52 +7913,52 @@
       <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="inlineStr"/>
       <c r="AH61" t="n">
-        <v>34</v>
+        <v>64</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>名家短冊 [1]</t>
+          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [10]</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>A00:4277</t>
+          <t>A00:6257</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>メイカ タンザク</t>
+          <t>レキダイ ザンケツ ニッキ</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>慶運</t>
+          <t>黒川 春村</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>慶運 [ほか自筆]</t>
+          <t>[書写者不明]</t>
         </is>
       </c>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr">
         <is>
-          <t>[鎌倉時代-江戸前期]</t>
+          <t>[安政5 (1858)]</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr">
         <is>
-          <t>折本|書名及び巻冊次は題簽による|2の筆者: 慶運 牡丹花, 了流, 宗長, 兼載, 宗碩, 宗牧, 一竿, 正廣, 正般, 祖田, 堯憲, 宗二, 利盛, 増春, 了向, 榮弘, 梅雪, 宗栁, 等惠, 宗訊, 宗養, 乘阿, 兼如, 壽慶, 意運, 本阿彌光悦, 松花堂昭乘, 紹巴, 玄仍, 玄仲, 玄陳, 玄的, 里村玄祥, 昌叱, 昌琢, 昌俔, 昌程, 昌隱, 昌通|3の筆者: 祐守, 祐夏, 詮平, 直國, 興國, 隆國, 武光, 祐範, 宗純, 等貴,  順, 最嶽, 策彦, 幽之, 應其, 堯然, 尊道, 尊應, 尊朝, 道永, 弘覺, 良俊, 道増, 道應, 道興, 藤之, 立承, 性舜, 義俊, 空性, 尊譽, 揚, 道澄, 興意, 道晃|4の筆者: 有三, 他阿, 教, 尊雅, 應猷, 秀順, 可ト, 圓祐, 道順, 実如, 兼俊, 公助, 應祐, 公順, 空慶, 看世, 定信, 玄桂, 道三, 道春, 永喜, 豊永, 葉由, 常弘|2: 古筆切40枚, 極札43枚|3: 古筆切36枚, 極札36枚|4: 古筆切28枚, 極札20枚|毎半面古筆切2枚|原104枚短冊を3帖に合綴|印記: 「順」, 「最嶽」|極印: 「琴山」, 「栄」(古筆了栄)|折り目破損あり</t>
+          <t>写本|責任表示及び書写年は『日本古典籍総合目録データベース』による|内容: 6: 光明院御記, 後光嚴院御記, 後小松院宸記, 天聴集. 28: 参議藤定長卿記 : 稱山丞記. 37: 定高卿記, 晴御会部類記, 家光卿御記, 權中納言平範輔卿記. 38: 左大史小槻季継記, 後堀川安貞二年放生會(実基公記), 石清水八幡宮, 弁官拝賀次第. 39: 大外記師光記, 資季卿記, 荒凉記, 忠高卿記. 40: 冷泉公相公記, 勝延法眼記 : 東寺大行事, 後中記 : 小路中納言資頼卿記葉室. 41: 中光記, 師兼記, 陽龍記. 42: 大宮司長則記, 口筆 : 實經, 顕朝卿記, 鴨御幸記. 43: 寳治二年記, 深心院關白記, 藤公親記, 照念院関白兼平公記. 44: 頼親記, 亀山殿行幸記 : 雅言卿記, 兼基公記. 45: 大嘗會御禊節下次第, 建治三年丁丑日記 : 三善康有, 建治四年正月廿一日 : 徳大寺大相國公孝記, 冬定卿記, 左大史小槻兼文記|内容: 46: 經任卿記, 前豊前守藤憲説記, 實兼公記. 47: 継塵記抄出. 48: 管見記, 公衡公記, 大外記師顕記, 大外記中原師淳記. 49: 真光院禪助僧正記, 吉田内府卿記. 50: 定清記, 叅議雅俊卿記, 太政大臣(公守公)御上表雜事, 仙洞御灌頂日記, 正安二年八月十一日於仙洞被始行熾盛光法, 正安三年御譲位記. 51: 實躬卿記. 52: 公茂公記, 冬平公記, 隆長卿記. 53: 忠教公記, 官記, 正三位長基卿記, 北面秀長記, 大外記中原師右記. 54: 文保元年, 日野中納言資朝卿記, 洞院大納言公敏卿記. 55: 隆蔭卿記, 文保三年記, 尹大納言師賢卿記, 革命記, 立倚子記, 萬里小路中納言藤藤房卿記|内容: 56: 資名卿記, 公秀公記, 一條家記装束抄出, 頼定卿記. 63: 松亞記, 日野大納言時光卿記, 後八條内府實継公記. 74: 成恩寺関白記. 78: 山科家礼記. 82: 諒闇記 : 後成恩寺殿, 宗典僧正記, 綱光公記, 贈従二位宗賢卿記, 義政公記. 84: 長禄二年戊寅正月, 見聞雜記. 87: 言國卿記. 88: 長興宿祢記, 元長卿記, 兼顕卿記, 小槻晴冨記|28末の原奥書に「右山丞記依 仰挍合書冩/享和二年四月 日撿挍保己一」とあり|50「正安二年八月十一日於仙洞被始行熾盛光法」末の原奥書に「文化十五年春二月以南山法曼院藏夲書冩之 撿挍保己一」とあり|横刷毛目表紙を使用|朱点, 朱引, 朱墨筆書き入れあり|付箋あり|蔵書印主信濃須坂藩主堀直格の命によって編集された古記録|他の原本は関東大震災により焼失|極札に「桂壽」(6), 「尚信」(53)との極書, 「武清」(44, 53), 「永海」(51), 「了伴」(52), 「了甫」(74), 「定時」(84, 88)との極印あり|印記: 「花廼家文庫」, 「墨阪十一代主寫藏記」(堀直格(1806-1880)), 「東京大學法理文學部書庫所藏」, 「閲覧室用 FOR USE IN THE READING ROOM」|虫損あり</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -7974,12 +7974,12 @@
       <c r="O62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/1469b736-a0ee-61aa-1e00-7a2cfa949411.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/941cae96-2884-09d1-316d-978da0fc83f5.json</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>1469b736-a0ee-61aa-1e00-7a2cfa949411</t>
+          <t>941cae96-2884-09d1-316d-978da0fc83f5</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
@@ -7989,7 +7989,7 @@
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/1469b736-a0ee-61aa-1e00-7a2cfa949411</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/941cae96-2884-09d1-316d-978da0fc83f5</t>
         </is>
       </c>
       <c r="T62" t="inlineStr">
@@ -7999,12 +7999,12 @@
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/7693d9aa48dbd471c84817ef0239807a5e246d64.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/9b2119b5a8cb266e4d44bebff61cd8b5383a810e.jpg</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296185</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296210</t>
         </is>
       </c>
       <c r="W62" t="inlineStr">
@@ -8027,7 +8027,7 @@
       <c r="AB62" t="inlineStr"/>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/1469b736-a0ee-61aa-1e00-7a2cfa949411/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/941cae96-2884-09d1-316d-978da0fc83f5/manifest</t>
         </is>
       </c>
       <c r="AD62" t="inlineStr"/>
@@ -8035,52 +8035,52 @@
       <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="inlineStr"/>
       <c r="AH62" t="n">
-        <v>27</v>
+        <v>70</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>名家短冊 [2]</t>
+          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [11]</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>A00:4277</t>
+          <t>A00:6257</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>メイカ タンザク</t>
+          <t>レキダイ ザンケツ ニッキ</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>慶運</t>
+          <t>黒川 春村</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>慶運 [ほか自筆]</t>
+          <t>[書写者不明]</t>
         </is>
       </c>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr">
         <is>
-          <t>[鎌倉時代-江戸前期]</t>
+          <t>[安政5 (1858)]</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr">
         <is>
-          <t>折本|書名及び巻冊次は題簽による|2の筆者: 慶運 牡丹花, 了流, 宗長, 兼載, 宗碩, 宗牧, 一竿, 正廣, 正般, 祖田, 堯憲, 宗二, 利盛, 増春, 了向, 榮弘, 梅雪, 宗栁, 等惠, 宗訊, 宗養, 乘阿, 兼如, 壽慶, 意運, 本阿彌光悦, 松花堂昭乘, 紹巴, 玄仍, 玄仲, 玄陳, 玄的, 里村玄祥, 昌叱, 昌琢, 昌俔, 昌程, 昌隱, 昌通|3の筆者: 祐守, 祐夏, 詮平, 直國, 興國, 隆國, 武光, 祐範, 宗純, 等貴,  順, 最嶽, 策彦, 幽之, 應其, 堯然, 尊道, 尊應, 尊朝, 道永, 弘覺, 良俊, 道増, 道應, 道興, 藤之, 立承, 性舜, 義俊, 空性, 尊譽, 揚, 道澄, 興意, 道晃|4の筆者: 有三, 他阿, 教, 尊雅, 應猷, 秀順, 可ト, 圓祐, 道順, 実如, 兼俊, 公助, 應祐, 公順, 空慶, 看世, 定信, 玄桂, 道三, 道春, 永喜, 豊永, 葉由, 常弘|2: 古筆切40枚, 極札43枚|3: 古筆切36枚, 極札36枚|4: 古筆切28枚, 極札20枚|毎半面古筆切2枚|原104枚短冊を3帖に合綴|印記: 「順」, 「最嶽」|極印: 「琴山」, 「栄」(古筆了栄)|折り目破損あり</t>
+          <t>写本|責任表示及び書写年は『日本古典籍総合目録データベース』による|内容: 6: 光明院御記, 後光嚴院御記, 後小松院宸記, 天聴集. 28: 参議藤定長卿記 : 稱山丞記. 37: 定高卿記, 晴御会部類記, 家光卿御記, 權中納言平範輔卿記. 38: 左大史小槻季継記, 後堀川安貞二年放生會(実基公記), 石清水八幡宮, 弁官拝賀次第. 39: 大外記師光記, 資季卿記, 荒凉記, 忠高卿記. 40: 冷泉公相公記, 勝延法眼記 : 東寺大行事, 後中記 : 小路中納言資頼卿記葉室. 41: 中光記, 師兼記, 陽龍記. 42: 大宮司長則記, 口筆 : 實經, 顕朝卿記, 鴨御幸記. 43: 寳治二年記, 深心院關白記, 藤公親記, 照念院関白兼平公記. 44: 頼親記, 亀山殿行幸記 : 雅言卿記, 兼基公記. 45: 大嘗會御禊節下次第, 建治三年丁丑日記 : 三善康有, 建治四年正月廿一日 : 徳大寺大相國公孝記, 冬定卿記, 左大史小槻兼文記|内容: 46: 經任卿記, 前豊前守藤憲説記, 實兼公記. 47: 継塵記抄出. 48: 管見記, 公衡公記, 大外記師顕記, 大外記中原師淳記. 49: 真光院禪助僧正記, 吉田内府卿記. 50: 定清記, 叅議雅俊卿記, 太政大臣(公守公)御上表雜事, 仙洞御灌頂日記, 正安二年八月十一日於仙洞被始行熾盛光法, 正安三年御譲位記. 51: 實躬卿記. 52: 公茂公記, 冬平公記, 隆長卿記. 53: 忠教公記, 官記, 正三位長基卿記, 北面秀長記, 大外記中原師右記. 54: 文保元年, 日野中納言資朝卿記, 洞院大納言公敏卿記. 55: 隆蔭卿記, 文保三年記, 尹大納言師賢卿記, 革命記, 立倚子記, 萬里小路中納言藤藤房卿記|内容: 56: 資名卿記, 公秀公記, 一條家記装束抄出, 頼定卿記. 63: 松亞記, 日野大納言時光卿記, 後八條内府實継公記. 74: 成恩寺関白記. 78: 山科家礼記. 82: 諒闇記 : 後成恩寺殿, 宗典僧正記, 綱光公記, 贈従二位宗賢卿記, 義政公記. 84: 長禄二年戊寅正月, 見聞雜記. 87: 言國卿記. 88: 長興宿祢記, 元長卿記, 兼顕卿記, 小槻晴冨記|28末の原奥書に「右山丞記依 仰挍合書冩/享和二年四月 日撿挍保己一」とあり|50「正安二年八月十一日於仙洞被始行熾盛光法」末の原奥書に「文化十五年春二月以南山法曼院藏夲書冩之 撿挍保己一」とあり|横刷毛目表紙を使用|朱点, 朱引, 朱墨筆書き入れあり|付箋あり|蔵書印主信濃須坂藩主堀直格の命によって編集された古記録|他の原本は関東大震災により焼失|極札に「桂壽」(6), 「尚信」(53)との極書, 「武清」(44, 53), 「永海」(51), 「了伴」(52), 「了甫」(74), 「定時」(84, 88)との極印あり|印記: 「花廼家文庫」, 「墨阪十一代主寫藏記」(堀直格(1806-1880)), 「東京大學法理文學部書庫所藏」, 「閲覧室用 FOR USE IN THE READING ROOM」|虫損あり</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -8096,12 +8096,12 @@
       <c r="O63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/53041b9e-294f-71af-3d1a-e305956f5560.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/b6a83876-30df-48c8-9c3f-3a68e8429d62.json</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>53041b9e-294f-71af-3d1a-e305956f5560</t>
+          <t>b6a83876-30df-48c8-9c3f-3a68e8429d62</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
@@ -8111,7 +8111,7 @@
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/53041b9e-294f-71af-3d1a-e305956f5560</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/b6a83876-30df-48c8-9c3f-3a68e8429d62</t>
         </is>
       </c>
       <c r="T63" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/11759cf221ad40925619344bacc4027d06e015ce.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/7f6bf7c4b28ea807212c7ead3da50d50601c8ed1.jpg</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296186</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296211</t>
         </is>
       </c>
       <c r="W63" t="inlineStr">
@@ -8149,7 +8149,7 @@
       <c r="AB63" t="inlineStr"/>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/53041b9e-294f-71af-3d1a-e305956f5560/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/b6a83876-30df-48c8-9c3f-3a68e8429d62/manifest</t>
         </is>
       </c>
       <c r="AD63" t="inlineStr"/>
@@ -8157,52 +8157,52 @@
       <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="inlineStr"/>
       <c r="AH63" t="n">
-        <v>24</v>
+        <v>64</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>名家短冊 [3]</t>
+          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [12]</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>A00:4277</t>
+          <t>A00:6257</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>メイカ タンザク</t>
+          <t>レキダイ ザンケツ ニッキ</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>慶運</t>
+          <t>黒川 春村</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>慶運 [ほか自筆]</t>
+          <t>[書写者不明]</t>
         </is>
       </c>
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr">
         <is>
-          <t>[鎌倉時代-江戸前期]</t>
+          <t>[安政5 (1858)]</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr">
         <is>
-          <t>折本|書名及び巻冊次は題簽による|2の筆者: 慶運 牡丹花, 了流, 宗長, 兼載, 宗碩, 宗牧, 一竿, 正廣, 正般, 祖田, 堯憲, 宗二, 利盛, 増春, 了向, 榮弘, 梅雪, 宗栁, 等惠, 宗訊, 宗養, 乘阿, 兼如, 壽慶, 意運, 本阿彌光悦, 松花堂昭乘, 紹巴, 玄仍, 玄仲, 玄陳, 玄的, 里村玄祥, 昌叱, 昌琢, 昌俔, 昌程, 昌隱, 昌通|3の筆者: 祐守, 祐夏, 詮平, 直國, 興國, 隆國, 武光, 祐範, 宗純, 等貴,  順, 最嶽, 策彦, 幽之, 應其, 堯然, 尊道, 尊應, 尊朝, 道永, 弘覺, 良俊, 道増, 道應, 道興, 藤之, 立承, 性舜, 義俊, 空性, 尊譽, 揚, 道澄, 興意, 道晃|4の筆者: 有三, 他阿, 教, 尊雅, 應猷, 秀順, 可ト, 圓祐, 道順, 実如, 兼俊, 公助, 應祐, 公順, 空慶, 看世, 定信, 玄桂, 道三, 道春, 永喜, 豊永, 葉由, 常弘|2: 古筆切40枚, 極札43枚|3: 古筆切36枚, 極札36枚|4: 古筆切28枚, 極札20枚|毎半面古筆切2枚|原104枚短冊を3帖に合綴|印記: 「順」, 「最嶽」|極印: 「琴山」, 「栄」(古筆了栄)|折り目破損あり</t>
+          <t>写本|責任表示及び書写年は『日本古典籍総合目録データベース』による|内容: 6: 光明院御記, 後光嚴院御記, 後小松院宸記, 天聴集. 28: 参議藤定長卿記 : 稱山丞記. 37: 定高卿記, 晴御会部類記, 家光卿御記, 權中納言平範輔卿記. 38: 左大史小槻季継記, 後堀川安貞二年放生會(実基公記), 石清水八幡宮, 弁官拝賀次第. 39: 大外記師光記, 資季卿記, 荒凉記, 忠高卿記. 40: 冷泉公相公記, 勝延法眼記 : 東寺大行事, 後中記 : 小路中納言資頼卿記葉室. 41: 中光記, 師兼記, 陽龍記. 42: 大宮司長則記, 口筆 : 實經, 顕朝卿記, 鴨御幸記. 43: 寳治二年記, 深心院關白記, 藤公親記, 照念院関白兼平公記. 44: 頼親記, 亀山殿行幸記 : 雅言卿記, 兼基公記. 45: 大嘗會御禊節下次第, 建治三年丁丑日記 : 三善康有, 建治四年正月廿一日 : 徳大寺大相國公孝記, 冬定卿記, 左大史小槻兼文記|内容: 46: 經任卿記, 前豊前守藤憲説記, 實兼公記. 47: 継塵記抄出. 48: 管見記, 公衡公記, 大外記師顕記, 大外記中原師淳記. 49: 真光院禪助僧正記, 吉田内府卿記. 50: 定清記, 叅議雅俊卿記, 太政大臣(公守公)御上表雜事, 仙洞御灌頂日記, 正安二年八月十一日於仙洞被始行熾盛光法, 正安三年御譲位記. 51: 實躬卿記. 52: 公茂公記, 冬平公記, 隆長卿記. 53: 忠教公記, 官記, 正三位長基卿記, 北面秀長記, 大外記中原師右記. 54: 文保元年, 日野中納言資朝卿記, 洞院大納言公敏卿記. 55: 隆蔭卿記, 文保三年記, 尹大納言師賢卿記, 革命記, 立倚子記, 萬里小路中納言藤藤房卿記|内容: 56: 資名卿記, 公秀公記, 一條家記装束抄出, 頼定卿記. 63: 松亞記, 日野大納言時光卿記, 後八條内府實継公記. 74: 成恩寺関白記. 78: 山科家礼記. 82: 諒闇記 : 後成恩寺殿, 宗典僧正記, 綱光公記, 贈従二位宗賢卿記, 義政公記. 84: 長禄二年戊寅正月, 見聞雜記. 87: 言國卿記. 88: 長興宿祢記, 元長卿記, 兼顕卿記, 小槻晴冨記|28末の原奥書に「右山丞記依 仰挍合書冩/享和二年四月 日撿挍保己一」とあり|50「正安二年八月十一日於仙洞被始行熾盛光法」末の原奥書に「文化十五年春二月以南山法曼院藏夲書冩之 撿挍保己一」とあり|横刷毛目表紙を使用|朱点, 朱引, 朱墨筆書き入れあり|付箋あり|蔵書印主信濃須坂藩主堀直格の命によって編集された古記録|他の原本は関東大震災により焼失|極札に「桂壽」(6), 「尚信」(53)との極書, 「武清」(44, 53), 「永海」(51), 「了伴」(52), 「了甫」(74), 「定時」(84, 88)との極印あり|印記: 「花廼家文庫」, 「墨阪十一代主寫藏記」(堀直格(1806-1880)), 「東京大學法理文學部書庫所藏」, 「閲覧室用 FOR USE IN THE READING ROOM」|虫損あり</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -8218,12 +8218,12 @@
       <c r="O64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/3d4ceb9b-9516-779a-7ced-f893e9d93b4e.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/d199046f-6bd4-6ca0-a0bf-c29ad3c19949.json</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>3d4ceb9b-9516-779a-7ced-f893e9d93b4e</t>
+          <t>d199046f-6bd4-6ca0-a0bf-c29ad3c19949</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
@@ -8233,7 +8233,7 @@
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/3d4ceb9b-9516-779a-7ced-f893e9d93b4e</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/d199046f-6bd4-6ca0-a0bf-c29ad3c19949</t>
         </is>
       </c>
       <c r="T64" t="inlineStr">
@@ -8243,12 +8243,12 @@
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/8fd1defea23c7c93fc4d908835c1fea38040580e.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/4cbd0825007ec7d3c89014f55d3b6825a8214769.jpg</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296187</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296212</t>
         </is>
       </c>
       <c r="W64" t="inlineStr">
@@ -8271,7 +8271,7 @@
       <c r="AB64" t="inlineStr"/>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/3d4ceb9b-9516-779a-7ced-f893e9d93b4e/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/d199046f-6bd4-6ca0-a0bf-c29ad3c19949/manifest</t>
         </is>
       </c>
       <c r="AD64" t="inlineStr"/>
@@ -8279,40 +8279,40 @@
       <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="inlineStr"/>
       <c r="AH64" t="n">
-        <v>24</v>
+        <v>77</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>御成敗式目絵鈔</t>
+          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [13]</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>A00:4737</t>
+          <t>A00:6257</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>ゴセイバイ シキモク エショウ</t>
+          <t>レキダイ ザンケツ ニッキ</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>岡本 竹籔</t>
+          <t>黒川 春村</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>岡夲竹籔 : 松川半山 [書]</t>
+          <t>[書写者不明]</t>
         </is>
       </c>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr">
         <is>
-          <t>[幕末期]</t>
+          <t>[安政5 (1858)]</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -8324,7 +8324,7 @@
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr">
         <is>
-          <t>写本|序首の書名: 御成敗式目繪鈔|版心の書名: 式目繪鈔|題簽に「板下本」とあり|巻末に「筆工 岡夲竹籔/画工 松川半山」とあり(「岡本」, 「憲道」, 「義卿」, 「翠宋堂長」との落款朱印あり)|巻末広告に「山田賞月堂先生筆 無雙用文章大成 全一冊」とあり|四周単辺有界2段5行, 内匡廓: 22.3×16.4cm, 白口無魚尾|頭書あり|付訓あり</t>
+          <t>写本|責任表示及び書写年は『日本古典籍総合目録データベース』による|内容: 6: 光明院御記, 後光嚴院御記, 後小松院宸記, 天聴集. 28: 参議藤定長卿記 : 稱山丞記. 37: 定高卿記, 晴御会部類記, 家光卿御記, 權中納言平範輔卿記. 38: 左大史小槻季継記, 後堀川安貞二年放生會(実基公記), 石清水八幡宮, 弁官拝賀次第. 39: 大外記師光記, 資季卿記, 荒凉記, 忠高卿記. 40: 冷泉公相公記, 勝延法眼記 : 東寺大行事, 後中記 : 小路中納言資頼卿記葉室. 41: 中光記, 師兼記, 陽龍記. 42: 大宮司長則記, 口筆 : 實經, 顕朝卿記, 鴨御幸記. 43: 寳治二年記, 深心院關白記, 藤公親記, 照念院関白兼平公記. 44: 頼親記, 亀山殿行幸記 : 雅言卿記, 兼基公記. 45: 大嘗會御禊節下次第, 建治三年丁丑日記 : 三善康有, 建治四年正月廿一日 : 徳大寺大相國公孝記, 冬定卿記, 左大史小槻兼文記|内容: 46: 經任卿記, 前豊前守藤憲説記, 實兼公記. 47: 継塵記抄出. 48: 管見記, 公衡公記, 大外記師顕記, 大外記中原師淳記. 49: 真光院禪助僧正記, 吉田内府卿記. 50: 定清記, 叅議雅俊卿記, 太政大臣(公守公)御上表雜事, 仙洞御灌頂日記, 正安二年八月十一日於仙洞被始行熾盛光法, 正安三年御譲位記. 51: 實躬卿記. 52: 公茂公記, 冬平公記, 隆長卿記. 53: 忠教公記, 官記, 正三位長基卿記, 北面秀長記, 大外記中原師右記. 54: 文保元年, 日野中納言資朝卿記, 洞院大納言公敏卿記. 55: 隆蔭卿記, 文保三年記, 尹大納言師賢卿記, 革命記, 立倚子記, 萬里小路中納言藤藤房卿記|内容: 56: 資名卿記, 公秀公記, 一條家記装束抄出, 頼定卿記. 63: 松亞記, 日野大納言時光卿記, 後八條内府實継公記. 74: 成恩寺関白記. 78: 山科家礼記. 82: 諒闇記 : 後成恩寺殿, 宗典僧正記, 綱光公記, 贈従二位宗賢卿記, 義政公記. 84: 長禄二年戊寅正月, 見聞雜記. 87: 言國卿記. 88: 長興宿祢記, 元長卿記, 兼顕卿記, 小槻晴冨記|28末の原奥書に「右山丞記依 仰挍合書冩/享和二年四月 日撿挍保己一」とあり|50「正安二年八月十一日於仙洞被始行熾盛光法」末の原奥書に「文化十五年春二月以南山法曼院藏夲書冩之 撿挍保己一」とあり|横刷毛目表紙を使用|朱点, 朱引, 朱墨筆書き入れあり|付箋あり|蔵書印主信濃須坂藩主堀直格の命によって編集された古記録|他の原本は関東大震災により焼失|極札に「桂壽」(6), 「尚信」(53)との極書, 「武清」(44, 53), 「永海」(51), 「了伴」(52), 「了甫」(74), 「定時」(84, 88)との極印あり|印記: 「花廼家文庫」, 「墨阪十一代主寫藏記」(堀直格(1806-1880)), 「東京大學法理文學部書庫所藏」, 「閲覧室用 FOR USE IN THE READING ROOM」|虫損あり</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -8340,12 +8340,12 @@
       <c r="O65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/463ab967-60a4-9ff1-3ef2-d2dee79b5315.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/1b5c5c7f-4892-39f9-4e5e-479a8e921be2.json</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>463ab967-60a4-9ff1-3ef2-d2dee79b5315</t>
+          <t>1b5c5c7f-4892-39f9-4e5e-479a8e921be2</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
@@ -8355,7 +8355,7 @@
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/463ab967-60a4-9ff1-3ef2-d2dee79b5315</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/1b5c5c7f-4892-39f9-4e5e-479a8e921be2</t>
         </is>
       </c>
       <c r="T65" t="inlineStr">
@@ -8365,12 +8365,12 @@
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/e0977d9ba261ea59386ce9f5104a412a5dccaf3f.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/95aeca9c3732100e9d926fc7a9cb98fba20b6444.jpg</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296188</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296213</t>
         </is>
       </c>
       <c r="W65" t="inlineStr">
@@ -8393,7 +8393,7 @@
       <c r="AB65" t="inlineStr"/>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/463ab967-60a4-9ff1-3ef2-d2dee79b5315/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/1b5c5c7f-4892-39f9-4e5e-479a8e921be2/manifest</t>
         </is>
       </c>
       <c r="AD65" t="inlineStr"/>
@@ -8401,40 +8401,40 @@
       <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="inlineStr"/>
       <c r="AH65" t="n">
-        <v>59</v>
+        <v>74</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>金界入壇作法</t>
+          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [14]</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>A00:5975</t>
+          <t>A00:6257</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>コンカイ ニュウダン サホウ</t>
+          <t>レキダイ ザンケツ ニッキ</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>良円</t>
+          <t>黒川 春村</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>良円 [写]</t>
+          <t>[書写者不明]</t>
         </is>
       </c>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr">
         <is>
-          <t>寛元元 [1243] 奥書</t>
+          <t>[安政5 (1858)]</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -8446,7 +8446,7 @@
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr">
         <is>
-          <t>写本|奥書に「寛元々年五月七日以先師法印御夲於常住護国院房以他筆書冩校點了良円」とあり|送り仮名, 返点あり|淡墨界の料紙を使用(界匡廓: 23.7×2.5cm)|貼紙あり|巻子本|箱入り|破損, 虫損あり (裏打ち補修あり)</t>
+          <t>写本|責任表示及び書写年は『日本古典籍総合目録データベース』による|内容: 6: 光明院御記, 後光嚴院御記, 後小松院宸記, 天聴集. 28: 参議藤定長卿記 : 稱山丞記. 37: 定高卿記, 晴御会部類記, 家光卿御記, 權中納言平範輔卿記. 38: 左大史小槻季継記, 後堀川安貞二年放生會(実基公記), 石清水八幡宮, 弁官拝賀次第. 39: 大外記師光記, 資季卿記, 荒凉記, 忠高卿記. 40: 冷泉公相公記, 勝延法眼記 : 東寺大行事, 後中記 : 小路中納言資頼卿記葉室. 41: 中光記, 師兼記, 陽龍記. 42: 大宮司長則記, 口筆 : 實經, 顕朝卿記, 鴨御幸記. 43: 寳治二年記, 深心院關白記, 藤公親記, 照念院関白兼平公記. 44: 頼親記, 亀山殿行幸記 : 雅言卿記, 兼基公記. 45: 大嘗會御禊節下次第, 建治三年丁丑日記 : 三善康有, 建治四年正月廿一日 : 徳大寺大相國公孝記, 冬定卿記, 左大史小槻兼文記|内容: 46: 經任卿記, 前豊前守藤憲説記, 實兼公記. 47: 継塵記抄出. 48: 管見記, 公衡公記, 大外記師顕記, 大外記中原師淳記. 49: 真光院禪助僧正記, 吉田内府卿記. 50: 定清記, 叅議雅俊卿記, 太政大臣(公守公)御上表雜事, 仙洞御灌頂日記, 正安二年八月十一日於仙洞被始行熾盛光法, 正安三年御譲位記. 51: 實躬卿記. 52: 公茂公記, 冬平公記, 隆長卿記. 53: 忠教公記, 官記, 正三位長基卿記, 北面秀長記, 大外記中原師右記. 54: 文保元年, 日野中納言資朝卿記, 洞院大納言公敏卿記. 55: 隆蔭卿記, 文保三年記, 尹大納言師賢卿記, 革命記, 立倚子記, 萬里小路中納言藤藤房卿記|内容: 56: 資名卿記, 公秀公記, 一條家記装束抄出, 頼定卿記. 63: 松亞記, 日野大納言時光卿記, 後八條内府實継公記. 74: 成恩寺関白記. 78: 山科家礼記. 82: 諒闇記 : 後成恩寺殿, 宗典僧正記, 綱光公記, 贈従二位宗賢卿記, 義政公記. 84: 長禄二年戊寅正月, 見聞雜記. 87: 言國卿記. 88: 長興宿祢記, 元長卿記, 兼顕卿記, 小槻晴冨記|28末の原奥書に「右山丞記依 仰挍合書冩/享和二年四月 日撿挍保己一」とあり|50「正安二年八月十一日於仙洞被始行熾盛光法」末の原奥書に「文化十五年春二月以南山法曼院藏夲書冩之 撿挍保己一」とあり|横刷毛目表紙を使用|朱点, 朱引, 朱墨筆書き入れあり|付箋あり|蔵書印主信濃須坂藩主堀直格の命によって編集された古記録|他の原本は関東大震災により焼失|極札に「桂壽」(6), 「尚信」(53)との極書, 「武清」(44, 53), 「永海」(51), 「了伴」(52), 「了甫」(74), 「定時」(84, 88)との極印あり|印記: 「花廼家文庫」, 「墨阪十一代主寫藏記」(堀直格(1806-1880)), 「東京大學法理文學部書庫所藏」, 「閲覧室用 FOR USE IN THE READING ROOM」|虫損あり</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -8462,12 +8462,12 @@
       <c r="O66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/ff6e2dd7-8128-3264-2081-15ad4e41857e.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/a83ab18c-4d05-492c-2121-ec90971ea54a.json</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>ff6e2dd7-8128-3264-2081-15ad4e41857e</t>
+          <t>a83ab18c-4d05-492c-2121-ec90971ea54a</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/ff6e2dd7-8128-3264-2081-15ad4e41857e</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/a83ab18c-4d05-492c-2121-ec90971ea54a</t>
         </is>
       </c>
       <c r="T66" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/7e2372f45914ea75c8d903fc80f309f16238b39f.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/b0fe976afebb52b245b298aabead8423fd0d1a6f.jpg</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296189</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296214</t>
         </is>
       </c>
       <c r="W66" t="inlineStr">
@@ -8515,7 +8515,7 @@
       <c r="AB66" t="inlineStr"/>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/ff6e2dd7-8128-3264-2081-15ad4e41857e/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/a83ab18c-4d05-492c-2121-ec90971ea54a/manifest</t>
         </is>
       </c>
       <c r="AD66" t="inlineStr"/>
@@ -8523,52 +8523,52 @@
       <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="inlineStr"/>
       <c r="AH66" t="n">
-        <v>39</v>
+        <v>59</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>玉蘂 [1]</t>
+          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [15]</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>A00:6067</t>
+          <t>A00:6257</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>ギョクズイ</t>
+          <t>レキダイ ザンケツ ニッキ</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>藤原 道家</t>
+          <t>黒川 春村</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>野宮定基 : 久世通夏 [ほか写]</t>
+          <t>[書写者不明]</t>
         </is>
       </c>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr">
         <is>
-          <t>元禄12 [1699]-宝永3 [1706] 奥書</t>
+          <t>[安政5 (1858)]</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr">
         <is>
-          <t>写本|書名及び巻冊次は表紙による|奥中の書名: 光明峯寺禅閤道家公記, 峯禅閤記, 峯摂政記, 峯入道摂政記|承元4年の原奥書に「右即位記一卷者光明峯寺禅閤自筆正記也以件本左令吾基春卿透以写之云々加挍正之 ... 永正七年夷則上浣 從一位(花押)」とあり|奥書に「右以或人夲自常州到来令書写之彼夲端書云此冊上下卷 ... 元禄第十二暦仲夏中旬 羽林左衞中郎将藤原定基丗一才」(承元3), 「右光明峯寺禅閤道家公承元二年三月五六月八月四年二三月九月十十一十二月記は借請或人之夲自常州邊来書写之加一挍了/于時元禄第十二端午節也 左中郎将藤原定基丗才」(承元4), 「右玉蘂建暦元年少弟左中将通清朝臣助筆僅加一挍原本文字不正後来得正夲可改之者也/元禄十三年九月十日 松堂閑士(花押)丗二才」(建暦元), 「右玉蘂峯禅閤記建暦二年自二月至九月一冊以或人夲自常州邊来命家僚令書写手自加挍合了/元禄十二年五月六日 左中郎将藤原定基丗一才」(建暦2年上), 「宝永二年十月一日書写畢/承久二春玉蘂以故常州牧權中納言光圀公夲謄写之于時俗務紛擾先請慈兄源亜相公所被写也今以彼夲手自馳禿筆 余識藤(花押)丗七才/同三年二月廿五日一挍了」(承久2年上), 「右峯摂政承久二年記命傭書謄冩之手自一挍了/元禄第十二嵗次著雍単閼蕤賓中旬 羽林軍左衞中郎将藤原定基丗一才」(承久2年下), 「嘉禎四年正月二月閏二月三月四月六月玉蘂先年假借故常州牧前中納言光圀夲無剋力速遂書写之功建暦元年建暦二年下承久二年上及此卷等先献慈兄亜相君写之今及数年申復彼夲謄写之 ... 宝永三年十二月念日 参議從三位行左近衞權中将藤原朝臣定基生年卅八才」(嘉禎4年)とあり|毎半葉11行注文双行|漢文体日記|拠徳川光圀本及び中院通躬鈔本謄写|朱筆書き入れあり|印記: 「定基」(野宮定基), 「野宮書印」|虫損あり (裏打ち補修あり)</t>
+          <t>写本|責任表示及び書写年は『日本古典籍総合目録データベース』による|内容: 6: 光明院御記, 後光嚴院御記, 後小松院宸記, 天聴集. 28: 参議藤定長卿記 : 稱山丞記. 37: 定高卿記, 晴御会部類記, 家光卿御記, 權中納言平範輔卿記. 38: 左大史小槻季継記, 後堀川安貞二年放生會(実基公記), 石清水八幡宮, 弁官拝賀次第. 39: 大外記師光記, 資季卿記, 荒凉記, 忠高卿記. 40: 冷泉公相公記, 勝延法眼記 : 東寺大行事, 後中記 : 小路中納言資頼卿記葉室. 41: 中光記, 師兼記, 陽龍記. 42: 大宮司長則記, 口筆 : 實經, 顕朝卿記, 鴨御幸記. 43: 寳治二年記, 深心院關白記, 藤公親記, 照念院関白兼平公記. 44: 頼親記, 亀山殿行幸記 : 雅言卿記, 兼基公記. 45: 大嘗會御禊節下次第, 建治三年丁丑日記 : 三善康有, 建治四年正月廿一日 : 徳大寺大相國公孝記, 冬定卿記, 左大史小槻兼文記|内容: 46: 經任卿記, 前豊前守藤憲説記, 實兼公記. 47: 継塵記抄出. 48: 管見記, 公衡公記, 大外記師顕記, 大外記中原師淳記. 49: 真光院禪助僧正記, 吉田内府卿記. 50: 定清記, 叅議雅俊卿記, 太政大臣(公守公)御上表雜事, 仙洞御灌頂日記, 正安二年八月十一日於仙洞被始行熾盛光法, 正安三年御譲位記. 51: 實躬卿記. 52: 公茂公記, 冬平公記, 隆長卿記. 53: 忠教公記, 官記, 正三位長基卿記, 北面秀長記, 大外記中原師右記. 54: 文保元年, 日野中納言資朝卿記, 洞院大納言公敏卿記. 55: 隆蔭卿記, 文保三年記, 尹大納言師賢卿記, 革命記, 立倚子記, 萬里小路中納言藤藤房卿記|内容: 56: 資名卿記, 公秀公記, 一條家記装束抄出, 頼定卿記. 63: 松亞記, 日野大納言時光卿記, 後八條内府實継公記. 74: 成恩寺関白記. 78: 山科家礼記. 82: 諒闇記 : 後成恩寺殿, 宗典僧正記, 綱光公記, 贈従二位宗賢卿記, 義政公記. 84: 長禄二年戊寅正月, 見聞雜記. 87: 言國卿記. 88: 長興宿祢記, 元長卿記, 兼顕卿記, 小槻晴冨記|28末の原奥書に「右山丞記依 仰挍合書冩/享和二年四月 日撿挍保己一」とあり|50「正安二年八月十一日於仙洞被始行熾盛光法」末の原奥書に「文化十五年春二月以南山法曼院藏夲書冩之 撿挍保己一」とあり|横刷毛目表紙を使用|朱点, 朱引, 朱墨筆書き入れあり|付箋あり|蔵書印主信濃須坂藩主堀直格の命によって編集された古記録|他の原本は関東大震災により焼失|極札に「桂壽」(6), 「尚信」(53)との極書, 「武清」(44, 53), 「永海」(51), 「了伴」(52), 「了甫」(74), 「定時」(84, 88)との極印あり|印記: 「花廼家文庫」, 「墨阪十一代主寫藏記」(堀直格(1806-1880)), 「東京大學法理文學部書庫所藏」, 「閲覧室用 FOR USE IN THE READING ROOM」|虫損あり</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -8584,12 +8584,12 @@
       <c r="O67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/b13a7a09-88d0-62d3-44e5-379780395f17.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/acf20dd5-459a-5438-8dd8-cbc11fe122bf.json</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>b13a7a09-88d0-62d3-44e5-379780395f17</t>
+          <t>acf20dd5-459a-5438-8dd8-cbc11fe122bf</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
@@ -8599,7 +8599,7 @@
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/b13a7a09-88d0-62d3-44e5-379780395f17</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/acf20dd5-459a-5438-8dd8-cbc11fe122bf</t>
         </is>
       </c>
       <c r="T67" t="inlineStr">
@@ -8609,12 +8609,12 @@
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/f7ae1bd23dec8f323199a9add81e315f1a653d24.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/cfeece07d99889e30589237e6d78b4933a56b7d6.jpg</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296190</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296215</t>
         </is>
       </c>
       <c r="W67" t="inlineStr">
@@ -8637,7 +8637,7 @@
       <c r="AB67" t="inlineStr"/>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/b13a7a09-88d0-62d3-44e5-379780395f17/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/acf20dd5-459a-5438-8dd8-cbc11fe122bf/manifest</t>
         </is>
       </c>
       <c r="AD67" t="inlineStr"/>
@@ -8645,52 +8645,52 @@
       <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="inlineStr"/>
       <c r="AH67" t="n">
-        <v>129</v>
+        <v>64</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>玉蘂 [2]</t>
+          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [16]</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>A00:6067</t>
+          <t>A00:6257</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>ギョクズイ</t>
+          <t>レキダイ ザンケツ ニッキ</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>藤原 道家</t>
+          <t>黒川 春村</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>野宮定基 : 久世通夏 [ほか写]</t>
+          <t>[書写者不明]</t>
         </is>
       </c>
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr">
         <is>
-          <t>元禄12 [1699]-宝永3 [1706] 奥書</t>
+          <t>[安政5 (1858)]</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr">
         <is>
-          <t>写本|書名及び巻冊次は表紙による|奥中の書名: 光明峯寺禅閤道家公記, 峯禅閤記, 峯摂政記, 峯入道摂政記|承元4年の原奥書に「右即位記一卷者光明峯寺禅閤自筆正記也以件本左令吾基春卿透以写之云々加挍正之 ... 永正七年夷則上浣 從一位(花押)」とあり|奥書に「右以或人夲自常州到来令書写之彼夲端書云此冊上下卷 ... 元禄第十二暦仲夏中旬 羽林左衞中郎将藤原定基丗一才」(承元3), 「右光明峯寺禅閤道家公承元二年三月五六月八月四年二三月九月十十一十二月記は借請或人之夲自常州邊来書写之加一挍了/于時元禄第十二端午節也 左中郎将藤原定基丗才」(承元4), 「右玉蘂建暦元年少弟左中将通清朝臣助筆僅加一挍原本文字不正後来得正夲可改之者也/元禄十三年九月十日 松堂閑士(花押)丗二才」(建暦元), 「右玉蘂峯禅閤記建暦二年自二月至九月一冊以或人夲自常州邊来命家僚令書写手自加挍合了/元禄十二年五月六日 左中郎将藤原定基丗一才」(建暦2年上), 「宝永二年十月一日書写畢/承久二春玉蘂以故常州牧權中納言光圀公夲謄写之于時俗務紛擾先請慈兄源亜相公所被写也今以彼夲手自馳禿筆 余識藤(花押)丗七才/同三年二月廿五日一挍了」(承久2年上), 「右峯摂政承久二年記命傭書謄冩之手自一挍了/元禄第十二嵗次著雍単閼蕤賓中旬 羽林軍左衞中郎将藤原定基丗一才」(承久2年下), 「嘉禎四年正月二月閏二月三月四月六月玉蘂先年假借故常州牧前中納言光圀夲無剋力速遂書写之功建暦元年建暦二年下承久二年上及此卷等先献慈兄亜相君写之今及数年申復彼夲謄写之 ... 宝永三年十二月念日 参議從三位行左近衞權中将藤原朝臣定基生年卅八才」(嘉禎4年)とあり|毎半葉11行注文双行|漢文体日記|拠徳川光圀本及び中院通躬鈔本謄写|朱筆書き入れあり|印記: 「定基」(野宮定基), 「野宮書印」|虫損あり (裏打ち補修あり)</t>
+          <t>写本|責任表示及び書写年は『日本古典籍総合目録データベース』による|内容: 6: 光明院御記, 後光嚴院御記, 後小松院宸記, 天聴集. 28: 参議藤定長卿記 : 稱山丞記. 37: 定高卿記, 晴御会部類記, 家光卿御記, 權中納言平範輔卿記. 38: 左大史小槻季継記, 後堀川安貞二年放生會(実基公記), 石清水八幡宮, 弁官拝賀次第. 39: 大外記師光記, 資季卿記, 荒凉記, 忠高卿記. 40: 冷泉公相公記, 勝延法眼記 : 東寺大行事, 後中記 : 小路中納言資頼卿記葉室. 41: 中光記, 師兼記, 陽龍記. 42: 大宮司長則記, 口筆 : 實經, 顕朝卿記, 鴨御幸記. 43: 寳治二年記, 深心院關白記, 藤公親記, 照念院関白兼平公記. 44: 頼親記, 亀山殿行幸記 : 雅言卿記, 兼基公記. 45: 大嘗會御禊節下次第, 建治三年丁丑日記 : 三善康有, 建治四年正月廿一日 : 徳大寺大相國公孝記, 冬定卿記, 左大史小槻兼文記|内容: 46: 經任卿記, 前豊前守藤憲説記, 實兼公記. 47: 継塵記抄出. 48: 管見記, 公衡公記, 大外記師顕記, 大外記中原師淳記. 49: 真光院禪助僧正記, 吉田内府卿記. 50: 定清記, 叅議雅俊卿記, 太政大臣(公守公)御上表雜事, 仙洞御灌頂日記, 正安二年八月十一日於仙洞被始行熾盛光法, 正安三年御譲位記. 51: 實躬卿記. 52: 公茂公記, 冬平公記, 隆長卿記. 53: 忠教公記, 官記, 正三位長基卿記, 北面秀長記, 大外記中原師右記. 54: 文保元年, 日野中納言資朝卿記, 洞院大納言公敏卿記. 55: 隆蔭卿記, 文保三年記, 尹大納言師賢卿記, 革命記, 立倚子記, 萬里小路中納言藤藤房卿記|内容: 56: 資名卿記, 公秀公記, 一條家記装束抄出, 頼定卿記. 63: 松亞記, 日野大納言時光卿記, 後八條内府實継公記. 74: 成恩寺関白記. 78: 山科家礼記. 82: 諒闇記 : 後成恩寺殿, 宗典僧正記, 綱光公記, 贈従二位宗賢卿記, 義政公記. 84: 長禄二年戊寅正月, 見聞雜記. 87: 言國卿記. 88: 長興宿祢記, 元長卿記, 兼顕卿記, 小槻晴冨記|28末の原奥書に「右山丞記依 仰挍合書冩/享和二年四月 日撿挍保己一」とあり|50「正安二年八月十一日於仙洞被始行熾盛光法」末の原奥書に「文化十五年春二月以南山法曼院藏夲書冩之 撿挍保己一」とあり|横刷毛目表紙を使用|朱点, 朱引, 朱墨筆書き入れあり|付箋あり|蔵書印主信濃須坂藩主堀直格の命によって編集された古記録|他の原本は関東大震災により焼失|極札に「桂壽」(6), 「尚信」(53)との極書, 「武清」(44, 53), 「永海」(51), 「了伴」(52), 「了甫」(74), 「定時」(84, 88)との極印あり|印記: 「花廼家文庫」, 「墨阪十一代主寫藏記」(堀直格(1806-1880)), 「東京大學法理文學部書庫所藏」, 「閲覧室用 FOR USE IN THE READING ROOM」|虫損あり</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -8706,12 +8706,12 @@
       <c r="O68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/20ddaef2-73cc-5ae8-949d-0bdc521924e9.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/31b47601-839e-83b4-6a49-7d11ed020385.json</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>20ddaef2-73cc-5ae8-949d-0bdc521924e9</t>
+          <t>31b47601-839e-83b4-6a49-7d11ed020385</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
@@ -8721,7 +8721,7 @@
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/20ddaef2-73cc-5ae8-949d-0bdc521924e9</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/31b47601-839e-83b4-6a49-7d11ed020385</t>
         </is>
       </c>
       <c r="T68" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/e2bfc2adbffcfb9eb459e7863108300f2722cdd2.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/d78a0b64be5f71b37b264b3b2eb8172d4e8a5002.jpg</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296191</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296216</t>
         </is>
       </c>
       <c r="W68" t="inlineStr">
@@ -8759,7 +8759,7 @@
       <c r="AB68" t="inlineStr"/>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/20ddaef2-73cc-5ae8-949d-0bdc521924e9/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/31b47601-839e-83b4-6a49-7d11ed020385/manifest</t>
         </is>
       </c>
       <c r="AD68" t="inlineStr"/>
@@ -8767,52 +8767,52 @@
       <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="inlineStr"/>
       <c r="AH68" t="n">
-        <v>104</v>
+        <v>58</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>玉蘂 [3]</t>
+          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [17]</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>A00:6067</t>
+          <t>A00:6257</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>ギョクズイ</t>
+          <t>レキダイ ザンケツ ニッキ</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>藤原 道家</t>
+          <t>黒川 春村</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>野宮定基 : 久世通夏 [ほか写]</t>
+          <t>[書写者不明]</t>
         </is>
       </c>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr">
         <is>
-          <t>元禄12 [1699]-宝永3 [1706] 奥書</t>
+          <t>[安政5 (1858)]</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr">
         <is>
-          <t>写本|書名及び巻冊次は表紙による|奥中の書名: 光明峯寺禅閤道家公記, 峯禅閤記, 峯摂政記, 峯入道摂政記|承元4年の原奥書に「右即位記一卷者光明峯寺禅閤自筆正記也以件本左令吾基春卿透以写之云々加挍正之 ... 永正七年夷則上浣 從一位(花押)」とあり|奥書に「右以或人夲自常州到来令書写之彼夲端書云此冊上下卷 ... 元禄第十二暦仲夏中旬 羽林左衞中郎将藤原定基丗一才」(承元3), 「右光明峯寺禅閤道家公承元二年三月五六月八月四年二三月九月十十一十二月記は借請或人之夲自常州邊来書写之加一挍了/于時元禄第十二端午節也 左中郎将藤原定基丗才」(承元4), 「右玉蘂建暦元年少弟左中将通清朝臣助筆僅加一挍原本文字不正後来得正夲可改之者也/元禄十三年九月十日 松堂閑士(花押)丗二才」(建暦元), 「右玉蘂峯禅閤記建暦二年自二月至九月一冊以或人夲自常州邊来命家僚令書写手自加挍合了/元禄十二年五月六日 左中郎将藤原定基丗一才」(建暦2年上), 「宝永二年十月一日書写畢/承久二春玉蘂以故常州牧權中納言光圀公夲謄写之于時俗務紛擾先請慈兄源亜相公所被写也今以彼夲手自馳禿筆 余識藤(花押)丗七才/同三年二月廿五日一挍了」(承久2年上), 「右峯摂政承久二年記命傭書謄冩之手自一挍了/元禄第十二嵗次著雍単閼蕤賓中旬 羽林軍左衞中郎将藤原定基丗一才」(承久2年下), 「嘉禎四年正月二月閏二月三月四月六月玉蘂先年假借故常州牧前中納言光圀夲無剋力速遂書写之功建暦元年建暦二年下承久二年上及此卷等先献慈兄亜相君写之今及数年申復彼夲謄写之 ... 宝永三年十二月念日 参議從三位行左近衞權中将藤原朝臣定基生年卅八才」(嘉禎4年)とあり|毎半葉11行注文双行|漢文体日記|拠徳川光圀本及び中院通躬鈔本謄写|朱筆書き入れあり|印記: 「定基」(野宮定基), 「野宮書印」|虫損あり (裏打ち補修あり)</t>
+          <t>写本|責任表示及び書写年は『日本古典籍総合目録データベース』による|内容: 6: 光明院御記, 後光嚴院御記, 後小松院宸記, 天聴集. 28: 参議藤定長卿記 : 稱山丞記. 37: 定高卿記, 晴御会部類記, 家光卿御記, 權中納言平範輔卿記. 38: 左大史小槻季継記, 後堀川安貞二年放生會(実基公記), 石清水八幡宮, 弁官拝賀次第. 39: 大外記師光記, 資季卿記, 荒凉記, 忠高卿記. 40: 冷泉公相公記, 勝延法眼記 : 東寺大行事, 後中記 : 小路中納言資頼卿記葉室. 41: 中光記, 師兼記, 陽龍記. 42: 大宮司長則記, 口筆 : 實經, 顕朝卿記, 鴨御幸記. 43: 寳治二年記, 深心院關白記, 藤公親記, 照念院関白兼平公記. 44: 頼親記, 亀山殿行幸記 : 雅言卿記, 兼基公記. 45: 大嘗會御禊節下次第, 建治三年丁丑日記 : 三善康有, 建治四年正月廿一日 : 徳大寺大相國公孝記, 冬定卿記, 左大史小槻兼文記|内容: 46: 經任卿記, 前豊前守藤憲説記, 實兼公記. 47: 継塵記抄出. 48: 管見記, 公衡公記, 大外記師顕記, 大外記中原師淳記. 49: 真光院禪助僧正記, 吉田内府卿記. 50: 定清記, 叅議雅俊卿記, 太政大臣(公守公)御上表雜事, 仙洞御灌頂日記, 正安二年八月十一日於仙洞被始行熾盛光法, 正安三年御譲位記. 51: 實躬卿記. 52: 公茂公記, 冬平公記, 隆長卿記. 53: 忠教公記, 官記, 正三位長基卿記, 北面秀長記, 大外記中原師右記. 54: 文保元年, 日野中納言資朝卿記, 洞院大納言公敏卿記. 55: 隆蔭卿記, 文保三年記, 尹大納言師賢卿記, 革命記, 立倚子記, 萬里小路中納言藤藤房卿記|内容: 56: 資名卿記, 公秀公記, 一條家記装束抄出, 頼定卿記. 63: 松亞記, 日野大納言時光卿記, 後八條内府實継公記. 74: 成恩寺関白記. 78: 山科家礼記. 82: 諒闇記 : 後成恩寺殿, 宗典僧正記, 綱光公記, 贈従二位宗賢卿記, 義政公記. 84: 長禄二年戊寅正月, 見聞雜記. 87: 言國卿記. 88: 長興宿祢記, 元長卿記, 兼顕卿記, 小槻晴冨記|28末の原奥書に「右山丞記依 仰挍合書冩/享和二年四月 日撿挍保己一」とあり|50「正安二年八月十一日於仙洞被始行熾盛光法」末の原奥書に「文化十五年春二月以南山法曼院藏夲書冩之 撿挍保己一」とあり|横刷毛目表紙を使用|朱点, 朱引, 朱墨筆書き入れあり|付箋あり|蔵書印主信濃須坂藩主堀直格の命によって編集された古記録|他の原本は関東大震災により焼失|極札に「桂壽」(6), 「尚信」(53)との極書, 「武清」(44, 53), 「永海」(51), 「了伴」(52), 「了甫」(74), 「定時」(84, 88)との極印あり|印記: 「花廼家文庫」, 「墨阪十一代主寫藏記」(堀直格(1806-1880)), 「東京大學法理文學部書庫所藏」, 「閲覧室用 FOR USE IN THE READING ROOM」|虫損あり</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -8828,12 +8828,12 @@
       <c r="O69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/7f62eb7a-844c-22ea-196e-998226c991ea.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/37d790df-458b-48bf-6b67-3f4755f40f0f.json</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>7f62eb7a-844c-22ea-196e-998226c991ea</t>
+          <t>37d790df-458b-48bf-6b67-3f4755f40f0f</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
@@ -8843,7 +8843,7 @@
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/7f62eb7a-844c-22ea-196e-998226c991ea</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/37d790df-458b-48bf-6b67-3f4755f40f0f</t>
         </is>
       </c>
       <c r="T69" t="inlineStr">
@@ -8853,12 +8853,12 @@
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/ac4d01393f2eb0586033bfface43acc61e64021e.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/dae05b3fca02a35e3363b381527ea7a899ca4f74.jpg</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296192</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296217</t>
         </is>
       </c>
       <c r="W69" t="inlineStr">
@@ -8881,7 +8881,7 @@
       <c r="AB69" t="inlineStr"/>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/7f62eb7a-844c-22ea-196e-998226c991ea/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/37d790df-458b-48bf-6b67-3f4755f40f0f/manifest</t>
         </is>
       </c>
       <c r="AD69" t="inlineStr"/>
@@ -8889,52 +8889,52 @@
       <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="inlineStr"/>
       <c r="AH69" t="n">
-        <v>77</v>
+        <v>54</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>玉蘂 [4]</t>
+          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [18]</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>A00:6067</t>
+          <t>A00:6257</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>ギョクズイ</t>
+          <t>レキダイ ザンケツ ニッキ</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>藤原 道家</t>
+          <t>黒川 春村</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>野宮定基 : 久世通夏 [ほか写]</t>
+          <t>[書写者不明]</t>
         </is>
       </c>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr">
         <is>
-          <t>元禄12 [1699]-宝永3 [1706] 奥書</t>
+          <t>[安政5 (1858)]</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr">
         <is>
-          <t>写本|書名及び巻冊次は表紙による|奥中の書名: 光明峯寺禅閤道家公記, 峯禅閤記, 峯摂政記, 峯入道摂政記|承元4年の原奥書に「右即位記一卷者光明峯寺禅閤自筆正記也以件本左令吾基春卿透以写之云々加挍正之 ... 永正七年夷則上浣 從一位(花押)」とあり|奥書に「右以或人夲自常州到来令書写之彼夲端書云此冊上下卷 ... 元禄第十二暦仲夏中旬 羽林左衞中郎将藤原定基丗一才」(承元3), 「右光明峯寺禅閤道家公承元二年三月五六月八月四年二三月九月十十一十二月記は借請或人之夲自常州邊来書写之加一挍了/于時元禄第十二端午節也 左中郎将藤原定基丗才」(承元4), 「右玉蘂建暦元年少弟左中将通清朝臣助筆僅加一挍原本文字不正後来得正夲可改之者也/元禄十三年九月十日 松堂閑士(花押)丗二才」(建暦元), 「右玉蘂峯禅閤記建暦二年自二月至九月一冊以或人夲自常州邊来命家僚令書写手自加挍合了/元禄十二年五月六日 左中郎将藤原定基丗一才」(建暦2年上), 「宝永二年十月一日書写畢/承久二春玉蘂以故常州牧權中納言光圀公夲謄写之于時俗務紛擾先請慈兄源亜相公所被写也今以彼夲手自馳禿筆 余識藤(花押)丗七才/同三年二月廿五日一挍了」(承久2年上), 「右峯摂政承久二年記命傭書謄冩之手自一挍了/元禄第十二嵗次著雍単閼蕤賓中旬 羽林軍左衞中郎将藤原定基丗一才」(承久2年下), 「嘉禎四年正月二月閏二月三月四月六月玉蘂先年假借故常州牧前中納言光圀夲無剋力速遂書写之功建暦元年建暦二年下承久二年上及此卷等先献慈兄亜相君写之今及数年申復彼夲謄写之 ... 宝永三年十二月念日 参議從三位行左近衞權中将藤原朝臣定基生年卅八才」(嘉禎4年)とあり|毎半葉11行注文双行|漢文体日記|拠徳川光圀本及び中院通躬鈔本謄写|朱筆書き入れあり|印記: 「定基」(野宮定基), 「野宮書印」|虫損あり (裏打ち補修あり)</t>
+          <t>写本|責任表示及び書写年は『日本古典籍総合目録データベース』による|内容: 6: 光明院御記, 後光嚴院御記, 後小松院宸記, 天聴集. 28: 参議藤定長卿記 : 稱山丞記. 37: 定高卿記, 晴御会部類記, 家光卿御記, 權中納言平範輔卿記. 38: 左大史小槻季継記, 後堀川安貞二年放生會(実基公記), 石清水八幡宮, 弁官拝賀次第. 39: 大外記師光記, 資季卿記, 荒凉記, 忠高卿記. 40: 冷泉公相公記, 勝延法眼記 : 東寺大行事, 後中記 : 小路中納言資頼卿記葉室. 41: 中光記, 師兼記, 陽龍記. 42: 大宮司長則記, 口筆 : 實經, 顕朝卿記, 鴨御幸記. 43: 寳治二年記, 深心院關白記, 藤公親記, 照念院関白兼平公記. 44: 頼親記, 亀山殿行幸記 : 雅言卿記, 兼基公記. 45: 大嘗會御禊節下次第, 建治三年丁丑日記 : 三善康有, 建治四年正月廿一日 : 徳大寺大相國公孝記, 冬定卿記, 左大史小槻兼文記|内容: 46: 經任卿記, 前豊前守藤憲説記, 實兼公記. 47: 継塵記抄出. 48: 管見記, 公衡公記, 大外記師顕記, 大外記中原師淳記. 49: 真光院禪助僧正記, 吉田内府卿記. 50: 定清記, 叅議雅俊卿記, 太政大臣(公守公)御上表雜事, 仙洞御灌頂日記, 正安二年八月十一日於仙洞被始行熾盛光法, 正安三年御譲位記. 51: 實躬卿記. 52: 公茂公記, 冬平公記, 隆長卿記. 53: 忠教公記, 官記, 正三位長基卿記, 北面秀長記, 大外記中原師右記. 54: 文保元年, 日野中納言資朝卿記, 洞院大納言公敏卿記. 55: 隆蔭卿記, 文保三年記, 尹大納言師賢卿記, 革命記, 立倚子記, 萬里小路中納言藤藤房卿記|内容: 56: 資名卿記, 公秀公記, 一條家記装束抄出, 頼定卿記. 63: 松亞記, 日野大納言時光卿記, 後八條内府實継公記. 74: 成恩寺関白記. 78: 山科家礼記. 82: 諒闇記 : 後成恩寺殿, 宗典僧正記, 綱光公記, 贈従二位宗賢卿記, 義政公記. 84: 長禄二年戊寅正月, 見聞雜記. 87: 言國卿記. 88: 長興宿祢記, 元長卿記, 兼顕卿記, 小槻晴冨記|28末の原奥書に「右山丞記依 仰挍合書冩/享和二年四月 日撿挍保己一」とあり|50「正安二年八月十一日於仙洞被始行熾盛光法」末の原奥書に「文化十五年春二月以南山法曼院藏夲書冩之 撿挍保己一」とあり|横刷毛目表紙を使用|朱点, 朱引, 朱墨筆書き入れあり|付箋あり|蔵書印主信濃須坂藩主堀直格の命によって編集された古記録|他の原本は関東大震災により焼失|極札に「桂壽」(6), 「尚信」(53)との極書, 「武清」(44, 53), 「永海」(51), 「了伴」(52), 「了甫」(74), 「定時」(84, 88)との極印あり|印記: 「花廼家文庫」, 「墨阪十一代主寫藏記」(堀直格(1806-1880)), 「東京大學法理文學部書庫所藏」, 「閲覧室用 FOR USE IN THE READING ROOM」|虫損あり</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -8950,12 +8950,12 @@
       <c r="O70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/f48a78a7-0365-73cb-4e46-dd013ef92813.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/c69854e0-18e9-71b3-a7b1-22422a16688b.json</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>f48a78a7-0365-73cb-4e46-dd013ef92813</t>
+          <t>c69854e0-18e9-71b3-a7b1-22422a16688b</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
@@ -8965,7 +8965,7 @@
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/f48a78a7-0365-73cb-4e46-dd013ef92813</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/c69854e0-18e9-71b3-a7b1-22422a16688b</t>
         </is>
       </c>
       <c r="T70" t="inlineStr">
@@ -8975,12 +8975,12 @@
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/d9d6bd695feea8f0816bee6e991e141accf01cd8.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/584cfd5ec1bb0f374ab03f25ca3600a8ec2e67bf.jpg</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296193</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296218</t>
         </is>
       </c>
       <c r="W70" t="inlineStr">
@@ -9003,7 +9003,7 @@
       <c r="AB70" t="inlineStr"/>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/f48a78a7-0365-73cb-4e46-dd013ef92813/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/c69854e0-18e9-71b3-a7b1-22422a16688b/manifest</t>
         </is>
       </c>
       <c r="AD70" t="inlineStr"/>
@@ -9011,52 +9011,52 @@
       <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="inlineStr"/>
       <c r="AH70" t="n">
-        <v>138</v>
+        <v>77</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>玉蘂 [5]</t>
+          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [19]</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>A00:6067</t>
+          <t>A00:6257</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>ギョクズイ</t>
+          <t>レキダイ ザンケツ ニッキ</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>藤原 道家</t>
+          <t>黒川 春村</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>野宮定基 : 久世通夏 [ほか写]</t>
+          <t>[書写者不明]</t>
         </is>
       </c>
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr">
         <is>
-          <t>元禄12 [1699]-宝永3 [1706] 奥書</t>
+          <t>[安政5 (1858)]</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr">
         <is>
-          <t>写本|書名及び巻冊次は表紙による|奥中の書名: 光明峯寺禅閤道家公記, 峯禅閤記, 峯摂政記, 峯入道摂政記|承元4年の原奥書に「右即位記一卷者光明峯寺禅閤自筆正記也以件本左令吾基春卿透以写之云々加挍正之 ... 永正七年夷則上浣 從一位(花押)」とあり|奥書に「右以或人夲自常州到来令書写之彼夲端書云此冊上下卷 ... 元禄第十二暦仲夏中旬 羽林左衞中郎将藤原定基丗一才」(承元3), 「右光明峯寺禅閤道家公承元二年三月五六月八月四年二三月九月十十一十二月記は借請或人之夲自常州邊来書写之加一挍了/于時元禄第十二端午節也 左中郎将藤原定基丗才」(承元4), 「右玉蘂建暦元年少弟左中将通清朝臣助筆僅加一挍原本文字不正後来得正夲可改之者也/元禄十三年九月十日 松堂閑士(花押)丗二才」(建暦元), 「右玉蘂峯禅閤記建暦二年自二月至九月一冊以或人夲自常州邊来命家僚令書写手自加挍合了/元禄十二年五月六日 左中郎将藤原定基丗一才」(建暦2年上), 「宝永二年十月一日書写畢/承久二春玉蘂以故常州牧權中納言光圀公夲謄写之于時俗務紛擾先請慈兄源亜相公所被写也今以彼夲手自馳禿筆 余識藤(花押)丗七才/同三年二月廿五日一挍了」(承久2年上), 「右峯摂政承久二年記命傭書謄冩之手自一挍了/元禄第十二嵗次著雍単閼蕤賓中旬 羽林軍左衞中郎将藤原定基丗一才」(承久2年下), 「嘉禎四年正月二月閏二月三月四月六月玉蘂先年假借故常州牧前中納言光圀夲無剋力速遂書写之功建暦元年建暦二年下承久二年上及此卷等先献慈兄亜相君写之今及数年申復彼夲謄写之 ... 宝永三年十二月念日 参議從三位行左近衞權中将藤原朝臣定基生年卅八才」(嘉禎4年)とあり|毎半葉11行注文双行|漢文体日記|拠徳川光圀本及び中院通躬鈔本謄写|朱筆書き入れあり|印記: 「定基」(野宮定基), 「野宮書印」|虫損あり (裏打ち補修あり)</t>
+          <t>写本|責任表示及び書写年は『日本古典籍総合目録データベース』による|内容: 6: 光明院御記, 後光嚴院御記, 後小松院宸記, 天聴集. 28: 参議藤定長卿記 : 稱山丞記. 37: 定高卿記, 晴御会部類記, 家光卿御記, 權中納言平範輔卿記. 38: 左大史小槻季継記, 後堀川安貞二年放生會(実基公記), 石清水八幡宮, 弁官拝賀次第. 39: 大外記師光記, 資季卿記, 荒凉記, 忠高卿記. 40: 冷泉公相公記, 勝延法眼記 : 東寺大行事, 後中記 : 小路中納言資頼卿記葉室. 41: 中光記, 師兼記, 陽龍記. 42: 大宮司長則記, 口筆 : 實經, 顕朝卿記, 鴨御幸記. 43: 寳治二年記, 深心院關白記, 藤公親記, 照念院関白兼平公記. 44: 頼親記, 亀山殿行幸記 : 雅言卿記, 兼基公記. 45: 大嘗會御禊節下次第, 建治三年丁丑日記 : 三善康有, 建治四年正月廿一日 : 徳大寺大相國公孝記, 冬定卿記, 左大史小槻兼文記|内容: 46: 經任卿記, 前豊前守藤憲説記, 實兼公記. 47: 継塵記抄出. 48: 管見記, 公衡公記, 大外記師顕記, 大外記中原師淳記. 49: 真光院禪助僧正記, 吉田内府卿記. 50: 定清記, 叅議雅俊卿記, 太政大臣(公守公)御上表雜事, 仙洞御灌頂日記, 正安二年八月十一日於仙洞被始行熾盛光法, 正安三年御譲位記. 51: 實躬卿記. 52: 公茂公記, 冬平公記, 隆長卿記. 53: 忠教公記, 官記, 正三位長基卿記, 北面秀長記, 大外記中原師右記. 54: 文保元年, 日野中納言資朝卿記, 洞院大納言公敏卿記. 55: 隆蔭卿記, 文保三年記, 尹大納言師賢卿記, 革命記, 立倚子記, 萬里小路中納言藤藤房卿記|内容: 56: 資名卿記, 公秀公記, 一條家記装束抄出, 頼定卿記. 63: 松亞記, 日野大納言時光卿記, 後八條内府實継公記. 74: 成恩寺関白記. 78: 山科家礼記. 82: 諒闇記 : 後成恩寺殿, 宗典僧正記, 綱光公記, 贈従二位宗賢卿記, 義政公記. 84: 長禄二年戊寅正月, 見聞雜記. 87: 言國卿記. 88: 長興宿祢記, 元長卿記, 兼顕卿記, 小槻晴冨記|28末の原奥書に「右山丞記依 仰挍合書冩/享和二年四月 日撿挍保己一」とあり|50「正安二年八月十一日於仙洞被始行熾盛光法」末の原奥書に「文化十五年春二月以南山法曼院藏夲書冩之 撿挍保己一」とあり|横刷毛目表紙を使用|朱点, 朱引, 朱墨筆書き入れあり|付箋あり|蔵書印主信濃須坂藩主堀直格の命によって編集された古記録|他の原本は関東大震災により焼失|極札に「桂壽」(6), 「尚信」(53)との極書, 「武清」(44, 53), 「永海」(51), 「了伴」(52), 「了甫」(74), 「定時」(84, 88)との極印あり|印記: 「花廼家文庫」, 「墨阪十一代主寫藏記」(堀直格(1806-1880)), 「東京大學法理文學部書庫所藏」, 「閲覧室用 FOR USE IN THE READING ROOM」|虫損あり</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -9072,12 +9072,12 @@
       <c r="O71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/c4ba4bb2-8d3c-7e43-4e3e-e6a6d0c2260f.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/1373f0d8-7cc0-4591-2c18-798fa20f483d.json</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>c4ba4bb2-8d3c-7e43-4e3e-e6a6d0c2260f</t>
+          <t>1373f0d8-7cc0-4591-2c18-798fa20f483d</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
@@ -9087,7 +9087,7 @@
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/c4ba4bb2-8d3c-7e43-4e3e-e6a6d0c2260f</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/1373f0d8-7cc0-4591-2c18-798fa20f483d</t>
         </is>
       </c>
       <c r="T71" t="inlineStr">
@@ -9097,12 +9097,12 @@
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/58826021e366d49d150087ff3478b98548b97c4a.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/326ed2db044321d7b007462c9ac98badfd7f671a.jpg</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296194</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296219</t>
         </is>
       </c>
       <c r="W71" t="inlineStr">
@@ -9125,7 +9125,7 @@
       <c r="AB71" t="inlineStr"/>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/c4ba4bb2-8d3c-7e43-4e3e-e6a6d0c2260f/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/1373f0d8-7cc0-4591-2c18-798fa20f483d/manifest</t>
         </is>
       </c>
       <c r="AD71" t="inlineStr"/>
@@ -9139,46 +9139,46 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>玉蘂 [6]</t>
+          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [20]</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>A00:6067</t>
+          <t>A00:6257</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>ギョクズイ</t>
+          <t>レキダイ ザンケツ ニッキ</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>藤原 道家</t>
+          <t>黒川 春村</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>野宮定基 : 久世通夏 [ほか写]</t>
+          <t>[書写者不明]</t>
         </is>
       </c>
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr">
         <is>
-          <t>元禄12 [1699]-宝永3 [1706] 奥書</t>
+          <t>[安政5 (1858)]</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr">
         <is>
-          <t>写本|書名及び巻冊次は表紙による|奥中の書名: 光明峯寺禅閤道家公記, 峯禅閤記, 峯摂政記, 峯入道摂政記|承元4年の原奥書に「右即位記一卷者光明峯寺禅閤自筆正記也以件本左令吾基春卿透以写之云々加挍正之 ... 永正七年夷則上浣 從一位(花押)」とあり|奥書に「右以或人夲自常州到来令書写之彼夲端書云此冊上下卷 ... 元禄第十二暦仲夏中旬 羽林左衞中郎将藤原定基丗一才」(承元3), 「右光明峯寺禅閤道家公承元二年三月五六月八月四年二三月九月十十一十二月記は借請或人之夲自常州邊来書写之加一挍了/于時元禄第十二端午節也 左中郎将藤原定基丗才」(承元4), 「右玉蘂建暦元年少弟左中将通清朝臣助筆僅加一挍原本文字不正後来得正夲可改之者也/元禄十三年九月十日 松堂閑士(花押)丗二才」(建暦元), 「右玉蘂峯禅閤記建暦二年自二月至九月一冊以或人夲自常州邊来命家僚令書写手自加挍合了/元禄十二年五月六日 左中郎将藤原定基丗一才」(建暦2年上), 「宝永二年十月一日書写畢/承久二春玉蘂以故常州牧權中納言光圀公夲謄写之于時俗務紛擾先請慈兄源亜相公所被写也今以彼夲手自馳禿筆 余識藤(花押)丗七才/同三年二月廿五日一挍了」(承久2年上), 「右峯摂政承久二年記命傭書謄冩之手自一挍了/元禄第十二嵗次著雍単閼蕤賓中旬 羽林軍左衞中郎将藤原定基丗一才」(承久2年下), 「嘉禎四年正月二月閏二月三月四月六月玉蘂先年假借故常州牧前中納言光圀夲無剋力速遂書写之功建暦元年建暦二年下承久二年上及此卷等先献慈兄亜相君写之今及数年申復彼夲謄写之 ... 宝永三年十二月念日 参議從三位行左近衞權中将藤原朝臣定基生年卅八才」(嘉禎4年)とあり|毎半葉11行注文双行|漢文体日記|拠徳川光圀本及び中院通躬鈔本謄写|朱筆書き入れあり|印記: 「定基」(野宮定基), 「野宮書印」|虫損あり (裏打ち補修あり)</t>
+          <t>写本|責任表示及び書写年は『日本古典籍総合目録データベース』による|内容: 6: 光明院御記, 後光嚴院御記, 後小松院宸記, 天聴集. 28: 参議藤定長卿記 : 稱山丞記. 37: 定高卿記, 晴御会部類記, 家光卿御記, 權中納言平範輔卿記. 38: 左大史小槻季継記, 後堀川安貞二年放生會(実基公記), 石清水八幡宮, 弁官拝賀次第. 39: 大外記師光記, 資季卿記, 荒凉記, 忠高卿記. 40: 冷泉公相公記, 勝延法眼記 : 東寺大行事, 後中記 : 小路中納言資頼卿記葉室. 41: 中光記, 師兼記, 陽龍記. 42: 大宮司長則記, 口筆 : 實經, 顕朝卿記, 鴨御幸記. 43: 寳治二年記, 深心院關白記, 藤公親記, 照念院関白兼平公記. 44: 頼親記, 亀山殿行幸記 : 雅言卿記, 兼基公記. 45: 大嘗會御禊節下次第, 建治三年丁丑日記 : 三善康有, 建治四年正月廿一日 : 徳大寺大相國公孝記, 冬定卿記, 左大史小槻兼文記|内容: 46: 經任卿記, 前豊前守藤憲説記, 實兼公記. 47: 継塵記抄出. 48: 管見記, 公衡公記, 大外記師顕記, 大外記中原師淳記. 49: 真光院禪助僧正記, 吉田内府卿記. 50: 定清記, 叅議雅俊卿記, 太政大臣(公守公)御上表雜事, 仙洞御灌頂日記, 正安二年八月十一日於仙洞被始行熾盛光法, 正安三年御譲位記. 51: 實躬卿記. 52: 公茂公記, 冬平公記, 隆長卿記. 53: 忠教公記, 官記, 正三位長基卿記, 北面秀長記, 大外記中原師右記. 54: 文保元年, 日野中納言資朝卿記, 洞院大納言公敏卿記. 55: 隆蔭卿記, 文保三年記, 尹大納言師賢卿記, 革命記, 立倚子記, 萬里小路中納言藤藤房卿記|内容: 56: 資名卿記, 公秀公記, 一條家記装束抄出, 頼定卿記. 63: 松亞記, 日野大納言時光卿記, 後八條内府實継公記. 74: 成恩寺関白記. 78: 山科家礼記. 82: 諒闇記 : 後成恩寺殿, 宗典僧正記, 綱光公記, 贈従二位宗賢卿記, 義政公記. 84: 長禄二年戊寅正月, 見聞雜記. 87: 言國卿記. 88: 長興宿祢記, 元長卿記, 兼顕卿記, 小槻晴冨記|28末の原奥書に「右山丞記依 仰挍合書冩/享和二年四月 日撿挍保己一」とあり|50「正安二年八月十一日於仙洞被始行熾盛光法」末の原奥書に「文化十五年春二月以南山法曼院藏夲書冩之 撿挍保己一」とあり|横刷毛目表紙を使用|朱点, 朱引, 朱墨筆書き入れあり|付箋あり|蔵書印主信濃須坂藩主堀直格の命によって編集された古記録|他の原本は関東大震災により焼失|極札に「桂壽」(6), 「尚信」(53)との極書, 「武清」(44, 53), 「永海」(51), 「了伴」(52), 「了甫」(74), 「定時」(84, 88)との極印あり|印記: 「花廼家文庫」, 「墨阪十一代主寫藏記」(堀直格(1806-1880)), 「東京大學法理文學部書庫所藏」, 「閲覧室用 FOR USE IN THE READING ROOM」|虫損あり</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -9194,12 +9194,12 @@
       <c r="O72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/73dc1d4b-7872-a0a3-780c-3c10d2a3758a.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/d64280ea-576f-4bf3-9413-1b0bf6485e16.json</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>73dc1d4b-7872-a0a3-780c-3c10d2a3758a</t>
+          <t>d64280ea-576f-4bf3-9413-1b0bf6485e16</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
@@ -9209,7 +9209,7 @@
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/73dc1d4b-7872-a0a3-780c-3c10d2a3758a</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/d64280ea-576f-4bf3-9413-1b0bf6485e16</t>
         </is>
       </c>
       <c r="T72" t="inlineStr">
@@ -9219,12 +9219,12 @@
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/6724525552ca8e3c1f42cdc0f0674a54828dc026.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/c5e3a0bdc0b67f7429d47677a33485a6a498e20f.jpg</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296195</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296220</t>
         </is>
       </c>
       <c r="W72" t="inlineStr">
@@ -9247,7 +9247,7 @@
       <c r="AB72" t="inlineStr"/>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/73dc1d4b-7872-a0a3-780c-3c10d2a3758a/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/d64280ea-576f-4bf3-9413-1b0bf6485e16/manifest</t>
         </is>
       </c>
       <c r="AD72" t="inlineStr"/>
@@ -9255,52 +9255,52 @@
       <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="inlineStr"/>
       <c r="AH72" t="n">
-        <v>106</v>
+        <v>75</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>玉蘂 [7]</t>
+          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [21]</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>A00:6067</t>
+          <t>A00:6257</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>ギョクズイ</t>
+          <t>レキダイ ザンケツ ニッキ</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>藤原 道家</t>
+          <t>黒川 春村</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>野宮定基 : 久世通夏 [ほか写]</t>
+          <t>[書写者不明]</t>
         </is>
       </c>
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr">
         <is>
-          <t>元禄12 [1699]-宝永3 [1706] 奥書</t>
+          <t>[安政5 (1858)]</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr">
         <is>
-          <t>写本|書名及び巻冊次は表紙による|奥中の書名: 光明峯寺禅閤道家公記, 峯禅閤記, 峯摂政記, 峯入道摂政記|承元4年の原奥書に「右即位記一卷者光明峯寺禅閤自筆正記也以件本左令吾基春卿透以写之云々加挍正之 ... 永正七年夷則上浣 從一位(花押)」とあり|奥書に「右以或人夲自常州到来令書写之彼夲端書云此冊上下卷 ... 元禄第十二暦仲夏中旬 羽林左衞中郎将藤原定基丗一才」(承元3), 「右光明峯寺禅閤道家公承元二年三月五六月八月四年二三月九月十十一十二月記は借請或人之夲自常州邊来書写之加一挍了/于時元禄第十二端午節也 左中郎将藤原定基丗才」(承元4), 「右玉蘂建暦元年少弟左中将通清朝臣助筆僅加一挍原本文字不正後来得正夲可改之者也/元禄十三年九月十日 松堂閑士(花押)丗二才」(建暦元), 「右玉蘂峯禅閤記建暦二年自二月至九月一冊以或人夲自常州邊来命家僚令書写手自加挍合了/元禄十二年五月六日 左中郎将藤原定基丗一才」(建暦2年上), 「宝永二年十月一日書写畢/承久二春玉蘂以故常州牧權中納言光圀公夲謄写之于時俗務紛擾先請慈兄源亜相公所被写也今以彼夲手自馳禿筆 余識藤(花押)丗七才/同三年二月廿五日一挍了」(承久2年上), 「右峯摂政承久二年記命傭書謄冩之手自一挍了/元禄第十二嵗次著雍単閼蕤賓中旬 羽林軍左衞中郎将藤原定基丗一才」(承久2年下), 「嘉禎四年正月二月閏二月三月四月六月玉蘂先年假借故常州牧前中納言光圀夲無剋力速遂書写之功建暦元年建暦二年下承久二年上及此卷等先献慈兄亜相君写之今及数年申復彼夲謄写之 ... 宝永三年十二月念日 参議從三位行左近衞權中将藤原朝臣定基生年卅八才」(嘉禎4年)とあり|毎半葉11行注文双行|漢文体日記|拠徳川光圀本及び中院通躬鈔本謄写|朱筆書き入れあり|印記: 「定基」(野宮定基), 「野宮書印」|虫損あり (裏打ち補修あり)</t>
+          <t>写本|責任表示及び書写年は『日本古典籍総合目録データベース』による|内容: 6: 光明院御記, 後光嚴院御記, 後小松院宸記, 天聴集. 28: 参議藤定長卿記 : 稱山丞記. 37: 定高卿記, 晴御会部類記, 家光卿御記, 權中納言平範輔卿記. 38: 左大史小槻季継記, 後堀川安貞二年放生會(実基公記), 石清水八幡宮, 弁官拝賀次第. 39: 大外記師光記, 資季卿記, 荒凉記, 忠高卿記. 40: 冷泉公相公記, 勝延法眼記 : 東寺大行事, 後中記 : 小路中納言資頼卿記葉室. 41: 中光記, 師兼記, 陽龍記. 42: 大宮司長則記, 口筆 : 實經, 顕朝卿記, 鴨御幸記. 43: 寳治二年記, 深心院關白記, 藤公親記, 照念院関白兼平公記. 44: 頼親記, 亀山殿行幸記 : 雅言卿記, 兼基公記. 45: 大嘗會御禊節下次第, 建治三年丁丑日記 : 三善康有, 建治四年正月廿一日 : 徳大寺大相國公孝記, 冬定卿記, 左大史小槻兼文記|内容: 46: 經任卿記, 前豊前守藤憲説記, 實兼公記. 47: 継塵記抄出. 48: 管見記, 公衡公記, 大外記師顕記, 大外記中原師淳記. 49: 真光院禪助僧正記, 吉田内府卿記. 50: 定清記, 叅議雅俊卿記, 太政大臣(公守公)御上表雜事, 仙洞御灌頂日記, 正安二年八月十一日於仙洞被始行熾盛光法, 正安三年御譲位記. 51: 實躬卿記. 52: 公茂公記, 冬平公記, 隆長卿記. 53: 忠教公記, 官記, 正三位長基卿記, 北面秀長記, 大外記中原師右記. 54: 文保元年, 日野中納言資朝卿記, 洞院大納言公敏卿記. 55: 隆蔭卿記, 文保三年記, 尹大納言師賢卿記, 革命記, 立倚子記, 萬里小路中納言藤藤房卿記|内容: 56: 資名卿記, 公秀公記, 一條家記装束抄出, 頼定卿記. 63: 松亞記, 日野大納言時光卿記, 後八條内府實継公記. 74: 成恩寺関白記. 78: 山科家礼記. 82: 諒闇記 : 後成恩寺殿, 宗典僧正記, 綱光公記, 贈従二位宗賢卿記, 義政公記. 84: 長禄二年戊寅正月, 見聞雜記. 87: 言國卿記. 88: 長興宿祢記, 元長卿記, 兼顕卿記, 小槻晴冨記|28末の原奥書に「右山丞記依 仰挍合書冩/享和二年四月 日撿挍保己一」とあり|50「正安二年八月十一日於仙洞被始行熾盛光法」末の原奥書に「文化十五年春二月以南山法曼院藏夲書冩之 撿挍保己一」とあり|横刷毛目表紙を使用|朱点, 朱引, 朱墨筆書き入れあり|付箋あり|蔵書印主信濃須坂藩主堀直格の命によって編集された古記録|他の原本は関東大震災により焼失|極札に「桂壽」(6), 「尚信」(53)との極書, 「武清」(44, 53), 「永海」(51), 「了伴」(52), 「了甫」(74), 「定時」(84, 88)との極印あり|印記: 「花廼家文庫」, 「墨阪十一代主寫藏記」(堀直格(1806-1880)), 「東京大學法理文學部書庫所藏」, 「閲覧室用 FOR USE IN THE READING ROOM」|虫損あり</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -9316,12 +9316,12 @@
       <c r="O73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/e775ea12-9867-70f2-6381-112e31478f75.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/decc377c-887e-7362-3bf7-81b1c9c58641.json</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>e775ea12-9867-70f2-6381-112e31478f75</t>
+          <t>decc377c-887e-7362-3bf7-81b1c9c58641</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
@@ -9331,7 +9331,7 @@
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/e775ea12-9867-70f2-6381-112e31478f75</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/decc377c-887e-7362-3bf7-81b1c9c58641</t>
         </is>
       </c>
       <c r="T73" t="inlineStr">
@@ -9341,12 +9341,12 @@
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/08e58358a211a53638e77e5431d7fedb34bd5f72.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/cfd0eab55fb67ed7ab341ab27bc1cb892d7a575c.jpg</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296196</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296221</t>
         </is>
       </c>
       <c r="W73" t="inlineStr">
@@ -9369,7 +9369,7 @@
       <c r="AB73" t="inlineStr"/>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/e775ea12-9867-70f2-6381-112e31478f75/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/decc377c-887e-7362-3bf7-81b1c9c58641/manifest</t>
         </is>
       </c>
       <c r="AD73" t="inlineStr"/>
@@ -9377,52 +9377,52 @@
       <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="inlineStr"/>
       <c r="AH73" t="n">
-        <v>146</v>
+        <v>51</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>玉蘂 [8]</t>
+          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [22]</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>A00:6067</t>
+          <t>A00:6257</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>ギョクズイ</t>
+          <t>レキダイ ザンケツ ニッキ</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>藤原 道家</t>
+          <t>黒川 春村</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>野宮定基 : 久世通夏 [ほか写]</t>
+          <t>[書写者不明]</t>
         </is>
       </c>
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr">
         <is>
-          <t>元禄12 [1699]-宝永3 [1706] 奥書</t>
+          <t>[安政5 (1858)]</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr">
         <is>
-          <t>写本|書名及び巻冊次は表紙による|奥中の書名: 光明峯寺禅閤道家公記, 峯禅閤記, 峯摂政記, 峯入道摂政記|承元4年の原奥書に「右即位記一卷者光明峯寺禅閤自筆正記也以件本左令吾基春卿透以写之云々加挍正之 ... 永正七年夷則上浣 從一位(花押)」とあり|奥書に「右以或人夲自常州到来令書写之彼夲端書云此冊上下卷 ... 元禄第十二暦仲夏中旬 羽林左衞中郎将藤原定基丗一才」(承元3), 「右光明峯寺禅閤道家公承元二年三月五六月八月四年二三月九月十十一十二月記は借請或人之夲自常州邊来書写之加一挍了/于時元禄第十二端午節也 左中郎将藤原定基丗才」(承元4), 「右玉蘂建暦元年少弟左中将通清朝臣助筆僅加一挍原本文字不正後来得正夲可改之者也/元禄十三年九月十日 松堂閑士(花押)丗二才」(建暦元), 「右玉蘂峯禅閤記建暦二年自二月至九月一冊以或人夲自常州邊来命家僚令書写手自加挍合了/元禄十二年五月六日 左中郎将藤原定基丗一才」(建暦2年上), 「宝永二年十月一日書写畢/承久二春玉蘂以故常州牧權中納言光圀公夲謄写之于時俗務紛擾先請慈兄源亜相公所被写也今以彼夲手自馳禿筆 余識藤(花押)丗七才/同三年二月廿五日一挍了」(承久2年上), 「右峯摂政承久二年記命傭書謄冩之手自一挍了/元禄第十二嵗次著雍単閼蕤賓中旬 羽林軍左衞中郎将藤原定基丗一才」(承久2年下), 「嘉禎四年正月二月閏二月三月四月六月玉蘂先年假借故常州牧前中納言光圀夲無剋力速遂書写之功建暦元年建暦二年下承久二年上及此卷等先献慈兄亜相君写之今及数年申復彼夲謄写之 ... 宝永三年十二月念日 参議從三位行左近衞權中将藤原朝臣定基生年卅八才」(嘉禎4年)とあり|毎半葉11行注文双行|漢文体日記|拠徳川光圀本及び中院通躬鈔本謄写|朱筆書き入れあり|印記: 「定基」(野宮定基), 「野宮書印」|虫損あり (裏打ち補修あり)</t>
+          <t>写本|責任表示及び書写年は『日本古典籍総合目録データベース』による|内容: 6: 光明院御記, 後光嚴院御記, 後小松院宸記, 天聴集. 28: 参議藤定長卿記 : 稱山丞記. 37: 定高卿記, 晴御会部類記, 家光卿御記, 權中納言平範輔卿記. 38: 左大史小槻季継記, 後堀川安貞二年放生會(実基公記), 石清水八幡宮, 弁官拝賀次第. 39: 大外記師光記, 資季卿記, 荒凉記, 忠高卿記. 40: 冷泉公相公記, 勝延法眼記 : 東寺大行事, 後中記 : 小路中納言資頼卿記葉室. 41: 中光記, 師兼記, 陽龍記. 42: 大宮司長則記, 口筆 : 實經, 顕朝卿記, 鴨御幸記. 43: 寳治二年記, 深心院關白記, 藤公親記, 照念院関白兼平公記. 44: 頼親記, 亀山殿行幸記 : 雅言卿記, 兼基公記. 45: 大嘗會御禊節下次第, 建治三年丁丑日記 : 三善康有, 建治四年正月廿一日 : 徳大寺大相國公孝記, 冬定卿記, 左大史小槻兼文記|内容: 46: 經任卿記, 前豊前守藤憲説記, 實兼公記. 47: 継塵記抄出. 48: 管見記, 公衡公記, 大外記師顕記, 大外記中原師淳記. 49: 真光院禪助僧正記, 吉田内府卿記. 50: 定清記, 叅議雅俊卿記, 太政大臣(公守公)御上表雜事, 仙洞御灌頂日記, 正安二年八月十一日於仙洞被始行熾盛光法, 正安三年御譲位記. 51: 實躬卿記. 52: 公茂公記, 冬平公記, 隆長卿記. 53: 忠教公記, 官記, 正三位長基卿記, 北面秀長記, 大外記中原師右記. 54: 文保元年, 日野中納言資朝卿記, 洞院大納言公敏卿記. 55: 隆蔭卿記, 文保三年記, 尹大納言師賢卿記, 革命記, 立倚子記, 萬里小路中納言藤藤房卿記|内容: 56: 資名卿記, 公秀公記, 一條家記装束抄出, 頼定卿記. 63: 松亞記, 日野大納言時光卿記, 後八條内府實継公記. 74: 成恩寺関白記. 78: 山科家礼記. 82: 諒闇記 : 後成恩寺殿, 宗典僧正記, 綱光公記, 贈従二位宗賢卿記, 義政公記. 84: 長禄二年戊寅正月, 見聞雜記. 87: 言國卿記. 88: 長興宿祢記, 元長卿記, 兼顕卿記, 小槻晴冨記|28末の原奥書に「右山丞記依 仰挍合書冩/享和二年四月 日撿挍保己一」とあり|50「正安二年八月十一日於仙洞被始行熾盛光法」末の原奥書に「文化十五年春二月以南山法曼院藏夲書冩之 撿挍保己一」とあり|横刷毛目表紙を使用|朱点, 朱引, 朱墨筆書き入れあり|付箋あり|蔵書印主信濃須坂藩主堀直格の命によって編集された古記録|他の原本は関東大震災により焼失|極札に「桂壽」(6), 「尚信」(53)との極書, 「武清」(44, 53), 「永海」(51), 「了伴」(52), 「了甫」(74), 「定時」(84, 88)との極印あり|印記: 「花廼家文庫」, 「墨阪十一代主寫藏記」(堀直格(1806-1880)), 「東京大學法理文學部書庫所藏」, 「閲覧室用 FOR USE IN THE READING ROOM」|虫損あり</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -9438,12 +9438,12 @@
       <c r="O74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/ca2da620-345c-76fa-9d1d-e7b2c55d757f.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/b6bde9f3-3f94-81f1-4307-d86d59d90fa3.json</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>ca2da620-345c-76fa-9d1d-e7b2c55d757f</t>
+          <t>b6bde9f3-3f94-81f1-4307-d86d59d90fa3</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
@@ -9453,7 +9453,7 @@
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/ca2da620-345c-76fa-9d1d-e7b2c55d757f</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/b6bde9f3-3f94-81f1-4307-d86d59d90fa3</t>
         </is>
       </c>
       <c r="T74" t="inlineStr">
@@ -9463,12 +9463,12 @@
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/8204e28b4e8f0e2f8abc1b939244f007093f3749.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/eda09740787be30df4b5cefc348bc2c063c8932c.jpg</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296197</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296222</t>
         </is>
       </c>
       <c r="W74" t="inlineStr">
@@ -9491,7 +9491,7 @@
       <c r="AB74" t="inlineStr"/>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/ca2da620-345c-76fa-9d1d-e7b2c55d757f/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/b6bde9f3-3f94-81f1-4307-d86d59d90fa3/manifest</t>
         </is>
       </c>
       <c r="AD74" t="inlineStr"/>
@@ -9499,27 +9499,31 @@
       <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="inlineStr"/>
       <c r="AH74" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>大明星天子法 : 又名法界虚空蔵法</t>
+          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [23]</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>A00:6097</t>
+          <t>A00:6257</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>ダイミョウジョウテンシホウ : マタミョウ ホッカイ コクウゾウホウ</t>
+          <t>レキダイ ザンケツ ニッキ</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
-      <c r="E75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>黒川 春村</t>
+        </is>
+      </c>
       <c r="F75" t="inlineStr">
         <is>
           <t>[書写者不明]</t>
@@ -9528,7 +9532,7 @@
       <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr">
         <is>
-          <t>[天文年間]</t>
+          <t>[安政5 (1858)]</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -9540,7 +9544,7 @@
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr">
         <is>
-          <t>写本|巻末の書名: 明星天子法|表紙の書名: 大明皇天子水|大尾に「明星天子法次苐 一交了」とあり|本奥書に「承久三年五月十三日/爲興法利生徃生極樂書冩之/金剛佛子觀照之」とあり|書袋に「天文古筆」, 「天明七未ノ年」とあり|毎半葉8行|押界を施した楮紙打紙を使用|粘葉装|虫損あり</t>
+          <t>写本|責任表示及び書写年は『日本古典籍総合目録データベース』による|内容: 6: 光明院御記, 後光嚴院御記, 後小松院宸記, 天聴集. 28: 参議藤定長卿記 : 稱山丞記. 37: 定高卿記, 晴御会部類記, 家光卿御記, 權中納言平範輔卿記. 38: 左大史小槻季継記, 後堀川安貞二年放生會(実基公記), 石清水八幡宮, 弁官拝賀次第. 39: 大外記師光記, 資季卿記, 荒凉記, 忠高卿記. 40: 冷泉公相公記, 勝延法眼記 : 東寺大行事, 後中記 : 小路中納言資頼卿記葉室. 41: 中光記, 師兼記, 陽龍記. 42: 大宮司長則記, 口筆 : 實經, 顕朝卿記, 鴨御幸記. 43: 寳治二年記, 深心院關白記, 藤公親記, 照念院関白兼平公記. 44: 頼親記, 亀山殿行幸記 : 雅言卿記, 兼基公記. 45: 大嘗會御禊節下次第, 建治三年丁丑日記 : 三善康有, 建治四年正月廿一日 : 徳大寺大相國公孝記, 冬定卿記, 左大史小槻兼文記|内容: 46: 經任卿記, 前豊前守藤憲説記, 實兼公記. 47: 継塵記抄出. 48: 管見記, 公衡公記, 大外記師顕記, 大外記中原師淳記. 49: 真光院禪助僧正記, 吉田内府卿記. 50: 定清記, 叅議雅俊卿記, 太政大臣(公守公)御上表雜事, 仙洞御灌頂日記, 正安二年八月十一日於仙洞被始行熾盛光法, 正安三年御譲位記. 51: 實躬卿記. 52: 公茂公記, 冬平公記, 隆長卿記. 53: 忠教公記, 官記, 正三位長基卿記, 北面秀長記, 大外記中原師右記. 54: 文保元年, 日野中納言資朝卿記, 洞院大納言公敏卿記. 55: 隆蔭卿記, 文保三年記, 尹大納言師賢卿記, 革命記, 立倚子記, 萬里小路中納言藤藤房卿記|内容: 56: 資名卿記, 公秀公記, 一條家記装束抄出, 頼定卿記. 63: 松亞記, 日野大納言時光卿記, 後八條内府實継公記. 74: 成恩寺関白記. 78: 山科家礼記. 82: 諒闇記 : 後成恩寺殿, 宗典僧正記, 綱光公記, 贈従二位宗賢卿記, 義政公記. 84: 長禄二年戊寅正月, 見聞雜記. 87: 言國卿記. 88: 長興宿祢記, 元長卿記, 兼顕卿記, 小槻晴冨記|28末の原奥書に「右山丞記依 仰挍合書冩/享和二年四月 日撿挍保己一」とあり|50「正安二年八月十一日於仙洞被始行熾盛光法」末の原奥書に「文化十五年春二月以南山法曼院藏夲書冩之 撿挍保己一」とあり|横刷毛目表紙を使用|朱点, 朱引, 朱墨筆書き入れあり|付箋あり|蔵書印主信濃須坂藩主堀直格の命によって編集された古記録|他の原本は関東大震災により焼失|極札に「桂壽」(6), 「尚信」(53)との極書, 「武清」(44, 53), 「永海」(51), 「了伴」(52), 「了甫」(74), 「定時」(84, 88)との極印あり|印記: 「花廼家文庫」, 「墨阪十一代主寫藏記」(堀直格(1806-1880)), 「東京大學法理文學部書庫所藏」, 「閲覧室用 FOR USE IN THE READING ROOM」|虫損あり</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -9556,12 +9560,12 @@
       <c r="O75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/a1905fc7-4727-0750-41d7-f0ca1df53f47.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/8bd2b968-05d3-77b9-352f-f36fa2260d39.json</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>a1905fc7-4727-0750-41d7-f0ca1df53f47</t>
+          <t>8bd2b968-05d3-77b9-352f-f36fa2260d39</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
@@ -9571,7 +9575,7 @@
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/a1905fc7-4727-0750-41d7-f0ca1df53f47</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/8bd2b968-05d3-77b9-352f-f36fa2260d39</t>
         </is>
       </c>
       <c r="T75" t="inlineStr">
@@ -9581,12 +9585,12 @@
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/b2590ef4e55f582d8059a5e072e1d6dad33bf996.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/30225b7ec7795f0c4d6102081bbf79b701183504.jpg</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296198</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296223</t>
         </is>
       </c>
       <c r="W75" t="inlineStr">
@@ -9609,7 +9613,7 @@
       <c r="AB75" t="inlineStr"/>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/a1905fc7-4727-0750-41d7-f0ca1df53f47/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/8bd2b968-05d3-77b9-352f-f36fa2260d39/manifest</t>
         </is>
       </c>
       <c r="AD75" t="inlineStr"/>
@@ -9617,36 +9621,40 @@
       <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="inlineStr"/>
       <c r="AH75" t="n">
-        <v>9</v>
+        <v>74</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>大嘗會悠紀主基鮮味之繪</t>
+          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [24]</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>A00:6108</t>
+          <t>A00:6257</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>ダイジョウエ ユキ スキ センミ ノ ズ</t>
+          <t>レキダイ ザンケツ ニッキ</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>黒川 春村</t>
+        </is>
+      </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>[佐伯]</t>
+          <t>[書写者不明]</t>
         </is>
       </c>
       <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr">
         <is>
-          <t>明和元 [1764] 識語</t>
+          <t>[安政5 (1858)]</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -9658,7 +9666,7 @@
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr">
         <is>
-          <t>絵巻|書名は識語による|書袋の書名: 悠紀主基鮮味之啚|表紙裏に「元文悠紀主基鮮味之圖 寛延同」とあり|巻末の識語に「右大嘗會悠紀主基鮮味之繪借請御厨子所預紀宗直朝臣令佐伯職房摸冩之畢 明和元年孟冬左少将藤原(花押)」とあり|絵4幅: 梅作枝, 糸作枩, 萩作枝, 萩作枝|紙本著色|彩色あり|帙入り|印記: 「野宮藏書」</t>
+          <t>写本|責任表示及び書写年は『日本古典籍総合目録データベース』による|内容: 6: 光明院御記, 後光嚴院御記, 後小松院宸記, 天聴集. 28: 参議藤定長卿記 : 稱山丞記. 37: 定高卿記, 晴御会部類記, 家光卿御記, 權中納言平範輔卿記. 38: 左大史小槻季継記, 後堀川安貞二年放生會(実基公記), 石清水八幡宮, 弁官拝賀次第. 39: 大外記師光記, 資季卿記, 荒凉記, 忠高卿記. 40: 冷泉公相公記, 勝延法眼記 : 東寺大行事, 後中記 : 小路中納言資頼卿記葉室. 41: 中光記, 師兼記, 陽龍記. 42: 大宮司長則記, 口筆 : 實經, 顕朝卿記, 鴨御幸記. 43: 寳治二年記, 深心院關白記, 藤公親記, 照念院関白兼平公記. 44: 頼親記, 亀山殿行幸記 : 雅言卿記, 兼基公記. 45: 大嘗會御禊節下次第, 建治三年丁丑日記 : 三善康有, 建治四年正月廿一日 : 徳大寺大相國公孝記, 冬定卿記, 左大史小槻兼文記|内容: 46: 經任卿記, 前豊前守藤憲説記, 實兼公記. 47: 継塵記抄出. 48: 管見記, 公衡公記, 大外記師顕記, 大外記中原師淳記. 49: 真光院禪助僧正記, 吉田内府卿記. 50: 定清記, 叅議雅俊卿記, 太政大臣(公守公)御上表雜事, 仙洞御灌頂日記, 正安二年八月十一日於仙洞被始行熾盛光法, 正安三年御譲位記. 51: 實躬卿記. 52: 公茂公記, 冬平公記, 隆長卿記. 53: 忠教公記, 官記, 正三位長基卿記, 北面秀長記, 大外記中原師右記. 54: 文保元年, 日野中納言資朝卿記, 洞院大納言公敏卿記. 55: 隆蔭卿記, 文保三年記, 尹大納言師賢卿記, 革命記, 立倚子記, 萬里小路中納言藤藤房卿記|内容: 56: 資名卿記, 公秀公記, 一條家記装束抄出, 頼定卿記. 63: 松亞記, 日野大納言時光卿記, 後八條内府實継公記. 74: 成恩寺関白記. 78: 山科家礼記. 82: 諒闇記 : 後成恩寺殿, 宗典僧正記, 綱光公記, 贈従二位宗賢卿記, 義政公記. 84: 長禄二年戊寅正月, 見聞雜記. 87: 言國卿記. 88: 長興宿祢記, 元長卿記, 兼顕卿記, 小槻晴冨記|28末の原奥書に「右山丞記依 仰挍合書冩/享和二年四月 日撿挍保己一」とあり|50「正安二年八月十一日於仙洞被始行熾盛光法」末の原奥書に「文化十五年春二月以南山法曼院藏夲書冩之 撿挍保己一」とあり|横刷毛目表紙を使用|朱点, 朱引, 朱墨筆書き入れあり|付箋あり|蔵書印主信濃須坂藩主堀直格の命によって編集された古記録|他の原本は関東大震災により焼失|極札に「桂壽」(6), 「尚信」(53)との極書, 「武清」(44, 53), 「永海」(51), 「了伴」(52), 「了甫」(74), 「定時」(84, 88)との極印あり|印記: 「花廼家文庫」, 「墨阪十一代主寫藏記」(堀直格(1806-1880)), 「東京大學法理文學部書庫所藏」, 「閲覧室用 FOR USE IN THE READING ROOM」|虫損あり</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -9674,12 +9682,12 @@
       <c r="O76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/d00e906c-5404-4fc1-44c9-1566cf7f7012.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/c6e97538-22ed-8a51-0e3a-550b7d652860.json</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>d00e906c-5404-4fc1-44c9-1566cf7f7012</t>
+          <t>c6e97538-22ed-8a51-0e3a-550b7d652860</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
@@ -9689,7 +9697,7 @@
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/d00e906c-5404-4fc1-44c9-1566cf7f7012</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/c6e97538-22ed-8a51-0e3a-550b7d652860</t>
         </is>
       </c>
       <c r="T76" t="inlineStr">
@@ -9699,12 +9707,12 @@
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/51e8aa982b380211852796b36819e6c6c6bf1583.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/a04dfdaed6c9dc7211358c5ad96c4bc6e9312747.jpg</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296199</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296224</t>
         </is>
       </c>
       <c r="W76" t="inlineStr">
@@ -9727,7 +9735,7 @@
       <c r="AB76" t="inlineStr"/>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/d00e906c-5404-4fc1-44c9-1566cf7f7012/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/c6e97538-22ed-8a51-0e3a-550b7d652860/manifest</t>
         </is>
       </c>
       <c r="AD76" t="inlineStr"/>
@@ -9735,36 +9743,40 @@
       <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="inlineStr"/>
       <c r="AH76" t="n">
-        <v>11</v>
+        <v>62</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>真言宗脈啚 : 栂尾夲</t>
+          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [25]</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>A00:6129</t>
+          <t>A00:6257</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>シンゴンシュウ ミャクズ : トガノオボン</t>
+          <t>レキダイ ザンケツ ニッキ</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
-      <c r="E77" t="inlineStr"/>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>黒川 春村</t>
+        </is>
+      </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>覺心</t>
+          <t>[書写者不明]</t>
         </is>
       </c>
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr">
         <is>
-          <t>享保9 [1724] 奥書</t>
+          <t>[安政5 (1858)]</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -9776,7 +9788,7 @@
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr">
         <is>
-          <t>写本|書名は題簽による|帙題簽の書名: 真言宗血脈圗|奥書に「正徳二年之春請自性院僧正開栂尾山宮御封之經藏求淂于古聖教若干部是其一也 沙門道空」, 「享保九年甲辰夏寓于洛西御阜草菴以五智山之本冩之訖 南紀護国寺沙門覺心/同年六月晦日以栂尾法鼓臺古本挍合之了」, 「昭和八年四月念三日閲覧砌訂正誤字記入落罫云尒 中野達慧識」とあり|朱筆書き入れあり|印記: 「和學講談所」, 「温故堂文庫」(塙家), 「松平家藏書印」|虫損あり</t>
+          <t>写本|責任表示及び書写年は『日本古典籍総合目録データベース』による|内容: 6: 光明院御記, 後光嚴院御記, 後小松院宸記, 天聴集. 28: 参議藤定長卿記 : 稱山丞記. 37: 定高卿記, 晴御会部類記, 家光卿御記, 權中納言平範輔卿記. 38: 左大史小槻季継記, 後堀川安貞二年放生會(実基公記), 石清水八幡宮, 弁官拝賀次第. 39: 大外記師光記, 資季卿記, 荒凉記, 忠高卿記. 40: 冷泉公相公記, 勝延法眼記 : 東寺大行事, 後中記 : 小路中納言資頼卿記葉室. 41: 中光記, 師兼記, 陽龍記. 42: 大宮司長則記, 口筆 : 實經, 顕朝卿記, 鴨御幸記. 43: 寳治二年記, 深心院關白記, 藤公親記, 照念院関白兼平公記. 44: 頼親記, 亀山殿行幸記 : 雅言卿記, 兼基公記. 45: 大嘗會御禊節下次第, 建治三年丁丑日記 : 三善康有, 建治四年正月廿一日 : 徳大寺大相國公孝記, 冬定卿記, 左大史小槻兼文記|内容: 46: 經任卿記, 前豊前守藤憲説記, 實兼公記. 47: 継塵記抄出. 48: 管見記, 公衡公記, 大外記師顕記, 大外記中原師淳記. 49: 真光院禪助僧正記, 吉田内府卿記. 50: 定清記, 叅議雅俊卿記, 太政大臣(公守公)御上表雜事, 仙洞御灌頂日記, 正安二年八月十一日於仙洞被始行熾盛光法, 正安三年御譲位記. 51: 實躬卿記. 52: 公茂公記, 冬平公記, 隆長卿記. 53: 忠教公記, 官記, 正三位長基卿記, 北面秀長記, 大外記中原師右記. 54: 文保元年, 日野中納言資朝卿記, 洞院大納言公敏卿記. 55: 隆蔭卿記, 文保三年記, 尹大納言師賢卿記, 革命記, 立倚子記, 萬里小路中納言藤藤房卿記|内容: 56: 資名卿記, 公秀公記, 一條家記装束抄出, 頼定卿記. 63: 松亞記, 日野大納言時光卿記, 後八條内府實継公記. 74: 成恩寺関白記. 78: 山科家礼記. 82: 諒闇記 : 後成恩寺殿, 宗典僧正記, 綱光公記, 贈従二位宗賢卿記, 義政公記. 84: 長禄二年戊寅正月, 見聞雜記. 87: 言國卿記. 88: 長興宿祢記, 元長卿記, 兼顕卿記, 小槻晴冨記|28末の原奥書に「右山丞記依 仰挍合書冩/享和二年四月 日撿挍保己一」とあり|50「正安二年八月十一日於仙洞被始行熾盛光法」末の原奥書に「文化十五年春二月以南山法曼院藏夲書冩之 撿挍保己一」とあり|横刷毛目表紙を使用|朱点, 朱引, 朱墨筆書き入れあり|付箋あり|蔵書印主信濃須坂藩主堀直格の命によって編集された古記録|他の原本は関東大震災により焼失|極札に「桂壽」(6), 「尚信」(53)との極書, 「武清」(44, 53), 「永海」(51), 「了伴」(52), 「了甫」(74), 「定時」(84, 88)との極印あり|印記: 「花廼家文庫」, 「墨阪十一代主寫藏記」(堀直格(1806-1880)), 「東京大學法理文學部書庫所藏」, 「閲覧室用 FOR USE IN THE READING ROOM」|虫損あり</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -9792,12 +9804,12 @@
       <c r="O77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/e6a30e98-5da6-7e0d-7a92-5b26c887309f.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/48123112-700b-8619-731b-649449ff034b.json</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>e6a30e98-5da6-7e0d-7a92-5b26c887309f</t>
+          <t>48123112-700b-8619-731b-649449ff034b</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
@@ -9807,7 +9819,7 @@
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/e6a30e98-5da6-7e0d-7a92-5b26c887309f</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/48123112-700b-8619-731b-649449ff034b</t>
         </is>
       </c>
       <c r="T77" t="inlineStr">
@@ -9817,12 +9829,12 @@
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/10842787f14673fb3729595dd908dde4c4dd6ad8.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/4c918a15ed3dc97a18f7bc977b4dc2e8c724d774.jpg</t>
         </is>
       </c>
       <c r="V77" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296200</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296225</t>
         </is>
       </c>
       <c r="W77" t="inlineStr">
@@ -9845,7 +9857,7 @@
       <c r="AB77" t="inlineStr"/>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/e6a30e98-5da6-7e0d-7a92-5b26c887309f/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/48123112-700b-8619-731b-649449ff034b/manifest</t>
         </is>
       </c>
       <c r="AD77" t="inlineStr"/>
@@ -9853,13 +9865,13 @@
       <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="inlineStr"/>
       <c r="AH77" t="n">
-        <v>22</v>
+        <v>78</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [1]</t>
+          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [26]</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -9914,12 +9926,12 @@
       <c r="O78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/c32632af-9dc0-504a-5437-15a055d52628.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/9b2b928b-4eda-76c6-0dfd-03bde69c046c.json</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>c32632af-9dc0-504a-5437-15a055d52628</t>
+          <t>9b2b928b-4eda-76c6-0dfd-03bde69c046c</t>
         </is>
       </c>
       <c r="R78" t="inlineStr">
@@ -9929,7 +9941,7 @@
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/c32632af-9dc0-504a-5437-15a055d52628</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/9b2b928b-4eda-76c6-0dfd-03bde69c046c</t>
         </is>
       </c>
       <c r="T78" t="inlineStr">
@@ -9939,12 +9951,12 @@
       </c>
       <c r="U78" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/2230dfedd3d91cc8b1c5532de33a8f8559be8357.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/7903cd89a232a0d9b4b243d90852d31d93c80300.jpg</t>
         </is>
       </c>
       <c r="V78" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296201</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296226</t>
         </is>
       </c>
       <c r="W78" t="inlineStr">
@@ -9967,7 +9979,7 @@
       <c r="AB78" t="inlineStr"/>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/c32632af-9dc0-504a-5437-15a055d52628/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/9b2b928b-4eda-76c6-0dfd-03bde69c046c/manifest</t>
         </is>
       </c>
       <c r="AD78" t="inlineStr"/>
@@ -9975,31 +9987,31 @@
       <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="inlineStr"/>
       <c r="AH78" t="n">
-        <v>72</v>
+        <v>66</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>おちくほのさうし</t>
+          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [27]</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>A00:4083</t>
+          <t>A00:6257</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>オチクボ ノ ソウシ</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>おちくほ物語|御本</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr"/>
+          <t>レキダイ ザンケツ ニッキ</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>黒川 春村</t>
+        </is>
+      </c>
       <c r="F79" t="inlineStr">
         <is>
           <t>[書写者不明]</t>
@@ -10008,7 +10020,7 @@
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr">
         <is>
-          <t>[江戸前期]</t>
+          <t>[安政5 (1858)]</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -10016,15 +10028,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>写本</t>
-        </is>
-      </c>
+      <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr">
         <is>
-          <t>書名は題簽による|毎半帖10行|漢字平仮名交じり文|奈良絵本|桜唐草文様緞子表紙, 松葉散しに山雲の金箔見返し, 金泥下絵鳥の子紙を使用|列帖装|二重箱入り</t>
+          <t>写本|責任表示及び書写年は『日本古典籍総合目録データベース』による|内容: 6: 光明院御記, 後光嚴院御記, 後小松院宸記, 天聴集. 28: 参議藤定長卿記 : 稱山丞記. 37: 定高卿記, 晴御会部類記, 家光卿御記, 權中納言平範輔卿記. 38: 左大史小槻季継記, 後堀川安貞二年放生會(実基公記), 石清水八幡宮, 弁官拝賀次第. 39: 大外記師光記, 資季卿記, 荒凉記, 忠高卿記. 40: 冷泉公相公記, 勝延法眼記 : 東寺大行事, 後中記 : 小路中納言資頼卿記葉室. 41: 中光記, 師兼記, 陽龍記. 42: 大宮司長則記, 口筆 : 實經, 顕朝卿記, 鴨御幸記. 43: 寳治二年記, 深心院關白記, 藤公親記, 照念院関白兼平公記. 44: 頼親記, 亀山殿行幸記 : 雅言卿記, 兼基公記. 45: 大嘗會御禊節下次第, 建治三年丁丑日記 : 三善康有, 建治四年正月廿一日 : 徳大寺大相國公孝記, 冬定卿記, 左大史小槻兼文記|内容: 46: 經任卿記, 前豊前守藤憲説記, 實兼公記. 47: 継塵記抄出. 48: 管見記, 公衡公記, 大外記師顕記, 大外記中原師淳記. 49: 真光院禪助僧正記, 吉田内府卿記. 50: 定清記, 叅議雅俊卿記, 太政大臣(公守公)御上表雜事, 仙洞御灌頂日記, 正安二年八月十一日於仙洞被始行熾盛光法, 正安三年御譲位記. 51: 實躬卿記. 52: 公茂公記, 冬平公記, 隆長卿記. 53: 忠教公記, 官記, 正三位長基卿記, 北面秀長記, 大外記中原師右記. 54: 文保元年, 日野中納言資朝卿記, 洞院大納言公敏卿記. 55: 隆蔭卿記, 文保三年記, 尹大納言師賢卿記, 革命記, 立倚子記, 萬里小路中納言藤藤房卿記|内容: 56: 資名卿記, 公秀公記, 一條家記装束抄出, 頼定卿記. 63: 松亞記, 日野大納言時光卿記, 後八條内府實継公記. 74: 成恩寺関白記. 78: 山科家礼記. 82: 諒闇記 : 後成恩寺殿, 宗典僧正記, 綱光公記, 贈従二位宗賢卿記, 義政公記. 84: 長禄二年戊寅正月, 見聞雜記. 87: 言國卿記. 88: 長興宿祢記, 元長卿記, 兼顕卿記, 小槻晴冨記|28末の原奥書に「右山丞記依 仰挍合書冩/享和二年四月 日撿挍保己一」とあり|50「正安二年八月十一日於仙洞被始行熾盛光法」末の原奥書に「文化十五年春二月以南山法曼院藏夲書冩之 撿挍保己一」とあり|横刷毛目表紙を使用|朱点, 朱引, 朱墨筆書き入れあり|付箋あり|蔵書印主信濃須坂藩主堀直格の命によって編集された古記録|他の原本は関東大震災により焼失|極札に「桂壽」(6), 「尚信」(53)との極書, 「武清」(44, 53), 「永海」(51), 「了伴」(52), 「了甫」(74), 「定時」(84, 88)との極印あり|印記: 「花廼家文庫」, 「墨阪十一代主寫藏記」(堀直格(1806-1880)), 「東京大學法理文學部書庫所藏」, 「閲覧室用 FOR USE IN THE READING ROOM」|虫損あり</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -10034,28 +10042,28 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>和古書</t>
+          <t>図書</t>
         </is>
       </c>
       <c r="O79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/8aa19100-0937-5fd9-29f1-ba41ad8d1830.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/ccc6c3da-1648-49f5-91fc-2faaf5400387.json</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>8aa19100-0937-5fd9-29f1-ba41ad8d1830</t>
+          <t>ccc6c3da-1648-49f5-91fc-2faaf5400387</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/8aa19100-0937-5fd9-29f1-ba41ad8d1830</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/ccc6c3da-1648-49f5-91fc-2faaf5400387</t>
         </is>
       </c>
       <c r="T79" t="inlineStr">
@@ -10065,12 +10073,12 @@
       </c>
       <c r="U79" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/124815802d3a78d8f78dd4fbb98d24d55e5c3b34.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/1e476c24ffbe9fd54b432acbf27eb918fc4162d0.jpg</t>
         </is>
       </c>
       <c r="V79" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1182819</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296227</t>
         </is>
       </c>
       <c r="W79" t="inlineStr">
@@ -10093,7 +10101,7 @@
       <c r="AB79" t="inlineStr"/>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/8aa19100-0937-5fd9-29f1-ba41ad8d1830/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/ccc6c3da-1648-49f5-91fc-2faaf5400387/manifest</t>
         </is>
       </c>
       <c r="AD79" t="inlineStr"/>
@@ -10101,48 +10109,40 @@
       <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="inlineStr"/>
       <c r="AH79" t="n">
-        <v>33</v>
+        <v>70</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>甲午日記 : 天保五年正月吉日</t>
+          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [28]</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>A00:4613</t>
+          <t>A00:6257</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>コウゴ ニッキ : テンポウ ゴネン ショウガツ キチジツ</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>天保五年馬琴日記</t>
-        </is>
-      </c>
+          <t>レキダイ ザンケツ ニッキ</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>滝沢 馬琴</t>
+          <t>黒川 春村</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>瀧澤馬琴 [自筆]</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>1834</t>
-        </is>
-      </c>
+          <t>[書写者不明]</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr">
         <is>
-          <t>天保5</t>
+          <t>[安政5 (1858)]</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -10150,15 +10150,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>写本</t>
-        </is>
-      </c>
+      <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr">
         <is>
-          <t>書名は扉による|巻末に「已上午年日記畢」とあり|裏表紙に「神田 瀧澤」とあり|内容: 天保五甲午年春正月-12月|墨抹, 胡粉による修正あり|巻末の識語末に「昭和五年十二月に至って脩覆を了せり」とあり|虫損あり (裏打ち補修あり)</t>
+          <t>写本|責任表示及び書写年は『日本古典籍総合目録データベース』による|内容: 6: 光明院御記, 後光嚴院御記, 後小松院宸記, 天聴集. 28: 参議藤定長卿記 : 稱山丞記. 37: 定高卿記, 晴御会部類記, 家光卿御記, 權中納言平範輔卿記. 38: 左大史小槻季継記, 後堀川安貞二年放生會(実基公記), 石清水八幡宮, 弁官拝賀次第. 39: 大外記師光記, 資季卿記, 荒凉記, 忠高卿記. 40: 冷泉公相公記, 勝延法眼記 : 東寺大行事, 後中記 : 小路中納言資頼卿記葉室. 41: 中光記, 師兼記, 陽龍記. 42: 大宮司長則記, 口筆 : 實經, 顕朝卿記, 鴨御幸記. 43: 寳治二年記, 深心院關白記, 藤公親記, 照念院関白兼平公記. 44: 頼親記, 亀山殿行幸記 : 雅言卿記, 兼基公記. 45: 大嘗會御禊節下次第, 建治三年丁丑日記 : 三善康有, 建治四年正月廿一日 : 徳大寺大相國公孝記, 冬定卿記, 左大史小槻兼文記|内容: 46: 經任卿記, 前豊前守藤憲説記, 實兼公記. 47: 継塵記抄出. 48: 管見記, 公衡公記, 大外記師顕記, 大外記中原師淳記. 49: 真光院禪助僧正記, 吉田内府卿記. 50: 定清記, 叅議雅俊卿記, 太政大臣(公守公)御上表雜事, 仙洞御灌頂日記, 正安二年八月十一日於仙洞被始行熾盛光法, 正安三年御譲位記. 51: 實躬卿記. 52: 公茂公記, 冬平公記, 隆長卿記. 53: 忠教公記, 官記, 正三位長基卿記, 北面秀長記, 大外記中原師右記. 54: 文保元年, 日野中納言資朝卿記, 洞院大納言公敏卿記. 55: 隆蔭卿記, 文保三年記, 尹大納言師賢卿記, 革命記, 立倚子記, 萬里小路中納言藤藤房卿記|内容: 56: 資名卿記, 公秀公記, 一條家記装束抄出, 頼定卿記. 63: 松亞記, 日野大納言時光卿記, 後八條内府實継公記. 74: 成恩寺関白記. 78: 山科家礼記. 82: 諒闇記 : 後成恩寺殿, 宗典僧正記, 綱光公記, 贈従二位宗賢卿記, 義政公記. 84: 長禄二年戊寅正月, 見聞雜記. 87: 言國卿記. 88: 長興宿祢記, 元長卿記, 兼顕卿記, 小槻晴冨記|28末の原奥書に「右山丞記依 仰挍合書冩/享和二年四月 日撿挍保己一」とあり|50「正安二年八月十一日於仙洞被始行熾盛光法」末の原奥書に「文化十五年春二月以南山法曼院藏夲書冩之 撿挍保己一」とあり|横刷毛目表紙を使用|朱点, 朱引, 朱墨筆書き入れあり|付箋あり|蔵書印主信濃須坂藩主堀直格の命によって編集された古記録|他の原本は関東大震災により焼失|極札に「桂壽」(6), 「尚信」(53)との極書, 「武清」(44, 53), 「永海」(51), 「了伴」(52), 「了甫」(74), 「定時」(84, 88)との極印あり|印記: 「花廼家文庫」, 「墨阪十一代主寫藏記」(堀直格(1806-1880)), 「東京大學法理文學部書庫所藏」, 「閲覧室用 FOR USE IN THE READING ROOM」|虫損あり</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -10168,28 +10164,28 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>和古書</t>
+          <t>図書</t>
         </is>
       </c>
       <c r="O80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/c91cb308-03bd-94f5-3c56-9d0fac9424d3.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/9f3a126c-84bb-8f96-2916-b65ace30a616.json</t>
         </is>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>c91cb308-03bd-94f5-3c56-9d0fac9424d3</t>
+          <t>9f3a126c-84bb-8f96-2916-b65ace30a616</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/c91cb308-03bd-94f5-3c56-9d0fac9424d3</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/9f3a126c-84bb-8f96-2916-b65ace30a616</t>
         </is>
       </c>
       <c r="T80" t="inlineStr">
@@ -10199,12 +10195,12 @@
       </c>
       <c r="U80" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/92f1a1f83433e8cf04243d82fb0811e6cf653db2.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/fc4844ae32ad2dd582e3570965cb142f5f370f74.jpg</t>
         </is>
       </c>
       <c r="V80" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1182820</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296228</t>
         </is>
       </c>
       <c r="W80" t="inlineStr">
@@ -10227,7 +10223,7 @@
       <c r="AB80" t="inlineStr"/>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/c91cb308-03bd-94f5-3c56-9d0fac9424d3/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/9f3a126c-84bb-8f96-2916-b65ace30a616/manifest</t>
         </is>
       </c>
       <c r="AD80" t="inlineStr"/>
@@ -10235,27 +10231,31 @@
       <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="inlineStr"/>
       <c r="AH80" t="n">
-        <v>172</v>
+        <v>70</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>天神記</t>
+          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [29]</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>A00:5770</t>
+          <t>A00:6257</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>テンジンキ</t>
+          <t>レキダイ ザンケツ ニッキ</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
-      <c r="E81" t="inlineStr"/>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>黒川 春村</t>
+        </is>
+      </c>
       <c r="F81" t="inlineStr">
         <is>
           <t>[書写者不明]</t>
@@ -10264,7 +10264,7 @@
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr">
         <is>
-          <t>[室町末期-江戸前期]</t>
+          <t>[安政5 (1858)]</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -10272,15 +10272,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>写本</t>
-        </is>
-      </c>
+      <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr">
         <is>
-          <t>書名は表紙( 朱書)による|毎半葉13行|奈良絵本|秋草に籬の紺紙金泥表紙, 麻の葉繋ぎに丸龍文様の銀箔見返しを使用|印記: 「渡郶文庫珍藏書印」(渡部信)</t>
+          <t>写本|責任表示及び書写年は『日本古典籍総合目録データベース』による|内容: 6: 光明院御記, 後光嚴院御記, 後小松院宸記, 天聴集. 28: 参議藤定長卿記 : 稱山丞記. 37: 定高卿記, 晴御会部類記, 家光卿御記, 權中納言平範輔卿記. 38: 左大史小槻季継記, 後堀川安貞二年放生會(実基公記), 石清水八幡宮, 弁官拝賀次第. 39: 大外記師光記, 資季卿記, 荒凉記, 忠高卿記. 40: 冷泉公相公記, 勝延法眼記 : 東寺大行事, 後中記 : 小路中納言資頼卿記葉室. 41: 中光記, 師兼記, 陽龍記. 42: 大宮司長則記, 口筆 : 實經, 顕朝卿記, 鴨御幸記. 43: 寳治二年記, 深心院關白記, 藤公親記, 照念院関白兼平公記. 44: 頼親記, 亀山殿行幸記 : 雅言卿記, 兼基公記. 45: 大嘗會御禊節下次第, 建治三年丁丑日記 : 三善康有, 建治四年正月廿一日 : 徳大寺大相國公孝記, 冬定卿記, 左大史小槻兼文記|内容: 46: 經任卿記, 前豊前守藤憲説記, 實兼公記. 47: 継塵記抄出. 48: 管見記, 公衡公記, 大外記師顕記, 大外記中原師淳記. 49: 真光院禪助僧正記, 吉田内府卿記. 50: 定清記, 叅議雅俊卿記, 太政大臣(公守公)御上表雜事, 仙洞御灌頂日記, 正安二年八月十一日於仙洞被始行熾盛光法, 正安三年御譲位記. 51: 實躬卿記. 52: 公茂公記, 冬平公記, 隆長卿記. 53: 忠教公記, 官記, 正三位長基卿記, 北面秀長記, 大外記中原師右記. 54: 文保元年, 日野中納言資朝卿記, 洞院大納言公敏卿記. 55: 隆蔭卿記, 文保三年記, 尹大納言師賢卿記, 革命記, 立倚子記, 萬里小路中納言藤藤房卿記|内容: 56: 資名卿記, 公秀公記, 一條家記装束抄出, 頼定卿記. 63: 松亞記, 日野大納言時光卿記, 後八條内府實継公記. 74: 成恩寺関白記. 78: 山科家礼記. 82: 諒闇記 : 後成恩寺殿, 宗典僧正記, 綱光公記, 贈従二位宗賢卿記, 義政公記. 84: 長禄二年戊寅正月, 見聞雜記. 87: 言國卿記. 88: 長興宿祢記, 元長卿記, 兼顕卿記, 小槻晴冨記|28末の原奥書に「右山丞記依 仰挍合書冩/享和二年四月 日撿挍保己一」とあり|50「正安二年八月十一日於仙洞被始行熾盛光法」末の原奥書に「文化十五年春二月以南山法曼院藏夲書冩之 撿挍保己一」とあり|横刷毛目表紙を使用|朱点, 朱引, 朱墨筆書き入れあり|付箋あり|蔵書印主信濃須坂藩主堀直格の命によって編集された古記録|他の原本は関東大震災により焼失|極札に「桂壽」(6), 「尚信」(53)との極書, 「武清」(44, 53), 「永海」(51), 「了伴」(52), 「了甫」(74), 「定時」(84, 88)との極印あり|印記: 「花廼家文庫」, 「墨阪十一代主寫藏記」(堀直格(1806-1880)), 「東京大學法理文學部書庫所藏」, 「閲覧室用 FOR USE IN THE READING ROOM」|虫損あり</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -10290,28 +10286,28 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>和古書</t>
+          <t>図書</t>
         </is>
       </c>
       <c r="O81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/f7abc34f-6ff4-1309-4e13-cd69cce698b7.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/7cdebe3a-8fb4-14b4-7ddb-3f92f3be9668.json</t>
         </is>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>f7abc34f-6ff4-1309-4e13-cd69cce698b7</t>
+          <t>7cdebe3a-8fb4-14b4-7ddb-3f92f3be9668</t>
         </is>
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/f7abc34f-6ff4-1309-4e13-cd69cce698b7</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/7cdebe3a-8fb4-14b4-7ddb-3f92f3be9668</t>
         </is>
       </c>
       <c r="T81" t="inlineStr">
@@ -10321,12 +10317,12 @@
       </c>
       <c r="U81" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/b6b3dd9c0e350f9b1b14c1a2ba0d012e6762e42c.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/08f5648a7b5512a896986520a6449d3620439071.jpg</t>
         </is>
       </c>
       <c r="V81" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1182821</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296229</t>
         </is>
       </c>
       <c r="W81" t="inlineStr">
@@ -10349,7 +10345,7 @@
       <c r="AB81" t="inlineStr"/>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/f7abc34f-6ff4-1309-4e13-cd69cce698b7/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/7cdebe3a-8fb4-14b4-7ddb-3f92f3be9668/manifest</t>
         </is>
       </c>
       <c r="AD81" t="inlineStr"/>
@@ -10357,36 +10353,40 @@
       <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="inlineStr"/>
       <c r="AH81" t="n">
-        <v>14</v>
+        <v>70</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>各種殘經 : 出鄯善縣土峪溝</t>
+          <t>普賢延命</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>A00:4033</t>
+          <t>A00:6264</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>カクシュ ザンキョウ : シュツ ゼンゼンケン トヨクコウ</t>
+          <t>フゲン エンメイ</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
-      <c r="E82" t="inlineStr"/>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>興然</t>
+        </is>
+      </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>[書写者不明]</t>
+          <t>長円 [写]</t>
         </is>
       </c>
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr">
         <is>
-          <t>[書写年不明]</t>
+          <t>嘉禎2 [1236] 奥書</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -10398,12 +10398,12 @@
       <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr">
         <is>
-          <t>写本残片|書名は題簽による|題簽に「出鄯善縣土峪溝 素文珍藏」とあり|識語に「為楊枝甘露滴入紙中展巻把玩但覺異香盈字 晉卿」, 「右二紙係亜利安字 晉卿」, 「右二紙係畏吾児字 晉卿」とあり|蔵書票に「殘經佛像梵字 十五段 鄯善」, 「梵字第一號」とあり|巻子本|箱入|印記: 「臣樹枏印」, 「晉卿」, 「王仲子」, 「王樹枏印」</t>
+          <t>写本|内題下に「師 理教」, 「嘉禎二年奥書アリ 長円書」とあり|巻末に「越前闍梨浄与口傳 興然夲」とあり|奥書に「嘉禎二年四月六月奉傳受空達御房ノ長円」とあり|裏に「正和元年壬子八月廿九日於成身院奉伝受之了」とあり|巻子本|送り仮名, 傍訓あり|虫損あり (裏打ち補修あり)</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>中国語</t>
+          <t>日本語</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -10414,12 +10414,12 @@
       <c r="O82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/704d2c7a-4882-6fc8-60d1-94c1e2799bbd.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/e57fef06-5cfd-a602-6a89-f4d7d4360e87.json</t>
         </is>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>704d2c7a-4882-6fc8-60d1-94c1e2799bbd</t>
+          <t>e57fef06-5cfd-a602-6a89-f4d7d4360e87</t>
         </is>
       </c>
       <c r="R82" t="inlineStr">
@@ -10429,7 +10429,7 @@
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/704d2c7a-4882-6fc8-60d1-94c1e2799bbd</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/e57fef06-5cfd-a602-6a89-f4d7d4360e87</t>
         </is>
       </c>
       <c r="T82" t="inlineStr">
@@ -10439,12 +10439,12 @@
       </c>
       <c r="U82" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/4cc89d9a25687c69b3dc3791fd39ac740de2c4a0.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/eec20da7736c221a3c86321abead9d8d9429dceb.jpg</t>
         </is>
       </c>
       <c r="V82" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296165</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296230</t>
         </is>
       </c>
       <c r="W82" t="inlineStr">
@@ -10467,7 +10467,7 @@
       <c r="AB82" t="inlineStr"/>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/704d2c7a-4882-6fc8-60d1-94c1e2799bbd/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/e57fef06-5cfd-a602-6a89-f4d7d4360e87/manifest</t>
         </is>
       </c>
       <c r="AD82" t="inlineStr"/>
@@ -10475,52 +10475,52 @@
       <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="inlineStr"/>
       <c r="AH82" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>和漢朗詠集 2巻 [1]</t>
+          <t>如法愛染王</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>A00:4081</t>
+          <t>A00:6265</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>ワカン ロウエイシュウ</t>
+          <t>ニョホウ アイゼンオウ</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
-          <t>藤原 公任</t>
+          <t>仁海</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>[書写者不明]</t>
+          <t>禅喜 [写]</t>
         </is>
       </c>
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr">
         <is>
-          <t>[江戸前期]</t>
+          <t>嘉暦2 [1327] 奥書</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
       <c r="L83" t="inlineStr">
         <is>
-          <t>写本|書名は目首及び題簽による|外箱の書名: 御本|責任表示は『日本古典籍総合目録データベース』による|巻上: 春, 夏, 秋, 冬. 巻下: 雜|題簽による巻冊次表示: 上, 下|毎半帖8行|漢字平仮名交じり文|鳳凰菱繋ぎ文様緞子表紙, 松葉散しに山雲の金箔見返し, 金泥下絵鳥の子紙を使用|列帖装|二重箱入り</t>
+          <t>写本|表紙の書名: 如法愛染|内題下に「付小野大次苐修之」とあり|本奥書に「延慶二年夘月十日於仁和寺真光院書写了 金剛佛子印法 生年卅二」とあり|奥書に「嘉暦二年正月廿二日全写了 禅喜 生年卅一」とあり|巻子本|小野流|淡墨界の料紙を使用(界匡廓: 23.8×2.2cm)|巻頭下部の貼紙に「嘉暦二年巨今五百八十二年鎌倉時代四一ノ六九七号」とあり|破損, 虫損あり (裏打ち補修あり)</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -10536,12 +10536,12 @@
       <c r="O83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/ba79db36-23e8-1a8a-1ad9-a5809c1109be.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/e321350d-483d-6e38-81a2-a637b8f798fb.json</t>
         </is>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>ba79db36-23e8-1a8a-1ad9-a5809c1109be</t>
+          <t>e321350d-483d-6e38-81a2-a637b8f798fb</t>
         </is>
       </c>
       <c r="R83" t="inlineStr">
@@ -10551,7 +10551,7 @@
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/ba79db36-23e8-1a8a-1ad9-a5809c1109be</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/e321350d-483d-6e38-81a2-a637b8f798fb</t>
         </is>
       </c>
       <c r="T83" t="inlineStr">
@@ -10561,12 +10561,12 @@
       </c>
       <c r="U83" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/0dbc6905fbe6d7441026c6ec7f4092a564cd7606.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/355285a0ec0b1cc8f12ae2c98e5215bdc9477998.jpg</t>
         </is>
       </c>
       <c r="V83" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296166</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296231</t>
         </is>
       </c>
       <c r="W83" t="inlineStr">
@@ -10589,7 +10589,7 @@
       <c r="AB83" t="inlineStr"/>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/ba79db36-23e8-1a8a-1ad9-a5809c1109be/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/e321350d-483d-6e38-81a2-a637b8f798fb/manifest</t>
         </is>
       </c>
       <c r="AD83" t="inlineStr"/>
@@ -10597,7 +10597,7 @@
       <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="inlineStr"/>
       <c r="AH83" t="n">
-        <v>54</v>
+        <v>7</v>
       </c>
     </row>
     <row r="84">

--- a/docs/collections/koten/metadata/data.xlsx
+++ b/docs/collections/koten/metadata/data.xlsx
@@ -820,7 +820,11 @@
           <t>日本語</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>図書</t>
+        </is>
+      </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>

--- a/docs/collections/koten/metadata/data.xlsx
+++ b/docs/collections/koten/metadata/data.xlsx
@@ -761,38 +761,42 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>中野蒐集佛教并三教及各部繪入板本目録</t>
+          <t>供様圖式</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>C40:4254</t>
+          <t>JG:32</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ナカノ シュウシュウ ブッキョウ ナラビニ サンキョウ オヨビ カクブ</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
+          <t>クヨウ ズシキ</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>供様図式</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>中野 達慧</t>
+          <t>四辻 公韶</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>東京帝国大学附属図書館</t>
+          <t>藤原公韶</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1926</t>
+          <t>1687</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>大正15/明治元</t>
+          <t>貞享4</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -807,12 +811,12 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>25cm</t>
+          <t>35.7cm</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>著者の自筆稿本|付:受入れ関係資料(袋入)</t>
+          <t>書名は題簽による|巻末に「貞享四年丁卯十一月一日忌火御飯十七日解齋御粥/左中将 (花押)写」とあり|奥書に「右圖式従園頭中将基勝朝臣/令借本写之畢/貞享四年十一月廿一日左中将 (花押) (「藤原公韶」の朱方印あり)」とあり|彩色あり|印記: 「野宮藏書」</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -822,18 +826,18 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>図書</t>
+          <t>和古書</t>
         </is>
       </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/fbf26de6-88d7-86db-7a3f-79a446c00445.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/f13b4435-13f6-1620-6ff9-c29077111174.json</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>fbf26de6-88d7-86db-7a3f-79a446c00445</t>
+          <t>f13b4435-13f6-1620-6ff9-c29077111174</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -843,7 +847,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/fbf26de6-88d7-86db-7a3f-79a446c00445</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/f13b4435-13f6-1620-6ff9-c29077111174</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -853,12 +857,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/010f8afb8aff57fed034d4d865411b48ec03a3bd.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/a1afc99196840b0659140d1885787a328f681db0.jpg</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1361385</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1361386</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -868,7 +872,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
+          <t>http://iiif.io/api/presentation/3#rightToLeftDirection</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr"/>
@@ -881,7 +885,7 @@
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/fbf26de6-88d7-86db-7a3f-79a446c00445/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/f13b4435-13f6-1620-6ff9-c29077111174/manifest</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr"/>
@@ -889,26 +893,30 @@
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="n">
-        <v>123</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>大嘗會調進物</t>
+          <t>大嘗會悠紀主基鮮味之繪</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>A00:6277</t>
+          <t>A00:6108</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ダイジョウエ チョウシンモノ</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>ダイジョウエ ユキ スキ センミ ノ ズ</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>悠紀主基鮮味之啚, 元文悠紀主基鮮味之圖</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>不明</t>
@@ -916,17 +924,17 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>[大藏省木工寮] [写]</t>
+          <t>[佐伯]</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>不明</t>
+          <t>1764</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>[明治期]</t>
+          <t>明和元</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,12 +949,12 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>28cm</t>
+          <t>40×165cm</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>巻頭の識語に「嘉永元戊申年八月廿九日 官局江差出但奉行ヨリ沙汰ニ依而也官務江茂白画圖一板写被頼差出也 此當家写尤薄彩色夲紙者」との朱書あり|巻末に「大藏省木工寮」とあり|絵巻|彩色あり</t>
+          <t>絵巻|書名は識語による|書袋の書名: 悠紀主基鮮味之啚|表紙裏に「元文悠紀主基鮮味之圖 寛延同」とあり|巻末の識語に「右大嘗會悠紀主基鮮味之繪借請御厨子所預紀宗直朝臣令佐伯職房摸冩之畢 明和元年孟冬左少将藤原(花押)」とあり|絵4幅: 梅作枝, 糸作枩, 萩作枝, 萩作枝|紙本著色|彩色あり|帙入り|印記: 「野宮藏書」</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -962,12 +970,12 @@
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/ff7901b5-7742-4d37-2621-ae0261c41dab.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/503a9098-4443-20f7-2ef1-cebc95096a74.json</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>ff7901b5-7742-4d37-2621-ae0261c41dab</t>
+          <t>503a9098-4443-20f7-2ef1-cebc95096a74</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -977,7 +985,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/ff7901b5-7742-4d37-2621-ae0261c41dab</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/503a9098-4443-20f7-2ef1-cebc95096a74</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -987,12 +995,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/426a2bea95a12ba2001d09cb79c81cf5c5db1129.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/2a7f21a6103a0653e35f8e5fada19af4c1a6d7bd.jpg</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1361387</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1361388</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1002,7 +1010,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>http://iiif.io/api/presentation/4#rightToLeftDirection</t>
+          <t>http://iiif.io/api/presentation/5#rightToLeftDirection</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr"/>
@@ -1015,7 +1023,7 @@
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/ff7901b5-7742-4d37-2621-ae0261c41dab/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/503a9098-4443-20f7-2ef1-cebc95096a74/manifest</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr"/>
@@ -1023,44 +1031,48 @@
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>御産部類</t>
+          <t>中御門大納言宣順卿記</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>G27:828</t>
+          <t>G27:165</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>オサン ブルイ</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>ナカミカド ダイナゴン ノブヨリ キョウ キ</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>宣順卿記, 承應二年中御門大納言宣順卿記</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>中御門 宣順</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>[書写者不明]</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
           <t>不明</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>[書写者不明]</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>1752</t>
-        </is>
-      </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>寳暦2</t>
+          <t>[書写年不明]</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1075,12 +1087,12 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>30cm</t>
+          <t>28cm</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>書名は表紙による|原奥書に「借請宰相中将定基卿本惟通卿書冩畢 寳永年正月廿四日 内大臣(花押)」とあり|奥書に「借請件奥書本於源前内府(通兄公)令書冩了 寳暦第二ノ季冬正三位□□(花押)」とあり|仮綴|朱墨書き入れあり(巻末に「宝暦二季冬一校了 愚然」と朱書あり)|虫損あり</t>
+          <t>書名及び巻次は表紙による|3: 承應二年|印記: 「和學講談所」,「温故堂文庫」,「渡部文庫珍藏書印」|虫損あり</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -1093,15 +1105,19 @@
           <t>和古書</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr"/>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>渡部文庫</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/519a0a21-28fc-86f1-91be-61b0c5c84d94.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/dc4aa20b-25b3-1976-505d-c313483199ba.json</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>519a0a21-28fc-86f1-91be-61b0c5c84d94</t>
+          <t>dc4aa20b-25b3-1976-505d-c313483199ba</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -1111,7 +1127,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/519a0a21-28fc-86f1-91be-61b0c5c84d94</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/dc4aa20b-25b3-1976-505d-c313483199ba</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1121,12 +1137,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/4d8113679682e972cf5c37311b94bb304455bbe2.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/4184c533168fcea03213cc03858c46672c2f3b30.jpg</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1361389</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1361390</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1136,7 +1152,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>http://iiif.io/api/presentation/6#rightToLeftDirection</t>
+          <t>http://iiif.io/api/presentation/7#rightToLeftDirection</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr"/>
@@ -1149,7 +1165,7 @@
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/519a0a21-28fc-86f1-91be-61b0c5c84d94/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/dc4aa20b-25b3-1976-505d-c313483199ba/manifest</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr"/>
@@ -1157,48 +1173,44 @@
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="n">
-        <v>74</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>拜賀部類記別勘</t>
+          <t>大嘗會部類 (存1巻)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>G26:1050</t>
+          <t>G26:966</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ハイガ ブルイキ ベッカン</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>拜賀部類別勘 : 當家之記, 拜賀部類 : 秘記</t>
-        </is>
-      </c>
+          <t>ダイジョウエ ブルイ</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>中院 通茂</t>
+          <t>不明</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>藤實岑 [写]</t>
+          <t>[書写者不明]</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1711</t>
+          <t>不明</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>寳永8</t>
+          <t>[書写年不明]</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1213,12 +1225,12 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>28cm</t>
+          <t>29cm</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>扉の書名: 拜賀部類別勘 : 當家之記|表紙の書名: 拜賀部類 : 秘記|奥書に「此一冊中院家拜賀記也(前内大臣通茂公自筆)其作法等三條西家諷諌事多且三條西家有作法事故請求通躬卿之処則被免仍摸冩加一校子孫之外努々不可許他見矣 于時寳永八稔孟夏上旬 羽林郎藤實岑」とあり|仮綴|付箋あり|虫損あり</t>
+          <t>書名及び巻次は表紙による|2を存す|仮綴|印記: 「野宮書印」|朱筆書き入れあり|虫損あり</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1234,12 +1246,12 @@
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/479b057d-7d61-0db0-0a50-9c798826783f.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/18bcd8ff-2df2-62ac-a685-fa22a8cb5a58.json</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>479b057d-7d61-0db0-0a50-9c798826783f</t>
+          <t>18bcd8ff-2df2-62ac-a685-fa22a8cb5a58</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1249,7 +1261,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/479b057d-7d61-0db0-0a50-9c798826783f</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/18bcd8ff-2df2-62ac-a685-fa22a8cb5a58</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1259,12 +1271,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/f7ec09b951da91d218e076889f2c1f75f429b846.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/17578c3efd5fd9990d9c44b722b4f881e0ba7231.jpg</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1361391</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1361392</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1274,7 +1286,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>http://iiif.io/api/presentation/8#rightToLeftDirection</t>
+          <t>http://iiif.io/api/presentation/9#rightToLeftDirection</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr"/>
@@ -1287,7 +1299,7 @@
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/479b057d-7d61-0db0-0a50-9c798826783f/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/18bcd8ff-2df2-62ac-a685-fa22a8cb5a58/manifest</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr"/>
@@ -1295,13 +1307,13 @@
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="inlineStr"/>
       <c r="AH6" t="n">
-        <v>60</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>柱史抄 下</t>
+          <t>柱史抄 上</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1311,7 +1323,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>チュウシショウ ゲ</t>
+          <t>チュウシショウ ジョウ</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -1372,12 +1384,12 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/e194f872-8917-1c7f-16f2-830299a79d87.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/aa9e6c3f-0a12-47dc-9d5f-b6d7466a7e28.json</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>e194f872-8917-1c7f-16f2-830299a79d87</t>
+          <t>aa9e6c3f-0a12-47dc-9d5f-b6d7466a7e28</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1387,7 +1399,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/e194f872-8917-1c7f-16f2-830299a79d87</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/aa9e6c3f-0a12-47dc-9d5f-b6d7466a7e28</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1397,12 +1409,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/ca70042589e928d9afd6a23ff1e73ae42fd6cf37.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/92f6ce8da05d1ee555c30e2821d0d2ac3c24592c.jpg</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1361393</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1361394</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1412,7 +1424,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>http://iiif.io/api/presentation/10#rightToLeftDirection</t>
+          <t>http://iiif.io/api/presentation/11#rightToLeftDirection</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr"/>
@@ -1425,7 +1437,7 @@
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/e194f872-8917-1c7f-16f2-830299a79d87/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/aa9e6c3f-0a12-47dc-9d5f-b6d7466a7e28/manifest</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr"/>
@@ -1433,13 +1445,13 @@
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="inlineStr"/>
       <c r="AH7" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>蛙抄 8</t>
+          <t>蛙抄 7</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1449,7 +1461,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>アショウ 8</t>
+          <t>アショウ 7</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1510,12 +1522,12 @@
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/f7a2c50b-0c62-15a7-68c3-a0f0e8c52ca1.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/4cb13342-3d2f-0027-2ad6-da984e2c3d6d.json</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>f7a2c50b-0c62-15a7-68c3-a0f0e8c52ca1</t>
+          <t>4cb13342-3d2f-0027-2ad6-da984e2c3d6d</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1525,7 +1537,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/f7a2c50b-0c62-15a7-68c3-a0f0e8c52ca1</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/4cb13342-3d2f-0027-2ad6-da984e2c3d6d</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -1535,12 +1547,12 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/f342b349e1a772b70e534d7100a687e127ebd6b4.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/b8c2cc84b66430038932deffec626f0f32a13959.jpg</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1361395</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1361396</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -1550,7 +1562,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>http://iiif.io/api/presentation/12#rightToLeftDirection</t>
+          <t>http://iiif.io/api/presentation/13#rightToLeftDirection</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr"/>
@@ -1563,7 +1575,7 @@
       <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/f7a2c50b-0c62-15a7-68c3-a0f0e8c52ca1/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/4cb13342-3d2f-0027-2ad6-da984e2c3d6d/manifest</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr"/>
@@ -1571,13 +1583,13 @@
       <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="inlineStr"/>
       <c r="AH8" t="n">
-        <v>38</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>蛙抄 6</t>
+          <t>蛙抄 5</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1587,7 +1599,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>アショウ 6</t>
+          <t>アショウ 5</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1648,12 +1660,12 @@
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/d8791f0a-777b-386d-21e8-6da9b37f02c8.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/546a78f4-428e-6dba-70bf-a012abfa0d8a.json</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>d8791f0a-777b-386d-21e8-6da9b37f02c8</t>
+          <t>546a78f4-428e-6dba-70bf-a012abfa0d8a</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1663,7 +1675,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/d8791f0a-777b-386d-21e8-6da9b37f02c8</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/546a78f4-428e-6dba-70bf-a012abfa0d8a</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
@@ -1673,12 +1685,12 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/340e9027fa29b9e2e037e6b59373dd51d91924a8.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/d0934b537402b27018cdeaf504cb5247102fe258.jpg</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1361397</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1361398</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -1688,7 +1700,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>http://iiif.io/api/presentation/14#rightToLeftDirection</t>
+          <t>http://iiif.io/api/presentation/15#rightToLeftDirection</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr"/>
@@ -1701,7 +1713,7 @@
       <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/d8791f0a-777b-386d-21e8-6da9b37f02c8/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/546a78f4-428e-6dba-70bf-a012abfa0d8a/manifest</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr"/>
@@ -1709,13 +1721,13 @@
       <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="inlineStr"/>
       <c r="AH9" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>蛙抄 4</t>
+          <t>蛙抄 3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1725,7 +1737,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>アショウ 4</t>
+          <t>アショウ 3</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1786,12 +1798,12 @@
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/977b1d81-65b0-4b65-2b3b-266bfde72fb4.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/722ddb21-8d89-37c1-30e7-eca05eb95176.json</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>977b1d81-65b0-4b65-2b3b-266bfde72fb4</t>
+          <t>722ddb21-8d89-37c1-30e7-eca05eb95176</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1801,7 +1813,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/977b1d81-65b0-4b65-2b3b-266bfde72fb4</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/722ddb21-8d89-37c1-30e7-eca05eb95176</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
@@ -1811,12 +1823,12 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/14e1cc135dbfcab9736fe828d1d78b9e64f489dd.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/c0ca51c9e6c25976f232f4ddb3182d541d6a4811.jpg</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1361399</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1361400</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
@@ -1826,7 +1838,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>http://iiif.io/api/presentation/16#rightToLeftDirection</t>
+          <t>http://iiif.io/api/presentation/17#rightToLeftDirection</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr"/>
@@ -1839,7 +1851,7 @@
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/977b1d81-65b0-4b65-2b3b-266bfde72fb4/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/722ddb21-8d89-37c1-30e7-eca05eb95176/manifest</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr"/>
@@ -1847,13 +1859,13 @@
       <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="inlineStr"/>
       <c r="AH10" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>蛙抄 2</t>
+          <t>蛙抄 1</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1863,7 +1875,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>アショウ 2</t>
+          <t>アショウ 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1924,12 +1936,12 @@
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/38c2b478-6a9c-3527-4f79-cf58fb142798.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/3cf264e7-3309-9308-461e-f40a43cf0382.json</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>38c2b478-6a9c-3527-4f79-cf58fb142798</t>
+          <t>3cf264e7-3309-9308-461e-f40a43cf0382</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1939,7 +1951,7 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/38c2b478-6a9c-3527-4f79-cf58fb142798</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/3cf264e7-3309-9308-461e-f40a43cf0382</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
@@ -1949,12 +1961,12 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/39e3ab2ee3a234d362b9d57bbf1e3d6ff10e41b3.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/33ff9a81a583cfab208f93ee171b7a185dc82b7d.jpg</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1361401</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1361402</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
@@ -1964,7 +1976,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>http://iiif.io/api/presentation/18#rightToLeftDirection</t>
+          <t>http://iiif.io/api/presentation/19#rightToLeftDirection</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr"/>
@@ -1977,7 +1989,7 @@
       <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/38c2b478-6a9c-3527-4f79-cf58fb142798/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/3cf264e7-3309-9308-461e-f40a43cf0382/manifest</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr"/>
@@ -1985,48 +1997,44 @@
       <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="inlineStr"/>
       <c r="AH11" t="n">
-        <v>21</v>
+        <v>41</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>醍醐天皇事記</t>
+          <t>中野蒐集佛教并三教及各部繪入板本目録</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>G27:966</t>
+          <t>C40:4254</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ダイゴ テンノウ ジキ</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>史料</t>
-        </is>
-      </c>
+          <t>ナカノ シュウシュウ ブッキョウ ナラビニ サンキョウ オヨビ カクブ</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>塙 保己一</t>
+          <t>中野 達慧</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>源行之 [写]</t>
+          <t>東京帝国大学附属図書館</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>不明</t>
+          <t>1926</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>[江戸後期]</t>
+          <t>大正15/明治元</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -2041,12 +2049,12 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>27cm</t>
+          <t>25cm</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>塙氏等編『史料』巻之33|識語: 「塙本ノ史料零本一冊 此ノ書ハ塙氏家蔵ノ原本ナリ其書全部ハ旧年元老院ニテ買上ケタルガ其ノ中数冊ハ紛失セリトテ新冩本ニテ雜レリ余先年彼ノ院ニ官セシトキ常ニ繙閲シタリキ今ハ内閣記録課ノ蔵本タリ此書一冊ハ塙氏ノ手冩既ニ紛失シタリトイヘル内ノ物ニテ早ク坊間ニ散シタルナリ明治卅八年三月酒井藤兵衞ニテ購フ零本トイヘトモ塙本原書ノ真面目ヲ見ルコトヲ得ヘシ 萩野由之(花押)」|表紙の貼紙に「塙本史料原本 零巻」と墨書あり|印記: 「和學講談所」,「温故堂文庫」</t>
+          <t>著者の自筆稿本|付:受入れ関係資料(袋入)</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -2056,22 +2064,18 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>和古書</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>萩野本</t>
-        </is>
-      </c>
+          <t>図書</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/45e324c7-01db-3830-0a24-e21a2e0c79e8.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/fbf26de6-88d7-86db-7a3f-79a446c00445.json</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>45e324c7-01db-3830-0a24-e21a2e0c79e8</t>
+          <t>fbf26de6-88d7-86db-7a3f-79a446c00445</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -2081,7 +2085,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/45e324c7-01db-3830-0a24-e21a2e0c79e8</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/fbf26de6-88d7-86db-7a3f-79a446c00445</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
@@ -2091,12 +2095,12 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/2ce84a1535191d6a4cfb10ee0765f5eb11f171c5.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/010f8afb8aff57fed034d4d865411b48ec03a3bd.jpg</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1361403</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1361385</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
@@ -2106,7 +2110,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>http://iiif.io/api/presentation/20#rightToLeftDirection</t>
+          <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr"/>
@@ -2119,7 +2123,7 @@
       <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/45e324c7-01db-3830-0a24-e21a2e0c79e8/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/fbf26de6-88d7-86db-7a3f-79a446c00445/manifest</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr"/>
@@ -2127,48 +2131,44 @@
       <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="inlineStr"/>
       <c r="AH12" t="n">
-        <v>32</v>
+        <v>123</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>供様圖式</t>
+          <t>大嘗會調進物</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>JG:32</t>
+          <t>A00:6277</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>クヨウ ズシキ</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>供様図式</t>
-        </is>
-      </c>
+          <t>ダイジョウエ チョウシンモノ</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>四辻 公韶</t>
+          <t>不明</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>藤原公韶</t>
+          <t>[大藏省木工寮] [写]</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1687</t>
+          <t>不明</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>貞享4</t>
+          <t>[明治期]</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2183,12 +2183,12 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>35.7cm</t>
+          <t>28cm</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>書名は題簽による|巻末に「貞享四年丁卯十一月一日忌火御飯十七日解齋御粥/左中将 (花押)写」とあり|奥書に「右圖式従園頭中将基勝朝臣/令借本写之畢/貞享四年十一月廿一日左中将 (花押) (「藤原公韶」の朱方印あり)」とあり|彩色あり|印記: 「野宮藏書」</t>
+          <t>巻頭の識語に「嘉永元戊申年八月廿九日 官局江差出但奉行ヨリ沙汰ニ依而也官務江茂白画圖一板写被頼差出也 此當家写尤薄彩色夲紙者」との朱書あり|巻末に「大藏省木工寮」とあり|絵巻|彩色あり</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -2204,12 +2204,12 @@
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/f13b4435-13f6-1620-6ff9-c29077111174.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/ff7901b5-7742-4d37-2621-ae0261c41dab.json</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>f13b4435-13f6-1620-6ff9-c29077111174</t>
+          <t>ff7901b5-7742-4d37-2621-ae0261c41dab</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -2219,7 +2219,7 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/f13b4435-13f6-1620-6ff9-c29077111174</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/ff7901b5-7742-4d37-2621-ae0261c41dab</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/a1afc99196840b0659140d1885787a328f681db0.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/426a2bea95a12ba2001d09cb79c81cf5c5db1129.jpg</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1361386</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1361387</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -2244,7 +2244,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>http://iiif.io/api/presentation/3#rightToLeftDirection</t>
+          <t>http://iiif.io/api/presentation/4#rightToLeftDirection</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr"/>
@@ -2257,7 +2257,7 @@
       <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/f13b4435-13f6-1620-6ff9-c29077111174/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/ff7901b5-7742-4d37-2621-ae0261c41dab/manifest</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr"/>
@@ -2265,30 +2265,26 @@
       <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="inlineStr"/>
       <c r="AH13" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>大嘗會悠紀主基鮮味之繪</t>
+          <t>御産部類</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>A00:6108</t>
+          <t>G27:828</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ダイジョウエ ユキ スキ センミ ノ ズ</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>悠紀主基鮮味之啚, 元文悠紀主基鮮味之圖</t>
-        </is>
-      </c>
+          <t>オサン ブルイ</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>不明</t>
@@ -2296,17 +2292,17 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>[佐伯]</t>
+          <t>[書写者不明]</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1764</t>
+          <t>1752</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>明和元</t>
+          <t>寳暦2</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2321,12 +2317,12 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>40×165cm</t>
+          <t>30cm</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>絵巻|書名は識語による|書袋の書名: 悠紀主基鮮味之啚|表紙裏に「元文悠紀主基鮮味之圖 寛延同」とあり|巻末の識語に「右大嘗會悠紀主基鮮味之繪借請御厨子所預紀宗直朝臣令佐伯職房摸冩之畢 明和元年孟冬左少将藤原(花押)」とあり|絵4幅: 梅作枝, 糸作枩, 萩作枝, 萩作枝|紙本著色|彩色あり|帙入り|印記: 「野宮藏書」</t>
+          <t>書名は表紙による|原奥書に「借請宰相中将定基卿本惟通卿書冩畢 寳永年正月廿四日 内大臣(花押)」とあり|奥書に「借請件奥書本於源前内府(通兄公)令書冩了 寳暦第二ノ季冬正三位□□(花押)」とあり|仮綴|朱墨書き入れあり(巻末に「宝暦二季冬一校了 愚然」と朱書あり)|虫損あり</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -2342,12 +2338,12 @@
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/503a9098-4443-20f7-2ef1-cebc95096a74.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/519a0a21-28fc-86f1-91be-61b0c5c84d94.json</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>503a9098-4443-20f7-2ef1-cebc95096a74</t>
+          <t>519a0a21-28fc-86f1-91be-61b0c5c84d94</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -2357,7 +2353,7 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/503a9098-4443-20f7-2ef1-cebc95096a74</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/519a0a21-28fc-86f1-91be-61b0c5c84d94</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
@@ -2367,12 +2363,12 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/2a7f21a6103a0653e35f8e5fada19af4c1a6d7bd.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/4d8113679682e972cf5c37311b94bb304455bbe2.jpg</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1361388</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1361389</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -2382,7 +2378,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>http://iiif.io/api/presentation/5#rightToLeftDirection</t>
+          <t>http://iiif.io/api/presentation/6#rightToLeftDirection</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr"/>
@@ -2395,7 +2391,7 @@
       <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/503a9098-4443-20f7-2ef1-cebc95096a74/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/519a0a21-28fc-86f1-91be-61b0c5c84d94/manifest</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr"/>
@@ -2403,48 +2399,48 @@
       <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="inlineStr"/>
       <c r="AH14" t="n">
-        <v>11</v>
+        <v>74</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>中御門大納言宣順卿記</t>
+          <t>拜賀部類記別勘</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>G27:165</t>
+          <t>G26:1050</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ナカミカド ダイナゴン ノブヨリ キョウ キ</t>
+          <t>ハイガ ブルイキ ベッカン</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>宣順卿記, 承應二年中御門大納言宣順卿記</t>
+          <t>拜賀部類別勘 : 當家之記, 拜賀部類 : 秘記</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>中御門 宣順</t>
+          <t>中院 通茂</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>[書写者不明]</t>
+          <t>藤實岑 [写]</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>不明</t>
+          <t>1711</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>[書写年不明]</t>
+          <t>寳永8</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2464,7 +2460,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>書名及び巻次は表紙による|3: 承應二年|印記: 「和學講談所」,「温故堂文庫」,「渡部文庫珍藏書印」|虫損あり</t>
+          <t>扉の書名: 拜賀部類別勘 : 當家之記|表紙の書名: 拜賀部類 : 秘記|奥書に「此一冊中院家拜賀記也(前内大臣通茂公自筆)其作法等三條西家諷諌事多且三條西家有作法事故請求通躬卿之処則被免仍摸冩加一校子孫之外努々不可許他見矣 于時寳永八稔孟夏上旬 羽林郎藤實岑」とあり|仮綴|付箋あり|虫損あり</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -2477,19 +2473,15 @@
           <t>和古書</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>渡部文庫</t>
-        </is>
-      </c>
+      <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/dc4aa20b-25b3-1976-505d-c313483199ba.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/479b057d-7d61-0db0-0a50-9c798826783f.json</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>dc4aa20b-25b3-1976-505d-c313483199ba</t>
+          <t>479b057d-7d61-0db0-0a50-9c798826783f</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -2499,7 +2491,7 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/dc4aa20b-25b3-1976-505d-c313483199ba</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/479b057d-7d61-0db0-0a50-9c798826783f</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
@@ -2509,12 +2501,12 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/4184c533168fcea03213cc03858c46672c2f3b30.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/f7ec09b951da91d218e076889f2c1f75f429b846.jpg</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1361390</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1361391</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
@@ -2524,7 +2516,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>http://iiif.io/api/presentation/7#rightToLeftDirection</t>
+          <t>http://iiif.io/api/presentation/8#rightToLeftDirection</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr"/>
@@ -2537,7 +2529,7 @@
       <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/dc4aa20b-25b3-1976-505d-c313483199ba/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/479b057d-7d61-0db0-0a50-9c798826783f/manifest</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr"/>
@@ -2545,41 +2537,41 @@
       <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="inlineStr"/>
       <c r="AH15" t="n">
-        <v>39</v>
+        <v>60</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>大嘗會部類 (存1巻)</t>
+          <t>柱史抄 下</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>G26:966</t>
+          <t>G26:256</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ダイジョウエ ブルイ</t>
+          <t>チュウシショウ ゲ</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
+          <t>藤原 孝範</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>[書写者不明]</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
           <t>不明</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>[書写者不明]</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>不明</t>
-        </is>
-      </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>[書写年不明]</t>
@@ -2587,7 +2579,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2597,12 +2589,12 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>29cm</t>
+          <t>27cm</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>書名及び巻次は表紙による|2を存す|仮綴|印記: 「野宮書印」|朱筆書き入れあり|虫損あり</t>
+          <t>印記: 「華山藏書之印」,「渡部文庫珍藏書印」|朱筆書き入れあり|虫損あり</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2615,15 +2607,19 @@
           <t>和古書</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr"/>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>渡部文庫</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/18bcd8ff-2df2-62ac-a685-fa22a8cb5a58.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/e194f872-8917-1c7f-16f2-830299a79d87.json</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>18bcd8ff-2df2-62ac-a685-fa22a8cb5a58</t>
+          <t>e194f872-8917-1c7f-16f2-830299a79d87</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -2633,7 +2629,7 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/18bcd8ff-2df2-62ac-a685-fa22a8cb5a58</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/e194f872-8917-1c7f-16f2-830299a79d87</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
@@ -2643,12 +2639,12 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/17578c3efd5fd9990d9c44b722b4f881e0ba7231.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/ca70042589e928d9afd6a23ff1e73ae42fd6cf37.jpg</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1361392</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1361393</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
@@ -2658,7 +2654,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>http://iiif.io/api/presentation/9#rightToLeftDirection</t>
+          <t>http://iiif.io/api/presentation/10#rightToLeftDirection</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr"/>
@@ -2671,7 +2667,7 @@
       <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/18bcd8ff-2df2-62ac-a685-fa22a8cb5a58/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/e194f872-8917-1c7f-16f2-830299a79d87/manifest</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr"/>
@@ -2679,29 +2675,33 @@
       <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="inlineStr"/>
       <c r="AH16" t="n">
-        <v>53</v>
+        <v>44</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>柱史抄 上</t>
+          <t>蛙抄 8</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>G26:256</t>
+          <t>G26:45</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>チュウシショウ ジョウ</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>アショウ 8</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>蛙鈔</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>藤原 孝範</t>
+          <t>洞院 実煕</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>[書写年不明]</t>
+          <t>[江戸後期]</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2731,12 +2731,12 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>27cm</t>
+          <t>28cm</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>印記: 「華山藏書之印」,「渡部文庫珍藏書印」|朱筆書き入れあり|虫損あり</t>
+          <t>書名及び巻次は題簽による|8の目首の書名: 蛙鈔|各奥書に「享和三年仲春一挍畢」(1-2)「享和三季春挍合畢」(3)「享和三年季春挍合畢」(4)「享和三年仲春一挍了」(5)「享和三年孟夏挍合畢」(6-7)「一挍畢」(8)とあり|頭注あり|1: 冠部, 剱部. 2: 袍部. 3-4: 下襲部. 5: 半臂, 袙, 表袴部. 6: 直衣部. 7: 打衣部. 8: 車輿部|印記: 「希賢亭圖書記」|1の扉裏に「經亮云蛙抄ハ三條家ニ秘藏セラレシ装束抄ナリ邂逅ニ袍部及車輿部ノ二冊ハ世ニ流布セリ今又下重部二冊半臂袙表袴部一冊直衣部一冊打衣部一冊以上八冊也此餘モアリトイヘトモイマタ知ラス半臂部ニ其事見小忌部トアルヲ見レハ小忌部ナドモアルベシ而シテ此抄ハ三條家ノモノトモミヘズ當家ト抄中ニアルハ洞院家ノコト也若疑ハ東山左府實凞公ナトノ手ニ出タリシニヤ可考事ナリ先年コノコトヲ瑜伽心院入道前権大納言紀光卿ニキコヱケレバサモアラント諾玉ヘリ」と朱書あり|朱筆書き入れあり|付箋あり|虫損あり</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2749,19 +2749,15 @@
           <t>和古書</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>渡部文庫</t>
-        </is>
-      </c>
+      <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/aa9e6c3f-0a12-47dc-9d5f-b6d7466a7e28.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/f7a2c50b-0c62-15a7-68c3-a0f0e8c52ca1.json</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>aa9e6c3f-0a12-47dc-9d5f-b6d7466a7e28</t>
+          <t>f7a2c50b-0c62-15a7-68c3-a0f0e8c52ca1</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -2771,7 +2767,7 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/aa9e6c3f-0a12-47dc-9d5f-b6d7466a7e28</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/f7a2c50b-0c62-15a7-68c3-a0f0e8c52ca1</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
@@ -2781,12 +2777,12 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/92f6ce8da05d1ee555c30e2821d0d2ac3c24592c.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/f342b349e1a772b70e534d7100a687e127ebd6b4.jpg</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1361394</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1361395</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
@@ -2796,7 +2792,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>http://iiif.io/api/presentation/11#rightToLeftDirection</t>
+          <t>http://iiif.io/api/presentation/12#rightToLeftDirection</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr"/>
@@ -2809,7 +2805,7 @@
       <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/aa9e6c3f-0a12-47dc-9d5f-b6d7466a7e28/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/f7a2c50b-0c62-15a7-68c3-a0f0e8c52ca1/manifest</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr"/>
@@ -2817,13 +2813,13 @@
       <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="inlineStr"/>
       <c r="AH17" t="n">
-        <v>53</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>蛙抄 7</t>
+          <t>蛙抄 6</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2833,7 +2829,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>アショウ 7</t>
+          <t>アショウ 6</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2894,12 +2890,12 @@
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/4cb13342-3d2f-0027-2ad6-da984e2c3d6d.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/d8791f0a-777b-386d-21e8-6da9b37f02c8.json</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>4cb13342-3d2f-0027-2ad6-da984e2c3d6d</t>
+          <t>d8791f0a-777b-386d-21e8-6da9b37f02c8</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -2909,7 +2905,7 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/4cb13342-3d2f-0027-2ad6-da984e2c3d6d</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/d8791f0a-777b-386d-21e8-6da9b37f02c8</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
@@ -2919,12 +2915,12 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/b8c2cc84b66430038932deffec626f0f32a13959.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/340e9027fa29b9e2e037e6b59373dd51d91924a8.jpg</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1361396</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1361397</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
@@ -2934,7 +2930,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>http://iiif.io/api/presentation/13#rightToLeftDirection</t>
+          <t>http://iiif.io/api/presentation/14#rightToLeftDirection</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr"/>
@@ -2947,7 +2943,7 @@
       <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/4cb13342-3d2f-0027-2ad6-da984e2c3d6d/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/d8791f0a-777b-386d-21e8-6da9b37f02c8/manifest</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr"/>
@@ -2955,13 +2951,13 @@
       <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="inlineStr"/>
       <c r="AH18" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>蛙抄 5</t>
+          <t>蛙抄 4</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2971,7 +2967,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>アショウ 5</t>
+          <t>アショウ 4</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3032,12 +3028,12 @@
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/546a78f4-428e-6dba-70bf-a012abfa0d8a.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/977b1d81-65b0-4b65-2b3b-266bfde72fb4.json</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>546a78f4-428e-6dba-70bf-a012abfa0d8a</t>
+          <t>977b1d81-65b0-4b65-2b3b-266bfde72fb4</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -3047,7 +3043,7 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/546a78f4-428e-6dba-70bf-a012abfa0d8a</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/977b1d81-65b0-4b65-2b3b-266bfde72fb4</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
@@ -3057,12 +3053,12 @@
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/d0934b537402b27018cdeaf504cb5247102fe258.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/14e1cc135dbfcab9736fe828d1d78b9e64f489dd.jpg</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1361398</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1361399</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
@@ -3072,7 +3068,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>http://iiif.io/api/presentation/15#rightToLeftDirection</t>
+          <t>http://iiif.io/api/presentation/16#rightToLeftDirection</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr"/>
@@ -3085,7 +3081,7 @@
       <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/546a78f4-428e-6dba-70bf-a012abfa0d8a/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/977b1d81-65b0-4b65-2b3b-266bfde72fb4/manifest</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr"/>
@@ -3093,13 +3089,13 @@
       <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="inlineStr"/>
       <c r="AH19" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>蛙抄 3</t>
+          <t>蛙抄 2</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -3109,7 +3105,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>アショウ 3</t>
+          <t>アショウ 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3170,12 +3166,12 @@
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/722ddb21-8d89-37c1-30e7-eca05eb95176.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/38c2b478-6a9c-3527-4f79-cf58fb142798.json</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>722ddb21-8d89-37c1-30e7-eca05eb95176</t>
+          <t>38c2b478-6a9c-3527-4f79-cf58fb142798</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -3185,7 +3181,7 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/722ddb21-8d89-37c1-30e7-eca05eb95176</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/38c2b478-6a9c-3527-4f79-cf58fb142798</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
@@ -3195,12 +3191,12 @@
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/c0ca51c9e6c25976f232f4ddb3182d541d6a4811.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/39e3ab2ee3a234d362b9d57bbf1e3d6ff10e41b3.jpg</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1361400</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1361401</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
@@ -3210,7 +3206,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>http://iiif.io/api/presentation/17#rightToLeftDirection</t>
+          <t>http://iiif.io/api/presentation/18#rightToLeftDirection</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr"/>
@@ -3223,7 +3219,7 @@
       <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/722ddb21-8d89-37c1-30e7-eca05eb95176/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/38c2b478-6a9c-3527-4f79-cf58fb142798/manifest</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr"/>
@@ -3231,38 +3227,38 @@
       <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="inlineStr"/>
       <c r="AH20" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>蛙抄 1</t>
+          <t>醍醐天皇事記</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>G26:45</t>
+          <t>G27:966</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>アショウ 1</t>
+          <t>ダイゴ テンノウ ジキ</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>蛙鈔</t>
+          <t>史料</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>洞院 実煕</t>
+          <t>塙 保己一</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>[書写者不明]</t>
+          <t>源行之 [写]</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -3277,7 +3273,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3287,12 +3283,12 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>28cm</t>
+          <t>27cm</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>書名及び巻次は題簽による|8の目首の書名: 蛙鈔|各奥書に「享和三年仲春一挍畢」(1-2)「享和三季春挍合畢」(3)「享和三年季春挍合畢」(4)「享和三年仲春一挍了」(5)「享和三年孟夏挍合畢」(6-7)「一挍畢」(8)とあり|頭注あり|1: 冠部, 剱部. 2: 袍部. 3-4: 下襲部. 5: 半臂, 袙, 表袴部. 6: 直衣部. 7: 打衣部. 8: 車輿部|印記: 「希賢亭圖書記」|1の扉裏に「經亮云蛙抄ハ三條家ニ秘藏セラレシ装束抄ナリ邂逅ニ袍部及車輿部ノ二冊ハ世ニ流布セリ今又下重部二冊半臂袙表袴部一冊直衣部一冊打衣部一冊以上八冊也此餘モアリトイヘトモイマタ知ラス半臂部ニ其事見小忌部トアルヲ見レハ小忌部ナドモアルベシ而シテ此抄ハ三條家ノモノトモミヘズ當家ト抄中ニアルハ洞院家ノコト也若疑ハ東山左府實凞公ナトノ手ニ出タリシニヤ可考事ナリ先年コノコトヲ瑜伽心院入道前権大納言紀光卿ニキコヱケレバサモアラント諾玉ヘリ」と朱書あり|朱筆書き入れあり|付箋あり|虫損あり</t>
+          <t>塙氏等編『史料』巻之33|識語: 「塙本ノ史料零本一冊 此ノ書ハ塙氏家蔵ノ原本ナリ其書全部ハ旧年元老院ニテ買上ケタルガ其ノ中数冊ハ紛失セリトテ新冩本ニテ雜レリ余先年彼ノ院ニ官セシトキ常ニ繙閲シタリキ今ハ内閣記録課ノ蔵本タリ此書一冊ハ塙氏ノ手冩既ニ紛失シタリトイヘル内ノ物ニテ早ク坊間ニ散シタルナリ明治卅八年三月酒井藤兵衞ニテ購フ零本トイヘトモ塙本原書ノ真面目ヲ見ルコトヲ得ヘシ 萩野由之(花押)」|表紙の貼紙に「塙本史料原本 零巻」と墨書あり|印記: 「和學講談所」,「温故堂文庫」</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -3305,15 +3301,19 @@
           <t>和古書</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr"/>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>萩野本</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/3cf264e7-3309-9308-461e-f40a43cf0382.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/45e324c7-01db-3830-0a24-e21a2e0c79e8.json</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>3cf264e7-3309-9308-461e-f40a43cf0382</t>
+          <t>45e324c7-01db-3830-0a24-e21a2e0c79e8</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -3323,7 +3323,7 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/3cf264e7-3309-9308-461e-f40a43cf0382</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/45e324c7-01db-3830-0a24-e21a2e0c79e8</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
@@ -3333,12 +3333,12 @@
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/33ff9a81a583cfab208f93ee171b7a185dc82b7d.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/2ce84a1535191d6a4cfb10ee0765f5eb11f171c5.jpg</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1361402</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1361403</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
@@ -3348,7 +3348,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>http://iiif.io/api/presentation/19#rightToLeftDirection</t>
+          <t>http://iiif.io/api/presentation/20#rightToLeftDirection</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr"/>
@@ -3361,7 +3361,7 @@
       <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/3cf264e7-3309-9308-461e-f40a43cf0382/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/45e324c7-01db-3830-0a24-e21a2e0c79e8/manifest</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr"/>
@@ -3369,7 +3369,7 @@
       <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="inlineStr"/>
       <c r="AH21" t="n">
-        <v>41</v>
+        <v>32</v>
       </c>
     </row>
     <row r="22">

--- a/docs/collections/koten/metadata/data.xlsx
+++ b/docs/collections/koten/metadata/data.xlsx
@@ -761,42 +761,42 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>供様圖式</t>
+          <t>大嘗會悠紀主基鮮味之繪</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>JG:32</t>
+          <t>A00:6108</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>クヨウ ズシキ</t>
+          <t>ダイジョウエ ユキ スキ センミ ノ ズ</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>供様図式</t>
+          <t>悠紀主基鮮味之啚, 元文悠紀主基鮮味之圖</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>四辻 公韶</t>
+          <t>不明</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>藤原公韶</t>
+          <t>[佐伯]</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1687</t>
+          <t>1764</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>貞享4</t>
+          <t>明和元</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -811,12 +811,12 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>35.7cm</t>
+          <t>40×165cm</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>書名は題簽による|巻末に「貞享四年丁卯十一月一日忌火御飯十七日解齋御粥/左中将 (花押)写」とあり|奥書に「右圖式従園頭中将基勝朝臣/令借本写之畢/貞享四年十一月廿一日左中将 (花押) (「藤原公韶」の朱方印あり)」とあり|彩色あり|印記: 「野宮藏書」</t>
+          <t>絵巻|書名は識語による|書袋の書名: 悠紀主基鮮味之啚|表紙裏に「元文悠紀主基鮮味之圖 寛延同」とあり|巻末の識語に「右大嘗會悠紀主基鮮味之繪借請御厨子所預紀宗直朝臣令佐伯職房摸冩之畢 明和元年孟冬左少将藤原(花押)」とあり|絵4幅: 梅作枝, 糸作枩, 萩作枝, 萩作枝|紙本著色|彩色あり|帙入り|印記: 「野宮藏書」</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -832,12 +832,12 @@
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/f13b4435-13f6-1620-6ff9-c29077111174.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/503a9098-4443-20f7-2ef1-cebc95096a74.json</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>f13b4435-13f6-1620-6ff9-c29077111174</t>
+          <t>503a9098-4443-20f7-2ef1-cebc95096a74</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/f13b4435-13f6-1620-6ff9-c29077111174</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/503a9098-4443-20f7-2ef1-cebc95096a74</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -857,12 +857,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/a1afc99196840b0659140d1885787a328f681db0.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/2a7f21a6103a0653e35f8e5fada19af4c1a6d7bd.jpg</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1361386</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1361388</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>http://iiif.io/api/presentation/3#rightToLeftDirection</t>
+          <t>http://iiif.io/api/presentation/5#rightToLeftDirection</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr"/>
@@ -885,7 +885,7 @@
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/f13b4435-13f6-1620-6ff9-c29077111174/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/503a9098-4443-20f7-2ef1-cebc95096a74/manifest</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr"/>
@@ -899,42 +899,42 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>大嘗會悠紀主基鮮味之繪</t>
+          <t>中御門大納言宣順卿記</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>A00:6108</t>
+          <t>G27:165</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ダイジョウエ ユキ スキ センミ ノ ズ</t>
+          <t>ナカミカド ダイナゴン ノブヨリ キョウ キ</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>悠紀主基鮮味之啚, 元文悠紀主基鮮味之圖</t>
+          <t>宣順卿記, 承應二年中御門大納言宣順卿記</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>中御門 宣順</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>[書写者不明]</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
           <t>不明</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>[佐伯]</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>1764</t>
-        </is>
-      </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>明和元</t>
+          <t>[書写年不明]</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>40×165cm</t>
+          <t>28cm</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>絵巻|書名は識語による|書袋の書名: 悠紀主基鮮味之啚|表紙裏に「元文悠紀主基鮮味之圖 寛延同」とあり|巻末の識語に「右大嘗會悠紀主基鮮味之繪借請御厨子所預紀宗直朝臣令佐伯職房摸冩之畢 明和元年孟冬左少将藤原(花押)」とあり|絵4幅: 梅作枝, 糸作枩, 萩作枝, 萩作枝|紙本著色|彩色あり|帙入り|印記: 「野宮藏書」</t>
+          <t>書名及び巻次は表紙による|3: 承應二年|印記: 「和學講談所」,「温故堂文庫」,「渡部文庫珍藏書印」|虫損あり</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -967,15 +967,19 @@
           <t>和古書</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr"/>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>渡部文庫</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/503a9098-4443-20f7-2ef1-cebc95096a74.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/dc4aa20b-25b3-1976-505d-c313483199ba.json</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>503a9098-4443-20f7-2ef1-cebc95096a74</t>
+          <t>dc4aa20b-25b3-1976-505d-c313483199ba</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -985,7 +989,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/503a9098-4443-20f7-2ef1-cebc95096a74</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/dc4aa20b-25b3-1976-505d-c313483199ba</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -995,12 +999,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/2a7f21a6103a0653e35f8e5fada19af4c1a6d7bd.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/4184c533168fcea03213cc03858c46672c2f3b30.jpg</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1361388</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1361390</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1010,7 +1014,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>http://iiif.io/api/presentation/5#rightToLeftDirection</t>
+          <t>http://iiif.io/api/presentation/7#rightToLeftDirection</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr"/>
@@ -1023,7 +1027,7 @@
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/503a9098-4443-20f7-2ef1-cebc95096a74/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/dc4aa20b-25b3-1976-505d-c313483199ba/manifest</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr"/>
@@ -1031,33 +1035,29 @@
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="n">
-        <v>11</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>中御門大納言宣順卿記</t>
+          <t>大嘗會部類 (存1巻)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>G27:165</t>
+          <t>G26:966</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ナカミカド ダイナゴン ノブヨリ キョウ キ</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>宣順卿記, 承應二年中御門大納言宣順卿記</t>
-        </is>
-      </c>
+          <t>ダイジョウエ ブルイ</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>中御門 宣順</t>
+          <t>不明</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>28cm</t>
+          <t>29cm</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>書名及び巻次は表紙による|3: 承應二年|印記: 「和學講談所」,「温故堂文庫」,「渡部文庫珍藏書印」|虫損あり</t>
+          <t>書名及び巻次は表紙による|2を存す|仮綴|印記: 「野宮書印」|朱筆書き入れあり|虫損あり</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -1105,19 +1105,15 @@
           <t>和古書</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>渡部文庫</t>
-        </is>
-      </c>
+      <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/dc4aa20b-25b3-1976-505d-c313483199ba.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/18bcd8ff-2df2-62ac-a685-fa22a8cb5a58.json</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>dc4aa20b-25b3-1976-505d-c313483199ba</t>
+          <t>18bcd8ff-2df2-62ac-a685-fa22a8cb5a58</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -1127,7 +1123,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/dc4aa20b-25b3-1976-505d-c313483199ba</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/18bcd8ff-2df2-62ac-a685-fa22a8cb5a58</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1137,12 +1133,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/4184c533168fcea03213cc03858c46672c2f3b30.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/17578c3efd5fd9990d9c44b722b4f881e0ba7231.jpg</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1361390</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1361392</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1152,7 +1148,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>http://iiif.io/api/presentation/7#rightToLeftDirection</t>
+          <t>http://iiif.io/api/presentation/9#rightToLeftDirection</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr"/>
@@ -1165,7 +1161,7 @@
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/dc4aa20b-25b3-1976-505d-c313483199ba/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/18bcd8ff-2df2-62ac-a685-fa22a8cb5a58/manifest</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr"/>
@@ -1173,41 +1169,41 @@
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="n">
-        <v>39</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>大嘗會部類 (存1巻)</t>
+          <t>柱史抄 上</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>G26:966</t>
+          <t>G26:256</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ダイジョウエ ブルイ</t>
+          <t>チュウシショウ ジョウ</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
+          <t>藤原 孝範</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>[書写者不明]</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
           <t>不明</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>[書写者不明]</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>不明</t>
-        </is>
-      </c>
       <c r="H6" t="inlineStr">
         <is>
           <t>[書写年不明]</t>
@@ -1215,7 +1211,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1225,12 +1221,12 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>29cm</t>
+          <t>27cm</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>書名及び巻次は表紙による|2を存す|仮綴|印記: 「野宮書印」|朱筆書き入れあり|虫損あり</t>
+          <t>印記: 「華山藏書之印」,「渡部文庫珍藏書印」|朱筆書き入れあり|虫損あり</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1243,15 +1239,19 @@
           <t>和古書</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr"/>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>渡部文庫</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/18bcd8ff-2df2-62ac-a685-fa22a8cb5a58.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/aa9e6c3f-0a12-47dc-9d5f-b6d7466a7e28.json</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>18bcd8ff-2df2-62ac-a685-fa22a8cb5a58</t>
+          <t>aa9e6c3f-0a12-47dc-9d5f-b6d7466a7e28</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/18bcd8ff-2df2-62ac-a685-fa22a8cb5a58</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/aa9e6c3f-0a12-47dc-9d5f-b6d7466a7e28</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/17578c3efd5fd9990d9c44b722b4f881e0ba7231.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/92f6ce8da05d1ee555c30e2821d0d2ac3c24592c.jpg</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1361392</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1361394</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1286,7 +1286,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>http://iiif.io/api/presentation/9#rightToLeftDirection</t>
+          <t>http://iiif.io/api/presentation/11#rightToLeftDirection</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr"/>
@@ -1299,7 +1299,7 @@
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/18bcd8ff-2df2-62ac-a685-fa22a8cb5a58/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/aa9e6c3f-0a12-47dc-9d5f-b6d7466a7e28/manifest</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr"/>
@@ -1313,23 +1313,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>柱史抄 上</t>
+          <t>蛙抄 7</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>G26:256</t>
+          <t>G26:45</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>チュウシショウ ジョウ</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>アショウ 7</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>蛙鈔</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>藤原 孝範</t>
+          <t>洞院 実煕</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1344,12 +1348,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>[書写年不明]</t>
+          <t>[江戸後期]</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1359,12 +1363,12 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>27cm</t>
+          <t>28cm</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>印記: 「華山藏書之印」,「渡部文庫珍藏書印」|朱筆書き入れあり|虫損あり</t>
+          <t>書名及び巻次は題簽による|8の目首の書名: 蛙鈔|各奥書に「享和三年仲春一挍畢」(1-2)「享和三季春挍合畢」(3)「享和三年季春挍合畢」(4)「享和三年仲春一挍了」(5)「享和三年孟夏挍合畢」(6-7)「一挍畢」(8)とあり|頭注あり|1: 冠部, 剱部. 2: 袍部. 3-4: 下襲部. 5: 半臂, 袙, 表袴部. 6: 直衣部. 7: 打衣部. 8: 車輿部|印記: 「希賢亭圖書記」|1の扉裏に「經亮云蛙抄ハ三條家ニ秘藏セラレシ装束抄ナリ邂逅ニ袍部及車輿部ノ二冊ハ世ニ流布セリ今又下重部二冊半臂袙表袴部一冊直衣部一冊打衣部一冊以上八冊也此餘モアリトイヘトモイマタ知ラス半臂部ニ其事見小忌部トアルヲ見レハ小忌部ナドモアルベシ而シテ此抄ハ三條家ノモノトモミヘズ當家ト抄中ニアルハ洞院家ノコト也若疑ハ東山左府實凞公ナトノ手ニ出タリシニヤ可考事ナリ先年コノコトヲ瑜伽心院入道前権大納言紀光卿ニキコヱケレバサモアラント諾玉ヘリ」と朱書あり|朱筆書き入れあり|付箋あり|虫損あり</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1377,19 +1381,15 @@
           <t>和古書</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>渡部文庫</t>
-        </is>
-      </c>
+      <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/aa9e6c3f-0a12-47dc-9d5f-b6d7466a7e28.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/4cb13342-3d2f-0027-2ad6-da984e2c3d6d.json</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>aa9e6c3f-0a12-47dc-9d5f-b6d7466a7e28</t>
+          <t>4cb13342-3d2f-0027-2ad6-da984e2c3d6d</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1399,7 +1399,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/aa9e6c3f-0a12-47dc-9d5f-b6d7466a7e28</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/4cb13342-3d2f-0027-2ad6-da984e2c3d6d</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1409,12 +1409,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/92f6ce8da05d1ee555c30e2821d0d2ac3c24592c.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/b8c2cc84b66430038932deffec626f0f32a13959.jpg</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1361394</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1361396</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>http://iiif.io/api/presentation/11#rightToLeftDirection</t>
+          <t>http://iiif.io/api/presentation/13#rightToLeftDirection</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr"/>
@@ -1437,7 +1437,7 @@
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/aa9e6c3f-0a12-47dc-9d5f-b6d7466a7e28/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/4cb13342-3d2f-0027-2ad6-da984e2c3d6d/manifest</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr"/>
@@ -1445,13 +1445,13 @@
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="inlineStr"/>
       <c r="AH7" t="n">
-        <v>53</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>蛙抄 7</t>
+          <t>蛙抄 5</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1461,7 +1461,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>アショウ 7</t>
+          <t>アショウ 5</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1522,12 +1522,12 @@
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/4cb13342-3d2f-0027-2ad6-da984e2c3d6d.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/546a78f4-428e-6dba-70bf-a012abfa0d8a.json</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>4cb13342-3d2f-0027-2ad6-da984e2c3d6d</t>
+          <t>546a78f4-428e-6dba-70bf-a012abfa0d8a</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/4cb13342-3d2f-0027-2ad6-da984e2c3d6d</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/546a78f4-428e-6dba-70bf-a012abfa0d8a</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/b8c2cc84b66430038932deffec626f0f32a13959.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/d0934b537402b27018cdeaf504cb5247102fe258.jpg</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1361396</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1361398</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>http://iiif.io/api/presentation/13#rightToLeftDirection</t>
+          <t>http://iiif.io/api/presentation/15#rightToLeftDirection</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr"/>
@@ -1575,7 +1575,7 @@
       <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/4cb13342-3d2f-0027-2ad6-da984e2c3d6d/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/546a78f4-428e-6dba-70bf-a012abfa0d8a/manifest</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr"/>
@@ -1583,13 +1583,13 @@
       <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="inlineStr"/>
       <c r="AH8" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>蛙抄 5</t>
+          <t>蛙抄 3</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1599,7 +1599,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>アショウ 5</t>
+          <t>アショウ 3</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1660,12 +1660,12 @@
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/546a78f4-428e-6dba-70bf-a012abfa0d8a.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/722ddb21-8d89-37c1-30e7-eca05eb95176.json</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>546a78f4-428e-6dba-70bf-a012abfa0d8a</t>
+          <t>722ddb21-8d89-37c1-30e7-eca05eb95176</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/546a78f4-428e-6dba-70bf-a012abfa0d8a</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/722ddb21-8d89-37c1-30e7-eca05eb95176</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
@@ -1685,12 +1685,12 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/d0934b537402b27018cdeaf504cb5247102fe258.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/c0ca51c9e6c25976f232f4ddb3182d541d6a4811.jpg</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1361398</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1361400</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>http://iiif.io/api/presentation/15#rightToLeftDirection</t>
+          <t>http://iiif.io/api/presentation/17#rightToLeftDirection</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr"/>
@@ -1713,7 +1713,7 @@
       <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/546a78f4-428e-6dba-70bf-a012abfa0d8a/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/722ddb21-8d89-37c1-30e7-eca05eb95176/manifest</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr"/>
@@ -1721,13 +1721,13 @@
       <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="inlineStr"/>
       <c r="AH9" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>蛙抄 3</t>
+          <t>蛙抄 1</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>アショウ 3</t>
+          <t>アショウ 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1798,12 +1798,12 @@
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/722ddb21-8d89-37c1-30e7-eca05eb95176.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/3cf264e7-3309-9308-461e-f40a43cf0382.json</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>722ddb21-8d89-37c1-30e7-eca05eb95176</t>
+          <t>3cf264e7-3309-9308-461e-f40a43cf0382</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/722ddb21-8d89-37c1-30e7-eca05eb95176</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/3cf264e7-3309-9308-461e-f40a43cf0382</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/c0ca51c9e6c25976f232f4ddb3182d541d6a4811.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/33ff9a81a583cfab208f93ee171b7a185dc82b7d.jpg</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1361400</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1361402</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>http://iiif.io/api/presentation/17#rightToLeftDirection</t>
+          <t>http://iiif.io/api/presentation/19#rightToLeftDirection</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr"/>
@@ -1851,7 +1851,7 @@
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/722ddb21-8d89-37c1-30e7-eca05eb95176/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/3cf264e7-3309-9308-461e-f40a43cf0382/manifest</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr"/>
@@ -1859,53 +1859,49 @@
       <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="inlineStr"/>
       <c r="AH10" t="n">
-        <v>22</v>
+        <v>41</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>蛙抄 1</t>
+          <t>中野蒐集佛教并三教及各部繪入板本目録</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>G26:45</t>
+          <t>C40:4254</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>アショウ 1</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>蛙鈔</t>
-        </is>
-      </c>
+          <t>ナカノ シュウシュウ ブッキョウ ナラビニ サンキョウ オヨビ カクブ</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>洞院 実煕</t>
+          <t>中野 達慧</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>[書写者不明]</t>
+          <t>東京帝国大学附属図書館</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>不明</t>
+          <t>1926</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>[江戸後期]</t>
+          <t>大正15/明治元</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1915,12 +1911,12 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>28cm</t>
+          <t>25cm</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>書名及び巻次は題簽による|8の目首の書名: 蛙鈔|各奥書に「享和三年仲春一挍畢」(1-2)「享和三季春挍合畢」(3)「享和三年季春挍合畢」(4)「享和三年仲春一挍了」(5)「享和三年孟夏挍合畢」(6-7)「一挍畢」(8)とあり|頭注あり|1: 冠部, 剱部. 2: 袍部. 3-4: 下襲部. 5: 半臂, 袙, 表袴部. 6: 直衣部. 7: 打衣部. 8: 車輿部|印記: 「希賢亭圖書記」|1の扉裏に「經亮云蛙抄ハ三條家ニ秘藏セラレシ装束抄ナリ邂逅ニ袍部及車輿部ノ二冊ハ世ニ流布セリ今又下重部二冊半臂袙表袴部一冊直衣部一冊打衣部一冊以上八冊也此餘モアリトイヘトモイマタ知ラス半臂部ニ其事見小忌部トアルヲ見レハ小忌部ナドモアルベシ而シテ此抄ハ三條家ノモノトモミヘズ當家ト抄中ニアルハ洞院家ノコト也若疑ハ東山左府實凞公ナトノ手ニ出タリシニヤ可考事ナリ先年コノコトヲ瑜伽心院入道前権大納言紀光卿ニキコヱケレバサモアラント諾玉ヘリ」と朱書あり|朱筆書き入れあり|付箋あり|虫損あり</t>
+          <t>著者の自筆稿本|付:受入れ関係資料(袋入)</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1930,18 +1926,18 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>和古書</t>
+          <t>図書</t>
         </is>
       </c>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/3cf264e7-3309-9308-461e-f40a43cf0382.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/fbf26de6-88d7-86db-7a3f-79a446c00445.json</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>3cf264e7-3309-9308-461e-f40a43cf0382</t>
+          <t>fbf26de6-88d7-86db-7a3f-79a446c00445</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1951,7 +1947,7 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/3cf264e7-3309-9308-461e-f40a43cf0382</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/fbf26de6-88d7-86db-7a3f-79a446c00445</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
@@ -1961,12 +1957,12 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/33ff9a81a583cfab208f93ee171b7a185dc82b7d.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/010f8afb8aff57fed034d4d865411b48ec03a3bd.jpg</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1361402</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1361385</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
@@ -1976,7 +1972,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>http://iiif.io/api/presentation/19#rightToLeftDirection</t>
+          <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr"/>
@@ -1989,7 +1985,7 @@
       <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/3cf264e7-3309-9308-461e-f40a43cf0382/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/fbf26de6-88d7-86db-7a3f-79a446c00445/manifest</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr"/>
@@ -1997,44 +1993,48 @@
       <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="inlineStr"/>
       <c r="AH11" t="n">
-        <v>41</v>
+        <v>123</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>中野蒐集佛教并三教及各部繪入板本目録</t>
+          <t>供様圖式</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>C40:4254</t>
+          <t>JG:32</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ナカノ シュウシュウ ブッキョウ ナラビニ サンキョウ オヨビ カクブ</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>クヨウ ズシキ</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>供様図式</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>中野 達慧</t>
+          <t>四辻 公韶</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>東京帝国大学附属図書館</t>
+          <t>藤原公韶</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1926</t>
+          <t>1687</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>大正15/明治元</t>
+          <t>貞享4</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -2049,12 +2049,12 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>25cm</t>
+          <t>35.7cm</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>著者の自筆稿本|付:受入れ関係資料(袋入)</t>
+          <t>書名は題簽による|巻末に「貞享四年丁卯十一月一日忌火御飯十七日解齋御粥/左中将 (花押)写」とあり|奥書に「右圖式従園頭中将基勝朝臣/令借本写之畢/貞享四年十一月廿一日左中将 (花押) (「藤原公韶」の朱方印あり)」とあり|彩色あり|印記: 「野宮藏書」</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -2064,18 +2064,18 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>図書</t>
+          <t>和古書</t>
         </is>
       </c>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/fbf26de6-88d7-86db-7a3f-79a446c00445.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/f13b4435-13f6-1620-6ff9-c29077111174.json</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>fbf26de6-88d7-86db-7a3f-79a446c00445</t>
+          <t>f13b4435-13f6-1620-6ff9-c29077111174</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -2085,7 +2085,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/fbf26de6-88d7-86db-7a3f-79a446c00445</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/f13b4435-13f6-1620-6ff9-c29077111174</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
@@ -2095,12 +2095,12 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/010f8afb8aff57fed034d4d865411b48ec03a3bd.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/a1afc99196840b0659140d1885787a328f681db0.jpg</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1361385</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1361386</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
+          <t>http://iiif.io/api/presentation/3#rightToLeftDirection</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr"/>
@@ -2123,7 +2123,7 @@
       <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/fbf26de6-88d7-86db-7a3f-79a446c00445/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/f13b4435-13f6-1620-6ff9-c29077111174/manifest</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr"/>
@@ -2131,7 +2131,7 @@
       <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="inlineStr"/>
       <c r="AH12" t="n">
-        <v>123</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13">

--- a/docs/collections/koten/metadata/data.xlsx
+++ b/docs/collections/koten/metadata/data.xlsx
@@ -761,42 +761,42 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>大嘗會悠紀主基鮮味之繪</t>
+          <t>中御門大納言宣順卿記</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>A00:6108</t>
+          <t>G27:165</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ダイジョウエ ユキ スキ センミ ノ ズ</t>
+          <t>ナカミカド ダイナゴン ノブヨリ キョウ キ</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>悠紀主基鮮味之啚, 元文悠紀主基鮮味之圖</t>
+          <t>宣順卿記, 承應二年中御門大納言宣順卿記</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>中御門 宣順</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>[書写者不明]</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
           <t>不明</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>[佐伯]</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>1764</t>
-        </is>
-      </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>明和元</t>
+          <t>[書写年不明]</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -811,12 +811,12 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>40×165cm</t>
+          <t>28cm</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>絵巻|書名は識語による|書袋の書名: 悠紀主基鮮味之啚|表紙裏に「元文悠紀主基鮮味之圖 寛延同」とあり|巻末の識語に「右大嘗會悠紀主基鮮味之繪借請御厨子所預紀宗直朝臣令佐伯職房摸冩之畢 明和元年孟冬左少将藤原(花押)」とあり|絵4幅: 梅作枝, 糸作枩, 萩作枝, 萩作枝|紙本著色|彩色あり|帙入り|印記: 「野宮藏書」</t>
+          <t>書名及び巻次は表紙による|3: 承應二年|印記: 「和學講談所」,「温故堂文庫」,「渡部文庫珍藏書印」|虫損あり</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -829,15 +829,19 @@
           <t>和古書</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr"/>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>渡部文庫</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/503a9098-4443-20f7-2ef1-cebc95096a74.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/dc4aa20b-25b3-1976-505d-c313483199ba.json</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>503a9098-4443-20f7-2ef1-cebc95096a74</t>
+          <t>dc4aa20b-25b3-1976-505d-c313483199ba</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -847,7 +851,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/503a9098-4443-20f7-2ef1-cebc95096a74</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/dc4aa20b-25b3-1976-505d-c313483199ba</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -857,12 +861,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/2a7f21a6103a0653e35f8e5fada19af4c1a6d7bd.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/4184c533168fcea03213cc03858c46672c2f3b30.jpg</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1361388</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1361390</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -872,7 +876,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>http://iiif.io/api/presentation/5#rightToLeftDirection</t>
+          <t>http://iiif.io/api/presentation/7#rightToLeftDirection</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr"/>
@@ -885,7 +889,7 @@
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/503a9098-4443-20f7-2ef1-cebc95096a74/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/dc4aa20b-25b3-1976-505d-c313483199ba/manifest</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr"/>
@@ -893,33 +897,29 @@
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="n">
-        <v>11</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>中御門大納言宣順卿記</t>
+          <t>大嘗會部類 (存1巻)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>G27:165</t>
+          <t>G26:966</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ナカミカド ダイナゴン ノブヨリ キョウ キ</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>宣順卿記, 承應二年中御門大納言宣順卿記</t>
-        </is>
-      </c>
+          <t>ダイジョウエ ブルイ</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>中御門 宣順</t>
+          <t>不明</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>28cm</t>
+          <t>29cm</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>書名及び巻次は表紙による|3: 承應二年|印記: 「和學講談所」,「温故堂文庫」,「渡部文庫珍藏書印」|虫損あり</t>
+          <t>書名及び巻次は表紙による|2を存す|仮綴|印記: 「野宮書印」|朱筆書き入れあり|虫損あり</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -967,19 +967,15 @@
           <t>和古書</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>渡部文庫</t>
-        </is>
-      </c>
+      <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/dc4aa20b-25b3-1976-505d-c313483199ba.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/18bcd8ff-2df2-62ac-a685-fa22a8cb5a58.json</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>dc4aa20b-25b3-1976-505d-c313483199ba</t>
+          <t>18bcd8ff-2df2-62ac-a685-fa22a8cb5a58</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -989,7 +985,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/dc4aa20b-25b3-1976-505d-c313483199ba</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/18bcd8ff-2df2-62ac-a685-fa22a8cb5a58</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -999,12 +995,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/4184c533168fcea03213cc03858c46672c2f3b30.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/17578c3efd5fd9990d9c44b722b4f881e0ba7231.jpg</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1361390</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1361392</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1014,7 +1010,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>http://iiif.io/api/presentation/7#rightToLeftDirection</t>
+          <t>http://iiif.io/api/presentation/9#rightToLeftDirection</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr"/>
@@ -1027,7 +1023,7 @@
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/dc4aa20b-25b3-1976-505d-c313483199ba/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/18bcd8ff-2df2-62ac-a685-fa22a8cb5a58/manifest</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr"/>
@@ -1035,41 +1031,41 @@
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="n">
-        <v>39</v>
+        <v>53</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>大嘗會部類 (存1巻)</t>
+          <t>柱史抄 上</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>G26:966</t>
+          <t>G26:256</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ダイジョウエ ブルイ</t>
+          <t>チュウシショウ ジョウ</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
+          <t>藤原 孝範</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>[書写者不明]</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
           <t>不明</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>[書写者不明]</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>不明</t>
-        </is>
-      </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>[書写年不明]</t>
@@ -1077,7 +1073,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1087,12 +1083,12 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>29cm</t>
+          <t>27cm</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>書名及び巻次は表紙による|2を存す|仮綴|印記: 「野宮書印」|朱筆書き入れあり|虫損あり</t>
+          <t>印記: 「華山藏書之印」,「渡部文庫珍藏書印」|朱筆書き入れあり|虫損あり</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -1105,15 +1101,19 @@
           <t>和古書</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr"/>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>渡部文庫</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/18bcd8ff-2df2-62ac-a685-fa22a8cb5a58.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/aa9e6c3f-0a12-47dc-9d5f-b6d7466a7e28.json</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>18bcd8ff-2df2-62ac-a685-fa22a8cb5a58</t>
+          <t>aa9e6c3f-0a12-47dc-9d5f-b6d7466a7e28</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/18bcd8ff-2df2-62ac-a685-fa22a8cb5a58</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/aa9e6c3f-0a12-47dc-9d5f-b6d7466a7e28</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1133,12 +1133,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/17578c3efd5fd9990d9c44b722b4f881e0ba7231.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/92f6ce8da05d1ee555c30e2821d0d2ac3c24592c.jpg</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1361392</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1361394</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>http://iiif.io/api/presentation/9#rightToLeftDirection</t>
+          <t>http://iiif.io/api/presentation/11#rightToLeftDirection</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr"/>
@@ -1161,7 +1161,7 @@
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/18bcd8ff-2df2-62ac-a685-fa22a8cb5a58/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/aa9e6c3f-0a12-47dc-9d5f-b6d7466a7e28/manifest</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr"/>
@@ -1175,23 +1175,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>柱史抄 上</t>
+          <t>蛙抄 7</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>G26:256</t>
+          <t>G26:45</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>チュウシショウ ジョウ</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>アショウ 7</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>蛙鈔</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>藤原 孝範</t>
+          <t>洞院 実煕</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1206,12 +1210,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>[書写年不明]</t>
+          <t>[江戸後期]</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1221,12 +1225,12 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>27cm</t>
+          <t>28cm</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>印記: 「華山藏書之印」,「渡部文庫珍藏書印」|朱筆書き入れあり|虫損あり</t>
+          <t>書名及び巻次は題簽による|8の目首の書名: 蛙鈔|各奥書に「享和三年仲春一挍畢」(1-2)「享和三季春挍合畢」(3)「享和三年季春挍合畢」(4)「享和三年仲春一挍了」(5)「享和三年孟夏挍合畢」(6-7)「一挍畢」(8)とあり|頭注あり|1: 冠部, 剱部. 2: 袍部. 3-4: 下襲部. 5: 半臂, 袙, 表袴部. 6: 直衣部. 7: 打衣部. 8: 車輿部|印記: 「希賢亭圖書記」|1の扉裏に「經亮云蛙抄ハ三條家ニ秘藏セラレシ装束抄ナリ邂逅ニ袍部及車輿部ノ二冊ハ世ニ流布セリ今又下重部二冊半臂袙表袴部一冊直衣部一冊打衣部一冊以上八冊也此餘モアリトイヘトモイマタ知ラス半臂部ニ其事見小忌部トアルヲ見レハ小忌部ナドモアルベシ而シテ此抄ハ三條家ノモノトモミヘズ當家ト抄中ニアルハ洞院家ノコト也若疑ハ東山左府實凞公ナトノ手ニ出タリシニヤ可考事ナリ先年コノコトヲ瑜伽心院入道前権大納言紀光卿ニキコヱケレバサモアラント諾玉ヘリ」と朱書あり|朱筆書き入れあり|付箋あり|虫損あり</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1239,19 +1243,15 @@
           <t>和古書</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>渡部文庫</t>
-        </is>
-      </c>
+      <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/aa9e6c3f-0a12-47dc-9d5f-b6d7466a7e28.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/4cb13342-3d2f-0027-2ad6-da984e2c3d6d.json</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>aa9e6c3f-0a12-47dc-9d5f-b6d7466a7e28</t>
+          <t>4cb13342-3d2f-0027-2ad6-da984e2c3d6d</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/aa9e6c3f-0a12-47dc-9d5f-b6d7466a7e28</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/4cb13342-3d2f-0027-2ad6-da984e2c3d6d</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/92f6ce8da05d1ee555c30e2821d0d2ac3c24592c.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/b8c2cc84b66430038932deffec626f0f32a13959.jpg</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1361394</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1361396</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1286,7 +1286,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>http://iiif.io/api/presentation/11#rightToLeftDirection</t>
+          <t>http://iiif.io/api/presentation/13#rightToLeftDirection</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr"/>
@@ -1299,7 +1299,7 @@
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/aa9e6c3f-0a12-47dc-9d5f-b6d7466a7e28/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/4cb13342-3d2f-0027-2ad6-da984e2c3d6d/manifest</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr"/>
@@ -1307,13 +1307,13 @@
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="inlineStr"/>
       <c r="AH6" t="n">
-        <v>53</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>蛙抄 7</t>
+          <t>蛙抄 5</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>アショウ 7</t>
+          <t>アショウ 5</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1384,12 +1384,12 @@
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/4cb13342-3d2f-0027-2ad6-da984e2c3d6d.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/546a78f4-428e-6dba-70bf-a012abfa0d8a.json</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>4cb13342-3d2f-0027-2ad6-da984e2c3d6d</t>
+          <t>546a78f4-428e-6dba-70bf-a012abfa0d8a</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1399,7 +1399,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/4cb13342-3d2f-0027-2ad6-da984e2c3d6d</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/546a78f4-428e-6dba-70bf-a012abfa0d8a</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1409,12 +1409,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/b8c2cc84b66430038932deffec626f0f32a13959.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/d0934b537402b27018cdeaf504cb5247102fe258.jpg</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1361396</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1361398</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>http://iiif.io/api/presentation/13#rightToLeftDirection</t>
+          <t>http://iiif.io/api/presentation/15#rightToLeftDirection</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr"/>
@@ -1437,7 +1437,7 @@
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/4cb13342-3d2f-0027-2ad6-da984e2c3d6d/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/546a78f4-428e-6dba-70bf-a012abfa0d8a/manifest</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr"/>
@@ -1445,13 +1445,13 @@
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="inlineStr"/>
       <c r="AH7" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>蛙抄 5</t>
+          <t>蛙抄 3</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1461,7 +1461,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>アショウ 5</t>
+          <t>アショウ 3</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1522,12 +1522,12 @@
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/546a78f4-428e-6dba-70bf-a012abfa0d8a.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/722ddb21-8d89-37c1-30e7-eca05eb95176.json</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>546a78f4-428e-6dba-70bf-a012abfa0d8a</t>
+          <t>722ddb21-8d89-37c1-30e7-eca05eb95176</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/546a78f4-428e-6dba-70bf-a012abfa0d8a</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/722ddb21-8d89-37c1-30e7-eca05eb95176</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/d0934b537402b27018cdeaf504cb5247102fe258.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/c0ca51c9e6c25976f232f4ddb3182d541d6a4811.jpg</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1361398</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1361400</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>http://iiif.io/api/presentation/15#rightToLeftDirection</t>
+          <t>http://iiif.io/api/presentation/17#rightToLeftDirection</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr"/>
@@ -1575,7 +1575,7 @@
       <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/546a78f4-428e-6dba-70bf-a012abfa0d8a/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/722ddb21-8d89-37c1-30e7-eca05eb95176/manifest</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr"/>
@@ -1583,13 +1583,13 @@
       <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="inlineStr"/>
       <c r="AH8" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>蛙抄 3</t>
+          <t>蛙抄 1</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1599,7 +1599,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>アショウ 3</t>
+          <t>アショウ 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1660,12 +1660,12 @@
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/722ddb21-8d89-37c1-30e7-eca05eb95176.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/3cf264e7-3309-9308-461e-f40a43cf0382.json</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>722ddb21-8d89-37c1-30e7-eca05eb95176</t>
+          <t>3cf264e7-3309-9308-461e-f40a43cf0382</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/722ddb21-8d89-37c1-30e7-eca05eb95176</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/3cf264e7-3309-9308-461e-f40a43cf0382</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
@@ -1685,12 +1685,12 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/c0ca51c9e6c25976f232f4ddb3182d541d6a4811.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/33ff9a81a583cfab208f93ee171b7a185dc82b7d.jpg</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1361400</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1361402</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>http://iiif.io/api/presentation/17#rightToLeftDirection</t>
+          <t>http://iiif.io/api/presentation/19#rightToLeftDirection</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr"/>
@@ -1713,7 +1713,7 @@
       <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/722ddb21-8d89-37c1-30e7-eca05eb95176/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/3cf264e7-3309-9308-461e-f40a43cf0382/manifest</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr"/>
@@ -1721,53 +1721,49 @@
       <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="inlineStr"/>
       <c r="AH9" t="n">
-        <v>22</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>蛙抄 1</t>
+          <t>中野蒐集佛教并三教及各部繪入板本目録</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>G26:45</t>
+          <t>C40:4254</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>アショウ 1</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>蛙鈔</t>
-        </is>
-      </c>
+          <t>ナカノ シュウシュウ ブッキョウ ナラビニ サンキョウ オヨビ カクブ</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>洞院 実煕</t>
+          <t>中野 達慧</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>[書写者不明]</t>
+          <t>東京帝国大学附属図書館</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>不明</t>
+          <t>1926</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>[江戸後期]</t>
+          <t>大正15/明治元</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1777,12 +1773,12 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>28cm</t>
+          <t>25cm</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>書名及び巻次は題簽による|8の目首の書名: 蛙鈔|各奥書に「享和三年仲春一挍畢」(1-2)「享和三季春挍合畢」(3)「享和三年季春挍合畢」(4)「享和三年仲春一挍了」(5)「享和三年孟夏挍合畢」(6-7)「一挍畢」(8)とあり|頭注あり|1: 冠部, 剱部. 2: 袍部. 3-4: 下襲部. 5: 半臂, 袙, 表袴部. 6: 直衣部. 7: 打衣部. 8: 車輿部|印記: 「希賢亭圖書記」|1の扉裏に「經亮云蛙抄ハ三條家ニ秘藏セラレシ装束抄ナリ邂逅ニ袍部及車輿部ノ二冊ハ世ニ流布セリ今又下重部二冊半臂袙表袴部一冊直衣部一冊打衣部一冊以上八冊也此餘モアリトイヘトモイマタ知ラス半臂部ニ其事見小忌部トアルヲ見レハ小忌部ナドモアルベシ而シテ此抄ハ三條家ノモノトモミヘズ當家ト抄中ニアルハ洞院家ノコト也若疑ハ東山左府實凞公ナトノ手ニ出タリシニヤ可考事ナリ先年コノコトヲ瑜伽心院入道前権大納言紀光卿ニキコヱケレバサモアラント諾玉ヘリ」と朱書あり|朱筆書き入れあり|付箋あり|虫損あり</t>
+          <t>著者の自筆稿本|付:受入れ関係資料(袋入)</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1792,18 +1788,18 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>和古書</t>
+          <t>図書</t>
         </is>
       </c>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/3cf264e7-3309-9308-461e-f40a43cf0382.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/fbf26de6-88d7-86db-7a3f-79a446c00445.json</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>3cf264e7-3309-9308-461e-f40a43cf0382</t>
+          <t>fbf26de6-88d7-86db-7a3f-79a446c00445</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1813,7 +1809,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/3cf264e7-3309-9308-461e-f40a43cf0382</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/fbf26de6-88d7-86db-7a3f-79a446c00445</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
@@ -1823,12 +1819,12 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/33ff9a81a583cfab208f93ee171b7a185dc82b7d.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/010f8afb8aff57fed034d4d865411b48ec03a3bd.jpg</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1361402</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1361385</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
@@ -1838,7 +1834,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>http://iiif.io/api/presentation/19#rightToLeftDirection</t>
+          <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr"/>
@@ -1851,7 +1847,7 @@
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/3cf264e7-3309-9308-461e-f40a43cf0382/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/fbf26de6-88d7-86db-7a3f-79a446c00445/manifest</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr"/>
@@ -1859,44 +1855,48 @@
       <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="inlineStr"/>
       <c r="AH10" t="n">
-        <v>41</v>
+        <v>123</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>中野蒐集佛教并三教及各部繪入板本目録</t>
+          <t>供様圖式</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>C40:4254</t>
+          <t>JG:32</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ナカノ シュウシュウ ブッキョウ ナラビニ サンキョウ オヨビ カクブ</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>クヨウ ズシキ</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>供様図式</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>中野 達慧</t>
+          <t>四辻 公韶</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>東京帝国大学附属図書館</t>
+          <t>藤原公韶</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1926</t>
+          <t>1687</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>大正15/明治元</t>
+          <t>貞享4</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1911,12 +1911,12 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>25cm</t>
+          <t>35.7cm</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>著者の自筆稿本|付:受入れ関係資料(袋入)</t>
+          <t>書名は題簽による|巻末に「貞享四年丁卯十一月一日忌火御飯十七日解齋御粥/左中将 (花押)写」とあり|奥書に「右圖式従園頭中将基勝朝臣/令借本写之畢/貞享四年十一月廿一日左中将 (花押) (「藤原公韶」の朱方印あり)」とあり|彩色あり|印記: 「野宮藏書」</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1926,18 +1926,18 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>図書</t>
+          <t>和古書</t>
         </is>
       </c>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/fbf26de6-88d7-86db-7a3f-79a446c00445.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/f13b4435-13f6-1620-6ff9-c29077111174.json</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>fbf26de6-88d7-86db-7a3f-79a446c00445</t>
+          <t>f13b4435-13f6-1620-6ff9-c29077111174</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/fbf26de6-88d7-86db-7a3f-79a446c00445</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/f13b4435-13f6-1620-6ff9-c29077111174</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/010f8afb8aff57fed034d4d865411b48ec03a3bd.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/a1afc99196840b0659140d1885787a328f681db0.jpg</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1361385</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1361386</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
+          <t>http://iiif.io/api/presentation/3#rightToLeftDirection</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr"/>
@@ -1985,7 +1985,7 @@
       <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/fbf26de6-88d7-86db-7a3f-79a446c00445/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/f13b4435-13f6-1620-6ff9-c29077111174/manifest</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr"/>
@@ -1993,48 +1993,44 @@
       <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="inlineStr"/>
       <c r="AH11" t="n">
-        <v>123</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>供様圖式</t>
+          <t>大嘗會調進物</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>JG:32</t>
+          <t>A00:6277</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>クヨウ ズシキ</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>供様図式</t>
-        </is>
-      </c>
+          <t>ダイジョウエ チョウシンモノ</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>四辻 公韶</t>
+          <t>不明</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>藤原公韶</t>
+          <t>[大藏省木工寮] [写]</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1687</t>
+          <t>不明</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>貞享4</t>
+          <t>[明治期]</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -2049,12 +2045,12 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>35.7cm</t>
+          <t>28cm</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>書名は題簽による|巻末に「貞享四年丁卯十一月一日忌火御飯十七日解齋御粥/左中将 (花押)写」とあり|奥書に「右圖式従園頭中将基勝朝臣/令借本写之畢/貞享四年十一月廿一日左中将 (花押) (「藤原公韶」の朱方印あり)」とあり|彩色あり|印記: 「野宮藏書」</t>
+          <t>巻頭の識語に「嘉永元戊申年八月廿九日 官局江差出但奉行ヨリ沙汰ニ依而也官務江茂白画圖一板写被頼差出也 此當家写尤薄彩色夲紙者」との朱書あり|巻末に「大藏省木工寮」とあり|絵巻|彩色あり</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -2070,12 +2066,12 @@
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/f13b4435-13f6-1620-6ff9-c29077111174.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/ff7901b5-7742-4d37-2621-ae0261c41dab.json</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>f13b4435-13f6-1620-6ff9-c29077111174</t>
+          <t>ff7901b5-7742-4d37-2621-ae0261c41dab</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -2085,7 +2081,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/f13b4435-13f6-1620-6ff9-c29077111174</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/ff7901b5-7742-4d37-2621-ae0261c41dab</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
@@ -2095,12 +2091,12 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/a1afc99196840b0659140d1885787a328f681db0.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/426a2bea95a12ba2001d09cb79c81cf5c5db1129.jpg</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1361386</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1361387</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
@@ -2110,7 +2106,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>http://iiif.io/api/presentation/3#rightToLeftDirection</t>
+          <t>http://iiif.io/api/presentation/4#rightToLeftDirection</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr"/>
@@ -2123,7 +2119,7 @@
       <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/f13b4435-13f6-1620-6ff9-c29077111174/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/ff7901b5-7742-4d37-2621-ae0261c41dab/manifest</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr"/>
@@ -2131,26 +2127,30 @@
       <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="inlineStr"/>
       <c r="AH12" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>大嘗會調進物</t>
+          <t>大嘗會悠紀主基鮮味之繪</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>A00:6277</t>
+          <t>A00:6108</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ダイジョウエ チョウシンモノ</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>ダイジョウエ ユキ スキ センミ ノ ズ</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>悠紀主基鮮味之啚, 元文悠紀主基鮮味之圖</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>不明</t>
@@ -2158,17 +2158,17 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>[大藏省木工寮] [写]</t>
+          <t>[佐伯]</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>不明</t>
+          <t>1764</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>[明治期]</t>
+          <t>明和元</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2183,12 +2183,12 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>28cm</t>
+          <t>40×165cm</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>巻頭の識語に「嘉永元戊申年八月廿九日 官局江差出但奉行ヨリ沙汰ニ依而也官務江茂白画圖一板写被頼差出也 此當家写尤薄彩色夲紙者」との朱書あり|巻末に「大藏省木工寮」とあり|絵巻|彩色あり</t>
+          <t>絵巻|書名は識語による|書袋の書名: 悠紀主基鮮味之啚|表紙裏に「元文悠紀主基鮮味之圖 寛延同」とあり|巻末の識語に「右大嘗會悠紀主基鮮味之繪借請御厨子所預紀宗直朝臣令佐伯職房摸冩之畢 明和元年孟冬左少将藤原(花押)」とあり|絵4幅: 梅作枝, 糸作枩, 萩作枝, 萩作枝|紙本著色|彩色あり|帙入り|印記: 「野宮藏書」</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -2204,12 +2204,12 @@
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/ff7901b5-7742-4d37-2621-ae0261c41dab.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/503a9098-4443-20f7-2ef1-cebc95096a74.json</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>ff7901b5-7742-4d37-2621-ae0261c41dab</t>
+          <t>503a9098-4443-20f7-2ef1-cebc95096a74</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -2219,7 +2219,7 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/ff7901b5-7742-4d37-2621-ae0261c41dab</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/503a9098-4443-20f7-2ef1-cebc95096a74</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/426a2bea95a12ba2001d09cb79c81cf5c5db1129.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/2a7f21a6103a0653e35f8e5fada19af4c1a6d7bd.jpg</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1361387</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1361388</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -2244,7 +2244,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>http://iiif.io/api/presentation/4#rightToLeftDirection</t>
+          <t>http://iiif.io/api/presentation/5#rightToLeftDirection</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr"/>
@@ -2257,7 +2257,7 @@
       <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/ff7901b5-7742-4d37-2621-ae0261c41dab/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/503a9098-4443-20f7-2ef1-cebc95096a74/manifest</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr"/>
@@ -2265,7 +2265,7 @@
       <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="inlineStr"/>
       <c r="AH13" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14">

--- a/docs/collections/koten/metadata/data.xlsx
+++ b/docs/collections/koten/metadata/data.xlsx
@@ -13091,50 +13091,58 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>おちくほのさうし</t>
+          <t>凱旋観艦式紀念写真帖</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>A00:4083</t>
+          <t>BW:23</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>オチクボ ノ ソウシ</t>
+          <t>ガイセン カンカンシキ キネン シャシンチョウ</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>おちくほ物語|御本</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr"/>
+          <t>凱旋観艦式 : 明治丗八年 : 紀念写真帖</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>大本営海軍部</t>
+        </is>
+      </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>[書写者不明]</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr"/>
+          <t>大本営海軍部</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>1906</t>
+        </is>
+      </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>[江戸前期]</t>
+          <t>明治39</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>写本</t>
-        </is>
-      </c>
-      <c r="K102" t="inlineStr"/>
+          <t>1冊</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>26X38cm</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>書名は題簽による|毎半帖10行|漢字平仮名交じり文|奈良絵本|桜唐草文様緞子表紙, 松葉散しに山雲の金箔見返し, 金泥下絵鳥の子紙を使用|列帖装|二重箱入り</t>
+          <t>書名は表紙による</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -13150,12 +13158,12 @@
       <c r="O102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/8aa19100-0937-5fd9-29f1-ba41ad8d1830.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/cf226493-0d04-2693-94c7-db99bb068777.json</t>
         </is>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>8aa19100-0937-5fd9-29f1-ba41ad8d1830</t>
+          <t>cf226493-0d04-2693-94c7-db99bb068777</t>
         </is>
       </c>
       <c r="R102" t="inlineStr">
@@ -13165,7 +13173,7 @@
       </c>
       <c r="S102" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/8aa19100-0937-5fd9-29f1-ba41ad8d1830</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/cf226493-0d04-2693-94c7-db99bb068777</t>
         </is>
       </c>
       <c r="T102" t="inlineStr">
@@ -13175,12 +13183,12 @@
       </c>
       <c r="U102" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/124815802d3a78d8f78dd4fbb98d24d55e5c3b34.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/0b0632d275e2d4bc40eded3cadea70aa0277b180.jpg</t>
         </is>
       </c>
       <c r="V102" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1182819</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1168834</t>
         </is>
       </c>
       <c r="W102" t="inlineStr">
@@ -13203,7 +13211,7 @@
       <c r="AB102" t="inlineStr"/>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/8aa19100-0937-5fd9-29f1-ba41ad8d1830/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/cf226493-0d04-2693-94c7-db99bb068777/manifest</t>
         </is>
       </c>
       <c r="AD102" t="inlineStr"/>
@@ -13211,64 +13219,56 @@
       <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="inlineStr"/>
       <c r="AH102" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>凱旋観艦式紀念写真帖</t>
+          <t>おちくほのさうし</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>BW:23</t>
+          <t>A00:4083</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>ガイセン カンカンシキ キネン シャシンチョウ</t>
+          <t>オチクボ ノ ソウシ</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>凱旋観艦式 : 明治丗八年 : 紀念写真帖</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>大本営海軍部</t>
-        </is>
-      </c>
+          <t>おちくほ物語|御本</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr">
         <is>
-          <t>大本営海軍部</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>1906</t>
-        </is>
-      </c>
+          <t>[書写者不明]</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr"/>
       <c r="H103" t="inlineStr">
         <is>
-          <t>明治39</t>
+          <t>[江戸前期]</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>1冊</t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr"/>
-      <c r="K103" t="inlineStr">
-        <is>
-          <t>26X38cm</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>写本</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr"/>
       <c r="L103" t="inlineStr">
         <is>
-          <t>書名は表紙による</t>
+          <t>書名は題簽による|毎半帖10行|漢字平仮名交じり文|奈良絵本|桜唐草文様緞子表紙, 松葉散しに山雲の金箔見返し, 金泥下絵鳥の子紙を使用|列帖装|二重箱入り</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -13284,12 +13284,12 @@
       <c r="O103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/cf226493-0d04-2693-94c7-db99bb068777.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/8aa19100-0937-5fd9-29f1-ba41ad8d1830.json</t>
         </is>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>cf226493-0d04-2693-94c7-db99bb068777</t>
+          <t>8aa19100-0937-5fd9-29f1-ba41ad8d1830</t>
         </is>
       </c>
       <c r="R103" t="inlineStr">
@@ -13299,7 +13299,7 @@
       </c>
       <c r="S103" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/cf226493-0d04-2693-94c7-db99bb068777</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/8aa19100-0937-5fd9-29f1-ba41ad8d1830</t>
         </is>
       </c>
       <c r="T103" t="inlineStr">
@@ -13309,12 +13309,12 @@
       </c>
       <c r="U103" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/0b0632d275e2d4bc40eded3cadea70aa0277b180.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/124815802d3a78d8f78dd4fbb98d24d55e5c3b34.jpg</t>
         </is>
       </c>
       <c r="V103" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1168834</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1182819</t>
         </is>
       </c>
       <c r="W103" t="inlineStr">
@@ -13337,7 +13337,7 @@
       <c r="AB103" t="inlineStr"/>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/cf226493-0d04-2693-94c7-db99bb068777/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/8aa19100-0937-5fd9-29f1-ba41ad8d1830/manifest</t>
         </is>
       </c>
       <c r="AD103" t="inlineStr"/>
@@ -13345,7 +13345,7 @@
       <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="inlineStr"/>
       <c r="AH103" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="104">

--- a/docs/collections/koten/metadata/data.xlsx
+++ b/docs/collections/koten/metadata/data.xlsx
@@ -761,7 +761,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>蛙抄 6</t>
+          <t>蛙抄 5</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -771,7 +771,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>アショウ 6</t>
+          <t>アショウ 5</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -832,12 +832,12 @@
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/d8791f0a-777b-386d-21e8-6da9b37f02c8.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/546a78f4-428e-6dba-70bf-a012abfa0d8a.json</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>d8791f0a-777b-386d-21e8-6da9b37f02c8</t>
+          <t>546a78f4-428e-6dba-70bf-a012abfa0d8a</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/d8791f0a-777b-386d-21e8-6da9b37f02c8</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/546a78f4-428e-6dba-70bf-a012abfa0d8a</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -857,12 +857,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/340e9027fa29b9e2e037e6b59373dd51d91924a8.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/d0934b537402b27018cdeaf504cb5247102fe258.jpg</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1361397</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1361398</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>http://iiif.io/api/presentation/14#rightToLeftDirection</t>
+          <t>http://iiif.io/api/presentation/15#rightToLeftDirection</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr"/>
@@ -885,7 +885,7 @@
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/d8791f0a-777b-386d-21e8-6da9b37f02c8/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/546a78f4-428e-6dba-70bf-a012abfa0d8a/manifest</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr"/>
@@ -893,13 +893,13 @@
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>蛙抄 5</t>
+          <t>蛙抄 4</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -909,7 +909,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>アショウ 5</t>
+          <t>アショウ 4</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -970,12 +970,12 @@
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/546a78f4-428e-6dba-70bf-a012abfa0d8a.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/977b1d81-65b0-4b65-2b3b-266bfde72fb4.json</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>546a78f4-428e-6dba-70bf-a012abfa0d8a</t>
+          <t>977b1d81-65b0-4b65-2b3b-266bfde72fb4</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -985,7 +985,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/546a78f4-428e-6dba-70bf-a012abfa0d8a</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/977b1d81-65b0-4b65-2b3b-266bfde72fb4</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -995,12 +995,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/d0934b537402b27018cdeaf504cb5247102fe258.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/14e1cc135dbfcab9736fe828d1d78b9e64f489dd.jpg</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1361398</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1361399</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>http://iiif.io/api/presentation/15#rightToLeftDirection</t>
+          <t>http://iiif.io/api/presentation/16#rightToLeftDirection</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr"/>
@@ -1023,7 +1023,7 @@
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/546a78f4-428e-6dba-70bf-a012abfa0d8a/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/977b1d81-65b0-4b65-2b3b-266bfde72fb4/manifest</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr"/>
@@ -1031,13 +1031,13 @@
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>蛙抄 4</t>
+          <t>蛙抄 3</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>アショウ 4</t>
+          <t>アショウ 3</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1108,12 +1108,12 @@
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/977b1d81-65b0-4b65-2b3b-266bfde72fb4.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/722ddb21-8d89-37c1-30e7-eca05eb95176.json</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>977b1d81-65b0-4b65-2b3b-266bfde72fb4</t>
+          <t>722ddb21-8d89-37c1-30e7-eca05eb95176</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/977b1d81-65b0-4b65-2b3b-266bfde72fb4</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/722ddb21-8d89-37c1-30e7-eca05eb95176</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1133,12 +1133,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/14e1cc135dbfcab9736fe828d1d78b9e64f489dd.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/c0ca51c9e6c25976f232f4ddb3182d541d6a4811.jpg</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1361399</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1361400</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>http://iiif.io/api/presentation/16#rightToLeftDirection</t>
+          <t>http://iiif.io/api/presentation/17#rightToLeftDirection</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr"/>
@@ -1161,7 +1161,7 @@
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/977b1d81-65b0-4b65-2b3b-266bfde72fb4/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/722ddb21-8d89-37c1-30e7-eca05eb95176/manifest</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr"/>
@@ -1169,13 +1169,13 @@
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>蛙抄 3</t>
+          <t>蛙抄 2</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>アショウ 3</t>
+          <t>アショウ 2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1246,12 +1246,12 @@
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/722ddb21-8d89-37c1-30e7-eca05eb95176.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/38c2b478-6a9c-3527-4f79-cf58fb142798.json</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>722ddb21-8d89-37c1-30e7-eca05eb95176</t>
+          <t>38c2b478-6a9c-3527-4f79-cf58fb142798</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/722ddb21-8d89-37c1-30e7-eca05eb95176</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/38c2b478-6a9c-3527-4f79-cf58fb142798</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/c0ca51c9e6c25976f232f4ddb3182d541d6a4811.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/39e3ab2ee3a234d362b9d57bbf1e3d6ff10e41b3.jpg</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1361400</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1361401</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1286,7 +1286,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>http://iiif.io/api/presentation/17#rightToLeftDirection</t>
+          <t>http://iiif.io/api/presentation/18#rightToLeftDirection</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr"/>
@@ -1299,7 +1299,7 @@
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/722ddb21-8d89-37c1-30e7-eca05eb95176/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/38c2b478-6a9c-3527-4f79-cf58fb142798/manifest</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr"/>
@@ -1307,13 +1307,13 @@
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="inlineStr"/>
       <c r="AH6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>蛙抄 2</t>
+          <t>蛙抄 1</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>アショウ 2</t>
+          <t>アショウ 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1384,12 +1384,12 @@
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/38c2b478-6a9c-3527-4f79-cf58fb142798.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/3cf264e7-3309-9308-461e-f40a43cf0382.json</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>38c2b478-6a9c-3527-4f79-cf58fb142798</t>
+          <t>3cf264e7-3309-9308-461e-f40a43cf0382</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1399,7 +1399,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/38c2b478-6a9c-3527-4f79-cf58fb142798</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/3cf264e7-3309-9308-461e-f40a43cf0382</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1409,12 +1409,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/39e3ab2ee3a234d362b9d57bbf1e3d6ff10e41b3.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/33ff9a81a583cfab208f93ee171b7a185dc82b7d.jpg</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1361401</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1361402</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>http://iiif.io/api/presentation/18#rightToLeftDirection</t>
+          <t>http://iiif.io/api/presentation/19#rightToLeftDirection</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr"/>
@@ -1437,7 +1437,7 @@
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/38c2b478-6a9c-3527-4f79-cf58fb142798/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/3cf264e7-3309-9308-461e-f40a43cf0382/manifest</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr"/>
@@ -1445,38 +1445,38 @@
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="inlineStr"/>
       <c r="AH7" t="n">
-        <v>21</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>蛙抄 1</t>
+          <t>醍醐天皇事記</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>G26:45</t>
+          <t>G27:966</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>アショウ 1</t>
+          <t>ダイゴ テンノウ ジキ</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>蛙鈔</t>
+          <t>史料</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>洞院 実煕</t>
+          <t>塙 保己一</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>[書写者不明]</t>
+          <t>源行之 [写]</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>28cm</t>
+          <t>27cm</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>書名及び巻次は題簽による|8の目首の書名: 蛙鈔|各奥書に「享和三年仲春一挍畢」(1-2)「享和三季春挍合畢」(3)「享和三年季春挍合畢」(4)「享和三年仲春一挍了」(5)「享和三年孟夏挍合畢」(6-7)「一挍畢」(8)とあり|頭注あり|1: 冠部, 剱部. 2: 袍部. 3-4: 下襲部. 5: 半臂, 袙, 表袴部. 6: 直衣部. 7: 打衣部. 8: 車輿部|印記: 「希賢亭圖書記」|1の扉裏に「經亮云蛙抄ハ三條家ニ秘藏セラレシ装束抄ナリ邂逅ニ袍部及車輿部ノ二冊ハ世ニ流布セリ今又下重部二冊半臂袙表袴部一冊直衣部一冊打衣部一冊以上八冊也此餘モアリトイヘトモイマタ知ラス半臂部ニ其事見小忌部トアルヲ見レハ小忌部ナドモアルベシ而シテ此抄ハ三條家ノモノトモミヘズ當家ト抄中ニアルハ洞院家ノコト也若疑ハ東山左府實凞公ナトノ手ニ出タリシニヤ可考事ナリ先年コノコトヲ瑜伽心院入道前権大納言紀光卿ニキコヱケレバサモアラント諾玉ヘリ」と朱書あり|朱筆書き入れあり|付箋あり|虫損あり</t>
+          <t>塙氏等編『史料』巻之33|識語: 「塙本ノ史料零本一冊 此ノ書ハ塙氏家蔵ノ原本ナリ其書全部ハ旧年元老院ニテ買上ケタルガ其ノ中数冊ハ紛失セリトテ新冩本ニテ雜レリ余先年彼ノ院ニ官セシトキ常ニ繙閲シタリキ今ハ内閣記録課ノ蔵本タリ此書一冊ハ塙氏ノ手冩既ニ紛失シタリトイヘル内ノ物ニテ早ク坊間ニ散シタルナリ明治卅八年三月酒井藤兵衞ニテ購フ零本トイヘトモ塙本原書ノ真面目ヲ見ルコトヲ得ヘシ 萩野由之(花押)」|表紙の貼紙に「塙本史料原本 零巻」と墨書あり|印記: 「和學講談所」,「温故堂文庫」</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1519,15 +1519,19 @@
           <t>和古書</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr"/>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>萩野本</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/3cf264e7-3309-9308-461e-f40a43cf0382.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/45e324c7-01db-3830-0a24-e21a2e0c79e8.json</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>3cf264e7-3309-9308-461e-f40a43cf0382</t>
+          <t>45e324c7-01db-3830-0a24-e21a2e0c79e8</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1537,7 +1541,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/3cf264e7-3309-9308-461e-f40a43cf0382</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/45e324c7-01db-3830-0a24-e21a2e0c79e8</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -1547,12 +1551,12 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/33ff9a81a583cfab208f93ee171b7a185dc82b7d.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/2ce84a1535191d6a4cfb10ee0765f5eb11f171c5.jpg</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1361402</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1361403</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -1562,7 +1566,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>http://iiif.io/api/presentation/19#rightToLeftDirection</t>
+          <t>http://iiif.io/api/presentation/20#rightToLeftDirection</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr"/>
@@ -1575,7 +1579,7 @@
       <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/3cf264e7-3309-9308-461e-f40a43cf0382/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/45e324c7-01db-3830-0a24-e21a2e0c79e8/manifest</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr"/>
@@ -1583,68 +1587,64 @@
       <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="inlineStr"/>
       <c r="AH8" t="n">
-        <v>41</v>
+        <v>32</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>醍醐天皇事記</t>
+          <t>凱旋観艦式紀念写真帖</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>G27:966</t>
+          <t>BW:23</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ダイゴ テンノウ ジキ</t>
+          <t>ガイセン カンカンシキ キネン シャシンチョウ</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>史料</t>
+          <t>凱旋観艦式 : 明治丗八年 : 紀念写真帖</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>塙 保己一</t>
+          <t>大本営海軍部</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>源行之 [写]</t>
+          <t>大本営海軍部</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>不明</t>
+          <t>1906</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>[江戸後期]</t>
+          <t>明治39</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>写本</t>
-        </is>
-      </c>
+          <t>1冊</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>27cm</t>
+          <t>26X38cm</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>塙氏等編『史料』巻之33|識語: 「塙本ノ史料零本一冊 此ノ書ハ塙氏家蔵ノ原本ナリ其書全部ハ旧年元老院ニテ買上ケタルガ其ノ中数冊ハ紛失セリトテ新冩本ニテ雜レリ余先年彼ノ院ニ官セシトキ常ニ繙閲シタリキ今ハ内閣記録課ノ蔵本タリ此書一冊ハ塙氏ノ手冩既ニ紛失シタリトイヘル内ノ物ニテ早ク坊間ニ散シタルナリ明治卅八年三月酒井藤兵衞ニテ購フ零本トイヘトモ塙本原書ノ真面目ヲ見ルコトヲ得ヘシ 萩野由之(花押)」|表紙の貼紙に「塙本史料原本 零巻」と墨書あり|印記: 「和學講談所」,「温故堂文庫」</t>
+          <t>書名は表紙による</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1657,29 +1657,25 @@
           <t>和古書</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>萩野本</t>
-        </is>
-      </c>
+      <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/45e324c7-01db-3830-0a24-e21a2e0c79e8.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/cf226493-0d04-2693-94c7-db99bb068777.json</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>45e324c7-01db-3830-0a24-e21a2e0c79e8</t>
+          <t>cf226493-0d04-2693-94c7-db99bb068777</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/45e324c7-01db-3830-0a24-e21a2e0c79e8</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/cf226493-0d04-2693-94c7-db99bb068777</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
@@ -1689,12 +1685,12 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/2ce84a1535191d6a4cfb10ee0765f5eb11f171c5.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/0b0632d275e2d4bc40eded3cadea70aa0277b180.jpg</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1361403</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1168834</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -1704,7 +1700,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>http://iiif.io/api/presentation/20#rightToLeftDirection</t>
+          <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr"/>
@@ -1717,7 +1713,7 @@
       <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/45e324c7-01db-3830-0a24-e21a2e0c79e8/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/cf226493-0d04-2693-94c7-db99bb068777/manifest</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr"/>
@@ -1725,64 +1721,56 @@
       <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="inlineStr"/>
       <c r="AH9" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>凱旋観艦式紀念写真帖</t>
+          <t>おちくほのさうし</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BW:23</t>
+          <t>A00:4083</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ガイセン カンカンシキ キネン シャシンチョウ</t>
+          <t>オチクボ ノ ソウシ</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>凱旋観艦式 : 明治丗八年 : 紀念写真帖</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>大本営海軍部</t>
-        </is>
-      </c>
+          <t>おちくほ物語|御本</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>大本営海軍部</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>1906</t>
-        </is>
-      </c>
+          <t>[書写者不明]</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>明治39</t>
+          <t>[江戸前期]</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1冊</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>26X38cm</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>写本</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>書名は表紙による</t>
+          <t>書名は題簽による|毎半帖10行|漢字平仮名交じり文|奈良絵本|桜唐草文様緞子表紙, 松葉散しに山雲の金箔見返し, 金泥下絵鳥の子紙を使用|列帖装|二重箱入り</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1798,12 +1786,12 @@
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/cf226493-0d04-2693-94c7-db99bb068777.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/8aa19100-0937-5fd9-29f1-ba41ad8d1830.json</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>cf226493-0d04-2693-94c7-db99bb068777</t>
+          <t>8aa19100-0937-5fd9-29f1-ba41ad8d1830</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1813,7 +1801,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/cf226493-0d04-2693-94c7-db99bb068777</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/8aa19100-0937-5fd9-29f1-ba41ad8d1830</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
@@ -1823,12 +1811,12 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/0b0632d275e2d4bc40eded3cadea70aa0277b180.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/124815802d3a78d8f78dd4fbb98d24d55e5c3b34.jpg</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1168834</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1182819</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
@@ -1851,7 +1839,7 @@
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/cf226493-0d04-2693-94c7-db99bb068777/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/8aa19100-0937-5fd9-29f1-ba41ad8d1830/manifest</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr"/>
@@ -1859,40 +1847,48 @@
       <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="inlineStr"/>
       <c r="AH10" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>おちくほのさうし</t>
+          <t>甲午日記 : 天保五年正月吉日</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A00:4083</t>
+          <t>A00:4613</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>オチクボ ノ ソウシ</t>
+          <t>コウゴ ニッキ : テンポウ ゴネン ショウガツ キチジツ</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>おちくほ物語|御本</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
+          <t>天保五年馬琴日記</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>滝沢 馬琴</t>
+        </is>
+      </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>[書写者不明]</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr"/>
+          <t>瀧澤馬琴 [自筆]</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>1834</t>
+        </is>
+      </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>[江戸前期]</t>
+          <t>天保5</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1908,7 +1904,7 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>書名は題簽による|毎半帖10行|漢字平仮名交じり文|奈良絵本|桜唐草文様緞子表紙, 松葉散しに山雲の金箔見返し, 金泥下絵鳥の子紙を使用|列帖装|二重箱入り</t>
+          <t>書名は扉による|巻末に「已上午年日記畢」とあり|裏表紙に「神田 瀧澤」とあり|内容: 天保五甲午年春正月-12月|墨抹, 胡粉による修正あり|巻末の識語末に「昭和五年十二月に至って脩覆を了せり」とあり|虫損あり (裏打ち補修あり)</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1924,12 +1920,12 @@
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/8aa19100-0937-5fd9-29f1-ba41ad8d1830.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/c91cb308-03bd-94f5-3c56-9d0fac9424d3.json</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>8aa19100-0937-5fd9-29f1-ba41ad8d1830</t>
+          <t>c91cb308-03bd-94f5-3c56-9d0fac9424d3</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1939,7 +1935,7 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/8aa19100-0937-5fd9-29f1-ba41ad8d1830</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/c91cb308-03bd-94f5-3c56-9d0fac9424d3</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
@@ -1949,12 +1945,12 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/124815802d3a78d8f78dd4fbb98d24d55e5c3b34.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/92f1a1f83433e8cf04243d82fb0811e6cf653db2.jpg</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1182819</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1182820</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
@@ -1977,7 +1973,7 @@
       <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/8aa19100-0937-5fd9-29f1-ba41ad8d1830/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/c91cb308-03bd-94f5-3c56-9d0fac9424d3/manifest</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr"/>
@@ -1985,48 +1981,36 @@
       <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="inlineStr"/>
       <c r="AH11" t="n">
-        <v>33</v>
+        <v>172</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>甲午日記 : 天保五年正月吉日</t>
+          <t>天神記</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>A00:4613</t>
+          <t>A00:5770</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>コウゴ ニッキ : テンポウ ゴネン ショウガツ キチジツ</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>天保五年馬琴日記</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>滝沢 馬琴</t>
-        </is>
-      </c>
+          <t>テンジンキ</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>瀧澤馬琴 [自筆]</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>1834</t>
-        </is>
-      </c>
+          <t>[書写者不明]</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>天保5</t>
+          <t>[室町末期-江戸前期]</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -2042,7 +2026,7 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>書名は扉による|巻末に「已上午年日記畢」とあり|裏表紙に「神田 瀧澤」とあり|内容: 天保五甲午年春正月-12月|墨抹, 胡粉による修正あり|巻末の識語末に「昭和五年十二月に至って脩覆を了せり」とあり|虫損あり (裏打ち補修あり)</t>
+          <t>書名は表紙( 朱書)による|毎半葉13行|奈良絵本|秋草に籬の紺紙金泥表紙, 麻の葉繋ぎに丸龍文様の銀箔見返しを使用|印記: 「渡郶文庫珍藏書印」(渡部信)</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -2058,12 +2042,12 @@
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/c91cb308-03bd-94f5-3c56-9d0fac9424d3.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/f7abc34f-6ff4-1309-4e13-cd69cce698b7.json</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>c91cb308-03bd-94f5-3c56-9d0fac9424d3</t>
+          <t>f7abc34f-6ff4-1309-4e13-cd69cce698b7</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -2073,7 +2057,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/c91cb308-03bd-94f5-3c56-9d0fac9424d3</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/f7abc34f-6ff4-1309-4e13-cd69cce698b7</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
@@ -2083,12 +2067,12 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/92f1a1f83433e8cf04243d82fb0811e6cf653db2.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/b6b3dd9c0e350f9b1b14c1a2ba0d012e6762e42c.jpg</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1182820</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1182821</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
@@ -2111,7 +2095,7 @@
       <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/c91cb308-03bd-94f5-3c56-9d0fac9424d3/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/f7abc34f-6ff4-1309-4e13-cd69cce698b7/manifest</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr"/>
@@ -2119,23 +2103,23 @@
       <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="inlineStr"/>
       <c r="AH12" t="n">
-        <v>172</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>天神記</t>
+          <t>各種殘經 : 出鄯善縣土峪溝</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>A00:5770</t>
+          <t>A00:4033</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>テンジンキ</t>
+          <t>カクシュ ザンキョウ : シュツ ゼンゼンケン トヨクコウ</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -2148,7 +2132,7 @@
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>[室町末期-江戸前期]</t>
+          <t>[書写年不明]</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2156,46 +2140,42 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>写本</t>
-        </is>
-      </c>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>書名は表紙( 朱書)による|毎半葉13行|奈良絵本|秋草に籬の紺紙金泥表紙, 麻の葉繋ぎに丸龍文様の銀箔見返しを使用|印記: 「渡郶文庫珍藏書印」(渡部信)</t>
+          <t>写本残片|書名は題簽による|題簽に「出鄯善縣土峪溝 素文珍藏」とあり|識語に「為楊枝甘露滴入紙中展巻把玩但覺異香盈字 晉卿」, 「右二紙係亜利安字 晉卿」, 「右二紙係畏吾児字 晉卿」とあり|蔵書票に「殘經佛像梵字 十五段 鄯善」, 「梵字第一號」とあり|巻子本|箱入|印記: 「臣樹枏印」, 「晉卿」, 「王仲子」, 「王樹枏印」</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>日本語</t>
+          <t>中国語</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>和古書</t>
+          <t>図書</t>
         </is>
       </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/f7abc34f-6ff4-1309-4e13-cd69cce698b7.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/704d2c7a-4882-6fc8-60d1-94c1e2799bbd.json</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>f7abc34f-6ff4-1309-4e13-cd69cce698b7</t>
+          <t>704d2c7a-4882-6fc8-60d1-94c1e2799bbd</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/f7abc34f-6ff4-1309-4e13-cd69cce698b7</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/704d2c7a-4882-6fc8-60d1-94c1e2799bbd</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
@@ -2205,12 +2185,12 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/b6b3dd9c0e350f9b1b14c1a2ba0d012e6762e42c.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/4cc89d9a25687c69b3dc3791fd39ac740de2c4a0.jpg</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1182821</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296165</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -2233,7 +2213,7 @@
       <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/f7abc34f-6ff4-1309-4e13-cd69cce698b7/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/704d2c7a-4882-6fc8-60d1-94c1e2799bbd/manifest</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr"/>
@@ -2241,27 +2221,31 @@
       <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="inlineStr"/>
       <c r="AH13" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>各種殘經 : 出鄯善縣土峪溝</t>
+          <t>和漢朗詠集 2巻 [1]</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>A00:4033</t>
+          <t>A00:4081</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>カクシュ ザンキョウ : シュツ ゼンゼンケン トヨクコウ</t>
+          <t>ワカン ロウエイシュウ</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>藤原 公任</t>
+        </is>
+      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>[書写者不明]</t>
@@ -2270,24 +2254,24 @@
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>[書写年不明]</t>
+          <t>[江戸前期]</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>写本残片|書名は題簽による|題簽に「出鄯善縣土峪溝 素文珍藏」とあり|識語に「為楊枝甘露滴入紙中展巻把玩但覺異香盈字 晉卿」, 「右二紙係亜利安字 晉卿」, 「右二紙係畏吾児字 晉卿」とあり|蔵書票に「殘經佛像梵字 十五段 鄯善」, 「梵字第一號」とあり|巻子本|箱入|印記: 「臣樹枏印」, 「晉卿」, 「王仲子」, 「王樹枏印」</t>
+          <t>写本|書名は目首及び題簽による|外箱の書名: 御本|責任表示は『日本古典籍総合目録データベース』による|巻上: 春, 夏, 秋, 冬. 巻下: 雜|題簽による巻冊次表示: 上, 下|毎半帖8行|漢字平仮名交じり文|鳳凰菱繋ぎ文様緞子表紙, 松葉散しに山雲の金箔見返し, 金泥下絵鳥の子紙を使用|列帖装|二重箱入り</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>中国語</t>
+          <t>日本語</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -2298,12 +2282,12 @@
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/704d2c7a-4882-6fc8-60d1-94c1e2799bbd.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/ba79db36-23e8-1a8a-1ad9-a5809c1109be.json</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>704d2c7a-4882-6fc8-60d1-94c1e2799bbd</t>
+          <t>ba79db36-23e8-1a8a-1ad9-a5809c1109be</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -2313,7 +2297,7 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/704d2c7a-4882-6fc8-60d1-94c1e2799bbd</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/ba79db36-23e8-1a8a-1ad9-a5809c1109be</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
@@ -2323,12 +2307,12 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/4cc89d9a25687c69b3dc3791fd39ac740de2c4a0.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/0dbc6905fbe6d7441026c6ec7f4092a564cd7606.jpg</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296165</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296166</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -2351,7 +2335,7 @@
       <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/704d2c7a-4882-6fc8-60d1-94c1e2799bbd/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/ba79db36-23e8-1a8a-1ad9-a5809c1109be/manifest</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr"/>
@@ -2359,13 +2343,13 @@
       <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="inlineStr"/>
       <c r="AH14" t="n">
-        <v>22</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>和漢朗詠集 2巻 [1]</t>
+          <t>和漢朗詠集 2巻 [2]</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2420,12 +2404,12 @@
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/ba79db36-23e8-1a8a-1ad9-a5809c1109be.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/a241b0e6-90d9-46db-1fe8-bf35f1e616c5.json</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>ba79db36-23e8-1a8a-1ad9-a5809c1109be</t>
+          <t>a241b0e6-90d9-46db-1fe8-bf35f1e616c5</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -2435,7 +2419,7 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/ba79db36-23e8-1a8a-1ad9-a5809c1109be</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/a241b0e6-90d9-46db-1fe8-bf35f1e616c5</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
@@ -2445,12 +2429,12 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/0dbc6905fbe6d7441026c6ec7f4092a564cd7606.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/f46b1242e2b77ba4f0d99feac20562f5cd3a0ee2.jpg</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296166</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296167</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
@@ -2473,7 +2457,7 @@
       <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/ba79db36-23e8-1a8a-1ad9-a5809c1109be/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/a241b0e6-90d9-46db-1fe8-bf35f1e616c5/manifest</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr"/>
@@ -2481,29 +2465,29 @@
       <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="inlineStr"/>
       <c r="AH15" t="n">
-        <v>54</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>和漢朗詠集 2巻 [2]</t>
+          <t>つれつれ草</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>A00:4081</t>
+          <t>A00:4082</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ワカン ロウエイシュウ</t>
+          <t>ツレズレグサ</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>藤原 公任</t>
+          <t>吉田 兼好</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2519,14 +2503,14 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>写本|書名は目首及び題簽による|外箱の書名: 御本|責任表示は『日本古典籍総合目録データベース』による|巻上: 春, 夏, 秋, 冬. 巻下: 雜|題簽による巻冊次表示: 上, 下|毎半帖8行|漢字平仮名交じり文|鳳凰菱繋ぎ文様緞子表紙, 松葉散しに山雲の金箔見返し, 金泥下絵鳥の子紙を使用|列帖装|二重箱入り</t>
+          <t>写本|書名は題簽による|書名の繰返し部分は踊り字|外箱の書名: 御本|責任表示は『日本古典籍総合目録データベース』による|毎半帖10行|漢字平仮名交じり文|花草窠文様緞子表紙, 松葉散しに山雲の金箔見返し, 金泥下絵鳥の子紙を使用|列帖装|二重箱入り</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2542,12 +2526,12 @@
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/a241b0e6-90d9-46db-1fe8-bf35f1e616c5.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/d19a62f6-4729-0ee3-3ea7-08f573851a48.json</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>a241b0e6-90d9-46db-1fe8-bf35f1e616c5</t>
+          <t>d19a62f6-4729-0ee3-3ea7-08f573851a48</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -2557,7 +2541,7 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/a241b0e6-90d9-46db-1fe8-bf35f1e616c5</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/d19a62f6-4729-0ee3-3ea7-08f573851a48</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
@@ -2567,12 +2551,12 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/f46b1242e2b77ba4f0d99feac20562f5cd3a0ee2.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/7966b7312c84644ee577a0390937964b1989586d.jpg</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296167</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296168</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
@@ -2595,7 +2579,7 @@
       <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/a241b0e6-90d9-46db-1fe8-bf35f1e616c5/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/d19a62f6-4729-0ee3-3ea7-08f573851a48/manifest</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr"/>
@@ -2603,29 +2587,29 @@
       <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="inlineStr"/>
       <c r="AH16" t="n">
-        <v>48</v>
+        <v>142</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>つれつれ草</t>
+          <t>日本廿四孝 6巻 [1]</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>A00:4082</t>
+          <t>A00:4084</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ツレズレグサ</t>
+          <t>ヤマト ニジュウシコウ</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>吉田 兼好</t>
+          <t>浅井 了意</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2641,14 +2625,14 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>写本|書名は題簽による|書名の繰返し部分は踊り字|外箱の書名: 御本|責任表示は『日本古典籍総合目録データベース』による|毎半帖10行|漢字平仮名交じり文|花草窠文様緞子表紙, 松葉散しに山雲の金箔見返し, 金泥下絵鳥の子紙を使用|列帖装|二重箱入り</t>
+          <t>写本|書名は目首及び題簽による|内箱の書名: 大和廿四孝|外箱の書名: 御本|責任表示は『日本古典籍総合目録データベース』による|1: 第1-4. 2: 第5-8. 3: 第9-12. 4: 第13-16. 5: 第17-20. 6: 第21-24|毎半帖10行|漢字平仮名交じり文|奈良絵本|梅唐草文様緞子表紙, 松葉散しに山雲の金箔見返し, 金泥下絵鳥の子紙を使用|列帖装|竪本|二重箱入り|糸切れあり</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2664,12 +2648,12 @@
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/d19a62f6-4729-0ee3-3ea7-08f573851a48.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/bf17bb0e-6d63-718e-218b-614134ee011d.json</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>d19a62f6-4729-0ee3-3ea7-08f573851a48</t>
+          <t>bf17bb0e-6d63-718e-218b-614134ee011d</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -2679,7 +2663,7 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/d19a62f6-4729-0ee3-3ea7-08f573851a48</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/bf17bb0e-6d63-718e-218b-614134ee011d</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
@@ -2689,12 +2673,12 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/7966b7312c84644ee577a0390937964b1989586d.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/2c48d85abc93bce026f680cc699c748fb0a877e2.jpg</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296168</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296169</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
@@ -2717,7 +2701,7 @@
       <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/d19a62f6-4729-0ee3-3ea7-08f573851a48/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/bf17bb0e-6d63-718e-218b-614134ee011d/manifest</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr"/>
@@ -2725,13 +2709,13 @@
       <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="inlineStr"/>
       <c r="AH17" t="n">
-        <v>142</v>
+        <v>47</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>日本廿四孝 6巻 [1]</t>
+          <t>日本廿四孝 6巻 [2]</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2786,12 +2770,12 @@
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/bf17bb0e-6d63-718e-218b-614134ee011d.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/c2996e14-8070-09ae-328a-159e60d17016.json</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>bf17bb0e-6d63-718e-218b-614134ee011d</t>
+          <t>c2996e14-8070-09ae-328a-159e60d17016</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -2801,7 +2785,7 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/bf17bb0e-6d63-718e-218b-614134ee011d</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/c2996e14-8070-09ae-328a-159e60d17016</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
@@ -2811,12 +2795,12 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/2c48d85abc93bce026f680cc699c748fb0a877e2.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/27ba12aa7661321f36193a30b8d8ffb8b32e574c.jpg</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296169</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296170</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
@@ -2839,7 +2823,7 @@
       <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/bf17bb0e-6d63-718e-218b-614134ee011d/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/c2996e14-8070-09ae-328a-159e60d17016/manifest</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr"/>
@@ -2847,13 +2831,13 @@
       <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="inlineStr"/>
       <c r="AH18" t="n">
-        <v>47</v>
+        <v>103</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>日本廿四孝 6巻 [2]</t>
+          <t>日本廿四孝 6巻 [3]</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2908,12 +2892,12 @@
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/c2996e14-8070-09ae-328a-159e60d17016.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/8bf2f649-5d15-2afc-2f36-84e0ac2f513e.json</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>c2996e14-8070-09ae-328a-159e60d17016</t>
+          <t>8bf2f649-5d15-2afc-2f36-84e0ac2f513e</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -2923,7 +2907,7 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/c2996e14-8070-09ae-328a-159e60d17016</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/8bf2f649-5d15-2afc-2f36-84e0ac2f513e</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
@@ -2933,12 +2917,12 @@
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/27ba12aa7661321f36193a30b8d8ffb8b32e574c.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/5841d5cb8d9895d0b483a2f842afc32f67e1719b.jpg</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296170</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296171</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
@@ -2961,7 +2945,7 @@
       <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/c2996e14-8070-09ae-328a-159e60d17016/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/8bf2f649-5d15-2afc-2f36-84e0ac2f513e/manifest</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr"/>
@@ -2969,13 +2953,13 @@
       <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="inlineStr"/>
       <c r="AH19" t="n">
-        <v>103</v>
+        <v>47</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>日本廿四孝 6巻 [3]</t>
+          <t>日本廿四孝 6巻 [4]</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -3030,12 +3014,12 @@
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/8bf2f649-5d15-2afc-2f36-84e0ac2f513e.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/59c5b4a7-529d-5e9f-454f-8879e85023eb.json</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>8bf2f649-5d15-2afc-2f36-84e0ac2f513e</t>
+          <t>59c5b4a7-529d-5e9f-454f-8879e85023eb</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -3045,7 +3029,7 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/8bf2f649-5d15-2afc-2f36-84e0ac2f513e</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/59c5b4a7-529d-5e9f-454f-8879e85023eb</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
@@ -3055,12 +3039,12 @@
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/5841d5cb8d9895d0b483a2f842afc32f67e1719b.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/e4d2c0aa6489eb2a071834a4a14714fecb372bce.jpg</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296171</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296172</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
@@ -3083,7 +3067,7 @@
       <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/8bf2f649-5d15-2afc-2f36-84e0ac2f513e/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/59c5b4a7-529d-5e9f-454f-8879e85023eb/manifest</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr"/>
@@ -3091,13 +3075,13 @@
       <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="inlineStr"/>
       <c r="AH20" t="n">
-        <v>47</v>
+        <v>76</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>日本廿四孝 6巻 [4]</t>
+          <t>日本廿四孝 6巻 [5]</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -3152,12 +3136,12 @@
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/59c5b4a7-529d-5e9f-454f-8879e85023eb.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/ff7eb5a9-8bd0-64c0-3cbf-03a54ac07e65.json</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>59c5b4a7-529d-5e9f-454f-8879e85023eb</t>
+          <t>ff7eb5a9-8bd0-64c0-3cbf-03a54ac07e65</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -3167,7 +3151,7 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/59c5b4a7-529d-5e9f-454f-8879e85023eb</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/ff7eb5a9-8bd0-64c0-3cbf-03a54ac07e65</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
@@ -3177,12 +3161,12 @@
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/e4d2c0aa6489eb2a071834a4a14714fecb372bce.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/550abdb28c4a764b0c1330b7551c32cee807416f.jpg</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296172</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296173</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
@@ -3205,7 +3189,7 @@
       <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/59c5b4a7-529d-5e9f-454f-8879e85023eb/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/ff7eb5a9-8bd0-64c0-3cbf-03a54ac07e65/manifest</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr"/>
@@ -3213,13 +3197,13 @@
       <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="inlineStr"/>
       <c r="AH21" t="n">
-        <v>76</v>
+        <v>87</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>日本廿四孝 6巻 [5]</t>
+          <t>日本廿四孝 6巻 [6]</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -3274,12 +3258,12 @@
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/ff7eb5a9-8bd0-64c0-3cbf-03a54ac07e65.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/0106be3f-16cb-3945-1c3c-419a27f26c16.json</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>ff7eb5a9-8bd0-64c0-3cbf-03a54ac07e65</t>
+          <t>0106be3f-16cb-3945-1c3c-419a27f26c16</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -3289,7 +3273,7 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/ff7eb5a9-8bd0-64c0-3cbf-03a54ac07e65</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/0106be3f-16cb-3945-1c3c-419a27f26c16</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
@@ -3299,12 +3283,12 @@
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/550abdb28c4a764b0c1330b7551c32cee807416f.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/b1c4cf868676ac5b8b2f574249475349a7a90813.jpg</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296173</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296174</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
@@ -3327,7 +3311,7 @@
       <c r="AB22" t="inlineStr"/>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/ff7eb5a9-8bd0-64c0-3cbf-03a54ac07e65/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/0106be3f-16cb-3945-1c3c-419a27f26c16/manifest</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr"/>
@@ -3335,29 +3319,29 @@
       <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="inlineStr"/>
       <c r="AH22" t="n">
-        <v>87</v>
+        <v>70</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>日本廿四孝 6巻 [6]</t>
+          <t>京ものかたり</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>A00:4084</t>
+          <t>A00:4085</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ヤマト ニジュウシコウ</t>
+          <t>キョウモノガタリ</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>浅井 了意</t>
+          <t>洛陽散人</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -3373,14 +3357,14 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
-          <t>写本|書名は目首及び題簽による|内箱の書名: 大和廿四孝|外箱の書名: 御本|責任表示は『日本古典籍総合目録データベース』による|1: 第1-4. 2: 第5-8. 3: 第9-12. 4: 第13-16. 5: 第17-20. 6: 第21-24|毎半帖10行|漢字平仮名交じり文|奈良絵本|梅唐草文様緞子表紙, 松葉散しに山雲の金箔見返し, 金泥下絵鳥の子紙を使用|列帖装|竪本|二重箱入り|糸切れあり</t>
+          <t>写本|書名は題簽による|[跋]中の書名: 見ぬ京ものかたり|外箱の書名: 御本|[跋]に「万治元年の秋夜長きひ ... いぬの年九月の末のはふのなん時 洛陽散人たれ某」とあり|内容: 儒佛の論, など|毎半帖10行|漢字平仮名交じり文|桜唐草文様緞子表紙, 松葉散しに山雲の金箔見返し, 金泥下絵鳥の子紙を使用|列帖装|二重箱入り</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -3396,12 +3380,12 @@
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/0106be3f-16cb-3945-1c3c-419a27f26c16.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/13969a60-692e-663a-3a83-97b8168b8fbe.json</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0106be3f-16cb-3945-1c3c-419a27f26c16</t>
+          <t>13969a60-692e-663a-3a83-97b8168b8fbe</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -3411,7 +3395,7 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/0106be3f-16cb-3945-1c3c-419a27f26c16</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/13969a60-692e-663a-3a83-97b8168b8fbe</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
@@ -3421,12 +3405,12 @@
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/b1c4cf868676ac5b8b2f574249475349a7a90813.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/b4c216cdd7c363c063be4e90de6eea21dd1da6e3.jpg</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296174</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296175</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
@@ -3449,7 +3433,7 @@
       <c r="AB23" t="inlineStr"/>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/0106be3f-16cb-3945-1c3c-419a27f26c16/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/13969a60-692e-663a-3a83-97b8168b8fbe/manifest</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr"/>
@@ -3457,52 +3441,52 @@
       <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="inlineStr"/>
       <c r="AH23" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>京ものかたり</t>
+          <t>北遊漫録 3巻再1巻 [1]</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>A00:4085</t>
+          <t>A00:4099</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>キョウモノガタリ</t>
+          <t>ホクユウ マンロク</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>洛陽散人</t>
+          <t>久保田 米僊</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>[書写者不明]</t>
+          <t>久保田米僊 [自筆]</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
-          <t>[江戸前期]</t>
+          <t>明治21 [1888]-明治24 [1891]</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
-          <t>写本|書名は題簽による|[跋]中の書名: 見ぬ京ものかたり|外箱の書名: 御本|[跋]に「万治元年の秋夜長きひ ... いぬの年九月の末のはふのなん時 洛陽散人たれ某」とあり|内容: 儒佛の論, など|毎半帖10行|漢字平仮名交じり文|桜唐草文様緞子表紙, 松葉散しに山雲の金箔見返し, 金泥下絵鳥の子紙を使用|列帖装|二重箱入り</t>
+          <t>写本|書名は扉による|帙題簽に「久保田米僊草稿」とあり|扉に「明治廿一年はる五月」(乾), 「明治廿一年はる六月」(坤), 「明治廿一年はる六月中澣」(瑞啚), 「明治廿四年五月十九日」(再)とあり|乾末に「増補考古畫譜五巻 發兌書肆 有隣堂」とあり|おもに図版|彩色あり|双葉装|印記: 「田寛之印」, 「山脊与弥との」</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -3518,12 +3502,12 @@
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/13969a60-692e-663a-3a83-97b8168b8fbe.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/fdb2f4c7-47bb-0fc6-53e6-e8ffb5796046.json</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>13969a60-692e-663a-3a83-97b8168b8fbe</t>
+          <t>fdb2f4c7-47bb-0fc6-53e6-e8ffb5796046</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -3533,7 +3517,7 @@
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/13969a60-692e-663a-3a83-97b8168b8fbe</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/fdb2f4c7-47bb-0fc6-53e6-e8ffb5796046</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
@@ -3543,12 +3527,12 @@
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/b4c216cdd7c363c063be4e90de6eea21dd1da6e3.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/789ef89fb4fc813de5d276f3c43f982c6760d60b.jpg</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296175</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296176</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
@@ -3571,7 +3555,7 @@
       <c r="AB24" t="inlineStr"/>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/13969a60-692e-663a-3a83-97b8168b8fbe/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/fdb2f4c7-47bb-0fc6-53e6-e8ffb5796046/manifest</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr"/>
@@ -3579,13 +3563,13 @@
       <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="inlineStr"/>
       <c r="AH24" t="n">
-        <v>68</v>
+        <v>31</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>北遊漫録 3巻再1巻 [1]</t>
+          <t>北遊漫録 3巻再1巻 [2]</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3640,12 +3624,12 @@
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/fdb2f4c7-47bb-0fc6-53e6-e8ffb5796046.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/01f5e469-1d82-36bd-3e33-34c56a942a2d.json</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>fdb2f4c7-47bb-0fc6-53e6-e8ffb5796046</t>
+          <t>01f5e469-1d82-36bd-3e33-34c56a942a2d</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -3655,7 +3639,7 @@
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/fdb2f4c7-47bb-0fc6-53e6-e8ffb5796046</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/01f5e469-1d82-36bd-3e33-34c56a942a2d</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
@@ -3665,12 +3649,12 @@
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/789ef89fb4fc813de5d276f3c43f982c6760d60b.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/0e331722b5a82ea48f273a6b7465d2784dc8a44c.jpg</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296176</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296177</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
@@ -3693,7 +3677,7 @@
       <c r="AB25" t="inlineStr"/>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/fdb2f4c7-47bb-0fc6-53e6-e8ffb5796046/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/01f5e469-1d82-36bd-3e33-34c56a942a2d/manifest</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr"/>
@@ -3707,7 +3691,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>北遊漫録 3巻再1巻 [2]</t>
+          <t>北遊漫録 3巻再1巻 [3]</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3762,12 +3746,12 @@
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/01f5e469-1d82-36bd-3e33-34c56a942a2d.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/1a4a12a3-0ae7-8858-3851-f3845f60709b.json</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>01f5e469-1d82-36bd-3e33-34c56a942a2d</t>
+          <t>1a4a12a3-0ae7-8858-3851-f3845f60709b</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -3777,7 +3761,7 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/01f5e469-1d82-36bd-3e33-34c56a942a2d</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/1a4a12a3-0ae7-8858-3851-f3845f60709b</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
@@ -3787,12 +3771,12 @@
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/0e331722b5a82ea48f273a6b7465d2784dc8a44c.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/3897bac3ffa751a75c02bb59922c185ca93a9f1e.jpg</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296177</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296178</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
@@ -3815,7 +3799,7 @@
       <c r="AB26" t="inlineStr"/>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/01f5e469-1d82-36bd-3e33-34c56a942a2d/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/1a4a12a3-0ae7-8858-3851-f3845f60709b/manifest</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr"/>
@@ -3829,7 +3813,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>北遊漫録 3巻再1巻 [3]</t>
+          <t>北遊漫録 3巻再1巻 [4]</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3884,12 +3868,12 @@
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/1a4a12a3-0ae7-8858-3851-f3845f60709b.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/73cbda29-23d4-a760-5213-0395cd767491.json</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>1a4a12a3-0ae7-8858-3851-f3845f60709b</t>
+          <t>73cbda29-23d4-a760-5213-0395cd767491</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -3899,7 +3883,7 @@
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/1a4a12a3-0ae7-8858-3851-f3845f60709b</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/73cbda29-23d4-a760-5213-0395cd767491</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
@@ -3909,12 +3893,12 @@
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/3897bac3ffa751a75c02bb59922c185ca93a9f1e.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/74a9af6c2a682e260aa96f2ded5a07abfcd3098c.jpg</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296178</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296179</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
@@ -3937,7 +3921,7 @@
       <c r="AB27" t="inlineStr"/>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/1a4a12a3-0ae7-8858-3851-f3845f60709b/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/73cbda29-23d4-a760-5213-0395cd767491/manifest</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr"/>
@@ -3945,52 +3929,48 @@
       <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="inlineStr"/>
       <c r="AH27" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>北遊漫録 3巻再1巻 [4]</t>
+          <t>蘭主之書翰使節持参叅途中之図</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>A00:4099</t>
+          <t>A00:4146</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ホクユウ マンロク</t>
+          <t>ランシュ ノ ショカン シセツ ジサン トチュウ ノ ズ</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>久保田 米僊</t>
-        </is>
-      </c>
+      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>久保田米僊 [自筆]</t>
+          <t>[製作者不明]</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
-          <t>明治21 [1888]-明治24 [1891]</t>
+          <t>天保15 [1844] 識語</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
-          <t>写本|書名は扉による|帙題簽に「久保田米僊草稿」とあり|扉に「明治廿一年はる五月」(乾), 「明治廿一年はる六月」(坤), 「明治廿一年はる六月中澣」(瑞啚), 「明治廿四年五月十九日」(再)とあり|乾末に「増補考古畫譜五巻 發兌書肆 有隣堂」とあり|おもに図版|彩色あり|双葉装|印記: 「田寛之印」, 「山脊与弥との」</t>
+          <t>書名は題簽による|箱の書名: 和蘭國軍艦人物兵器等図|冒頭に「天保十五年甲辰秋七月二日和蘭國官船奉其主命来進於我﨑嶴茲掲略圖摸其全般及内面結構所備之諸兵器等」との識語あり|絵巻|彩色あり|印記: 「籌海庫」</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -4006,12 +3986,12 @@
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/73cbda29-23d4-a760-5213-0395cd767491.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/ca3ac8e1-6c03-5832-3987-70b1fa71258a.json</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>73cbda29-23d4-a760-5213-0395cd767491</t>
+          <t>ca3ac8e1-6c03-5832-3987-70b1fa71258a</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -4021,7 +4001,7 @@
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/73cbda29-23d4-a760-5213-0395cd767491</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/ca3ac8e1-6c03-5832-3987-70b1fa71258a</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
@@ -4031,12 +4011,12 @@
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/74a9af6c2a682e260aa96f2ded5a07abfcd3098c.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/32f72c2d68d9e56e4f46528e6997cbb4c330cc23.jpg</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296179</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296180</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
@@ -4059,7 +4039,7 @@
       <c r="AB28" t="inlineStr"/>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/73cbda29-23d4-a760-5213-0395cd767491/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/ca3ac8e1-6c03-5832-3987-70b1fa71258a/manifest</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr"/>
@@ -4073,17 +4053,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>蘭主之書翰使節持参叅途中之図</t>
+          <t>喎蘭軍艦プレカット並銃劍等之図</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>A00:4146</t>
+          <t>A00:4147</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ランシュ ノ ショカン シセツ ジサン トチュウ ノ ズ</t>
+          <t>オランダ グンカン プレカット ナラビニ ジュウケン トウ ノ ズ</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -4096,7 +4076,7 @@
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
-          <t>天保15 [1844] 識語</t>
+          <t>[天保弘化年間]</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -4108,7 +4088,7 @@
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
-          <t>書名は題簽による|箱の書名: 和蘭國軍艦人物兵器等図|冒頭に「天保十五年甲辰秋七月二日和蘭國官船奉其主命来進於我﨑嶴茲掲略圖摸其全般及内面結構所備之諸兵器等」との識語あり|絵巻|彩色あり|印記: 「籌海庫」</t>
+          <t>書名は題簽による|箱の書名: 和蘭國軍艦人物兵器等図|巻末に「圖説」あり|絵巻|彩色あり</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -4124,12 +4104,12 @@
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/ca3ac8e1-6c03-5832-3987-70b1fa71258a.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/8509e124-5c2f-173b-2502-4d9cd27f9f85.json</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>ca3ac8e1-6c03-5832-3987-70b1fa71258a</t>
+          <t>8509e124-5c2f-173b-2502-4d9cd27f9f85</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -4139,7 +4119,7 @@
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/ca3ac8e1-6c03-5832-3987-70b1fa71258a</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/8509e124-5c2f-173b-2502-4d9cd27f9f85</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
@@ -4149,12 +4129,12 @@
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/32f72c2d68d9e56e4f46528e6997cbb4c330cc23.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/18d2fe489472e7f697dd92568da44185793c8f4d.jpg</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296180</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296181</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
@@ -4177,7 +4157,7 @@
       <c r="AB29" t="inlineStr"/>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/ca3ac8e1-6c03-5832-3987-70b1fa71258a/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/8509e124-5c2f-173b-2502-4d9cd27f9f85/manifest</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr"/>
@@ -4185,23 +4165,23 @@
       <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="inlineStr"/>
       <c r="AH29" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>喎蘭軍艦プレカット並銃劍等之図</t>
+          <t>能面圗譜</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>A00:4147</t>
+          <t>A00:4269</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>オランダ グンカン プレカット ナラビニ ジュウケン トウ ノ ズ</t>
+          <t>ノウメン ズフ</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -4214,7 +4194,7 @@
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
-          <t>[天保弘化年間]</t>
+          <t>[江戸中期以降]</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -4226,7 +4206,7 @@
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
-          <t>書名は題簽による|箱の書名: 和蘭國軍艦人物兵器等図|巻末に「圖説」あり|絵巻|彩色あり</t>
+          <t>折本|書名は題簽(墨書)による|帙題簽の書名(墨書): 能面圖譜|絹本彩色|図42幅|本紙: 16×13cm|金切箔散し料紙, 福寿文字布目地表紙を使用</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -4242,12 +4222,12 @@
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/8509e124-5c2f-173b-2502-4d9cd27f9f85.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/8b3019c4-7584-208c-0c75-7c855ddc0b9e.json</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>8509e124-5c2f-173b-2502-4d9cd27f9f85</t>
+          <t>8b3019c4-7584-208c-0c75-7c855ddc0b9e</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -4257,7 +4237,7 @@
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/8509e124-5c2f-173b-2502-4d9cd27f9f85</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/8b3019c4-7584-208c-0c75-7c855ddc0b9e</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
@@ -4267,12 +4247,12 @@
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/18d2fe489472e7f697dd92568da44185793c8f4d.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/3109e43cd273e3e02f2a227b4f1053cc1d4558bb.jpg</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296181</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296182</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
@@ -4295,7 +4275,7 @@
       <c r="AB30" t="inlineStr"/>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/8509e124-5c2f-173b-2502-4d9cd27f9f85/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/8b3019c4-7584-208c-0c75-7c855ddc0b9e/manifest</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr"/>
@@ -4303,36 +4283,40 @@
       <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="inlineStr"/>
       <c r="AH30" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>能面圗譜</t>
+          <t>法蕐經集驗記 2巻</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>A00:4269</t>
+          <t>A00:4273</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ノウメン ズフ</t>
+          <t>ホケキョウ シュウゲンキ</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>義寂</t>
+        </is>
+      </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>[製作者不明]</t>
+          <t>[書写者不明]</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
-          <t>[江戸中期以降]</t>
+          <t>[平安時代]</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -4344,7 +4328,7 @@
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
-          <t>折本|書名は題簽(墨書)による|帙題簽の書名(墨書): 能面圖譜|絹本彩色|図42幅|本紙: 16×13cm|金切箔散し料紙, 福寿文字布目地表紙を使用</t>
+          <t>鈔本|書名は卷下の巻頭による|大尾の書名: 法蕐集驗記|後付題簽の書名: 法花經集驗記|箱の書名: 法華驗記|卷下の内題下に「并序沙門寂撰」とあり|奥書に「護持僧(花押)夲之」とあり|巻末識語に「嘉應二年庚寅二月十八日傳得之釈子有慶在判」, 「十帋半」とあり|卷上: 諷誦第1. 卷下: 轉讀第2, 書寫第3, 聽聞第4|巻子本|訓点付|卷上の巻頭を欠損|原十紙半を1軸に合綴|朱筆書き入れあり|破損, 虫損あり (裏打ち補修あり)</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -4360,12 +4344,12 @@
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/8b3019c4-7584-208c-0c75-7c855ddc0b9e.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/ec4bceb1-0ab9-74c7-0dc7-f90d0a98a66e.json</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>8b3019c4-7584-208c-0c75-7c855ddc0b9e</t>
+          <t>ec4bceb1-0ab9-74c7-0dc7-f90d0a98a66e</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -4375,7 +4359,7 @@
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/8b3019c4-7584-208c-0c75-7c855ddc0b9e</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/ec4bceb1-0ab9-74c7-0dc7-f90d0a98a66e</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
@@ -4385,12 +4369,12 @@
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/3109e43cd273e3e02f2a227b4f1053cc1d4558bb.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/d1c457097d78f2d8a4b38eebd630ef233026cc5e.jpg</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296182</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296183</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
@@ -4413,7 +4397,7 @@
       <c r="AB31" t="inlineStr"/>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/8b3019c4-7584-208c-0c75-7c855ddc0b9e/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/ec4bceb1-0ab9-74c7-0dc7-f90d0a98a66e/manifest</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr"/>
@@ -4421,40 +4405,36 @@
       <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="inlineStr"/>
       <c r="AH31" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>法蕐經集驗記 2巻</t>
+          <t>道成寺</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>A00:4273</t>
+          <t>A00:4276</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ホケキョウ シュウゲンキ</t>
+          <t>ドウジョウジ</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>義寂</t>
-        </is>
-      </c>
+      <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>[書写者不明]</t>
+          <t>[製作者不明]</t>
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr">
         <is>
-          <t>[平安時代]</t>
+          <t>天明2 [1782] 識語</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -4466,7 +4446,7 @@
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
-          <t>鈔本|書名は卷下の巻頭による|大尾の書名: 法蕐集驗記|後付題簽の書名: 法花經集驗記|箱の書名: 法華驗記|卷下の内題下に「并序沙門寂撰」とあり|奥書に「護持僧(花押)夲之」とあり|巻末識語に「嘉應二年庚寅二月十八日傳得之釈子有慶在判」, 「十帋半」とあり|卷上: 諷誦第1. 卷下: 轉讀第2, 書寫第3, 聽聞第4|巻子本|訓点付|卷上の巻頭を欠損|原十紙半を1軸に合綴|朱筆書き入れあり|破損, 虫損あり (裏打ち補修あり)</t>
+          <t>書名は識語による|巻末識語に「道成寺建立年号大長五年三月吉日以後于二百三拾年去テ延長六戊子暦八月十日鐘巻也」, 「時天明二壬寅十月 尚良書之」とあり|絵巻|紙本著色|彩色あり|本紙: 855×28cm|界高: 25.8cm|軸物|軸頭欠損あり|印記: 「尚良印」|破損あり (裏打ち補修あり)</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -4482,12 +4462,12 @@
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/ec4bceb1-0ab9-74c7-0dc7-f90d0a98a66e.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/79185d0c-7fa3-2efd-863e-93927e137a23.json</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>ec4bceb1-0ab9-74c7-0dc7-f90d0a98a66e</t>
+          <t>79185d0c-7fa3-2efd-863e-93927e137a23</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -4497,7 +4477,7 @@
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/ec4bceb1-0ab9-74c7-0dc7-f90d0a98a66e</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/79185d0c-7fa3-2efd-863e-93927e137a23</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
@@ -4507,12 +4487,12 @@
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/d1c457097d78f2d8a4b38eebd630ef233026cc5e.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/0c47939e767d716fe085cc41c86d91be28f9df1a.jpg</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296183</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296184</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
@@ -4535,7 +4515,7 @@
       <c r="AB32" t="inlineStr"/>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/ec4bceb1-0ab9-74c7-0dc7-f90d0a98a66e/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/79185d0c-7fa3-2efd-863e-93927e137a23/manifest</t>
         </is>
       </c>
       <c r="AD32" t="inlineStr"/>
@@ -4543,48 +4523,52 @@
       <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="inlineStr"/>
       <c r="AH32" t="n">
-        <v>19</v>
+        <v>34</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>道成寺</t>
+          <t>名家短冊 [1]</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>A00:4276</t>
+          <t>A00:4277</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ドウジョウジ</t>
+          <t>メイカ タンザク</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>慶運</t>
+        </is>
+      </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>[製作者不明]</t>
+          <t>慶運 [ほか自筆]</t>
         </is>
       </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
-          <t>天明2 [1782] 識語</t>
+          <t>[鎌倉時代-江戸前期]</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
-          <t>書名は識語による|巻末識語に「道成寺建立年号大長五年三月吉日以後于二百三拾年去テ延長六戊子暦八月十日鐘巻也」, 「時天明二壬寅十月 尚良書之」とあり|絵巻|紙本著色|彩色あり|本紙: 855×28cm|界高: 25.8cm|軸物|軸頭欠損あり|印記: 「尚良印」|破損あり (裏打ち補修あり)</t>
+          <t>折本|書名及び巻冊次は題簽による|2の筆者: 慶運 牡丹花, 了流, 宗長, 兼載, 宗碩, 宗牧, 一竿, 正廣, 正般, 祖田, 堯憲, 宗二, 利盛, 増春, 了向, 榮弘, 梅雪, 宗栁, 等惠, 宗訊, 宗養, 乘阿, 兼如, 壽慶, 意運, 本阿彌光悦, 松花堂昭乘, 紹巴, 玄仍, 玄仲, 玄陳, 玄的, 里村玄祥, 昌叱, 昌琢, 昌俔, 昌程, 昌隱, 昌通|3の筆者: 祐守, 祐夏, 詮平, 直國, 興國, 隆國, 武光, 祐範, 宗純, 等貴,  順, 最嶽, 策彦, 幽之, 應其, 堯然, 尊道, 尊應, 尊朝, 道永, 弘覺, 良俊, 道増, 道應, 道興, 藤之, 立承, 性舜, 義俊, 空性, 尊譽, 揚, 道澄, 興意, 道晃|4の筆者: 有三, 他阿, 教, 尊雅, 應猷, 秀順, 可ト, 圓祐, 道順, 実如, 兼俊, 公助, 應祐, 公順, 空慶, 看世, 定信, 玄桂, 道三, 道春, 永喜, 豊永, 葉由, 常弘|2: 古筆切40枚, 極札43枚|3: 古筆切36枚, 極札36枚|4: 古筆切28枚, 極札20枚|毎半面古筆切2枚|原104枚短冊を3帖に合綴|印記: 「順」, 「最嶽」|極印: 「琴山」, 「栄」(古筆了栄)|折り目破損あり</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -4600,12 +4584,12 @@
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/79185d0c-7fa3-2efd-863e-93927e137a23.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/1469b736-a0ee-61aa-1e00-7a2cfa949411.json</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>79185d0c-7fa3-2efd-863e-93927e137a23</t>
+          <t>1469b736-a0ee-61aa-1e00-7a2cfa949411</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -4615,7 +4599,7 @@
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/79185d0c-7fa3-2efd-863e-93927e137a23</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/1469b736-a0ee-61aa-1e00-7a2cfa949411</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
@@ -4625,12 +4609,12 @@
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/0c47939e767d716fe085cc41c86d91be28f9df1a.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/7693d9aa48dbd471c84817ef0239807a5e246d64.jpg</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296184</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296185</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
@@ -4653,7 +4637,7 @@
       <c r="AB33" t="inlineStr"/>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/79185d0c-7fa3-2efd-863e-93927e137a23/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/1469b736-a0ee-61aa-1e00-7a2cfa949411/manifest</t>
         </is>
       </c>
       <c r="AD33" t="inlineStr"/>
@@ -4661,13 +4645,13 @@
       <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="inlineStr"/>
       <c r="AH33" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>名家短冊 [1]</t>
+          <t>名家短冊 [2]</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4722,12 +4706,12 @@
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/1469b736-a0ee-61aa-1e00-7a2cfa949411.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/53041b9e-294f-71af-3d1a-e305956f5560.json</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>1469b736-a0ee-61aa-1e00-7a2cfa949411</t>
+          <t>53041b9e-294f-71af-3d1a-e305956f5560</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -4737,7 +4721,7 @@
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/1469b736-a0ee-61aa-1e00-7a2cfa949411</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/53041b9e-294f-71af-3d1a-e305956f5560</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
@@ -4747,12 +4731,12 @@
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/7693d9aa48dbd471c84817ef0239807a5e246d64.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/11759cf221ad40925619344bacc4027d06e015ce.jpg</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296185</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296186</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
@@ -4775,7 +4759,7 @@
       <c r="AB34" t="inlineStr"/>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/1469b736-a0ee-61aa-1e00-7a2cfa949411/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/53041b9e-294f-71af-3d1a-e305956f5560/manifest</t>
         </is>
       </c>
       <c r="AD34" t="inlineStr"/>
@@ -4783,13 +4767,13 @@
       <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="inlineStr"/>
       <c r="AH34" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>名家短冊 [2]</t>
+          <t>名家短冊 [3]</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4844,12 +4828,12 @@
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/53041b9e-294f-71af-3d1a-e305956f5560.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/3d4ceb9b-9516-779a-7ced-f893e9d93b4e.json</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>53041b9e-294f-71af-3d1a-e305956f5560</t>
+          <t>3d4ceb9b-9516-779a-7ced-f893e9d93b4e</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -4859,7 +4843,7 @@
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/53041b9e-294f-71af-3d1a-e305956f5560</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/3d4ceb9b-9516-779a-7ced-f893e9d93b4e</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
@@ -4869,12 +4853,12 @@
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/11759cf221ad40925619344bacc4027d06e015ce.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/8fd1defea23c7c93fc4d908835c1fea38040580e.jpg</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296186</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296187</t>
         </is>
       </c>
       <c r="W35" t="inlineStr">
@@ -4897,7 +4881,7 @@
       <c r="AB35" t="inlineStr"/>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/53041b9e-294f-71af-3d1a-e305956f5560/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/3d4ceb9b-9516-779a-7ced-f893e9d93b4e/manifest</t>
         </is>
       </c>
       <c r="AD35" t="inlineStr"/>
@@ -4911,46 +4895,46 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>名家短冊 [3]</t>
+          <t>御成敗式目絵鈔</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>A00:4277</t>
+          <t>A00:4737</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>メイカ タンザク</t>
+          <t>ゴセイバイ シキモク エショウ</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>慶運</t>
+          <t>岡本 竹籔</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>慶運 [ほか自筆]</t>
+          <t>岡夲竹籔 : 松川半山 [書]</t>
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr">
         <is>
-          <t>[鎌倉時代-江戸前期]</t>
+          <t>[幕末期]</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
-          <t>折本|書名及び巻冊次は題簽による|2の筆者: 慶運 牡丹花, 了流, 宗長, 兼載, 宗碩, 宗牧, 一竿, 正廣, 正般, 祖田, 堯憲, 宗二, 利盛, 増春, 了向, 榮弘, 梅雪, 宗栁, 等惠, 宗訊, 宗養, 乘阿, 兼如, 壽慶, 意運, 本阿彌光悦, 松花堂昭乘, 紹巴, 玄仍, 玄仲, 玄陳, 玄的, 里村玄祥, 昌叱, 昌琢, 昌俔, 昌程, 昌隱, 昌通|3の筆者: 祐守, 祐夏, 詮平, 直國, 興國, 隆國, 武光, 祐範, 宗純, 等貴,  順, 最嶽, 策彦, 幽之, 應其, 堯然, 尊道, 尊應, 尊朝, 道永, 弘覺, 良俊, 道増, 道應, 道興, 藤之, 立承, 性舜, 義俊, 空性, 尊譽, 揚, 道澄, 興意, 道晃|4の筆者: 有三, 他阿, 教, 尊雅, 應猷, 秀順, 可ト, 圓祐, 道順, 実如, 兼俊, 公助, 應祐, 公順, 空慶, 看世, 定信, 玄桂, 道三, 道春, 永喜, 豊永, 葉由, 常弘|2: 古筆切40枚, 極札43枚|3: 古筆切36枚, 極札36枚|4: 古筆切28枚, 極札20枚|毎半面古筆切2枚|原104枚短冊を3帖に合綴|印記: 「順」, 「最嶽」|極印: 「琴山」, 「栄」(古筆了栄)|折り目破損あり</t>
+          <t>写本|序首の書名: 御成敗式目繪鈔|版心の書名: 式目繪鈔|題簽に「板下本」とあり|巻末に「筆工 岡夲竹籔/画工 松川半山」とあり(「岡本」, 「憲道」, 「義卿」, 「翠宋堂長」との落款朱印あり)|巻末広告に「山田賞月堂先生筆 無雙用文章大成 全一冊」とあり|四周単辺有界2段5行, 内匡廓: 22.3×16.4cm, 白口無魚尾|頭書あり|付訓あり</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -4966,12 +4950,12 @@
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/3d4ceb9b-9516-779a-7ced-f893e9d93b4e.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/463ab967-60a4-9ff1-3ef2-d2dee79b5315.json</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>3d4ceb9b-9516-779a-7ced-f893e9d93b4e</t>
+          <t>463ab967-60a4-9ff1-3ef2-d2dee79b5315</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -4981,7 +4965,7 @@
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/3d4ceb9b-9516-779a-7ced-f893e9d93b4e</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/463ab967-60a4-9ff1-3ef2-d2dee79b5315</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
@@ -4991,12 +4975,12 @@
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/8fd1defea23c7c93fc4d908835c1fea38040580e.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/e0977d9ba261ea59386ce9f5104a412a5dccaf3f.jpg</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296187</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296188</t>
         </is>
       </c>
       <c r="W36" t="inlineStr">
@@ -5019,7 +5003,7 @@
       <c r="AB36" t="inlineStr"/>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/3d4ceb9b-9516-779a-7ced-f893e9d93b4e/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/463ab967-60a4-9ff1-3ef2-d2dee79b5315/manifest</t>
         </is>
       </c>
       <c r="AD36" t="inlineStr"/>
@@ -5027,40 +5011,40 @@
       <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="inlineStr"/>
       <c r="AH36" t="n">
-        <v>24</v>
+        <v>59</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>御成敗式目絵鈔</t>
+          <t>金界入壇作法</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>A00:4737</t>
+          <t>A00:5975</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ゴセイバイ シキモク エショウ</t>
+          <t>コンカイ ニュウダン サホウ</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>岡本 竹籔</t>
+          <t>良円</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>岡夲竹籔 : 松川半山 [書]</t>
+          <t>良円 [写]</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
-          <t>[幕末期]</t>
+          <t>寛元元 [1243] 奥書</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -5072,7 +5056,7 @@
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
-          <t>写本|序首の書名: 御成敗式目繪鈔|版心の書名: 式目繪鈔|題簽に「板下本」とあり|巻末に「筆工 岡夲竹籔/画工 松川半山」とあり(「岡本」, 「憲道」, 「義卿」, 「翠宋堂長」との落款朱印あり)|巻末広告に「山田賞月堂先生筆 無雙用文章大成 全一冊」とあり|四周単辺有界2段5行, 内匡廓: 22.3×16.4cm, 白口無魚尾|頭書あり|付訓あり</t>
+          <t>写本|奥書に「寛元々年五月七日以先師法印御夲於常住護国院房以他筆書冩校點了良円」とあり|送り仮名, 返点あり|淡墨界の料紙を使用(界匡廓: 23.7×2.5cm)|貼紙あり|巻子本|箱入り|破損, 虫損あり (裏打ち補修あり)</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -5088,12 +5072,12 @@
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/463ab967-60a4-9ff1-3ef2-d2dee79b5315.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/ff6e2dd7-8128-3264-2081-15ad4e41857e.json</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>463ab967-60a4-9ff1-3ef2-d2dee79b5315</t>
+          <t>ff6e2dd7-8128-3264-2081-15ad4e41857e</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
@@ -5103,7 +5087,7 @@
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/463ab967-60a4-9ff1-3ef2-d2dee79b5315</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/ff6e2dd7-8128-3264-2081-15ad4e41857e</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
@@ -5113,12 +5097,12 @@
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/e0977d9ba261ea59386ce9f5104a412a5dccaf3f.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/7e2372f45914ea75c8d903fc80f309f16238b39f.jpg</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296188</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296189</t>
         </is>
       </c>
       <c r="W37" t="inlineStr">
@@ -5141,7 +5125,7 @@
       <c r="AB37" t="inlineStr"/>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/463ab967-60a4-9ff1-3ef2-d2dee79b5315/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/ff6e2dd7-8128-3264-2081-15ad4e41857e/manifest</t>
         </is>
       </c>
       <c r="AD37" t="inlineStr"/>
@@ -5149,52 +5133,52 @@
       <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="inlineStr"/>
       <c r="AH37" t="n">
-        <v>59</v>
+        <v>39</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>金界入壇作法</t>
+          <t>玉蘂 [1]</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>A00:5975</t>
+          <t>A00:6067</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>コンカイ ニュウダン サホウ</t>
+          <t>ギョクズイ</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>良円</t>
+          <t>藤原 道家</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>良円 [写]</t>
+          <t>野宮定基 : 久世通夏 [ほか写]</t>
         </is>
       </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
-          <t>寛元元 [1243] 奥書</t>
+          <t>元禄12 [1699]-宝永3 [1706] 奥書</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
         <is>
-          <t>写本|奥書に「寛元々年五月七日以先師法印御夲於常住護国院房以他筆書冩校點了良円」とあり|送り仮名, 返点あり|淡墨界の料紙を使用(界匡廓: 23.7×2.5cm)|貼紙あり|巻子本|箱入り|破損, 虫損あり (裏打ち補修あり)</t>
+          <t>写本|書名及び巻冊次は表紙による|奥中の書名: 光明峯寺禅閤道家公記, 峯禅閤記, 峯摂政記, 峯入道摂政記|承元4年の原奥書に「右即位記一卷者光明峯寺禅閤自筆正記也以件本左令吾基春卿透以写之云々加挍正之 ... 永正七年夷則上浣 從一位(花押)」とあり|奥書に「右以或人夲自常州到来令書写之彼夲端書云此冊上下卷 ... 元禄第十二暦仲夏中旬 羽林左衞中郎将藤原定基丗一才」(承元3), 「右光明峯寺禅閤道家公承元二年三月五六月八月四年二三月九月十十一十二月記は借請或人之夲自常州邊来書写之加一挍了/于時元禄第十二端午節也 左中郎将藤原定基丗才」(承元4), 「右玉蘂建暦元年少弟左中将通清朝臣助筆僅加一挍原本文字不正後来得正夲可改之者也/元禄十三年九月十日 松堂閑士(花押)丗二才」(建暦元), 「右玉蘂峯禅閤記建暦二年自二月至九月一冊以或人夲自常州邊来命家僚令書写手自加挍合了/元禄十二年五月六日 左中郎将藤原定基丗一才」(建暦2年上), 「宝永二年十月一日書写畢/承久二春玉蘂以故常州牧權中納言光圀公夲謄写之于時俗務紛擾先請慈兄源亜相公所被写也今以彼夲手自馳禿筆 余識藤(花押)丗七才/同三年二月廿五日一挍了」(承久2年上), 「右峯摂政承久二年記命傭書謄冩之手自一挍了/元禄第十二嵗次著雍単閼蕤賓中旬 羽林軍左衞中郎将藤原定基丗一才」(承久2年下), 「嘉禎四年正月二月閏二月三月四月六月玉蘂先年假借故常州牧前中納言光圀夲無剋力速遂書写之功建暦元年建暦二年下承久二年上及此卷等先献慈兄亜相君写之今及数年申復彼夲謄写之 ... 宝永三年十二月念日 参議從三位行左近衞權中将藤原朝臣定基生年卅八才」(嘉禎4年)とあり|毎半葉11行注文双行|漢文体日記|拠徳川光圀本及び中院通躬鈔本謄写|朱筆書き入れあり|印記: 「定基」(野宮定基), 「野宮書印」|虫損あり (裏打ち補修あり)</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -5210,12 +5194,12 @@
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/ff6e2dd7-8128-3264-2081-15ad4e41857e.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/b13a7a09-88d0-62d3-44e5-379780395f17.json</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>ff6e2dd7-8128-3264-2081-15ad4e41857e</t>
+          <t>b13a7a09-88d0-62d3-44e5-379780395f17</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
@@ -5225,7 +5209,7 @@
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/ff6e2dd7-8128-3264-2081-15ad4e41857e</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/b13a7a09-88d0-62d3-44e5-379780395f17</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
@@ -5235,12 +5219,12 @@
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/7e2372f45914ea75c8d903fc80f309f16238b39f.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/f7ae1bd23dec8f323199a9add81e315f1a653d24.jpg</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296189</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296190</t>
         </is>
       </c>
       <c r="W38" t="inlineStr">
@@ -5263,7 +5247,7 @@
       <c r="AB38" t="inlineStr"/>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/ff6e2dd7-8128-3264-2081-15ad4e41857e/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/b13a7a09-88d0-62d3-44e5-379780395f17/manifest</t>
         </is>
       </c>
       <c r="AD38" t="inlineStr"/>
@@ -5271,13 +5255,13 @@
       <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="inlineStr"/>
       <c r="AH38" t="n">
-        <v>39</v>
+        <v>129</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>玉蘂 [1]</t>
+          <t>玉蘂 [2]</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -5332,12 +5316,12 @@
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/b13a7a09-88d0-62d3-44e5-379780395f17.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/20ddaef2-73cc-5ae8-949d-0bdc521924e9.json</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>b13a7a09-88d0-62d3-44e5-379780395f17</t>
+          <t>20ddaef2-73cc-5ae8-949d-0bdc521924e9</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
@@ -5347,7 +5331,7 @@
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/b13a7a09-88d0-62d3-44e5-379780395f17</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/20ddaef2-73cc-5ae8-949d-0bdc521924e9</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
@@ -5357,12 +5341,12 @@
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/f7ae1bd23dec8f323199a9add81e315f1a653d24.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/e2bfc2adbffcfb9eb459e7863108300f2722cdd2.jpg</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296190</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296191</t>
         </is>
       </c>
       <c r="W39" t="inlineStr">
@@ -5385,7 +5369,7 @@
       <c r="AB39" t="inlineStr"/>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/b13a7a09-88d0-62d3-44e5-379780395f17/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/20ddaef2-73cc-5ae8-949d-0bdc521924e9/manifest</t>
         </is>
       </c>
       <c r="AD39" t="inlineStr"/>
@@ -5393,13 +5377,13 @@
       <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="inlineStr"/>
       <c r="AH39" t="n">
-        <v>129</v>
+        <v>104</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>玉蘂 [2]</t>
+          <t>玉蘂 [3]</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -5454,12 +5438,12 @@
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/20ddaef2-73cc-5ae8-949d-0bdc521924e9.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/7f62eb7a-844c-22ea-196e-998226c991ea.json</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>20ddaef2-73cc-5ae8-949d-0bdc521924e9</t>
+          <t>7f62eb7a-844c-22ea-196e-998226c991ea</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
@@ -5469,7 +5453,7 @@
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/20ddaef2-73cc-5ae8-949d-0bdc521924e9</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/7f62eb7a-844c-22ea-196e-998226c991ea</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
@@ -5479,12 +5463,12 @@
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/e2bfc2adbffcfb9eb459e7863108300f2722cdd2.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/ac4d01393f2eb0586033bfface43acc61e64021e.jpg</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296191</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296192</t>
         </is>
       </c>
       <c r="W40" t="inlineStr">
@@ -5507,7 +5491,7 @@
       <c r="AB40" t="inlineStr"/>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/20ddaef2-73cc-5ae8-949d-0bdc521924e9/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/7f62eb7a-844c-22ea-196e-998226c991ea/manifest</t>
         </is>
       </c>
       <c r="AD40" t="inlineStr"/>
@@ -5515,13 +5499,13 @@
       <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="inlineStr"/>
       <c r="AH40" t="n">
-        <v>104</v>
+        <v>77</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>玉蘂 [3]</t>
+          <t>玉蘂 [4]</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5576,12 +5560,12 @@
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/7f62eb7a-844c-22ea-196e-998226c991ea.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/f48a78a7-0365-73cb-4e46-dd013ef92813.json</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>7f62eb7a-844c-22ea-196e-998226c991ea</t>
+          <t>f48a78a7-0365-73cb-4e46-dd013ef92813</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
@@ -5591,7 +5575,7 @@
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/7f62eb7a-844c-22ea-196e-998226c991ea</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/f48a78a7-0365-73cb-4e46-dd013ef92813</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
@@ -5601,12 +5585,12 @@
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/ac4d01393f2eb0586033bfface43acc61e64021e.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/d9d6bd695feea8f0816bee6e991e141accf01cd8.jpg</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296192</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296193</t>
         </is>
       </c>
       <c r="W41" t="inlineStr">
@@ -5629,7 +5613,7 @@
       <c r="AB41" t="inlineStr"/>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/7f62eb7a-844c-22ea-196e-998226c991ea/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/f48a78a7-0365-73cb-4e46-dd013ef92813/manifest</t>
         </is>
       </c>
       <c r="AD41" t="inlineStr"/>
@@ -5637,13 +5621,13 @@
       <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="inlineStr"/>
       <c r="AH41" t="n">
-        <v>77</v>
+        <v>138</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>玉蘂 [4]</t>
+          <t>玉蘂 [5]</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5698,12 +5682,12 @@
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/f48a78a7-0365-73cb-4e46-dd013ef92813.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/c4ba4bb2-8d3c-7e43-4e3e-e6a6d0c2260f.json</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>f48a78a7-0365-73cb-4e46-dd013ef92813</t>
+          <t>c4ba4bb2-8d3c-7e43-4e3e-e6a6d0c2260f</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
@@ -5713,7 +5697,7 @@
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/f48a78a7-0365-73cb-4e46-dd013ef92813</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/c4ba4bb2-8d3c-7e43-4e3e-e6a6d0c2260f</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
@@ -5723,12 +5707,12 @@
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/d9d6bd695feea8f0816bee6e991e141accf01cd8.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/58826021e366d49d150087ff3478b98548b97c4a.jpg</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296193</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296194</t>
         </is>
       </c>
       <c r="W42" t="inlineStr">
@@ -5751,7 +5735,7 @@
       <c r="AB42" t="inlineStr"/>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/f48a78a7-0365-73cb-4e46-dd013ef92813/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/c4ba4bb2-8d3c-7e43-4e3e-e6a6d0c2260f/manifest</t>
         </is>
       </c>
       <c r="AD42" t="inlineStr"/>
@@ -5759,13 +5743,13 @@
       <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="inlineStr"/>
       <c r="AH42" t="n">
-        <v>138</v>
+        <v>69</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>玉蘂 [5]</t>
+          <t>玉蘂 [6]</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5820,12 +5804,12 @@
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/c4ba4bb2-8d3c-7e43-4e3e-e6a6d0c2260f.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/73dc1d4b-7872-a0a3-780c-3c10d2a3758a.json</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>c4ba4bb2-8d3c-7e43-4e3e-e6a6d0c2260f</t>
+          <t>73dc1d4b-7872-a0a3-780c-3c10d2a3758a</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
@@ -5835,7 +5819,7 @@
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/c4ba4bb2-8d3c-7e43-4e3e-e6a6d0c2260f</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/73dc1d4b-7872-a0a3-780c-3c10d2a3758a</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
@@ -5845,12 +5829,12 @@
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/58826021e366d49d150087ff3478b98548b97c4a.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/6724525552ca8e3c1f42cdc0f0674a54828dc026.jpg</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296194</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296195</t>
         </is>
       </c>
       <c r="W43" t="inlineStr">
@@ -5873,7 +5857,7 @@
       <c r="AB43" t="inlineStr"/>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/c4ba4bb2-8d3c-7e43-4e3e-e6a6d0c2260f/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/73dc1d4b-7872-a0a3-780c-3c10d2a3758a/manifest</t>
         </is>
       </c>
       <c r="AD43" t="inlineStr"/>
@@ -5881,13 +5865,13 @@
       <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="inlineStr"/>
       <c r="AH43" t="n">
-        <v>69</v>
+        <v>106</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>玉蘂 [6]</t>
+          <t>玉蘂 [7]</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5942,12 +5926,12 @@
       <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/73dc1d4b-7872-a0a3-780c-3c10d2a3758a.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/e775ea12-9867-70f2-6381-112e31478f75.json</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>73dc1d4b-7872-a0a3-780c-3c10d2a3758a</t>
+          <t>e775ea12-9867-70f2-6381-112e31478f75</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
@@ -5957,7 +5941,7 @@
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/73dc1d4b-7872-a0a3-780c-3c10d2a3758a</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/e775ea12-9867-70f2-6381-112e31478f75</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
@@ -5967,12 +5951,12 @@
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/6724525552ca8e3c1f42cdc0f0674a54828dc026.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/08e58358a211a53638e77e5431d7fedb34bd5f72.jpg</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296195</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296196</t>
         </is>
       </c>
       <c r="W44" t="inlineStr">
@@ -5995,7 +5979,7 @@
       <c r="AB44" t="inlineStr"/>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/73dc1d4b-7872-a0a3-780c-3c10d2a3758a/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/e775ea12-9867-70f2-6381-112e31478f75/manifest</t>
         </is>
       </c>
       <c r="AD44" t="inlineStr"/>
@@ -6003,13 +5987,13 @@
       <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="inlineStr"/>
       <c r="AH44" t="n">
-        <v>106</v>
+        <v>146</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>玉蘂 [7]</t>
+          <t>玉蘂 [8]</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -6064,12 +6048,12 @@
       <c r="O45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/e775ea12-9867-70f2-6381-112e31478f75.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/ca2da620-345c-76fa-9d1d-e7b2c55d757f.json</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>e775ea12-9867-70f2-6381-112e31478f75</t>
+          <t>ca2da620-345c-76fa-9d1d-e7b2c55d757f</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
@@ -6079,7 +6063,7 @@
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/e775ea12-9867-70f2-6381-112e31478f75</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/ca2da620-345c-76fa-9d1d-e7b2c55d757f</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
@@ -6089,12 +6073,12 @@
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/08e58358a211a53638e77e5431d7fedb34bd5f72.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/8204e28b4e8f0e2f8abc1b939244f007093f3749.jpg</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296196</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296197</t>
         </is>
       </c>
       <c r="W45" t="inlineStr">
@@ -6117,7 +6101,7 @@
       <c r="AB45" t="inlineStr"/>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/e775ea12-9867-70f2-6381-112e31478f75/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/ca2da620-345c-76fa-9d1d-e7b2c55d757f/manifest</t>
         </is>
       </c>
       <c r="AD45" t="inlineStr"/>
@@ -6125,52 +6109,48 @@
       <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="inlineStr"/>
       <c r="AH45" t="n">
-        <v>146</v>
+        <v>63</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>玉蘂 [8]</t>
+          <t>大明星天子法 : 又名法界虚空蔵法</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>A00:6067</t>
+          <t>A00:6097</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>ギョクズイ</t>
+          <t>ダイミョウジョウテンシホウ : マタミョウ ホッカイ コクウゾウホウ</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>藤原 道家</t>
-        </is>
-      </c>
+      <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
-          <t>野宮定基 : 久世通夏 [ほか写]</t>
+          <t>[書写者不明]</t>
         </is>
       </c>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr">
         <is>
-          <t>元禄12 [1699]-宝永3 [1706] 奥書</t>
+          <t>[天文年間]</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr">
         <is>
-          <t>写本|書名及び巻冊次は表紙による|奥中の書名: 光明峯寺禅閤道家公記, 峯禅閤記, 峯摂政記, 峯入道摂政記|承元4年の原奥書に「右即位記一卷者光明峯寺禅閤自筆正記也以件本左令吾基春卿透以写之云々加挍正之 ... 永正七年夷則上浣 從一位(花押)」とあり|奥書に「右以或人夲自常州到来令書写之彼夲端書云此冊上下卷 ... 元禄第十二暦仲夏中旬 羽林左衞中郎将藤原定基丗一才」(承元3), 「右光明峯寺禅閤道家公承元二年三月五六月八月四年二三月九月十十一十二月記は借請或人之夲自常州邊来書写之加一挍了/于時元禄第十二端午節也 左中郎将藤原定基丗才」(承元4), 「右玉蘂建暦元年少弟左中将通清朝臣助筆僅加一挍原本文字不正後来得正夲可改之者也/元禄十三年九月十日 松堂閑士(花押)丗二才」(建暦元), 「右玉蘂峯禅閤記建暦二年自二月至九月一冊以或人夲自常州邊来命家僚令書写手自加挍合了/元禄十二年五月六日 左中郎将藤原定基丗一才」(建暦2年上), 「宝永二年十月一日書写畢/承久二春玉蘂以故常州牧權中納言光圀公夲謄写之于時俗務紛擾先請慈兄源亜相公所被写也今以彼夲手自馳禿筆 余識藤(花押)丗七才/同三年二月廿五日一挍了」(承久2年上), 「右峯摂政承久二年記命傭書謄冩之手自一挍了/元禄第十二嵗次著雍単閼蕤賓中旬 羽林軍左衞中郎将藤原定基丗一才」(承久2年下), 「嘉禎四年正月二月閏二月三月四月六月玉蘂先年假借故常州牧前中納言光圀夲無剋力速遂書写之功建暦元年建暦二年下承久二年上及此卷等先献慈兄亜相君写之今及数年申復彼夲謄写之 ... 宝永三年十二月念日 参議從三位行左近衞權中将藤原朝臣定基生年卅八才」(嘉禎4年)とあり|毎半葉11行注文双行|漢文体日記|拠徳川光圀本及び中院通躬鈔本謄写|朱筆書き入れあり|印記: 「定基」(野宮定基), 「野宮書印」|虫損あり (裏打ち補修あり)</t>
+          <t>写本|巻末の書名: 明星天子法|表紙の書名: 大明皇天子水|大尾に「明星天子法次苐 一交了」とあり|本奥書に「承久三年五月十三日/爲興法利生徃生極樂書冩之/金剛佛子觀照之」とあり|書袋に「天文古筆」, 「天明七未ノ年」とあり|毎半葉8行|押界を施した楮紙打紙を使用|粘葉装|虫損あり</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -6186,12 +6166,12 @@
       <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/ca2da620-345c-76fa-9d1d-e7b2c55d757f.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/a1905fc7-4727-0750-41d7-f0ca1df53f47.json</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>ca2da620-345c-76fa-9d1d-e7b2c55d757f</t>
+          <t>a1905fc7-4727-0750-41d7-f0ca1df53f47</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
@@ -6201,7 +6181,7 @@
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/ca2da620-345c-76fa-9d1d-e7b2c55d757f</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/a1905fc7-4727-0750-41d7-f0ca1df53f47</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
@@ -6211,12 +6191,12 @@
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/8204e28b4e8f0e2f8abc1b939244f007093f3749.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/b2590ef4e55f582d8059a5e072e1d6dad33bf996.jpg</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296197</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296198</t>
         </is>
       </c>
       <c r="W46" t="inlineStr">
@@ -6239,7 +6219,7 @@
       <c r="AB46" t="inlineStr"/>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/ca2da620-345c-76fa-9d1d-e7b2c55d757f/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/a1905fc7-4727-0750-41d7-f0ca1df53f47/manifest</t>
         </is>
       </c>
       <c r="AD46" t="inlineStr"/>
@@ -6247,36 +6227,36 @@
       <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="inlineStr"/>
       <c r="AH46" t="n">
-        <v>63</v>
+        <v>9</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>大明星天子法 : 又名法界虚空蔵法</t>
+          <t>大嘗會悠紀主基鮮味之繪</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>A00:6097</t>
+          <t>A00:6108</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ダイミョウジョウテンシホウ : マタミョウ ホッカイ コクウゾウホウ</t>
+          <t>ダイジョウエ ユキ スキ センミ ノ ズ</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
-          <t>[書写者不明]</t>
+          <t>[佐伯]</t>
         </is>
       </c>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr">
         <is>
-          <t>[天文年間]</t>
+          <t>明和元 [1764] 識語</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -6288,7 +6268,7 @@
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr">
         <is>
-          <t>写本|巻末の書名: 明星天子法|表紙の書名: 大明皇天子水|大尾に「明星天子法次苐 一交了」とあり|本奥書に「承久三年五月十三日/爲興法利生徃生極樂書冩之/金剛佛子觀照之」とあり|書袋に「天文古筆」, 「天明七未ノ年」とあり|毎半葉8行|押界を施した楮紙打紙を使用|粘葉装|虫損あり</t>
+          <t>絵巻|書名は識語による|書袋の書名: 悠紀主基鮮味之啚|表紙裏に「元文悠紀主基鮮味之圖 寛延同」とあり|巻末の識語に「右大嘗會悠紀主基鮮味之繪借請御厨子所預紀宗直朝臣令佐伯職房摸冩之畢 明和元年孟冬左少将藤原(花押)」とあり|絵4幅: 梅作枝, 糸作枩, 萩作枝, 萩作枝|紙本著色|彩色あり|帙入り|印記: 「野宮藏書」</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -6304,12 +6284,12 @@
       <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/a1905fc7-4727-0750-41d7-f0ca1df53f47.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/d00e906c-5404-4fc1-44c9-1566cf7f7012.json</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>a1905fc7-4727-0750-41d7-f0ca1df53f47</t>
+          <t>d00e906c-5404-4fc1-44c9-1566cf7f7012</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
@@ -6319,7 +6299,7 @@
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/a1905fc7-4727-0750-41d7-f0ca1df53f47</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/d00e906c-5404-4fc1-44c9-1566cf7f7012</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
@@ -6329,12 +6309,12 @@
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/b2590ef4e55f582d8059a5e072e1d6dad33bf996.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/51e8aa982b380211852796b36819e6c6c6bf1583.jpg</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296198</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296199</t>
         </is>
       </c>
       <c r="W47" t="inlineStr">
@@ -6357,7 +6337,7 @@
       <c r="AB47" t="inlineStr"/>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/a1905fc7-4727-0750-41d7-f0ca1df53f47/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/d00e906c-5404-4fc1-44c9-1566cf7f7012/manifest</t>
         </is>
       </c>
       <c r="AD47" t="inlineStr"/>
@@ -6365,36 +6345,36 @@
       <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="inlineStr"/>
       <c r="AH47" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>大嘗會悠紀主基鮮味之繪</t>
+          <t>真言宗脈啚 : 栂尾夲</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>A00:6108</t>
+          <t>A00:6129</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>ダイジョウエ ユキ スキ センミ ノ ズ</t>
+          <t>シンゴンシュウ ミャクズ : トガノオボン</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>[佐伯]</t>
+          <t>覺心</t>
         </is>
       </c>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr">
         <is>
-          <t>明和元 [1764] 識語</t>
+          <t>享保9 [1724] 奥書</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -6406,7 +6386,7 @@
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr">
         <is>
-          <t>絵巻|書名は識語による|書袋の書名: 悠紀主基鮮味之啚|表紙裏に「元文悠紀主基鮮味之圖 寛延同」とあり|巻末の識語に「右大嘗會悠紀主基鮮味之繪借請御厨子所預紀宗直朝臣令佐伯職房摸冩之畢 明和元年孟冬左少将藤原(花押)」とあり|絵4幅: 梅作枝, 糸作枩, 萩作枝, 萩作枝|紙本著色|彩色あり|帙入り|印記: 「野宮藏書」</t>
+          <t>写本|書名は題簽による|帙題簽の書名: 真言宗血脈圗|奥書に「正徳二年之春請自性院僧正開栂尾山宮御封之經藏求淂于古聖教若干部是其一也 沙門道空」, 「享保九年甲辰夏寓于洛西御阜草菴以五智山之本冩之訖 南紀護国寺沙門覺心/同年六月晦日以栂尾法鼓臺古本挍合之了」, 「昭和八年四月念三日閲覧砌訂正誤字記入落罫云尒 中野達慧識」とあり|朱筆書き入れあり|印記: 「和學講談所」, 「温故堂文庫」(塙家), 「松平家藏書印」|虫損あり</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -6422,12 +6402,12 @@
       <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/d00e906c-5404-4fc1-44c9-1566cf7f7012.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/e6a30e98-5da6-7e0d-7a92-5b26c887309f.json</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>d00e906c-5404-4fc1-44c9-1566cf7f7012</t>
+          <t>e6a30e98-5da6-7e0d-7a92-5b26c887309f</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
@@ -6437,7 +6417,7 @@
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/d00e906c-5404-4fc1-44c9-1566cf7f7012</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/e6a30e98-5da6-7e0d-7a92-5b26c887309f</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
@@ -6447,12 +6427,12 @@
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/51e8aa982b380211852796b36819e6c6c6bf1583.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/10842787f14673fb3729595dd908dde4c4dd6ad8.jpg</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296199</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296200</t>
         </is>
       </c>
       <c r="W48" t="inlineStr">
@@ -6475,7 +6455,7 @@
       <c r="AB48" t="inlineStr"/>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/d00e906c-5404-4fc1-44c9-1566cf7f7012/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/e6a30e98-5da6-7e0d-7a92-5b26c887309f/manifest</t>
         </is>
       </c>
       <c r="AD48" t="inlineStr"/>
@@ -6483,36 +6463,40 @@
       <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="inlineStr"/>
       <c r="AH48" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>真言宗脈啚 : 栂尾夲</t>
+          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [1]</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>A00:6129</t>
+          <t>A00:6257</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>シンゴンシュウ ミャクズ : トガノオボン</t>
+          <t>レキダイ ザンケツ ニッキ</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>黒川 春村</t>
+        </is>
+      </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>覺心</t>
+          <t>[書写者不明]</t>
         </is>
       </c>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr">
         <is>
-          <t>享保9 [1724] 奥書</t>
+          <t>[安政5 (1858)]</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -6524,7 +6508,7 @@
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
-          <t>写本|書名は題簽による|帙題簽の書名: 真言宗血脈圗|奥書に「正徳二年之春請自性院僧正開栂尾山宮御封之經藏求淂于古聖教若干部是其一也 沙門道空」, 「享保九年甲辰夏寓于洛西御阜草菴以五智山之本冩之訖 南紀護国寺沙門覺心/同年六月晦日以栂尾法鼓臺古本挍合之了」, 「昭和八年四月念三日閲覧砌訂正誤字記入落罫云尒 中野達慧識」とあり|朱筆書き入れあり|印記: 「和學講談所」, 「温故堂文庫」(塙家), 「松平家藏書印」|虫損あり</t>
+          <t>写本|責任表示及び書写年は『日本古典籍総合目録データベース』による|内容: 6: 光明院御記, 後光嚴院御記, 後小松院宸記, 天聴集. 28: 参議藤定長卿記 : 稱山丞記. 37: 定高卿記, 晴御会部類記, 家光卿御記, 權中納言平範輔卿記. 38: 左大史小槻季継記, 後堀川安貞二年放生會(実基公記), 石清水八幡宮, 弁官拝賀次第. 39: 大外記師光記, 資季卿記, 荒凉記, 忠高卿記. 40: 冷泉公相公記, 勝延法眼記 : 東寺大行事, 後中記 : 小路中納言資頼卿記葉室. 41: 中光記, 師兼記, 陽龍記. 42: 大宮司長則記, 口筆 : 實經, 顕朝卿記, 鴨御幸記. 43: 寳治二年記, 深心院關白記, 藤公親記, 照念院関白兼平公記. 44: 頼親記, 亀山殿行幸記 : 雅言卿記, 兼基公記. 45: 大嘗會御禊節下次第, 建治三年丁丑日記 : 三善康有, 建治四年正月廿一日 : 徳大寺大相國公孝記, 冬定卿記, 左大史小槻兼文記|内容: 46: 經任卿記, 前豊前守藤憲説記, 實兼公記. 47: 継塵記抄出. 48: 管見記, 公衡公記, 大外記師顕記, 大外記中原師淳記. 49: 真光院禪助僧正記, 吉田内府卿記. 50: 定清記, 叅議雅俊卿記, 太政大臣(公守公)御上表雜事, 仙洞御灌頂日記, 正安二年八月十一日於仙洞被始行熾盛光法, 正安三年御譲位記. 51: 實躬卿記. 52: 公茂公記, 冬平公記, 隆長卿記. 53: 忠教公記, 官記, 正三位長基卿記, 北面秀長記, 大外記中原師右記. 54: 文保元年, 日野中納言資朝卿記, 洞院大納言公敏卿記. 55: 隆蔭卿記, 文保三年記, 尹大納言師賢卿記, 革命記, 立倚子記, 萬里小路中納言藤藤房卿記|内容: 56: 資名卿記, 公秀公記, 一條家記装束抄出, 頼定卿記. 63: 松亞記, 日野大納言時光卿記, 後八條内府實継公記. 74: 成恩寺関白記. 78: 山科家礼記. 82: 諒闇記 : 後成恩寺殿, 宗典僧正記, 綱光公記, 贈従二位宗賢卿記, 義政公記. 84: 長禄二年戊寅正月, 見聞雜記. 87: 言國卿記. 88: 長興宿祢記, 元長卿記, 兼顕卿記, 小槻晴冨記|28末の原奥書に「右山丞記依 仰挍合書冩/享和二年四月 日撿挍保己一」とあり|50「正安二年八月十一日於仙洞被始行熾盛光法」末の原奥書に「文化十五年春二月以南山法曼院藏夲書冩之 撿挍保己一」とあり|横刷毛目表紙を使用|朱点, 朱引, 朱墨筆書き入れあり|付箋あり|蔵書印主信濃須坂藩主堀直格の命によって編集された古記録|他の原本は関東大震災により焼失|極札に「桂壽」(6), 「尚信」(53)との極書, 「武清」(44, 53), 「永海」(51), 「了伴」(52), 「了甫」(74), 「定時」(84, 88)との極印あり|印記: 「花廼家文庫」, 「墨阪十一代主寫藏記」(堀直格(1806-1880)), 「東京大學法理文學部書庫所藏」, 「閲覧室用 FOR USE IN THE READING ROOM」|虫損あり</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -6540,12 +6524,12 @@
       <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/e6a30e98-5da6-7e0d-7a92-5b26c887309f.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/c32632af-9dc0-504a-5437-15a055d52628.json</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>e6a30e98-5da6-7e0d-7a92-5b26c887309f</t>
+          <t>c32632af-9dc0-504a-5437-15a055d52628</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
@@ -6555,7 +6539,7 @@
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/e6a30e98-5da6-7e0d-7a92-5b26c887309f</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/c32632af-9dc0-504a-5437-15a055d52628</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
@@ -6565,12 +6549,12 @@
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/10842787f14673fb3729595dd908dde4c4dd6ad8.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/2230dfedd3d91cc8b1c5532de33a8f8559be8357.jpg</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296200</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296201</t>
         </is>
       </c>
       <c r="W49" t="inlineStr">
@@ -6593,7 +6577,7 @@
       <c r="AB49" t="inlineStr"/>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/e6a30e98-5da6-7e0d-7a92-5b26c887309f/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/c32632af-9dc0-504a-5437-15a055d52628/manifest</t>
         </is>
       </c>
       <c r="AD49" t="inlineStr"/>
@@ -6601,13 +6585,13 @@
       <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="inlineStr"/>
       <c r="AH49" t="n">
-        <v>22</v>
+        <v>72</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [1]</t>
+          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [2]</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -6662,12 +6646,12 @@
       <c r="O50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/c32632af-9dc0-504a-5437-15a055d52628.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/f31d474b-60bb-5efd-a570-d8f971a97e5e.json</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>c32632af-9dc0-504a-5437-15a055d52628</t>
+          <t>f31d474b-60bb-5efd-a570-d8f971a97e5e</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
@@ -6677,7 +6661,7 @@
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/c32632af-9dc0-504a-5437-15a055d52628</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/f31d474b-60bb-5efd-a570-d8f971a97e5e</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
@@ -6687,12 +6671,12 @@
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/2230dfedd3d91cc8b1c5532de33a8f8559be8357.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/378909456e17de7b588873b8890cd6945bba3cc8.jpg</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296201</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296202</t>
         </is>
       </c>
       <c r="W50" t="inlineStr">
@@ -6715,7 +6699,7 @@
       <c r="AB50" t="inlineStr"/>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/c32632af-9dc0-504a-5437-15a055d52628/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/f31d474b-60bb-5efd-a570-d8f971a97e5e/manifest</t>
         </is>
       </c>
       <c r="AD50" t="inlineStr"/>
@@ -6723,13 +6707,13 @@
       <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="inlineStr"/>
       <c r="AH50" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [2]</t>
+          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [3]</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -6784,12 +6768,12 @@
       <c r="O51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/f31d474b-60bb-5efd-a570-d8f971a97e5e.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/0ddf4bea-7e5d-145a-1812-20986271091f.json</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>f31d474b-60bb-5efd-a570-d8f971a97e5e</t>
+          <t>0ddf4bea-7e5d-145a-1812-20986271091f</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
@@ -6799,7 +6783,7 @@
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/f31d474b-60bb-5efd-a570-d8f971a97e5e</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/0ddf4bea-7e5d-145a-1812-20986271091f</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
@@ -6809,12 +6793,12 @@
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/378909456e17de7b588873b8890cd6945bba3cc8.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/f1d109214b4c636205f357c37df4079371b1c32f.jpg</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296202</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296203</t>
         </is>
       </c>
       <c r="W51" t="inlineStr">
@@ -6837,7 +6821,7 @@
       <c r="AB51" t="inlineStr"/>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/f31d474b-60bb-5efd-a570-d8f971a97e5e/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/0ddf4bea-7e5d-145a-1812-20986271091f/manifest</t>
         </is>
       </c>
       <c r="AD51" t="inlineStr"/>
@@ -6845,13 +6829,13 @@
       <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="inlineStr"/>
       <c r="AH51" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [3]</t>
+          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [4]</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -6906,12 +6890,12 @@
       <c r="O52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/0ddf4bea-7e5d-145a-1812-20986271091f.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/5bf3d0ca-0a42-80a4-6959-af4f28d23fa3.json</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>0ddf4bea-7e5d-145a-1812-20986271091f</t>
+          <t>5bf3d0ca-0a42-80a4-6959-af4f28d23fa3</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
@@ -6921,7 +6905,7 @@
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/0ddf4bea-7e5d-145a-1812-20986271091f</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/5bf3d0ca-0a42-80a4-6959-af4f28d23fa3</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
@@ -6931,12 +6915,12 @@
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/f1d109214b4c636205f357c37df4079371b1c32f.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/b3dd61edd0ba78499c058ae1c9d57f1980d4b058.jpg</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296203</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296204</t>
         </is>
       </c>
       <c r="W52" t="inlineStr">
@@ -6959,7 +6943,7 @@
       <c r="AB52" t="inlineStr"/>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/0ddf4bea-7e5d-145a-1812-20986271091f/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/5bf3d0ca-0a42-80a4-6959-af4f28d23fa3/manifest</t>
         </is>
       </c>
       <c r="AD52" t="inlineStr"/>
@@ -6967,13 +6951,13 @@
       <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="inlineStr"/>
       <c r="AH52" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [4]</t>
+          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [5]</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -7028,12 +7012,12 @@
       <c r="O53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/5bf3d0ca-0a42-80a4-6959-af4f28d23fa3.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/92efd5a7-2a66-1ead-1e71-bdf9c70e12d0.json</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>5bf3d0ca-0a42-80a4-6959-af4f28d23fa3</t>
+          <t>92efd5a7-2a66-1ead-1e71-bdf9c70e12d0</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
@@ -7043,7 +7027,7 @@
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/5bf3d0ca-0a42-80a4-6959-af4f28d23fa3</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/92efd5a7-2a66-1ead-1e71-bdf9c70e12d0</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
@@ -7053,12 +7037,12 @@
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/b3dd61edd0ba78499c058ae1c9d57f1980d4b058.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/aaef2fe4c4feeefa7fd4fb27983a6dfd085d4a7b.jpg</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296204</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296205</t>
         </is>
       </c>
       <c r="W53" t="inlineStr">
@@ -7081,7 +7065,7 @@
       <c r="AB53" t="inlineStr"/>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/5bf3d0ca-0a42-80a4-6959-af4f28d23fa3/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/92efd5a7-2a66-1ead-1e71-bdf9c70e12d0/manifest</t>
         </is>
       </c>
       <c r="AD53" t="inlineStr"/>
@@ -7089,13 +7073,13 @@
       <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="inlineStr"/>
       <c r="AH53" t="n">
-        <v>52</v>
+        <v>68</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [5]</t>
+          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [6]</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -7150,12 +7134,12 @@
       <c r="O54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/92efd5a7-2a66-1ead-1e71-bdf9c70e12d0.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/70ac8e25-6d33-9123-6fb2-0339224b41cc.json</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>92efd5a7-2a66-1ead-1e71-bdf9c70e12d0</t>
+          <t>70ac8e25-6d33-9123-6fb2-0339224b41cc</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
@@ -7165,7 +7149,7 @@
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/92efd5a7-2a66-1ead-1e71-bdf9c70e12d0</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/70ac8e25-6d33-9123-6fb2-0339224b41cc</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
@@ -7175,12 +7159,12 @@
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/aaef2fe4c4feeefa7fd4fb27983a6dfd085d4a7b.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/3d36b605983eef3eb9e60d5e9f2d3016a497dd98.jpg</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296205</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296206</t>
         </is>
       </c>
       <c r="W54" t="inlineStr">
@@ -7203,7 +7187,7 @@
       <c r="AB54" t="inlineStr"/>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/92efd5a7-2a66-1ead-1e71-bdf9c70e12d0/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/70ac8e25-6d33-9123-6fb2-0339224b41cc/manifest</t>
         </is>
       </c>
       <c r="AD54" t="inlineStr"/>
@@ -7211,13 +7195,13 @@
       <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="inlineStr"/>
       <c r="AH54" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [6]</t>
+          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [7]</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -7272,12 +7256,12 @@
       <c r="O55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/70ac8e25-6d33-9123-6fb2-0339224b41cc.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/87cadcc3-3c6c-1f0e-a10f-d8c8b16b34e3.json</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>70ac8e25-6d33-9123-6fb2-0339224b41cc</t>
+          <t>87cadcc3-3c6c-1f0e-a10f-d8c8b16b34e3</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
@@ -7287,7 +7271,7 @@
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/70ac8e25-6d33-9123-6fb2-0339224b41cc</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/87cadcc3-3c6c-1f0e-a10f-d8c8b16b34e3</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
@@ -7297,12 +7281,12 @@
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/3d36b605983eef3eb9e60d5e9f2d3016a497dd98.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/60cd75676a83bcd5331212ff419346e6088f81e4.jpg</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296206</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296207</t>
         </is>
       </c>
       <c r="W55" t="inlineStr">
@@ -7325,7 +7309,7 @@
       <c r="AB55" t="inlineStr"/>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/70ac8e25-6d33-9123-6fb2-0339224b41cc/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/87cadcc3-3c6c-1f0e-a10f-d8c8b16b34e3/manifest</t>
         </is>
       </c>
       <c r="AD55" t="inlineStr"/>
@@ -7333,13 +7317,13 @@
       <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="inlineStr"/>
       <c r="AH55" t="n">
-        <v>72</v>
+        <v>67</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [7]</t>
+          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [8]</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -7394,12 +7378,12 @@
       <c r="O56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/87cadcc3-3c6c-1f0e-a10f-d8c8b16b34e3.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/d4dc2699-5a8e-7ad5-3160-80d5fae78074.json</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>87cadcc3-3c6c-1f0e-a10f-d8c8b16b34e3</t>
+          <t>d4dc2699-5a8e-7ad5-3160-80d5fae78074</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
@@ -7409,7 +7393,7 @@
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/87cadcc3-3c6c-1f0e-a10f-d8c8b16b34e3</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/d4dc2699-5a8e-7ad5-3160-80d5fae78074</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
@@ -7419,12 +7403,12 @@
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/60cd75676a83bcd5331212ff419346e6088f81e4.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/596a21f68644c95bd76b3f3600fb73bc78fb9124.jpg</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296207</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296208</t>
         </is>
       </c>
       <c r="W56" t="inlineStr">
@@ -7447,7 +7431,7 @@
       <c r="AB56" t="inlineStr"/>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/87cadcc3-3c6c-1f0e-a10f-d8c8b16b34e3/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/d4dc2699-5a8e-7ad5-3160-80d5fae78074/manifest</t>
         </is>
       </c>
       <c r="AD56" t="inlineStr"/>
@@ -7461,7 +7445,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [8]</t>
+          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [9]</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -7516,12 +7500,12 @@
       <c r="O57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/d4dc2699-5a8e-7ad5-3160-80d5fae78074.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/a5e4d339-47a5-92a8-3fb3-15464db0a1f8.json</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>d4dc2699-5a8e-7ad5-3160-80d5fae78074</t>
+          <t>a5e4d339-47a5-92a8-3fb3-15464db0a1f8</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
@@ -7531,7 +7515,7 @@
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/d4dc2699-5a8e-7ad5-3160-80d5fae78074</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/a5e4d339-47a5-92a8-3fb3-15464db0a1f8</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
@@ -7541,12 +7525,12 @@
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/596a21f68644c95bd76b3f3600fb73bc78fb9124.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/965ce572fe0c064509727c2dbba58751771f36b4.jpg</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296208</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296209</t>
         </is>
       </c>
       <c r="W57" t="inlineStr">
@@ -7569,7 +7553,7 @@
       <c r="AB57" t="inlineStr"/>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/d4dc2699-5a8e-7ad5-3160-80d5fae78074/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/a5e4d339-47a5-92a8-3fb3-15464db0a1f8/manifest</t>
         </is>
       </c>
       <c r="AD57" t="inlineStr"/>
@@ -7577,13 +7561,13 @@
       <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="inlineStr"/>
       <c r="AH57" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [9]</t>
+          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [10]</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -7638,12 +7622,12 @@
       <c r="O58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/a5e4d339-47a5-92a8-3fb3-15464db0a1f8.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/941cae96-2884-09d1-316d-978da0fc83f5.json</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>a5e4d339-47a5-92a8-3fb3-15464db0a1f8</t>
+          <t>941cae96-2884-09d1-316d-978da0fc83f5</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
@@ -7653,7 +7637,7 @@
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/a5e4d339-47a5-92a8-3fb3-15464db0a1f8</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/941cae96-2884-09d1-316d-978da0fc83f5</t>
         </is>
       </c>
       <c r="T58" t="inlineStr">
@@ -7663,12 +7647,12 @@
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/965ce572fe0c064509727c2dbba58751771f36b4.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/9b2119b5a8cb266e4d44bebff61cd8b5383a810e.jpg</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296209</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296210</t>
         </is>
       </c>
       <c r="W58" t="inlineStr">
@@ -7691,7 +7675,7 @@
       <c r="AB58" t="inlineStr"/>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/a5e4d339-47a5-92a8-3fb3-15464db0a1f8/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/941cae96-2884-09d1-316d-978da0fc83f5/manifest</t>
         </is>
       </c>
       <c r="AD58" t="inlineStr"/>
@@ -7699,13 +7683,13 @@
       <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="inlineStr"/>
       <c r="AH58" t="n">
-        <v>64</v>
+        <v>70</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [10]</t>
+          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [11]</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -7760,12 +7744,12 @@
       <c r="O59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/941cae96-2884-09d1-316d-978da0fc83f5.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/b6a83876-30df-48c8-9c3f-3a68e8429d62.json</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>941cae96-2884-09d1-316d-978da0fc83f5</t>
+          <t>b6a83876-30df-48c8-9c3f-3a68e8429d62</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
@@ -7775,7 +7759,7 @@
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/941cae96-2884-09d1-316d-978da0fc83f5</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/b6a83876-30df-48c8-9c3f-3a68e8429d62</t>
         </is>
       </c>
       <c r="T59" t="inlineStr">
@@ -7785,12 +7769,12 @@
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/9b2119b5a8cb266e4d44bebff61cd8b5383a810e.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/7f6bf7c4b28ea807212c7ead3da50d50601c8ed1.jpg</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296210</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296211</t>
         </is>
       </c>
       <c r="W59" t="inlineStr">
@@ -7813,7 +7797,7 @@
       <c r="AB59" t="inlineStr"/>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/941cae96-2884-09d1-316d-978da0fc83f5/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/b6a83876-30df-48c8-9c3f-3a68e8429d62/manifest</t>
         </is>
       </c>
       <c r="AD59" t="inlineStr"/>
@@ -7821,13 +7805,13 @@
       <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="inlineStr"/>
       <c r="AH59" t="n">
-        <v>70</v>
+        <v>64</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [11]</t>
+          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [12]</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -7882,12 +7866,12 @@
       <c r="O60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/b6a83876-30df-48c8-9c3f-3a68e8429d62.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/d199046f-6bd4-6ca0-a0bf-c29ad3c19949.json</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>b6a83876-30df-48c8-9c3f-3a68e8429d62</t>
+          <t>d199046f-6bd4-6ca0-a0bf-c29ad3c19949</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
@@ -7897,7 +7881,7 @@
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/b6a83876-30df-48c8-9c3f-3a68e8429d62</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/d199046f-6bd4-6ca0-a0bf-c29ad3c19949</t>
         </is>
       </c>
       <c r="T60" t="inlineStr">
@@ -7907,12 +7891,12 @@
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/7f6bf7c4b28ea807212c7ead3da50d50601c8ed1.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/4cbd0825007ec7d3c89014f55d3b6825a8214769.jpg</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296211</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296212</t>
         </is>
       </c>
       <c r="W60" t="inlineStr">
@@ -7935,7 +7919,7 @@
       <c r="AB60" t="inlineStr"/>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/b6a83876-30df-48c8-9c3f-3a68e8429d62/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/d199046f-6bd4-6ca0-a0bf-c29ad3c19949/manifest</t>
         </is>
       </c>
       <c r="AD60" t="inlineStr"/>
@@ -7943,13 +7927,13 @@
       <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="inlineStr"/>
       <c r="AH60" t="n">
-        <v>64</v>
+        <v>77</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [12]</t>
+          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [13]</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -8004,12 +7988,12 @@
       <c r="O61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/d199046f-6bd4-6ca0-a0bf-c29ad3c19949.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/1b5c5c7f-4892-39f9-4e5e-479a8e921be2.json</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>d199046f-6bd4-6ca0-a0bf-c29ad3c19949</t>
+          <t>1b5c5c7f-4892-39f9-4e5e-479a8e921be2</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
@@ -8019,7 +8003,7 @@
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/d199046f-6bd4-6ca0-a0bf-c29ad3c19949</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/1b5c5c7f-4892-39f9-4e5e-479a8e921be2</t>
         </is>
       </c>
       <c r="T61" t="inlineStr">
@@ -8029,12 +8013,12 @@
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/4cbd0825007ec7d3c89014f55d3b6825a8214769.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/95aeca9c3732100e9d926fc7a9cb98fba20b6444.jpg</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296212</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296213</t>
         </is>
       </c>
       <c r="W61" t="inlineStr">
@@ -8057,7 +8041,7 @@
       <c r="AB61" t="inlineStr"/>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/d199046f-6bd4-6ca0-a0bf-c29ad3c19949/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/1b5c5c7f-4892-39f9-4e5e-479a8e921be2/manifest</t>
         </is>
       </c>
       <c r="AD61" t="inlineStr"/>
@@ -8065,13 +8049,13 @@
       <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="inlineStr"/>
       <c r="AH61" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [13]</t>
+          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [14]</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -8126,12 +8110,12 @@
       <c r="O62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/1b5c5c7f-4892-39f9-4e5e-479a8e921be2.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/a83ab18c-4d05-492c-2121-ec90971ea54a.json</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>1b5c5c7f-4892-39f9-4e5e-479a8e921be2</t>
+          <t>a83ab18c-4d05-492c-2121-ec90971ea54a</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
@@ -8141,7 +8125,7 @@
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/1b5c5c7f-4892-39f9-4e5e-479a8e921be2</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/a83ab18c-4d05-492c-2121-ec90971ea54a</t>
         </is>
       </c>
       <c r="T62" t="inlineStr">
@@ -8151,12 +8135,12 @@
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/95aeca9c3732100e9d926fc7a9cb98fba20b6444.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/b0fe976afebb52b245b298aabead8423fd0d1a6f.jpg</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296213</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296214</t>
         </is>
       </c>
       <c r="W62" t="inlineStr">
@@ -8179,7 +8163,7 @@
       <c r="AB62" t="inlineStr"/>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/1b5c5c7f-4892-39f9-4e5e-479a8e921be2/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/a83ab18c-4d05-492c-2121-ec90971ea54a/manifest</t>
         </is>
       </c>
       <c r="AD62" t="inlineStr"/>
@@ -8187,13 +8171,13 @@
       <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="inlineStr"/>
       <c r="AH62" t="n">
-        <v>74</v>
+        <v>59</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [14]</t>
+          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [15]</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -8248,12 +8232,12 @@
       <c r="O63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/a83ab18c-4d05-492c-2121-ec90971ea54a.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/acf20dd5-459a-5438-8dd8-cbc11fe122bf.json</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>a83ab18c-4d05-492c-2121-ec90971ea54a</t>
+          <t>acf20dd5-459a-5438-8dd8-cbc11fe122bf</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
@@ -8263,7 +8247,7 @@
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/a83ab18c-4d05-492c-2121-ec90971ea54a</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/acf20dd5-459a-5438-8dd8-cbc11fe122bf</t>
         </is>
       </c>
       <c r="T63" t="inlineStr">
@@ -8273,12 +8257,12 @@
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/b0fe976afebb52b245b298aabead8423fd0d1a6f.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/cfeece07d99889e30589237e6d78b4933a56b7d6.jpg</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296214</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296215</t>
         </is>
       </c>
       <c r="W63" t="inlineStr">
@@ -8301,7 +8285,7 @@
       <c r="AB63" t="inlineStr"/>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/a83ab18c-4d05-492c-2121-ec90971ea54a/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/acf20dd5-459a-5438-8dd8-cbc11fe122bf/manifest</t>
         </is>
       </c>
       <c r="AD63" t="inlineStr"/>
@@ -8309,13 +8293,13 @@
       <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="inlineStr"/>
       <c r="AH63" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [15]</t>
+          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [16]</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -8370,12 +8354,12 @@
       <c r="O64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/acf20dd5-459a-5438-8dd8-cbc11fe122bf.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/31b47601-839e-83b4-6a49-7d11ed020385.json</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>acf20dd5-459a-5438-8dd8-cbc11fe122bf</t>
+          <t>31b47601-839e-83b4-6a49-7d11ed020385</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
@@ -8385,7 +8369,7 @@
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/acf20dd5-459a-5438-8dd8-cbc11fe122bf</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/31b47601-839e-83b4-6a49-7d11ed020385</t>
         </is>
       </c>
       <c r="T64" t="inlineStr">
@@ -8395,12 +8379,12 @@
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/cfeece07d99889e30589237e6d78b4933a56b7d6.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/d78a0b64be5f71b37b264b3b2eb8172d4e8a5002.jpg</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296215</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296216</t>
         </is>
       </c>
       <c r="W64" t="inlineStr">
@@ -8423,7 +8407,7 @@
       <c r="AB64" t="inlineStr"/>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/acf20dd5-459a-5438-8dd8-cbc11fe122bf/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/31b47601-839e-83b4-6a49-7d11ed020385/manifest</t>
         </is>
       </c>
       <c r="AD64" t="inlineStr"/>
@@ -8431,13 +8415,13 @@
       <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="inlineStr"/>
       <c r="AH64" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [16]</t>
+          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [17]</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -8492,12 +8476,12 @@
       <c r="O65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/31b47601-839e-83b4-6a49-7d11ed020385.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/37d790df-458b-48bf-6b67-3f4755f40f0f.json</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>31b47601-839e-83b4-6a49-7d11ed020385</t>
+          <t>37d790df-458b-48bf-6b67-3f4755f40f0f</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
@@ -8507,7 +8491,7 @@
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/31b47601-839e-83b4-6a49-7d11ed020385</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/37d790df-458b-48bf-6b67-3f4755f40f0f</t>
         </is>
       </c>
       <c r="T65" t="inlineStr">
@@ -8517,12 +8501,12 @@
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/d78a0b64be5f71b37b264b3b2eb8172d4e8a5002.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/dae05b3fca02a35e3363b381527ea7a899ca4f74.jpg</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296216</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296217</t>
         </is>
       </c>
       <c r="W65" t="inlineStr">
@@ -8545,7 +8529,7 @@
       <c r="AB65" t="inlineStr"/>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/31b47601-839e-83b4-6a49-7d11ed020385/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/37d790df-458b-48bf-6b67-3f4755f40f0f/manifest</t>
         </is>
       </c>
       <c r="AD65" t="inlineStr"/>
@@ -8553,13 +8537,13 @@
       <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="inlineStr"/>
       <c r="AH65" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [17]</t>
+          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [18]</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -8614,12 +8598,12 @@
       <c r="O66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/37d790df-458b-48bf-6b67-3f4755f40f0f.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/c69854e0-18e9-71b3-a7b1-22422a16688b.json</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>37d790df-458b-48bf-6b67-3f4755f40f0f</t>
+          <t>c69854e0-18e9-71b3-a7b1-22422a16688b</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
@@ -8629,7 +8613,7 @@
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/37d790df-458b-48bf-6b67-3f4755f40f0f</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/c69854e0-18e9-71b3-a7b1-22422a16688b</t>
         </is>
       </c>
       <c r="T66" t="inlineStr">
@@ -8639,12 +8623,12 @@
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/dae05b3fca02a35e3363b381527ea7a899ca4f74.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/584cfd5ec1bb0f374ab03f25ca3600a8ec2e67bf.jpg</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296217</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296218</t>
         </is>
       </c>
       <c r="W66" t="inlineStr">
@@ -8667,7 +8651,7 @@
       <c r="AB66" t="inlineStr"/>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/37d790df-458b-48bf-6b67-3f4755f40f0f/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/c69854e0-18e9-71b3-a7b1-22422a16688b/manifest</t>
         </is>
       </c>
       <c r="AD66" t="inlineStr"/>
@@ -8675,13 +8659,13 @@
       <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="inlineStr"/>
       <c r="AH66" t="n">
-        <v>54</v>
+        <v>77</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [18]</t>
+          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [19]</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -8736,12 +8720,12 @@
       <c r="O67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/c69854e0-18e9-71b3-a7b1-22422a16688b.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/1373f0d8-7cc0-4591-2c18-798fa20f483d.json</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>c69854e0-18e9-71b3-a7b1-22422a16688b</t>
+          <t>1373f0d8-7cc0-4591-2c18-798fa20f483d</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
@@ -8751,7 +8735,7 @@
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/c69854e0-18e9-71b3-a7b1-22422a16688b</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/1373f0d8-7cc0-4591-2c18-798fa20f483d</t>
         </is>
       </c>
       <c r="T67" t="inlineStr">
@@ -8761,12 +8745,12 @@
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/584cfd5ec1bb0f374ab03f25ca3600a8ec2e67bf.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/326ed2db044321d7b007462c9ac98badfd7f671a.jpg</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296218</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296219</t>
         </is>
       </c>
       <c r="W67" t="inlineStr">
@@ -8789,7 +8773,7 @@
       <c r="AB67" t="inlineStr"/>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/c69854e0-18e9-71b3-a7b1-22422a16688b/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/1373f0d8-7cc0-4591-2c18-798fa20f483d/manifest</t>
         </is>
       </c>
       <c r="AD67" t="inlineStr"/>
@@ -8797,13 +8781,13 @@
       <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="inlineStr"/>
       <c r="AH67" t="n">
-        <v>77</v>
+        <v>69</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [19]</t>
+          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [20]</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -8858,12 +8842,12 @@
       <c r="O68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/1373f0d8-7cc0-4591-2c18-798fa20f483d.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/d64280ea-576f-4bf3-9413-1b0bf6485e16.json</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>1373f0d8-7cc0-4591-2c18-798fa20f483d</t>
+          <t>d64280ea-576f-4bf3-9413-1b0bf6485e16</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
@@ -8873,7 +8857,7 @@
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/1373f0d8-7cc0-4591-2c18-798fa20f483d</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/d64280ea-576f-4bf3-9413-1b0bf6485e16</t>
         </is>
       </c>
       <c r="T68" t="inlineStr">
@@ -8883,12 +8867,12 @@
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/326ed2db044321d7b007462c9ac98badfd7f671a.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/c5e3a0bdc0b67f7429d47677a33485a6a498e20f.jpg</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296219</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296220</t>
         </is>
       </c>
       <c r="W68" t="inlineStr">
@@ -8911,7 +8895,7 @@
       <c r="AB68" t="inlineStr"/>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/1373f0d8-7cc0-4591-2c18-798fa20f483d/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/d64280ea-576f-4bf3-9413-1b0bf6485e16/manifest</t>
         </is>
       </c>
       <c r="AD68" t="inlineStr"/>
@@ -8919,13 +8903,13 @@
       <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="inlineStr"/>
       <c r="AH68" t="n">
-        <v>69</v>
+        <v>75</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [20]</t>
+          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [21]</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -8980,12 +8964,12 @@
       <c r="O69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/d64280ea-576f-4bf3-9413-1b0bf6485e16.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/decc377c-887e-7362-3bf7-81b1c9c58641.json</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>d64280ea-576f-4bf3-9413-1b0bf6485e16</t>
+          <t>decc377c-887e-7362-3bf7-81b1c9c58641</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
@@ -8995,7 +8979,7 @@
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/d64280ea-576f-4bf3-9413-1b0bf6485e16</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/decc377c-887e-7362-3bf7-81b1c9c58641</t>
         </is>
       </c>
       <c r="T69" t="inlineStr">
@@ -9005,12 +8989,12 @@
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/c5e3a0bdc0b67f7429d47677a33485a6a498e20f.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/cfd0eab55fb67ed7ab341ab27bc1cb892d7a575c.jpg</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296220</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296221</t>
         </is>
       </c>
       <c r="W69" t="inlineStr">
@@ -9033,7 +9017,7 @@
       <c r="AB69" t="inlineStr"/>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/d64280ea-576f-4bf3-9413-1b0bf6485e16/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/decc377c-887e-7362-3bf7-81b1c9c58641/manifest</t>
         </is>
       </c>
       <c r="AD69" t="inlineStr"/>
@@ -9041,13 +9025,13 @@
       <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="inlineStr"/>
       <c r="AH69" t="n">
-        <v>75</v>
+        <v>51</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [21]</t>
+          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [22]</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -9102,12 +9086,12 @@
       <c r="O70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/decc377c-887e-7362-3bf7-81b1c9c58641.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/b6bde9f3-3f94-81f1-4307-d86d59d90fa3.json</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>decc377c-887e-7362-3bf7-81b1c9c58641</t>
+          <t>b6bde9f3-3f94-81f1-4307-d86d59d90fa3</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
@@ -9117,7 +9101,7 @@
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/decc377c-887e-7362-3bf7-81b1c9c58641</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/b6bde9f3-3f94-81f1-4307-d86d59d90fa3</t>
         </is>
       </c>
       <c r="T70" t="inlineStr">
@@ -9127,12 +9111,12 @@
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/cfd0eab55fb67ed7ab341ab27bc1cb892d7a575c.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/eda09740787be30df4b5cefc348bc2c063c8932c.jpg</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296221</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296222</t>
         </is>
       </c>
       <c r="W70" t="inlineStr">
@@ -9155,7 +9139,7 @@
       <c r="AB70" t="inlineStr"/>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/decc377c-887e-7362-3bf7-81b1c9c58641/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/b6bde9f3-3f94-81f1-4307-d86d59d90fa3/manifest</t>
         </is>
       </c>
       <c r="AD70" t="inlineStr"/>
@@ -9163,13 +9147,13 @@
       <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="inlineStr"/>
       <c r="AH70" t="n">
-        <v>51</v>
+        <v>62</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [22]</t>
+          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [23]</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -9224,12 +9208,12 @@
       <c r="O71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/b6bde9f3-3f94-81f1-4307-d86d59d90fa3.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/8bd2b968-05d3-77b9-352f-f36fa2260d39.json</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>b6bde9f3-3f94-81f1-4307-d86d59d90fa3</t>
+          <t>8bd2b968-05d3-77b9-352f-f36fa2260d39</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
@@ -9239,7 +9223,7 @@
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/b6bde9f3-3f94-81f1-4307-d86d59d90fa3</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/8bd2b968-05d3-77b9-352f-f36fa2260d39</t>
         </is>
       </c>
       <c r="T71" t="inlineStr">
@@ -9249,12 +9233,12 @@
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/eda09740787be30df4b5cefc348bc2c063c8932c.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/30225b7ec7795f0c4d6102081bbf79b701183504.jpg</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296222</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296223</t>
         </is>
       </c>
       <c r="W71" t="inlineStr">
@@ -9277,7 +9261,7 @@
       <c r="AB71" t="inlineStr"/>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/b6bde9f3-3f94-81f1-4307-d86d59d90fa3/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/8bd2b968-05d3-77b9-352f-f36fa2260d39/manifest</t>
         </is>
       </c>
       <c r="AD71" t="inlineStr"/>
@@ -9285,13 +9269,13 @@
       <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="inlineStr"/>
       <c r="AH71" t="n">
-        <v>62</v>
+        <v>74</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [23]</t>
+          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [24]</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -9346,12 +9330,12 @@
       <c r="O72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/8bd2b968-05d3-77b9-352f-f36fa2260d39.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/c6e97538-22ed-8a51-0e3a-550b7d652860.json</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>8bd2b968-05d3-77b9-352f-f36fa2260d39</t>
+          <t>c6e97538-22ed-8a51-0e3a-550b7d652860</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
@@ -9361,7 +9345,7 @@
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/8bd2b968-05d3-77b9-352f-f36fa2260d39</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/c6e97538-22ed-8a51-0e3a-550b7d652860</t>
         </is>
       </c>
       <c r="T72" t="inlineStr">
@@ -9371,12 +9355,12 @@
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/30225b7ec7795f0c4d6102081bbf79b701183504.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/a04dfdaed6c9dc7211358c5ad96c4bc6e9312747.jpg</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296223</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296224</t>
         </is>
       </c>
       <c r="W72" t="inlineStr">
@@ -9399,7 +9383,7 @@
       <c r="AB72" t="inlineStr"/>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/8bd2b968-05d3-77b9-352f-f36fa2260d39/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/c6e97538-22ed-8a51-0e3a-550b7d652860/manifest</t>
         </is>
       </c>
       <c r="AD72" t="inlineStr"/>
@@ -9407,13 +9391,13 @@
       <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="inlineStr"/>
       <c r="AH72" t="n">
-        <v>74</v>
+        <v>62</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [24]</t>
+          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [25]</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -9468,12 +9452,12 @@
       <c r="O73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/c6e97538-22ed-8a51-0e3a-550b7d652860.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/48123112-700b-8619-731b-649449ff034b.json</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>c6e97538-22ed-8a51-0e3a-550b7d652860</t>
+          <t>48123112-700b-8619-731b-649449ff034b</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
@@ -9483,7 +9467,7 @@
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/c6e97538-22ed-8a51-0e3a-550b7d652860</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/48123112-700b-8619-731b-649449ff034b</t>
         </is>
       </c>
       <c r="T73" t="inlineStr">
@@ -9493,12 +9477,12 @@
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/a04dfdaed6c9dc7211358c5ad96c4bc6e9312747.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/4c918a15ed3dc97a18f7bc977b4dc2e8c724d774.jpg</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296224</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296225</t>
         </is>
       </c>
       <c r="W73" t="inlineStr">
@@ -9521,7 +9505,7 @@
       <c r="AB73" t="inlineStr"/>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/c6e97538-22ed-8a51-0e3a-550b7d652860/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/48123112-700b-8619-731b-649449ff034b/manifest</t>
         </is>
       </c>
       <c r="AD73" t="inlineStr"/>
@@ -9529,13 +9513,13 @@
       <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="inlineStr"/>
       <c r="AH73" t="n">
-        <v>62</v>
+        <v>78</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [25]</t>
+          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [26]</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -9590,12 +9574,12 @@
       <c r="O74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/48123112-700b-8619-731b-649449ff034b.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/9b2b928b-4eda-76c6-0dfd-03bde69c046c.json</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>48123112-700b-8619-731b-649449ff034b</t>
+          <t>9b2b928b-4eda-76c6-0dfd-03bde69c046c</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
@@ -9605,7 +9589,7 @@
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/48123112-700b-8619-731b-649449ff034b</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/9b2b928b-4eda-76c6-0dfd-03bde69c046c</t>
         </is>
       </c>
       <c r="T74" t="inlineStr">
@@ -9615,12 +9599,12 @@
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/4c918a15ed3dc97a18f7bc977b4dc2e8c724d774.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/7903cd89a232a0d9b4b243d90852d31d93c80300.jpg</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296225</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296226</t>
         </is>
       </c>
       <c r="W74" t="inlineStr">
@@ -9643,7 +9627,7 @@
       <c r="AB74" t="inlineStr"/>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/48123112-700b-8619-731b-649449ff034b/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/9b2b928b-4eda-76c6-0dfd-03bde69c046c/manifest</t>
         </is>
       </c>
       <c r="AD74" t="inlineStr"/>
@@ -9651,13 +9635,13 @@
       <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="inlineStr"/>
       <c r="AH74" t="n">
-        <v>78</v>
+        <v>66</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [26]</t>
+          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [27]</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -9712,12 +9696,12 @@
       <c r="O75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/9b2b928b-4eda-76c6-0dfd-03bde69c046c.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/ccc6c3da-1648-49f5-91fc-2faaf5400387.json</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>9b2b928b-4eda-76c6-0dfd-03bde69c046c</t>
+          <t>ccc6c3da-1648-49f5-91fc-2faaf5400387</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
@@ -9727,7 +9711,7 @@
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/9b2b928b-4eda-76c6-0dfd-03bde69c046c</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/ccc6c3da-1648-49f5-91fc-2faaf5400387</t>
         </is>
       </c>
       <c r="T75" t="inlineStr">
@@ -9737,12 +9721,12 @@
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/7903cd89a232a0d9b4b243d90852d31d93c80300.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/1e476c24ffbe9fd54b432acbf27eb918fc4162d0.jpg</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296226</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296227</t>
         </is>
       </c>
       <c r="W75" t="inlineStr">
@@ -9765,7 +9749,7 @@
       <c r="AB75" t="inlineStr"/>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/9b2b928b-4eda-76c6-0dfd-03bde69c046c/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/ccc6c3da-1648-49f5-91fc-2faaf5400387/manifest</t>
         </is>
       </c>
       <c r="AD75" t="inlineStr"/>
@@ -9773,13 +9757,13 @@
       <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="inlineStr"/>
       <c r="AH75" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [27]</t>
+          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [28]</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -9834,12 +9818,12 @@
       <c r="O76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/ccc6c3da-1648-49f5-91fc-2faaf5400387.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/9f3a126c-84bb-8f96-2916-b65ace30a616.json</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>ccc6c3da-1648-49f5-91fc-2faaf5400387</t>
+          <t>9f3a126c-84bb-8f96-2916-b65ace30a616</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
@@ -9849,7 +9833,7 @@
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/ccc6c3da-1648-49f5-91fc-2faaf5400387</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/9f3a126c-84bb-8f96-2916-b65ace30a616</t>
         </is>
       </c>
       <c r="T76" t="inlineStr">
@@ -9859,12 +9843,12 @@
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/1e476c24ffbe9fd54b432acbf27eb918fc4162d0.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/fc4844ae32ad2dd582e3570965cb142f5f370f74.jpg</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296227</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296228</t>
         </is>
       </c>
       <c r="W76" t="inlineStr">
@@ -9887,7 +9871,7 @@
       <c r="AB76" t="inlineStr"/>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/ccc6c3da-1648-49f5-91fc-2faaf5400387/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/9f3a126c-84bb-8f96-2916-b65ace30a616/manifest</t>
         </is>
       </c>
       <c r="AD76" t="inlineStr"/>
@@ -9901,7 +9885,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [28]</t>
+          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [29]</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -9956,12 +9940,12 @@
       <c r="O77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/9f3a126c-84bb-8f96-2916-b65ace30a616.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/7cdebe3a-8fb4-14b4-7ddb-3f92f3be9668.json</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>9f3a126c-84bb-8f96-2916-b65ace30a616</t>
+          <t>7cdebe3a-8fb4-14b4-7ddb-3f92f3be9668</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
@@ -9971,7 +9955,7 @@
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/9f3a126c-84bb-8f96-2916-b65ace30a616</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/7cdebe3a-8fb4-14b4-7ddb-3f92f3be9668</t>
         </is>
       </c>
       <c r="T77" t="inlineStr">
@@ -9981,12 +9965,12 @@
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/fc4844ae32ad2dd582e3570965cb142f5f370f74.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/08f5648a7b5512a896986520a6449d3620439071.jpg</t>
         </is>
       </c>
       <c r="V77" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296228</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296229</t>
         </is>
       </c>
       <c r="W77" t="inlineStr">
@@ -10009,7 +9993,7 @@
       <c r="AB77" t="inlineStr"/>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/9f3a126c-84bb-8f96-2916-b65ace30a616/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/7cdebe3a-8fb4-14b4-7ddb-3f92f3be9668/manifest</t>
         </is>
       </c>
       <c r="AD77" t="inlineStr"/>
@@ -10023,34 +10007,34 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>歴代殘闕日記 127巻目録1巻 (存29巻) [29]</t>
+          <t>普賢延命</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>A00:6257</t>
+          <t>A00:6264</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>レキダイ ザンケツ ニッキ</t>
+          <t>フゲン エンメイ</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
-          <t>黒川 春村</t>
+          <t>興然</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>[書写者不明]</t>
+          <t>長円 [写]</t>
         </is>
       </c>
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr">
         <is>
-          <t>[安政5 (1858)]</t>
+          <t>嘉禎2 [1236] 奥書</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -10062,7 +10046,7 @@
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr">
         <is>
-          <t>写本|責任表示及び書写年は『日本古典籍総合目録データベース』による|内容: 6: 光明院御記, 後光嚴院御記, 後小松院宸記, 天聴集. 28: 参議藤定長卿記 : 稱山丞記. 37: 定高卿記, 晴御会部類記, 家光卿御記, 權中納言平範輔卿記. 38: 左大史小槻季継記, 後堀川安貞二年放生會(実基公記), 石清水八幡宮, 弁官拝賀次第. 39: 大外記師光記, 資季卿記, 荒凉記, 忠高卿記. 40: 冷泉公相公記, 勝延法眼記 : 東寺大行事, 後中記 : 小路中納言資頼卿記葉室. 41: 中光記, 師兼記, 陽龍記. 42: 大宮司長則記, 口筆 : 實經, 顕朝卿記, 鴨御幸記. 43: 寳治二年記, 深心院關白記, 藤公親記, 照念院関白兼平公記. 44: 頼親記, 亀山殿行幸記 : 雅言卿記, 兼基公記. 45: 大嘗會御禊節下次第, 建治三年丁丑日記 : 三善康有, 建治四年正月廿一日 : 徳大寺大相國公孝記, 冬定卿記, 左大史小槻兼文記|内容: 46: 經任卿記, 前豊前守藤憲説記, 實兼公記. 47: 継塵記抄出. 48: 管見記, 公衡公記, 大外記師顕記, 大外記中原師淳記. 49: 真光院禪助僧正記, 吉田内府卿記. 50: 定清記, 叅議雅俊卿記, 太政大臣(公守公)御上表雜事, 仙洞御灌頂日記, 正安二年八月十一日於仙洞被始行熾盛光法, 正安三年御譲位記. 51: 實躬卿記. 52: 公茂公記, 冬平公記, 隆長卿記. 53: 忠教公記, 官記, 正三位長基卿記, 北面秀長記, 大外記中原師右記. 54: 文保元年, 日野中納言資朝卿記, 洞院大納言公敏卿記. 55: 隆蔭卿記, 文保三年記, 尹大納言師賢卿記, 革命記, 立倚子記, 萬里小路中納言藤藤房卿記|内容: 56: 資名卿記, 公秀公記, 一條家記装束抄出, 頼定卿記. 63: 松亞記, 日野大納言時光卿記, 後八條内府實継公記. 74: 成恩寺関白記. 78: 山科家礼記. 82: 諒闇記 : 後成恩寺殿, 宗典僧正記, 綱光公記, 贈従二位宗賢卿記, 義政公記. 84: 長禄二年戊寅正月, 見聞雜記. 87: 言國卿記. 88: 長興宿祢記, 元長卿記, 兼顕卿記, 小槻晴冨記|28末の原奥書に「右山丞記依 仰挍合書冩/享和二年四月 日撿挍保己一」とあり|50「正安二年八月十一日於仙洞被始行熾盛光法」末の原奥書に「文化十五年春二月以南山法曼院藏夲書冩之 撿挍保己一」とあり|横刷毛目表紙を使用|朱点, 朱引, 朱墨筆書き入れあり|付箋あり|蔵書印主信濃須坂藩主堀直格の命によって編集された古記録|他の原本は関東大震災により焼失|極札に「桂壽」(6), 「尚信」(53)との極書, 「武清」(44, 53), 「永海」(51), 「了伴」(52), 「了甫」(74), 「定時」(84, 88)との極印あり|印記: 「花廼家文庫」, 「墨阪十一代主寫藏記」(堀直格(1806-1880)), 「東京大學法理文學部書庫所藏」, 「閲覧室用 FOR USE IN THE READING ROOM」|虫損あり</t>
+          <t>写本|内題下に「師 理教」, 「嘉禎二年奥書アリ 長円書」とあり|巻末に「越前闍梨浄与口傳 興然夲」とあり|奥書に「嘉禎二年四月六月奉傳受空達御房ノ長円」とあり|裏に「正和元年壬子八月廿九日於成身院奉伝受之了」とあり|巻子本|送り仮名, 傍訓あり|虫損あり (裏打ち補修あり)</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -10078,12 +10062,12 @@
       <c r="O78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/7cdebe3a-8fb4-14b4-7ddb-3f92f3be9668.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/e57fef06-5cfd-a602-6a89-f4d7d4360e87.json</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>7cdebe3a-8fb4-14b4-7ddb-3f92f3be9668</t>
+          <t>e57fef06-5cfd-a602-6a89-f4d7d4360e87</t>
         </is>
       </c>
       <c r="R78" t="inlineStr">
@@ -10093,7 +10077,7 @@
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/7cdebe3a-8fb4-14b4-7ddb-3f92f3be9668</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/e57fef06-5cfd-a602-6a89-f4d7d4360e87</t>
         </is>
       </c>
       <c r="T78" t="inlineStr">
@@ -10103,12 +10087,12 @@
       </c>
       <c r="U78" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/08f5648a7b5512a896986520a6449d3620439071.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/eec20da7736c221a3c86321abead9d8d9429dceb.jpg</t>
         </is>
       </c>
       <c r="V78" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296229</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296230</t>
         </is>
       </c>
       <c r="W78" t="inlineStr">
@@ -10131,7 +10115,7 @@
       <c r="AB78" t="inlineStr"/>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/7cdebe3a-8fb4-14b4-7ddb-3f92f3be9668/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/e57fef06-5cfd-a602-6a89-f4d7d4360e87/manifest</t>
         </is>
       </c>
       <c r="AD78" t="inlineStr"/>
@@ -10139,40 +10123,40 @@
       <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="inlineStr"/>
       <c r="AH78" t="n">
-        <v>70</v>
+        <v>7</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>普賢延命</t>
+          <t>如法愛染王</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>A00:6264</t>
+          <t>A00:6265</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>フゲン エンメイ</t>
+          <t>ニョホウ アイゼンオウ</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>興然</t>
+          <t>仁海</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>長円 [写]</t>
+          <t>禅喜 [写]</t>
         </is>
       </c>
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr">
         <is>
-          <t>嘉禎2 [1236] 奥書</t>
+          <t>嘉暦2 [1327] 奥書</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -10184,7 +10168,7 @@
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr">
         <is>
-          <t>写本|内題下に「師 理教」, 「嘉禎二年奥書アリ 長円書」とあり|巻末に「越前闍梨浄与口傳 興然夲」とあり|奥書に「嘉禎二年四月六月奉傳受空達御房ノ長円」とあり|裏に「正和元年壬子八月廿九日於成身院奉伝受之了」とあり|巻子本|送り仮名, 傍訓あり|虫損あり (裏打ち補修あり)</t>
+          <t>写本|表紙の書名: 如法愛染|内題下に「付小野大次苐修之」とあり|本奥書に「延慶二年夘月十日於仁和寺真光院書写了 金剛佛子印法 生年卅二」とあり|奥書に「嘉暦二年正月廿二日全写了 禅喜 生年卅一」とあり|巻子本|小野流|淡墨界の料紙を使用(界匡廓: 23.8×2.2cm)|巻頭下部の貼紙に「嘉暦二年巨今五百八十二年鎌倉時代四一ノ六九七号」とあり|破損, 虫損あり (裏打ち補修あり)</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -10200,12 +10184,12 @@
       <c r="O79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/e57fef06-5cfd-a602-6a89-f4d7d4360e87.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/e321350d-483d-6e38-81a2-a637b8f798fb.json</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>e57fef06-5cfd-a602-6a89-f4d7d4360e87</t>
+          <t>e321350d-483d-6e38-81a2-a637b8f798fb</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
@@ -10215,7 +10199,7 @@
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/e57fef06-5cfd-a602-6a89-f4d7d4360e87</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/e321350d-483d-6e38-81a2-a637b8f798fb</t>
         </is>
       </c>
       <c r="T79" t="inlineStr">
@@ -10225,12 +10209,12 @@
       </c>
       <c r="U79" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/eec20da7736c221a3c86321abead9d8d9429dceb.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/355285a0ec0b1cc8f12ae2c98e5215bdc9477998.jpg</t>
         </is>
       </c>
       <c r="V79" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296230</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296231</t>
         </is>
       </c>
       <c r="W79" t="inlineStr">
@@ -10253,7 +10237,7 @@
       <c r="AB79" t="inlineStr"/>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/e57fef06-5cfd-a602-6a89-f4d7d4360e87/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/e321350d-483d-6e38-81a2-a637b8f798fb/manifest</t>
         </is>
       </c>
       <c r="AD79" t="inlineStr"/>
@@ -10267,34 +10251,34 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>如法愛染王</t>
+          <t>三摩耶戒作法 : 東寺</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>A00:6265</t>
+          <t>A00:6266</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>ニョホウ アイゼンオウ</t>
+          <t>サンマヤカイ サホウ : トウジ</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>仁海</t>
+          <t>聖快</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>禅喜 [写]</t>
+          <t>道快 [自筆]</t>
         </is>
       </c>
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr">
         <is>
-          <t>嘉暦2 [1327] 奥書</t>
+          <t>康暦元 [1379] 奥書</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -10306,7 +10290,7 @@
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr">
         <is>
-          <t>写本|表紙の書名: 如法愛染|内題下に「付小野大次苐修之」とあり|本奥書に「延慶二年夘月十日於仁和寺真光院書写了 金剛佛子印法 生年卅二」とあり|奥書に「嘉暦二年正月廿二日全写了 禅喜 生年卅一」とあり|巻子本|小野流|淡墨界の料紙を使用(界匡廓: 23.8×2.2cm)|巻頭下部の貼紙に「嘉暦二年巨今五百八十二年鎌倉時代四一ノ六九七号」とあり|破損, 虫損あり (裏打ち補修あり)</t>
+          <t>写本|書名は表紙による|本奥書に「康和元年十月廿日午時書了 深禅夲(第三轉)」, 「以小野僧正御夲理趣房書御夲也(初轉)」, 「承暦四年十一月十二日給預又書冩并傳受了 峯大阿闍梨御房事也(第二轉)」とあり|奥書に「康暦元年八月十二日於地藏院以平等坊永嚴自筆夲書冩之訖 東寺沙門道快」, 「同十四日於同院以或夲重挍合入落字注異説削謬詞尤可秘藏而已」とあり|表紙の貼紙に「康暦元年八月十二日於地藏院以平等坊永嚴自筆本書写之訖 東寺沙門道快 南北類」とある|巻子本|朱筆書き入れあり|淡墨界の料紙を使用(界匡廓: 19.5×2.0cm)|印記: 「僧正弘基」|破損, 虫損あり</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -10322,12 +10306,12 @@
       <c r="O80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/e321350d-483d-6e38-81a2-a637b8f798fb.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/2b2562eb-7577-32f6-4c99-462a84e0647c.json</t>
         </is>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>e321350d-483d-6e38-81a2-a637b8f798fb</t>
+          <t>2b2562eb-7577-32f6-4c99-462a84e0647c</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
@@ -10337,7 +10321,7 @@
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/e321350d-483d-6e38-81a2-a637b8f798fb</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/2b2562eb-7577-32f6-4c99-462a84e0647c</t>
         </is>
       </c>
       <c r="T80" t="inlineStr">
@@ -10347,12 +10331,12 @@
       </c>
       <c r="U80" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/355285a0ec0b1cc8f12ae2c98e5215bdc9477998.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/60a9be2785b442f57f54089c594f63b8df5ae1f4.jpg</t>
         </is>
       </c>
       <c r="V80" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296231</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296232</t>
         </is>
       </c>
       <c r="W80" t="inlineStr">
@@ -10375,7 +10359,7 @@
       <c r="AB80" t="inlineStr"/>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/e321350d-483d-6e38-81a2-a637b8f798fb/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/2b2562eb-7577-32f6-4c99-462a84e0647c/manifest</t>
         </is>
       </c>
       <c r="AD80" t="inlineStr"/>
@@ -10383,52 +10367,48 @@
       <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="inlineStr"/>
       <c r="AH80" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>三摩耶戒作法 : 東寺</t>
+          <t>騁懐帖 2巻 [1]</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>A00:6266</t>
+          <t>A00:6379</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>サンマヤカイ サホウ : トウジ</t>
+          <t>テイカイジョウ</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
-          <t>聖快</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>道快 [自筆]</t>
-        </is>
-      </c>
+          <t>芳賀矢一[ほか自筆] ; 松本百藏 [集]</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr">
         <is>
-          <t>康暦元 [1379] 奥書</t>
+          <t>[明治-昭和年間]</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr">
         <is>
-          <t>写本|書名は表紙による|本奥書に「康和元年十月廿日午時書了 深禅夲(第三轉)」, 「以小野僧正御夲理趣房書御夲也(初轉)」, 「承暦四年十一月十二日給預又書冩并傳受了 峯大阿闍梨御房事也(第二轉)」とあり|奥書に「康暦元年八月十二日於地藏院以平等坊永嚴自筆夲書冩之訖 東寺沙門道快」, 「同十四日於同院以或夲重挍合入落字注異説削謬詞尤可秘藏而已」とあり|表紙の貼紙に「康暦元年八月十二日於地藏院以平等坊永嚴自筆本書写之訖 東寺沙門道快 南北類」とある|巻子本|朱筆書き入れあり|淡墨界の料紙を使用(界匡廓: 19.5×2.0cm)|印記: 「僧正弘基」|破損, 虫損あり</t>
+          <t>写本|書名及び巻冊次は題簽による|跋末に「松夲生名ハ百藏東京帝國大學ノ使丁タリ職ヲ山上會議所ニ奉スルコト四十有餘年 ... 頃来マタ諸賢ノ揮毫ヲ乞上名ケテ騁懐帖トイフ ... 帖成リテ予ニ其由来ヲ記セシコトヲ求ム乃チ之ヲ録シテ以テ跋後トス 昭和二年三月 辻善之助識」とあり|折本|書画帖|彩色あり|名録2冊(大和綴)を付す|落款朱印: 「長成」(坪井九馬三), 「圭卿」(市村瓚次郎), 「簣山」(鹽谷時敏), 「維亭」(塚本靖), 「土肥慶藏」, 「忠太」(伊東忠太), 「萬」(和田万吉), 「芳溪」(呉秀三), 「前田慧雲」, 「大澤謙二」, 「南條文雄」, 「有坂氏」(有坂鉊藏), 「博」, 「石亭」(林博太郎), 「長與又郎」, 「宇野哲人」, ほかあり</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -10444,12 +10424,12 @@
       <c r="O81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/2b2562eb-7577-32f6-4c99-462a84e0647c.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/bfdc576b-6ce2-9274-914e-8cc9c52c04de.json</t>
         </is>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>2b2562eb-7577-32f6-4c99-462a84e0647c</t>
+          <t>bfdc576b-6ce2-9274-914e-8cc9c52c04de</t>
         </is>
       </c>
       <c r="R81" t="inlineStr">
@@ -10459,7 +10439,7 @@
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/2b2562eb-7577-32f6-4c99-462a84e0647c</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/bfdc576b-6ce2-9274-914e-8cc9c52c04de</t>
         </is>
       </c>
       <c r="T81" t="inlineStr">
@@ -10469,12 +10449,12 @@
       </c>
       <c r="U81" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/60a9be2785b442f57f54089c594f63b8df5ae1f4.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/4061afb959aba92577bf3357712e3556cd07cf8e.jpg</t>
         </is>
       </c>
       <c r="V81" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296232</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296233</t>
         </is>
       </c>
       <c r="W81" t="inlineStr">
@@ -10497,7 +10477,7 @@
       <c r="AB81" t="inlineStr"/>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/2b2562eb-7577-32f6-4c99-462a84e0647c/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/bfdc576b-6ce2-9274-914e-8cc9c52c04de/manifest</t>
         </is>
       </c>
       <c r="AD81" t="inlineStr"/>
@@ -10505,13 +10485,13 @@
       <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="inlineStr"/>
       <c r="AH81" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>騁懐帖 2巻 [1]</t>
+          <t>騁懐帖 2巻 [2]</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -10562,12 +10542,12 @@
       <c r="O82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/bfdc576b-6ce2-9274-914e-8cc9c52c04de.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/6a4c18fb-90e9-6d15-1234-9cadcc683544.json</t>
         </is>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>bfdc576b-6ce2-9274-914e-8cc9c52c04de</t>
+          <t>6a4c18fb-90e9-6d15-1234-9cadcc683544</t>
         </is>
       </c>
       <c r="R82" t="inlineStr">
@@ -10577,7 +10557,7 @@
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/bfdc576b-6ce2-9274-914e-8cc9c52c04de</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/6a4c18fb-90e9-6d15-1234-9cadcc683544</t>
         </is>
       </c>
       <c r="T82" t="inlineStr">
@@ -10587,12 +10567,12 @@
       </c>
       <c r="U82" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/4061afb959aba92577bf3357712e3556cd07cf8e.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/f705bcd1873bb88e3f1edef2b79dcc86dc2c417b.jpg</t>
         </is>
       </c>
       <c r="V82" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296233</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296234</t>
         </is>
       </c>
       <c r="W82" t="inlineStr">
@@ -10615,7 +10595,7 @@
       <c r="AB82" t="inlineStr"/>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/bfdc576b-6ce2-9274-914e-8cc9c52c04de/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/6a4c18fb-90e9-6d15-1234-9cadcc683544/manifest</t>
         </is>
       </c>
       <c r="AD82" t="inlineStr"/>
@@ -10623,48 +10603,48 @@
       <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="inlineStr"/>
       <c r="AH82" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>騁懐帖 2巻 [2]</t>
+          <t>清玩書巻</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>A00:6379</t>
+          <t>A00:6380</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>テイカイジョウ</t>
+          <t>セイガン ショカン</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
-          <t>芳賀矢一[ほか自筆] ; 松本百藏 [集]</t>
+          <t>石黒忠悳[ほか自筆] ; [松本百藏収集]</t>
         </is>
       </c>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr">
         <is>
-          <t>[明治-昭和年間]</t>
+          <t>[明治大正年間]</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
       <c r="L83" t="inlineStr">
         <is>
-          <t>写本|書名及び巻冊次は題簽による|跋末に「松夲生名ハ百藏東京帝國大學ノ使丁タリ職ヲ山上會議所ニ奉スルコト四十有餘年 ... 頃来マタ諸賢ノ揮毫ヲ乞上名ケテ騁懐帖トイフ ... 帖成リテ予ニ其由来ヲ記セシコトヲ求ム乃チ之ヲ録シテ以テ跋後トス 昭和二年三月 辻善之助識」とあり|折本|書画帖|彩色あり|名録2冊(大和綴)を付す|落款朱印: 「長成」(坪井九馬三), 「圭卿」(市村瓚次郎), 「簣山」(鹽谷時敏), 「維亭」(塚本靖), 「土肥慶藏」, 「忠太」(伊東忠太), 「萬」(和田万吉), 「芳溪」(呉秀三), 「前田慧雲」, 「大澤謙二」, 「南條文雄」, 「有坂氏」(有坂鉊藏), 「博」, 「石亭」(林博太郎), 「長與又郎」, 「宇野哲人」, ほかあり</t>
+          <t>写本|書名は題簽による|その他の筆者: 市村瓚次郎, 外山正一, 緒方正規, 村上専精, 佐藤進, 菊池大麓, 三宅秀, 箕作佳吉, 三上參次, 箕作元八|冒頭に井上哲の題辞「清玩」あり|巻末に萩野由之の識語あり|収集者は『理翰片影』&lt;BC06713253&gt;の跋による|巻子本|往来書簡貼付集|名録1冊(大和綴)を付す|落款朱印: 「文学博士」, 「井上喆」, 「井上哲印」(井上哲次郎), 「和葊」(萩野由之)</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -10680,12 +10660,12 @@
       <c r="O83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/6a4c18fb-90e9-6d15-1234-9cadcc683544.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/ae3b180b-9cbe-6902-48c2-f0abfdf0a27e.json</t>
         </is>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>6a4c18fb-90e9-6d15-1234-9cadcc683544</t>
+          <t>ae3b180b-9cbe-6902-48c2-f0abfdf0a27e</t>
         </is>
       </c>
       <c r="R83" t="inlineStr">
@@ -10695,7 +10675,7 @@
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/6a4c18fb-90e9-6d15-1234-9cadcc683544</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/ae3b180b-9cbe-6902-48c2-f0abfdf0a27e</t>
         </is>
       </c>
       <c r="T83" t="inlineStr">
@@ -10705,12 +10685,12 @@
       </c>
       <c r="U83" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/f705bcd1873bb88e3f1edef2b79dcc86dc2c417b.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/e799186565cb40d919d91c02eef1308118771dd3.jpg</t>
         </is>
       </c>
       <c r="V83" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296234</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296235</t>
         </is>
       </c>
       <c r="W83" t="inlineStr">
@@ -10733,7 +10713,7 @@
       <c r="AB83" t="inlineStr"/>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/6a4c18fb-90e9-6d15-1234-9cadcc683544/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/ae3b180b-9cbe-6902-48c2-f0abfdf0a27e/manifest</t>
         </is>
       </c>
       <c r="AD83" t="inlineStr"/>
@@ -10741,36 +10721,36 @@
       <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="inlineStr"/>
       <c r="AH83" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>清玩書巻</t>
+          <t>聚珍書巻</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>A00:6380</t>
+          <t>A00:6381</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>セイガン ショカン</t>
+          <t>シュウチン ショカン</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
         <is>
-          <t>石黒忠悳[ほか自筆] ; [松本百藏収集]</t>
+          <t>濱尾新 [ほか自筆] ; 松本百藏 [収集]</t>
         </is>
       </c>
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr"/>
       <c r="H84" t="inlineStr">
         <is>
-          <t>[明治大正年間]</t>
+          <t>[明治年間]</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -10782,7 +10762,7 @@
       <c r="K84" t="inlineStr"/>
       <c r="L84" t="inlineStr">
         <is>
-          <t>写本|書名は題簽による|その他の筆者: 市村瓚次郎, 外山正一, 緒方正規, 村上専精, 佐藤進, 菊池大麓, 三宅秀, 箕作佳吉, 三上參次, 箕作元八|冒頭に井上哲の題辞「清玩」あり|巻末に萩野由之の識語あり|収集者は『理翰片影』&lt;BC06713253&gt;の跋による|巻子本|往来書簡貼付集|名録1冊(大和綴)を付す|落款朱印: 「文学博士」, 「井上喆」, 「井上哲印」(井上哲次郎), 「和葊」(萩野由之)</t>
+          <t>写本|書名は題簽による|題辞に「聚珍 明治己酉夏八十三老人成斎題」とあり|巻末識語に「松本百蔵為東亰帝國大學厮養二十餘年毎掃故紙籠見有文字者輒収而弆之頃揀其署名氏者十餘紙装潢成卷皆名賢鉅公碩學鴻儒之筆也 ... 明治庚戌二月初夏 豊城陳人恒書時年七十又二」とあり|その他の筆者: 細川潤次郎, 渡邊洪基, 加藤弘之, 川田剛, 辻新次, 中村正直, 古市公威, 小中村清矩, 木村正辭, 島田重禮|巻子本|往来書簡貼付集|名録1冊(大和綴)を付す|落款朱印: 「晩香」, 「徳天」, 「星野恒印」, 「續古堂」, 「重野」, 「重埜士徳」, 「藤原安繹」</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -10798,12 +10778,12 @@
       <c r="O84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/ae3b180b-9cbe-6902-48c2-f0abfdf0a27e.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/4e78ded3-2829-990e-572b-4b5e029a69cc.json</t>
         </is>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>ae3b180b-9cbe-6902-48c2-f0abfdf0a27e</t>
+          <t>4e78ded3-2829-990e-572b-4b5e029a69cc</t>
         </is>
       </c>
       <c r="R84" t="inlineStr">
@@ -10813,7 +10793,7 @@
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/ae3b180b-9cbe-6902-48c2-f0abfdf0a27e</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/4e78ded3-2829-990e-572b-4b5e029a69cc</t>
         </is>
       </c>
       <c r="T84" t="inlineStr">
@@ -10823,12 +10803,12 @@
       </c>
       <c r="U84" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/e799186565cb40d919d91c02eef1308118771dd3.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/fe6e0e801688014b204ebe9deee8085c19831bc3.jpg</t>
         </is>
       </c>
       <c r="V84" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296235</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296236</t>
         </is>
       </c>
       <c r="W84" t="inlineStr">
@@ -10851,7 +10831,7 @@
       <c r="AB84" t="inlineStr"/>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/ae3b180b-9cbe-6902-48c2-f0abfdf0a27e/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/4e78ded3-2829-990e-572b-4b5e029a69cc/manifest</t>
         </is>
       </c>
       <c r="AD84" t="inlineStr"/>
@@ -10859,36 +10839,36 @@
       <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="inlineStr"/>
       <c r="AH84" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>聚珍書巻</t>
+          <t>理翰片影</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>A00:6381</t>
+          <t>A00:6382</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>シュウチン ショカン</t>
+          <t>リカン ヘンエイ</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
-          <t>濱尾新 [ほか自筆] ; 松本百藏 [収集]</t>
+          <t>井上毅 [ほか自筆] ; 松本百藏 [蒐集]</t>
         </is>
       </c>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr"/>
       <c r="H85" t="inlineStr">
         <is>
-          <t>[明治年間]</t>
+          <t>[明治大正年間]</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -10900,7 +10880,7 @@
       <c r="K85" t="inlineStr"/>
       <c r="L85" t="inlineStr">
         <is>
-          <t>写本|書名は題簽による|題辞に「聚珍 明治己酉夏八十三老人成斎題」とあり|巻末識語に「松本百蔵為東亰帝國大學厮養二十餘年毎掃故紙籠見有文字者輒収而弆之頃揀其署名氏者十餘紙装潢成卷皆名賢鉅公碩學鴻儒之筆也 ... 明治庚戌二月初夏 豊城陳人恒書時年七十又二」とあり|その他の筆者: 細川潤次郎, 渡邊洪基, 加藤弘之, 川田剛, 辻新次, 中村正直, 古市公威, 小中村清矩, 木村正辭, 島田重禮|巻子本|往来書簡貼付集|名録1冊(大和綴)を付す|落款朱印: 「晩香」, 「徳天」, 「星野恒印」, 「續古堂」, 「重野」, 「重埜士徳」, 「藤原安繹」</t>
+          <t>写本|書名は題簽による|敘に「松本百藏君我が東京帝國大學に縁故ある諸君の筆蹟を蒐集シ己ニ三卷をなす此卷収む事といわは故子爵井上毅先生をはじめとし神保小虎博士に至るまで十二君の消息なり ... 大正十四年春日三上参次(花押)」とあり|跋に「松本百藏奉職東京帝國大學勞使四十年夙昔不怠其所勤非尋常也大正十四年以古稀辤其軄以平生所収簡牘装潢之得四巻二帖納大學書庫 ... 大正十五年五月於東京帝國大學夲部象軒平野直文識」とあり|その他の筆者: 八代六郎, 垪和爲昌, 鶴田賢次, 長井長義, 久原躬弦, 藤澤利喜太郎, 小藤文次郎, 寺野精一, 青山胤通, 佐藤三吉, 神保小乕|巻子本|往来書簡貼付集|落款朱印: 「士可」, 「虚坣居士」, 「平野直文」</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -10916,12 +10896,12 @@
       <c r="O85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/4e78ded3-2829-990e-572b-4b5e029a69cc.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/31b15e19-44d8-6c52-9780-873a7f1a2480.json</t>
         </is>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>4e78ded3-2829-990e-572b-4b5e029a69cc</t>
+          <t>31b15e19-44d8-6c52-9780-873a7f1a2480</t>
         </is>
       </c>
       <c r="R85" t="inlineStr">
@@ -10931,7 +10911,7 @@
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/4e78ded3-2829-990e-572b-4b5e029a69cc</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/31b15e19-44d8-6c52-9780-873a7f1a2480</t>
         </is>
       </c>
       <c r="T85" t="inlineStr">
@@ -10941,12 +10921,12 @@
       </c>
       <c r="U85" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/fe6e0e801688014b204ebe9deee8085c19831bc3.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/c34f4eff76edef5a959de5048f588d40ac1cccac.jpg</t>
         </is>
       </c>
       <c r="V85" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296236</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296237</t>
         </is>
       </c>
       <c r="W85" t="inlineStr">
@@ -10969,7 +10949,7 @@
       <c r="AB85" t="inlineStr"/>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/4e78ded3-2829-990e-572b-4b5e029a69cc/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/31b15e19-44d8-6c52-9780-873a7f1a2480/manifest</t>
         </is>
       </c>
       <c r="AD85" t="inlineStr"/>
@@ -10977,29 +10957,29 @@
       <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="inlineStr"/>
       <c r="AH85" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>理翰片影</t>
+          <t>學海拾遺珠</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>A00:6382</t>
+          <t>A00:6383</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>リカン ヘンエイ</t>
+          <t>ガッカイ シュウイシュ</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
-          <t>井上毅 [ほか自筆] ; 松本百藏 [蒐集]</t>
+          <t>渡邊渡 [ほか自筆] ; 松本[百藏 集]</t>
         </is>
       </c>
       <c r="F86" t="inlineStr"/>
@@ -11018,7 +10998,7 @@
       <c r="K86" t="inlineStr"/>
       <c r="L86" t="inlineStr">
         <is>
-          <t>写本|書名は題簽による|敘に「松本百藏君我が東京帝國大學に縁故ある諸君の筆蹟を蒐集シ己ニ三卷をなす此卷収む事といわは故子爵井上毅先生をはじめとし神保小虎博士に至るまで十二君の消息なり ... 大正十四年春日三上参次(花押)」とあり|跋に「松本百藏奉職東京帝國大學勞使四十年夙昔不怠其所勤非尋常也大正十四年以古稀辤其軄以平生所収簡牘装潢之得四巻二帖納大學書庫 ... 大正十五年五月於東京帝國大學夲部象軒平野直文識」とあり|その他の筆者: 八代六郎, 垪和爲昌, 鶴田賢次, 長井長義, 久原躬弦, 藤澤利喜太郎, 小藤文次郎, 寺野精一, 青山胤通, 佐藤三吉, 神保小乕|巻子本|往来書簡貼付集|落款朱印: 「士可」, 「虚坣居士」, 「平野直文」</t>
+          <t>写本|書名は題簽による|題辞に「學海拾遺珠 大正十二年初夏 讀律書屋主人題」とあり|巻末識語に「東京帝國大學の地小丘有り丘上に會議所有り總長教授等會食聚議の處と為に松本君其の役たると久し親しく碩學大家に接し之を敬するを知る留意して敗紙中に諸家の手跡を索め嵗月を累収て十数家に及へは輙ち裝潢して卷を成す今や第三卷成り文を予に求む松本君孤影孑然會議所に起臥す伴侶は唯名家手簡と手栽の盆柎有るのみ ... 大正十二年二月十九日 隨軒學人」とあり|その他の筆者: 和田垣謙三, 川瀬善太郎, 高松豊吉, 田中義成, 永井久一郎, 中村恭平, 山川健次郎, 松井直吉, 松村任三, 古在由直, 寺尾寿, 櫻井錠二, 清水彦五郎|巻子本|往来書簡貼付集|名録1冊(大和綴)を付す|落款朱印: 「讀經堂主人號随軒」, 「服部宇之吉印記」, 「直文」(平野直文)</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -11034,12 +11014,12 @@
       <c r="O86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/31b15e19-44d8-6c52-9780-873a7f1a2480.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/9639e5f3-92bd-7423-1bf1-08c4dc087bdf.json</t>
         </is>
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>31b15e19-44d8-6c52-9780-873a7f1a2480</t>
+          <t>9639e5f3-92bd-7423-1bf1-08c4dc087bdf</t>
         </is>
       </c>
       <c r="R86" t="inlineStr">
@@ -11049,7 +11029,7 @@
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/31b15e19-44d8-6c52-9780-873a7f1a2480</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/9639e5f3-92bd-7423-1bf1-08c4dc087bdf</t>
         </is>
       </c>
       <c r="T86" t="inlineStr">
@@ -11059,12 +11039,12 @@
       </c>
       <c r="U86" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/c34f4eff76edef5a959de5048f588d40ac1cccac.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/b210fc9854d945b959acd96b0e4fa57d3578ea07.jpg</t>
         </is>
       </c>
       <c r="V86" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296237</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296238</t>
         </is>
       </c>
       <c r="W86" t="inlineStr">
@@ -11087,7 +11067,7 @@
       <c r="AB86" t="inlineStr"/>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/31b15e19-44d8-6c52-9780-873a7f1a2480/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/9639e5f3-92bd-7423-1bf1-08c4dc087bdf/manifest</t>
         </is>
       </c>
       <c r="AD86" t="inlineStr"/>
@@ -11095,36 +11075,40 @@
       <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="inlineStr"/>
       <c r="AH86" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>學海拾遺珠</t>
+          <t>御成敗式目</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>A00:6383</t>
+          <t>A00:6456</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>ガッカイ シュウイシュ</t>
+          <t>ゴセイバイ シキモク</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr">
         <is>
-          <t>渡邊渡 [ほか自筆] ; 松本[百藏 集]</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr"/>
+          <t>平泰時 [ほか定]</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>[書写者不明]</t>
+        </is>
+      </c>
       <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr">
         <is>
-          <t>[明治大正年間]</t>
+          <t>康永2 [1343] 奥書</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -11136,7 +11120,7 @@
       <c r="K87" t="inlineStr"/>
       <c r="L87" t="inlineStr">
         <is>
-          <t>写本|書名は題簽による|題辞に「學海拾遺珠 大正十二年初夏 讀律書屋主人題」とあり|巻末識語に「東京帝國大學の地小丘有り丘上に會議所有り總長教授等會食聚議の處と為に松本君其の役たると久し親しく碩學大家に接し之を敬するを知る留意して敗紙中に諸家の手跡を索め嵗月を累収て十数家に及へは輙ち裝潢して卷を成す今や第三卷成り文を予に求む松本君孤影孑然會議所に起臥す伴侶は唯名家手簡と手栽の盆柎有るのみ ... 大正十二年二月十九日 隨軒學人」とあり|その他の筆者: 和田垣謙三, 川瀬善太郎, 高松豊吉, 田中義成, 永井久一郎, 中村恭平, 山川健次郎, 松井直吉, 松村任三, 古在由直, 寺尾寿, 櫻井錠二, 清水彦五郎|巻子本|往来書簡貼付集|名録1冊(大和綴)を付す|落款朱印: 「讀經堂主人號随軒」, 「服部宇之吉印記」, 「直文」(平野直文)</t>
+          <t>写本|本文末に「貞永元年七月十日 沙弥浄圎/相模大掾藤原業時/玄蕃允三善康連/左衞門少尉藤原朝臣基綱/沙弥行然/散位三善朝臣倫重/加賀守三善朝臣康俊/沙弥行西/前出羽守藤原朝臣家長/前駿河守平義村/前攝津守中原師貟/武蔵守平泰時/相模守平時房」との連署名あり|巻末に「嘉禎三年八月十七日評定之」, 「延應二年五月廾五日評定之」, 「暦仁元年十二月十九日評定之」, 「延應元年九月廾日評定之改嫁事」, 「仁治三十二五評定」, 「嘉禎四年九月二十七日評定之」, 「仁治四二廾五追評定之」, 「延應二年五月廾五日評定之」, 「延應二四廾五評」など追加補抄及び「御式目事」(貞永元八月八日 武蔵守御判/するかの守殿)書簡抄を付す|奥書に「康永二年三月三日於高辻冨小路宿所書冩之訖」とあり|毎葉7行17字注文双行|本文は真字, 送り仮名, 返り点を施し|金砂子散し花菱繋ぎの見返し, 押界を施した楮紙打紙を使用|朱墨筆書き入れあり|軸物(打紙継ぎ)|桐箱入り|印記: 「本立堂記」|汚損, 虫損あり</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
@@ -11152,12 +11136,12 @@
       <c r="O87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/9639e5f3-92bd-7423-1bf1-08c4dc087bdf.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/1dc60eb8-0dd2-1716-521a-8b436e899759.json</t>
         </is>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>9639e5f3-92bd-7423-1bf1-08c4dc087bdf</t>
+          <t>1dc60eb8-0dd2-1716-521a-8b436e899759</t>
         </is>
       </c>
       <c r="R87" t="inlineStr">
@@ -11167,7 +11151,7 @@
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/9639e5f3-92bd-7423-1bf1-08c4dc087bdf</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/1dc60eb8-0dd2-1716-521a-8b436e899759</t>
         </is>
       </c>
       <c r="T87" t="inlineStr">
@@ -11177,12 +11161,12 @@
       </c>
       <c r="U87" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/b210fc9854d945b959acd96b0e4fa57d3578ea07.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/8182eba23e72331505a8074acdfe6b5481d358fd.jpg</t>
         </is>
       </c>
       <c r="V87" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296238</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296239</t>
         </is>
       </c>
       <c r="W87" t="inlineStr">
@@ -11205,7 +11189,7 @@
       <c r="AB87" t="inlineStr"/>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/9639e5f3-92bd-7423-1bf1-08c4dc087bdf/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/1dc60eb8-0dd2-1716-521a-8b436e899759/manifest</t>
         </is>
       </c>
       <c r="AD87" t="inlineStr"/>
@@ -11213,52 +11197,52 @@
       <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="inlineStr"/>
       <c r="AH87" t="n">
-        <v>27</v>
+        <v>45</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>御成敗式目</t>
+          <t>辨證配劑醫燈 3巻 [1]</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>A00:6456</t>
+          <t>A00:6517</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>ゴセイバイ シキモク</t>
+          <t>ベンショウ ハイザイ イトウ</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr">
         <is>
-          <t>平泰時 [ほか定]</t>
+          <t>曲直瀬 道三</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>[書写者不明]</t>
+          <t>道三 [自筆]</t>
         </is>
       </c>
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr">
         <is>
-          <t>康永2 [1343] 奥書</t>
+          <t>元亀2 [1571] 大尾</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr"/>
       <c r="L88" t="inlineStr">
         <is>
-          <t>写本|本文末に「貞永元年七月十日 沙弥浄圎/相模大掾藤原業時/玄蕃允三善康連/左衞門少尉藤原朝臣基綱/沙弥行然/散位三善朝臣倫重/加賀守三善朝臣康俊/沙弥行西/前出羽守藤原朝臣家長/前駿河守平義村/前攝津守中原師貟/武蔵守平泰時/相模守平時房」との連署名あり|巻末に「嘉禎三年八月十七日評定之」, 「延應二年五月廾五日評定之」, 「暦仁元年十二月十九日評定之」, 「延應元年九月廾日評定之改嫁事」, 「仁治三十二五評定」, 「嘉禎四年九月二十七日評定之」, 「仁治四二廾五追評定之」, 「延應二年五月廾五日評定之」, 「延應二四廾五評」など追加補抄及び「御式目事」(貞永元八月八日 武蔵守御判/するかの守殿)書簡抄を付す|奥書に「康永二年三月三日於高辻冨小路宿所書冩之訖」とあり|毎葉7行17字注文双行|本文は真字, 送り仮名, 返り点を施し|金砂子散し花菱繋ぎの見返し, 押界を施した楮紙打紙を使用|朱墨筆書き入れあり|軸物(打紙継ぎ)|桐箱入り|印記: 「本立堂記」|汚損, 虫損あり</t>
+          <t>写本|巻之2の巻頭書名: 辨證配剤醫燈|大尾に「治病用藥之時欲使侄姪孫一覧如指掌而已/旹元亀第二辛未年冬日南至六十五齢老眼寒窓/日東洛下雖知苦斎盍静翁 道三」とあり|巻末識語に「辨證配劑醫燈全三册壹帙一溪叟道三所親筆也不可忽諸故附一語於後耳」とあり|箱に「和氣道三自書寫配劑醫燈三卷林道春跋之櫻井老人苐一家藏子孫永寶之 葛辰識」との墨書あり|毎半面11行|朱点, 朱引, 朱藍筆書き入れあり|付箋あり|箱入り|印記: 「石堂」, 「昃印」|虫損, 汚損あり</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
@@ -11274,12 +11258,12 @@
       <c r="O88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/1dc60eb8-0dd2-1716-521a-8b436e899759.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/ede81088-3a4b-221d-711c-889d446e8d7e.json</t>
         </is>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>1dc60eb8-0dd2-1716-521a-8b436e899759</t>
+          <t>ede81088-3a4b-221d-711c-889d446e8d7e</t>
         </is>
       </c>
       <c r="R88" t="inlineStr">
@@ -11289,7 +11273,7 @@
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/1dc60eb8-0dd2-1716-521a-8b436e899759</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/ede81088-3a4b-221d-711c-889d446e8d7e</t>
         </is>
       </c>
       <c r="T88" t="inlineStr">
@@ -11299,12 +11283,12 @@
       </c>
       <c r="U88" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/8182eba23e72331505a8074acdfe6b5481d358fd.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/1089675f22f8a9e5e8d856bf42c0b3fa7e2b5168.jpg</t>
         </is>
       </c>
       <c r="V88" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296239</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296240</t>
         </is>
       </c>
       <c r="W88" t="inlineStr">
@@ -11327,7 +11311,7 @@
       <c r="AB88" t="inlineStr"/>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/1dc60eb8-0dd2-1716-521a-8b436e899759/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/ede81088-3a4b-221d-711c-889d446e8d7e/manifest</t>
         </is>
       </c>
       <c r="AD88" t="inlineStr"/>
@@ -11335,13 +11319,13 @@
       <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="inlineStr"/>
       <c r="AH88" t="n">
-        <v>45</v>
+        <v>61</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>辨證配劑醫燈 3巻 [1]</t>
+          <t>辨證配劑醫燈 3巻 [2]</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -11396,12 +11380,12 @@
       <c r="O89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/ede81088-3a4b-221d-711c-889d446e8d7e.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/93511b52-3de6-4102-980b-24d00b6c5851.json</t>
         </is>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>ede81088-3a4b-221d-711c-889d446e8d7e</t>
+          <t>93511b52-3de6-4102-980b-24d00b6c5851</t>
         </is>
       </c>
       <c r="R89" t="inlineStr">
@@ -11411,7 +11395,7 @@
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/ede81088-3a4b-221d-711c-889d446e8d7e</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/93511b52-3de6-4102-980b-24d00b6c5851</t>
         </is>
       </c>
       <c r="T89" t="inlineStr">
@@ -11421,12 +11405,12 @@
       </c>
       <c r="U89" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/1089675f22f8a9e5e8d856bf42c0b3fa7e2b5168.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/a82992bab1da44c99dc71e9ac8ef6ff3d626dc4d.jpg</t>
         </is>
       </c>
       <c r="V89" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296240</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296241</t>
         </is>
       </c>
       <c r="W89" t="inlineStr">
@@ -11449,7 +11433,7 @@
       <c r="AB89" t="inlineStr"/>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/ede81088-3a4b-221d-711c-889d446e8d7e/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/93511b52-3de6-4102-980b-24d00b6c5851/manifest</t>
         </is>
       </c>
       <c r="AD89" t="inlineStr"/>
@@ -11457,13 +11441,13 @@
       <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="inlineStr"/>
       <c r="AH89" t="n">
-        <v>61</v>
+        <v>52</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>辨證配劑醫燈 3巻 [2]</t>
+          <t>辨證配劑醫燈 3巻 [3]</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -11518,12 +11502,12 @@
       <c r="O90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/93511b52-3de6-4102-980b-24d00b6c5851.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/a23dae2e-701a-8d7c-1359-fe786c2e2cdd.json</t>
         </is>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>93511b52-3de6-4102-980b-24d00b6c5851</t>
+          <t>a23dae2e-701a-8d7c-1359-fe786c2e2cdd</t>
         </is>
       </c>
       <c r="R90" t="inlineStr">
@@ -11533,7 +11517,7 @@
       </c>
       <c r="S90" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/93511b52-3de6-4102-980b-24d00b6c5851</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/a23dae2e-701a-8d7c-1359-fe786c2e2cdd</t>
         </is>
       </c>
       <c r="T90" t="inlineStr">
@@ -11543,12 +11527,12 @@
       </c>
       <c r="U90" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/a82992bab1da44c99dc71e9ac8ef6ff3d626dc4d.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/21b02bac7c065db97c214037acfa4b232d2ddc89.jpg</t>
         </is>
       </c>
       <c r="V90" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296241</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296242</t>
         </is>
       </c>
       <c r="W90" t="inlineStr">
@@ -11571,7 +11555,7 @@
       <c r="AB90" t="inlineStr"/>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/93511b52-3de6-4102-980b-24d00b6c5851/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/a23dae2e-701a-8d7c-1359-fe786c2e2cdd/manifest</t>
         </is>
       </c>
       <c r="AD90" t="inlineStr"/>
@@ -11579,52 +11563,64 @@
       <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="inlineStr"/>
       <c r="AH90" t="n">
-        <v>52</v>
+        <v>63</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>辨證配劑醫燈 3巻 [3]</t>
+          <t>中野蒐集佛教并三教及各部繪入板本目録</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>A00:6517</t>
+          <t>C40:4254</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>ベンショウ ハイザイ イトウ</t>
+          <t>ナカノ シュウシュウ ブッキョウ ナラビニ サンキョウ オヨビ カクブ</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
-          <t>曲直瀬 道三</t>
+          <t>中野 達慧</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>道三 [自筆]</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr"/>
+          <t>東京帝国大学附属図書館</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>1926</t>
+        </is>
+      </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>元亀2 [1571] 大尾</t>
+          <t>大正15/明治元</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>写本</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>25cm</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>写本|巻之2の巻頭書名: 辨證配剤醫燈|大尾に「治病用藥之時欲使侄姪孫一覧如指掌而已/旹元亀第二辛未年冬日南至六十五齢老眼寒窓/日東洛下雖知苦斎盍静翁 道三」とあり|巻末識語に「辨證配劑醫燈全三册壹帙一溪叟道三所親筆也不可忽諸故附一語於後耳」とあり|箱に「和氣道三自書寫配劑醫燈三卷林道春跋之櫻井老人苐一家藏子孫永寶之 葛辰識」との墨書あり|毎半面11行|朱点, 朱引, 朱藍筆書き入れあり|付箋あり|箱入り|印記: 「石堂」, 「昃印」|虫損, 汚損あり</t>
+          <t>著者の自筆稿本|付:受入れ関係資料(袋入)</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -11640,12 +11636,12 @@
       <c r="O91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/a23dae2e-701a-8d7c-1359-fe786c2e2cdd.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/fbf26de6-88d7-86db-7a3f-79a446c00445.json</t>
         </is>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>a23dae2e-701a-8d7c-1359-fe786c2e2cdd</t>
+          <t>fbf26de6-88d7-86db-7a3f-79a446c00445</t>
         </is>
       </c>
       <c r="R91" t="inlineStr">
@@ -11655,7 +11651,7 @@
       </c>
       <c r="S91" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/a23dae2e-701a-8d7c-1359-fe786c2e2cdd</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/fbf26de6-88d7-86db-7a3f-79a446c00445</t>
         </is>
       </c>
       <c r="T91" t="inlineStr">
@@ -11665,12 +11661,12 @@
       </c>
       <c r="U91" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/21b02bac7c065db97c214037acfa4b232d2ddc89.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/010f8afb8aff57fed034d4d865411b48ec03a3bd.jpg</t>
         </is>
       </c>
       <c r="V91" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1296242</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1361385</t>
         </is>
       </c>
       <c r="W91" t="inlineStr">
@@ -11693,7 +11689,7 @@
       <c r="AB91" t="inlineStr"/>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/a23dae2e-701a-8d7c-1359-fe786c2e2cdd/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/fbf26de6-88d7-86db-7a3f-79a446c00445/manifest</t>
         </is>
       </c>
       <c r="AD91" t="inlineStr"/>
@@ -11701,44 +11697,48 @@
       <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="inlineStr"/>
       <c r="AH91" t="n">
-        <v>63</v>
+        <v>123</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>中野蒐集佛教并三教及各部繪入板本目録</t>
+          <t>供様圖式</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>C40:4254</t>
+          <t>JG:32</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>ナカノ シュウシュウ ブッキョウ ナラビニ サンキョウ オヨビ カクブ</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr"/>
+          <t>クヨウ ズシキ</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>供様図式</t>
+        </is>
+      </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>中野 達慧</t>
+          <t>四辻 公韶</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>東京帝国大学附属図書館</t>
+          <t>藤原公韶</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>1926</t>
+          <t>1687</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>大正15/明治元</t>
+          <t>貞享4</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -11753,12 +11753,12 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>25cm</t>
+          <t>35.7cm</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>著者の自筆稿本|付:受入れ関係資料(袋入)</t>
+          <t>書名は題簽による|巻末に「貞享四年丁卯十一月一日忌火御飯十七日解齋御粥/左中将 (花押)写」とあり|奥書に「右圖式従園頭中将基勝朝臣/令借本写之畢/貞享四年十一月廿一日左中将 (花押) (「藤原公韶」の朱方印あり)」とあり|彩色あり|印記: 「野宮藏書」</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -11768,18 +11768,18 @@
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>図書</t>
+          <t>和古書</t>
         </is>
       </c>
       <c r="O92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/fbf26de6-88d7-86db-7a3f-79a446c00445.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/f13b4435-13f6-1620-6ff9-c29077111174.json</t>
         </is>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>fbf26de6-88d7-86db-7a3f-79a446c00445</t>
+          <t>f13b4435-13f6-1620-6ff9-c29077111174</t>
         </is>
       </c>
       <c r="R92" t="inlineStr">
@@ -11789,7 +11789,7 @@
       </c>
       <c r="S92" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/fbf26de6-88d7-86db-7a3f-79a446c00445</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/f13b4435-13f6-1620-6ff9-c29077111174</t>
         </is>
       </c>
       <c r="T92" t="inlineStr">
@@ -11799,12 +11799,12 @@
       </c>
       <c r="U92" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/010f8afb8aff57fed034d4d865411b48ec03a3bd.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/a1afc99196840b0659140d1885787a328f681db0.jpg</t>
         </is>
       </c>
       <c r="V92" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1361385</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1361386</t>
         </is>
       </c>
       <c r="W92" t="inlineStr">
@@ -11814,7 +11814,7 @@
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
+          <t>http://iiif.io/api/presentation/3#rightToLeftDirection</t>
         </is>
       </c>
       <c r="Y92" t="inlineStr"/>
@@ -11827,7 +11827,7 @@
       <c r="AB92" t="inlineStr"/>
       <c r="AC92" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/fbf26de6-88d7-86db-7a3f-79a446c00445/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/f13b4435-13f6-1620-6ff9-c29077111174/manifest</t>
         </is>
       </c>
       <c r="AD92" t="inlineStr"/>
@@ -11835,48 +11835,44 @@
       <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="inlineStr"/>
       <c r="AH92" t="n">
-        <v>123</v>
+        <v>11</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>供様圖式</t>
+          <t>大嘗會調進物</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>JG:32</t>
+          <t>A00:6277</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>クヨウ ズシキ</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>供様図式</t>
-        </is>
-      </c>
+          <t>ダイジョウエ チョウシンモノ</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr">
         <is>
-          <t>四辻 公韶</t>
+          <t>不明</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>藤原公韶</t>
+          <t>[大藏省木工寮] [写]</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>1687</t>
+          <t>不明</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>貞享4</t>
+          <t>[明治期]</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -11891,12 +11887,12 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>35.7cm</t>
+          <t>28cm</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>書名は題簽による|巻末に「貞享四年丁卯十一月一日忌火御飯十七日解齋御粥/左中将 (花押)写」とあり|奥書に「右圖式従園頭中将基勝朝臣/令借本写之畢/貞享四年十一月廿一日左中将 (花押) (「藤原公韶」の朱方印あり)」とあり|彩色あり|印記: 「野宮藏書」</t>
+          <t>巻頭の識語に「嘉永元戊申年八月廿九日 官局江差出但奉行ヨリ沙汰ニ依而也官務江茂白画圖一板写被頼差出也 此當家写尤薄彩色夲紙者」との朱書あり|巻末に「大藏省木工寮」とあり|絵巻|彩色あり</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
@@ -11912,12 +11908,12 @@
       <c r="O93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/f13b4435-13f6-1620-6ff9-c29077111174.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/ff7901b5-7742-4d37-2621-ae0261c41dab.json</t>
         </is>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>f13b4435-13f6-1620-6ff9-c29077111174</t>
+          <t>ff7901b5-7742-4d37-2621-ae0261c41dab</t>
         </is>
       </c>
       <c r="R93" t="inlineStr">
@@ -11927,7 +11923,7 @@
       </c>
       <c r="S93" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/f13b4435-13f6-1620-6ff9-c29077111174</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/ff7901b5-7742-4d37-2621-ae0261c41dab</t>
         </is>
       </c>
       <c r="T93" t="inlineStr">
@@ -11937,12 +11933,12 @@
       </c>
       <c r="U93" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/a1afc99196840b0659140d1885787a328f681db0.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/426a2bea95a12ba2001d09cb79c81cf5c5db1129.jpg</t>
         </is>
       </c>
       <c r="V93" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1361386</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1361387</t>
         </is>
       </c>
       <c r="W93" t="inlineStr">
@@ -11952,7 +11948,7 @@
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>http://iiif.io/api/presentation/3#rightToLeftDirection</t>
+          <t>http://iiif.io/api/presentation/4#rightToLeftDirection</t>
         </is>
       </c>
       <c r="Y93" t="inlineStr"/>
@@ -11965,7 +11961,7 @@
       <c r="AB93" t="inlineStr"/>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/f13b4435-13f6-1620-6ff9-c29077111174/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/ff7901b5-7742-4d37-2621-ae0261c41dab/manifest</t>
         </is>
       </c>
       <c r="AD93" t="inlineStr"/>
@@ -11973,26 +11969,30 @@
       <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="inlineStr"/>
       <c r="AH93" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>大嘗會調進物</t>
+          <t>大嘗會悠紀主基鮮味之繪</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>A00:6277</t>
+          <t>A00:6108</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>ダイジョウエ チョウシンモノ</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr"/>
+          <t>ダイジョウエ ユキ スキ センミ ノ ズ</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>悠紀主基鮮味之啚, 元文悠紀主基鮮味之圖</t>
+        </is>
+      </c>
       <c r="E94" t="inlineStr">
         <is>
           <t>不明</t>
@@ -12000,17 +12000,17 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>[大藏省木工寮] [写]</t>
+          <t>[佐伯]</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>不明</t>
+          <t>1764</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>[明治期]</t>
+          <t>明和元</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -12025,12 +12025,12 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>28cm</t>
+          <t>40×165cm</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>巻頭の識語に「嘉永元戊申年八月廿九日 官局江差出但奉行ヨリ沙汰ニ依而也官務江茂白画圖一板写被頼差出也 此當家写尤薄彩色夲紙者」との朱書あり|巻末に「大藏省木工寮」とあり|絵巻|彩色あり</t>
+          <t>絵巻|書名は識語による|書袋の書名: 悠紀主基鮮味之啚|表紙裏に「元文悠紀主基鮮味之圖 寛延同」とあり|巻末の識語に「右大嘗會悠紀主基鮮味之繪借請御厨子所預紀宗直朝臣令佐伯職房摸冩之畢 明和元年孟冬左少将藤原(花押)」とあり|絵4幅: 梅作枝, 糸作枩, 萩作枝, 萩作枝|紙本著色|彩色あり|帙入り|印記: 「野宮藏書」</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -12046,12 +12046,12 @@
       <c r="O94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/ff7901b5-7742-4d37-2621-ae0261c41dab.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/503a9098-4443-20f7-2ef1-cebc95096a74.json</t>
         </is>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>ff7901b5-7742-4d37-2621-ae0261c41dab</t>
+          <t>503a9098-4443-20f7-2ef1-cebc95096a74</t>
         </is>
       </c>
       <c r="R94" t="inlineStr">
@@ -12061,7 +12061,7 @@
       </c>
       <c r="S94" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/ff7901b5-7742-4d37-2621-ae0261c41dab</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/503a9098-4443-20f7-2ef1-cebc95096a74</t>
         </is>
       </c>
       <c r="T94" t="inlineStr">
@@ -12071,12 +12071,12 @@
       </c>
       <c r="U94" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/426a2bea95a12ba2001d09cb79c81cf5c5db1129.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/2a7f21a6103a0653e35f8e5fada19af4c1a6d7bd.jpg</t>
         </is>
       </c>
       <c r="V94" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1361387</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1361388</t>
         </is>
       </c>
       <c r="W94" t="inlineStr">
@@ -12086,7 +12086,7 @@
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>http://iiif.io/api/presentation/4#rightToLeftDirection</t>
+          <t>http://iiif.io/api/presentation/5#rightToLeftDirection</t>
         </is>
       </c>
       <c r="Y94" t="inlineStr"/>
@@ -12099,7 +12099,7 @@
       <c r="AB94" t="inlineStr"/>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/ff7901b5-7742-4d37-2621-ae0261c41dab/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/503a9098-4443-20f7-2ef1-cebc95096a74/manifest</t>
         </is>
       </c>
       <c r="AD94" t="inlineStr"/>
@@ -12107,30 +12107,26 @@
       <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="inlineStr"/>
       <c r="AH94" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>大嘗會悠紀主基鮮味之繪</t>
+          <t>御産部類</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>A00:6108</t>
+          <t>G27:828</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>ダイジョウエ ユキ スキ センミ ノ ズ</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>悠紀主基鮮味之啚, 元文悠紀主基鮮味之圖</t>
-        </is>
-      </c>
+          <t>オサン ブルイ</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr">
         <is>
           <t>不明</t>
@@ -12138,17 +12134,17 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>[佐伯]</t>
+          <t>[書写者不明]</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>1764</t>
+          <t>1752</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>明和元</t>
+          <t>寳暦2</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -12163,12 +12159,12 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>40×165cm</t>
+          <t>30cm</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>絵巻|書名は識語による|書袋の書名: 悠紀主基鮮味之啚|表紙裏に「元文悠紀主基鮮味之圖 寛延同」とあり|巻末の識語に「右大嘗會悠紀主基鮮味之繪借請御厨子所預紀宗直朝臣令佐伯職房摸冩之畢 明和元年孟冬左少将藤原(花押)」とあり|絵4幅: 梅作枝, 糸作枩, 萩作枝, 萩作枝|紙本著色|彩色あり|帙入り|印記: 「野宮藏書」</t>
+          <t>書名は表紙による|原奥書に「借請宰相中将定基卿本惟通卿書冩畢 寳永年正月廿四日 内大臣(花押)」とあり|奥書に「借請件奥書本於源前内府(通兄公)令書冩了 寳暦第二ノ季冬正三位□□(花押)」とあり|仮綴|朱墨書き入れあり(巻末に「宝暦二季冬一校了 愚然」と朱書あり)|虫損あり</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -12184,12 +12180,12 @@
       <c r="O95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/503a9098-4443-20f7-2ef1-cebc95096a74.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/519a0a21-28fc-86f1-91be-61b0c5c84d94.json</t>
         </is>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>503a9098-4443-20f7-2ef1-cebc95096a74</t>
+          <t>519a0a21-28fc-86f1-91be-61b0c5c84d94</t>
         </is>
       </c>
       <c r="R95" t="inlineStr">
@@ -12199,7 +12195,7 @@
       </c>
       <c r="S95" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/503a9098-4443-20f7-2ef1-cebc95096a74</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/519a0a21-28fc-86f1-91be-61b0c5c84d94</t>
         </is>
       </c>
       <c r="T95" t="inlineStr">
@@ -12209,12 +12205,12 @@
       </c>
       <c r="U95" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/2a7f21a6103a0653e35f8e5fada19af4c1a6d7bd.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/4d8113679682e972cf5c37311b94bb304455bbe2.jpg</t>
         </is>
       </c>
       <c r="V95" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1361388</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1361389</t>
         </is>
       </c>
       <c r="W95" t="inlineStr">
@@ -12224,7 +12220,7 @@
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>http://iiif.io/api/presentation/5#rightToLeftDirection</t>
+          <t>http://iiif.io/api/presentation/6#rightToLeftDirection</t>
         </is>
       </c>
       <c r="Y95" t="inlineStr"/>
@@ -12237,7 +12233,7 @@
       <c r="AB95" t="inlineStr"/>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/503a9098-4443-20f7-2ef1-cebc95096a74/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/519a0a21-28fc-86f1-91be-61b0c5c84d94/manifest</t>
         </is>
       </c>
       <c r="AD95" t="inlineStr"/>
@@ -12245,44 +12241,48 @@
       <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="inlineStr"/>
       <c r="AH95" t="n">
-        <v>11</v>
+        <v>74</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>御産部類</t>
+          <t>中御門大納言宣順卿記</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>G27:828</t>
+          <t>G27:165</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>オサン ブルイ</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr"/>
+          <t>ナカミカド ダイナゴン ノブヨリ キョウ キ</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>宣順卿記, 承應二年中御門大納言宣順卿記</t>
+        </is>
+      </c>
       <c r="E96" t="inlineStr">
         <is>
+          <t>中御門 宣順</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>[書写者不明]</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
           <t>不明</t>
         </is>
       </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>[書写者不明]</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>1752</t>
-        </is>
-      </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>寳暦2</t>
+          <t>[書写年不明]</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -12297,12 +12297,12 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>30cm</t>
+          <t>28cm</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>書名は表紙による|原奥書に「借請宰相中将定基卿本惟通卿書冩畢 寳永年正月廿四日 内大臣(花押)」とあり|奥書に「借請件奥書本於源前内府(通兄公)令書冩了 寳暦第二ノ季冬正三位□□(花押)」とあり|仮綴|朱墨書き入れあり(巻末に「宝暦二季冬一校了 愚然」と朱書あり)|虫損あり</t>
+          <t>書名及び巻次は表紙による|3: 承應二年|印記: 「和學講談所」,「温故堂文庫」,「渡部文庫珍藏書印」|虫損あり</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -12315,15 +12315,19 @@
           <t>和古書</t>
         </is>
       </c>
-      <c r="O96" t="inlineStr"/>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>渡部文庫</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/519a0a21-28fc-86f1-91be-61b0c5c84d94.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/dc4aa20b-25b3-1976-505d-c313483199ba.json</t>
         </is>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>519a0a21-28fc-86f1-91be-61b0c5c84d94</t>
+          <t>dc4aa20b-25b3-1976-505d-c313483199ba</t>
         </is>
       </c>
       <c r="R96" t="inlineStr">
@@ -12333,7 +12337,7 @@
       </c>
       <c r="S96" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/519a0a21-28fc-86f1-91be-61b0c5c84d94</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/dc4aa20b-25b3-1976-505d-c313483199ba</t>
         </is>
       </c>
       <c r="T96" t="inlineStr">
@@ -12343,12 +12347,12 @@
       </c>
       <c r="U96" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/4d8113679682e972cf5c37311b94bb304455bbe2.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/4184c533168fcea03213cc03858c46672c2f3b30.jpg</t>
         </is>
       </c>
       <c r="V96" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1361389</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1361390</t>
         </is>
       </c>
       <c r="W96" t="inlineStr">
@@ -12358,7 +12362,7 @@
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>http://iiif.io/api/presentation/6#rightToLeftDirection</t>
+          <t>http://iiif.io/api/presentation/7#rightToLeftDirection</t>
         </is>
       </c>
       <c r="Y96" t="inlineStr"/>
@@ -12371,7 +12375,7 @@
       <c r="AB96" t="inlineStr"/>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/519a0a21-28fc-86f1-91be-61b0c5c84d94/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/dc4aa20b-25b3-1976-505d-c313483199ba/manifest</t>
         </is>
       </c>
       <c r="AD96" t="inlineStr"/>
@@ -12379,48 +12383,48 @@
       <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="inlineStr"/>
       <c r="AH96" t="n">
-        <v>74</v>
+        <v>39</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>中御門大納言宣順卿記</t>
+          <t>拜賀部類記別勘</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>G27:165</t>
+          <t>G26:1050</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>ナカミカド ダイナゴン ノブヨリ キョウ キ</t>
+          <t>ハイガ ブルイキ ベッカン</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>宣順卿記, 承應二年中御門大納言宣順卿記</t>
+          <t>拜賀部類別勘 : 當家之記, 拜賀部類 : 秘記</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>中御門 宣順</t>
+          <t>中院 通茂</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>[書写者不明]</t>
+          <t>藤實岑 [写]</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>不明</t>
+          <t>1711</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>[書写年不明]</t>
+          <t>寳永8</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -12440,7 +12444,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>書名及び巻次は表紙による|3: 承應二年|印記: 「和學講談所」,「温故堂文庫」,「渡部文庫珍藏書印」|虫損あり</t>
+          <t>扉の書名: 拜賀部類別勘 : 當家之記|表紙の書名: 拜賀部類 : 秘記|奥書に「此一冊中院家拜賀記也(前内大臣通茂公自筆)其作法等三條西家諷諌事多且三條西家有作法事故請求通躬卿之処則被免仍摸冩加一校子孫之外努々不可許他見矣 于時寳永八稔孟夏上旬 羽林郎藤實岑」とあり|仮綴|付箋あり|虫損あり</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
@@ -12453,19 +12457,15 @@
           <t>和古書</t>
         </is>
       </c>
-      <c r="O97" t="inlineStr">
-        <is>
-          <t>渡部文庫</t>
-        </is>
-      </c>
+      <c r="O97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/dc4aa20b-25b3-1976-505d-c313483199ba.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/479b057d-7d61-0db0-0a50-9c798826783f.json</t>
         </is>
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>dc4aa20b-25b3-1976-505d-c313483199ba</t>
+          <t>479b057d-7d61-0db0-0a50-9c798826783f</t>
         </is>
       </c>
       <c r="R97" t="inlineStr">
@@ -12475,7 +12475,7 @@
       </c>
       <c r="S97" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/dc4aa20b-25b3-1976-505d-c313483199ba</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/479b057d-7d61-0db0-0a50-9c798826783f</t>
         </is>
       </c>
       <c r="T97" t="inlineStr">
@@ -12485,12 +12485,12 @@
       </c>
       <c r="U97" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/4184c533168fcea03213cc03858c46672c2f3b30.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/f7ec09b951da91d218e076889f2c1f75f429b846.jpg</t>
         </is>
       </c>
       <c r="V97" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1361390</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1361391</t>
         </is>
       </c>
       <c r="W97" t="inlineStr">
@@ -12500,7 +12500,7 @@
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>http://iiif.io/api/presentation/7#rightToLeftDirection</t>
+          <t>http://iiif.io/api/presentation/8#rightToLeftDirection</t>
         </is>
       </c>
       <c r="Y97" t="inlineStr"/>
@@ -12513,7 +12513,7 @@
       <c r="AB97" t="inlineStr"/>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/dc4aa20b-25b3-1976-505d-c313483199ba/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/479b057d-7d61-0db0-0a50-9c798826783f/manifest</t>
         </is>
       </c>
       <c r="AD97" t="inlineStr"/>
@@ -12521,48 +12521,44 @@
       <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="inlineStr"/>
       <c r="AH97" t="n">
-        <v>39</v>
+        <v>60</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>拜賀部類記別勘</t>
+          <t>大嘗會部類 (存1巻)</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>G26:1050</t>
+          <t>G26:966</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>ハイガ ブルイキ ベッカン</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>拜賀部類別勘 : 當家之記, 拜賀部類 : 秘記</t>
-        </is>
-      </c>
+          <t>ダイジョウエ ブルイ</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr">
         <is>
-          <t>中院 通茂</t>
+          <t>不明</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>藤實岑 [写]</t>
+          <t>[書写者不明]</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>1711</t>
+          <t>不明</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>寳永8</t>
+          <t>[書写年不明]</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -12577,12 +12573,12 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>28cm</t>
+          <t>29cm</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>扉の書名: 拜賀部類別勘 : 當家之記|表紙の書名: 拜賀部類 : 秘記|奥書に「此一冊中院家拜賀記也(前内大臣通茂公自筆)其作法等三條西家諷諌事多且三條西家有作法事故請求通躬卿之処則被免仍摸冩加一校子孫之外努々不可許他見矣 于時寳永八稔孟夏上旬 羽林郎藤實岑」とあり|仮綴|付箋あり|虫損あり</t>
+          <t>書名及び巻次は表紙による|2を存す|仮綴|印記: 「野宮書印」|朱筆書き入れあり|虫損あり</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -12598,12 +12594,12 @@
       <c r="O98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/479b057d-7d61-0db0-0a50-9c798826783f.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/18bcd8ff-2df2-62ac-a685-fa22a8cb5a58.json</t>
         </is>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
-          <t>479b057d-7d61-0db0-0a50-9c798826783f</t>
+          <t>18bcd8ff-2df2-62ac-a685-fa22a8cb5a58</t>
         </is>
       </c>
       <c r="R98" t="inlineStr">
@@ -12613,7 +12609,7 @@
       </c>
       <c r="S98" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/479b057d-7d61-0db0-0a50-9c798826783f</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/18bcd8ff-2df2-62ac-a685-fa22a8cb5a58</t>
         </is>
       </c>
       <c r="T98" t="inlineStr">
@@ -12623,12 +12619,12 @@
       </c>
       <c r="U98" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/f7ec09b951da91d218e076889f2c1f75f429b846.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/17578c3efd5fd9990d9c44b722b4f881e0ba7231.jpg</t>
         </is>
       </c>
       <c r="V98" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1361391</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1361392</t>
         </is>
       </c>
       <c r="W98" t="inlineStr">
@@ -12638,7 +12634,7 @@
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>http://iiif.io/api/presentation/8#rightToLeftDirection</t>
+          <t>http://iiif.io/api/presentation/9#rightToLeftDirection</t>
         </is>
       </c>
       <c r="Y98" t="inlineStr"/>
@@ -12651,7 +12647,7 @@
       <c r="AB98" t="inlineStr"/>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/479b057d-7d61-0db0-0a50-9c798826783f/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/18bcd8ff-2df2-62ac-a685-fa22a8cb5a58/manifest</t>
         </is>
       </c>
       <c r="AD98" t="inlineStr"/>
@@ -12659,41 +12655,41 @@
       <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="inlineStr"/>
       <c r="AH98" t="n">
-        <v>60</v>
+        <v>53</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>大嘗會部類 (存1巻)</t>
+          <t>柱史抄 下</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>G26:966</t>
+          <t>G26:256</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>ダイジョウエ ブルイ</t>
+          <t>チュウシショウ ゲ</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr">
         <is>
+          <t>藤原 孝範</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>[書写者不明]</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
           <t>不明</t>
         </is>
       </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>[書写者不明]</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>不明</t>
-        </is>
-      </c>
       <c r="H99" t="inlineStr">
         <is>
           <t>[書写年不明]</t>
@@ -12701,7 +12697,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -12711,12 +12707,12 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>29cm</t>
+          <t>27cm</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>書名及び巻次は表紙による|2を存す|仮綴|印記: 「野宮書印」|朱筆書き入れあり|虫損あり</t>
+          <t>印記: 「華山藏書之印」,「渡部文庫珍藏書印」|朱筆書き入れあり|虫損あり</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -12729,15 +12725,19 @@
           <t>和古書</t>
         </is>
       </c>
-      <c r="O99" t="inlineStr"/>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>渡部文庫</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/18bcd8ff-2df2-62ac-a685-fa22a8cb5a58.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/e194f872-8917-1c7f-16f2-830299a79d87.json</t>
         </is>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>18bcd8ff-2df2-62ac-a685-fa22a8cb5a58</t>
+          <t>e194f872-8917-1c7f-16f2-830299a79d87</t>
         </is>
       </c>
       <c r="R99" t="inlineStr">
@@ -12747,7 +12747,7 @@
       </c>
       <c r="S99" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/18bcd8ff-2df2-62ac-a685-fa22a8cb5a58</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/e194f872-8917-1c7f-16f2-830299a79d87</t>
         </is>
       </c>
       <c r="T99" t="inlineStr">
@@ -12757,12 +12757,12 @@
       </c>
       <c r="U99" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/17578c3efd5fd9990d9c44b722b4f881e0ba7231.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/ca70042589e928d9afd6a23ff1e73ae42fd6cf37.jpg</t>
         </is>
       </c>
       <c r="V99" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1361392</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1361393</t>
         </is>
       </c>
       <c r="W99" t="inlineStr">
@@ -12772,7 +12772,7 @@
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>http://iiif.io/api/presentation/9#rightToLeftDirection</t>
+          <t>http://iiif.io/api/presentation/10#rightToLeftDirection</t>
         </is>
       </c>
       <c r="Y99" t="inlineStr"/>
@@ -12785,7 +12785,7 @@
       <c r="AB99" t="inlineStr"/>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/18bcd8ff-2df2-62ac-a685-fa22a8cb5a58/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/e194f872-8917-1c7f-16f2-830299a79d87/manifest</t>
         </is>
       </c>
       <c r="AD99" t="inlineStr"/>
@@ -12793,13 +12793,13 @@
       <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="inlineStr"/>
       <c r="AH99" t="n">
-        <v>53</v>
+        <v>44</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>柱史抄 下</t>
+          <t>柱史抄 上</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -12809,7 +12809,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>チュウシショウ ゲ</t>
+          <t>チュウシショウ ジョウ</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
@@ -12870,12 +12870,12 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/e194f872-8917-1c7f-16f2-830299a79d87.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/aa9e6c3f-0a12-47dc-9d5f-b6d7466a7e28.json</t>
         </is>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
-          <t>e194f872-8917-1c7f-16f2-830299a79d87</t>
+          <t>aa9e6c3f-0a12-47dc-9d5f-b6d7466a7e28</t>
         </is>
       </c>
       <c r="R100" t="inlineStr">
@@ -12885,7 +12885,7 @@
       </c>
       <c r="S100" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/e194f872-8917-1c7f-16f2-830299a79d87</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/aa9e6c3f-0a12-47dc-9d5f-b6d7466a7e28</t>
         </is>
       </c>
       <c r="T100" t="inlineStr">
@@ -12895,12 +12895,12 @@
       </c>
       <c r="U100" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/ca70042589e928d9afd6a23ff1e73ae42fd6cf37.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/92f6ce8da05d1ee555c30e2821d0d2ac3c24592c.jpg</t>
         </is>
       </c>
       <c r="V100" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1361393</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1361394</t>
         </is>
       </c>
       <c r="W100" t="inlineStr">
@@ -12910,7 +12910,7 @@
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>http://iiif.io/api/presentation/10#rightToLeftDirection</t>
+          <t>http://iiif.io/api/presentation/11#rightToLeftDirection</t>
         </is>
       </c>
       <c r="Y100" t="inlineStr"/>
@@ -12923,7 +12923,7 @@
       <c r="AB100" t="inlineStr"/>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/e194f872-8917-1c7f-16f2-830299a79d87/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/aa9e6c3f-0a12-47dc-9d5f-b6d7466a7e28/manifest</t>
         </is>
       </c>
       <c r="AD100" t="inlineStr"/>
@@ -12931,29 +12931,33 @@
       <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="inlineStr"/>
       <c r="AH100" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>柱史抄 上</t>
+          <t>蛙抄 8</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>G26:256</t>
+          <t>G26:45</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>チュウシショウ ジョウ</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr"/>
+          <t>アショウ 8</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>蛙鈔</t>
+        </is>
+      </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>藤原 孝範</t>
+          <t>洞院 実煕</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -12968,12 +12972,12 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>[書写年不明]</t>
+          <t>[江戸後期]</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -12983,12 +12987,12 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>27cm</t>
+          <t>28cm</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>印記: 「華山藏書之印」,「渡部文庫珍藏書印」|朱筆書き入れあり|虫損あり</t>
+          <t>書名及び巻次は題簽による|8の目首の書名: 蛙鈔|各奥書に「享和三年仲春一挍畢」(1-2)「享和三季春挍合畢」(3)「享和三年季春挍合畢」(4)「享和三年仲春一挍了」(5)「享和三年孟夏挍合畢」(6-7)「一挍畢」(8)とあり|頭注あり|1: 冠部, 剱部. 2: 袍部. 3-4: 下襲部. 5: 半臂, 袙, 表袴部. 6: 直衣部. 7: 打衣部. 8: 車輿部|印記: 「希賢亭圖書記」|1の扉裏に「經亮云蛙抄ハ三條家ニ秘藏セラレシ装束抄ナリ邂逅ニ袍部及車輿部ノ二冊ハ世ニ流布セリ今又下重部二冊半臂袙表袴部一冊直衣部一冊打衣部一冊以上八冊也此餘モアリトイヘトモイマタ知ラス半臂部ニ其事見小忌部トアルヲ見レハ小忌部ナドモアルベシ而シテ此抄ハ三條家ノモノトモミヘズ當家ト抄中ニアルハ洞院家ノコト也若疑ハ東山左府實凞公ナトノ手ニ出タリシニヤ可考事ナリ先年コノコトヲ瑜伽心院入道前権大納言紀光卿ニキコヱケレバサモアラント諾玉ヘリ」と朱書あり|朱筆書き入れあり|付箋あり|虫損あり</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -13001,19 +13005,15 @@
           <t>和古書</t>
         </is>
       </c>
-      <c r="O101" t="inlineStr">
-        <is>
-          <t>渡部文庫</t>
-        </is>
-      </c>
+      <c r="O101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/aa9e6c3f-0a12-47dc-9d5f-b6d7466a7e28.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/f7a2c50b-0c62-15a7-68c3-a0f0e8c52ca1.json</t>
         </is>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
-          <t>aa9e6c3f-0a12-47dc-9d5f-b6d7466a7e28</t>
+          <t>f7a2c50b-0c62-15a7-68c3-a0f0e8c52ca1</t>
         </is>
       </c>
       <c r="R101" t="inlineStr">
@@ -13023,7 +13023,7 @@
       </c>
       <c r="S101" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/aa9e6c3f-0a12-47dc-9d5f-b6d7466a7e28</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/f7a2c50b-0c62-15a7-68c3-a0f0e8c52ca1</t>
         </is>
       </c>
       <c r="T101" t="inlineStr">
@@ -13033,12 +13033,12 @@
       </c>
       <c r="U101" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/92f6ce8da05d1ee555c30e2821d0d2ac3c24592c.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/f342b349e1a772b70e534d7100a687e127ebd6b4.jpg</t>
         </is>
       </c>
       <c r="V101" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1361394</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1361395</t>
         </is>
       </c>
       <c r="W101" t="inlineStr">
@@ -13048,7 +13048,7 @@
       </c>
       <c r="X101" t="inlineStr">
         <is>
-          <t>http://iiif.io/api/presentation/11#rightToLeftDirection</t>
+          <t>http://iiif.io/api/presentation/12#rightToLeftDirection</t>
         </is>
       </c>
       <c r="Y101" t="inlineStr"/>
@@ -13061,7 +13061,7 @@
       <c r="AB101" t="inlineStr"/>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/aa9e6c3f-0a12-47dc-9d5f-b6d7466a7e28/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/f7a2c50b-0c62-15a7-68c3-a0f0e8c52ca1/manifest</t>
         </is>
       </c>
       <c r="AD101" t="inlineStr"/>
@@ -13069,13 +13069,13 @@
       <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="inlineStr"/>
       <c r="AH101" t="n">
-        <v>53</v>
+        <v>38</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>蛙抄 8</t>
+          <t>蛙抄 7</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -13085,7 +13085,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>アショウ 8</t>
+          <t>アショウ 7</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13146,12 +13146,12 @@
       <c r="O102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/f7a2c50b-0c62-15a7-68c3-a0f0e8c52ca1.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/4cb13342-3d2f-0027-2ad6-da984e2c3d6d.json</t>
         </is>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>f7a2c50b-0c62-15a7-68c3-a0f0e8c52ca1</t>
+          <t>4cb13342-3d2f-0027-2ad6-da984e2c3d6d</t>
         </is>
       </c>
       <c r="R102" t="inlineStr">
@@ -13161,7 +13161,7 @@
       </c>
       <c r="S102" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/f7a2c50b-0c62-15a7-68c3-a0f0e8c52ca1</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/4cb13342-3d2f-0027-2ad6-da984e2c3d6d</t>
         </is>
       </c>
       <c r="T102" t="inlineStr">
@@ -13171,12 +13171,12 @@
       </c>
       <c r="U102" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/f342b349e1a772b70e534d7100a687e127ebd6b4.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/b8c2cc84b66430038932deffec626f0f32a13959.jpg</t>
         </is>
       </c>
       <c r="V102" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1361395</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1361396</t>
         </is>
       </c>
       <c r="W102" t="inlineStr">
@@ -13186,7 +13186,7 @@
       </c>
       <c r="X102" t="inlineStr">
         <is>
-          <t>http://iiif.io/api/presentation/12#rightToLeftDirection</t>
+          <t>http://iiif.io/api/presentation/13#rightToLeftDirection</t>
         </is>
       </c>
       <c r="Y102" t="inlineStr"/>
@@ -13199,7 +13199,7 @@
       <c r="AB102" t="inlineStr"/>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/f7a2c50b-0c62-15a7-68c3-a0f0e8c52ca1/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/4cb13342-3d2f-0027-2ad6-da984e2c3d6d/manifest</t>
         </is>
       </c>
       <c r="AD102" t="inlineStr"/>
@@ -13207,13 +13207,13 @@
       <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="inlineStr"/>
       <c r="AH102" t="n">
-        <v>38</v>
+        <v>20</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>蛙抄 7</t>
+          <t>蛙抄 6</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -13223,7 +13223,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>アショウ 7</t>
+          <t>アショウ 6</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -13284,12 +13284,12 @@
       <c r="O103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/4cb13342-3d2f-0027-2ad6-da984e2c3d6d.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/d8791f0a-777b-386d-21e8-6da9b37f02c8.json</t>
         </is>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>4cb13342-3d2f-0027-2ad6-da984e2c3d6d</t>
+          <t>d8791f0a-777b-386d-21e8-6da9b37f02c8</t>
         </is>
       </c>
       <c r="R103" t="inlineStr">
@@ -13299,7 +13299,7 @@
       </c>
       <c r="S103" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/4cb13342-3d2f-0027-2ad6-da984e2c3d6d</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/koten/document/d8791f0a-777b-386d-21e8-6da9b37f02c8</t>
         </is>
       </c>
       <c r="T103" t="inlineStr">
@@ -13309,12 +13309,12 @@
       </c>
       <c r="U103" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/b8c2cc84b66430038932deffec626f0f32a13959.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/340e9027fa29b9e2e037e6b59373dd51d91924a8.jpg</t>
         </is>
       </c>
       <c r="V103" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1361396</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1361397</t>
         </is>
       </c>
       <c r="W103" t="inlineStr">
@@ -13324,7 +13324,7 @@
       </c>
       <c r="X103" t="inlineStr">
         <is>
-          <t>http://iiif.io/api/presentation/13#rightToLeftDirection</t>
+          <t>http://iiif.io/api/presentation/14#rightToLeftDirection</t>
         </is>
       </c>
       <c r="Y103" t="inlineStr"/>
@@ -13337,7 +13337,7 @@
       <c r="AB103" t="inlineStr"/>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/4cb13342-3d2f-0027-2ad6-da984e2c3d6d/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/d8791f0a-777b-386d-21e8-6da9b37f02c8/manifest</t>
         </is>
       </c>
       <c r="AD103" t="inlineStr"/>
@@ -13345,7 +13345,7 @@
       <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="inlineStr"/>
       <c r="AH103" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="104">
